--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R5fbb048e441f4596"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Ra3e1101e2eac4045"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R223e66e6fb724b88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R2486a64db6284474"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Ra200e32d1a904c4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rfe4a095bea01414a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R8b13e6d5bb8c450b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rdd4093ae2b4f4078"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R97459e44b4534c7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R14cc543c2d0b4973"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R7790dbc62de644e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R046ed2fbaaef4304"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R8573fe1a4d684450"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb7a5b573dea048ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R99f70fcbf0544d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rfc9fec22444b442f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -214,7 +214,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="63">
+  <x:cellXfs count="65">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -356,6 +356,12 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -711,35 +717,31 @@
       </x:c>
       <x:c r="H5" s="44" t="str"/>
       <x:c r="I5" s="44" t="str">
-        <x:v>当前原型</x:v>
+        <x:v>当前3D原型</x:v>
       </x:c>
       <x:c r="J5" s="44" t="str">
-        <x:v>胶囊防护体 v001</x:v>
+        <x:v>基地 + 四主题副本 + 独立靶场</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="45" t="n">
-        <x:f>COUNTA('资产主表'!$A$6:$A$200)</x:f>
-        <x:v>107</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B6" s="43"/>
       <x:c r="C6" s="45" t="n">
-        <x:f>COUNTIF('资产主表'!$K$6:$K$200,"已完成")+COUNTIF('资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>7</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
-        <x:f>COUNTIF('资产主表'!$K$6:$K$200,"待制作")+COUNTIF('资产主表'!$K$6:$K$200,"程序占位")</x:f>
         <x:v>99</x:v>
       </x:c>
       <x:c r="F6" s="43"/>
       <x:c r="G6" s="45" t="n">
-        <x:f>COUNTIF('资产主表'!$S$6:$S$200,"重复")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="43"/>
       <x:c r="I6" s="46" t="str">
-        <x:v>侧面 / 无腿 / 单手随向镜像 / 独立红围巾</x:v>
+        <x:v>全3D闭环 / 三档房间 / 七类怪 / 56枪弹组合 / 废土灯池</x:v>
       </x:c>
       <x:c r="J6" s="46"/>
     </x:row>
@@ -793,11 +795,11 @@
       </x:c>
       <x:c r="B10" s="50" t="n">
         <x:f>COUNTIF('资产主表'!$C$6:$C$200,A10)</x:f>
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C10" s="50" t="n">
         <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A10,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A10,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D10" s="43"/>
       <x:c r="E10" s="51" t="str">
@@ -818,12 +820,10 @@
         <x:v>敌人</x:v>
       </x:c>
       <x:c r="B11" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A11)</x:f>
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A11,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A11,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D11" s="43"/>
       <x:c r="E11" s="51" t="str">
@@ -844,12 +844,10 @@
         <x:v>枪械</x:v>
       </x:c>
       <x:c r="B12" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A12)</x:f>
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A12,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A12,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D12" s="43"/>
       <x:c r="E12" s="51" t="str">
@@ -870,11 +868,9 @@
         <x:v>道具</x:v>
       </x:c>
       <x:c r="B13" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A13)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="C13" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A13,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A13,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="43"/>
@@ -882,10 +878,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F13" s="52" t="str">
-        <x:v>角色先拆 head/body/hand/accessory；按设计决定是否需要第二只手</x:v>
+        <x:v>3D房间/家具/枪械/怪物/灯具先查共用根与尺寸类</x:v>
       </x:c>
       <x:c r="G13" s="52" t="str">
-        <x:v>枪械和 UI 也按挂点/组件拆分</x:v>
+        <x:v>主题差异进入资源或配置，禁止复制关卡局部目录</x:v>
       </x:c>
       <x:c r="H13" s="43"/>
       <x:c r="I13" s="43"/>
@@ -896,12 +892,10 @@
         <x:v>场景</x:v>
       </x:c>
       <x:c r="B14" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A14)</x:f>
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A14,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A14,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D14" s="43"/>
       <x:c r="E14" s="51" t="str">
@@ -922,12 +916,10 @@
         <x:v>场景道具</x:v>
       </x:c>
       <x:c r="B15" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A15)</x:f>
-        <x:v>10</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C15" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A15,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A15,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="43"/>
       <x:c r="E15" s="43"/>
@@ -942,11 +934,9 @@
         <x:v>UI</x:v>
       </x:c>
       <x:c r="B16" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A16)</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A16,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A16,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="43"/>
@@ -962,12 +952,10 @@
         <x:v>特效</x:v>
       </x:c>
       <x:c r="B17" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A17)</x:f>
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A17,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A17,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D17" s="43"/>
       <x:c r="E17" s="43"/>
@@ -982,11 +970,9 @@
         <x:v>音频</x:v>
       </x:c>
       <x:c r="B18" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A18)</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="C18" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A18,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A18,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D18" s="43"/>
@@ -1273,7 +1259,7 @@
         <x:v>角色|player|player_capsule01|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S6" s="36" t="str">
-        <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$112,R6)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$139,R6)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T6" s="36" t="str"/>
@@ -1347,7 +1333,7 @@
         <x:v>角色|player_component|player_capsule01|head|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S7" s="37" t="str">
-        <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$112,R7)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$139,R7)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T7" s="37" t="str">
@@ -1423,7 +1409,7 @@
         <x:v>角色|player_component|player_capsule01|body|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S8" s="37" t="str">
-        <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$112,R8)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$139,R8)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T8" s="37" t="str">
@@ -1499,7 +1485,7 @@
         <x:v>角色|player_component|player_capsule01|hand_l_source|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S9" s="37" t="str">
-        <x:f>IF(A9="","",IF(COUNTIF($R$6:$R$112,R9)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A9="","",IF(COUNTIF($R$6:$R$139,R9)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T9" s="37" t="str">
@@ -1575,7 +1561,7 @@
         <x:v>角色|player_component|player_capsule01|hand|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S10" s="37" t="str">
-        <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$112,R10)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$139,R10)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T10" s="37" t="str">
@@ -1651,7 +1637,7 @@
         <x:v>角色|player_accessory|player_capsule01|scarf|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S11" s="37" t="str">
-        <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$112,R11)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$139,R11)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T11" s="37" t="str">
@@ -1727,7 +1713,7 @@
         <x:v>角色|review_board|player_capsule01|preview|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S12" s="37" t="str">
-        <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$112,R12)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$139,R12)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T12" s="37" t="str"/>
@@ -1795,7 +1781,7 @@
         <x:v>特效|player_state|player_dash|root|侧面朝右（可水平翻转）|dashing</x:v>
       </x:c>
       <x:c r="S13" s="37" t="str">
-        <x:f>IF(A13="","",IF(COUNTIF($R$6:$R$112,R13)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A13="","",IF(COUNTIF($R$6:$R$139,R13)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T13" s="37" t="str"/>
@@ -1863,7 +1849,7 @@
         <x:v>特效|player_state|player_hurt|root|侧面朝右（可水平翻转）|hurt</x:v>
       </x:c>
       <x:c r="S14" s="37" t="str">
-        <x:f>IF(A14="","",IF(COUNTIF($R$6:$R$112,R14)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A14="","",IF(COUNTIF($R$6:$R$139,R14)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T14" s="37" t="str"/>
@@ -1929,7 +1915,7 @@
         <x:v>特效|player_overlay|player_low_hp|root|侧面朝右（可水平翻转）|low_health</x:v>
       </x:c>
       <x:c r="S15" s="37" t="str">
-        <x:f>IF(A15="","",IF(COUNTIF($R$6:$R$112,R15)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A15="","",IF(COUNTIF($R$6:$R$139,R15)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T15" s="37" t="str"/>
@@ -1995,7 +1981,7 @@
         <x:v>特效|player_overlay|player_silenced|root|侧面朝右（可水平翻转）|silenced</x:v>
       </x:c>
       <x:c r="S16" s="37" t="str">
-        <x:f>IF(A16="","",IF(COUNTIF($R$6:$R$112,R16)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A16="","",IF(COUNTIF($R$6:$R$139,R16)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T16" s="37" t="str"/>
@@ -2063,7 +2049,7 @@
         <x:v>敌人|normal_melee|melee_chaser|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S17" s="37" t="str">
-        <x:f>IF(A17="","",IF(COUNTIF($R$6:$R$112,R17)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A17="","",IF(COUNTIF($R$6:$R$139,R17)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T17" s="37" t="str"/>
@@ -2133,7 +2119,7 @@
         <x:v>敌人|normal_ranged|ranged_caster|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S18" s="37" t="str">
-        <x:f>IF(A18="","",IF(COUNTIF($R$6:$R$112,R18)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A18="","",IF(COUNTIF($R$6:$R$139,R18)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T18" s="37" t="str"/>
@@ -2201,7 +2187,7 @@
         <x:v>敌人|normal_summoner|summoner|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S19" s="37" t="str">
-        <x:f>IF(A19="","",IF(COUNTIF($R$6:$R$112,R19)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A19="","",IF(COUNTIF($R$6:$R$139,R19)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T19" s="37" t="str"/>
@@ -2269,7 +2255,7 @@
         <x:v>敌人|normal_tank|shielded|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S20" s="37" t="str">
-        <x:f>IF(A20="","",IF(COUNTIF($R$6:$R$112,R20)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A20="","",IF(COUNTIF($R$6:$R$139,R20)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T20" s="37" t="str"/>
@@ -2337,7 +2323,7 @@
         <x:v>敌人|normal_bomber|exploder|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S21" s="37" t="str">
-        <x:f>IF(A21="","",IF(COUNTIF($R$6:$R$112,R21)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A21="","",IF(COUNTIF($R$6:$R$139,R21)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T21" s="37" t="str"/>
@@ -2405,7 +2391,7 @@
         <x:v>敌人|normal_ambusher|ambusher|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S22" s="37" t="str">
-        <x:f>IF(A22="","",IF(COUNTIF($R$6:$R$112,R22)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A22="","",IF(COUNTIF($R$6:$R$139,R22)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T22" s="37" t="str"/>
@@ -2473,7 +2459,7 @@
         <x:v>敌人|boss|boss|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S23" s="37" t="str">
-        <x:f>IF(A23="","",IF(COUNTIF($R$6:$R$112,R23)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A23="","",IF(COUNTIF($R$6:$R$139,R23)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T23" s="37" t="str"/>
@@ -2543,7 +2529,7 @@
         <x:v>枪械|gunbody|bp_pistol|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S24" s="37" t="str">
-        <x:f>IF(A24="","",IF(COUNTIF($R$6:$R$112,R24)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A24="","",IF(COUNTIF($R$6:$R$139,R24)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T24" s="37" t="str"/>
@@ -2613,7 +2599,7 @@
         <x:v>枪械|gunbody|bp_shotgun|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S25" s="37" t="str">
-        <x:f>IF(A25="","",IF(COUNTIF($R$6:$R$112,R25)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A25="","",IF(COUNTIF($R$6:$R$139,R25)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T25" s="37" t="str"/>
@@ -2683,7 +2669,7 @@
         <x:v>枪械|gunbody|bp_rifle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S26" s="37" t="str">
-        <x:f>IF(A26="","",IF(COUNTIF($R$6:$R$112,R26)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A26="","",IF(COUNTIF($R$6:$R$139,R26)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T26" s="37" t="str"/>
@@ -2753,7 +2739,7 @@
         <x:v>枪械|gunbody|bp_machinegun|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S27" s="37" t="str">
-        <x:f>IF(A27="","",IF(COUNTIF($R$6:$R$112,R27)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A27="","",IF(COUNTIF($R$6:$R$139,R27)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T27" s="37" t="str"/>
@@ -2823,7 +2809,7 @@
         <x:v>枪械|gunbody|bp_sniper|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S28" s="37" t="str">
-        <x:f>IF(A28="","",IF(COUNTIF($R$6:$R$112,R28)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A28="","",IF(COUNTIF($R$6:$R$139,R28)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T28" s="37" t="str"/>
@@ -2893,7 +2879,7 @@
         <x:v>枪械|gunbody|bp_launcher|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S29" s="37" t="str">
-        <x:f>IF(A29="","",IF(COUNTIF($R$6:$R$112,R29)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A29="","",IF(COUNTIF($R$6:$R$139,R29)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T29" s="37" t="str"/>
@@ -2963,7 +2949,7 @@
         <x:v>枪械|gunbody|bp_charge|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S30" s="37" t="str">
-        <x:f>IF(A30="","",IF(COUNTIF($R$6:$R$112,R30)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A30="","",IF(COUNTIF($R$6:$R$139,R30)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T30" s="37" t="str"/>
@@ -3031,7 +3017,7 @@
         <x:v>枪械|bullet_module|mod_bullet_standard|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S31" s="37" t="str">
-        <x:f>IF(A31="","",IF(COUNTIF($R$6:$R$112,R31)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A31="","",IF(COUNTIF($R$6:$R$139,R31)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T31" s="37" t="str"/>
@@ -3099,7 +3085,7 @@
         <x:v>枪械|bullet_module|mod_bullet_sticky|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S32" s="37" t="str">
-        <x:f>IF(A32="","",IF(COUNTIF($R$6:$R$112,R32)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A32="","",IF(COUNTIF($R$6:$R$139,R32)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T32" s="37" t="str"/>
@@ -3167,7 +3153,7 @@
         <x:v>枪械|bullet_module|mod_bullet_bounce|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S33" s="37" t="str">
-        <x:f>IF(A33="","",IF(COUNTIF($R$6:$R$112,R33)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A33="","",IF(COUNTIF($R$6:$R$139,R33)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T33" s="37" t="str"/>
@@ -3235,7 +3221,7 @@
         <x:v>枪械|bullet_module|mod_bullet_piercing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S34" s="37" t="str">
-        <x:f>IF(A34="","",IF(COUNTIF($R$6:$R$112,R34)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A34="","",IF(COUNTIF($R$6:$R$139,R34)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T34" s="37" t="str"/>
@@ -3303,7 +3289,7 @@
         <x:v>枪械|bullet_module|mod_bullet_explosive|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S35" s="37" t="str">
-        <x:f>IF(A35="","",IF(COUNTIF($R$6:$R$112,R35)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A35="","",IF(COUNTIF($R$6:$R$139,R35)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T35" s="37" t="str"/>
@@ -3371,7 +3357,7 @@
         <x:v>枪械|bullet_module|mod_bullet_homing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S36" s="37" t="str">
-        <x:f>IF(A36="","",IF(COUNTIF($R$6:$R$112,R36)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A36="","",IF(COUNTIF($R$6:$R$139,R36)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T36" s="37" t="str"/>
@@ -3439,7 +3425,7 @@
         <x:v>枪械|bullet_module|mod_bullet_blackhole|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S37" s="37" t="str">
-        <x:f>IF(A37="","",IF(COUNTIF($R$6:$R$112,R37)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A37="","",IF(COUNTIF($R$6:$R$139,R37)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T37" s="37" t="str"/>
@@ -3507,7 +3493,7 @@
         <x:v>枪械|bullet_module|mod_bullet_balloon|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S38" s="37" t="str">
-        <x:f>IF(A38="","",IF(COUNTIF($R$6:$R$112,R38)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A38="","",IF(COUNTIF($R$6:$R$139,R38)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T38" s="37" t="str"/>
@@ -3575,7 +3561,7 @@
         <x:v>枪械|attachment|attach_triple_muzzle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S39" s="37" t="str">
-        <x:f>IF(A39="","",IF(COUNTIF($R$6:$R$112,R39)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A39="","",IF(COUNTIF($R$6:$R$139,R39)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T39" s="37" t="str"/>
@@ -3643,7 +3629,7 @@
         <x:v>枪械|attachment|attach_rubber_stock|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S40" s="37" t="str">
-        <x:f>IF(A40="","",IF(COUNTIF($R$6:$R$112,R40)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A40="","",IF(COUNTIF($R$6:$R$139,R40)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T40" s="37" t="str"/>
@@ -3711,7 +3697,7 @@
         <x:v>枪械|attachment|attach_scope|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S41" s="37" t="str">
-        <x:f>IF(A41="","",IF(COUNTIF($R$6:$R$112,R41)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A41="","",IF(COUNTIF($R$6:$R$139,R41)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T41" s="37" t="str"/>
@@ -3779,7 +3765,7 @@
         <x:v>枪械|attachment|attach_big_mag|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S42" s="37" t="str">
-        <x:f>IF(A42="","",IF(COUNTIF($R$6:$R$112,R42)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A42="","",IF(COUNTIF($R$6:$R$139,R42)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T42" s="37" t="str"/>
@@ -3847,7 +3833,7 @@
         <x:v>枪械|attachment|attach_fan|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S43" s="37" t="str">
-        <x:f>IF(A43="","",IF(COUNTIF($R$6:$R$112,R43)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A43="","",IF(COUNTIF($R$6:$R$139,R43)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T43" s="37" t="str"/>
@@ -3915,7 +3901,7 @@
         <x:v>枪械|attachment|attach_copy_sticker|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S44" s="37" t="str">
-        <x:f>IF(A44="","",IF(COUNTIF($R$6:$R$112,R44)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A44="","",IF(COUNTIF($R$6:$R$139,R44)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T44" s="37" t="str"/>
@@ -3983,7 +3969,7 @@
         <x:v>道具|consumable|item_beacon|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S45" s="37" t="str">
-        <x:f>IF(A45="","",IF(COUNTIF($R$6:$R$112,R45)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A45="","",IF(COUNTIF($R$6:$R$139,R45)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T45" s="37" t="str"/>
@@ -4049,7 +4035,7 @@
         <x:v>道具|key|item_room_key|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S46" s="37" t="str">
-        <x:f>IF(A46="","",IF(COUNTIF($R$6:$R$112,R46)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A46="","",IF(COUNTIF($R$6:$R$139,R46)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T46" s="37" t="str"/>
@@ -4115,7 +4101,7 @@
         <x:v>道具|pickup|soul_orb|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S47" s="37" t="str">
-        <x:f>IF(A47="","",IF(COUNTIF($R$6:$R$112,R47)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A47="","",IF(COUNTIF($R$6:$R$139,R47)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T47" s="37" t="str"/>
@@ -4181,7 +4167,7 @@
         <x:v>道具|container|container|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S48" s="37" t="str">
-        <x:f>IF(A48="","",IF(COUNTIF($R$6:$R$112,R48)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A48="","",IF(COUNTIF($R$6:$R$139,R48)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T48" s="37" t="str"/>
@@ -4247,7 +4233,7 @@
         <x:v>道具|pickup|room_key_pickup|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S49" s="37" t="str">
-        <x:f>IF(A49="","",IF(COUNTIF($R$6:$R$112,R49)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A49="","",IF(COUNTIF($R$6:$R$139,R49)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T49" s="37" t="str"/>
@@ -4313,7 +4299,7 @@
         <x:v>道具|pickup_base|ground_item|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S50" s="37" t="str">
-        <x:f>IF(A50="","",IF(COUNTIF($R$6:$R$112,R50)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A50="","",IF(COUNTIF($R$6:$R$139,R50)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T50" s="37" t="str"/>
@@ -4379,7 +4365,7 @@
         <x:v>场景|biome_kit|base_world|root|顶视|default</x:v>
       </x:c>
       <x:c r="S51" s="37" t="str">
-        <x:f>IF(A51="","",IF(COUNTIF($R$6:$R$112,R51)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A51="","",IF(COUNTIF($R$6:$R$139,R51)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T51" s="37" t="str"/>
@@ -4447,7 +4433,7 @@
         <x:v>场景|biome_kit|iron_frontier|root|顶视|default</x:v>
       </x:c>
       <x:c r="S52" s="37" t="str">
-        <x:f>IF(A52="","",IF(COUNTIF($R$6:$R$112,R52)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A52="","",IF(COUNTIF($R$6:$R$139,R52)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T52" s="37" t="str"/>
@@ -4515,7 +4501,7 @@
         <x:v>场景|biome_kit|rust_foundry|root|顶视|default</x:v>
       </x:c>
       <x:c r="S53" s="37" t="str">
-        <x:f>IF(A53="","",IF(COUNTIF($R$6:$R$112,R53)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A53="","",IF(COUNTIF($R$6:$R$139,R53)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T53" s="37" t="str"/>
@@ -4583,7 +4569,7 @@
         <x:v>场景|biome_kit|spore_depths|root|顶视|default</x:v>
       </x:c>
       <x:c r="S54" s="37" t="str">
-        <x:f>IF(A54="","",IF(COUNTIF($R$6:$R$112,R54)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A54="","",IF(COUNTIF($R$6:$R$139,R54)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T54" s="37" t="str"/>
@@ -4651,7 +4637,7 @@
         <x:v>场景|biome_kit|abyss_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S55" s="37" t="str">
-        <x:f>IF(A55="","",IF(COUNTIF($R$6:$R$112,R55)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A55="","",IF(COUNTIF($R$6:$R$139,R55)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T55" s="37" t="str"/>
@@ -4719,7 +4705,7 @@
         <x:v>场景|biome_kit|training_range|root|顶视|default</x:v>
       </x:c>
       <x:c r="S56" s="37" t="str">
-        <x:f>IF(A56="","",IF(COUNTIF($R$6:$R$112,R56)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A56="","",IF(COUNTIF($R$6:$R$139,R56)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T56" s="37" t="str"/>
@@ -4787,7 +4773,7 @@
         <x:v>场景|room_dressing|room_combat|root|顶视|default</x:v>
       </x:c>
       <x:c r="S57" s="37" t="str">
-        <x:f>IF(A57="","",IF(COUNTIF($R$6:$R$112,R57)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A57="","",IF(COUNTIF($R$6:$R$139,R57)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T57" s="37" t="str"/>
@@ -4855,7 +4841,7 @@
         <x:v>场景|room_dressing|room_elite|root|顶视|default</x:v>
       </x:c>
       <x:c r="S58" s="37" t="str">
-        <x:f>IF(A58="","",IF(COUNTIF($R$6:$R$112,R58)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A58="","",IF(COUNTIF($R$6:$R$139,R58)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T58" s="37" t="str"/>
@@ -4923,7 +4909,7 @@
         <x:v>场景|room_dressing|room_boss|root|顶视|default</x:v>
       </x:c>
       <x:c r="S59" s="37" t="str">
-        <x:f>IF(A59="","",IF(COUNTIF($R$6:$R$112,R59)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A59="","",IF(COUNTIF($R$6:$R$139,R59)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T59" s="37" t="str"/>
@@ -4991,7 +4977,7 @@
         <x:v>场景|room_dressing|room_event|root|顶视|default</x:v>
       </x:c>
       <x:c r="S60" s="37" t="str">
-        <x:f>IF(A60="","",IF(COUNTIF($R$6:$R$112,R60)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A60="","",IF(COUNTIF($R$6:$R$139,R60)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T60" s="37" t="str"/>
@@ -5059,7 +5045,7 @@
         <x:v>场景|room_dressing|room_extraction|root|顶视|default</x:v>
       </x:c>
       <x:c r="S61" s="37" t="str">
-        <x:f>IF(A61="","",IF(COUNTIF($R$6:$R$112,R61)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A61="","",IF(COUNTIF($R$6:$R$139,R61)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T61" s="37" t="str"/>
@@ -5127,7 +5113,7 @@
         <x:v>场景|room_dressing|room_merchant|root|顶视|default</x:v>
       </x:c>
       <x:c r="S62" s="37" t="str">
-        <x:f>IF(A62="","",IF(COUNTIF($R$6:$R$112,R62)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A62="","",IF(COUNTIF($R$6:$R$139,R62)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T62" s="37" t="str"/>
@@ -5195,7 +5181,7 @@
         <x:v>场景|room_dressing|room_scavenge|root|顶视|default</x:v>
       </x:c>
       <x:c r="S63" s="37" t="str">
-        <x:f>IF(A63="","",IF(COUNTIF($R$6:$R$112,R63)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A63="","",IF(COUNTIF($R$6:$R$139,R63)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T63" s="37" t="str"/>
@@ -5263,7 +5249,7 @@
         <x:v>场景|room_dressing|room_storage|root|顶视|default</x:v>
       </x:c>
       <x:c r="S64" s="37" t="str">
-        <x:f>IF(A64="","",IF(COUNTIF($R$6:$R$112,R64)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A64="","",IF(COUNTIF($R$6:$R$139,R64)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T64" s="37" t="str"/>
@@ -5331,7 +5317,7 @@
         <x:v>场景|room_dressing|room_trap|root|顶视|default</x:v>
       </x:c>
       <x:c r="S65" s="37" t="str">
-        <x:f>IF(A65="","",IF(COUNTIF($R$6:$R$112,R65)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A65="","",IF(COUNTIF($R$6:$R$139,R65)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T65" s="37" t="str"/>
@@ -5399,7 +5385,7 @@
         <x:v>场景|room_dressing|room_upgrade|root|顶视|default</x:v>
       </x:c>
       <x:c r="S66" s="37" t="str">
-        <x:f>IF(A66="","",IF(COUNTIF($R$6:$R$112,R66)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A66="","",IF(COUNTIF($R$6:$R$139,R66)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T66" s="37" t="str"/>
@@ -5467,7 +5453,7 @@
         <x:v>场景|room_dressing|room_spawn|root|顶视|default</x:v>
       </x:c>
       <x:c r="S67" s="37" t="str">
-        <x:f>IF(A67="","",IF(COUNTIF($R$6:$R$112,R67)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A67="","",IF(COUNTIF($R$6:$R$139,R67)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T67" s="37" t="str"/>
@@ -5535,7 +5521,7 @@
         <x:v>场景|room_dressing|room_stairs|root|顶视|default</x:v>
       </x:c>
       <x:c r="S68" s="37" t="str">
-        <x:f>IF(A68="","",IF(COUNTIF($R$6:$R$112,R68)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A68="","",IF(COUNTIF($R$6:$R$139,R68)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T68" s="37" t="str"/>
@@ -5603,7 +5589,7 @@
         <x:v>场景道具|facility|base_briefing|root|顶视|default</x:v>
       </x:c>
       <x:c r="S69" s="37" t="str">
-        <x:f>IF(A69="","",IF(COUNTIF($R$6:$R$112,R69)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A69="","",IF(COUNTIF($R$6:$R$139,R69)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T69" s="37" t="str"/>
@@ -5671,7 +5657,7 @@
         <x:v>场景道具|facility|base_workshop|root|顶视|default</x:v>
       </x:c>
       <x:c r="S70" s="37" t="str">
-        <x:f>IF(A70="","",IF(COUNTIF($R$6:$R$112,R70)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A70="","",IF(COUNTIF($R$6:$R$139,R70)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T70" s="37" t="str"/>
@@ -5739,7 +5725,7 @@
         <x:v>场景道具|facility|base_divination|root|顶视|default</x:v>
       </x:c>
       <x:c r="S71" s="37" t="str">
-        <x:f>IF(A71="","",IF(COUNTIF($R$6:$R$112,R71)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A71="","",IF(COUNTIF($R$6:$R$139,R71)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T71" s="37" t="str"/>
@@ -5807,7 +5793,7 @@
         <x:v>场景道具|facility|base_vault|root|顶视|default</x:v>
       </x:c>
       <x:c r="S72" s="37" t="str">
-        <x:f>IF(A72="","",IF(COUNTIF($R$6:$R$112,R72)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A72="","",IF(COUNTIF($R$6:$R$139,R72)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T72" s="37" t="str"/>
@@ -5875,7 +5861,7 @@
         <x:v>场景道具|facility|base_monster_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S73" s="37" t="str">
-        <x:f>IF(A73="","",IF(COUNTIF($R$6:$R$112,R73)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A73="","",IF(COUNTIF($R$6:$R$139,R73)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T73" s="37" t="str"/>
@@ -5943,7 +5929,7 @@
         <x:v>场景道具|facility|base_card_collection|root|顶视|default</x:v>
       </x:c>
       <x:c r="S74" s="37" t="str">
-        <x:f>IF(A74="","",IF(COUNTIF($R$6:$R$112,R74)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A74="","",IF(COUNTIF($R$6:$R$139,R74)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T74" s="37" t="str"/>
@@ -6011,7 +5997,7 @@
         <x:v>场景道具|facility|base_terminal|root|顶视|default</x:v>
       </x:c>
       <x:c r="S75" s="37" t="str">
-        <x:f>IF(A75="","",IF(COUNTIF($R$6:$R$112,R75)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A75="","",IF(COUNTIF($R$6:$R$139,R75)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T75" s="37" t="str"/>
@@ -6079,7 +6065,7 @@
         <x:v>场景道具|facility|dungeon_gate|root|顶视|default</x:v>
       </x:c>
       <x:c r="S76" s="37" t="str">
-        <x:f>IF(A76="","",IF(COUNTIF($R$6:$R$112,R76)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A76="","",IF(COUNTIF($R$6:$R$139,R76)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T76" s="37" t="str"/>
@@ -6147,7 +6133,7 @@
         <x:v>场景道具|facility|workbench|root|顶视|default</x:v>
       </x:c>
       <x:c r="S77" s="37" t="str">
-        <x:f>IF(A77="","",IF(COUNTIF($R$6:$R$112,R77)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A77="","",IF(COUNTIF($R$6:$R$139,R77)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T77" s="37" t="str"/>
@@ -6215,7 +6201,7 @@
         <x:v>场景道具|facility|door|root|顶视|default</x:v>
       </x:c>
       <x:c r="S78" s="37" t="str">
-        <x:f>IF(A78="","",IF(COUNTIF($R$6:$R$112,R78)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A78="","",IF(COUNTIF($R$6:$R$139,R78)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T78" s="37" t="str"/>
@@ -6283,7 +6269,7 @@
         <x:v>ui|screen|hud|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S79" s="37" t="str">
-        <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$112,R79)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$139,R79)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T79" s="37" t="str"/>
@@ -6351,7 +6337,7 @@
         <x:v>ui|screen|inventory|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S80" s="37" t="str">
-        <x:f>IF(A80="","",IF(COUNTIF($R$6:$R$112,R80)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A80="","",IF(COUNTIF($R$6:$R$139,R80)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T80" s="37" t="str"/>
@@ -6419,7 +6405,7 @@
         <x:v>ui|screen|merchant|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S81" s="37" t="str">
-        <x:f>IF(A81="","",IF(COUNTIF($R$6:$R$112,R81)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A81="","",IF(COUNTIF($R$6:$R$139,R81)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T81" s="37" t="str"/>
@@ -6487,7 +6473,7 @@
         <x:v>ui|screen|workshop|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S82" s="37" t="str">
-        <x:f>IF(A82="","",IF(COUNTIF($R$6:$R$112,R82)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A82="","",IF(COUNTIF($R$6:$R$139,R82)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T82" s="37" t="str"/>
@@ -6555,7 +6541,7 @@
         <x:v>ui|screen|workbench|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S83" s="37" t="str">
-        <x:f>IF(A83="","",IF(COUNTIF($R$6:$R$112,R83)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A83="","",IF(COUNTIF($R$6:$R$139,R83)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T83" s="37" t="str"/>
@@ -6623,7 +6609,7 @@
         <x:v>ui|screen|weapon_tree|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S84" s="37" t="str">
-        <x:f>IF(A84="","",IF(COUNTIF($R$6:$R$112,R84)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A84="","",IF(COUNTIF($R$6:$R$139,R84)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T84" s="37" t="str"/>
@@ -6691,7 +6677,7 @@
         <x:v>ui|screen|fate_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S85" s="37" t="str">
-        <x:f>IF(A85="","",IF(COUNTIF($R$6:$R$112,R85)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A85="","",IF(COUNTIF($R$6:$R$139,R85)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T85" s="37" t="str"/>
@@ -6759,7 +6745,7 @@
         <x:v>ui|screen|fate_collection|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S86" s="37" t="str">
-        <x:f>IF(A86="","",IF(COUNTIF($R$6:$R$112,R86)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A86="","",IF(COUNTIF($R$6:$R$139,R86)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T86" s="37" t="str"/>
@@ -6827,7 +6813,7 @@
         <x:v>ui|screen|level_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S87" s="37" t="str">
-        <x:f>IF(A87="","",IF(COUNTIF($R$6:$R$112,R87)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A87="","",IF(COUNTIF($R$6:$R$139,R87)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T87" s="37" t="str"/>
@@ -6895,7 +6881,7 @@
         <x:v>ui|screen|vault|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S88" s="37" t="str">
-        <x:f>IF(A88="","",IF(COUNTIF($R$6:$R$112,R88)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A88="","",IF(COUNTIF($R$6:$R$139,R88)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T88" s="37" t="str"/>
@@ -6963,7 +6949,7 @@
         <x:v>ui|screen|monster_archive|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S89" s="37" t="str">
-        <x:f>IF(A89="","",IF(COUNTIF($R$6:$R$112,R89)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A89="","",IF(COUNTIF($R$6:$R$139,R89)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T89" s="37" t="str"/>
@@ -7031,7 +7017,7 @@
         <x:v>ui|screen|base_menu|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S90" s="37" t="str">
-        <x:f>IF(A90="","",IF(COUNTIF($R$6:$R$112,R90)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A90="","",IF(COUNTIF($R$6:$R$139,R90)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T90" s="37" t="str"/>
@@ -7099,7 +7085,7 @@
         <x:v>ui|screen|mobile_controls|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S91" s="37" t="str">
-        <x:f>IF(A91="","",IF(COUNTIF($R$6:$R$112,R91)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A91="","",IF(COUNTIF($R$6:$R$139,R91)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T91" s="37" t="str"/>
@@ -7167,7 +7153,7 @@
         <x:v>特效|gameplay_vfx|explosion|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S92" s="37" t="str">
-        <x:f>IF(A92="","",IF(COUNTIF($R$6:$R$112,R92)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A92="","",IF(COUNTIF($R$6:$R$139,R92)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T92" s="37" t="str"/>
@@ -7235,7 +7221,7 @@
         <x:v>特效|gameplay_vfx|muzzle_flash|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S93" s="37" t="str">
-        <x:f>IF(A93="","",IF(COUNTIF($R$6:$R$112,R93)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A93="","",IF(COUNTIF($R$6:$R$139,R93)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T93" s="37" t="str"/>
@@ -7303,7 +7289,7 @@
         <x:v>特效|gameplay_vfx|damage_number|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S94" s="37" t="str">
-        <x:f>IF(A94="","",IF(COUNTIF($R$6:$R$112,R94)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A94="","",IF(COUNTIF($R$6:$R$139,R94)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T94" s="37" t="str"/>
@@ -7371,7 +7357,7 @@
         <x:v>特效|gameplay_vfx|spark|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S95" s="37" t="str">
-        <x:f>IF(A95="","",IF(COUNTIF($R$6:$R$112,R95)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A95="","",IF(COUNTIF($R$6:$R$139,R95)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T95" s="37" t="str"/>
@@ -7439,7 +7425,7 @@
         <x:v>特效|gameplay_vfx|room_transition|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S96" s="37" t="str">
-        <x:f>IF(A96="","",IF(COUNTIF($R$6:$R$112,R96)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A96="","",IF(COUNTIF($R$6:$R$139,R96)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T96" s="37" t="str"/>
@@ -7507,7 +7493,7 @@
         <x:v>特效|gameplay_vfx|health_vignette|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S97" s="37" t="str">
-        <x:f>IF(A97="","",IF(COUNTIF($R$6:$R$112,R97)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A97="","",IF(COUNTIF($R$6:$R$139,R97)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T97" s="37" t="str"/>
@@ -7575,7 +7561,7 @@
         <x:v>特效|gameplay_vfx|visibility_light|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S98" s="37" t="str">
-        <x:f>IF(A98="","",IF(COUNTIF($R$6:$R$112,R98)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A98="","",IF(COUNTIF($R$6:$R$139,R98)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T98" s="37" t="str"/>
@@ -7643,7 +7629,7 @@
         <x:v>特效|gameplay_vfx|extraction_beacon|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S99" s="37" t="str">
-        <x:f>IF(A99="","",IF(COUNTIF($R$6:$R$112,R99)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A99="","",IF(COUNTIF($R$6:$R$139,R99)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T99" s="37" t="str"/>
@@ -7711,7 +7697,7 @@
         <x:v>音频|bgm|bgm_wasteland|root|不适用|default</x:v>
       </x:c>
       <x:c r="S100" s="37" t="str">
-        <x:f>IF(A100="","",IF(COUNTIF($R$6:$R$112,R100)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A100="","",IF(COUNTIF($R$6:$R$139,R100)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T100" s="37" t="str"/>
@@ -7777,7 +7763,7 @@
         <x:v>音频|sfx|pistol_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S101" s="37" t="str">
-        <x:f>IF(A101="","",IF(COUNTIF($R$6:$R$112,R101)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A101="","",IF(COUNTIF($R$6:$R$139,R101)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T101" s="37" t="str"/>
@@ -7843,7 +7829,7 @@
         <x:v>音频|sfx|rifle_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S102" s="37" t="str">
-        <x:f>IF(A102="","",IF(COUNTIF($R$6:$R$112,R102)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A102="","",IF(COUNTIF($R$6:$R$139,R102)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T102" s="37" t="str"/>
@@ -7909,7 +7895,7 @@
         <x:v>音频|sfx|shotgun_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S103" s="37" t="str">
-        <x:f>IF(A103="","",IF(COUNTIF($R$6:$R$112,R103)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A103="","",IF(COUNTIF($R$6:$R$139,R103)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T103" s="37" t="str"/>
@@ -7975,7 +7961,7 @@
         <x:v>音频|sfx|smg_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S104" s="37" t="str">
-        <x:f>IF(A104="","",IF(COUNTIF($R$6:$R$112,R104)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A104="","",IF(COUNTIF($R$6:$R$139,R104)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T104" s="37" t="str"/>
@@ -8041,7 +8027,7 @@
         <x:v>音频|sfx|sniper_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S105" s="37" t="str">
-        <x:f>IF(A105="","",IF(COUNTIF($R$6:$R$112,R105)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A105="","",IF(COUNTIF($R$6:$R$139,R105)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T105" s="37" t="str"/>
@@ -8107,7 +8093,7 @@
         <x:v>音频|sfx|player_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S106" s="37" t="str">
-        <x:f>IF(A106="","",IF(COUNTIF($R$6:$R$112,R106)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A106="","",IF(COUNTIF($R$6:$R$139,R106)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T106" s="37" t="str"/>
@@ -8173,7 +8159,7 @@
         <x:v>音频|sfx|player_dash|root|不适用|default</x:v>
       </x:c>
       <x:c r="S107" s="37" t="str">
-        <x:f>IF(A107="","",IF(COUNTIF($R$6:$R$112,R107)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A107="","",IF(COUNTIF($R$6:$R$139,R107)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T107" s="37" t="str"/>
@@ -8239,7 +8225,7 @@
         <x:v>音频|sfx|enemy_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S108" s="37" t="str">
-        <x:f>IF(A108="","",IF(COUNTIF($R$6:$R$112,R108)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A108="","",IF(COUNTIF($R$6:$R$139,R108)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T108" s="37" t="str"/>
@@ -8305,7 +8291,7 @@
         <x:v>音频|sfx|enemy_die|root|不适用|default</x:v>
       </x:c>
       <x:c r="S109" s="37" t="str">
-        <x:f>IF(A109="","",IF(COUNTIF($R$6:$R$112,R109)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A109="","",IF(COUNTIF($R$6:$R$139,R109)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T109" s="37" t="str"/>
@@ -8371,7 +8357,7 @@
         <x:v>音频|sfx|reload|root|不适用|default</x:v>
       </x:c>
       <x:c r="S110" s="37" t="str">
-        <x:f>IF(A110="","",IF(COUNTIF($R$6:$R$112,R110)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A110="","",IF(COUNTIF($R$6:$R$139,R110)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T110" s="37" t="str"/>
@@ -8437,7 +8423,7 @@
         <x:v>音频|sfx|extraction_start|root|不适用|default</x:v>
       </x:c>
       <x:c r="S111" s="37" t="str">
-        <x:f>IF(A111="","",IF(COUNTIF($R$6:$R$112,R111)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A111="","",IF(COUNTIF($R$6:$R$139,R111)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T111" s="37" t="str"/>
@@ -8503,7 +8489,7 @@
         <x:v>音频|sfx|extraction_done|root|不适用|default</x:v>
       </x:c>
       <x:c r="S112" s="37" t="str">
-        <x:f>IF(A112="","",IF(COUNTIF($R$6:$R$112,R112)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A112="","",IF(COUNTIF($R$6:$R$139,R112)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T112" s="37" t="str"/>
@@ -8517,6 +8503,2048 @@
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X112" s="37" t="str"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="B113" t="str">
+        <x:v>胶囊防护体3D根组件</x:v>
+      </x:c>
+      <x:c r="C113" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D113" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="E113" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F113" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G113" t="str">
+        <x:v>CHR-PLY-CAPSULE01</x:v>
+      </x:c>
+      <x:c r="H113" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I113" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J113" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K113" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L113" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M113" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N113" t="str">
+        <x:v>PackedScene/程序材质</x:v>
+      </x:c>
+      <x:c r="O113" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P113" t="str">
+        <x:v>scenes/Player3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q113" t="str">
+        <x:v>胶囊;防护服;3D;模块角色</x:v>
+      </x:c>
+      <x:c r="R113" t="str">
+        <x:f>LOWER(TRIM(C113)&amp;"|"&amp;TRIM(D113)&amp;"|"&amp;TRIM(E113)&amp;"|"&amp;TRIM(F113)&amp;"|"&amp;TRIM(H113)&amp;"|"&amp;TRIM(I113))</x:f>
+        <x:v>角色|player|player_capsule01|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S113" t="str">
+        <x:f>IF(A113="","",IF(COUNTIF($R$6:$R$139,R113)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T113" t="str">
+        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+      </x:c>
+      <x:c r="U113" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V113" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W113" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X113" t="str">
+        <x:v>2D逻辑资产的3D表现变体；无腿、单手、无手臂</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="str">
+        <x:v>CHR-PLY-CAPSULE01-BODY-3D</x:v>
+      </x:c>
+      <x:c r="B114" t="str">
+        <x:v>胶囊防护体3D身躯</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D114" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="E114" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F114" t="str">
+        <x:v>body_3d</x:v>
+      </x:c>
+      <x:c r="G114" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="H114" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I114" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J114" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K114" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L114" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M114" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N114" t="str">
+        <x:v>CapsuleMesh节点</x:v>
+      </x:c>
+      <x:c r="O114" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P114" t="str">
+        <x:v>VisualRoot/Body</x:v>
+      </x:c>
+      <x:c r="Q114" t="str">
+        <x:v>身躯;防护服;无腿;3D</x:v>
+      </x:c>
+      <x:c r="R114" t="str">
+        <x:f>LOWER(TRIM(C114)&amp;"|"&amp;TRIM(D114)&amp;"|"&amp;TRIM(E114)&amp;"|"&amp;TRIM(F114)&amp;"|"&amp;TRIM(H114)&amp;"|"&amp;TRIM(I114))</x:f>
+        <x:v>角色|player|player_capsule01|body_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S114" t="str">
+        <x:f>IF(A114="","",IF(COUNTIF($R$6:$R$139,R114)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T114" t="str">
+        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+      </x:c>
+      <x:c r="U114" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V114" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W114" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X114" t="str">
+        <x:v>PackedScene内独立Body节点；后续可替换GLB</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HEAD-3D</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>胶囊防护体3D头壳</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D115" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="E115" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F115" t="str">
+        <x:v>head_3d</x:v>
+      </x:c>
+      <x:c r="G115" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="H115" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I115" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J115" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K115" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L115" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M115" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N115" t="str">
+        <x:v>SphereMesh节点</x:v>
+      </x:c>
+      <x:c r="O115" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P115" t="str">
+        <x:v>VisualRoot/Head</x:v>
+      </x:c>
+      <x:c r="Q115" t="str">
+        <x:v>头壳;单传感器;3D</x:v>
+      </x:c>
+      <x:c r="R115" t="str">
+        <x:f>LOWER(TRIM(C115)&amp;"|"&amp;TRIM(D115)&amp;"|"&amp;TRIM(E115)&amp;"|"&amp;TRIM(F115)&amp;"|"&amp;TRIM(H115)&amp;"|"&amp;TRIM(I115))</x:f>
+        <x:v>角色|player|player_capsule01|head_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S115" t="str">
+        <x:f>IF(A115="","",IF(COUNTIF($R$6:$R$139,R115)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T115" t="str">
+        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+      </x:c>
+      <x:c r="U115" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V115" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W115" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X115" t="str">
+        <x:v>PackedScene内独立Head节点；无嘴无人脸</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HAND-3D</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>胶囊防护体3D唯一手部</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D116" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="E116" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F116" t="str">
+        <x:v>hand_3d</x:v>
+      </x:c>
+      <x:c r="G116" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="H116" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I116" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J116" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K116" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L116" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M116" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N116" t="str">
+        <x:v>SphereMesh节点</x:v>
+      </x:c>
+      <x:c r="O116" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P116" t="str">
+        <x:v>VisualRoot/Hand</x:v>
+      </x:c>
+      <x:c r="Q116" t="str">
+        <x:v>单手;悬浮手;握持;3D</x:v>
+      </x:c>
+      <x:c r="R116" t="str">
+        <x:f>LOWER(TRIM(C116)&amp;"|"&amp;TRIM(D116)&amp;"|"&amp;TRIM(E116)&amp;"|"&amp;TRIM(F116)&amp;"|"&amp;TRIM(H116)&amp;"|"&amp;TRIM(I116))</x:f>
+        <x:v>角色|player|player_capsule01|hand_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S116" t="str">
+        <x:f>IF(A116="","",IF(COUNTIF($R$6:$R$139,R116)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T116" t="str">
+        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+      </x:c>
+      <x:c r="U116" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V116" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W116" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X116" t="str">
+        <x:v>唯一可见手；随VisualRoot转向并保持身体局部位置</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="str">
+        <x:v>CHR-PLY-CAPSULE01-SCARF-3D</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>胶囊防护体3D红围巾</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D117" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="E117" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F117" t="str">
+        <x:v>scarf_3d</x:v>
+      </x:c>
+      <x:c r="G117" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="H117" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I117" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J117" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K117" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L117" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M117" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N117" t="str">
+        <x:v>Cylinder+Box节点</x:v>
+      </x:c>
+      <x:c r="O117" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P117" t="str">
+        <x:v>VisualRoot/Scarf</x:v>
+      </x:c>
+      <x:c r="Q117" t="str">
+        <x:v>红围巾;身份配件;3D</x:v>
+      </x:c>
+      <x:c r="R117" t="str">
+        <x:f>LOWER(TRIM(C117)&amp;"|"&amp;TRIM(D117)&amp;"|"&amp;TRIM(E117)&amp;"|"&amp;TRIM(F117)&amp;"|"&amp;TRIM(H117)&amp;"|"&amp;TRIM(I117))</x:f>
+        <x:v>角色|player|player_capsule01|scarf_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S117" t="str">
+        <x:f>IF(A117="","",IF(COUNTIF($R$6:$R$139,R117)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T117" t="str">
+        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+      </x:c>
+      <x:c r="U117" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V117" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W117" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X117" t="str">
+        <x:v>独立Scarf节点；保留移动与冲刺滞后动态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str">
+        <x:v>CHR-PLY-CAPSULE01-WEAPON-SOCKET-3D</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>胶囊防护体3D武器挂点</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D118" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="E118" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F118" t="str">
+        <x:v>weapon_socket_3d</x:v>
+      </x:c>
+      <x:c r="G118" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="H118" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I118" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J118" t="str">
+        <x:v>武器系统</x:v>
+      </x:c>
+      <x:c r="K118" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L118" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M118" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N118" t="str">
+        <x:v>Marker3D</x:v>
+      </x:c>
+      <x:c r="O118" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P118" t="str">
+        <x:v>VisualRoot/WeaponSocket</x:v>
+      </x:c>
+      <x:c r="Q118" t="str">
+        <x:v>武器挂点;Marker3D;瞄准</x:v>
+      </x:c>
+      <x:c r="R118" t="str">
+        <x:f>LOWER(TRIM(C118)&amp;"|"&amp;TRIM(D118)&amp;"|"&amp;TRIM(E118)&amp;"|"&amp;TRIM(F118)&amp;"|"&amp;TRIM(H118)&amp;"|"&amp;TRIM(I118))</x:f>
+        <x:v>角色|player|player_capsule01|weapon_socket_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S118" t="str">
+        <x:f>IF(A118="","",IF(COUNTIF($R$6:$R$139,R118)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T118" t="str">
+        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+      </x:c>
+      <x:c r="U118" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V118" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W118" t="str">
+        <x:v>原创逻辑挂点</x:v>
+      </x:c>
+      <x:c r="X118" t="str">
+        <x:v>手和挂点保持局部关系；VisualRoot统一跟随准星转向</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="str">
+        <x:v>ENV-BASE-WORLD-KIT-3D</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>入口基地3D环境套件</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D119" t="str">
+        <x:v>base</x:v>
+      </x:c>
+      <x:c r="E119" t="str">
+        <x:v>base_world</x:v>
+      </x:c>
+      <x:c r="F119" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G119" t="str">
+        <x:v>ENV-BASE-WORLD-KIT</x:v>
+      </x:c>
+      <x:c r="H119" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I119" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J119" t="str">
+        <x:v>入口基地地图</x:v>
+      </x:c>
+      <x:c r="K119" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L119" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M119" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N119" t="str">
+        <x:v>约1:100迁移/程序几何</x:v>
+      </x:c>
+      <x:c r="O119" t="str">
+        <x:v>assets/art/environments/base_world_3d/env_base_world_kit_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P119" t="str">
+        <x:v>scenes/BaseWorld3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q119" t="str">
+        <x:v>基地;道路;废墟;3D;入口地图</x:v>
+      </x:c>
+      <x:c r="R119" t="str">
+        <x:f>LOWER(TRIM(C119)&amp;"|"&amp;TRIM(D119)&amp;"|"&amp;TRIM(E119)&amp;"|"&amp;TRIM(F119)&amp;"|"&amp;TRIM(H119)&amp;"|"&amp;TRIM(I119))</x:f>
+        <x:v>场景|base|base_world|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S119" t="str">
+        <x:f>IF(A119="","",IF(COUNTIF($R$6:$R$139,R119)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T119" t="str">
+        <x:v>63c840d59bcecefab946690136474c9ca7b70408fb7b6bcc264819f9b66f14a5</x:v>
+      </x:c>
+      <x:c r="U119" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V119" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W119" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X119" t="str">
+        <x:v>保留原2D布局语义；首张3D迁移地图</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>PRP-BASE-FACILITY-3D</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>基地设施3D通用模块</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D120" t="str">
+        <x:v>facility</x:v>
+      </x:c>
+      <x:c r="E120" t="str">
+        <x:v>base_facility_module</x:v>
+      </x:c>
+      <x:c r="F120" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G120" t="str">
+        <x:v>ENV-BASE-WORLD-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H120" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I120" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J120" t="str">
+        <x:v>8类基地设施</x:v>
+      </x:c>
+      <x:c r="K120" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L120" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M120" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N120" t="str">
+        <x:v>PackedScene/材质变体</x:v>
+      </x:c>
+      <x:c r="O120" t="str">
+        <x:v>assets/art/props/base_world_3d/prp_base_facility_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P120" t="str">
+        <x:v>src/base3d/BaseFacility3D.gd</x:v>
+      </x:c>
+      <x:c r="Q120" t="str">
+        <x:v>设施;交互;信标;3D</x:v>
+      </x:c>
+      <x:c r="R120" t="str">
+        <x:f>LOWER(TRIM(C120)&amp;"|"&amp;TRIM(D120)&amp;"|"&amp;TRIM(E120)&amp;"|"&amp;TRIM(F120)&amp;"|"&amp;TRIM(H120)&amp;"|"&amp;TRIM(I120))</x:f>
+        <x:v>场景道具|facility|base_facility_module|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S120" t="str">
+        <x:f>IF(A120="","",IF(COUNTIF($R$6:$R$139,R120)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T120" t="str">
+        <x:v>18921dbda4e5997f5c49c6efa66b7af030310d5d086b60fe476e8f0e664e104e</x:v>
+      </x:c>
+      <x:c r="U120" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V120" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W120" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X120" t="str">
+        <x:v>由配置生成8个设施变体；复用同一场景</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>PRP-DUNGEON-GATE-3D</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>地下城入口3D模块</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D121" t="str">
+        <x:v>door</x:v>
+      </x:c>
+      <x:c r="E121" t="str">
+        <x:v>dungeon_gate</x:v>
+      </x:c>
+      <x:c r="F121" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G121" t="str">
+        <x:v>PRP-DUNGEON-GATE</x:v>
+      </x:c>
+      <x:c r="H121" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I121" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J121" t="str">
+        <x:v>4个地下城入口</x:v>
+      </x:c>
+      <x:c r="K121" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L121" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M121" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N121" t="str">
+        <x:v>PackedScene/材质变体</x:v>
+      </x:c>
+      <x:c r="O121" t="str">
+        <x:v>assets/art/props/base_world_3d/prp_dungeon_gate_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P121" t="str">
+        <x:v>src/base3d/DungeonEntrance3D.gd</x:v>
+      </x:c>
+      <x:c r="Q121" t="str">
+        <x:v>地下城;门;交互;3D</x:v>
+      </x:c>
+      <x:c r="R121" t="str">
+        <x:f>LOWER(TRIM(C121)&amp;"|"&amp;TRIM(D121)&amp;"|"&amp;TRIM(E121)&amp;"|"&amp;TRIM(F121)&amp;"|"&amp;TRIM(H121)&amp;"|"&amp;TRIM(I121))</x:f>
+        <x:v>场景道具|door|dungeon_gate|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S121" t="str">
+        <x:f>IF(A121="","",IF(COUNTIF($R$6:$R$139,R121)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T121" t="str">
+        <x:v>1fc802ceb8caef1ce77a54958a8b5e82a0fcae37459106fee970c8941146ba8f</x:v>
+      </x:c>
+      <x:c r="U121" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V121" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W121" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X121" t="str">
+        <x:v>保持旧入口ID与目标场景；地下城内部暂保留2D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>ENV-BASE-WORLD-3D-PREVIEW</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>入口基地3D验收预览</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D122" t="str">
+        <x:v>review_board</x:v>
+      </x:c>
+      <x:c r="E122" t="str">
+        <x:v>base_world</x:v>
+      </x:c>
+      <x:c r="F122" t="str">
+        <x:v>preview_3d</x:v>
+      </x:c>
+      <x:c r="G122" t="str">
+        <x:v>ENV-BASE-WORLD-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H122" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I122" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J122" t="str">
+        <x:v>评审与资产QA</x:v>
+      </x:c>
+      <x:c r="K122" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L122" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M122" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N122" t="str">
+        <x:v>1280×720 PNG</x:v>
+      </x:c>
+      <x:c r="O122" t="str">
+        <x:v>assets/art/environments/base_world_3d/env_base_world_preview_top3d_v001.png</x:v>
+      </x:c>
+      <x:c r="P122" t="str">
+        <x:v>verify_base_world_3d_visual.tscn</x:v>
+      </x:c>
+      <x:c r="Q122" t="str">
+        <x:v>3D预览;评审;入口地图</x:v>
+      </x:c>
+      <x:c r="R122" t="str">
+        <x:f>LOWER(TRIM(C122)&amp;"|"&amp;TRIM(D122)&amp;"|"&amp;TRIM(E122)&amp;"|"&amp;TRIM(F122)&amp;"|"&amp;TRIM(H122)&amp;"|"&amp;TRIM(I122))</x:f>
+        <x:v>场景|review_board|base_world|preview_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S122" t="str">
+        <x:f>IF(A122="","",IF(COUNTIF($R$6:$R$139,R122)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T122" t="str">
+        <x:v>7dc3ff5d1bb5942c8340359bfa6d55374604dfbc9fc8b2a23b68a3079fac2e01</x:v>
+      </x:c>
+      <x:c r="U122" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V122" s="62" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W122" t="str">
+        <x:v>项目运行截图</x:v>
+      </x:c>
+      <x:c r="X122" t="str">
+        <x:v>用于检查3D布局、镜头、组件比例与交互可读性</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="34" customHeight="1">
+      <x:c r="A123" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="B123" s="63" t="str">
+        <x:v>3D随机关卡通用房间套件</x:v>
+      </x:c>
+      <x:c r="C123" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D123" s="63" t="str">
+        <x:v>room</x:v>
+      </x:c>
+      <x:c r="E123" s="63" t="str">
+        <x:v>dungeon_runtime</x:v>
+      </x:c>
+      <x:c r="F123" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G123" s="63"/>
+      <x:c r="H123" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I123" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J123" s="63" t="str">
+        <x:v>四主题副本/随机房间</x:v>
+      </x:c>
+      <x:c r="K123" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L123" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M123" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N123" s="63" t="str">
+        <x:v>PackedScene/三档程序几何</x:v>
+      </x:c>
+      <x:c r="O123" s="63" t="str">
+        <x:v>assets/art/environments/dungeon_3d/env_dungeon_runtime_kit_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P123" s="63" t="str">
+        <x:v>src/world3d/DungeonRoom3D.gd</x:v>
+      </x:c>
+      <x:c r="Q123" s="63" t="str">
+        <x:v>房间;门洞;走廊;随机地图;3D</x:v>
+      </x:c>
+      <x:c r="R123" s="63" t="str">
+        <x:f>LOWER(TRIM(C123)&amp;"|"&amp;TRIM(D123)&amp;"|"&amp;TRIM(E123)&amp;"|"&amp;TRIM(F123)&amp;"|"&amp;TRIM(H123)&amp;"|"&amp;TRIM(I123))</x:f>
+        <x:v>场景|room|dungeon_runtime|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S123" s="63" t="str">
+        <x:f>IF(A123="","",IF(COUNTIF($R$6:$R$139,R123)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T123" s="63" t="str">
+        <x:v>fc33ac084150c3e3cbba89505b3e04f35712abbceaa5cec297c94fe4d7dcc2f3</x:v>
+      </x:c>
+      <x:c r="U123" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V123" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W123" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X123" s="63" t="str">
+        <x:v>small/medium/large；四向门；家具、搜索、服务、危险区共用根</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="34" customHeight="1">
+      <x:c r="A124" s="63" t="str">
+        <x:v>ENV-DUNGEON-IRON-FRONTIER-3D</x:v>
+      </x:c>
+      <x:c r="B124" s="63" t="str">
+        <x:v>冷钢边境3D主题资源</x:v>
+      </x:c>
+      <x:c r="C124" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D124" s="63" t="str">
+        <x:v>biome</x:v>
+      </x:c>
+      <x:c r="E124" s="63" t="str">
+        <x:v>iron_frontier</x:v>
+      </x:c>
+      <x:c r="F124" s="63" t="str">
+        <x:v>theme_3d</x:v>
+      </x:c>
+      <x:c r="G124" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H124" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I124" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J124" s="63" t="str">
+        <x:v>冷钢边境</x:v>
+      </x:c>
+      <x:c r="K124" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L124" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M124" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N124" s="63" t="str">
+        <x:v>DungeonTheme3D Resource</x:v>
+      </x:c>
+      <x:c r="O124" s="63" t="str">
+        <x:v>assets/art/environments/dungeon_3d/env_iron_frontier_kit_top3d_v001.tres</x:v>
+      </x:c>
+      <x:c r="P124" s="63" t="str">
+        <x:v>scenes/levels3d/IronFrontier3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q124" s="63" t="str">
+        <x:v>冷钢;冷蓝;边境;雾;灯光</x:v>
+      </x:c>
+      <x:c r="R124" s="63" t="str">
+        <x:f>LOWER(TRIM(C124)&amp;"|"&amp;TRIM(D124)&amp;"|"&amp;TRIM(E124)&amp;"|"&amp;TRIM(F124)&amp;"|"&amp;TRIM(H124)&amp;"|"&amp;TRIM(I124))</x:f>
+        <x:v>场景|biome|iron_frontier|theme_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S124" s="63" t="str">
+        <x:f>IF(A124="","",IF(COUNTIF($R$6:$R$139,R124)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T124" s="63" t="str">
+        <x:v>a3c6e7e5433928b790e1fa0fe5124beaeb5ab579f2d376aa35a1be25b6736b58</x:v>
+      </x:c>
+      <x:c r="U124" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V124" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W124" s="63" t="str">
+        <x:v>原创程序配置</x:v>
+      </x:c>
+      <x:c r="X124" s="63" t="str">
+        <x:v>只保存3D色彩/雾/灯光/家具倾向；玩法读取MapThemeProfile</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="34" customHeight="1">
+      <x:c r="A125" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUST-FOUNDRY-3D</x:v>
+      </x:c>
+      <x:c r="B125" s="63" t="str">
+        <x:v>锈蚀铸造厂3D主题资源</x:v>
+      </x:c>
+      <x:c r="C125" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D125" s="63" t="str">
+        <x:v>biome</x:v>
+      </x:c>
+      <x:c r="E125" s="63" t="str">
+        <x:v>rust_foundry</x:v>
+      </x:c>
+      <x:c r="F125" s="63" t="str">
+        <x:v>theme_3d</x:v>
+      </x:c>
+      <x:c r="G125" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H125" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I125" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J125" s="63" t="str">
+        <x:v>锈蚀铸造厂</x:v>
+      </x:c>
+      <x:c r="K125" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L125" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M125" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N125" s="63" t="str">
+        <x:v>DungeonTheme3D Resource</x:v>
+      </x:c>
+      <x:c r="O125" s="63" t="str">
+        <x:v>assets/art/environments/dungeon_3d/env_rust_foundry_kit_top3d_v001.tres</x:v>
+      </x:c>
+      <x:c r="P125" s="63" t="str">
+        <x:v>scenes/levels3d/RustFoundry3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q125" s="63" t="str">
+        <x:v>锈蚀;铸造;橙光;工业</x:v>
+      </x:c>
+      <x:c r="R125" s="63" t="str">
+        <x:f>LOWER(TRIM(C125)&amp;"|"&amp;TRIM(D125)&amp;"|"&amp;TRIM(E125)&amp;"|"&amp;TRIM(F125)&amp;"|"&amp;TRIM(H125)&amp;"|"&amp;TRIM(I125))</x:f>
+        <x:v>场景|biome|rust_foundry|theme_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S125" s="63" t="str">
+        <x:f>IF(A125="","",IF(COUNTIF($R$6:$R$139,R125)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T125" s="63" t="str">
+        <x:v>0c14c1dd5a5b8edcb51fa5bb024666d845611bfd87c3c4ee0ded56c4614010a8</x:v>
+      </x:c>
+      <x:c r="U125" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V125" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W125" s="63" t="str">
+        <x:v>原创程序配置</x:v>
+      </x:c>
+      <x:c r="X125" s="63" t="str">
+        <x:v>复用通用房间根；主题资源不复制玩法规则</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="34" customHeight="1">
+      <x:c r="A126" s="63" t="str">
+        <x:v>ENV-DUNGEON-SPORE-DEPTHS-3D</x:v>
+      </x:c>
+      <x:c r="B126" s="63" t="str">
+        <x:v>孢子深层3D主题资源</x:v>
+      </x:c>
+      <x:c r="C126" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D126" s="63" t="str">
+        <x:v>biome</x:v>
+      </x:c>
+      <x:c r="E126" s="63" t="str">
+        <x:v>spore_depths</x:v>
+      </x:c>
+      <x:c r="F126" s="63" t="str">
+        <x:v>theme_3d</x:v>
+      </x:c>
+      <x:c r="G126" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H126" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I126" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J126" s="63" t="str">
+        <x:v>孢子深层</x:v>
+      </x:c>
+      <x:c r="K126" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L126" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M126" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N126" s="63" t="str">
+        <x:v>DungeonTheme3D Resource</x:v>
+      </x:c>
+      <x:c r="O126" s="63" t="str">
+        <x:v>assets/art/environments/dungeon_3d/env_spore_depths_kit_top3d_v001.tres</x:v>
+      </x:c>
+      <x:c r="P126" s="63" t="str">
+        <x:v>scenes/levels3d/SporeDepths3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q126" s="63" t="str">
+        <x:v>孢子;病绿;地下;异化</x:v>
+      </x:c>
+      <x:c r="R126" s="63" t="str">
+        <x:f>LOWER(TRIM(C126)&amp;"|"&amp;TRIM(D126)&amp;"|"&amp;TRIM(E126)&amp;"|"&amp;TRIM(F126)&amp;"|"&amp;TRIM(H126)&amp;"|"&amp;TRIM(I126))</x:f>
+        <x:v>场景|biome|spore_depths|theme_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S126" s="63" t="str">
+        <x:f>IF(A126="","",IF(COUNTIF($R$6:$R$139,R126)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T126" s="63" t="str">
+        <x:v>bbd5cc04028e3962ce9eb8ea04c1c06157d128b5dbad1cea64bed7b4a02e7689</x:v>
+      </x:c>
+      <x:c r="U126" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V126" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W126" s="63" t="str">
+        <x:v>原创程序配置</x:v>
+      </x:c>
+      <x:c r="X126" s="63" t="str">
+        <x:v>复用通用房间根；主题资源不复制玩法规则</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="34" customHeight="1">
+      <x:c r="A127" s="63" t="str">
+        <x:v>ENV-DUNGEON-ABYSS-ARCHIVE-3D</x:v>
+      </x:c>
+      <x:c r="B127" s="63" t="str">
+        <x:v>深渊档案库3D主题资源</x:v>
+      </x:c>
+      <x:c r="C127" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D127" s="63" t="str">
+        <x:v>biome</x:v>
+      </x:c>
+      <x:c r="E127" s="63" t="str">
+        <x:v>abyss_archive</x:v>
+      </x:c>
+      <x:c r="F127" s="63" t="str">
+        <x:v>theme_3d</x:v>
+      </x:c>
+      <x:c r="G127" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H127" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I127" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J127" s="63" t="str">
+        <x:v>深渊档案库</x:v>
+      </x:c>
+      <x:c r="K127" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L127" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M127" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N127" s="63" t="str">
+        <x:v>DungeonTheme3D Resource</x:v>
+      </x:c>
+      <x:c r="O127" s="63" t="str">
+        <x:v>assets/art/environments/dungeon_3d/env_abyss_archive_kit_top3d_v001.tres</x:v>
+      </x:c>
+      <x:c r="P127" s="63" t="str">
+        <x:v>scenes/levels3d/AbyssArchive3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q127" s="63" t="str">
+        <x:v>深渊;档案;紫光;禁区</x:v>
+      </x:c>
+      <x:c r="R127" s="63" t="str">
+        <x:f>LOWER(TRIM(C127)&amp;"|"&amp;TRIM(D127)&amp;"|"&amp;TRIM(E127)&amp;"|"&amp;TRIM(F127)&amp;"|"&amp;TRIM(H127)&amp;"|"&amp;TRIM(I127))</x:f>
+        <x:v>场景|biome|abyss_archive|theme_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S127" s="63" t="str">
+        <x:f>IF(A127="","",IF(COUNTIF($R$6:$R$139,R127)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T127" s="63" t="str">
+        <x:v>fb276fb1586de1b69d306ff894800f51da600b8dfb2780cf8bc8d22695ad3a52</x:v>
+      </x:c>
+      <x:c r="U127" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V127" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W127" s="63" t="str">
+        <x:v>原创程序配置</x:v>
+      </x:c>
+      <x:c r="X127" s="63" t="str">
+        <x:v>复用通用房间根；主题资源不复制玩法规则</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="34" customHeight="1">
+      <x:c r="A128" s="63" t="str">
+        <x:v>PRP-WASTELAND-LIGHT-3D</x:v>
+      </x:c>
+      <x:c r="B128" s="63" t="str">
+        <x:v>废土灯具3D通用模块</x:v>
+      </x:c>
+      <x:c r="C128" s="63" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D128" s="63" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="E128" s="63" t="str">
+        <x:v>wasteland_light</x:v>
+      </x:c>
+      <x:c r="F128" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G128" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H128" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I128" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J128" s="63" t="str">
+        <x:v>关卡/靶场照明</x:v>
+      </x:c>
+      <x:c r="K128" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L128" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M128" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N128" s="63" t="str">
+        <x:v>PackedScene/OmniLight3D</x:v>
+      </x:c>
+      <x:c r="O128" s="63" t="str">
+        <x:v>assets/art/props/dungeon_3d/prp_wasteland_light_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P128" s="63" t="str">
+        <x:v>src/world3d/WastelandLight3D.gd</x:v>
+      </x:c>
+      <x:c r="Q128" s="63" t="str">
+        <x:v>灯具;光池;故障灯;废土</x:v>
+      </x:c>
+      <x:c r="R128" s="63" t="str">
+        <x:f>LOWER(TRIM(C128)&amp;"|"&amp;TRIM(D128)&amp;"|"&amp;TRIM(E128)&amp;"|"&amp;TRIM(F128)&amp;"|"&amp;TRIM(H128)&amp;"|"&amp;TRIM(I128))</x:f>
+        <x:v>场景道具|light|wasteland_light|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S128" s="63" t="str">
+        <x:f>IF(A128="","",IF(COUNTIF($R$6:$R$139,R128)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T128" s="63" t="str">
+        <x:v>0a6ec0add8b6e01b83f4dbaae421ff0dc69ed08648d304bac061f540af27d99b</x:v>
+      </x:c>
+      <x:c r="U128" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V128" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W128" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X128" s="63" t="str">
+        <x:v>灯架、灯罩、真实光源、低频故障与地面光池同一根</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="34" customHeight="1">
+      <x:c r="A129" s="63" t="str">
+        <x:v>PRP-ROOM-FURNITURE-3D</x:v>
+      </x:c>
+      <x:c r="B129" s="63" t="str">
+        <x:v>房间家具3D通用模块</x:v>
+      </x:c>
+      <x:c r="C129" s="63" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D129" s="63" t="str">
+        <x:v>furniture</x:v>
+      </x:c>
+      <x:c r="E129" s="63" t="str">
+        <x:v>room_furniture</x:v>
+      </x:c>
+      <x:c r="F129" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G129" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H129" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I129" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J129" s="63" t="str">
+        <x:v>全部3D房间</x:v>
+      </x:c>
+      <x:c r="K129" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L129" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M129" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N129" s="63" t="str">
+        <x:v>PackedScene/类型与尺寸配置</x:v>
+      </x:c>
+      <x:c r="O129" s="63" t="str">
+        <x:v>assets/art/props/dungeon_3d/prp_room_furniture_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P129" s="63" t="str">
+        <x:v>src/world3d/RoomFurniture3D.gd</x:v>
+      </x:c>
+      <x:c r="Q129" s="63" t="str">
+        <x:v>家具;小中大;箱柜;工作台</x:v>
+      </x:c>
+      <x:c r="R129" s="63" t="str">
+        <x:f>LOWER(TRIM(C129)&amp;"|"&amp;TRIM(D129)&amp;"|"&amp;TRIM(E129)&amp;"|"&amp;TRIM(F129)&amp;"|"&amp;TRIM(H129)&amp;"|"&amp;TRIM(I129))</x:f>
+        <x:v>场景道具|furniture|room_furniture|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S129" s="63" t="str">
+        <x:f>IF(A129="","",IF(COUNTIF($R$6:$R$139,R129)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T129" s="63" t="str">
+        <x:v>a78a7eaac02ce39add97d8a57754cc86ea34e740e24e0e901f4e037198a086e9</x:v>
+      </x:c>
+      <x:c r="U129" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V129" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W129" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X129" s="63" t="str">
+        <x:v>11类轮廓；small/medium/large影响占地与碰撞</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="34" customHeight="1">
+      <x:c r="A130" s="63" t="str">
+        <x:v>PRP-SEARCH-CONTAINER-3D</x:v>
+      </x:c>
+      <x:c r="B130" s="63" t="str">
+        <x:v>可搜索容器3D通用模块</x:v>
+      </x:c>
+      <x:c r="C130" s="63" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D130" s="63" t="str">
+        <x:v>container</x:v>
+      </x:c>
+      <x:c r="E130" s="63" t="str">
+        <x:v>search_container</x:v>
+      </x:c>
+      <x:c r="F130" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G130" s="63" t="str">
+        <x:v>PRP-ROOM-FURNITURE-3D</x:v>
+      </x:c>
+      <x:c r="H130" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I130" s="63" t="str">
+        <x:v>closed_opened</x:v>
+      </x:c>
+      <x:c r="J130" s="63" t="str">
+        <x:v>搜索房/仓储/事件</x:v>
+      </x:c>
+      <x:c r="K130" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L130" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M130" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N130" s="63" t="str">
+        <x:v>PackedScene/搜索状态</x:v>
+      </x:c>
+      <x:c r="O130" s="63" t="str">
+        <x:v>assets/art/props/dungeon_3d/prp_search_container_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P130" s="63" t="str">
+        <x:v>src/world3d/RoomFurniture3D.gd</x:v>
+      </x:c>
+      <x:c r="Q130" s="63" t="str">
+        <x:v>搜索;容器;战利品;小中大</x:v>
+      </x:c>
+      <x:c r="R130" s="63" t="str">
+        <x:f>LOWER(TRIM(C130)&amp;"|"&amp;TRIM(D130)&amp;"|"&amp;TRIM(E130)&amp;"|"&amp;TRIM(F130)&amp;"|"&amp;TRIM(H130)&amp;"|"&amp;TRIM(I130))</x:f>
+        <x:v>场景道具|container|search_container|root_3d|俯视3d|closed_opened</x:v>
+      </x:c>
+      <x:c r="S130" s="63" t="str">
+        <x:f>IF(A130="","",IF(COUNTIF($R$6:$R$139,R130)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T130" s="63" t="str">
+        <x:v>2c0852d86e7c0e635e76197ff8d2f6a030daa186f760dfb339d3fdeddf3c192d</x:v>
+      </x:c>
+      <x:c r="U130" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V130" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W130" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X130" s="63" t="str">
+        <x:v>搜索为家具状态与配置，不建立关卡局部重复模型</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="34" customHeight="1">
+      <x:c r="A131" s="63" t="str">
+        <x:v>PRP-SERVICE-STATION-3D</x:v>
+      </x:c>
+      <x:c r="B131" s="63" t="str">
+        <x:v>废土服务终端3D模块</x:v>
+      </x:c>
+      <x:c r="C131" s="63" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D131" s="63" t="str">
+        <x:v>facility</x:v>
+      </x:c>
+      <x:c r="E131" s="63" t="str">
+        <x:v>service_station</x:v>
+      </x:c>
+      <x:c r="F131" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G131" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H131" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I131" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J131" s="63" t="str">
+        <x:v>商店/升级/事件/重置</x:v>
+      </x:c>
+      <x:c r="K131" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L131" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M131" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N131" s="63" t="str">
+        <x:v>PackedScene/程序组件</x:v>
+      </x:c>
+      <x:c r="O131" s="63" t="str">
+        <x:v>assets/art/props/dungeon_3d/prp_service_station_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P131" s="63" t="str">
+        <x:v>src/world3d/ServiceStation3D.gd</x:v>
+      </x:c>
+      <x:c r="Q131" s="63" t="str">
+        <x:v>终端;商店;升级;事件;重置</x:v>
+      </x:c>
+      <x:c r="R131" s="63" t="str">
+        <x:f>LOWER(TRIM(C131)&amp;"|"&amp;TRIM(D131)&amp;"|"&amp;TRIM(E131)&amp;"|"&amp;TRIM(F131)&amp;"|"&amp;TRIM(H131)&amp;"|"&amp;TRIM(I131))</x:f>
+        <x:v>场景道具|facility|service_station|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S131" s="63" t="str">
+        <x:f>IF(A131="","",IF(COUNTIF($R$6:$R$139,R131)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T131" s="63" t="str">
+        <x:v>da288e4a8ffc005053741d2eda3bbcbf2f6ad34c32c6657e35d0ddf62b837be4</x:v>
+      </x:c>
+      <x:c r="U131" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V131" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W131" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X131" s="63" t="str">
+        <x:v>四种服务行为复用同一视觉与交互组件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="34" customHeight="1">
+      <x:c r="A132" s="63" t="str">
+        <x:v>PRP-EXTRACTION-BEACON-3D</x:v>
+      </x:c>
+      <x:c r="B132" s="63" t="str">
+        <x:v>撤离信标3D模块</x:v>
+      </x:c>
+      <x:c r="C132" s="63" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D132" s="63" t="str">
+        <x:v>facility</x:v>
+      </x:c>
+      <x:c r="E132" s="63" t="str">
+        <x:v>extraction_beacon</x:v>
+      </x:c>
+      <x:c r="F132" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G132" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H132" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I132" s="63" t="str">
+        <x:v>locked_active_done</x:v>
+      </x:c>
+      <x:c r="J132" s="63" t="str">
+        <x:v>四主题撤离房</x:v>
+      </x:c>
+      <x:c r="K132" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L132" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M132" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N132" s="63" t="str">
+        <x:v>PackedScene/程序组件</x:v>
+      </x:c>
+      <x:c r="O132" s="63" t="str">
+        <x:v>assets/art/props/dungeon_3d/prp_extraction_beacon_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P132" s="63" t="str">
+        <x:v>src/world3d/ExtractionBeacon3D.gd</x:v>
+      </x:c>
+      <x:c r="Q132" s="63" t="str">
+        <x:v>撤离;信标;倒计时;Boss解锁</x:v>
+      </x:c>
+      <x:c r="R132" s="63" t="str">
+        <x:f>LOWER(TRIM(C132)&amp;"|"&amp;TRIM(D132)&amp;"|"&amp;TRIM(E132)&amp;"|"&amp;TRIM(F132)&amp;"|"&amp;TRIM(H132)&amp;"|"&amp;TRIM(I132))</x:f>
+        <x:v>场景道具|facility|extraction_beacon|root_3d|俯视3d|locked_active_done</x:v>
+      </x:c>
+      <x:c r="S132" s="63" t="str">
+        <x:f>IF(A132="","",IF(COUNTIF($R$6:$R$139,R132)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T132" s="63" t="str">
+        <x:v>f2638fdaca3f9542e918a56750bda04a5828b18a763569eb16a36619e9e336b4</x:v>
+      </x:c>
+      <x:c r="U132" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V132" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W132" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X132" s="63" t="str">
+        <x:v>锁定/同步/取消/完成四段生命周期</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="34" customHeight="1">
+      <x:c r="A133" s="63" t="str">
+        <x:v>VFX-HAZARD-FIELD-3D</x:v>
+      </x:c>
+      <x:c r="B133" s="63" t="str">
+        <x:v>房间危险场3D特效</x:v>
+      </x:c>
+      <x:c r="C133" s="63" t="str">
+        <x:v>特效</x:v>
+      </x:c>
+      <x:c r="D133" s="63" t="str">
+        <x:v>environment</x:v>
+      </x:c>
+      <x:c r="E133" s="63" t="str">
+        <x:v>hazard_field</x:v>
+      </x:c>
+      <x:c r="F133" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G133" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H133" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I133" s="63" t="str">
+        <x:v>active</x:v>
+      </x:c>
+      <x:c r="J133" s="63" t="str">
+        <x:v>陷阱房</x:v>
+      </x:c>
+      <x:c r="K133" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L133" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M133" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N133" s="63" t="str">
+        <x:v>PackedScene/程序环形特效</x:v>
+      </x:c>
+      <x:c r="O133" s="63" t="str">
+        <x:v>assets/art/vfx/environment_3d/vfx_hazard_field_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P133" s="63" t="str">
+        <x:v>src/world3d/HazardField3D.gd</x:v>
+      </x:c>
+      <x:c r="Q133" s="63" t="str">
+        <x:v>危险区;陷阱;范围伤害;3D</x:v>
+      </x:c>
+      <x:c r="R133" s="63" t="str">
+        <x:f>LOWER(TRIM(C133)&amp;"|"&amp;TRIM(D133)&amp;"|"&amp;TRIM(E133)&amp;"|"&amp;TRIM(F133)&amp;"|"&amp;TRIM(H133)&amp;"|"&amp;TRIM(I133))</x:f>
+        <x:v>特效|environment|hazard_field|root_3d|俯视3d|active</x:v>
+      </x:c>
+      <x:c r="S133" s="63" t="str">
+        <x:f>IF(A133="","",IF(COUNTIF($R$6:$R$139,R133)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T133" s="63" t="str">
+        <x:v>66ab8d6bc0e2729ca56c7f3c46a588e5f74890cfdf02b90de1fdc46fd1a67648</x:v>
+      </x:c>
+      <x:c r="U133" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V133" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W133" s="63" t="str">
+        <x:v>原创程序特效</x:v>
+      </x:c>
+      <x:c r="X133" s="63" t="str">
+        <x:v>颜色、半径与伤害可按主题配置</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="34" customHeight="1">
+      <x:c r="A134" s="63" t="str">
+        <x:v>WPN-GUN-KIT-3D</x:v>
+      </x:c>
+      <x:c r="B134" s="63" t="str">
+        <x:v>枪械3D通用模型套件</x:v>
+      </x:c>
+      <x:c r="C134" s="63" t="str">
+        <x:v>枪械</x:v>
+      </x:c>
+      <x:c r="D134" s="63" t="str">
+        <x:v>gunbody</x:v>
+      </x:c>
+      <x:c r="E134" s="63" t="str">
+        <x:v>blueprint_gun_catalog</x:v>
+      </x:c>
+      <x:c r="F134" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G134" s="63"/>
+      <x:c r="H134" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I134" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J134" s="63" t="str">
+        <x:v>玩家/靶场/全部副本</x:v>
+      </x:c>
+      <x:c r="K134" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L134" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M134" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N134" s="63" t="str">
+        <x:v>PackedScene/7枪配置模型</x:v>
+      </x:c>
+      <x:c r="O134" s="63" t="str">
+        <x:v>assets/art/weapons/weapon_3d/wpn_gun_kit_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P134" s="63" t="str">
+        <x:v>src/combat3d/WeaponModel3D.gd</x:v>
+      </x:c>
+      <x:c r="Q134" s="63" t="str">
+        <x:v>枪械;7枪身;8弹药;后坐力;枪口</x:v>
+      </x:c>
+      <x:c r="R134" s="63" t="str">
+        <x:f>LOWER(TRIM(C134)&amp;"|"&amp;TRIM(D134)&amp;"|"&amp;TRIM(E134)&amp;"|"&amp;TRIM(F134)&amp;"|"&amp;TRIM(H134)&amp;"|"&amp;TRIM(I134))</x:f>
+        <x:v>枪械|gunbody|blueprint_gun_catalog|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S134" s="63" t="str">
+        <x:f>IF(A134="","",IF(COUNTIF($R$6:$R$139,R134)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T134" s="63" t="str">
+        <x:v>e13801540404433f6fc5f00faa0f523b804d18ec7fa30c0f6c15fab48f1ec4c9</x:v>
+      </x:c>
+      <x:c r="U134" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V134" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W134" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X134" s="63" t="str">
+        <x:v>读取BlueprintRegistry唯一目录；覆盖56种组合；枪局部后坐力不带动手</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="34" customHeight="1">
+      <x:c r="A135" s="63" t="str">
+        <x:v>ENM-ECOSYSTEM-KIT-3D</x:v>
+      </x:c>
+      <x:c r="B135" s="63" t="str">
+        <x:v>七类怪物3D生态套件</x:v>
+      </x:c>
+      <x:c r="C135" s="63" t="str">
+        <x:v>敌人</x:v>
+      </x:c>
+      <x:c r="D135" s="63" t="str">
+        <x:v>normal_elite_boss</x:v>
+      </x:c>
+      <x:c r="E135" s="63" t="str">
+        <x:v>enemy_ecosystem</x:v>
+      </x:c>
+      <x:c r="F135" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G135" s="63"/>
+      <x:c r="H135" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I135" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J135" s="63" t="str">
+        <x:v>四主题战斗房</x:v>
+      </x:c>
+      <x:c r="K135" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L135" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M135" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N135" s="63" t="str">
+        <x:v>PackedScene/模块敌人</x:v>
+      </x:c>
+      <x:c r="O135" s="63" t="str">
+        <x:v>assets/art/enemies/enemy_3d/enm_ecosystem_kit_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P135" s="63" t="str">
+        <x:v>src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="Q135" s="63" t="str">
+        <x:v>怪物;七类;核心;外壳;附肢;状态</x:v>
+      </x:c>
+      <x:c r="R135" s="63" t="str">
+        <x:f>LOWER(TRIM(C135)&amp;"|"&amp;TRIM(D135)&amp;"|"&amp;TRIM(E135)&amp;"|"&amp;TRIM(F135)&amp;"|"&amp;TRIM(H135)&amp;"|"&amp;TRIM(I135))</x:f>
+        <x:v>敌人|normal_elite_boss|enemy_ecosystem|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S135" s="63" t="str">
+        <x:f>IF(A135="","",IF(COUNTIF($R$6:$R$139,R135)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T135" s="63" t="str">
+        <x:v>d9d8a49bed3fdcb863bad72f60be1f774309c7dda52753f5efb3d4e56159c12d</x:v>
+      </x:c>
+      <x:c r="U135" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V135" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W135" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X135" s="63" t="str">
+        <x:v>追猎/远程/召唤/盾甲/自爆/伏击/Boss；统一七态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="34" customHeight="1">
+      <x:c r="A136" s="63" t="str">
+        <x:v>VFX-COMBAT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="B136" s="63" t="str">
+        <x:v>战斗反馈3D通用特效套件</x:v>
+      </x:c>
+      <x:c r="C136" s="63" t="str">
+        <x:v>特效</x:v>
+      </x:c>
+      <x:c r="D136" s="63" t="str">
+        <x:v>combat</x:v>
+      </x:c>
+      <x:c r="E136" s="63" t="str">
+        <x:v>combat_feedback</x:v>
+      </x:c>
+      <x:c r="F136" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G136" s="63"/>
+      <x:c r="H136" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I136" s="63" t="str">
+        <x:v>muzzle_impact_damage_explosion</x:v>
+      </x:c>
+      <x:c r="J136" s="63" t="str">
+        <x:v>枪械/敌人/关卡</x:v>
+      </x:c>
+      <x:c r="K136" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L136" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M136" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N136" s="63" t="str">
+        <x:v>PackedScene/参数化特效</x:v>
+      </x:c>
+      <x:c r="O136" s="63" t="str">
+        <x:v>assets/art/vfx/combat_3d/vfx_combat_kit_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P136" s="63" t="str">
+        <x:v>src/combat3d/CombatEffect3D.gd</x:v>
+      </x:c>
+      <x:c r="Q136" s="63" t="str">
+        <x:v>枪口;命中;伤害;爆炸;3D</x:v>
+      </x:c>
+      <x:c r="R136" s="63" t="str">
+        <x:f>LOWER(TRIM(C136)&amp;"|"&amp;TRIM(D136)&amp;"|"&amp;TRIM(E136)&amp;"|"&amp;TRIM(F136)&amp;"|"&amp;TRIM(H136)&amp;"|"&amp;TRIM(I136))</x:f>
+        <x:v>特效|combat|combat_feedback|root_3d|俯视3d|muzzle_impact_damage_explosion</x:v>
+      </x:c>
+      <x:c r="S136" s="63" t="str">
+        <x:f>IF(A136="","",IF(COUNTIF($R$6:$R$139,R136)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T136" s="63" t="str">
+        <x:v>2ee5109b1876ea2114ac5c73b4bd0e2fc0348e1209a9d2ca16bc8ef9834ff357</x:v>
+      </x:c>
+      <x:c r="U136" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V136" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W136" s="63" t="str">
+        <x:v>原创程序特效</x:v>
+      </x:c>
+      <x:c r="X136" s="63" t="str">
+        <x:v>effect kind、颜色与尺寸参数化，避免每把枪复制特效</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="34" customHeight="1">
+      <x:c r="A137" s="63" t="str">
+        <x:v>ENV-TRAINING-RANGE-KIT-3D</x:v>
+      </x:c>
+      <x:c r="B137" s="63" t="str">
+        <x:v>独立3D训练靶场套件</x:v>
+      </x:c>
+      <x:c r="C137" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D137" s="63" t="str">
+        <x:v>training_range</x:v>
+      </x:c>
+      <x:c r="E137" s="63" t="str">
+        <x:v>training_range</x:v>
+      </x:c>
+      <x:c r="F137" s="63" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G137" s="63"/>
+      <x:c r="H137" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I137" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J137" s="63" t="str">
+        <x:v>独立训练地图</x:v>
+      </x:c>
+      <x:c r="K137" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L137" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M137" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N137" s="63" t="str">
+        <x:v>PackedScene/程序环境</x:v>
+      </x:c>
+      <x:c r="O137" s="63" t="str">
+        <x:v>assets/art/environments/training_range_3d/env_training_range_kit_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P137" s="63" t="str">
+        <x:v>scenes/TrainingRange3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q137" s="63" t="str">
+        <x:v>靶场;射击道;货架;56组合;三类靶</x:v>
+      </x:c>
+      <x:c r="R137" s="63" t="str">
+        <x:f>LOWER(TRIM(C137)&amp;"|"&amp;TRIM(D137)&amp;"|"&amp;TRIM(E137)&amp;"|"&amp;TRIM(F137)&amp;"|"&amp;TRIM(H137)&amp;"|"&amp;TRIM(I137))</x:f>
+        <x:v>场景|training_range|training_range|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S137" s="63" t="str">
+        <x:f>IF(A137="","",IF(COUNTIF($R$6:$R$139,R137)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T137" s="63" t="str">
+        <x:v>4d1153bc736fab0790300f171beef8435002670f3789d6434e966bca0a79d28e</x:v>
+      </x:c>
+      <x:c r="U137" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V137" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W137" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X137" s="63" t="str">
+        <x:v>15货架、三射击道、三靶标、重置与返回；BaseData隔离</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="34" customHeight="1">
+      <x:c r="A138" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D-PREVIEW</x:v>
+      </x:c>
+      <x:c r="B138" s="63" t="str">
+        <x:v>3D关卡运行时验收预览</x:v>
+      </x:c>
+      <x:c r="C138" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D138" s="63" t="str">
+        <x:v>review_board</x:v>
+      </x:c>
+      <x:c r="E138" s="63" t="str">
+        <x:v>dungeon_runtime</x:v>
+      </x:c>
+      <x:c r="F138" s="63" t="str">
+        <x:v>preview_3d</x:v>
+      </x:c>
+      <x:c r="G138" s="63" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H138" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I138" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J138" s="63" t="str">
+        <x:v>评审与资产QA</x:v>
+      </x:c>
+      <x:c r="K138" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L138" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M138" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N138" s="63" t="str">
+        <x:v>1280×720 PNG</x:v>
+      </x:c>
+      <x:c r="O138" s="63" t="str">
+        <x:v>assets/art/environments/dungeon_3d/env_dungeon_runtime_preview_top3d_v001.png</x:v>
+      </x:c>
+      <x:c r="P138" s="63" t="str">
+        <x:v>verify_full_3d_visual.tscn</x:v>
+      </x:c>
+      <x:c r="Q138" s="63" t="str">
+        <x:v>3D关卡;预览;灯光;战斗;QA</x:v>
+      </x:c>
+      <x:c r="R138" s="63" t="str">
+        <x:f>LOWER(TRIM(C138)&amp;"|"&amp;TRIM(D138)&amp;"|"&amp;TRIM(E138)&amp;"|"&amp;TRIM(F138)&amp;"|"&amp;TRIM(H138)&amp;"|"&amp;TRIM(I138))</x:f>
+        <x:v>场景|review_board|dungeon_runtime|preview_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S138" s="63" t="str">
+        <x:f>IF(A138="","",IF(COUNTIF($R$6:$R$139,R138)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T138" s="63" t="str">
+        <x:v>b6001154cf08404addb31b69dd38eaba41abe2a82ff6d2408bb5af8fe7a105b0</x:v>
+      </x:c>
+      <x:c r="U138" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V138" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W138" s="63" t="str">
+        <x:v>项目运行截图</x:v>
+      </x:c>
+      <x:c r="X138" s="63" t="str">
+        <x:v>真实GPU窗口检查房间、灯池、家具、角色、怪物和战斗可读性</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="34" customHeight="1">
+      <x:c r="A139" s="63" t="str">
+        <x:v>ENV-TRAINING-RANGE-3D-PREVIEW</x:v>
+      </x:c>
+      <x:c r="B139" s="63" t="str">
+        <x:v>3D训练靶场验收预览</x:v>
+      </x:c>
+      <x:c r="C139" s="63" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D139" s="63" t="str">
+        <x:v>review_board</x:v>
+      </x:c>
+      <x:c r="E139" s="63" t="str">
+        <x:v>training_range</x:v>
+      </x:c>
+      <x:c r="F139" s="63" t="str">
+        <x:v>preview_3d</x:v>
+      </x:c>
+      <x:c r="G139" s="63" t="str">
+        <x:v>ENV-TRAINING-RANGE-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H139" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I139" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J139" s="63" t="str">
+        <x:v>评审与资产QA</x:v>
+      </x:c>
+      <x:c r="K139" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L139" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M139" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N139" s="63" t="str">
+        <x:v>1280×720 PNG</x:v>
+      </x:c>
+      <x:c r="O139" s="63" t="str">
+        <x:v>assets/art/environments/training_range_3d/env_training_range_preview_top3d_v001.png</x:v>
+      </x:c>
+      <x:c r="P139" s="63" t="str">
+        <x:v>verify_training_range_3d_visual.tscn</x:v>
+      </x:c>
+      <x:c r="Q139" s="63" t="str">
+        <x:v>3D靶场;预览;射击道;目标;QA</x:v>
+      </x:c>
+      <x:c r="R139" s="63" t="str">
+        <x:f>LOWER(TRIM(C139)&amp;"|"&amp;TRIM(D139)&amp;"|"&amp;TRIM(E139)&amp;"|"&amp;TRIM(F139)&amp;"|"&amp;TRIM(H139)&amp;"|"&amp;TRIM(I139))</x:f>
+        <x:v>场景|review_board|training_range|preview_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S139" s="63" t="str">
+        <x:f>IF(A139="","",IF(COUNTIF($R$6:$R$139,R139)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T139" s="63" t="str">
+        <x:v>51b63097607e69009e9b2e5ed9315b3c642cdc05e823a2fee547cb0bb1ad8377</x:v>
+      </x:c>
+      <x:c r="U139" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V139" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="W139" s="63" t="str">
+        <x:v>项目运行截图</x:v>
+      </x:c>
+      <x:c r="X139" s="63" t="str">
+        <x:v>真实GPU窗口检查三条射击道、三类靶、枪弹组合区与灯光</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8543,7 +10571,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89c057befe3b4ede"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2abd959a34ee4d7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8983,6 +11011,252 @@
       </x:c>
       <x:c r="M13" s="37" t="str">
         <x:v>必要时高于双手</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="34" customHeight="1">
+      <x:c r="A14" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B14" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="C14" s="63" t="str">
+        <x:v>Avatar3D/CapsuleAvatar3D/VisualRoot</x:v>
+      </x:c>
+      <x:c r="D14" s="63" t="str">
+        <x:v>player_root</x:v>
+      </x:c>
+      <x:c r="E14" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F14" s="63" t="str">
+        <x:v>Node3D</x:v>
+      </x:c>
+      <x:c r="G14" s="63" t="str">
+        <x:v>(0,0,0)</x:v>
+      </x:c>
+      <x:c r="H14" s="63" t="str">
+        <x:v>整体随准星绕Y轴</x:v>
+      </x:c>
+      <x:c r="I14" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="63" t="str">
+        <x:v>六态整体变换</x:v>
+      </x:c>
+      <x:c r="K14" s="63" t="str">
+        <x:v>3D表现根</x:v>
+      </x:c>
+      <x:c r="L14" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M14" s="63" t="str">
+        <x:v>与2D共用状态ID；摄像机不跟随VisualRoot旋转</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="34" customHeight="1">
+      <x:c r="A15" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B15" s="63" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="C15" s="63" t="str">
+        <x:v>VisualRoot/Body</x:v>
+      </x:c>
+      <x:c r="D15" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E15" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F15" s="63" t="str">
+        <x:v>CapsuleMesh</x:v>
+      </x:c>
+      <x:c r="G15" s="63" t="str">
+        <x:v>(0,0.88,0)</x:v>
+      </x:c>
+      <x:c r="H15" s="63" t="str">
+        <x:v>随root</x:v>
+      </x:c>
+      <x:c r="I15" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J15" s="63" t="str">
+        <x:v>呼吸/移动压缩/死亡倾倒</x:v>
+      </x:c>
+      <x:c r="K15" s="63" t="str">
+        <x:v>防护服主体</x:v>
+      </x:c>
+      <x:c r="L15" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M15" s="63" t="str">
+        <x:v>无腿、无脚、无手臂</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="34" customHeight="1">
+      <x:c r="A16" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B16" s="63" t="str">
+        <x:v>scarf</x:v>
+      </x:c>
+      <x:c r="C16" s="63" t="str">
+        <x:v>VisualRoot/Scarf</x:v>
+      </x:c>
+      <x:c r="D16" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E16" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F16" s="63" t="str">
+        <x:v>Cylinder+Box</x:v>
+      </x:c>
+      <x:c r="G16" s="63" t="str">
+        <x:v>(0,1.43,0)</x:v>
+      </x:c>
+      <x:c r="H16" s="63" t="str">
+        <x:v>随root + 轻摆</x:v>
+      </x:c>
+      <x:c r="I16" s="63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J16" s="63" t="str">
+        <x:v>移动滞后/冲刺飘动</x:v>
+      </x:c>
+      <x:c r="K16" s="63" t="str">
+        <x:v>身份配件</x:v>
+      </x:c>
+      <x:c r="L16" s="63" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="M16" s="63" t="str">
+        <x:v>独立红围巾组件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="34" customHeight="1">
+      <x:c r="A17" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B17" s="63" t="str">
+        <x:v>head</x:v>
+      </x:c>
+      <x:c r="C17" s="63" t="str">
+        <x:v>VisualRoot/Head</x:v>
+      </x:c>
+      <x:c r="D17" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E17" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F17" s="63" t="str">
+        <x:v>SphereMesh</x:v>
+      </x:c>
+      <x:c r="G17" s="63" t="str">
+        <x:v>(0,1.84,-0.01)</x:v>
+      </x:c>
+      <x:c r="H17" s="63" t="str">
+        <x:v>随root</x:v>
+      </x:c>
+      <x:c r="I17" s="63" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J17" s="63" t="str">
+        <x:v>呼吸滞后/受击/死亡</x:v>
+      </x:c>
+      <x:c r="K17" s="63" t="str">
+        <x:v>头壳/传感器</x:v>
+      </x:c>
+      <x:c r="L17" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M17" s="63" t="str">
+        <x:v>单传感器；无嘴无人脸</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="34" customHeight="1">
+      <x:c r="A18" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B18" s="63" t="str">
+        <x:v>hand</x:v>
+      </x:c>
+      <x:c r="C18" s="63" t="str">
+        <x:v>VisualRoot/Hand</x:v>
+      </x:c>
+      <x:c r="D18" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E18" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F18" s="63" t="str">
+        <x:v>SphereMesh</x:v>
+      </x:c>
+      <x:c r="G18" s="63" t="str">
+        <x:v>(0.72,1.22,-0.18)</x:v>
+      </x:c>
+      <x:c r="H18" s="63" t="str">
+        <x:v>随root；局部不旋转</x:v>
+      </x:c>
+      <x:c r="I18" s="63" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J18" s="63" t="str">
+        <x:v>随身体转向；保持局部握持位</x:v>
+      </x:c>
+      <x:c r="K18" s="63" t="str">
+        <x:v>唯一握持手</x:v>
+      </x:c>
+      <x:c r="L18" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M18" s="63" t="str">
+        <x:v>只有一只手；不单独追踪准星</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="34" customHeight="1">
+      <x:c r="A19" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B19" s="63" t="str">
+        <x:v>weapon_socket</x:v>
+      </x:c>
+      <x:c r="C19" s="63" t="str">
+        <x:v>VisualRoot/WeaponSocket</x:v>
+      </x:c>
+      <x:c r="D19" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E19" s="63" t="str">
+        <x:v>无纹理</x:v>
+      </x:c>
+      <x:c r="F19" s="63" t="str">
+        <x:v>Marker3D</x:v>
+      </x:c>
+      <x:c r="G19" s="63" t="str">
+        <x:v>(0.72,1.24,-0.34)</x:v>
+      </x:c>
+      <x:c r="H19" s="63" t="str">
+        <x:v>随root；局部不旋转</x:v>
+      </x:c>
+      <x:c r="I19" s="63" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J19" s="63" t="str">
+        <x:v>枪械挂载/枪口特效</x:v>
+      </x:c>
+      <x:c r="K19" s="63" t="str">
+        <x:v>武器系统</x:v>
+      </x:c>
+      <x:c r="L19" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M19" s="63" t="str">
+        <x:v>挂点与手保持固定局部关系；枪身读取BlueprintRegistry并只做局部后坐力</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9049,7 +11323,7 @@
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>顶层六态互斥；Low HP / Silenced / Invincible 是可叠加层。首版用组件变换，新增逐帧图前先查本表</x:v>
+        <x:v>2D/3D 共用六态 ID 与转换白名单；Low HP / Silenced / Invincible 为叠加层。3D 首版继续用组件变换，新增动画前先查本表</x:v>
       </x:c>
       <x:c r="B3" s="6"/>
       <x:c r="C3" s="6"/>
@@ -9136,7 +11410,7 @@
         <x:v>HUD 待命</x:v>
       </x:c>
       <x:c r="L6" s="36" t="str">
-        <x:v>代码变换；单手离散镜像插槽</x:v>
+        <x:v>2D/3D组件变换；单手保持局部挂点</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -9174,7 +11448,7 @@
         <x:v>地面划痕</x:v>
       </x:c>
       <x:c r="L7" s="37" t="str">
-        <x:v>代码变换；枪械独立连续瞄准</x:v>
+        <x:v>2D/3D组件变换；整体表现根随准星转向</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -9212,7 +11486,7 @@
         <x:v>青色尾迹</x:v>
       </x:c>
       <x:c r="L8" s="37" t="str">
-        <x:v>代码变换 + 程序尾迹；局部距离不变</x:v>
+        <x:v>2D/3D组件变换 + 程序尾迹；握持关系不变</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -9250,7 +11524,7 @@
         <x:v>红闪/屏闪</x:v>
       </x:c>
       <x:c r="L9" s="37" t="str">
-        <x:v>0.14s 整体变换；握持关系不变</x:v>
+        <x:v>2D/3D受击压缩/闪色；握持关系不变</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -9288,7 +11562,7 @@
         <x:v>琥珀锁定环</x:v>
       </x:c>
       <x:c r="L10" s="37" t="str">
-        <x:v>代码变换；握持关系不变</x:v>
+        <x:v>2D/3D降亮 + 锁定环；输入锁转换一致</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -9326,7 +11600,7 @@
         <x:v>HUD 终止</x:v>
       </x:c>
       <x:c r="L11" s="37" t="str">
-        <x:v>终态守卫 + 整体倾倒</x:v>
+        <x:v>2D/3D终态守卫 + 整体倾倒</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -9441,6 +11715,326 @@
       </x:c>
       <x:c r="L14" s="37" t="str">
         <x:v>InvincibleTimer 唯一解除</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="63" t="str">
+        <x:v>Enemy3D 七态状态机 × 模块表现映射</x:v>
+      </x:c>
+      <x:c r="B16" s="63"/>
+      <x:c r="C16" s="63"/>
+      <x:c r="D16" s="63"/>
+      <x:c r="E16" s="63"/>
+      <x:c r="F16" s="63"/>
+      <x:c r="G16" s="63"/>
+      <x:c r="H16" s="63"/>
+      <x:c r="I16" s="63"/>
+      <x:c r="J16" s="63"/>
+      <x:c r="K16" s="63"/>
+      <x:c r="L16" s="63"/>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="63" t="str">
+        <x:v>层级</x:v>
+      </x:c>
+      <x:c r="B17" s="63" t="str">
+        <x:v>状态ID</x:v>
+      </x:c>
+      <x:c r="C17" s="63" t="str">
+        <x:v>中文名</x:v>
+      </x:c>
+      <x:c r="D17" s="63" t="str">
+        <x:v>允许来源</x:v>
+      </x:c>
+      <x:c r="E17" s="63" t="str">
+        <x:v>允许去向</x:v>
+      </x:c>
+      <x:c r="F17" s="63" t="str">
+        <x:v>Core</x:v>
+      </x:c>
+      <x:c r="G17" s="63" t="str">
+        <x:v>Shell</x:v>
+      </x:c>
+      <x:c r="H17" s="63" t="str">
+        <x:v>Appendages</x:v>
+      </x:c>
+      <x:c r="I17" s="63" t="str">
+        <x:v>StateVFX</x:v>
+      </x:c>
+      <x:c r="J17" s="63" t="str">
+        <x:v>行为职责</x:v>
+      </x:c>
+      <x:c r="K17" s="63" t="str">
+        <x:v>验收</x:v>
+      </x:c>
+      <x:c r="L17" s="63" t="str">
+        <x:v>首版实现</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="63" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B18" s="63" t="str">
+        <x:v>idle</x:v>
+      </x:c>
+      <x:c r="C18" s="63" t="str">
+        <x:v>待机</x:v>
+      </x:c>
+      <x:c r="D18" s="63" t="str">
+        <x:v>start/stagger</x:v>
+      </x:c>
+      <x:c r="E18" s="63" t="str">
+        <x:v>alert/dead</x:v>
+      </x:c>
+      <x:c r="F18" s="63" t="str">
+        <x:v>低频脉冲</x:v>
+      </x:c>
+      <x:c r="G18" s="63" t="str">
+        <x:v>轻浮动</x:v>
+      </x:c>
+      <x:c r="H18" s="63" t="str">
+        <x:v>低速</x:v>
+      </x:c>
+      <x:c r="I18" s="63" t="str">
+        <x:v>关闭</x:v>
+      </x:c>
+      <x:c r="J18" s="63" t="str">
+        <x:v>等待目标</x:v>
+      </x:c>
+      <x:c r="K18" s="63" t="str">
+        <x:v>静态轮廓可读</x:v>
+      </x:c>
+      <x:c r="L18" s="63" t="str">
+        <x:v>模块变换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="A19" s="63" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B19" s="63" t="str">
+        <x:v>alert</x:v>
+      </x:c>
+      <x:c r="C19" s="63" t="str">
+        <x:v>警觉</x:v>
+      </x:c>
+      <x:c r="D19" s="63" t="str">
+        <x:v>idle</x:v>
+      </x:c>
+      <x:c r="E19" s="63" t="str">
+        <x:v>chase/dead</x:v>
+      </x:c>
+      <x:c r="F19" s="63" t="str">
+        <x:v>加速</x:v>
+      </x:c>
+      <x:c r="G19" s="63" t="str">
+        <x:v>抬升</x:v>
+      </x:c>
+      <x:c r="H19" s="63" t="str">
+        <x:v>展开</x:v>
+      </x:c>
+      <x:c r="I19" s="63" t="str">
+        <x:v>关闭</x:v>
+      </x:c>
+      <x:c r="J19" s="63" t="str">
+        <x:v>发现玩家</x:v>
+      </x:c>
+      <x:c r="K19" s="63" t="str">
+        <x:v>0.28s响应</x:v>
+      </x:c>
+      <x:c r="L19" s="63" t="str">
+        <x:v>模块变换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="A20" s="63" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B20" s="63" t="str">
+        <x:v>chase</x:v>
+      </x:c>
+      <x:c r="C20" s="63" t="str">
+        <x:v>追击</x:v>
+      </x:c>
+      <x:c r="D20" s="63" t="str">
+        <x:v>alert/attack/stagger</x:v>
+      </x:c>
+      <x:c r="E20" s="63" t="str">
+        <x:v>telegraph/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F20" s="63" t="str">
+        <x:v>稳定</x:v>
+      </x:c>
+      <x:c r="G20" s="63" t="str">
+        <x:v>朝目标</x:v>
+      </x:c>
+      <x:c r="H20" s="63" t="str">
+        <x:v>步态</x:v>
+      </x:c>
+      <x:c r="I20" s="63" t="str">
+        <x:v>关闭</x:v>
+      </x:c>
+      <x:c r="J20" s="63" t="str">
+        <x:v>距离控制</x:v>
+      </x:c>
+      <x:c r="K20" s="63" t="str">
+        <x:v>七类速度差</x:v>
+      </x:c>
+      <x:c r="L20" s="63" t="str">
+        <x:v>CharacterBody3D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="63" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B21" s="63" t="str">
+        <x:v>telegraph</x:v>
+      </x:c>
+      <x:c r="C21" s="63" t="str">
+        <x:v>预警</x:v>
+      </x:c>
+      <x:c r="D21" s="63" t="str">
+        <x:v>chase</x:v>
+      </x:c>
+      <x:c r="E21" s="63" t="str">
+        <x:v>attack/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F21" s="63" t="str">
+        <x:v>高频脉冲</x:v>
+      </x:c>
+      <x:c r="G21" s="63" t="str">
+        <x:v>稳定</x:v>
+      </x:c>
+      <x:c r="H21" s="63" t="str">
+        <x:v>蓄势</x:v>
+      </x:c>
+      <x:c r="I21" s="63" t="str">
+        <x:v>红色预警环</x:v>
+      </x:c>
+      <x:c r="J21" s="63" t="str">
+        <x:v>攻击前摇</x:v>
+      </x:c>
+      <x:c r="K21" s="63" t="str">
+        <x:v>不可省略</x:v>
+      </x:c>
+      <x:c r="L21" s="63" t="str">
+        <x:v>计时状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="A22" s="63" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B22" s="63" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="C22" s="63" t="str">
+        <x:v>攻击</x:v>
+      </x:c>
+      <x:c r="D22" s="63" t="str">
+        <x:v>telegraph</x:v>
+      </x:c>
+      <x:c r="E22" s="63" t="str">
+        <x:v>chase/dead</x:v>
+      </x:c>
+      <x:c r="F22" s="63" t="str">
+        <x:v>峰值</x:v>
+      </x:c>
+      <x:c r="G22" s="63" t="str">
+        <x:v>反冲</x:v>
+      </x:c>
+      <x:c r="H22" s="63" t="str">
+        <x:v>执行</x:v>
+      </x:c>
+      <x:c r="I22" s="63" t="str">
+        <x:v>按攻击类型</x:v>
+      </x:c>
+      <x:c r="J22" s="63" t="str">
+        <x:v>近战/远程/召唤/爆炸</x:v>
+      </x:c>
+      <x:c r="K22" s="63" t="str">
+        <x:v>七类差异</x:v>
+      </x:c>
+      <x:c r="L22" s="63" t="str">
+        <x:v>profile策略</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="63" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B23" s="63" t="str">
+        <x:v>stagger</x:v>
+      </x:c>
+      <x:c r="C23" s="63" t="str">
+        <x:v>硬直</x:v>
+      </x:c>
+      <x:c r="D23" s="63" t="str">
+        <x:v>任意存活态</x:v>
+      </x:c>
+      <x:c r="E23" s="63" t="str">
+        <x:v>chase/dead</x:v>
+      </x:c>
+      <x:c r="F23" s="63" t="str">
+        <x:v>闪色</x:v>
+      </x:c>
+      <x:c r="G23" s="63" t="str">
+        <x:v>冲击</x:v>
+      </x:c>
+      <x:c r="H23" s="63" t="str">
+        <x:v>暂停</x:v>
+      </x:c>
+      <x:c r="I23" s="63" t="str">
+        <x:v>伤害反馈</x:v>
+      </x:c>
+      <x:c r="J23" s="63" t="str">
+        <x:v>受击窗口</x:v>
+      </x:c>
+      <x:c r="K23" s="63" t="str">
+        <x:v>方向可读</x:v>
+      </x:c>
+      <x:c r="L23" s="63" t="str">
+        <x:v>统一伤害入口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="A24" s="63" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B24" s="63" t="str">
+        <x:v>dead</x:v>
+      </x:c>
+      <x:c r="C24" s="63" t="str">
+        <x:v>死亡</x:v>
+      </x:c>
+      <x:c r="D24" s="63" t="str">
+        <x:v>任意存活态</x:v>
+      </x:c>
+      <x:c r="E24" s="63" t="str">
+        <x:v>无（终态）</x:v>
+      </x:c>
+      <x:c r="F24" s="63" t="str">
+        <x:v>熄灭</x:v>
+      </x:c>
+      <x:c r="G24" s="63" t="str">
+        <x:v>压扁</x:v>
+      </x:c>
+      <x:c r="H24" s="63" t="str">
+        <x:v>停止</x:v>
+      </x:c>
+      <x:c r="I24" s="63" t="str">
+        <x:v>爆散/淡出</x:v>
+      </x:c>
+      <x:c r="J24" s="63" t="str">
+        <x:v>掉落与计数</x:v>
+      </x:c>
+      <x:c r="K24" s="63" t="str">
+        <x:v>不可回存活态</x:v>
+      </x:c>
+      <x:c r="L24" s="63" t="str">
+        <x:v>终态 + Tween</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9526,7 +12120,7 @@
         <x:v>assets/art/characters/</x:v>
       </x:c>
       <x:c r="E6" s="36" t="str">
-        <x:v>chr_{role}_{name}{nn}_{component}_{view}_v{nnn}.png</x:v>
+        <x:v>chr_{role}_{name}{nn}_{component}_{view}_v{nnn}.{png|glb|tscn}</x:v>
       </x:c>
       <x:c r="F6" s="36" t="str">
         <x:v>CHR-PLY-CAPSULE01-HEAD-SIDE</x:v>
@@ -9546,7 +12140,7 @@
         <x:v>assets/art/enemies/</x:v>
       </x:c>
       <x:c r="E7" s="37" t="str">
-        <x:v>enm_{archetype}_{name}{nn}_{part}_{view}_v{nnn}.png</x:v>
+        <x:v>enm_{archetype}_{name}{nn}_{part}_{view}_v{nnn}.{png|glb|tscn}</x:v>
       </x:c>
       <x:c r="F7" s="37" t="str">
         <x:v>ENM-MELEE-FUNGBOAR01-BODY</x:v>
@@ -9566,7 +12160,7 @@
         <x:v>assets/art/weapons/</x:v>
       </x:c>
       <x:c r="E8" s="37" t="str">
-        <x:v>wpn_{family}_{logic_id}_{view}_v{nnn}.png</x:v>
+        <x:v>wpn_{family}_{logic_id}_{view}_v{nnn}.{png|glb|tscn}</x:v>
       </x:c>
       <x:c r="F8" s="37" t="str">
         <x:v>WPN-GUN-BP-PISTOL-SIDE</x:v>
@@ -9606,7 +12200,7 @@
         <x:v>assets/art/environments/</x:v>
       </x:c>
       <x:c r="E10" s="37" t="str">
-        <x:v>env_{biome}_{set}_{piece}_v{nnn}.png</x:v>
+        <x:v>env_{biome}_{set}_{piece}_v{nnn}.{png|glb|tres|tscn}</x:v>
       </x:c>
       <x:c r="F10" s="37" t="str">
         <x:v>ENV-IRON-FRONTIER-FLOOR-A</x:v>
@@ -9626,7 +12220,7 @@
         <x:v>assets/art/props/</x:v>
       </x:c>
       <x:c r="E11" s="37" t="str">
-        <x:v>prp_{set}_{logic_id}_{state}_v{nnn}.png</x:v>
+        <x:v>prp_{set}_{logic_id}_{state}_v{nnn}.{png|glb|tscn}</x:v>
       </x:c>
       <x:c r="F11" s="37" t="str">
         <x:v>PRP-BASE-WORKBENCH-IDLE</x:v>
@@ -9666,7 +12260,7 @@
         <x:v>assets/art/vfx/</x:v>
       </x:c>
       <x:c r="E13" s="37" t="str">
-        <x:v>vfx_{system}_{effect}_{variant}_v{nnn}.png</x:v>
+        <x:v>vfx_{system}_{effect}_{variant}_v{nnn}.{png|glb|tscn}</x:v>
       </x:c>
       <x:c r="F13" s="37" t="str">
         <x:v>VFX-PLAYER-DASH-TRAIL-A</x:v>
@@ -9887,22 +12481,22 @@
         <x:v>组件制作</x:v>
       </x:c>
       <x:c r="C10" s="37" t="str">
-        <x:v>角色组件契约/挂点</x:v>
+        <x:v>角色/房间/家具尺寸/枪械/怪物/灯具共用根</x:v>
       </x:c>
       <x:c r="D10" s="37" t="str">
-        <x:v>独立透明 PNG；共同像素密度</x:v>
+        <x:v>组件独立；3D用配置与父子变体</x:v>
       </x:c>
       <x:c r="E10" s="37" t="str">
-        <x:v>手臂并回 body；武器烘焙进手</x:v>
+        <x:v>关卡内复制枪表/房间/怪物根</x:v>
       </x:c>
       <x:c r="F10" s="37" t="str">
-        <x:v>悬浮主手</x:v>
+        <x:v>large可搜索柜</x:v>
       </x:c>
       <x:c r="G10" s="37" t="str">
-        <x:v>独立 hand_r + weapon_socket</x:v>
+        <x:v>复用RoomFurniture3D + size=large</x:v>
       </x:c>
       <x:c r="H10" s="37" t="str">
-        <x:v>F/N/O</x:v>
+        <x:v>F/N/O/X</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -9913,19 +12507,19 @@
         <x:v>验收</x:v>
       </x:c>
       <x:c r="C11" s="37" t="str">
-        <x:v>透明边缘、比例、状态矩阵、游戏内截图</x:v>
+        <x:v>透明边缘或3D灯光/雾/碰撞/状态/节点预算</x:v>
       </x:c>
       <x:c r="D11" s="37" t="str">
-        <x:v>最近邻清晰；六态无遮挡</x:v>
+        <x:v>真实游戏镜头与严格专项通过</x:v>
       </x:c>
       <x:c r="E11" s="37" t="str">
-        <x:v>只看母版不进游戏</x:v>
+        <x:v>只看母版或编辑器预览</x:v>
       </x:c>
       <x:c r="F11" s="37" t="str">
-        <x:v>capsule01 v001</x:v>
+        <x:v>3D主题关卡</x:v>
       </x:c>
       <x:c r="G11" s="37" t="str">
-        <x:v>verify_player_pixel_art_flow PASS</x:v>
+        <x:v>seed/灯池/七怪/56组合/撤离 PASS</x:v>
       </x:c>
       <x:c r="H11" s="37" t="str">
         <x:v>K/P/X</x:v>
@@ -9985,7 +12579,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="56" t="str">
-        <x:v>命名正则：文件名 ^[a-z0-9]+(?:_[a-z0-9]+)*_v[0-9]{3}\.(png|webp|svg|wav|ogg)$ ｜ AssetID ^[A-Z0-9]+(?:-[A-Z0-9]+)+$</x:v>
+        <x:v>命名正则：文件名 ^[a-z0-9]+(?:_[a-z0-9]+)*_v[0-9]{3}\.(png|webp|svg|wav|ogg|glb|gltf|tres|tscn)$ ｜ AssetID ^[A-Z0-9]+(?:-[A-Z0-9]+)+$</x:v>
       </x:c>
       <x:c r="B17" s="56"/>
       <x:c r="C17" s="56"/>
@@ -10511,6 +13105,52 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="9" ht="48" customHeight="1">
+      <x:c r="A9" s="63" t="str">
+        <x:v>v1.3</x:v>
+      </x:c>
+      <x:c r="B9" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="C9" s="63" t="str">
+        <x:v>3D变体登记</x:v>
+      </x:c>
+      <x:c r="D9" s="63" t="str">
+        <x:v>入口基地 / player_capsule01</x:v>
+      </x:c>
+      <x:c r="E9" s="63" t="str">
+        <x:v>登记首张3D入口地图、设施/入口模块、3D角色root/body/head/hand/scarf/socket；六态ID与2D保持一致</x:v>
+      </x:c>
+      <x:c r="F9" s="63" t="str">
+        <x:v>保留原2D资产与场景作为基线</x:v>
+      </x:c>
+      <x:c r="G9" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="63" t="str">
+        <x:v>v1.4</x:v>
+      </x:c>
+      <x:c r="B10" s="64" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="C10" s="63" t="str">
+        <x:v>全游戏3D原型登记</x:v>
+      </x:c>
+      <x:c r="D10" s="63" t="str">
+        <x:v>四主题副本 / 靶场 / 战斗 / 共用资产</x:v>
+      </x:c>
+      <x:c r="E10" s="63" t="str">
+        <x:v>登记通用房间、4主题、灯具、三档家具与搜索、服务/撤离、枪械、七怪、战斗VFX、3D靶场和两张GPU验收预览</x:v>
+      </x:c>
+      <x:c r="F10" s="63" t="str">
+        <x:v>复用原玩法ID与BlueprintRegistry；保留2D基线</x:v>
+      </x:c>
+      <x:c r="G10" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G2"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R97459e44b4534c7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R14cc543c2d0b4973"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R7790dbc62de644e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R046ed2fbaaef4304"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R8573fe1a4d684450"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb7a5b573dea048ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R99f70fcbf0544d95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rfc9fec22444b442f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf037c12262a645be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R3e1cd7d8497b4ae3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rdf02083753b14321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rabe250e950244608"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R039802b8ef1641a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb8d16a866a6d4d67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R9ea68df7be064d6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R8059162294d64002"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="18">
+  <x:fonts count="19">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -126,8 +126,14 @@
       <x:color rgb="FF176C4A"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -162,6 +168,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFD9F3E8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF10212C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF10212C"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -214,7 +230,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="65">
+  <x:cellXfs count="72">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -361,6 +377,27 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -725,23 +762,27 @@
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="45" t="n">
-        <x:v>134</x:v>
+        <x:f>COUNTA('资产主表'!$A$6:$A$200)</x:f>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B6" s="43"/>
       <x:c r="C6" s="45" t="n">
-        <x:v>34</x:v>
+        <x:f>COUNTIF('资产主表'!$K$6:$K$200,"已完成")+COUNTIF('资产主表'!$K$6:$K$200,"原型已接入")</x:f>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
-        <x:v>99</x:v>
+        <x:f>COUNTIF('资产主表'!$K$6:$K$200,"待制作")+COUNTIF('资产主表'!$K$6:$K$200,"程序占位")</x:f>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F6" s="43"/>
       <x:c r="G6" s="45" t="n">
+        <x:f>COUNTIF('资产主表'!$S$6:$S$200,"重复")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="43"/>
       <x:c r="I6" s="46" t="str">
-        <x:v>全3D闭环 / 三档房间 / 七类怪 / 56枪弹组合 / 废土灯池</x:v>
+        <x:v>全3D闭环 / 三档房间 / 暗室开关 / 七类怪 / 56枪弹组合</x:v>
       </x:c>
       <x:c r="J6" s="46"/>
     </x:row>
@@ -820,9 +861,11 @@
         <x:v>敌人</x:v>
       </x:c>
       <x:c r="B11" s="52" t="n">
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A11)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="52" t="n">
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A11,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A11,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D11" s="43"/>
@@ -844,9 +887,11 @@
         <x:v>枪械</x:v>
       </x:c>
       <x:c r="B12" s="52" t="n">
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A12)</x:f>
         <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="52" t="n">
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A12,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A12,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D12" s="43"/>
@@ -868,9 +913,11 @@
         <x:v>道具</x:v>
       </x:c>
       <x:c r="B13" s="52" t="n">
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A13)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="C13" s="52" t="n">
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A13,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A13,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="43"/>
@@ -892,9 +939,11 @@
         <x:v>场景</x:v>
       </x:c>
       <x:c r="B14" s="52" t="n">
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A14)</x:f>
         <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="52" t="n">
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A14,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A14,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="D14" s="43"/>
@@ -902,7 +951,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F14" s="52" t="str">
-        <x:v>游戏内、状态矩阵、透明边缘三项验收</x:v>
+        <x:v>游戏内表现、状态机、玩法逻辑、性能四项验收</x:v>
       </x:c>
       <x:c r="G14" s="52" t="str">
         <x:v>通过后填写路径、尺寸、哈希、日期</x:v>
@@ -916,10 +965,12 @@
         <x:v>场景道具</x:v>
       </x:c>
       <x:c r="B15" s="52" t="n">
-        <x:v>17</x:v>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A15)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C15" s="52" t="n">
-        <x:v>7</x:v>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A15,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A15,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D15" s="43"/>
       <x:c r="E15" s="43"/>
@@ -934,10 +985,12 @@
         <x:v>UI</x:v>
       </x:c>
       <x:c r="B16" s="52" t="n">
-        <x:v>13</x:v>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A16)</x:f>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C16" s="52" t="n">
-        <x:v>0</x:v>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A16,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A16,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D16" s="43"/>
       <x:c r="E16" s="43"/>
@@ -952,10 +1005,12 @@
         <x:v>特效</x:v>
       </x:c>
       <x:c r="B17" s="52" t="n">
-        <x:v>14</x:v>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A17)</x:f>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C17" s="52" t="n">
-        <x:v>2</x:v>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A17,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A17,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D17" s="43"/>
       <x:c r="E17" s="43"/>
@@ -970,9 +1025,11 @@
         <x:v>音频</x:v>
       </x:c>
       <x:c r="B18" s="52" t="n">
+        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A18)</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="C18" s="52" t="n">
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A18,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A18,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D18" s="43"/>
@@ -1259,7 +1316,7 @@
         <x:v>角色|player|player_capsule01|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S6" s="36" t="str">
-        <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$139,R6)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$145,R6)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T6" s="36" t="str"/>
@@ -1333,7 +1390,7 @@
         <x:v>角色|player_component|player_capsule01|head|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S7" s="37" t="str">
-        <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$139,R7)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$145,R7)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T7" s="37" t="str">
@@ -1409,7 +1466,7 @@
         <x:v>角色|player_component|player_capsule01|body|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S8" s="37" t="str">
-        <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$139,R8)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$145,R8)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T8" s="37" t="str">
@@ -1485,7 +1542,7 @@
         <x:v>角色|player_component|player_capsule01|hand_l_source|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S9" s="37" t="str">
-        <x:f>IF(A9="","",IF(COUNTIF($R$6:$R$139,R9)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A9="","",IF(COUNTIF($R$6:$R$145,R9)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T9" s="37" t="str">
@@ -1561,7 +1618,7 @@
         <x:v>角色|player_component|player_capsule01|hand|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S10" s="37" t="str">
-        <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$139,R10)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$145,R10)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T10" s="37" t="str">
@@ -1637,7 +1694,7 @@
         <x:v>角色|player_accessory|player_capsule01|scarf|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S11" s="37" t="str">
-        <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$139,R11)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$145,R11)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T11" s="37" t="str">
@@ -1713,7 +1770,7 @@
         <x:v>角色|review_board|player_capsule01|preview|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S12" s="37" t="str">
-        <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$139,R12)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$145,R12)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T12" s="37" t="str"/>
@@ -1781,7 +1838,7 @@
         <x:v>特效|player_state|player_dash|root|侧面朝右（可水平翻转）|dashing</x:v>
       </x:c>
       <x:c r="S13" s="37" t="str">
-        <x:f>IF(A13="","",IF(COUNTIF($R$6:$R$139,R13)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A13="","",IF(COUNTIF($R$6:$R$145,R13)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T13" s="37" t="str"/>
@@ -1849,7 +1906,7 @@
         <x:v>特效|player_state|player_hurt|root|侧面朝右（可水平翻转）|hurt</x:v>
       </x:c>
       <x:c r="S14" s="37" t="str">
-        <x:f>IF(A14="","",IF(COUNTIF($R$6:$R$139,R14)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A14="","",IF(COUNTIF($R$6:$R$145,R14)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T14" s="37" t="str"/>
@@ -1915,7 +1972,7 @@
         <x:v>特效|player_overlay|player_low_hp|root|侧面朝右（可水平翻转）|low_health</x:v>
       </x:c>
       <x:c r="S15" s="37" t="str">
-        <x:f>IF(A15="","",IF(COUNTIF($R$6:$R$139,R15)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A15="","",IF(COUNTIF($R$6:$R$145,R15)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T15" s="37" t="str"/>
@@ -1981,7 +2038,7 @@
         <x:v>特效|player_overlay|player_silenced|root|侧面朝右（可水平翻转）|silenced</x:v>
       </x:c>
       <x:c r="S16" s="37" t="str">
-        <x:f>IF(A16="","",IF(COUNTIF($R$6:$R$139,R16)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A16="","",IF(COUNTIF($R$6:$R$145,R16)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T16" s="37" t="str"/>
@@ -2049,7 +2106,7 @@
         <x:v>敌人|normal_melee|melee_chaser|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S17" s="37" t="str">
-        <x:f>IF(A17="","",IF(COUNTIF($R$6:$R$139,R17)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A17="","",IF(COUNTIF($R$6:$R$145,R17)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T17" s="37" t="str"/>
@@ -2119,7 +2176,7 @@
         <x:v>敌人|normal_ranged|ranged_caster|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S18" s="37" t="str">
-        <x:f>IF(A18="","",IF(COUNTIF($R$6:$R$139,R18)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A18="","",IF(COUNTIF($R$6:$R$145,R18)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T18" s="37" t="str"/>
@@ -2187,7 +2244,7 @@
         <x:v>敌人|normal_summoner|summoner|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S19" s="37" t="str">
-        <x:f>IF(A19="","",IF(COUNTIF($R$6:$R$139,R19)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A19="","",IF(COUNTIF($R$6:$R$145,R19)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T19" s="37" t="str"/>
@@ -2255,7 +2312,7 @@
         <x:v>敌人|normal_tank|shielded|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S20" s="37" t="str">
-        <x:f>IF(A20="","",IF(COUNTIF($R$6:$R$139,R20)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A20="","",IF(COUNTIF($R$6:$R$145,R20)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T20" s="37" t="str"/>
@@ -2323,7 +2380,7 @@
         <x:v>敌人|normal_bomber|exploder|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S21" s="37" t="str">
-        <x:f>IF(A21="","",IF(COUNTIF($R$6:$R$139,R21)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A21="","",IF(COUNTIF($R$6:$R$145,R21)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T21" s="37" t="str"/>
@@ -2391,7 +2448,7 @@
         <x:v>敌人|normal_ambusher|ambusher|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S22" s="37" t="str">
-        <x:f>IF(A22="","",IF(COUNTIF($R$6:$R$139,R22)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A22="","",IF(COUNTIF($R$6:$R$145,R22)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T22" s="37" t="str"/>
@@ -2459,7 +2516,7 @@
         <x:v>敌人|boss|boss|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S23" s="37" t="str">
-        <x:f>IF(A23="","",IF(COUNTIF($R$6:$R$139,R23)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A23="","",IF(COUNTIF($R$6:$R$145,R23)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T23" s="37" t="str"/>
@@ -2529,7 +2586,7 @@
         <x:v>枪械|gunbody|bp_pistol|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S24" s="37" t="str">
-        <x:f>IF(A24="","",IF(COUNTIF($R$6:$R$139,R24)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A24="","",IF(COUNTIF($R$6:$R$145,R24)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T24" s="37" t="str"/>
@@ -2599,7 +2656,7 @@
         <x:v>枪械|gunbody|bp_shotgun|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S25" s="37" t="str">
-        <x:f>IF(A25="","",IF(COUNTIF($R$6:$R$139,R25)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A25="","",IF(COUNTIF($R$6:$R$145,R25)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T25" s="37" t="str"/>
@@ -2669,7 +2726,7 @@
         <x:v>枪械|gunbody|bp_rifle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S26" s="37" t="str">
-        <x:f>IF(A26="","",IF(COUNTIF($R$6:$R$139,R26)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A26="","",IF(COUNTIF($R$6:$R$145,R26)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T26" s="37" t="str"/>
@@ -2739,7 +2796,7 @@
         <x:v>枪械|gunbody|bp_machinegun|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S27" s="37" t="str">
-        <x:f>IF(A27="","",IF(COUNTIF($R$6:$R$139,R27)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A27="","",IF(COUNTIF($R$6:$R$145,R27)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T27" s="37" t="str"/>
@@ -2809,7 +2866,7 @@
         <x:v>枪械|gunbody|bp_sniper|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S28" s="37" t="str">
-        <x:f>IF(A28="","",IF(COUNTIF($R$6:$R$139,R28)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A28="","",IF(COUNTIF($R$6:$R$145,R28)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T28" s="37" t="str"/>
@@ -2879,7 +2936,7 @@
         <x:v>枪械|gunbody|bp_launcher|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S29" s="37" t="str">
-        <x:f>IF(A29="","",IF(COUNTIF($R$6:$R$139,R29)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A29="","",IF(COUNTIF($R$6:$R$145,R29)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T29" s="37" t="str"/>
@@ -2949,7 +3006,7 @@
         <x:v>枪械|gunbody|bp_charge|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S30" s="37" t="str">
-        <x:f>IF(A30="","",IF(COUNTIF($R$6:$R$139,R30)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A30="","",IF(COUNTIF($R$6:$R$145,R30)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T30" s="37" t="str"/>
@@ -3017,7 +3074,7 @@
         <x:v>枪械|bullet_module|mod_bullet_standard|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S31" s="37" t="str">
-        <x:f>IF(A31="","",IF(COUNTIF($R$6:$R$139,R31)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A31="","",IF(COUNTIF($R$6:$R$145,R31)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T31" s="37" t="str"/>
@@ -3085,7 +3142,7 @@
         <x:v>枪械|bullet_module|mod_bullet_sticky|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S32" s="37" t="str">
-        <x:f>IF(A32="","",IF(COUNTIF($R$6:$R$139,R32)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A32="","",IF(COUNTIF($R$6:$R$145,R32)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T32" s="37" t="str"/>
@@ -3153,7 +3210,7 @@
         <x:v>枪械|bullet_module|mod_bullet_bounce|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S33" s="37" t="str">
-        <x:f>IF(A33="","",IF(COUNTIF($R$6:$R$139,R33)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A33="","",IF(COUNTIF($R$6:$R$145,R33)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T33" s="37" t="str"/>
@@ -3221,7 +3278,7 @@
         <x:v>枪械|bullet_module|mod_bullet_piercing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S34" s="37" t="str">
-        <x:f>IF(A34="","",IF(COUNTIF($R$6:$R$139,R34)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A34="","",IF(COUNTIF($R$6:$R$145,R34)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T34" s="37" t="str"/>
@@ -3289,7 +3346,7 @@
         <x:v>枪械|bullet_module|mod_bullet_explosive|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S35" s="37" t="str">
-        <x:f>IF(A35="","",IF(COUNTIF($R$6:$R$139,R35)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A35="","",IF(COUNTIF($R$6:$R$145,R35)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T35" s="37" t="str"/>
@@ -3357,7 +3414,7 @@
         <x:v>枪械|bullet_module|mod_bullet_homing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S36" s="37" t="str">
-        <x:f>IF(A36="","",IF(COUNTIF($R$6:$R$139,R36)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A36="","",IF(COUNTIF($R$6:$R$145,R36)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T36" s="37" t="str"/>
@@ -3425,7 +3482,7 @@
         <x:v>枪械|bullet_module|mod_bullet_blackhole|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S37" s="37" t="str">
-        <x:f>IF(A37="","",IF(COUNTIF($R$6:$R$139,R37)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A37="","",IF(COUNTIF($R$6:$R$145,R37)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T37" s="37" t="str"/>
@@ -3493,7 +3550,7 @@
         <x:v>枪械|bullet_module|mod_bullet_balloon|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S38" s="37" t="str">
-        <x:f>IF(A38="","",IF(COUNTIF($R$6:$R$139,R38)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A38="","",IF(COUNTIF($R$6:$R$145,R38)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T38" s="37" t="str"/>
@@ -3561,7 +3618,7 @@
         <x:v>枪械|attachment|attach_triple_muzzle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S39" s="37" t="str">
-        <x:f>IF(A39="","",IF(COUNTIF($R$6:$R$139,R39)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A39="","",IF(COUNTIF($R$6:$R$145,R39)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T39" s="37" t="str"/>
@@ -3629,7 +3686,7 @@
         <x:v>枪械|attachment|attach_rubber_stock|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S40" s="37" t="str">
-        <x:f>IF(A40="","",IF(COUNTIF($R$6:$R$139,R40)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A40="","",IF(COUNTIF($R$6:$R$145,R40)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T40" s="37" t="str"/>
@@ -3697,7 +3754,7 @@
         <x:v>枪械|attachment|attach_scope|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S41" s="37" t="str">
-        <x:f>IF(A41="","",IF(COUNTIF($R$6:$R$139,R41)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A41="","",IF(COUNTIF($R$6:$R$145,R41)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T41" s="37" t="str"/>
@@ -3765,7 +3822,7 @@
         <x:v>枪械|attachment|attach_big_mag|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S42" s="37" t="str">
-        <x:f>IF(A42="","",IF(COUNTIF($R$6:$R$139,R42)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A42="","",IF(COUNTIF($R$6:$R$145,R42)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T42" s="37" t="str"/>
@@ -3833,7 +3890,7 @@
         <x:v>枪械|attachment|attach_fan|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S43" s="37" t="str">
-        <x:f>IF(A43="","",IF(COUNTIF($R$6:$R$139,R43)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A43="","",IF(COUNTIF($R$6:$R$145,R43)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T43" s="37" t="str"/>
@@ -3901,7 +3958,7 @@
         <x:v>枪械|attachment|attach_copy_sticker|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S44" s="37" t="str">
-        <x:f>IF(A44="","",IF(COUNTIF($R$6:$R$139,R44)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A44="","",IF(COUNTIF($R$6:$R$145,R44)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T44" s="37" t="str"/>
@@ -3969,7 +4026,7 @@
         <x:v>道具|consumable|item_beacon|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S45" s="37" t="str">
-        <x:f>IF(A45="","",IF(COUNTIF($R$6:$R$139,R45)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A45="","",IF(COUNTIF($R$6:$R$145,R45)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T45" s="37" t="str"/>
@@ -4035,7 +4092,7 @@
         <x:v>道具|key|item_room_key|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S46" s="37" t="str">
-        <x:f>IF(A46="","",IF(COUNTIF($R$6:$R$139,R46)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A46="","",IF(COUNTIF($R$6:$R$145,R46)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T46" s="37" t="str"/>
@@ -4101,7 +4158,7 @@
         <x:v>道具|pickup|soul_orb|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S47" s="37" t="str">
-        <x:f>IF(A47="","",IF(COUNTIF($R$6:$R$139,R47)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A47="","",IF(COUNTIF($R$6:$R$145,R47)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T47" s="37" t="str"/>
@@ -4167,7 +4224,7 @@
         <x:v>道具|container|container|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S48" s="37" t="str">
-        <x:f>IF(A48="","",IF(COUNTIF($R$6:$R$139,R48)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A48="","",IF(COUNTIF($R$6:$R$145,R48)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T48" s="37" t="str"/>
@@ -4233,7 +4290,7 @@
         <x:v>道具|pickup|room_key_pickup|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S49" s="37" t="str">
-        <x:f>IF(A49="","",IF(COUNTIF($R$6:$R$139,R49)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A49="","",IF(COUNTIF($R$6:$R$145,R49)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T49" s="37" t="str"/>
@@ -4299,7 +4356,7 @@
         <x:v>道具|pickup_base|ground_item|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S50" s="37" t="str">
-        <x:f>IF(A50="","",IF(COUNTIF($R$6:$R$139,R50)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A50="","",IF(COUNTIF($R$6:$R$145,R50)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T50" s="37" t="str"/>
@@ -4365,7 +4422,7 @@
         <x:v>场景|biome_kit|base_world|root|顶视|default</x:v>
       </x:c>
       <x:c r="S51" s="37" t="str">
-        <x:f>IF(A51="","",IF(COUNTIF($R$6:$R$139,R51)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A51="","",IF(COUNTIF($R$6:$R$145,R51)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T51" s="37" t="str"/>
@@ -4433,7 +4490,7 @@
         <x:v>场景|biome_kit|iron_frontier|root|顶视|default</x:v>
       </x:c>
       <x:c r="S52" s="37" t="str">
-        <x:f>IF(A52="","",IF(COUNTIF($R$6:$R$139,R52)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A52="","",IF(COUNTIF($R$6:$R$145,R52)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T52" s="37" t="str"/>
@@ -4501,7 +4558,7 @@
         <x:v>场景|biome_kit|rust_foundry|root|顶视|default</x:v>
       </x:c>
       <x:c r="S53" s="37" t="str">
-        <x:f>IF(A53="","",IF(COUNTIF($R$6:$R$139,R53)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A53="","",IF(COUNTIF($R$6:$R$145,R53)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T53" s="37" t="str"/>
@@ -4569,7 +4626,7 @@
         <x:v>场景|biome_kit|spore_depths|root|顶视|default</x:v>
       </x:c>
       <x:c r="S54" s="37" t="str">
-        <x:f>IF(A54="","",IF(COUNTIF($R$6:$R$139,R54)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A54="","",IF(COUNTIF($R$6:$R$145,R54)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T54" s="37" t="str"/>
@@ -4637,7 +4694,7 @@
         <x:v>场景|biome_kit|abyss_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S55" s="37" t="str">
-        <x:f>IF(A55="","",IF(COUNTIF($R$6:$R$139,R55)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A55="","",IF(COUNTIF($R$6:$R$145,R55)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T55" s="37" t="str"/>
@@ -4705,7 +4762,7 @@
         <x:v>场景|biome_kit|training_range|root|顶视|default</x:v>
       </x:c>
       <x:c r="S56" s="37" t="str">
-        <x:f>IF(A56="","",IF(COUNTIF($R$6:$R$139,R56)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A56="","",IF(COUNTIF($R$6:$R$145,R56)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T56" s="37" t="str"/>
@@ -4773,7 +4830,7 @@
         <x:v>场景|room_dressing|room_combat|root|顶视|default</x:v>
       </x:c>
       <x:c r="S57" s="37" t="str">
-        <x:f>IF(A57="","",IF(COUNTIF($R$6:$R$139,R57)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A57="","",IF(COUNTIF($R$6:$R$145,R57)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T57" s="37" t="str"/>
@@ -4841,7 +4898,7 @@
         <x:v>场景|room_dressing|room_elite|root|顶视|default</x:v>
       </x:c>
       <x:c r="S58" s="37" t="str">
-        <x:f>IF(A58="","",IF(COUNTIF($R$6:$R$139,R58)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A58="","",IF(COUNTIF($R$6:$R$145,R58)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T58" s="37" t="str"/>
@@ -4909,7 +4966,7 @@
         <x:v>场景|room_dressing|room_boss|root|顶视|default</x:v>
       </x:c>
       <x:c r="S59" s="37" t="str">
-        <x:f>IF(A59="","",IF(COUNTIF($R$6:$R$139,R59)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A59="","",IF(COUNTIF($R$6:$R$145,R59)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T59" s="37" t="str"/>
@@ -4977,7 +5034,7 @@
         <x:v>场景|room_dressing|room_event|root|顶视|default</x:v>
       </x:c>
       <x:c r="S60" s="37" t="str">
-        <x:f>IF(A60="","",IF(COUNTIF($R$6:$R$139,R60)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A60="","",IF(COUNTIF($R$6:$R$145,R60)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T60" s="37" t="str"/>
@@ -5045,7 +5102,7 @@
         <x:v>场景|room_dressing|room_extraction|root|顶视|default</x:v>
       </x:c>
       <x:c r="S61" s="37" t="str">
-        <x:f>IF(A61="","",IF(COUNTIF($R$6:$R$139,R61)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A61="","",IF(COUNTIF($R$6:$R$145,R61)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T61" s="37" t="str"/>
@@ -5113,7 +5170,7 @@
         <x:v>场景|room_dressing|room_merchant|root|顶视|default</x:v>
       </x:c>
       <x:c r="S62" s="37" t="str">
-        <x:f>IF(A62="","",IF(COUNTIF($R$6:$R$139,R62)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A62="","",IF(COUNTIF($R$6:$R$145,R62)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T62" s="37" t="str"/>
@@ -5181,7 +5238,7 @@
         <x:v>场景|room_dressing|room_scavenge|root|顶视|default</x:v>
       </x:c>
       <x:c r="S63" s="37" t="str">
-        <x:f>IF(A63="","",IF(COUNTIF($R$6:$R$139,R63)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A63="","",IF(COUNTIF($R$6:$R$145,R63)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T63" s="37" t="str"/>
@@ -5249,7 +5306,7 @@
         <x:v>场景|room_dressing|room_storage|root|顶视|default</x:v>
       </x:c>
       <x:c r="S64" s="37" t="str">
-        <x:f>IF(A64="","",IF(COUNTIF($R$6:$R$139,R64)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A64="","",IF(COUNTIF($R$6:$R$145,R64)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T64" s="37" t="str"/>
@@ -5317,7 +5374,7 @@
         <x:v>场景|room_dressing|room_trap|root|顶视|default</x:v>
       </x:c>
       <x:c r="S65" s="37" t="str">
-        <x:f>IF(A65="","",IF(COUNTIF($R$6:$R$139,R65)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A65="","",IF(COUNTIF($R$6:$R$145,R65)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T65" s="37" t="str"/>
@@ -5385,7 +5442,7 @@
         <x:v>场景|room_dressing|room_upgrade|root|顶视|default</x:v>
       </x:c>
       <x:c r="S66" s="37" t="str">
-        <x:f>IF(A66="","",IF(COUNTIF($R$6:$R$139,R66)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A66="","",IF(COUNTIF($R$6:$R$145,R66)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T66" s="37" t="str"/>
@@ -5453,7 +5510,7 @@
         <x:v>场景|room_dressing|room_spawn|root|顶视|default</x:v>
       </x:c>
       <x:c r="S67" s="37" t="str">
-        <x:f>IF(A67="","",IF(COUNTIF($R$6:$R$139,R67)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A67="","",IF(COUNTIF($R$6:$R$145,R67)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T67" s="37" t="str"/>
@@ -5521,7 +5578,7 @@
         <x:v>场景|room_dressing|room_stairs|root|顶视|default</x:v>
       </x:c>
       <x:c r="S68" s="37" t="str">
-        <x:f>IF(A68="","",IF(COUNTIF($R$6:$R$139,R68)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A68="","",IF(COUNTIF($R$6:$R$145,R68)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T68" s="37" t="str"/>
@@ -5589,7 +5646,7 @@
         <x:v>场景道具|facility|base_briefing|root|顶视|default</x:v>
       </x:c>
       <x:c r="S69" s="37" t="str">
-        <x:f>IF(A69="","",IF(COUNTIF($R$6:$R$139,R69)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A69="","",IF(COUNTIF($R$6:$R$145,R69)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T69" s="37" t="str"/>
@@ -5657,7 +5714,7 @@
         <x:v>场景道具|facility|base_workshop|root|顶视|default</x:v>
       </x:c>
       <x:c r="S70" s="37" t="str">
-        <x:f>IF(A70="","",IF(COUNTIF($R$6:$R$139,R70)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A70="","",IF(COUNTIF($R$6:$R$145,R70)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T70" s="37" t="str"/>
@@ -5725,7 +5782,7 @@
         <x:v>场景道具|facility|base_divination|root|顶视|default</x:v>
       </x:c>
       <x:c r="S71" s="37" t="str">
-        <x:f>IF(A71="","",IF(COUNTIF($R$6:$R$139,R71)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A71="","",IF(COUNTIF($R$6:$R$145,R71)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T71" s="37" t="str"/>
@@ -5793,7 +5850,7 @@
         <x:v>场景道具|facility|base_vault|root|顶视|default</x:v>
       </x:c>
       <x:c r="S72" s="37" t="str">
-        <x:f>IF(A72="","",IF(COUNTIF($R$6:$R$139,R72)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A72="","",IF(COUNTIF($R$6:$R$145,R72)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T72" s="37" t="str"/>
@@ -5861,7 +5918,7 @@
         <x:v>场景道具|facility|base_monster_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S73" s="37" t="str">
-        <x:f>IF(A73="","",IF(COUNTIF($R$6:$R$139,R73)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A73="","",IF(COUNTIF($R$6:$R$145,R73)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T73" s="37" t="str"/>
@@ -5929,7 +5986,7 @@
         <x:v>场景道具|facility|base_card_collection|root|顶视|default</x:v>
       </x:c>
       <x:c r="S74" s="37" t="str">
-        <x:f>IF(A74="","",IF(COUNTIF($R$6:$R$139,R74)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A74="","",IF(COUNTIF($R$6:$R$145,R74)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T74" s="37" t="str"/>
@@ -5997,7 +6054,7 @@
         <x:v>场景道具|facility|base_terminal|root|顶视|default</x:v>
       </x:c>
       <x:c r="S75" s="37" t="str">
-        <x:f>IF(A75="","",IF(COUNTIF($R$6:$R$139,R75)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A75="","",IF(COUNTIF($R$6:$R$145,R75)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T75" s="37" t="str"/>
@@ -6065,7 +6122,7 @@
         <x:v>场景道具|facility|dungeon_gate|root|顶视|default</x:v>
       </x:c>
       <x:c r="S76" s="37" t="str">
-        <x:f>IF(A76="","",IF(COUNTIF($R$6:$R$139,R76)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A76="","",IF(COUNTIF($R$6:$R$145,R76)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T76" s="37" t="str"/>
@@ -6133,7 +6190,7 @@
         <x:v>场景道具|facility|workbench|root|顶视|default</x:v>
       </x:c>
       <x:c r="S77" s="37" t="str">
-        <x:f>IF(A77="","",IF(COUNTIF($R$6:$R$139,R77)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A77="","",IF(COUNTIF($R$6:$R$145,R77)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T77" s="37" t="str"/>
@@ -6201,7 +6258,7 @@
         <x:v>场景道具|facility|door|root|顶视|default</x:v>
       </x:c>
       <x:c r="S78" s="37" t="str">
-        <x:f>IF(A78="","",IF(COUNTIF($R$6:$R$139,R78)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A78="","",IF(COUNTIF($R$6:$R$145,R78)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T78" s="37" t="str"/>
@@ -6269,7 +6326,7 @@
         <x:v>ui|screen|hud|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S79" s="37" t="str">
-        <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$139,R79)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$145,R79)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T79" s="37" t="str"/>
@@ -6316,7 +6373,7 @@
         <x:v>跨分辨率</x:v>
       </x:c>
       <x:c r="K80" s="37" t="str">
-        <x:v>程序占位</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L80" s="37" t="str">
         <x:v>P0</x:v>
@@ -6337,7 +6394,7 @@
         <x:v>ui|screen|inventory|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S80" s="37" t="str">
-        <x:f>IF(A80="","",IF(COUNTIF($R$6:$R$139,R80)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A80="","",IF(COUNTIF($R$6:$R$145,R80)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T80" s="37" t="str"/>
@@ -6345,13 +6402,13 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V80" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W80" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X80" s="37" t="str">
-        <x:v>先建组件库，再做页面，避免每页重复画按钮/面板</x:v>
+        <x:v>背包共享逻辑根；3D表现登记为 UI-SCREEN-INVENTORY-3D；12+2槽与保险契约不变</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -6405,7 +6462,7 @@
         <x:v>ui|screen|merchant|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S81" s="37" t="str">
-        <x:f>IF(A81="","",IF(COUNTIF($R$6:$R$139,R81)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A81="","",IF(COUNTIF($R$6:$R$145,R81)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T81" s="37" t="str"/>
@@ -6473,7 +6530,7 @@
         <x:v>ui|screen|workshop|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S82" s="37" t="str">
-        <x:f>IF(A82="","",IF(COUNTIF($R$6:$R$139,R82)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A82="","",IF(COUNTIF($R$6:$R$145,R82)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T82" s="37" t="str"/>
@@ -6541,7 +6598,7 @@
         <x:v>ui|screen|workbench|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S83" s="37" t="str">
-        <x:f>IF(A83="","",IF(COUNTIF($R$6:$R$139,R83)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A83="","",IF(COUNTIF($R$6:$R$145,R83)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T83" s="37" t="str"/>
@@ -6609,7 +6666,7 @@
         <x:v>ui|screen|weapon_tree|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S84" s="37" t="str">
-        <x:f>IF(A84="","",IF(COUNTIF($R$6:$R$139,R84)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A84="","",IF(COUNTIF($R$6:$R$145,R84)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T84" s="37" t="str"/>
@@ -6677,7 +6734,7 @@
         <x:v>ui|screen|fate_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S85" s="37" t="str">
-        <x:f>IF(A85="","",IF(COUNTIF($R$6:$R$139,R85)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A85="","",IF(COUNTIF($R$6:$R$145,R85)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T85" s="37" t="str"/>
@@ -6745,7 +6802,7 @@
         <x:v>ui|screen|fate_collection|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S86" s="37" t="str">
-        <x:f>IF(A86="","",IF(COUNTIF($R$6:$R$139,R86)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A86="","",IF(COUNTIF($R$6:$R$145,R86)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T86" s="37" t="str"/>
@@ -6813,7 +6870,7 @@
         <x:v>ui|screen|level_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S87" s="37" t="str">
-        <x:f>IF(A87="","",IF(COUNTIF($R$6:$R$139,R87)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A87="","",IF(COUNTIF($R$6:$R$145,R87)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T87" s="37" t="str"/>
@@ -6881,7 +6938,7 @@
         <x:v>ui|screen|vault|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S88" s="37" t="str">
-        <x:f>IF(A88="","",IF(COUNTIF($R$6:$R$139,R88)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A88="","",IF(COUNTIF($R$6:$R$145,R88)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T88" s="37" t="str"/>
@@ -6949,7 +7006,7 @@
         <x:v>ui|screen|monster_archive|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S89" s="37" t="str">
-        <x:f>IF(A89="","",IF(COUNTIF($R$6:$R$139,R89)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A89="","",IF(COUNTIF($R$6:$R$145,R89)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T89" s="37" t="str"/>
@@ -7017,7 +7074,7 @@
         <x:v>ui|screen|base_menu|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S90" s="37" t="str">
-        <x:f>IF(A90="","",IF(COUNTIF($R$6:$R$139,R90)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A90="","",IF(COUNTIF($R$6:$R$145,R90)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T90" s="37" t="str"/>
@@ -7085,7 +7142,7 @@
         <x:v>ui|screen|mobile_controls|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S91" s="37" t="str">
-        <x:f>IF(A91="","",IF(COUNTIF($R$6:$R$139,R91)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A91="","",IF(COUNTIF($R$6:$R$145,R91)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T91" s="37" t="str"/>
@@ -7153,7 +7210,7 @@
         <x:v>特效|gameplay_vfx|explosion|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S92" s="37" t="str">
-        <x:f>IF(A92="","",IF(COUNTIF($R$6:$R$139,R92)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A92="","",IF(COUNTIF($R$6:$R$145,R92)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T92" s="37" t="str"/>
@@ -7221,7 +7278,7 @@
         <x:v>特效|gameplay_vfx|muzzle_flash|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S93" s="37" t="str">
-        <x:f>IF(A93="","",IF(COUNTIF($R$6:$R$139,R93)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A93="","",IF(COUNTIF($R$6:$R$145,R93)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T93" s="37" t="str"/>
@@ -7289,7 +7346,7 @@
         <x:v>特效|gameplay_vfx|damage_number|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S94" s="37" t="str">
-        <x:f>IF(A94="","",IF(COUNTIF($R$6:$R$139,R94)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A94="","",IF(COUNTIF($R$6:$R$145,R94)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T94" s="37" t="str"/>
@@ -7357,7 +7414,7 @@
         <x:v>特效|gameplay_vfx|spark|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S95" s="37" t="str">
-        <x:f>IF(A95="","",IF(COUNTIF($R$6:$R$139,R95)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A95="","",IF(COUNTIF($R$6:$R$145,R95)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T95" s="37" t="str"/>
@@ -7425,7 +7482,7 @@
         <x:v>特效|gameplay_vfx|room_transition|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S96" s="37" t="str">
-        <x:f>IF(A96="","",IF(COUNTIF($R$6:$R$139,R96)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A96="","",IF(COUNTIF($R$6:$R$145,R96)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T96" s="37" t="str"/>
@@ -7472,7 +7529,7 @@
         <x:v>跨武器/跨场景</x:v>
       </x:c>
       <x:c r="K97" s="37" t="str">
-        <x:v>程序占位</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L97" s="37" t="str">
         <x:v>P2</x:v>
@@ -7483,9 +7540,11 @@
       <x:c r="N97" s="37" t="str">
         <x:v>粒子或 8–16 帧序列</x:v>
       </x:c>
-      <x:c r="O97" s="37" t="str"/>
+      <x:c r="O97" s="37" t="str">
+        <x:v>scenes/Dungeon3D.tscn</x:v>
+      </x:c>
       <x:c r="P97" s="37" t="str">
-        <x:v>src/fx/HealthVignette.gd</x:v>
+        <x:v>src/world3d/Dungeon3D.gd</x:v>
       </x:c>
       <x:c r="Q97" s="37" t="str"/>
       <x:c r="R97" s="37" t="str">
@@ -7493,7 +7552,7 @@
         <x:v>特效|gameplay_vfx|health_vignette|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S97" s="37" t="str">
-        <x:f>IF(A97="","",IF(COUNTIF($R$6:$R$139,R97)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A97="","",IF(COUNTIF($R$6:$R$145,R97)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T97" s="37" t="str"/>
@@ -7501,13 +7560,13 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V97" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W97" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X97" s="37" t="str">
-        <x:v>颜色/尺寸作参数变体，禁止复制整套</x:v>
+        <x:v>复用低血暗角身份；3D HUD低血时提高边缘强度，不复制第二套逻辑ID</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -7561,7 +7620,7 @@
         <x:v>特效|gameplay_vfx|visibility_light|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S98" s="37" t="str">
-        <x:f>IF(A98="","",IF(COUNTIF($R$6:$R$139,R98)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A98="","",IF(COUNTIF($R$6:$R$145,R98)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T98" s="37" t="str"/>
@@ -7569,13 +7628,13 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V98" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W98" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X98" s="37" t="str">
-        <x:v>颜色/尺寸作参数变体，禁止复制整套</x:v>
+        <x:v>2D视野表现根；3D真实判定与地面网格登记为 VFX-VISIBILITY-FIELD-3D，禁止用灯光替代</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -7629,7 +7688,7 @@
         <x:v>特效|gameplay_vfx|extraction_beacon|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S99" s="37" t="str">
-        <x:f>IF(A99="","",IF(COUNTIF($R$6:$R$139,R99)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A99="","",IF(COUNTIF($R$6:$R$145,R99)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T99" s="37" t="str"/>
@@ -7697,7 +7756,7 @@
         <x:v>音频|bgm|bgm_wasteland|root|不适用|default</x:v>
       </x:c>
       <x:c r="S100" s="37" t="str">
-        <x:f>IF(A100="","",IF(COUNTIF($R$6:$R$139,R100)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A100="","",IF(COUNTIF($R$6:$R$145,R100)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T100" s="37" t="str"/>
@@ -7763,7 +7822,7 @@
         <x:v>音频|sfx|pistol_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S101" s="37" t="str">
-        <x:f>IF(A101="","",IF(COUNTIF($R$6:$R$139,R101)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A101="","",IF(COUNTIF($R$6:$R$145,R101)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T101" s="37" t="str"/>
@@ -7829,7 +7888,7 @@
         <x:v>音频|sfx|rifle_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S102" s="37" t="str">
-        <x:f>IF(A102="","",IF(COUNTIF($R$6:$R$139,R102)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A102="","",IF(COUNTIF($R$6:$R$145,R102)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T102" s="37" t="str"/>
@@ -7895,7 +7954,7 @@
         <x:v>音频|sfx|shotgun_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S103" s="37" t="str">
-        <x:f>IF(A103="","",IF(COUNTIF($R$6:$R$139,R103)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A103="","",IF(COUNTIF($R$6:$R$145,R103)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T103" s="37" t="str"/>
@@ -7961,7 +8020,7 @@
         <x:v>音频|sfx|smg_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S104" s="37" t="str">
-        <x:f>IF(A104="","",IF(COUNTIF($R$6:$R$139,R104)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A104="","",IF(COUNTIF($R$6:$R$145,R104)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T104" s="37" t="str"/>
@@ -8027,7 +8086,7 @@
         <x:v>音频|sfx|sniper_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S105" s="37" t="str">
-        <x:f>IF(A105="","",IF(COUNTIF($R$6:$R$139,R105)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A105="","",IF(COUNTIF($R$6:$R$145,R105)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T105" s="37" t="str"/>
@@ -8093,7 +8152,7 @@
         <x:v>音频|sfx|player_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S106" s="37" t="str">
-        <x:f>IF(A106="","",IF(COUNTIF($R$6:$R$139,R106)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A106="","",IF(COUNTIF($R$6:$R$145,R106)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T106" s="37" t="str"/>
@@ -8159,7 +8218,7 @@
         <x:v>音频|sfx|player_dash|root|不适用|default</x:v>
       </x:c>
       <x:c r="S107" s="37" t="str">
-        <x:f>IF(A107="","",IF(COUNTIF($R$6:$R$139,R107)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A107="","",IF(COUNTIF($R$6:$R$145,R107)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T107" s="37" t="str"/>
@@ -8225,7 +8284,7 @@
         <x:v>音频|sfx|enemy_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S108" s="37" t="str">
-        <x:f>IF(A108="","",IF(COUNTIF($R$6:$R$139,R108)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A108="","",IF(COUNTIF($R$6:$R$145,R108)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T108" s="37" t="str"/>
@@ -8291,7 +8350,7 @@
         <x:v>音频|sfx|enemy_die|root|不适用|default</x:v>
       </x:c>
       <x:c r="S109" s="37" t="str">
-        <x:f>IF(A109="","",IF(COUNTIF($R$6:$R$139,R109)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A109="","",IF(COUNTIF($R$6:$R$145,R109)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T109" s="37" t="str"/>
@@ -8357,7 +8416,7 @@
         <x:v>音频|sfx|reload|root|不适用|default</x:v>
       </x:c>
       <x:c r="S110" s="37" t="str">
-        <x:f>IF(A110="","",IF(COUNTIF($R$6:$R$139,R110)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A110="","",IF(COUNTIF($R$6:$R$145,R110)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T110" s="37" t="str"/>
@@ -8423,7 +8482,7 @@
         <x:v>音频|sfx|extraction_start|root|不适用|default</x:v>
       </x:c>
       <x:c r="S111" s="37" t="str">
-        <x:f>IF(A111="","",IF(COUNTIF($R$6:$R$139,R111)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A111="","",IF(COUNTIF($R$6:$R$145,R111)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T111" s="37" t="str"/>
@@ -8489,7 +8548,7 @@
         <x:v>音频|sfx|extraction_done|root|不适用|default</x:v>
       </x:c>
       <x:c r="S112" s="37" t="str">
-        <x:f>IF(A112="","",IF(COUNTIF($R$6:$R$139,R112)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A112="","",IF(COUNTIF($R$6:$R$145,R112)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T112" s="37" t="str"/>
@@ -8561,7 +8620,7 @@
         <x:v>角色|player|player_capsule01|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S113" t="str">
-        <x:f>IF(A113="","",IF(COUNTIF($R$6:$R$139,R113)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A113="","",IF(COUNTIF($R$6:$R$145,R113)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T113" t="str">
@@ -8637,7 +8696,7 @@
         <x:v>角色|player|player_capsule01|body_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S114" t="str">
-        <x:f>IF(A114="","",IF(COUNTIF($R$6:$R$139,R114)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A114="","",IF(COUNTIF($R$6:$R$145,R114)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T114" t="str">
@@ -8713,7 +8772,7 @@
         <x:v>角色|player|player_capsule01|head_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S115" t="str">
-        <x:f>IF(A115="","",IF(COUNTIF($R$6:$R$139,R115)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A115="","",IF(COUNTIF($R$6:$R$145,R115)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T115" t="str">
@@ -8789,7 +8848,7 @@
         <x:v>角色|player|player_capsule01|hand_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S116" t="str">
-        <x:f>IF(A116="","",IF(COUNTIF($R$6:$R$139,R116)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A116="","",IF(COUNTIF($R$6:$R$145,R116)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T116" t="str">
@@ -8865,7 +8924,7 @@
         <x:v>角色|player|player_capsule01|scarf_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S117" t="str">
-        <x:f>IF(A117="","",IF(COUNTIF($R$6:$R$139,R117)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A117="","",IF(COUNTIF($R$6:$R$145,R117)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T117" t="str">
@@ -8941,7 +9000,7 @@
         <x:v>角色|player|player_capsule01|weapon_socket_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S118" t="str">
-        <x:f>IF(A118="","",IF(COUNTIF($R$6:$R$139,R118)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A118="","",IF(COUNTIF($R$6:$R$145,R118)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T118" t="str">
@@ -9017,7 +9076,7 @@
         <x:v>场景|base|base_world|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S119" t="str">
-        <x:f>IF(A119="","",IF(COUNTIF($R$6:$R$139,R119)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A119="","",IF(COUNTIF($R$6:$R$145,R119)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T119" t="str">
@@ -9093,7 +9152,7 @@
         <x:v>场景道具|facility|base_facility_module|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S120" t="str">
-        <x:f>IF(A120="","",IF(COUNTIF($R$6:$R$139,R120)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A120="","",IF(COUNTIF($R$6:$R$145,R120)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T120" t="str">
@@ -9169,7 +9228,7 @@
         <x:v>场景道具|door|dungeon_gate|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S121" t="str">
-        <x:f>IF(A121="","",IF(COUNTIF($R$6:$R$139,R121)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A121="","",IF(COUNTIF($R$6:$R$145,R121)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T121" t="str">
@@ -9245,7 +9304,7 @@
         <x:v>场景|review_board|base_world|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S122" t="str">
-        <x:f>IF(A122="","",IF(COUNTIF($R$6:$R$139,R122)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A122="","",IF(COUNTIF($R$6:$R$145,R122)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T122" t="str">
@@ -9319,7 +9378,7 @@
         <x:v>场景|room|dungeon_runtime|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S123" s="63" t="str">
-        <x:f>IF(A123="","",IF(COUNTIF($R$6:$R$139,R123)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A123="","",IF(COUNTIF($R$6:$R$145,R123)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T123" s="63" t="str">
@@ -9395,7 +9454,7 @@
         <x:v>场景|biome|iron_frontier|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S124" s="63" t="str">
-        <x:f>IF(A124="","",IF(COUNTIF($R$6:$R$139,R124)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A124="","",IF(COUNTIF($R$6:$R$145,R124)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T124" s="63" t="str">
@@ -9471,7 +9530,7 @@
         <x:v>场景|biome|rust_foundry|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S125" s="63" t="str">
-        <x:f>IF(A125="","",IF(COUNTIF($R$6:$R$139,R125)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A125="","",IF(COUNTIF($R$6:$R$145,R125)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T125" s="63" t="str">
@@ -9547,7 +9606,7 @@
         <x:v>场景|biome|spore_depths|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S126" s="63" t="str">
-        <x:f>IF(A126="","",IF(COUNTIF($R$6:$R$139,R126)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A126="","",IF(COUNTIF($R$6:$R$145,R126)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T126" s="63" t="str">
@@ -9623,7 +9682,7 @@
         <x:v>场景|biome|abyss_archive|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S127" s="63" t="str">
-        <x:f>IF(A127="","",IF(COUNTIF($R$6:$R$139,R127)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A127="","",IF(COUNTIF($R$6:$R$145,R127)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T127" s="63" t="str">
@@ -9647,7 +9706,7 @@
         <x:v>PRP-WASTELAND-LIGHT-3D</x:v>
       </x:c>
       <x:c r="B128" s="63" t="str">
-        <x:v>废土灯具3D通用模块</x:v>
+        <x:v>废土灯具3D通用模块（街灯/顶灯）</x:v>
       </x:c>
       <x:c r="C128" s="63" t="str">
         <x:v>场景道具</x:v>
@@ -9671,7 +9730,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="J128" s="63" t="str">
-        <x:v>关卡/靶场照明</x:v>
+        <x:v>关卡/靶场/房间中央照明</x:v>
       </x:c>
       <x:c r="K128" s="63" t="str">
         <x:v>原型已接入</x:v>
@@ -9692,14 +9751,14 @@
         <x:v>src/world3d/WastelandLight3D.gd</x:v>
       </x:c>
       <x:c r="Q128" s="63" t="str">
-        <x:v>灯具;光池;故障灯;废土</x:v>
+        <x:v>灯具;街灯;中央顶灯;故障灯;废土</x:v>
       </x:c>
       <x:c r="R128" s="63" t="str">
         <x:f>LOWER(TRIM(C128)&amp;"|"&amp;TRIM(D128)&amp;"|"&amp;TRIM(E128)&amp;"|"&amp;TRIM(F128)&amp;"|"&amp;TRIM(H128)&amp;"|"&amp;TRIM(I128))</x:f>
         <x:v>场景道具|light|wasteland_light|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S128" s="63" t="str">
-        <x:f>IF(A128="","",IF(COUNTIF($R$6:$R$139,R128)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A128="","",IF(COUNTIF($R$6:$R$145,R128)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T128" s="63" t="str">
@@ -9709,13 +9768,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V128" s="64" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W128" s="63" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X128" s="63" t="str">
-        <x:v>灯架、灯罩、真实光源、低频故障与地面光池同一根</x:v>
+        <x:v>同根支持 street/ceiling；房间只实例化唯一中央顶灯，不生成室内路灯或假光池；默认关闭并由墙面开关控制</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="34" customHeight="1">
@@ -9775,7 +9834,7 @@
         <x:v>场景道具|furniture|room_furniture|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S129" s="63" t="str">
-        <x:f>IF(A129="","",IF(COUNTIF($R$6:$R$139,R129)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A129="","",IF(COUNTIF($R$6:$R$145,R129)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T129" s="63" t="str">
@@ -9851,7 +9910,7 @@
         <x:v>场景道具|container|search_container|root_3d|俯视3d|closed_opened</x:v>
       </x:c>
       <x:c r="S130" s="63" t="str">
-        <x:f>IF(A130="","",IF(COUNTIF($R$6:$R$139,R130)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A130="","",IF(COUNTIF($R$6:$R$145,R130)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T130" s="63" t="str">
@@ -9927,7 +9986,7 @@
         <x:v>场景道具|facility|service_station|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S131" s="63" t="str">
-        <x:f>IF(A131="","",IF(COUNTIF($R$6:$R$139,R131)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A131="","",IF(COUNTIF($R$6:$R$145,R131)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T131" s="63" t="str">
@@ -10003,7 +10062,7 @@
         <x:v>场景道具|facility|extraction_beacon|root_3d|俯视3d|locked_active_done</x:v>
       </x:c>
       <x:c r="S132" s="63" t="str">
-        <x:f>IF(A132="","",IF(COUNTIF($R$6:$R$139,R132)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A132="","",IF(COUNTIF($R$6:$R$145,R132)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T132" s="63" t="str">
@@ -10079,7 +10138,7 @@
         <x:v>特效|environment|hazard_field|root_3d|俯视3d|active</x:v>
       </x:c>
       <x:c r="S133" s="63" t="str">
-        <x:f>IF(A133="","",IF(COUNTIF($R$6:$R$139,R133)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A133="","",IF(COUNTIF($R$6:$R$145,R133)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T133" s="63" t="str">
@@ -10153,7 +10212,7 @@
         <x:v>枪械|gunbody|blueprint_gun_catalog|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S134" s="63" t="str">
-        <x:f>IF(A134="","",IF(COUNTIF($R$6:$R$139,R134)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A134="","",IF(COUNTIF($R$6:$R$145,R134)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T134" s="63" t="str">
@@ -10169,7 +10228,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X134" s="63" t="str">
-        <x:v>读取BlueprintRegistry唯一目录；覆盖56种组合；枪局部后坐力不带动手</x:v>
+        <x:v>真实GPU窗口检查暗室、家具、角色、怪物和战斗；开灯状态复用同一身份，验收图：assets/art/environments/dungeon_3d/env_dungeon_runtime_light_on_preview_top3d_v001.png</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="34" customHeight="1">
@@ -10227,7 +10286,7 @@
         <x:v>敌人|normal_elite_boss|enemy_ecosystem|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S135" s="63" t="str">
-        <x:f>IF(A135="","",IF(COUNTIF($R$6:$R$139,R135)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A135="","",IF(COUNTIF($R$6:$R$145,R135)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T135" s="63" t="str">
@@ -10237,13 +10296,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V135" s="64" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W135" s="63" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X135" s="63" t="str">
-        <x:v>追猎/远程/召唤/盾甲/自爆/伏击/Boss；统一七态</x:v>
+        <x:v>追猎/远程/召唤/盾甲/自爆/伏击/Boss；统一九态：idle/patrol/alert/chase/search/telegraph/attack/stagger/dead</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="34" customHeight="1">
@@ -10301,7 +10360,7 @@
         <x:v>特效|combat|combat_feedback|root_3d|俯视3d|muzzle_impact_damage_explosion</x:v>
       </x:c>
       <x:c r="S136" s="63" t="str">
-        <x:f>IF(A136="","",IF(COUNTIF($R$6:$R$139,R136)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A136="","",IF(COUNTIF($R$6:$R$145,R136)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T136" s="63" t="str">
@@ -10375,7 +10434,7 @@
         <x:v>场景|training_range|training_range|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S137" s="63" t="str">
-        <x:f>IF(A137="","",IF(COUNTIF($R$6:$R$139,R137)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A137="","",IF(COUNTIF($R$6:$R$145,R137)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T137" s="63" t="str">
@@ -10451,7 +10510,7 @@
         <x:v>场景|review_board|dungeon_runtime|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S138" s="63" t="str">
-        <x:f>IF(A138="","",IF(COUNTIF($R$6:$R$139,R138)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A138="","",IF(COUNTIF($R$6:$R$145,R138)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T138" s="63" t="str">
@@ -10527,7 +10586,7 @@
         <x:v>场景|review_board|training_range|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S139" s="63" t="str">
-        <x:f>IF(A139="","",IF(COUNTIF($R$6:$R$139,R139)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A139="","",IF(COUNTIF($R$6:$R$145,R139)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T139" s="63" t="str">
@@ -10544,6 +10603,460 @@
       </x:c>
       <x:c r="X139" s="63" t="str">
         <x:v>真实GPU窗口检查三条射击道、三类靶、枪弹组合区与灯光</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>VFX-VISIBILITY-FIELD-3D</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>柔边真实单位视野场3D</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>特效</x:v>
+      </x:c>
+      <x:c r="D140" t="str">
+        <x:v>gameplay_vfx</x:v>
+      </x:c>
+      <x:c r="E140" t="str">
+        <x:v>visibility_field</x:v>
+      </x:c>
+      <x:c r="F140" t="str">
+        <x:v>field_mesh_3d</x:v>
+      </x:c>
+      <x:c r="G140" t="str">
+        <x:v>VFX-VISIBILITY-LIGHT</x:v>
+      </x:c>
+      <x:c r="H140" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I140" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J140" t="str">
+        <x:v>3D行动区/靶场/基地</x:v>
+      </x:c>
+      <x:c r="K140" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L140" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M140" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N140" t="str">
+        <x:v>ImmediateMesh 49+28射线</x:v>
+      </x:c>
+      <x:c r="O140" t="str">
+        <x:v>src/player3d/PlayerVision3D.gd</x:v>
+      </x:c>
+      <x:c r="P140" t="str">
+        <x:v>scenes/Player3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q140" t="str">
+        <x:v>真实视野;柔边;墙体遮挡;无描边;非灯光判定</x:v>
+      </x:c>
+      <x:c r="R140" t="str">
+        <x:f>LOWER(TRIM(C140)&amp;"|"&amp;TRIM(D140)&amp;"|"&amp;TRIM(E140)&amp;"|"&amp;TRIM(F140)&amp;"|"&amp;TRIM(H140)&amp;"|"&amp;TRIM(I140))</x:f>
+        <x:v>特效|gameplay_vfx|visibility_field|field_mesh_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S140" t="str">
+        <x:f>IF(A140="","",IF(COUNTIF($R$6:$R$145,R140)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T140" t="str">
+        <x:v>9cf388d92b26316426fe4aab529001ebd544731ea466470236ad73cdd655e87c</x:v>
+      </x:c>
+      <x:c r="U140" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V140" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="W140" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X140" t="str">
+        <x:v>逻辑与地面表现复用同批射线；96°/21m + 2.4m；柔边无描边且不受地板深度遮挡；真实照明拆为 VFX-PLAYER-FLASHLIGHT-3D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>UI-SCREEN-INVENTORY-3D</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>3D背包与保险界面</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="D141" t="str">
+        <x:v>screen</x:v>
+      </x:c>
+      <x:c r="E141" t="str">
+        <x:v>inventory</x:v>
+      </x:c>
+      <x:c r="F141" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G141" t="str">
+        <x:v>UI-SCREEN-INVENTORY</x:v>
+      </x:c>
+      <x:c r="H141" t="str">
+        <x:v>屏幕空间</x:v>
+      </x:c>
+      <x:c r="I141" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J141" t="str">
+        <x:v>3D行动区</x:v>
+      </x:c>
+      <x:c r="K141" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L141" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M141" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N141" t="str">
+        <x:v>全屏Control/12+2槽/96×96投影</x:v>
+      </x:c>
+      <x:c r="O141" t="str">
+        <x:v>src/ui/InventoryUI.gd</x:v>
+      </x:c>
+      <x:c r="P141" t="str">
+        <x:v>scenes/Dungeon3D.tscn</x:v>
+      </x:c>
+      <x:c r="Q141" t="str">
+        <x:v>背包;保险;I键;Tab;模态输入锁;3D道具投影;实际点击装备</x:v>
+      </x:c>
+      <x:c r="R141" t="str">
+        <x:f>LOWER(TRIM(C141)&amp;"|"&amp;TRIM(D141)&amp;"|"&amp;TRIM(E141)&amp;"|"&amp;TRIM(F141)&amp;"|"&amp;TRIM(H141)&amp;"|"&amp;TRIM(I141))</x:f>
+        <x:v>ui|screen|inventory|root_3d|屏幕空间|default</x:v>
+      </x:c>
+      <x:c r="S141" t="str">
+        <x:f>IF(A141="","",IF(COUNTIF($R$6:$R$145,R141)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T141" t="str">
+        <x:v>ccd8f7d7f3c99454d157f0dfd2f34631a4d404931f2e1997b5c381db9ac90c99</x:v>
+      </x:c>
+      <x:c r="U141" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V141" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="W141" t="str">
+        <x:v>原创程序UI</x:v>
+      </x:c>
+      <x:c r="X141" t="str">
+        <x:v>复用背包根身份的3D子变体；I/Tab；打开时锁输入；道具共用 ItemModelFactory3D；实际 ItemSlot 信号完成换枪</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>UI-SCREEN-PAUSE-3D</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>3D共用暂停界面</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="D142" t="str">
+        <x:v>screen</x:v>
+      </x:c>
+      <x:c r="E142" t="str">
+        <x:v>pause</x:v>
+      </x:c>
+      <x:c r="F142" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G142"/>
+      <x:c r="H142" t="str">
+        <x:v>屏幕空间</x:v>
+      </x:c>
+      <x:c r="I142" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J142" t="str">
+        <x:v>地下城/基地/靶场</x:v>
+      </x:c>
+      <x:c r="K142" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L142" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M142" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N142" t="str">
+        <x:v>PackedScene/全屏Control</x:v>
+      </x:c>
+      <x:c r="O142" t="str">
+        <x:v>assets/art/ui/pause_3d/ui_pause_overlay_screen_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P142" t="str">
+        <x:v>src/ui/PauseMenu3D.gd</x:v>
+      </x:c>
+      <x:c r="Q142" t="str">
+        <x:v>暂停;Esc;继续;全局模态;3D HUD</x:v>
+      </x:c>
+      <x:c r="R142" t="str">
+        <x:f>LOWER(TRIM(C142)&amp;"|"&amp;TRIM(D142)&amp;"|"&amp;TRIM(E142)&amp;"|"&amp;TRIM(F142)&amp;"|"&amp;TRIM(H142)&amp;"|"&amp;TRIM(I142))</x:f>
+        <x:v>ui|screen|pause|root_3d|屏幕空间|default</x:v>
+      </x:c>
+      <x:c r="S142" t="str">
+        <x:f>IF(A142="","",IF(COUNTIF($R$6:$R$145,R142)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T142" t="str">
+        <x:v>8fed542ebf6b89002c6922a287e666394472252ad9673d8183dd9db604c19a88</x:v>
+      </x:c>
+      <x:c r="U142" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V142" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="W142" t="str">
+        <x:v>原创程序UI</x:v>
+      </x:c>
+      <x:c r="X142" t="str">
+        <x:v>三张3D地图共用；Esc先关闭最上层模态，再进入真实暂停</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>PRP-ROOM-LIGHT-SWITCH-3D</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>房间中央灯墙面开关3D</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>场景道具</x:v>
+      </x:c>
+      <x:c r="D143" t="str">
+        <x:v>facility</x:v>
+      </x:c>
+      <x:c r="E143" t="str">
+        <x:v>room_light_switch</x:v>
+      </x:c>
+      <x:c r="F143" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G143" t="str">
+        <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
+      </x:c>
+      <x:c r="H143" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I143" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J143" t="str">
+        <x:v>随机关卡房间/四主题复用</x:v>
+      </x:c>
+      <x:c r="K143" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L143" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M143" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N143" t="str">
+        <x:v>PackedScene/Area3D</x:v>
+      </x:c>
+      <x:c r="O143" t="str">
+        <x:v>assets/art/props/dungeon_3d/prp_room_light_switch_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P143" t="str">
+        <x:v>src/world3d/RoomLightSwitch3D.gd</x:v>
+      </x:c>
+      <x:c r="Q143" t="str">
+        <x:v>房灯开关;墙面交互;中央顶灯;E键</x:v>
+      </x:c>
+      <x:c r="R143" t="str">
+        <x:f>LOWER(TRIM(C143)&amp;"|"&amp;TRIM(D143)&amp;"|"&amp;TRIM(E143)&amp;"|"&amp;TRIM(F143)&amp;"|"&amp;TRIM(H143)&amp;"|"&amp;TRIM(I143))</x:f>
+        <x:v>场景道具|facility|room_light_switch|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S143" t="str">
+        <x:f>IF(A143="","",IF(COUNTIF($R$6:$R$145,R143)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T143" t="str">
+        <x:v>7802bc3a71d892072e43962875e26b60443d19de35bcc77fe0cbedcfa6dd5d94</x:v>
+      </x:c>
+      <x:c r="U143" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V143" s="62" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="W143" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X143" t="str">
+        <x:v>每个房间共用一件；E键切换唯一中央顶灯；禁止复制到各主题局部目录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>VFX-PLAYER-FLASHLIGHT-3D</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>玩家真实探照灯组件3D</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>特效</x:v>
+      </x:c>
+      <x:c r="D144" t="str">
+        <x:v>gameplay_vfx</x:v>
+      </x:c>
+      <x:c r="E144" t="str">
+        <x:v>player_flashlight</x:v>
+      </x:c>
+      <x:c r="F144" t="str">
+        <x:v>light_rig_3d</x:v>
+      </x:c>
+      <x:c r="G144" t="str">
+        <x:v>VFX-VISIBILITY-FIELD-3D</x:v>
+      </x:c>
+      <x:c r="H144" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I144" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J144" t="str">
+        <x:v>3D行动区/靶场/基地</x:v>
+      </x:c>
+      <x:c r="K144" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L144" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M144" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N144" t="str">
+        <x:v>PackedScene/SpotLight3D+OmniLight3D</x:v>
+      </x:c>
+      <x:c r="O144" t="str">
+        <x:v>assets/art/vfx/visibility_3d/vfx_player_flashlight_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P144" t="str">
+        <x:v>src/player3d/PlayerFlashlight3D.gd</x:v>
+      </x:c>
+      <x:c r="Q144" t="str">
+        <x:v>真实探照灯;玩家灯光;前向聚光;角色补光;可调灯光</x:v>
+      </x:c>
+      <x:c r="R144" t="str">
+        <x:f>LOWER(TRIM(C144)&amp;"|"&amp;TRIM(D144)&amp;"|"&amp;TRIM(E144)&amp;"|"&amp;TRIM(F144)&amp;"|"&amp;TRIM(H144)&amp;"|"&amp;TRIM(I144))</x:f>
+        <x:v>特效|gameplay_vfx|player_flashlight|light_rig_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S144" t="str">
+        <x:f>IF(A144="","",IF(COUNTIF($R$6:$R$145,R144)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T144" t="str">
+        <x:v>b389efe1d1fcfd30087a6d3f3f2784effee95cf6c54769fde27ecb6806011a05</x:v>
+      </x:c>
+      <x:c r="U144" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V144" s="62" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="W144" t="str">
+        <x:v>原创程序灯光</x:v>
+      </x:c>
+      <x:c r="X144" t="str">
+        <x:v>独立于玩法视野；1盏投影主聚光 + 1盏无阴影近身补光；颜色/能量/范围/角度/衰减/挂点均可调</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>UI-ICON-ITEM-MODEL-3D</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>背包道具3D模型投影组件</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="D145" t="str">
+        <x:v>icon</x:v>
+      </x:c>
+      <x:c r="E145" t="str">
+        <x:v>item_model_icon</x:v>
+      </x:c>
+      <x:c r="F145" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G145" t="str">
+        <x:v>UI-SCREEN-INVENTORY-3D</x:v>
+      </x:c>
+      <x:c r="H145" t="str">
+        <x:v>屏幕空间/3D投影</x:v>
+      </x:c>
+      <x:c r="I145" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J145" t="str">
+        <x:v>背包/保险格/道具预览</x:v>
+      </x:c>
+      <x:c r="K145" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L145" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M145" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N145" t="str">
+        <x:v>96×96 SubViewport/UPDATE_ONCE</x:v>
+      </x:c>
+      <x:c r="O145" t="str">
+        <x:v>assets/art/ui/inventory_3d/ui_item_model_icon_root_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P145" t="str">
+        <x:v>src/ui/ItemModelIcon3D.gd</x:v>
+      </x:c>
+      <x:c r="Q145" t="str">
+        <x:v>3D道具图标;模型投影;背包图标;共享世界模型;单次渲染</x:v>
+      </x:c>
+      <x:c r="R145" t="str">
+        <x:f>LOWER(TRIM(C145)&amp;"|"&amp;TRIM(D145)&amp;"|"&amp;TRIM(E145)&amp;"|"&amp;TRIM(F145)&amp;"|"&amp;TRIM(H145)&amp;"|"&amp;TRIM(I145))</x:f>
+        <x:v>ui|icon|item_model_icon|root_3d|屏幕空间/3d投影|default</x:v>
+      </x:c>
+      <x:c r="S145" t="str">
+        <x:f>IF(A145="","",IF(COUNTIF($R$6:$R$145,R145)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T145" t="str">
+        <x:v>97c10f3884107c1263f3de1f8bc1ce84bb568ecd80418b62bdb023c55cdab9fe</x:v>
+      </x:c>
+      <x:c r="U145" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V145" s="62" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="W145" t="str">
+        <x:v>原创程序UI</x:v>
+      </x:c>
+      <x:c r="X145" t="str">
+        <x:v>与地面拾取共用 ItemModelFactory3D；96×96 内部视口缩放至56px槽位；只渲染一次；验收图：assets/art/ui/inventory_3d/ui_inventory_item_model_preview_v001.png</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10571,7 +11084,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2abd959a34ee4d7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2edbae0a0fb542b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11717,21 +12230,21 @@
         <x:v>InvincibleTimer 唯一解除</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="63" t="str">
-        <x:v>Enemy3D 七态状态机 × 模块表现映射</x:v>
-      </x:c>
-      <x:c r="B16" s="63"/>
-      <x:c r="C16" s="63"/>
-      <x:c r="D16" s="63"/>
-      <x:c r="E16" s="63"/>
-      <x:c r="F16" s="63"/>
-      <x:c r="G16" s="63"/>
-      <x:c r="H16" s="63"/>
-      <x:c r="I16" s="63"/>
-      <x:c r="J16" s="63"/>
-      <x:c r="K16" s="63"/>
-      <x:c r="L16" s="63"/>
+    <x:row r="16" ht="28" customHeight="1">
+      <x:c r="A16" s="69" t="str">
+        <x:v>Enemy3D 九态状态机 × 模块表现 × 模型轮廓碰撞</x:v>
+      </x:c>
+      <x:c r="B16" s="69"/>
+      <x:c r="C16" s="69"/>
+      <x:c r="D16" s="69"/>
+      <x:c r="E16" s="69"/>
+      <x:c r="F16" s="69"/>
+      <x:c r="G16" s="69"/>
+      <x:c r="H16" s="69"/>
+      <x:c r="I16" s="69"/>
+      <x:c r="J16" s="69"/>
+      <x:c r="K16" s="69"/>
+      <x:c r="L16" s="69"/>
     </x:row>
     <x:row r="17" ht="36" customHeight="1">
       <x:c r="A17" s="63" t="str">
@@ -11782,10 +12295,10 @@
         <x:v>待机</x:v>
       </x:c>
       <x:c r="D18" s="63" t="str">
-        <x:v>start/stagger</x:v>
+        <x:v>start/patrol/stagger</x:v>
       </x:c>
       <x:c r="E18" s="63" t="str">
-        <x:v>alert/dead</x:v>
+        <x:v>patrol/alert/dead</x:v>
       </x:c>
       <x:c r="F18" s="63" t="str">
         <x:v>低频脉冲</x:v>
@@ -11814,37 +12327,37 @@
         <x:v>顶层</x:v>
       </x:c>
       <x:c r="B19" s="63" t="str">
-        <x:v>alert</x:v>
+        <x:v>patrol</x:v>
       </x:c>
       <x:c r="C19" s="63" t="str">
-        <x:v>警觉</x:v>
+        <x:v>巡逻</x:v>
       </x:c>
       <x:c r="D19" s="63" t="str">
-        <x:v>idle</x:v>
+        <x:v>idle/search</x:v>
       </x:c>
       <x:c r="E19" s="63" t="str">
-        <x:v>chase/dead</x:v>
+        <x:v>idle/alert/stagger/dead</x:v>
       </x:c>
       <x:c r="F19" s="63" t="str">
-        <x:v>加速</x:v>
+        <x:v>低频脉冲</x:v>
       </x:c>
       <x:c r="G19" s="63" t="str">
-        <x:v>抬升</x:v>
+        <x:v>朝巡逻点</x:v>
       </x:c>
       <x:c r="H19" s="63" t="str">
-        <x:v>展开</x:v>
+        <x:v>慢速步态</x:v>
       </x:c>
       <x:c r="I19" s="63" t="str">
         <x:v>关闭</x:v>
       </x:c>
       <x:c r="J19" s="63" t="str">
-        <x:v>发现玩家</x:v>
+        <x:v>出生点附近巡逻</x:v>
       </x:c>
       <x:c r="K19" s="63" t="str">
-        <x:v>0.28s响应</x:v>
+        <x:v>无目标不原地僵住</x:v>
       </x:c>
       <x:c r="L19" s="63" t="str">
-        <x:v>模块变换</x:v>
+        <x:v>CharacterBody3D</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
@@ -11852,37 +12365,37 @@
         <x:v>顶层</x:v>
       </x:c>
       <x:c r="B20" s="63" t="str">
-        <x:v>chase</x:v>
+        <x:v>alert</x:v>
       </x:c>
       <x:c r="C20" s="63" t="str">
-        <x:v>追击</x:v>
+        <x:v>警觉</x:v>
       </x:c>
       <x:c r="D20" s="63" t="str">
-        <x:v>alert/attack/stagger</x:v>
+        <x:v>idle/patrol/search</x:v>
       </x:c>
       <x:c r="E20" s="63" t="str">
-        <x:v>telegraph/stagger/dead</x:v>
+        <x:v>chase/stagger/dead</x:v>
       </x:c>
       <x:c r="F20" s="63" t="str">
-        <x:v>稳定</x:v>
+        <x:v>加速</x:v>
       </x:c>
       <x:c r="G20" s="63" t="str">
-        <x:v>朝目标</x:v>
+        <x:v>抬升</x:v>
       </x:c>
       <x:c r="H20" s="63" t="str">
-        <x:v>步态</x:v>
+        <x:v>展开</x:v>
       </x:c>
       <x:c r="I20" s="63" t="str">
         <x:v>关闭</x:v>
       </x:c>
       <x:c r="J20" s="63" t="str">
-        <x:v>距离控制</x:v>
+        <x:v>发现玩家</x:v>
       </x:c>
       <x:c r="K20" s="63" t="str">
-        <x:v>七类速度差</x:v>
+        <x:v>0.28s响应</x:v>
       </x:c>
       <x:c r="L20" s="63" t="str">
-        <x:v>CharacterBody3D</x:v>
+        <x:v>模块变换</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
@@ -11890,37 +12403,37 @@
         <x:v>顶层</x:v>
       </x:c>
       <x:c r="B21" s="63" t="str">
-        <x:v>telegraph</x:v>
+        <x:v>chase</x:v>
       </x:c>
       <x:c r="C21" s="63" t="str">
-        <x:v>预警</x:v>
+        <x:v>追击</x:v>
       </x:c>
       <x:c r="D21" s="63" t="str">
-        <x:v>chase</x:v>
+        <x:v>alert/attack/stagger</x:v>
       </x:c>
       <x:c r="E21" s="63" t="str">
-        <x:v>attack/stagger/dead</x:v>
+        <x:v>search/telegraph/stagger/dead</x:v>
       </x:c>
       <x:c r="F21" s="63" t="str">
-        <x:v>高频脉冲</x:v>
+        <x:v>稳定</x:v>
       </x:c>
       <x:c r="G21" s="63" t="str">
-        <x:v>稳定</x:v>
+        <x:v>朝目标</x:v>
       </x:c>
       <x:c r="H21" s="63" t="str">
-        <x:v>蓄势</x:v>
+        <x:v>步态</x:v>
       </x:c>
       <x:c r="I21" s="63" t="str">
-        <x:v>红色预警环</x:v>
+        <x:v>关闭</x:v>
       </x:c>
       <x:c r="J21" s="63" t="str">
-        <x:v>攻击前摇</x:v>
+        <x:v>距离控制</x:v>
       </x:c>
       <x:c r="K21" s="63" t="str">
-        <x:v>不可省略</x:v>
+        <x:v>七类速度差</x:v>
       </x:c>
       <x:c r="L21" s="63" t="str">
-        <x:v>计时状态</x:v>
+        <x:v>CharacterBody3D</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="42" customHeight="1">
@@ -11928,37 +12441,37 @@
         <x:v>顶层</x:v>
       </x:c>
       <x:c r="B22" s="63" t="str">
-        <x:v>attack</x:v>
+        <x:v>search</x:v>
       </x:c>
       <x:c r="C22" s="63" t="str">
-        <x:v>攻击</x:v>
+        <x:v>搜索</x:v>
       </x:c>
       <x:c r="D22" s="63" t="str">
-        <x:v>telegraph</x:v>
+        <x:v>chase</x:v>
       </x:c>
       <x:c r="E22" s="63" t="str">
-        <x:v>chase/dead</x:v>
+        <x:v>patrol/alert/stagger/dead</x:v>
       </x:c>
       <x:c r="F22" s="63" t="str">
-        <x:v>峰值</x:v>
+        <x:v>渐缓</x:v>
       </x:c>
       <x:c r="G22" s="63" t="str">
-        <x:v>反冲</x:v>
+        <x:v>朝最后位置</x:v>
       </x:c>
       <x:c r="H22" s="63" t="str">
-        <x:v>执行</x:v>
+        <x:v>搜索步态</x:v>
       </x:c>
       <x:c r="I22" s="63" t="str">
-        <x:v>按攻击类型</x:v>
+        <x:v>搜索提示</x:v>
       </x:c>
       <x:c r="J22" s="63" t="str">
-        <x:v>近战/远程/召唤/爆炸</x:v>
+        <x:v>失去视线后搜索</x:v>
       </x:c>
       <x:c r="K22" s="63" t="str">
-        <x:v>七类差异</x:v>
+        <x:v>2.4s后回巡逻</x:v>
       </x:c>
       <x:c r="L22" s="63" t="str">
-        <x:v>profile策略</x:v>
+        <x:v>射线+最后位置</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
@@ -11966,37 +12479,37 @@
         <x:v>顶层</x:v>
       </x:c>
       <x:c r="B23" s="63" t="str">
-        <x:v>stagger</x:v>
+        <x:v>telegraph</x:v>
       </x:c>
       <x:c r="C23" s="63" t="str">
-        <x:v>硬直</x:v>
+        <x:v>预警</x:v>
       </x:c>
       <x:c r="D23" s="63" t="str">
-        <x:v>任意存活态</x:v>
+        <x:v>chase</x:v>
       </x:c>
       <x:c r="E23" s="63" t="str">
-        <x:v>chase/dead</x:v>
+        <x:v>attack/stagger/dead</x:v>
       </x:c>
       <x:c r="F23" s="63" t="str">
-        <x:v>闪色</x:v>
+        <x:v>高频脉冲</x:v>
       </x:c>
       <x:c r="G23" s="63" t="str">
-        <x:v>冲击</x:v>
+        <x:v>稳定</x:v>
       </x:c>
       <x:c r="H23" s="63" t="str">
-        <x:v>暂停</x:v>
+        <x:v>蓄势</x:v>
       </x:c>
       <x:c r="I23" s="63" t="str">
-        <x:v>伤害反馈</x:v>
+        <x:v>红色预警环</x:v>
       </x:c>
       <x:c r="J23" s="63" t="str">
-        <x:v>受击窗口</x:v>
+        <x:v>攻击前摇</x:v>
       </x:c>
       <x:c r="K23" s="63" t="str">
-        <x:v>方向可读</x:v>
+        <x:v>不可省略</x:v>
       </x:c>
       <x:c r="L23" s="63" t="str">
-        <x:v>统一伤害入口</x:v>
+        <x:v>计时状态</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="42" customHeight="1">
@@ -12004,36 +12517,112 @@
         <x:v>顶层</x:v>
       </x:c>
       <x:c r="B24" s="63" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="C24" s="63" t="str">
+        <x:v>攻击</x:v>
+      </x:c>
+      <x:c r="D24" s="63" t="str">
+        <x:v>telegraph</x:v>
+      </x:c>
+      <x:c r="E24" s="63" t="str">
+        <x:v>chase/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F24" s="63" t="str">
+        <x:v>峰值</x:v>
+      </x:c>
+      <x:c r="G24" s="63" t="str">
+        <x:v>反冲</x:v>
+      </x:c>
+      <x:c r="H24" s="63" t="str">
+        <x:v>执行</x:v>
+      </x:c>
+      <x:c r="I24" s="63" t="str">
+        <x:v>按攻击类型</x:v>
+      </x:c>
+      <x:c r="J24" s="63" t="str">
+        <x:v>近战/远程/召唤/爆炸</x:v>
+      </x:c>
+      <x:c r="K24" s="63" t="str">
+        <x:v>七类差异</x:v>
+      </x:c>
+      <x:c r="L24" s="63" t="str">
+        <x:v>profile策略</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>stagger</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>硬直</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>任意存活态</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>chase/dead</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>闪色</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>冲击</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>暂停</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>伤害反馈</x:v>
+      </x:c>
+      <x:c r="J25" t="str">
+        <x:v>受击窗口</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>方向可读</x:v>
+      </x:c>
+      <x:c r="L25" t="str">
+        <x:v>统一伤害入口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
         <x:v>dead</x:v>
       </x:c>
-      <x:c r="C24" s="63" t="str">
+      <x:c r="C26" t="str">
         <x:v>死亡</x:v>
       </x:c>
-      <x:c r="D24" s="63" t="str">
+      <x:c r="D26" t="str">
         <x:v>任意存活态</x:v>
       </x:c>
-      <x:c r="E24" s="63" t="str">
+      <x:c r="E26" t="str">
         <x:v>无（终态）</x:v>
       </x:c>
-      <x:c r="F24" s="63" t="str">
+      <x:c r="F26" t="str">
         <x:v>熄灭</x:v>
       </x:c>
-      <x:c r="G24" s="63" t="str">
+      <x:c r="G26" t="str">
         <x:v>压扁</x:v>
       </x:c>
-      <x:c r="H24" s="63" t="str">
+      <x:c r="H26" t="str">
         <x:v>停止</x:v>
       </x:c>
-      <x:c r="I24" s="63" t="str">
+      <x:c r="I26" t="str">
         <x:v>爆散/淡出</x:v>
       </x:c>
-      <x:c r="J24" s="63" t="str">
+      <x:c r="J26" t="str">
         <x:v>掉落与计数</x:v>
       </x:c>
-      <x:c r="K24" s="63" t="str">
+      <x:c r="K26" t="str">
         <x:v>不可回存活态</x:v>
       </x:c>
-      <x:c r="L24" s="63" t="str">
+      <x:c r="L26" t="str">
         <x:v>终态 + Tween</x:v>
       </x:c>
     </x:row>
@@ -12041,6 +12630,7 @@
   <x:mergeCells>
     <x:mergeCell ref="A1:L2"/>
     <x:mergeCell ref="A3:L3"/>
+    <x:mergeCell ref="A16:L16"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -12214,7 +12804,7 @@
         <x:v>场景道具</x:v>
       </x:c>
       <x:c r="C11" s="37" t="str">
-        <x:v>facility / container / door / debris</x:v>
+        <x:v>facility / container / door / debris / light / switch</x:v>
       </x:c>
       <x:c r="D11" s="37" t="str">
         <x:v>assets/art/props/</x:v>
@@ -12507,10 +13097,10 @@
         <x:v>验收</x:v>
       </x:c>
       <x:c r="C11" s="37" t="str">
-        <x:v>透明边缘或3D灯光/雾/碰撞/状态/节点预算</x:v>
+        <x:v>透明边缘或3D灯光/雾/碰撞/状态/玩法逻辑/节点预算</x:v>
       </x:c>
       <x:c r="D11" s="37" t="str">
-        <x:v>真实游戏镜头与严格专项通过</x:v>
+        <x:v>真实游戏镜头 + 玩法专项 + 性能专项通过</x:v>
       </x:c>
       <x:c r="E11" s="37" t="str">
         <x:v>只看母版或编辑器预览</x:v>
@@ -12519,7 +13109,7 @@
         <x:v>3D主题关卡</x:v>
       </x:c>
       <x:c r="G11" s="37" t="str">
-        <x:v>seed/灯池/七怪/56组合/撤离 PASS</x:v>
+        <x:v>seed/暗室开关/遮挡视野/七怪/56组合/撤离 PASS</x:v>
       </x:c>
       <x:c r="H11" s="37" t="str">
         <x:v>K/P/X</x:v>
@@ -13151,6 +13741,75 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="63" t="str">
+        <x:v>v1.5</x:v>
+      </x:c>
+      <x:c r="B11" s="64" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="C11" s="63" t="str">
+        <x:v>真实视野与3D输入验收登记</x:v>
+      </x:c>
+      <x:c r="D11" s="63" t="str">
+        <x:v>3D视野 / 背包 / 暂停 / Enemy3D</x:v>
+      </x:c>
+      <x:c r="E11" s="63" t="str">
+        <x:v>登记真实视野场、3D背包子变体和共用暂停UI；低血暗角完成接入；Enemy3D状态表由七态修正为九态</x:v>
+      </x:c>
+      <x:c r="F11" s="63" t="str">
+        <x:v>复用既有视野/背包/VFX根身份；新增暂停根；不改变2D资产ID</x:v>
+      </x:c>
+      <x:c r="G11" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="63" t="str">
+        <x:v>v1.6</x:v>
+      </x:c>
+      <x:c r="B12" s="64" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="C12" s="63" t="str">
+        <x:v>暗室照明与战斗生态登记</x:v>
+      </x:c>
+      <x:c r="D12" s="63" t="str">
+        <x:v>3D视野 / 房灯 / 怪物 / 枪械组合</x:v>
+      </x:c>
+      <x:c r="E12" s="63" t="str">
+        <x:v>登记柔边视野与表现层探照灯、中央顶灯与墙面开关；七类怪碰撞随模型轮廓；枪械/子弹3D适配与开局副枪完成</x:v>
+      </x:c>
+      <x:c r="F12" s="63" t="str">
+        <x:v>新增一个房灯开关根；其余复用既有根ID；玩法逻辑与表现解耦</x:v>
+      </x:c>
+      <x:c r="G12" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="60" customHeight="1">
+      <x:c r="A13" s="70" t="str">
+        <x:v>v1.7</x:v>
+      </x:c>
+      <x:c r="B13" s="71" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="C13" s="70" t="str">
+        <x:v>真实灯光与3D背包投影登记</x:v>
+      </x:c>
+      <x:c r="D13" s="70" t="str">
+        <x:v>玩家探照灯 / 3D背包 / 世界道具模型</x:v>
+      </x:c>
+      <x:c r="E13" s="70" t="str">
+        <x:v>登记独立真实探照灯和共用3D道具投影；视野不再持有灯光；实际槽位点击换枪纳入资产验收</x:v>
+      </x:c>
+      <x:c r="F13" s="70" t="str">
+        <x:v>新增两个可复用子资产；不复制每个道具图标；玩法视野与灯光继续解耦</x:v>
+      </x:c>
+      <x:c r="G13" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G2"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf037c12262a645be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R3e1cd7d8497b4ae3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rdf02083753b14321"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rabe250e950244608"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R039802b8ef1641a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb8d16a866a6d4d67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R9ea68df7be064d6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R8059162294d64002"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf64f1312d80946d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rd986e361c39d4b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rbb4561200bcd4f4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rf0b0c6022c314180"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R1e250af707284e99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rac42cf6b203a4968"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R5dfbe29cb13a4b58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R71dcffa382ea424f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="19">
+  <x:fonts count="20">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -132,8 +132,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF137333"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -178,6 +184,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF10212C"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F3E7"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -230,7 +241,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="72">
+  <x:cellXfs count="74">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -399,6 +410,8 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -768,12 +781,12 @@
       <x:c r="B6" s="43"/>
       <x:c r="C6" s="45" t="n">
         <x:f>COUNTIF('资产主表'!$K$6:$K$200,"已完成")+COUNTIF('资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
         <x:f>COUNTIF('资产主表'!$K$6:$K$200,"待制作")+COUNTIF('资产主表'!$K$6:$K$200,"程序占位")</x:f>
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F6" s="43"/>
       <x:c r="G6" s="45" t="n">
@@ -782,7 +795,7 @@
       </x:c>
       <x:c r="H6" s="43"/>
       <x:c r="I6" s="46" t="str">
-        <x:v>全3D闭环 / 三档房间 / 暗室开关 / 七类怪 / 56枪弹组合</x:v>
+        <x:v>全3D闭环 / PH29 换弹覆盖态 / 真实头顶进度 / 单手枪同相</x:v>
       </x:c>
       <x:c r="J6" s="46"/>
     </x:row>
@@ -918,7 +931,7 @@
       </x:c>
       <x:c r="C13" s="52" t="n">
         <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A13,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A13,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D13" s="43"/>
       <x:c r="E13" s="51" t="str">
@@ -4266,10 +4279,10 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="J49" s="37" t="str">
-        <x:v>世界拾取/UI 图标</x:v>
+        <x:v>全部3D房间/清房奖励</x:v>
       </x:c>
       <x:c r="K49" s="37" t="str">
-        <x:v>程序占位</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L49" s="37" t="str">
         <x:v>P1</x:v>
@@ -4278,11 +4291,11 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="N49" s="37" t="str">
-        <x:v>世界 24–40 px；UI 32 px</x:v>
-      </x:c>
-      <x:c r="O49" s="37" t="str"/>
+        <x:v>程序模型/0.32s Tween</x:v>
+      </x:c>
+      <x:c r="O49" s="37"/>
       <x:c r="P49" s="37" t="str">
-        <x:v>scenes/</x:v>
+        <x:v>src/world3d/RoomKeyPickup3D.gd</x:v>
       </x:c>
       <x:c r="Q49" s="37" t="str"/>
       <x:c r="R49" s="37" t="str">
@@ -4295,15 +4308,17 @@
       </x:c>
       <x:c r="T49" s="37" t="str"/>
       <x:c r="U49" s="37" t="str">
-        <x:v>待分配</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="V49" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W49" s="37" t="str">
-        <x:v>原创/待确认</x:v>
-      </x:c>
-      <x:c r="X49" s="37" t="str"/>
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X49" s="37" t="str">
+        <x:v>清房后在玩家附近安全边界生成；同房唯一且返回时可补发；成功拾取先关闭碰撞，再上弹旋转缩小后回收</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="37" t="str">
@@ -4332,10 +4347,10 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="J50" s="37" t="str">
-        <x:v>世界拾取/UI 图标</x:v>
+        <x:v>地面掉落/背包投影</x:v>
       </x:c>
       <x:c r="K50" s="37" t="str">
-        <x:v>程序占位</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L50" s="37" t="str">
         <x:v>P2</x:v>
@@ -4344,11 +4359,11 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="N50" s="37" t="str">
-        <x:v>世界 24–40 px；UI 32 px</x:v>
-      </x:c>
-      <x:c r="O50" s="37" t="str"/>
+        <x:v>程序模型/0.32s Tween</x:v>
+      </x:c>
+      <x:c r="O50" s="37"/>
       <x:c r="P50" s="37" t="str">
-        <x:v>scenes/</x:v>
+        <x:v>src/world3d/GroundLootPickup3D.gd</x:v>
       </x:c>
       <x:c r="Q50" s="37" t="str"/>
       <x:c r="R50" s="37" t="str">
@@ -4361,15 +4376,17 @@
       </x:c>
       <x:c r="T50" s="37" t="str"/>
       <x:c r="U50" s="37" t="str">
-        <x:v>待分配</x:v>
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="V50" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W50" s="37" t="str">
-        <x:v>原创/待确认</x:v>
-      </x:c>
-      <x:c r="X50" s="37" t="str"/>
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X50" s="37" t="str">
+        <x:v>与背包投影共用 ItemModelFactory3D；满包时保留，成功接收后播放0.32秒上弹旋转缩小动画</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="37" t="str">
@@ -8624,19 +8641,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T113" t="str">
-        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
       </x:c>
       <x:c r="U113" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V113" s="62" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W113" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X113" t="str">
-        <x:v>2D逻辑资产的3D表现变体；无腿、单手、无手臂</x:v>
+        <x:v>2D逻辑资产的3D表现变体；六态白名单正常；moving使用位移驱动独立组件循环；角色网格使用render layer 2；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -8700,19 +8717,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T114" t="str">
-        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
       </x:c>
       <x:c r="U114" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V114" s="62" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W114" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X114" t="str">
-        <x:v>PackedScene内独立Body节点；后续可替换GLB</x:v>
+        <x:v>PackedScene内独立Body节点；moving执行0.10m弹跳与压缩回弹；后续可替换GLB；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -8776,19 +8793,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T115" t="str">
-        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
       </x:c>
       <x:c r="U115" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V115" s="62" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W115" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X115" t="str">
-        <x:v>PackedScene内独立Head节点；无嘴无人脸</x:v>
+        <x:v>PackedScene内独立Head节点；无人脸；移动时采用小幅反相滞后，避免与身体刚性粘连；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -8852,19 +8869,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T116" t="str">
-        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
       </x:c>
       <x:c r="U116" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V116" s="62" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W116" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X116" t="str">
-        <x:v>唯一可见手；随VisualRoot转向并保持身体局部位置</x:v>
+        <x:v>唯一可见手；随VisualRoot转向；与weapon_socket使用完全相同的移动偏移，局部关系不变；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -8928,19 +8945,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T117" t="str">
-        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
       </x:c>
       <x:c r="U117" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V117" s="62" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W117" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X117" t="str">
-        <x:v>独立Scarf节点；保留移动与冲刺滞后动态</x:v>
+        <x:v>独立Scarf节点；moving读取同一周期并使用较慢跟随形成滞后，冲刺保留飘动；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -9004,19 +9021,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T118" t="str">
-        <x:v>3ac48a7d002f3a49cf07c9d425d39c557084f85cbe25ca3ce65c366677f41795</x:v>
+        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
       </x:c>
       <x:c r="U118" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V118" s="62" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W118" t="str">
         <x:v>原创逻辑挂点</x:v>
       </x:c>
       <x:c r="X118" t="str">
-        <x:v>手和挂点保持局部关系；VisualRoot统一跟随准星转向</x:v>
+        <x:v>手和挂点保持固定局部关系；随moving同相偏移；手持枪模型使用render layer 2；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -9774,7 +9791,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X128" s="63" t="str">
-        <x:v>同根支持 street/ceiling；房间只实例化唯一中央顶灯，不生成室内路灯或假光池；默认关闭并由墙面开关控制</x:v>
+        <x:v>同根支持street/ceiling；房间只实例化唯一中央顶灯，默认关闭并由墙面开关控制；PH28开启能量较旧基线提高约22%</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="34" customHeight="1">
@@ -10222,13 +10239,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V134" s="64" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W134" s="63" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X134" s="63" t="str">
-        <x:v>真实GPU窗口检查暗室、家具、角色、怪物和战斗；开灯状态复用同一身份，验收图：assets/art/environments/dungeon_3d/env_dungeon_runtime_light_on_preview_top3d_v001.png</x:v>
+        <x:v>真实GPU窗口检查暗室、家具、角色、怪物和战斗；开灯状态复用同一身份，验收图：assets/art/environments/dungeon_3d/env_dungeon_runtime_light_on_preview_top3d_v001.png；WeaponModel3D为换弹唯一计时源；开始/连续进度/完成或取消信号驱动六态覆盖动画与头顶条；56组合共用</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="34" customHeight="1">
@@ -10302,7 +10319,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X135" s="63" t="str">
-        <x:v>追猎/远程/召唤/盾甲/自爆/伏击/Boss；统一九态：idle/patrol/alert/chase/search/telegraph/attack/stagger/dead</x:v>
+        <x:v>九态AI视线允许射线命中玩家本体并保留实体墙遮挡；3D基础HP乘旧楼层/主题/精英倍率，开局手枪普通命中不秒杀基础怪</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="34" customHeight="1">
@@ -10514,19 +10531,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T138" s="63" t="str">
-        <x:v>b6001154cf08404addb31b69dd38eaba41abe2a82ff6d2408bb5af8fe7a105b0</x:v>
+        <x:v>3b2c2212f1283ed366a31dc3a101b3555c78768c3906600eb0b18c74423fb247</x:v>
       </x:c>
       <x:c r="U138" s="63" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V138" s="64" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="W138" s="63" t="str">
         <x:v>项目运行截图</x:v>
       </x:c>
       <x:c r="X138" s="63" t="str">
-        <x:v>真实GPU窗口检查房间、灯池、家具、角色、怪物和战斗可读性</x:v>
+        <x:v>实际GPU窗口确认360°遮挡逻辑与96°定向表现；PH28三层玩家灯去除头顶溢光，角色正面柔光、增强中央灯与战斗轮廓通过验收</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="34" customHeight="1">
@@ -10646,7 +10663,7 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="N140" t="str">
-        <x:v>ImmediateMesh 49+28射线</x:v>
+        <x:v>360°逻辑射线 + ImmediateMesh 49+28表现射线</x:v>
       </x:c>
       <x:c r="O140" t="str">
         <x:v>src/player3d/PlayerVision3D.gd</x:v>
@@ -10655,7 +10672,7 @@
         <x:v>scenes/Player3D.tscn</x:v>
       </x:c>
       <x:c r="Q140" t="str">
-        <x:v>真实视野;柔边;墙体遮挡;无描边;非灯光判定</x:v>
+        <x:v>360度逻辑视野;96度目光表现;柔边;墙体遮挡;无描边;非灯光判定</x:v>
       </x:c>
       <x:c r="R140" t="str">
         <x:f>LOWER(TRIM(C140)&amp;"|"&amp;TRIM(D140)&amp;"|"&amp;TRIM(E140)&amp;"|"&amp;TRIM(F140)&amp;"|"&amp;TRIM(H140)&amp;"|"&amp;TRIM(I140))</x:f>
@@ -10666,7 +10683,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T140" t="str">
-        <x:v>9cf388d92b26316426fe4aab529001ebd544731ea466470236ad73cdd655e87c</x:v>
+        <x:v>f2b2eaf61798845c9068d45db0fdad2b32930df5b14a259e36bb8be67eefda07</x:v>
       </x:c>
       <x:c r="U140" t="str">
         <x:v>Codex</x:v>
@@ -10678,7 +10695,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X140" t="str">
-        <x:v>逻辑与地面表现复用同批射线；96°/21m + 2.4m；柔边无描边且不受地板深度遮挡；真实照明拆为 VFX-PLAYER-FLASHLIGHT-3D</x:v>
+        <x:v>目标显隐使用21m内360°逐目标物理遮挡；身后无遮挡目标保持可见，任意方向的墙/关闭门/实体家具均可遮挡。地面表现保留96°/21m + 2.4m、49+28固定射线、柔边无描边和地板深度豁免；真实照明仍拆为 VFX-PLAYER-FLASHLIGHT-3D。</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -10948,7 +10965,7 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="N144" t="str">
-        <x:v>PackedScene/SpotLight3D+OmniLight3D</x:v>
+        <x:v>PackedScene/2 SpotLight3D+1 OmniLight3D</x:v>
       </x:c>
       <x:c r="O144" t="str">
         <x:v>assets/art/vfx/visibility_3d/vfx_player_flashlight_root_top3d_v001.tscn</x:v>
@@ -10980,7 +10997,7 @@
         <x:v>原创程序灯光</x:v>
       </x:c>
       <x:c r="X144" t="str">
-        <x:v>独立于玩法视野；1盏投影主聚光 + 1盏无阴影近身补光；颜色/能量/范围/角度/衰减/挂点均可调</x:v>
+        <x:v>独立于玩法视野；环境layer1=投影主聚光+无阴影近身溢光，角色/手持枪layer2=微弱无阴影正面柔光；头顶环境灯不影响角色</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -11084,7 +11101,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2edbae0a0fb542b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc54e4f8a28d64a35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11555,7 +11572,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J14" s="63" t="str">
-        <x:v>六态整体变换</x:v>
+        <x:v>六态整体变换 + reloading覆盖</x:v>
       </x:c>
       <x:c r="K14" s="63" t="str">
         <x:v>3D表现根</x:v>
@@ -11564,7 +11581,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M14" s="63" t="str">
-        <x:v>与2D共用状态ID；摄像机不跟随VisualRoot旋转</x:v>
+        <x:v>与2D共用六态ID；reloading不替换顶层；摄像机和头顶条不跟随VisualRoot旋转</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="34" customHeight="1">
@@ -11596,7 +11613,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="63" t="str">
-        <x:v>呼吸/移动压缩/死亡倾倒</x:v>
+        <x:v>独立移动弹性/呼吸/死亡倾倒</x:v>
       </x:c>
       <x:c r="K15" s="63" t="str">
         <x:v>防护服主体</x:v>
@@ -11605,7 +11622,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M15" s="63" t="str">
-        <x:v>无腿、无脚、无手臂</x:v>
+        <x:v>无腿、无脚、无手臂；render layer 2；移动振幅沿用2D弹性</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -11637,7 +11654,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="63" t="str">
-        <x:v>移动滞后/冲刺飘动</x:v>
+        <x:v>移动周期滞后/冲刺飘动</x:v>
       </x:c>
       <x:c r="K16" s="63" t="str">
         <x:v>身份配件</x:v>
@@ -11646,7 +11663,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="M16" s="63" t="str">
-        <x:v>独立红围巾组件</x:v>
+        <x:v>独立红围巾组件；moving以较慢跟随形成可读滞后</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
@@ -11678,7 +11695,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J17" s="63" t="str">
-        <x:v>呼吸滞后/受击/死亡</x:v>
+        <x:v>移动反相滞后/呼吸/受击/死亡</x:v>
       </x:c>
       <x:c r="K17" s="63" t="str">
         <x:v>头壳/传感器</x:v>
@@ -11687,7 +11704,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M17" s="63" t="str">
-        <x:v>单传感器；无嘴无人脸</x:v>
+        <x:v>单传感器；无嘴无人脸；只受角色正面柔光与房间公共灯</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="34" customHeight="1">
@@ -11713,13 +11730,13 @@
         <x:v>(0.72,1.22,-0.18)</x:v>
       </x:c>
       <x:c r="H18" s="63" t="str">
-        <x:v>随root；局部不旋转</x:v>
+        <x:v>随root；换弹时同相位移/旋转</x:v>
       </x:c>
       <x:c r="I18" s="63" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J18" s="63" t="str">
-        <x:v>随身体转向；保持局部握持位</x:v>
+        <x:v>moving同相；换弹下压/操作/回位；保持握持位</x:v>
       </x:c>
       <x:c r="K18" s="63" t="str">
         <x:v>唯一握持手</x:v>
@@ -11728,7 +11745,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M18" s="63" t="str">
-        <x:v>只有一只手；不单独追踪准星</x:v>
+        <x:v>只有一只手；与weapon_socket在moving/reloading全周期保持固定相对向量</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="34" customHeight="1">
@@ -11754,13 +11771,13 @@
         <x:v>(0.72,1.24,-0.34)</x:v>
       </x:c>
       <x:c r="H19" s="63" t="str">
-        <x:v>随root；局部不旋转</x:v>
+        <x:v>随root；换弹时同相位移/旋转</x:v>
       </x:c>
       <x:c r="I19" s="63" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="J19" s="63" t="str">
-        <x:v>枪械挂载/枪口特效</x:v>
+        <x:v>与唯一手同相；换弹下压/操作/回位；枪械挂载/枪口特效</x:v>
       </x:c>
       <x:c r="K19" s="63" t="str">
         <x:v>武器系统</x:v>
@@ -11769,7 +11786,48 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M19" s="63" t="str">
-        <x:v>挂点与手保持固定局部关系；枪身读取BlueprintRegistry并只做局部后坐力</x:v>
+        <x:v>挂点与手在moving/reloading保持固定局部关系；手持枪网格统一render layer 2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="34" customHeight="1">
+      <x:c r="A20" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B20" s="63" t="str">
+        <x:v>reload_progress</x:v>
+      </x:c>
+      <x:c r="C20" s="63" t="str">
+        <x:v>ReloadProgress3D</x:v>
+      </x:c>
+      <x:c r="D20" s="63" t="str">
+        <x:v>player_root</x:v>
+      </x:c>
+      <x:c r="E20" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F20" s="63" t="str">
+        <x:v>QuadMesh×2</x:v>
+      </x:c>
+      <x:c r="G20" s="63" t="str">
+        <x:v>(0,2.72,0.06)</x:v>
+      </x:c>
+      <x:c r="H20" s="63" t="str">
+        <x:v>朝向相机；不随VisualRoot旋转</x:v>
+      </x:c>
+      <x:c r="I20" s="63" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J20" s="63" t="str">
+        <x:v>读取真实换弹进度；左端固定；完成/取消隐藏</x:v>
+      </x:c>
+      <x:c r="K20" s="63" t="str">
+        <x:v>状态UI子组件</x:v>
+      </x:c>
+      <x:c r="L20" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M20" s="63" t="str">
+        <x:v>无独立计时器/SubViewport；不参与碰撞、视野、灯光或输入；56组合共用</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11836,7 +11894,7 @@
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>2D/3D 共用六态 ID 与转换白名单；Low HP / Silenced / Invincible 为叠加层。3D 首版继续用组件变换，新增动画前先查本表</x:v>
+        <x:v>2D/3D 共用六态 ID 与转换白名单；Low HP / Silenced / Invincible / Reloading 为叠加层。Reloading 读取武器唯一计时，新增动画前先查本表</x:v>
       </x:c>
       <x:c r="B3" s="6"/>
       <x:c r="C3" s="6"/>
@@ -11943,25 +12001,25 @@
         <x:v>idle,dashing,hurt,locked,dead</x:v>
       </x:c>
       <x:c r="F7" s="37" t="str">
-        <x:v>上下弹性</x:v>
+        <x:v>位移驱动弹跳/压缩回弹</x:v>
       </x:c>
       <x:c r="G7" s="37" t="str">
-        <x:v>随身滞后</x:v>
+        <x:v>较小反相滞后</x:v>
       </x:c>
       <x:c r="H7" s="37" t="str">
         <x:v>不显示</x:v>
       </x:c>
       <x:c r="I7" s="37" t="str">
-        <x:v>随身体左右镜像</x:v>
+        <x:v>与挂点同相移动</x:v>
       </x:c>
       <x:c r="J7" s="37" t="str">
-        <x:v>移动滞后</x:v>
+        <x:v>周期滞后</x:v>
       </x:c>
       <x:c r="K7" s="37" t="str">
         <x:v>地面划痕</x:v>
       </x:c>
       <x:c r="L7" s="37" t="str">
-        <x:v>2D/3D组件变换；整体表现根随准星转向</x:v>
+        <x:v>2D/3D组件变换；独立moving循环；整体根随准星；手与挂点局部关系固定</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -12228,6 +12286,44 @@
       </x:c>
       <x:c r="L14" s="37" t="str">
         <x:v>InvincibleTimer 唯一解除</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="34" customHeight="1">
+      <x:c r="A15" s="63" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B15" s="63" t="str">
+        <x:v>reloading</x:v>
+      </x:c>
+      <x:c r="C15" s="63" t="str">
+        <x:v>换弹</x:v>
+      </x:c>
+      <x:c r="D15" s="63" t="str">
+        <x:v>任意持枪存活态</x:v>
+      </x:c>
+      <x:c r="E15" s="63" t="str">
+        <x:v>不改变顶层；完成/取消退出</x:v>
+      </x:c>
+      <x:c r="F15" s="63" t="str">
+        <x:v>保持当前顶层</x:v>
+      </x:c>
+      <x:c r="G15" s="63" t="str">
+        <x:v>保持当前顶层</x:v>
+      </x:c>
+      <x:c r="H15" s="63" t="str">
+        <x:v>不显示</x:v>
+      </x:c>
+      <x:c r="I15" s="63" t="str">
+        <x:v>与weapon_socket同相下压/操作/回位</x:v>
+      </x:c>
+      <x:c r="J15" s="63" t="str">
+        <x:v>保持当前顶层</x:v>
+      </x:c>
+      <x:c r="K15" s="63" t="str">
+        <x:v>3D头顶billboard进度条；2D弹药栏</x:v>
+      </x:c>
+      <x:c r="L15" s="63" t="str">
+        <x:v>WeaponModel3D唯一计时源；0→1；换枪/补弹/清空/死亡取消</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="28" customHeight="1">
@@ -13547,6 +13643,24 @@
       <x:c r="G23" s="61"/>
       <x:c r="H23" s="61"/>
     </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="73" t="str">
+        <x:v>换弹覆盖层：唯一手 + weapon_socket 同相三阶段动作；头顶 billboard 读取真实 0→1 进度；verify_3d_reload_state_flow.tscn PASS</x:v>
+      </x:c>
+      <x:c r="B24" s="73"/>
+      <x:c r="C24" s="73"/>
+      <x:c r="D24" s="73"/>
+      <x:c r="E24" s="73"/>
+      <x:c r="F24" s="73"/>
+      <x:c r="G24" s="73"/>
+      <x:c r="H24" s="73"/>
+      <x:c r="I24" s="73"/>
+      <x:c r="J24" s="73"/>
+      <x:c r="K24" s="73"/>
+      <x:c r="L24" s="73"/>
+      <x:c r="M24" s="73"/>
+      <x:c r="N24" s="73"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:N2"/>
@@ -13554,6 +13668,7 @@
     <x:mergeCell ref="A13:H13"/>
     <x:mergeCell ref="A21:H21"/>
     <x:mergeCell ref="A23:H23"/>
+    <x:mergeCell ref="A24:N24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -13810,6 +13925,75 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="14" ht="54" customHeight="1">
+      <x:c r="A14" s="63" t="str">
+        <x:v>v1.8</x:v>
+      </x:c>
+      <x:c r="B14" s="64" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="C14" s="63" t="str">
+        <x:v>360°逻辑视野契约修正</x:v>
+      </x:c>
+      <x:c r="D14" s="63" t="str">
+        <x:v>VFX-VISIBILITY-FIELD-3D / PlayerVision3D</x:v>
+      </x:c>
+      <x:c r="E14" s="63" t="str">
+        <x:v>目标显隐改为21m内360°物理遮挡；保留96°柔边目光场与探照灯表现。</x:v>
+      </x:c>
+      <x:c r="F14" s="63" t="str">
+        <x:v>AssetID和路径不变；只更新玩法角度契约、诊断字段与验收。</x:v>
+      </x:c>
+      <x:c r="G14" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="72" customHeight="1">
+      <x:c r="A15" s="70" t="str">
+        <x:v>v1.9</x:v>
+      </x:c>
+      <x:c r="B15" s="71" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="C15" s="70" t="str">
+        <x:v>3D战斗生命、AI与反馈闭环</x:v>
+      </x:c>
+      <x:c r="D15" s="70" t="str">
+        <x:v>Enemy3D / 玩家状态动画 / 三层灯组 / 钥匙与掉落</x:v>
+      </x:c>
+      <x:c r="E15" s="70" t="str">
+        <x:v>修复AI视线与3D HP倍率；moving独立动画；环境/角色灯分层；中央灯增强；拾取上弹旋转；钥匙近距生成、查重与补发</x:v>
+      </x:c>
+      <x:c r="F15" s="70" t="str">
+        <x:v>不新增AssetID或复制模型；更新既有根资产行为、哈希、状态职责与验收契约</x:v>
+      </x:c>
+      <x:c r="G15" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="72" customHeight="1">
+      <x:c r="A16" s="63" t="str">
+        <x:v>v1.10</x:v>
+      </x:c>
+      <x:c r="B16" s="64" t="n">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="C16" s="63" t="str">
+        <x:v>3D换弹覆盖状态登记</x:v>
+      </x:c>
+      <x:c r="D16" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D / WPN-GUN-KIT-3D / 玩家状态机</x:v>
+      </x:c>
+      <x:c r="E16" s="63" t="str">
+        <x:v>换弹成为可与移动并存的覆盖态；武器唯一计时驱动单手/枪同相动画和头顶billboard进度条；完成/补弹/换枪/死亡清理</x:v>
+      </x:c>
+      <x:c r="F16" s="63" t="str">
+        <x:v>不新增AssetID；六态白名单与56组合不变；复用既有角色根和枪械套件</x:v>
+      </x:c>
+      <x:c r="G16" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G2"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf64f1312d80946d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rd986e361c39d4b34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rbb4561200bcd4f4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rf0b0c6022c314180"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R1e250af707284e99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rac42cf6b203a4968"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R5dfbe29cb13a4b58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R71dcffa382ea424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8db6a911985d42be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R35b8b0bedd9b4554"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rc39ac0ba6b8d4f2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Re947ec0d70f2431b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R0d468249c12e48b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R07671a5e19124163"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R7cb7398f221e4b8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rb332978a099b43a4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="20">
+  <x:fonts count="23">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -138,8 +138,26 @@
       <x:color rgb="FF137333"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFD8F4FF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FFD8F4FF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FFE2F8FF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="23">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -189,6 +207,66 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE2F3E7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF163044"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234B63"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17384A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF163044"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234B63"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17384A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF163044"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234B63"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF24495D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF163044"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234B63"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF24495D"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -241,7 +319,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="74">
+  <x:cellXfs count="96">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -412,6 +490,44 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -775,13 +891,11 @@
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="45" t="n">
-        <x:f>COUNTA('资产主表'!$A$6:$A$200)</x:f>
-        <x:v>140</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B6" s="43"/>
       <x:c r="C6" s="45" t="n">
-        <x:f>COUNTIF('资产主表'!$K$6:$K$200,"已完成")+COUNTIF('资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>44</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
@@ -795,9 +909,11 @@
       </x:c>
       <x:c r="H6" s="43"/>
       <x:c r="I6" s="46" t="str">
-        <x:v>全3D闭环 / PH29 换弹覆盖态 / 真实头顶进度 / 单手枪同相</x:v>
-      </x:c>
-      <x:c r="J6" s="46"/>
+        <x:v>PH33 方形猫：头/身/单手/脚四模块；双眼双耳；圆短尾</x:v>
+      </x:c>
+      <x:c r="J6" s="46" t="str">
+        <x:v>基地 + 四主题副本 + 独立靶场 + 角色与遭遇预览场</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="43"/>
@@ -848,12 +964,10 @@
         <x:v>角色</x:v>
       </x:c>
       <x:c r="B10" s="50" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A10)</x:f>
-        <x:v>13</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="50" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A10,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A10,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D10" s="43"/>
       <x:c r="E10" s="51" t="str">
@@ -1329,7 +1443,7 @@
         <x:v>角色|player|player_capsule01|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S6" s="36" t="str">
-        <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$145,R6)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$155,R6)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T6" s="36" t="str"/>
@@ -1403,7 +1517,7 @@
         <x:v>角色|player_component|player_capsule01|head|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S7" s="37" t="str">
-        <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$145,R7)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$155,R7)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T7" s="37" t="str">
@@ -1479,7 +1593,7 @@
         <x:v>角色|player_component|player_capsule01|body|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S8" s="37" t="str">
-        <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$145,R8)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$155,R8)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T8" s="37" t="str">
@@ -1555,7 +1669,7 @@
         <x:v>角色|player_component|player_capsule01|hand_l_source|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S9" s="37" t="str">
-        <x:f>IF(A9="","",IF(COUNTIF($R$6:$R$145,R9)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A9="","",IF(COUNTIF($R$6:$R$155,R9)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T9" s="37" t="str">
@@ -1631,7 +1745,7 @@
         <x:v>角色|player_component|player_capsule01|hand|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S10" s="37" t="str">
-        <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$145,R10)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$155,R10)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T10" s="37" t="str">
@@ -1707,7 +1821,7 @@
         <x:v>角色|player_accessory|player_capsule01|scarf|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S11" s="37" t="str">
-        <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$145,R11)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$155,R11)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T11" s="37" t="str">
@@ -1783,7 +1897,7 @@
         <x:v>角色|review_board|player_capsule01|preview|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S12" s="37" t="str">
-        <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$145,R12)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$155,R12)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T12" s="37" t="str"/>
@@ -1851,7 +1965,7 @@
         <x:v>特效|player_state|player_dash|root|侧面朝右（可水平翻转）|dashing</x:v>
       </x:c>
       <x:c r="S13" s="37" t="str">
-        <x:f>IF(A13="","",IF(COUNTIF($R$6:$R$145,R13)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A13="","",IF(COUNTIF($R$6:$R$155,R13)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T13" s="37" t="str"/>
@@ -1919,7 +2033,7 @@
         <x:v>特效|player_state|player_hurt|root|侧面朝右（可水平翻转）|hurt</x:v>
       </x:c>
       <x:c r="S14" s="37" t="str">
-        <x:f>IF(A14="","",IF(COUNTIF($R$6:$R$145,R14)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A14="","",IF(COUNTIF($R$6:$R$155,R14)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T14" s="37" t="str"/>
@@ -1985,7 +2099,7 @@
         <x:v>特效|player_overlay|player_low_hp|root|侧面朝右（可水平翻转）|low_health</x:v>
       </x:c>
       <x:c r="S15" s="37" t="str">
-        <x:f>IF(A15="","",IF(COUNTIF($R$6:$R$145,R15)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A15="","",IF(COUNTIF($R$6:$R$155,R15)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T15" s="37" t="str"/>
@@ -2051,7 +2165,7 @@
         <x:v>特效|player_overlay|player_silenced|root|侧面朝右（可水平翻转）|silenced</x:v>
       </x:c>
       <x:c r="S16" s="37" t="str">
-        <x:f>IF(A16="","",IF(COUNTIF($R$6:$R$145,R16)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A16="","",IF(COUNTIF($R$6:$R$155,R16)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T16" s="37" t="str"/>
@@ -2119,7 +2233,7 @@
         <x:v>敌人|normal_melee|melee_chaser|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S17" s="37" t="str">
-        <x:f>IF(A17="","",IF(COUNTIF($R$6:$R$145,R17)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A17="","",IF(COUNTIF($R$6:$R$155,R17)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T17" s="37" t="str"/>
@@ -2189,7 +2303,7 @@
         <x:v>敌人|normal_ranged|ranged_caster|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S18" s="37" t="str">
-        <x:f>IF(A18="","",IF(COUNTIF($R$6:$R$145,R18)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A18="","",IF(COUNTIF($R$6:$R$155,R18)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T18" s="37" t="str"/>
@@ -2257,7 +2371,7 @@
         <x:v>敌人|normal_summoner|summoner|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S19" s="37" t="str">
-        <x:f>IF(A19="","",IF(COUNTIF($R$6:$R$145,R19)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A19="","",IF(COUNTIF($R$6:$R$155,R19)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T19" s="37" t="str"/>
@@ -2325,7 +2439,7 @@
         <x:v>敌人|normal_tank|shielded|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S20" s="37" t="str">
-        <x:f>IF(A20="","",IF(COUNTIF($R$6:$R$145,R20)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A20="","",IF(COUNTIF($R$6:$R$155,R20)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T20" s="37" t="str"/>
@@ -2393,7 +2507,7 @@
         <x:v>敌人|normal_bomber|exploder|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S21" s="37" t="str">
-        <x:f>IF(A21="","",IF(COUNTIF($R$6:$R$145,R21)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A21="","",IF(COUNTIF($R$6:$R$155,R21)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T21" s="37" t="str"/>
@@ -2461,7 +2575,7 @@
         <x:v>敌人|normal_ambusher|ambusher|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S22" s="37" t="str">
-        <x:f>IF(A22="","",IF(COUNTIF($R$6:$R$145,R22)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A22="","",IF(COUNTIF($R$6:$R$155,R22)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T22" s="37" t="str"/>
@@ -2529,7 +2643,7 @@
         <x:v>敌人|boss|boss|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S23" s="37" t="str">
-        <x:f>IF(A23="","",IF(COUNTIF($R$6:$R$145,R23)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A23="","",IF(COUNTIF($R$6:$R$155,R23)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T23" s="37" t="str"/>
@@ -2599,7 +2713,7 @@
         <x:v>枪械|gunbody|bp_pistol|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S24" s="37" t="str">
-        <x:f>IF(A24="","",IF(COUNTIF($R$6:$R$145,R24)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A24="","",IF(COUNTIF($R$6:$R$155,R24)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T24" s="37" t="str"/>
@@ -2669,7 +2783,7 @@
         <x:v>枪械|gunbody|bp_shotgun|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S25" s="37" t="str">
-        <x:f>IF(A25="","",IF(COUNTIF($R$6:$R$145,R25)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A25="","",IF(COUNTIF($R$6:$R$155,R25)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T25" s="37" t="str"/>
@@ -2739,7 +2853,7 @@
         <x:v>枪械|gunbody|bp_rifle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S26" s="37" t="str">
-        <x:f>IF(A26="","",IF(COUNTIF($R$6:$R$145,R26)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A26="","",IF(COUNTIF($R$6:$R$155,R26)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T26" s="37" t="str"/>
@@ -2809,7 +2923,7 @@
         <x:v>枪械|gunbody|bp_machinegun|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S27" s="37" t="str">
-        <x:f>IF(A27="","",IF(COUNTIF($R$6:$R$145,R27)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A27="","",IF(COUNTIF($R$6:$R$155,R27)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T27" s="37" t="str"/>
@@ -2879,7 +2993,7 @@
         <x:v>枪械|gunbody|bp_sniper|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S28" s="37" t="str">
-        <x:f>IF(A28="","",IF(COUNTIF($R$6:$R$145,R28)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A28="","",IF(COUNTIF($R$6:$R$155,R28)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T28" s="37" t="str"/>
@@ -2949,7 +3063,7 @@
         <x:v>枪械|gunbody|bp_launcher|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S29" s="37" t="str">
-        <x:f>IF(A29="","",IF(COUNTIF($R$6:$R$145,R29)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A29="","",IF(COUNTIF($R$6:$R$155,R29)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T29" s="37" t="str"/>
@@ -3019,7 +3133,7 @@
         <x:v>枪械|gunbody|bp_charge|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S30" s="37" t="str">
-        <x:f>IF(A30="","",IF(COUNTIF($R$6:$R$145,R30)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A30="","",IF(COUNTIF($R$6:$R$155,R30)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T30" s="37" t="str"/>
@@ -3087,7 +3201,7 @@
         <x:v>枪械|bullet_module|mod_bullet_standard|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S31" s="37" t="str">
-        <x:f>IF(A31="","",IF(COUNTIF($R$6:$R$145,R31)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A31="","",IF(COUNTIF($R$6:$R$155,R31)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T31" s="37" t="str"/>
@@ -3155,7 +3269,7 @@
         <x:v>枪械|bullet_module|mod_bullet_sticky|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S32" s="37" t="str">
-        <x:f>IF(A32="","",IF(COUNTIF($R$6:$R$145,R32)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A32="","",IF(COUNTIF($R$6:$R$155,R32)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T32" s="37" t="str"/>
@@ -3223,7 +3337,7 @@
         <x:v>枪械|bullet_module|mod_bullet_bounce|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S33" s="37" t="str">
-        <x:f>IF(A33="","",IF(COUNTIF($R$6:$R$145,R33)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A33="","",IF(COUNTIF($R$6:$R$155,R33)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T33" s="37" t="str"/>
@@ -3291,7 +3405,7 @@
         <x:v>枪械|bullet_module|mod_bullet_piercing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S34" s="37" t="str">
-        <x:f>IF(A34="","",IF(COUNTIF($R$6:$R$145,R34)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A34="","",IF(COUNTIF($R$6:$R$155,R34)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T34" s="37" t="str"/>
@@ -3359,7 +3473,7 @@
         <x:v>枪械|bullet_module|mod_bullet_explosive|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S35" s="37" t="str">
-        <x:f>IF(A35="","",IF(COUNTIF($R$6:$R$145,R35)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A35="","",IF(COUNTIF($R$6:$R$155,R35)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T35" s="37" t="str"/>
@@ -3427,7 +3541,7 @@
         <x:v>枪械|bullet_module|mod_bullet_homing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S36" s="37" t="str">
-        <x:f>IF(A36="","",IF(COUNTIF($R$6:$R$145,R36)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A36="","",IF(COUNTIF($R$6:$R$155,R36)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T36" s="37" t="str"/>
@@ -3495,7 +3609,7 @@
         <x:v>枪械|bullet_module|mod_bullet_blackhole|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S37" s="37" t="str">
-        <x:f>IF(A37="","",IF(COUNTIF($R$6:$R$145,R37)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A37="","",IF(COUNTIF($R$6:$R$155,R37)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T37" s="37" t="str"/>
@@ -3563,7 +3677,7 @@
         <x:v>枪械|bullet_module|mod_bullet_balloon|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S38" s="37" t="str">
-        <x:f>IF(A38="","",IF(COUNTIF($R$6:$R$145,R38)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A38="","",IF(COUNTIF($R$6:$R$155,R38)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T38" s="37" t="str"/>
@@ -3631,7 +3745,7 @@
         <x:v>枪械|attachment|attach_triple_muzzle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S39" s="37" t="str">
-        <x:f>IF(A39="","",IF(COUNTIF($R$6:$R$145,R39)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A39="","",IF(COUNTIF($R$6:$R$155,R39)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T39" s="37" t="str"/>
@@ -3699,7 +3813,7 @@
         <x:v>枪械|attachment|attach_rubber_stock|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S40" s="37" t="str">
-        <x:f>IF(A40="","",IF(COUNTIF($R$6:$R$145,R40)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A40="","",IF(COUNTIF($R$6:$R$155,R40)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T40" s="37" t="str"/>
@@ -3767,7 +3881,7 @@
         <x:v>枪械|attachment|attach_scope|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S41" s="37" t="str">
-        <x:f>IF(A41="","",IF(COUNTIF($R$6:$R$145,R41)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A41="","",IF(COUNTIF($R$6:$R$155,R41)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T41" s="37" t="str"/>
@@ -3835,7 +3949,7 @@
         <x:v>枪械|attachment|attach_big_mag|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S42" s="37" t="str">
-        <x:f>IF(A42="","",IF(COUNTIF($R$6:$R$145,R42)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A42="","",IF(COUNTIF($R$6:$R$155,R42)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T42" s="37" t="str"/>
@@ -3903,7 +4017,7 @@
         <x:v>枪械|attachment|attach_fan|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S43" s="37" t="str">
-        <x:f>IF(A43="","",IF(COUNTIF($R$6:$R$145,R43)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A43="","",IF(COUNTIF($R$6:$R$155,R43)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T43" s="37" t="str"/>
@@ -3971,7 +4085,7 @@
         <x:v>枪械|attachment|attach_copy_sticker|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S44" s="37" t="str">
-        <x:f>IF(A44="","",IF(COUNTIF($R$6:$R$145,R44)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A44="","",IF(COUNTIF($R$6:$R$155,R44)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T44" s="37" t="str"/>
@@ -4039,7 +4153,7 @@
         <x:v>道具|consumable|item_beacon|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S45" s="37" t="str">
-        <x:f>IF(A45="","",IF(COUNTIF($R$6:$R$145,R45)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A45="","",IF(COUNTIF($R$6:$R$155,R45)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T45" s="37" t="str"/>
@@ -4105,7 +4219,7 @@
         <x:v>道具|key|item_room_key|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S46" s="37" t="str">
-        <x:f>IF(A46="","",IF(COUNTIF($R$6:$R$145,R46)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A46="","",IF(COUNTIF($R$6:$R$155,R46)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T46" s="37" t="str"/>
@@ -4171,7 +4285,7 @@
         <x:v>道具|pickup|soul_orb|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S47" s="37" t="str">
-        <x:f>IF(A47="","",IF(COUNTIF($R$6:$R$145,R47)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A47="","",IF(COUNTIF($R$6:$R$155,R47)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T47" s="37" t="str"/>
@@ -4237,7 +4351,7 @@
         <x:v>道具|container|container|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S48" s="37" t="str">
-        <x:f>IF(A48="","",IF(COUNTIF($R$6:$R$145,R48)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A48="","",IF(COUNTIF($R$6:$R$155,R48)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T48" s="37" t="str"/>
@@ -4303,7 +4417,7 @@
         <x:v>道具|pickup|room_key_pickup|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S49" s="37" t="str">
-        <x:f>IF(A49="","",IF(COUNTIF($R$6:$R$145,R49)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A49="","",IF(COUNTIF($R$6:$R$155,R49)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T49" s="37" t="str"/>
@@ -4371,7 +4485,7 @@
         <x:v>道具|pickup_base|ground_item|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S50" s="37" t="str">
-        <x:f>IF(A50="","",IF(COUNTIF($R$6:$R$145,R50)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A50="","",IF(COUNTIF($R$6:$R$155,R50)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T50" s="37" t="str"/>
@@ -4439,7 +4553,7 @@
         <x:v>场景|biome_kit|base_world|root|顶视|default</x:v>
       </x:c>
       <x:c r="S51" s="37" t="str">
-        <x:f>IF(A51="","",IF(COUNTIF($R$6:$R$145,R51)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A51="","",IF(COUNTIF($R$6:$R$155,R51)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T51" s="37" t="str"/>
@@ -4507,7 +4621,7 @@
         <x:v>场景|biome_kit|iron_frontier|root|顶视|default</x:v>
       </x:c>
       <x:c r="S52" s="37" t="str">
-        <x:f>IF(A52="","",IF(COUNTIF($R$6:$R$145,R52)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A52="","",IF(COUNTIF($R$6:$R$155,R52)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T52" s="37" t="str"/>
@@ -4575,7 +4689,7 @@
         <x:v>场景|biome_kit|rust_foundry|root|顶视|default</x:v>
       </x:c>
       <x:c r="S53" s="37" t="str">
-        <x:f>IF(A53="","",IF(COUNTIF($R$6:$R$145,R53)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A53="","",IF(COUNTIF($R$6:$R$155,R53)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T53" s="37" t="str"/>
@@ -4643,7 +4757,7 @@
         <x:v>场景|biome_kit|spore_depths|root|顶视|default</x:v>
       </x:c>
       <x:c r="S54" s="37" t="str">
-        <x:f>IF(A54="","",IF(COUNTIF($R$6:$R$145,R54)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A54="","",IF(COUNTIF($R$6:$R$155,R54)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T54" s="37" t="str"/>
@@ -4711,7 +4825,7 @@
         <x:v>场景|biome_kit|abyss_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S55" s="37" t="str">
-        <x:f>IF(A55="","",IF(COUNTIF($R$6:$R$145,R55)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A55="","",IF(COUNTIF($R$6:$R$155,R55)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T55" s="37" t="str"/>
@@ -4779,7 +4893,7 @@
         <x:v>场景|biome_kit|training_range|root|顶视|default</x:v>
       </x:c>
       <x:c r="S56" s="37" t="str">
-        <x:f>IF(A56="","",IF(COUNTIF($R$6:$R$145,R56)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A56="","",IF(COUNTIF($R$6:$R$155,R56)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T56" s="37" t="str"/>
@@ -4847,7 +4961,7 @@
         <x:v>场景|room_dressing|room_combat|root|顶视|default</x:v>
       </x:c>
       <x:c r="S57" s="37" t="str">
-        <x:f>IF(A57="","",IF(COUNTIF($R$6:$R$145,R57)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A57="","",IF(COUNTIF($R$6:$R$155,R57)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T57" s="37" t="str"/>
@@ -4915,7 +5029,7 @@
         <x:v>场景|room_dressing|room_elite|root|顶视|default</x:v>
       </x:c>
       <x:c r="S58" s="37" t="str">
-        <x:f>IF(A58="","",IF(COUNTIF($R$6:$R$145,R58)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A58="","",IF(COUNTIF($R$6:$R$155,R58)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T58" s="37" t="str"/>
@@ -4983,7 +5097,7 @@
         <x:v>场景|room_dressing|room_boss|root|顶视|default</x:v>
       </x:c>
       <x:c r="S59" s="37" t="str">
-        <x:f>IF(A59="","",IF(COUNTIF($R$6:$R$145,R59)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A59="","",IF(COUNTIF($R$6:$R$155,R59)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T59" s="37" t="str"/>
@@ -5051,7 +5165,7 @@
         <x:v>场景|room_dressing|room_event|root|顶视|default</x:v>
       </x:c>
       <x:c r="S60" s="37" t="str">
-        <x:f>IF(A60="","",IF(COUNTIF($R$6:$R$145,R60)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A60="","",IF(COUNTIF($R$6:$R$155,R60)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T60" s="37" t="str"/>
@@ -5119,7 +5233,7 @@
         <x:v>场景|room_dressing|room_extraction|root|顶视|default</x:v>
       </x:c>
       <x:c r="S61" s="37" t="str">
-        <x:f>IF(A61="","",IF(COUNTIF($R$6:$R$145,R61)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A61="","",IF(COUNTIF($R$6:$R$155,R61)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T61" s="37" t="str"/>
@@ -5187,7 +5301,7 @@
         <x:v>场景|room_dressing|room_merchant|root|顶视|default</x:v>
       </x:c>
       <x:c r="S62" s="37" t="str">
-        <x:f>IF(A62="","",IF(COUNTIF($R$6:$R$145,R62)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A62="","",IF(COUNTIF($R$6:$R$155,R62)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T62" s="37" t="str"/>
@@ -5255,7 +5369,7 @@
         <x:v>场景|room_dressing|room_scavenge|root|顶视|default</x:v>
       </x:c>
       <x:c r="S63" s="37" t="str">
-        <x:f>IF(A63="","",IF(COUNTIF($R$6:$R$145,R63)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A63="","",IF(COUNTIF($R$6:$R$155,R63)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T63" s="37" t="str"/>
@@ -5323,7 +5437,7 @@
         <x:v>场景|room_dressing|room_storage|root|顶视|default</x:v>
       </x:c>
       <x:c r="S64" s="37" t="str">
-        <x:f>IF(A64="","",IF(COUNTIF($R$6:$R$145,R64)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A64="","",IF(COUNTIF($R$6:$R$155,R64)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T64" s="37" t="str"/>
@@ -5391,7 +5505,7 @@
         <x:v>场景|room_dressing|room_trap|root|顶视|default</x:v>
       </x:c>
       <x:c r="S65" s="37" t="str">
-        <x:f>IF(A65="","",IF(COUNTIF($R$6:$R$145,R65)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A65="","",IF(COUNTIF($R$6:$R$155,R65)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T65" s="37" t="str"/>
@@ -5459,7 +5573,7 @@
         <x:v>场景|room_dressing|room_upgrade|root|顶视|default</x:v>
       </x:c>
       <x:c r="S66" s="37" t="str">
-        <x:f>IF(A66="","",IF(COUNTIF($R$6:$R$145,R66)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A66="","",IF(COUNTIF($R$6:$R$155,R66)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T66" s="37" t="str"/>
@@ -5527,7 +5641,7 @@
         <x:v>场景|room_dressing|room_spawn|root|顶视|default</x:v>
       </x:c>
       <x:c r="S67" s="37" t="str">
-        <x:f>IF(A67="","",IF(COUNTIF($R$6:$R$145,R67)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A67="","",IF(COUNTIF($R$6:$R$155,R67)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T67" s="37" t="str"/>
@@ -5595,7 +5709,7 @@
         <x:v>场景|room_dressing|room_stairs|root|顶视|default</x:v>
       </x:c>
       <x:c r="S68" s="37" t="str">
-        <x:f>IF(A68="","",IF(COUNTIF($R$6:$R$145,R68)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A68="","",IF(COUNTIF($R$6:$R$155,R68)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T68" s="37" t="str"/>
@@ -5663,7 +5777,7 @@
         <x:v>场景道具|facility|base_briefing|root|顶视|default</x:v>
       </x:c>
       <x:c r="S69" s="37" t="str">
-        <x:f>IF(A69="","",IF(COUNTIF($R$6:$R$145,R69)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A69="","",IF(COUNTIF($R$6:$R$155,R69)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T69" s="37" t="str"/>
@@ -5731,7 +5845,7 @@
         <x:v>场景道具|facility|base_workshop|root|顶视|default</x:v>
       </x:c>
       <x:c r="S70" s="37" t="str">
-        <x:f>IF(A70="","",IF(COUNTIF($R$6:$R$145,R70)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A70="","",IF(COUNTIF($R$6:$R$155,R70)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T70" s="37" t="str"/>
@@ -5799,7 +5913,7 @@
         <x:v>场景道具|facility|base_divination|root|顶视|default</x:v>
       </x:c>
       <x:c r="S71" s="37" t="str">
-        <x:f>IF(A71="","",IF(COUNTIF($R$6:$R$145,R71)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A71="","",IF(COUNTIF($R$6:$R$155,R71)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T71" s="37" t="str"/>
@@ -5867,7 +5981,7 @@
         <x:v>场景道具|facility|base_vault|root|顶视|default</x:v>
       </x:c>
       <x:c r="S72" s="37" t="str">
-        <x:f>IF(A72="","",IF(COUNTIF($R$6:$R$145,R72)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A72="","",IF(COUNTIF($R$6:$R$155,R72)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T72" s="37" t="str"/>
@@ -5935,7 +6049,7 @@
         <x:v>场景道具|facility|base_monster_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S73" s="37" t="str">
-        <x:f>IF(A73="","",IF(COUNTIF($R$6:$R$145,R73)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A73="","",IF(COUNTIF($R$6:$R$155,R73)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T73" s="37" t="str"/>
@@ -6003,7 +6117,7 @@
         <x:v>场景道具|facility|base_card_collection|root|顶视|default</x:v>
       </x:c>
       <x:c r="S74" s="37" t="str">
-        <x:f>IF(A74="","",IF(COUNTIF($R$6:$R$145,R74)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A74="","",IF(COUNTIF($R$6:$R$155,R74)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T74" s="37" t="str"/>
@@ -6071,7 +6185,7 @@
         <x:v>场景道具|facility|base_terminal|root|顶视|default</x:v>
       </x:c>
       <x:c r="S75" s="37" t="str">
-        <x:f>IF(A75="","",IF(COUNTIF($R$6:$R$145,R75)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A75="","",IF(COUNTIF($R$6:$R$155,R75)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T75" s="37" t="str"/>
@@ -6139,7 +6253,7 @@
         <x:v>场景道具|facility|dungeon_gate|root|顶视|default</x:v>
       </x:c>
       <x:c r="S76" s="37" t="str">
-        <x:f>IF(A76="","",IF(COUNTIF($R$6:$R$145,R76)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A76="","",IF(COUNTIF($R$6:$R$155,R76)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T76" s="37" t="str"/>
@@ -6207,7 +6321,7 @@
         <x:v>场景道具|facility|workbench|root|顶视|default</x:v>
       </x:c>
       <x:c r="S77" s="37" t="str">
-        <x:f>IF(A77="","",IF(COUNTIF($R$6:$R$145,R77)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A77="","",IF(COUNTIF($R$6:$R$155,R77)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T77" s="37" t="str"/>
@@ -6275,7 +6389,7 @@
         <x:v>场景道具|facility|door|root|顶视|default</x:v>
       </x:c>
       <x:c r="S78" s="37" t="str">
-        <x:f>IF(A78="","",IF(COUNTIF($R$6:$R$145,R78)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A78="","",IF(COUNTIF($R$6:$R$155,R78)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T78" s="37" t="str"/>
@@ -6343,7 +6457,7 @@
         <x:v>ui|screen|hud|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S79" s="37" t="str">
-        <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$145,R79)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$155,R79)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T79" s="37" t="str"/>
@@ -6411,7 +6525,7 @@
         <x:v>ui|screen|inventory|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S80" s="37" t="str">
-        <x:f>IF(A80="","",IF(COUNTIF($R$6:$R$145,R80)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A80="","",IF(COUNTIF($R$6:$R$155,R80)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T80" s="37" t="str"/>
@@ -6479,7 +6593,7 @@
         <x:v>ui|screen|merchant|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S81" s="37" t="str">
-        <x:f>IF(A81="","",IF(COUNTIF($R$6:$R$145,R81)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A81="","",IF(COUNTIF($R$6:$R$155,R81)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T81" s="37" t="str"/>
@@ -6547,7 +6661,7 @@
         <x:v>ui|screen|workshop|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S82" s="37" t="str">
-        <x:f>IF(A82="","",IF(COUNTIF($R$6:$R$145,R82)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A82="","",IF(COUNTIF($R$6:$R$155,R82)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T82" s="37" t="str"/>
@@ -6615,7 +6729,7 @@
         <x:v>ui|screen|workbench|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S83" s="37" t="str">
-        <x:f>IF(A83="","",IF(COUNTIF($R$6:$R$145,R83)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A83="","",IF(COUNTIF($R$6:$R$155,R83)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T83" s="37" t="str"/>
@@ -6683,7 +6797,7 @@
         <x:v>ui|screen|weapon_tree|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S84" s="37" t="str">
-        <x:f>IF(A84="","",IF(COUNTIF($R$6:$R$145,R84)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A84="","",IF(COUNTIF($R$6:$R$155,R84)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T84" s="37" t="str"/>
@@ -6751,7 +6865,7 @@
         <x:v>ui|screen|fate_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S85" s="37" t="str">
-        <x:f>IF(A85="","",IF(COUNTIF($R$6:$R$145,R85)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A85="","",IF(COUNTIF($R$6:$R$155,R85)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T85" s="37" t="str"/>
@@ -6819,7 +6933,7 @@
         <x:v>ui|screen|fate_collection|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S86" s="37" t="str">
-        <x:f>IF(A86="","",IF(COUNTIF($R$6:$R$145,R86)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A86="","",IF(COUNTIF($R$6:$R$155,R86)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T86" s="37" t="str"/>
@@ -6887,7 +7001,7 @@
         <x:v>ui|screen|level_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S87" s="37" t="str">
-        <x:f>IF(A87="","",IF(COUNTIF($R$6:$R$145,R87)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A87="","",IF(COUNTIF($R$6:$R$155,R87)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T87" s="37" t="str"/>
@@ -6955,7 +7069,7 @@
         <x:v>ui|screen|vault|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S88" s="37" t="str">
-        <x:f>IF(A88="","",IF(COUNTIF($R$6:$R$145,R88)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A88="","",IF(COUNTIF($R$6:$R$155,R88)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T88" s="37" t="str"/>
@@ -7023,7 +7137,7 @@
         <x:v>ui|screen|monster_archive|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S89" s="37" t="str">
-        <x:f>IF(A89="","",IF(COUNTIF($R$6:$R$145,R89)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A89="","",IF(COUNTIF($R$6:$R$155,R89)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T89" s="37" t="str"/>
@@ -7091,7 +7205,7 @@
         <x:v>ui|screen|base_menu|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S90" s="37" t="str">
-        <x:f>IF(A90="","",IF(COUNTIF($R$6:$R$145,R90)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A90="","",IF(COUNTIF($R$6:$R$155,R90)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T90" s="37" t="str"/>
@@ -7159,7 +7273,7 @@
         <x:v>ui|screen|mobile_controls|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S91" s="37" t="str">
-        <x:f>IF(A91="","",IF(COUNTIF($R$6:$R$145,R91)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A91="","",IF(COUNTIF($R$6:$R$155,R91)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T91" s="37" t="str"/>
@@ -7227,7 +7341,7 @@
         <x:v>特效|gameplay_vfx|explosion|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S92" s="37" t="str">
-        <x:f>IF(A92="","",IF(COUNTIF($R$6:$R$145,R92)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A92="","",IF(COUNTIF($R$6:$R$155,R92)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T92" s="37" t="str"/>
@@ -7295,7 +7409,7 @@
         <x:v>特效|gameplay_vfx|muzzle_flash|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S93" s="37" t="str">
-        <x:f>IF(A93="","",IF(COUNTIF($R$6:$R$145,R93)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A93="","",IF(COUNTIF($R$6:$R$155,R93)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T93" s="37" t="str"/>
@@ -7363,7 +7477,7 @@
         <x:v>特效|gameplay_vfx|damage_number|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S94" s="37" t="str">
-        <x:f>IF(A94="","",IF(COUNTIF($R$6:$R$145,R94)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A94="","",IF(COUNTIF($R$6:$R$155,R94)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T94" s="37" t="str"/>
@@ -7431,7 +7545,7 @@
         <x:v>特效|gameplay_vfx|spark|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S95" s="37" t="str">
-        <x:f>IF(A95="","",IF(COUNTIF($R$6:$R$145,R95)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A95="","",IF(COUNTIF($R$6:$R$155,R95)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T95" s="37" t="str"/>
@@ -7499,7 +7613,7 @@
         <x:v>特效|gameplay_vfx|room_transition|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S96" s="37" t="str">
-        <x:f>IF(A96="","",IF(COUNTIF($R$6:$R$145,R96)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A96="","",IF(COUNTIF($R$6:$R$155,R96)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T96" s="37" t="str"/>
@@ -7569,7 +7683,7 @@
         <x:v>特效|gameplay_vfx|health_vignette|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S97" s="37" t="str">
-        <x:f>IF(A97="","",IF(COUNTIF($R$6:$R$145,R97)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A97="","",IF(COUNTIF($R$6:$R$155,R97)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T97" s="37" t="str"/>
@@ -7637,7 +7751,7 @@
         <x:v>特效|gameplay_vfx|visibility_light|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S98" s="37" t="str">
-        <x:f>IF(A98="","",IF(COUNTIF($R$6:$R$145,R98)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A98="","",IF(COUNTIF($R$6:$R$155,R98)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T98" s="37" t="str"/>
@@ -7705,7 +7819,7 @@
         <x:v>特效|gameplay_vfx|extraction_beacon|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S99" s="37" t="str">
-        <x:f>IF(A99="","",IF(COUNTIF($R$6:$R$145,R99)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A99="","",IF(COUNTIF($R$6:$R$155,R99)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T99" s="37" t="str"/>
@@ -7773,7 +7887,7 @@
         <x:v>音频|bgm|bgm_wasteland|root|不适用|default</x:v>
       </x:c>
       <x:c r="S100" s="37" t="str">
-        <x:f>IF(A100="","",IF(COUNTIF($R$6:$R$145,R100)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A100="","",IF(COUNTIF($R$6:$R$155,R100)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T100" s="37" t="str"/>
@@ -7839,7 +7953,7 @@
         <x:v>音频|sfx|pistol_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S101" s="37" t="str">
-        <x:f>IF(A101="","",IF(COUNTIF($R$6:$R$145,R101)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A101="","",IF(COUNTIF($R$6:$R$155,R101)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T101" s="37" t="str"/>
@@ -7905,7 +8019,7 @@
         <x:v>音频|sfx|rifle_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S102" s="37" t="str">
-        <x:f>IF(A102="","",IF(COUNTIF($R$6:$R$145,R102)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A102="","",IF(COUNTIF($R$6:$R$155,R102)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T102" s="37" t="str"/>
@@ -7971,7 +8085,7 @@
         <x:v>音频|sfx|shotgun_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S103" s="37" t="str">
-        <x:f>IF(A103="","",IF(COUNTIF($R$6:$R$145,R103)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A103="","",IF(COUNTIF($R$6:$R$155,R103)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T103" s="37" t="str"/>
@@ -8037,7 +8151,7 @@
         <x:v>音频|sfx|smg_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S104" s="37" t="str">
-        <x:f>IF(A104="","",IF(COUNTIF($R$6:$R$145,R104)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A104="","",IF(COUNTIF($R$6:$R$155,R104)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T104" s="37" t="str"/>
@@ -8103,7 +8217,7 @@
         <x:v>音频|sfx|sniper_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S105" s="37" t="str">
-        <x:f>IF(A105="","",IF(COUNTIF($R$6:$R$145,R105)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A105="","",IF(COUNTIF($R$6:$R$155,R105)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T105" s="37" t="str"/>
@@ -8169,7 +8283,7 @@
         <x:v>音频|sfx|player_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S106" s="37" t="str">
-        <x:f>IF(A106="","",IF(COUNTIF($R$6:$R$145,R106)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A106="","",IF(COUNTIF($R$6:$R$155,R106)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T106" s="37" t="str"/>
@@ -8235,7 +8349,7 @@
         <x:v>音频|sfx|player_dash|root|不适用|default</x:v>
       </x:c>
       <x:c r="S107" s="37" t="str">
-        <x:f>IF(A107="","",IF(COUNTIF($R$6:$R$145,R107)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A107="","",IF(COUNTIF($R$6:$R$155,R107)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T107" s="37" t="str"/>
@@ -8301,7 +8415,7 @@
         <x:v>音频|sfx|enemy_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S108" s="37" t="str">
-        <x:f>IF(A108="","",IF(COUNTIF($R$6:$R$145,R108)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A108="","",IF(COUNTIF($R$6:$R$155,R108)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T108" s="37" t="str"/>
@@ -8367,7 +8481,7 @@
         <x:v>音频|sfx|enemy_die|root|不适用|default</x:v>
       </x:c>
       <x:c r="S109" s="37" t="str">
-        <x:f>IF(A109="","",IF(COUNTIF($R$6:$R$145,R109)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A109="","",IF(COUNTIF($R$6:$R$155,R109)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T109" s="37" t="str"/>
@@ -8433,7 +8547,7 @@
         <x:v>音频|sfx|reload|root|不适用|default</x:v>
       </x:c>
       <x:c r="S110" s="37" t="str">
-        <x:f>IF(A110="","",IF(COUNTIF($R$6:$R$145,R110)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A110="","",IF(COUNTIF($R$6:$R$155,R110)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T110" s="37" t="str"/>
@@ -8499,7 +8613,7 @@
         <x:v>音频|sfx|extraction_start|root|不适用|default</x:v>
       </x:c>
       <x:c r="S111" s="37" t="str">
-        <x:f>IF(A111="","",IF(COUNTIF($R$6:$R$145,R111)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A111="","",IF(COUNTIF($R$6:$R$155,R111)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T111" s="37" t="str"/>
@@ -8565,7 +8679,7 @@
         <x:v>音频|sfx|extraction_done|root|不适用|default</x:v>
       </x:c>
       <x:c r="S112" s="37" t="str">
-        <x:f>IF(A112="","",IF(COUNTIF($R$6:$R$145,R112)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A112="","",IF(COUNTIF($R$6:$R$155,R112)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T112" s="37" t="str"/>
@@ -8585,7 +8699,7 @@
         <x:v>CHR-PLY-CAPSULE01-3D</x:v>
       </x:c>
       <x:c r="B113" t="str">
-        <x:v>胶囊防护体3D根组件</x:v>
+        <x:v>方形猫角色3D根组件</x:v>
       </x:c>
       <x:c r="C113" t="str">
         <x:v>角色</x:v>
@@ -8637,23 +8751,23 @@
         <x:v>角色|player|player_capsule01|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S113" t="str">
-        <x:f>IF(A113="","",IF(COUNTIF($R$6:$R$145,R113)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A113="","",IF(COUNTIF($R$6:$R$155,R113)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T113" t="str">
-        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
       </x:c>
       <x:c r="U113" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V113" s="62" t="n">
-        <x:v>46225</x:v>
+      <x:c r="V113" s="62" t="str">
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="W113" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
-      <x:c r="X113" t="str">
-        <x:v>2D逻辑资产的3D表现变体；六态白名单正常；moving使用位移驱动独立组件循环；角色网格使用render layer 2；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
+      <x:c r="X113" s="63" t="str">
+        <x:v>VisualRoot四主模块；方头/方身/方手/方脚；双眼双耳；圆短尾；六态与动作覆盖保持；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -8661,7 +8775,7 @@
         <x:v>CHR-PLY-CAPSULE01-BODY-3D</x:v>
       </x:c>
       <x:c r="B114" t="str">
-        <x:v>胶囊防护体3D身躯</x:v>
+        <x:v>方形猫角色3D身躯</x:v>
       </x:c>
       <x:c r="C114" t="str">
         <x:v>角色</x:v>
@@ -8713,23 +8827,23 @@
         <x:v>角色|player|player_capsule01|body_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S114" t="str">
-        <x:f>IF(A114="","",IF(COUNTIF($R$6:$R$145,R114)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A114="","",IF(COUNTIF($R$6:$R$155,R114)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T114" t="str">
-        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
       </x:c>
       <x:c r="U114" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V114" s="62" t="n">
-        <x:v>46225</x:v>
+      <x:c r="V114" s="62" t="str">
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="W114" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X114" t="str">
-        <x:v>PackedScene内独立Body节点；moving执行0.10m弹跳与压缩回弹；后续可替换GLB；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
+        <x:v>VisualRoot/Body：BoxMesh身躯、BellyPatch、圆形TailStub；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -8737,7 +8851,7 @@
         <x:v>CHR-PLY-CAPSULE01-HEAD-3D</x:v>
       </x:c>
       <x:c r="B115" t="str">
-        <x:v>胶囊防护体3D头壳</x:v>
+        <x:v>方形猫角色3D头部</x:v>
       </x:c>
       <x:c r="C115" t="str">
         <x:v>角色</x:v>
@@ -8789,23 +8903,23 @@
         <x:v>角色|player|player_capsule01|head_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S115" t="str">
-        <x:f>IF(A115="","",IF(COUNTIF($R$6:$R$145,R115)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A115="","",IF(COUNTIF($R$6:$R$155,R115)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T115" t="str">
-        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
       </x:c>
       <x:c r="U115" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V115" s="62" t="n">
-        <x:v>46225</x:v>
+      <x:c r="V115" s="62" t="str">
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="W115" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X115" t="str">
-        <x:v>PackedScene内独立Head节点；无人脸；移动时采用小幅反相滞后，避免与身体刚性粘连；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
+        <x:v>VisualRoot/Head：BoxMesh方头；Eyes双矩形眼；Ears双三角耳；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -8813,7 +8927,7 @@
         <x:v>CHR-PLY-CAPSULE01-HAND-3D</x:v>
       </x:c>
       <x:c r="B116" t="str">
-        <x:v>胶囊防护体3D唯一手部</x:v>
+        <x:v>方形猫角色3D唯一手部</x:v>
       </x:c>
       <x:c r="C116" t="str">
         <x:v>角色</x:v>
@@ -8865,23 +8979,23 @@
         <x:v>角色|player|player_capsule01|hand_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S116" t="str">
-        <x:f>IF(A116="","",IF(COUNTIF($R$6:$R$145,R116)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A116="","",IF(COUNTIF($R$6:$R$155,R116)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T116" t="str">
-        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
       </x:c>
       <x:c r="U116" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V116" s="62" t="n">
-        <x:v>46225</x:v>
+      <x:c r="V116" s="62" t="str">
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="W116" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X116" t="str">
-        <x:v>唯一可见手；随VisualRoot转向；与weapon_socket使用完全相同的移动偏移，局部关系不变；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
+        <x:v>VisualRoot/Hand：单个BoxMesh悬浮握持手；全动作与weapon_socket同相；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -8889,7 +9003,7 @@
         <x:v>CHR-PLY-CAPSULE01-SCARF-3D</x:v>
       </x:c>
       <x:c r="B117" t="str">
-        <x:v>胶囊防护体3D红围巾</x:v>
+        <x:v>旧3D红围巾兼容节点</x:v>
       </x:c>
       <x:c r="C117" t="str">
         <x:v>角色</x:v>
@@ -8941,23 +9055,23 @@
         <x:v>角色|player|player_capsule01|scarf_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S117" t="str">
-        <x:f>IF(A117="","",IF(COUNTIF($R$6:$R$145,R117)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A117="","",IF(COUNTIF($R$6:$R$155,R117)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T117" t="str">
-        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
       </x:c>
       <x:c r="U117" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V117" s="62" t="n">
-        <x:v>46225</x:v>
+      <x:c r="V117" s="62" t="str">
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="W117" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X117" t="str">
-        <x:v>独立Scarf节点；moving读取同一周期并使用较慢跟随形成滞后，冲刺保留飘动；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
+        <x:v>VisualRoot/Scarf默认隐藏，仅为旧场景兼容；当前四主模块不计入scarf；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -8965,7 +9079,7 @@
         <x:v>CHR-PLY-CAPSULE01-WEAPON-SOCKET-3D</x:v>
       </x:c>
       <x:c r="B118" t="str">
-        <x:v>胶囊防护体3D武器挂点</x:v>
+        <x:v>方形猫角色3D武器挂点</x:v>
       </x:c>
       <x:c r="C118" t="str">
         <x:v>角色</x:v>
@@ -9017,23 +9131,23 @@
         <x:v>角色|player|player_capsule01|weapon_socket_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S118" t="str">
-        <x:f>IF(A118="","",IF(COUNTIF($R$6:$R$145,R118)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A118="","",IF(COUNTIF($R$6:$R$155,R118)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T118" t="str">
-        <x:v>1bf2c9b88ecdcb9f8763c0d37b3b4c280e29a8a046e1c6bc22353f4a4fa102a1</x:v>
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
       </x:c>
       <x:c r="U118" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V118" s="62" t="n">
-        <x:v>46225</x:v>
+      <x:c r="V118" s="62" t="str">
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="W118" t="str">
         <x:v>原创逻辑挂点</x:v>
       </x:c>
       <x:c r="X118" t="str">
-        <x:v>手和挂点保持固定局部关系；随moving同相偏移；手持枪模型使用render layer 2；reloading覆盖层读取武器真实计时；唯一手与weapon_socket同相；头顶billboard进度条；完成/补弹/换枪/死亡无残留；verify_3d_reload_state_flow PASS</x:v>
+        <x:v>VisualRoot/WeaponSocket：(0.60,1.15,-0.42)，与唯一手固定相对向量；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -9093,7 +9207,7 @@
         <x:v>场景|base|base_world|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S119" t="str">
-        <x:f>IF(A119="","",IF(COUNTIF($R$6:$R$145,R119)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A119="","",IF(COUNTIF($R$6:$R$155,R119)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T119" t="str">
@@ -9169,7 +9283,7 @@
         <x:v>场景道具|facility|base_facility_module|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S120" t="str">
-        <x:f>IF(A120="","",IF(COUNTIF($R$6:$R$145,R120)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A120="","",IF(COUNTIF($R$6:$R$155,R120)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T120" t="str">
@@ -9245,7 +9359,7 @@
         <x:v>场景道具|door|dungeon_gate|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S121" t="str">
-        <x:f>IF(A121="","",IF(COUNTIF($R$6:$R$145,R121)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A121="","",IF(COUNTIF($R$6:$R$155,R121)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T121" t="str">
@@ -9321,7 +9435,7 @@
         <x:v>场景|review_board|base_world|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S122" t="str">
-        <x:f>IF(A122="","",IF(COUNTIF($R$6:$R$145,R122)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A122="","",IF(COUNTIF($R$6:$R$155,R122)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T122" t="str">
@@ -9395,7 +9509,7 @@
         <x:v>场景|room|dungeon_runtime|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S123" s="63" t="str">
-        <x:f>IF(A123="","",IF(COUNTIF($R$6:$R$145,R123)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A123="","",IF(COUNTIF($R$6:$R$155,R123)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T123" s="63" t="str">
@@ -9471,7 +9585,7 @@
         <x:v>场景|biome|iron_frontier|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S124" s="63" t="str">
-        <x:f>IF(A124="","",IF(COUNTIF($R$6:$R$145,R124)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A124="","",IF(COUNTIF($R$6:$R$155,R124)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T124" s="63" t="str">
@@ -9547,7 +9661,7 @@
         <x:v>场景|biome|rust_foundry|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S125" s="63" t="str">
-        <x:f>IF(A125="","",IF(COUNTIF($R$6:$R$145,R125)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A125="","",IF(COUNTIF($R$6:$R$155,R125)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T125" s="63" t="str">
@@ -9623,7 +9737,7 @@
         <x:v>场景|biome|spore_depths|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S126" s="63" t="str">
-        <x:f>IF(A126="","",IF(COUNTIF($R$6:$R$145,R126)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A126="","",IF(COUNTIF($R$6:$R$155,R126)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T126" s="63" t="str">
@@ -9699,7 +9813,7 @@
         <x:v>场景|biome|abyss_archive|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S127" s="63" t="str">
-        <x:f>IF(A127="","",IF(COUNTIF($R$6:$R$145,R127)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A127="","",IF(COUNTIF($R$6:$R$155,R127)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T127" s="63" t="str">
@@ -9775,7 +9889,7 @@
         <x:v>场景道具|light|wasteland_light|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S128" s="63" t="str">
-        <x:f>IF(A128="","",IF(COUNTIF($R$6:$R$145,R128)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A128="","",IF(COUNTIF($R$6:$R$155,R128)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T128" s="63" t="str">
@@ -9851,7 +9965,7 @@
         <x:v>场景道具|furniture|room_furniture|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S129" s="63" t="str">
-        <x:f>IF(A129="","",IF(COUNTIF($R$6:$R$145,R129)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A129="","",IF(COUNTIF($R$6:$R$155,R129)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T129" s="63" t="str">
@@ -9927,7 +10041,7 @@
         <x:v>场景道具|container|search_container|root_3d|俯视3d|closed_opened</x:v>
       </x:c>
       <x:c r="S130" s="63" t="str">
-        <x:f>IF(A130="","",IF(COUNTIF($R$6:$R$145,R130)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A130="","",IF(COUNTIF($R$6:$R$155,R130)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T130" s="63" t="str">
@@ -10003,7 +10117,7 @@
         <x:v>场景道具|facility|service_station|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S131" s="63" t="str">
-        <x:f>IF(A131="","",IF(COUNTIF($R$6:$R$145,R131)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A131="","",IF(COUNTIF($R$6:$R$155,R131)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T131" s="63" t="str">
@@ -10079,7 +10193,7 @@
         <x:v>场景道具|facility|extraction_beacon|root_3d|俯视3d|locked_active_done</x:v>
       </x:c>
       <x:c r="S132" s="63" t="str">
-        <x:f>IF(A132="","",IF(COUNTIF($R$6:$R$145,R132)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A132="","",IF(COUNTIF($R$6:$R$155,R132)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T132" s="63" t="str">
@@ -10155,7 +10269,7 @@
         <x:v>特效|environment|hazard_field|root_3d|俯视3d|active</x:v>
       </x:c>
       <x:c r="S133" s="63" t="str">
-        <x:f>IF(A133="","",IF(COUNTIF($R$6:$R$145,R133)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A133="","",IF(COUNTIF($R$6:$R$155,R133)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T133" s="63" t="str">
@@ -10229,7 +10343,7 @@
         <x:v>枪械|gunbody|blueprint_gun_catalog|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S134" s="63" t="str">
-        <x:f>IF(A134="","",IF(COUNTIF($R$6:$R$145,R134)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A134="","",IF(COUNTIF($R$6:$R$155,R134)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T134" s="63" t="str">
@@ -10303,7 +10417,7 @@
         <x:v>敌人|normal_elite_boss|enemy_ecosystem|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S135" s="63" t="str">
-        <x:f>IF(A135="","",IF(COUNTIF($R$6:$R$145,R135)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A135="","",IF(COUNTIF($R$6:$R$155,R135)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T135" s="63" t="str">
@@ -10377,7 +10491,7 @@
         <x:v>特效|combat|combat_feedback|root_3d|俯视3d|muzzle_impact_damage_explosion</x:v>
       </x:c>
       <x:c r="S136" s="63" t="str">
-        <x:f>IF(A136="","",IF(COUNTIF($R$6:$R$145,R136)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A136="","",IF(COUNTIF($R$6:$R$155,R136)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T136" s="63" t="str">
@@ -10451,7 +10565,7 @@
         <x:v>场景|training_range|training_range|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S137" s="63" t="str">
-        <x:f>IF(A137="","",IF(COUNTIF($R$6:$R$145,R137)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A137="","",IF(COUNTIF($R$6:$R$155,R137)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T137" s="63" t="str">
@@ -10527,7 +10641,7 @@
         <x:v>场景|review_board|dungeon_runtime|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S138" s="63" t="str">
-        <x:f>IF(A138="","",IF(COUNTIF($R$6:$R$145,R138)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A138="","",IF(COUNTIF($R$6:$R$155,R138)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T138" s="63" t="str">
@@ -10603,7 +10717,7 @@
         <x:v>场景|review_board|training_range|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S139" s="63" t="str">
-        <x:f>IF(A139="","",IF(COUNTIF($R$6:$R$145,R139)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A139="","",IF(COUNTIF($R$6:$R$155,R139)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T139" s="63" t="str">
@@ -10679,7 +10793,7 @@
         <x:v>特效|gameplay_vfx|visibility_field|field_mesh_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S140" t="str">
-        <x:f>IF(A140="","",IF(COUNTIF($R$6:$R$145,R140)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A140="","",IF(COUNTIF($R$6:$R$155,R140)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T140" t="str">
@@ -10755,7 +10869,7 @@
         <x:v>ui|screen|inventory|root_3d|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S141" t="str">
-        <x:f>IF(A141="","",IF(COUNTIF($R$6:$R$145,R141)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A141="","",IF(COUNTIF($R$6:$R$155,R141)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T141" t="str">
@@ -10829,7 +10943,7 @@
         <x:v>ui|screen|pause|root_3d|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S142" t="str">
-        <x:f>IF(A142="","",IF(COUNTIF($R$6:$R$145,R142)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A142="","",IF(COUNTIF($R$6:$R$155,R142)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T142" t="str">
@@ -10905,7 +11019,7 @@
         <x:v>场景道具|facility|room_light_switch|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S143" t="str">
-        <x:f>IF(A143="","",IF(COUNTIF($R$6:$R$145,R143)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A143="","",IF(COUNTIF($R$6:$R$155,R143)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T143" t="str">
@@ -10981,7 +11095,7 @@
         <x:v>特效|gameplay_vfx|player_flashlight|light_rig_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S144" t="str">
-        <x:f>IF(A144="","",IF(COUNTIF($R$6:$R$145,R144)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A144="","",IF(COUNTIF($R$6:$R$155,R144)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T144" t="str">
@@ -11057,7 +11171,7 @@
         <x:v>ui|icon|item_model_icon|root_3d|屏幕空间/3d投影|default</x:v>
       </x:c>
       <x:c r="S145" t="str">
-        <x:f>IF(A145="","",IF(COUNTIF($R$6:$R$145,R145)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A145="","",IF(COUNTIF($R$6:$R$155,R145)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T145" t="str">
@@ -11074,6 +11188,766 @@
       </x:c>
       <x:c r="X145" t="str">
         <x:v>与地面拾取共用 ItemModelFactory3D；96×96 内部视口缩放至56px槽位；只渲染一次；验收图：assets/art/ui/inventory_3d/ui_inventory_item_model_preview_v001.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="44" customHeight="1">
+      <x:c r="A146" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-BODY-DIY-3D</x:v>
+      </x:c>
+      <x:c r="B146" s="63" t="str">
+        <x:v>胶囊防护体3D身体DIY变体</x:v>
+      </x:c>
+      <x:c r="C146" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D146" s="63" t="str">
+        <x:v>player_variant</x:v>
+      </x:c>
+      <x:c r="E146" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F146" s="63" t="str">
+        <x:v>body_diy_3d</x:v>
+      </x:c>
+      <x:c r="G146" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-BODY-3D</x:v>
+      </x:c>
+      <x:c r="H146" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I146" s="63" t="str">
+        <x:v>diy</x:v>
+      </x:c>
+      <x:c r="J146" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K146" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L146" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M146" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N146" s="63" t="str">
+        <x:v>3种程序材质</x:v>
+      </x:c>
+      <x:c r="O146" s="63" t="str">
+        <x:v>src/player3d/PlayerAvatar3D.gd</x:v>
+      </x:c>
+      <x:c r="P146" s="63" t="str">
+        <x:v>VisualRoot/Body</x:v>
+      </x:c>
+      <x:c r="Q146" s="63" t="str">
+        <x:v>身体;防护服;DIY;橄榄;沙色;钴蓝</x:v>
+      </x:c>
+      <x:c r="R146" s="63" t="str">
+        <x:f>LOWER(TRIM(C146)&amp;"|"&amp;TRIM(D146)&amp;"|"&amp;TRIM(E146)&amp;"|"&amp;TRIM(F146)&amp;"|"&amp;TRIM(H146)&amp;"|"&amp;TRIM(I146))</x:f>
+        <x:v>角色|player_variant|player_capsule01|body_diy_3d|俯视3d|diy</x:v>
+      </x:c>
+      <x:c r="S146" s="63" t="str">
+        <x:f>IF(A146="","",IF(COUNTIF($R$6:$R$155,R146)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T146" s="63" t="str">
+        <x:v>43c7fa3fa002c9e5a2ec27f04fedeefacee2f32f3a91cb232e98f080513e2f7b</x:v>
+      </x:c>
+      <x:c r="U146" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V146" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W146" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X146" s="63" t="str">
+        <x:v>胶囊防护体3D身体DIY变体；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="44" customHeight="1">
+      <x:c r="A147" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HEAD-DIY-3D</x:v>
+      </x:c>
+      <x:c r="B147" s="63" t="str">
+        <x:v>胶囊防护体3D头部DIY变体</x:v>
+      </x:c>
+      <x:c r="C147" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D147" s="63" t="str">
+        <x:v>player_variant</x:v>
+      </x:c>
+      <x:c r="E147" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F147" s="63" t="str">
+        <x:v>head_diy_3d</x:v>
+      </x:c>
+      <x:c r="G147" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HEAD-3D</x:v>
+      </x:c>
+      <x:c r="H147" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I147" s="63" t="str">
+        <x:v>diy</x:v>
+      </x:c>
+      <x:c r="J147" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K147" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L147" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M147" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N147" s="63" t="str">
+        <x:v>3种程序材质</x:v>
+      </x:c>
+      <x:c r="O147" s="63" t="str">
+        <x:v>src/player3d/PlayerAvatar3D.gd</x:v>
+      </x:c>
+      <x:c r="P147" s="63" t="str">
+        <x:v>VisualRoot/Head</x:v>
+      </x:c>
+      <x:c r="Q147" s="63" t="str">
+        <x:v>头壳;传感器;DIY;青色面板;琥珀装甲</x:v>
+      </x:c>
+      <x:c r="R147" s="63" t="str">
+        <x:f>LOWER(TRIM(C147)&amp;"|"&amp;TRIM(D147)&amp;"|"&amp;TRIM(E147)&amp;"|"&amp;TRIM(F147)&amp;"|"&amp;TRIM(H147)&amp;"|"&amp;TRIM(I147))</x:f>
+        <x:v>角色|player_variant|player_capsule01|head_diy_3d|俯视3d|diy</x:v>
+      </x:c>
+      <x:c r="S147" s="63" t="str">
+        <x:f>IF(A147="","",IF(COUNTIF($R$6:$R$155,R147)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T147" s="63" t="str">
+        <x:v>43c7fa3fa002c9e5a2ec27f04fedeefacee2f32f3a91cb232e98f080513e2f7b</x:v>
+      </x:c>
+      <x:c r="U147" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V147" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W147" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X147" s="63" t="str">
+        <x:v>胶囊防护体3D头部DIY变体；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="44" customHeight="1">
+      <x:c r="A148" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HAND-DIY-3D</x:v>
+      </x:c>
+      <x:c r="B148" s="63" t="str">
+        <x:v>胶囊防护体3D手部DIY变体</x:v>
+      </x:c>
+      <x:c r="C148" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D148" s="63" t="str">
+        <x:v>player_variant</x:v>
+      </x:c>
+      <x:c r="E148" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F148" s="63" t="str">
+        <x:v>hand_diy_3d</x:v>
+      </x:c>
+      <x:c r="G148" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HAND-3D</x:v>
+      </x:c>
+      <x:c r="H148" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I148" s="63" t="str">
+        <x:v>diy</x:v>
+      </x:c>
+      <x:c r="J148" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K148" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L148" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M148" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N148" s="63" t="str">
+        <x:v>3种程序材质/抓握压缩</x:v>
+      </x:c>
+      <x:c r="O148" s="63" t="str">
+        <x:v>src/player3d/PlayerAvatar3D.gd</x:v>
+      </x:c>
+      <x:c r="P148" s="63" t="str">
+        <x:v>VisualRoot/Hand</x:v>
+      </x:c>
+      <x:c r="Q148" s="63" t="str">
+        <x:v>唯一手;握持;DIY;橙色;青绿</x:v>
+      </x:c>
+      <x:c r="R148" s="63" t="str">
+        <x:f>LOWER(TRIM(C148)&amp;"|"&amp;TRIM(D148)&amp;"|"&amp;TRIM(E148)&amp;"|"&amp;TRIM(F148)&amp;"|"&amp;TRIM(H148)&amp;"|"&amp;TRIM(I148))</x:f>
+        <x:v>角色|player_variant|player_capsule01|hand_diy_3d|俯视3d|diy</x:v>
+      </x:c>
+      <x:c r="S148" s="63" t="str">
+        <x:f>IF(A148="","",IF(COUNTIF($R$6:$R$155,R148)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T148" s="63" t="str">
+        <x:v>43c7fa3fa002c9e5a2ec27f04fedeefacee2f32f3a91cb232e98f080513e2f7b</x:v>
+      </x:c>
+      <x:c r="U148" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V148" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W148" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X148" s="63" t="str">
+        <x:v>胶囊防护体3D手部DIY变体；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="44" customHeight="1">
+      <x:c r="A149" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HAT-DIY-3D</x:v>
+      </x:c>
+      <x:c r="B149" s="63" t="str">
+        <x:v>胶囊防护体3D帽子DIY组件</x:v>
+      </x:c>
+      <x:c r="C149" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D149" s="63" t="str">
+        <x:v>player_accessory</x:v>
+      </x:c>
+      <x:c r="E149" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F149" s="63" t="str">
+        <x:v>hat_diy_3d</x:v>
+      </x:c>
+      <x:c r="G149" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HEAD-3D</x:v>
+      </x:c>
+      <x:c r="H149" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I149" s="63" t="str">
+        <x:v>diy</x:v>
+      </x:c>
+      <x:c r="J149" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K149" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L149" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M149" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N149" s="63" t="str">
+        <x:v>软帽/安全帽/密封兜帽</x:v>
+      </x:c>
+      <x:c r="O149" s="63" t="str">
+        <x:v>src/player3d/PlayerAvatar3D.gd</x:v>
+      </x:c>
+      <x:c r="P149" s="63" t="str">
+        <x:v>VisualRoot/Head/Wearables</x:v>
+      </x:c>
+      <x:c r="Q149" s="63" t="str">
+        <x:v>帽子;软帽;安全帽;兜帽;DIY</x:v>
+      </x:c>
+      <x:c r="R149" s="63" t="str">
+        <x:f>LOWER(TRIM(C149)&amp;"|"&amp;TRIM(D149)&amp;"|"&amp;TRIM(E149)&amp;"|"&amp;TRIM(F149)&amp;"|"&amp;TRIM(H149)&amp;"|"&amp;TRIM(I149))</x:f>
+        <x:v>角色|player_accessory|player_capsule01|hat_diy_3d|俯视3d|diy</x:v>
+      </x:c>
+      <x:c r="S149" s="63" t="str">
+        <x:f>IF(A149="","",IF(COUNTIF($R$6:$R$155,R149)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T149" s="63" t="str">
+        <x:v>43c7fa3fa002c9e5a2ec27f04fedeefacee2f32f3a91cb232e98f080513e2f7b</x:v>
+      </x:c>
+      <x:c r="U149" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V149" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W149" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X149" s="63" t="str">
+        <x:v>胶囊防护体3D帽子DIY组件；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH32灯光修正：角色专用层2；禁用投影/GI，仅接收AvatarFrontFill，不遮挡头壳传感器或探照灯 ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="44" customHeight="1">
+      <x:c r="A150" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-GLASSES-DIY-3D</x:v>
+      </x:c>
+      <x:c r="B150" s="63" t="str">
+        <x:v>胶囊防护体3D眼镜DIY组件</x:v>
+      </x:c>
+      <x:c r="C150" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D150" s="63" t="str">
+        <x:v>player_accessory</x:v>
+      </x:c>
+      <x:c r="E150" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F150" s="63" t="str">
+        <x:v>glasses_diy_3d</x:v>
+      </x:c>
+      <x:c r="G150" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HEAD-3D</x:v>
+      </x:c>
+      <x:c r="H150" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I150" s="63" t="str">
+        <x:v>diy</x:v>
+      </x:c>
+      <x:c r="J150" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K150" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L150" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M150" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N150" s="63" t="str">
+        <x:v>单目镜/双目护镜/宽面护目镜</x:v>
+      </x:c>
+      <x:c r="O150" s="63" t="str">
+        <x:v>src/player3d/PlayerAvatar3D.gd</x:v>
+      </x:c>
+      <x:c r="P150" s="63" t="str">
+        <x:v>VisualRoot/Head/Wearables</x:v>
+      </x:c>
+      <x:c r="Q150" s="63" t="str">
+        <x:v>眼镜;单目镜;护目镜;宽面护目镜;DIY</x:v>
+      </x:c>
+      <x:c r="R150" s="63" t="str">
+        <x:f>LOWER(TRIM(C150)&amp;"|"&amp;TRIM(D150)&amp;"|"&amp;TRIM(E150)&amp;"|"&amp;TRIM(F150)&amp;"|"&amp;TRIM(H150)&amp;"|"&amp;TRIM(I150))</x:f>
+        <x:v>角色|player_accessory|player_capsule01|glasses_diy_3d|俯视3d|diy</x:v>
+      </x:c>
+      <x:c r="S150" s="63" t="str">
+        <x:f>IF(A150="","",IF(COUNTIF($R$6:$R$155,R150)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T150" s="63" t="str">
+        <x:v>43c7fa3fa002c9e5a2ec27f04fedeefacee2f32f3a91cb232e98f080513e2f7b</x:v>
+      </x:c>
+      <x:c r="U150" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V150" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W150" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X150" s="63" t="str">
+        <x:v>胶囊防护体3D眼镜DIY组件；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH32灯光修正：角色专用层2；禁用投影/GI，仅接收AvatarFrontFill，不遮挡头壳传感器或探照灯 ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="44" customHeight="1">
+      <x:c r="A151" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-FOOT-3D</x:v>
+      </x:c>
+      <x:c r="B151" s="63" t="str">
+        <x:v>方形猫角色3D脚部模块</x:v>
+      </x:c>
+      <x:c r="C151" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D151" s="63" t="str">
+        <x:v>player</x:v>
+      </x:c>
+      <x:c r="E151" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F151" s="63" t="str">
+        <x:v>feet_3d</x:v>
+      </x:c>
+      <x:c r="G151" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="H151" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I151" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J151" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K151" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L151" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M151" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N151" s="63" t="str">
+        <x:v>双BoxMesh短脚</x:v>
+      </x:c>
+      <x:c r="O151" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P151" s="63" t="str">
+        <x:v>VisualRoot/Feet</x:v>
+      </x:c>
+      <x:c r="Q151" s="63" t="str">
+        <x:v>脚;脚部;双脚;方脚;猫脚</x:v>
+      </x:c>
+      <x:c r="R151" s="63" t="str">
+        <x:f>LOWER(TRIM(C151)&amp;"|"&amp;TRIM(D151)&amp;"|"&amp;TRIM(E151)&amp;"|"&amp;TRIM(F151)&amp;"|"&amp;TRIM(H151)&amp;"|"&amp;TRIM(I151))</x:f>
+        <x:v>角色|player|player_capsule01|feet_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S151" s="63" t="str">
+        <x:f>IF(A151="","",IF(COUNTIF($R$6:$R$155,R151)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T151" s="63" t="str">
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+      </x:c>
+      <x:c r="U151" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V151" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W151" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X151" s="63" t="str">
+        <x:v>方形猫角色3D脚部模块；复用CHR-PLY-CAPSULE01-3D玩家根；方形主语言，TailStub为用户指定圆尾例外；自动与视觉验收PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="44" customHeight="1">
+      <x:c r="A152" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-EYES-3D</x:v>
+      </x:c>
+      <x:c r="B152" s="63" t="str">
+        <x:v>方形猫角色3D双眼配件</x:v>
+      </x:c>
+      <x:c r="C152" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D152" s="63" t="str">
+        <x:v>player_accessory</x:v>
+      </x:c>
+      <x:c r="E152" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F152" s="63" t="str">
+        <x:v>eyes_3d</x:v>
+      </x:c>
+      <x:c r="G152" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HEAD-3D</x:v>
+      </x:c>
+      <x:c r="H152" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I152" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J152" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K152" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L152" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M152" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N152" s="63" t="str">
+        <x:v>2个矩形豆豆眼</x:v>
+      </x:c>
+      <x:c r="O152" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P152" s="63" t="str">
+        <x:v>VisualRoot/Head/Eyes</x:v>
+      </x:c>
+      <x:c r="Q152" s="63" t="str">
+        <x:v>眼睛;双眼;豆豆眼;矩形眼</x:v>
+      </x:c>
+      <x:c r="R152" s="63" t="str">
+        <x:f>LOWER(TRIM(C152)&amp;"|"&amp;TRIM(D152)&amp;"|"&amp;TRIM(E152)&amp;"|"&amp;TRIM(F152)&amp;"|"&amp;TRIM(H152)&amp;"|"&amp;TRIM(I152))</x:f>
+        <x:v>角色|player_accessory|player_capsule01|eyes_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S152" s="63" t="str">
+        <x:f>IF(A152="","",IF(COUNTIF($R$6:$R$155,R152)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T152" s="63" t="str">
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+      </x:c>
+      <x:c r="U152" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V152" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W152" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X152" s="63" t="str">
+        <x:v>方形猫角色3D双眼配件；复用CHR-PLY-CAPSULE01-3D玩家根；方形主语言，TailStub为用户指定圆尾例外；自动与视觉验收PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="44" customHeight="1">
+      <x:c r="A153" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-EARS-3D</x:v>
+      </x:c>
+      <x:c r="B153" s="63" t="str">
+        <x:v>方形猫角色3D双耳配件</x:v>
+      </x:c>
+      <x:c r="C153" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D153" s="63" t="str">
+        <x:v>player_accessory</x:v>
+      </x:c>
+      <x:c r="E153" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F153" s="63" t="str">
+        <x:v>ears_3d</x:v>
+      </x:c>
+      <x:c r="G153" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-HEAD-3D</x:v>
+      </x:c>
+      <x:c r="H153" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I153" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J153" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K153" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L153" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M153" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N153" s="63" t="str">
+        <x:v>2个三角耳</x:v>
+      </x:c>
+      <x:c r="O153" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P153" s="63" t="str">
+        <x:v>VisualRoot/Head/Ears</x:v>
+      </x:c>
+      <x:c r="Q153" s="63" t="str">
+        <x:v>耳朵;双耳;猫耳;三角耳</x:v>
+      </x:c>
+      <x:c r="R153" s="63" t="str">
+        <x:f>LOWER(TRIM(C153)&amp;"|"&amp;TRIM(D153)&amp;"|"&amp;TRIM(E153)&amp;"|"&amp;TRIM(F153)&amp;"|"&amp;TRIM(H153)&amp;"|"&amp;TRIM(I153))</x:f>
+        <x:v>角色|player_accessory|player_capsule01|ears_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S153" s="63" t="str">
+        <x:f>IF(A153="","",IF(COUNTIF($R$6:$R$155,R153)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T153" s="63" t="str">
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+      </x:c>
+      <x:c r="U153" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V153" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W153" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X153" s="63" t="str">
+        <x:v>方形猫角色3D双耳配件；复用CHR-PLY-CAPSULE01-3D玩家根；方形主语言，TailStub为用户指定圆尾例外；自动与视觉验收PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="44" customHeight="1">
+      <x:c r="A154" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-TAIL-STUB-3D</x:v>
+      </x:c>
+      <x:c r="B154" s="63" t="str">
+        <x:v>方形猫角色3D圆短尾</x:v>
+      </x:c>
+      <x:c r="C154" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D154" s="63" t="str">
+        <x:v>player_accessory</x:v>
+      </x:c>
+      <x:c r="E154" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F154" s="63" t="str">
+        <x:v>tail_stub_3d</x:v>
+      </x:c>
+      <x:c r="G154" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-BODY-3D</x:v>
+      </x:c>
+      <x:c r="H154" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I154" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J154" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K154" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L154" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M154" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N154" s="63" t="str">
+        <x:v>单个SphereMesh圆尾团</x:v>
+      </x:c>
+      <x:c r="O154" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P154" s="63" t="str">
+        <x:v>VisualRoot/Body/TailStub</x:v>
+      </x:c>
+      <x:c r="Q154" s="63" t="str">
+        <x:v>尾巴;短尾;圆尾;尾团;无长尾</x:v>
+      </x:c>
+      <x:c r="R154" s="63" t="str">
+        <x:f>LOWER(TRIM(C154)&amp;"|"&amp;TRIM(D154)&amp;"|"&amp;TRIM(E154)&amp;"|"&amp;TRIM(F154)&amp;"|"&amp;TRIM(H154)&amp;"|"&amp;TRIM(I154))</x:f>
+        <x:v>角色|player_accessory|player_capsule01|tail_stub_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S154" s="63" t="str">
+        <x:f>IF(A154="","",IF(COUNTIF($R$6:$R$155,R154)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T154" s="63" t="str">
+        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+      </x:c>
+      <x:c r="U154" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V154" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W154" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X154" s="63" t="str">
+        <x:v>方形猫角色3D圆短尾；复用CHR-PLY-CAPSULE01-3D玩家根；方形主语言，TailStub为用户指定圆尾例外；自动与视觉验收PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="44" customHeight="1">
+      <x:c r="A155" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-FEET-DIY-3D</x:v>
+      </x:c>
+      <x:c r="B155" s="63" t="str">
+        <x:v>方形猫角色3D脚部DIY变体</x:v>
+      </x:c>
+      <x:c r="C155" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D155" s="63" t="str">
+        <x:v>player_variant</x:v>
+      </x:c>
+      <x:c r="E155" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F155" s="63" t="str">
+        <x:v>feet_diy_3d</x:v>
+      </x:c>
+      <x:c r="G155" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-FOOT-3D</x:v>
+      </x:c>
+      <x:c r="H155" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I155" s="63" t="str">
+        <x:v>diy</x:v>
+      </x:c>
+      <x:c r="J155" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="K155" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L155" s="63" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M155" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N155" s="63" t="str">
+        <x:v>4种程序材质</x:v>
+      </x:c>
+      <x:c r="O155" s="63" t="str">
+        <x:v>src/player3d/PlayerAvatar3D.gd</x:v>
+      </x:c>
+      <x:c r="P155" s="63" t="str">
+        <x:v>VisualRoot/Feet</x:v>
+      </x:c>
+      <x:c r="Q155" s="63" t="str">
+        <x:v>脚部DIY;猫脚;短靴;橙色;沙色;钴蓝;青绿</x:v>
+      </x:c>
+      <x:c r="R155" s="63" t="str">
+        <x:f>LOWER(TRIM(C155)&amp;"|"&amp;TRIM(D155)&amp;"|"&amp;TRIM(E155)&amp;"|"&amp;TRIM(F155)&amp;"|"&amp;TRIM(H155)&amp;"|"&amp;TRIM(I155))</x:f>
+        <x:v>角色|player_variant|player_capsule01|feet_diy_3d|俯视3d|diy</x:v>
+      </x:c>
+      <x:c r="S155" s="63" t="str">
+        <x:f>IF(A155="","",IF(COUNTIF($R$6:$R$155,R155)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T155" s="63" t="str">
+        <x:v>43c7fa3fa002c9e5a2ec27f04fedeefacee2f32f3a91cb232e98f080513e2f7b</x:v>
+      </x:c>
+      <x:c r="U155" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V155" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="W155" s="63" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X155" s="63" t="str">
+        <x:v>方形猫角色3D脚部DIY变体；复用CHR-PLY-CAPSULE01-3D玩家根；方形主语言，TailStub为用户指定圆尾例外；自动与视觉验收PASS</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11101,7 +11975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc54e4f8a28d64a35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54ff6c904d8a485a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11543,7 +12417,7 @@
         <x:v>必要时高于双手</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="34" customHeight="1">
+    <x:row r="14" ht="38" customHeight="1">
       <x:c r="A14" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
@@ -11572,7 +12446,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J14" s="63" t="str">
-        <x:v>六态整体变换 + reloading覆盖</x:v>
+        <x:v>六态整体 + reloading/firing/charging/knockback覆盖</x:v>
       </x:c>
       <x:c r="K14" s="63" t="str">
         <x:v>3D表现根</x:v>
@@ -11581,10 +12455,10 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M14" s="63" t="str">
-        <x:v>与2D共用六态ID；reloading不替换顶层；摄像机和头顶条不跟随VisualRoot旋转</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="34" customHeight="1">
+        <x:v>四主模块：Body/Head/Hand/Feet；2D旧胶囊不在本次迁移范围</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="38" customHeight="1">
       <x:c r="A15" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
@@ -11601,10 +12475,10 @@
         <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
       </x:c>
       <x:c r="F15" s="63" t="str">
-        <x:v>CapsuleMesh</x:v>
+        <x:v>BoxMesh + 子件</x:v>
       </x:c>
       <x:c r="G15" s="63" t="str">
-        <x:v>(0,0.88,0)</x:v>
+        <x:v>(0,0.76,0.02)</x:v>
       </x:c>
       <x:c r="H15" s="63" t="str">
         <x:v>随root</x:v>
@@ -11613,27 +12487,27 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="63" t="str">
-        <x:v>独立移动弹性/呼吸/死亡倾倒</x:v>
+        <x:v>呼吸/移动压缩/射击前探/死亡倾倒</x:v>
       </x:c>
       <x:c r="K15" s="63" t="str">
-        <x:v>防护服主体</x:v>
+        <x:v>方形猫身</x:v>
       </x:c>
       <x:c r="L15" s="63" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="M15" s="63" t="str">
-        <x:v>无腿、无脚、无手臂；render layer 2；移动振幅沿用2D弹性</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="34" customHeight="1">
+        <x:v>BodyShell + BellyPatch；方形主轮廓</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="38" customHeight="1">
       <x:c r="A16" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
       <x:c r="B16" s="63" t="str">
-        <x:v>scarf</x:v>
+        <x:v>head</x:v>
       </x:c>
       <x:c r="C16" s="63" t="str">
-        <x:v>VisualRoot/Scarf</x:v>
+        <x:v>VisualRoot/Head</x:v>
       </x:c>
       <x:c r="D16" s="63" t="str">
         <x:v>root</x:v>
@@ -11642,39 +12516,39 @@
         <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
       </x:c>
       <x:c r="F16" s="63" t="str">
-        <x:v>Cylinder+Box</x:v>
+        <x:v>BoxMesh + 子件</x:v>
       </x:c>
       <x:c r="G16" s="63" t="str">
-        <x:v>(0,1.43,0)</x:v>
+        <x:v>(0,1.72,-0.08)</x:v>
       </x:c>
       <x:c r="H16" s="63" t="str">
-        <x:v>随root + 轻摆</x:v>
+        <x:v>随root</x:v>
       </x:c>
       <x:c r="I16" s="63" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J16" s="63" t="str">
-        <x:v>移动周期滞后/冲刺飘动</x:v>
+        <x:v>移动反相滞后/后坐/受击/死亡</x:v>
       </x:c>
       <x:c r="K16" s="63" t="str">
-        <x:v>身份配件</x:v>
+        <x:v>方形猫头</x:v>
       </x:c>
       <x:c r="L16" s="63" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M16" s="63" t="str">
-        <x:v>独立红围巾组件；moving以较慢跟随形成可读滞后</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="34" customHeight="1">
+        <x:v>无嘴无鼻；Eyes与Ears固定归Head</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="38" customHeight="1">
       <x:c r="A17" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
       <x:c r="B17" s="63" t="str">
-        <x:v>head</x:v>
+        <x:v>hand</x:v>
       </x:c>
       <x:c r="C17" s="63" t="str">
-        <x:v>VisualRoot/Head</x:v>
+        <x:v>VisualRoot/Hand</x:v>
       </x:c>
       <x:c r="D17" s="63" t="str">
         <x:v>root</x:v>
@@ -11683,39 +12557,39 @@
         <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
       </x:c>
       <x:c r="F17" s="63" t="str">
-        <x:v>SphereMesh</x:v>
+        <x:v>BoxMesh</x:v>
       </x:c>
       <x:c r="G17" s="63" t="str">
-        <x:v>(0,1.84,-0.01)</x:v>
+        <x:v>(0.60,1.10,-0.30)</x:v>
       </x:c>
       <x:c r="H17" s="63" t="str">
-        <x:v>随root</x:v>
+        <x:v>随root；动作同相</x:v>
       </x:c>
       <x:c r="I17" s="63" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J17" s="63" t="str">
-        <x:v>移动反相滞后/呼吸/受击/死亡</x:v>
+        <x:v>移动/换弹/射击/蓄力/击飞保持握持</x:v>
       </x:c>
       <x:c r="K17" s="63" t="str">
-        <x:v>头壳/传感器</x:v>
+        <x:v>唯一悬浮手</x:v>
       </x:c>
       <x:c r="L17" s="63" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="M17" s="63" t="str">
-        <x:v>单传感器；无嘴无人脸；只受角色正面柔光与房间公共灯</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="34" customHeight="1">
+        <x:v>无手臂、无第二手；与WeaponSocket固定相对向量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="38" customHeight="1">
       <x:c r="A18" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
       <x:c r="B18" s="63" t="str">
-        <x:v>hand</x:v>
+        <x:v>feet</x:v>
       </x:c>
       <x:c r="C18" s="63" t="str">
-        <x:v>VisualRoot/Hand</x:v>
+        <x:v>VisualRoot/Feet</x:v>
       </x:c>
       <x:c r="D18" s="63" t="str">
         <x:v>root</x:v>
@@ -11724,110 +12598,520 @@
         <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
       </x:c>
       <x:c r="F18" s="63" t="str">
-        <x:v>SphereMesh</x:v>
+        <x:v>BoxMesh×2</x:v>
       </x:c>
       <x:c r="G18" s="63" t="str">
-        <x:v>(0.72,1.22,-0.18)</x:v>
+        <x:v>(0,0.22,-0.02)</x:v>
       </x:c>
       <x:c r="H18" s="63" t="str">
-        <x:v>随root；换弹时同相位移/旋转</x:v>
+        <x:v>随root；FootL/R交替</x:v>
       </x:c>
       <x:c r="I18" s="63" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J18" s="63" t="str">
-        <x:v>moving同相；换弹下压/操作/回位；保持握持位</x:v>
+        <x:v>moving交替抬脚；冲刺/受击/死亡随整体</x:v>
       </x:c>
       <x:c r="K18" s="63" t="str">
-        <x:v>唯一握持手</x:v>
+        <x:v>双脚主模块</x:v>
       </x:c>
       <x:c r="L18" s="63" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="M18" s="63" t="str">
-        <x:v>只有一只手；与weapon_socket在moving/reloading全周期保持固定相对向量</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="34" customHeight="1">
+        <x:v>FootL/FootR属于同一可替换Feet模块</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="38" customHeight="1">
       <x:c r="A19" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
       <x:c r="B19" s="63" t="str">
-        <x:v>weapon_socket</x:v>
+        <x:v>eyes</x:v>
       </x:c>
       <x:c r="C19" s="63" t="str">
-        <x:v>VisualRoot/WeaponSocket</x:v>
+        <x:v>VisualRoot/Head/Eyes</x:v>
       </x:c>
       <x:c r="D19" s="63" t="str">
-        <x:v>root</x:v>
+        <x:v>head</x:v>
       </x:c>
       <x:c r="E19" s="63" t="str">
-        <x:v>无纹理</x:v>
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
       </x:c>
       <x:c r="F19" s="63" t="str">
-        <x:v>Marker3D</x:v>
+        <x:v>BoxMesh×2</x:v>
       </x:c>
       <x:c r="G19" s="63" t="str">
-        <x:v>(0.72,1.24,-0.34)</x:v>
+        <x:v>(0,-0.03,-0.56)</x:v>
       </x:c>
       <x:c r="H19" s="63" t="str">
-        <x:v>随root；换弹时同相位移/旋转</x:v>
+        <x:v>继承Head</x:v>
       </x:c>
       <x:c r="I19" s="63" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J19" s="63" t="str">
-        <x:v>与唯一手同相；换弹下压/操作/回位；枪械挂载/枪口特效</x:v>
+        <x:v>随头部滞后/后坐/受击</x:v>
       </x:c>
       <x:c r="K19" s="63" t="str">
-        <x:v>武器系统</x:v>
+        <x:v>面部配件</x:v>
       </x:c>
       <x:c r="L19" s="63" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="M19" s="63" t="str">
-        <x:v>挂点与手在moving/reloading保持固定局部关系；手持枪网格统一render layer 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="34" customHeight="1">
+        <x:v>EyeL/EyeR；深色窄矩形豆豆眼；无嘴</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="38" customHeight="1">
       <x:c r="A20" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
       <x:c r="B20" s="63" t="str">
-        <x:v>reload_progress</x:v>
+        <x:v>ears</x:v>
       </x:c>
       <x:c r="C20" s="63" t="str">
-        <x:v>ReloadProgress3D</x:v>
+        <x:v>VisualRoot/Head/Ears</x:v>
       </x:c>
       <x:c r="D20" s="63" t="str">
-        <x:v>player_root</x:v>
+        <x:v>head</x:v>
       </x:c>
       <x:c r="E20" s="63" t="str">
         <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
       </x:c>
       <x:c r="F20" s="63" t="str">
-        <x:v>QuadMesh×2</x:v>
+        <x:v>三边CylinderMesh×4</x:v>
       </x:c>
       <x:c r="G20" s="63" t="str">
-        <x:v>(0,2.72,0.06)</x:v>
+        <x:v>沿Head顶部</x:v>
       </x:c>
       <x:c r="H20" s="63" t="str">
-        <x:v>朝向相机；不随VisualRoot旋转</x:v>
+        <x:v>继承Head</x:v>
       </x:c>
       <x:c r="I20" s="63" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J20" s="63" t="str">
-        <x:v>读取真实换弹进度；左端固定；完成/取消隐藏</x:v>
+        <x:v>随头部滞后/后坐/受击</x:v>
       </x:c>
       <x:c r="K20" s="63" t="str">
-        <x:v>状态UI子组件</x:v>
+        <x:v>头部配件</x:v>
       </x:c>
       <x:c r="L20" s="63" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="M20" s="63" t="str">
-        <x:v>无独立计时器/SubViewport；不参与碰撞、视野、灯光或输入；56组合共用</x:v>
+        <x:v>EarL/EarR各含Inner；三角形语言</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="38" customHeight="1">
+      <x:c r="A21" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B21" s="63" t="str">
+        <x:v>tail_stub</x:v>
+      </x:c>
+      <x:c r="C21" s="63" t="str">
+        <x:v>VisualRoot/Body/TailStub</x:v>
+      </x:c>
+      <x:c r="D21" s="63" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="E21" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F21" s="63" t="str">
+        <x:v>SphereMesh</x:v>
+      </x:c>
+      <x:c r="G21" s="63" t="str">
+        <x:v>(-0.51,-0.02,0.24)</x:v>
+      </x:c>
+      <x:c r="H21" s="63" t="str">
+        <x:v>继承Body + 轻摆</x:v>
+      </x:c>
+      <x:c r="I21" s="63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J21" s="63" t="str">
+        <x:v>moving轻摆/弹性缩放</x:v>
+      </x:c>
+      <x:c r="K21" s="63" t="str">
+        <x:v>身体配件</x:v>
+      </x:c>
+      <x:c r="L21" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M21" s="63" t="str">
+        <x:v>唯一圆形例外；短圆尾团，禁止长尾</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="38" customHeight="1">
+      <x:c r="A22" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B22" s="63" t="str">
+        <x:v>weapon_socket</x:v>
+      </x:c>
+      <x:c r="C22" s="63" t="str">
+        <x:v>VisualRoot/WeaponSocket</x:v>
+      </x:c>
+      <x:c r="D22" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E22" s="63" t="str">
+        <x:v>无纹理</x:v>
+      </x:c>
+      <x:c r="F22" s="63" t="str">
+        <x:v>Marker3D</x:v>
+      </x:c>
+      <x:c r="G22" s="63" t="str">
+        <x:v>(0.60,1.15,-0.42)</x:v>
+      </x:c>
+      <x:c r="H22" s="63" t="str">
+        <x:v>随root；动作同相</x:v>
+      </x:c>
+      <x:c r="I22" s="63" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J22" s="63" t="str">
+        <x:v>枪械挂载/枪口特效</x:v>
+      </x:c>
+      <x:c r="K22" s="63" t="str">
+        <x:v>武器系统</x:v>
+      </x:c>
+      <x:c r="L22" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M22" s="63" t="str">
+        <x:v>与唯一手全动作固定局部关系；枪模layer 2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="38" customHeight="1">
+      <x:c r="A23" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B23" s="63" t="str">
+        <x:v>reload_progress</x:v>
+      </x:c>
+      <x:c r="C23" s="63" t="str">
+        <x:v>ReloadProgress3D</x:v>
+      </x:c>
+      <x:c r="D23" s="63" t="str">
+        <x:v>player_root</x:v>
+      </x:c>
+      <x:c r="E23" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F23" s="63" t="str">
+        <x:v>QuadMesh×2</x:v>
+      </x:c>
+      <x:c r="G23" s="63" t="str">
+        <x:v>(0,2.92,0.06)</x:v>
+      </x:c>
+      <x:c r="H23" s="63" t="str">
+        <x:v>朝向相机；不随VisualRoot旋转</x:v>
+      </x:c>
+      <x:c r="I23" s="63" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J23" s="63" t="str">
+        <x:v>读取真实换弹进度</x:v>
+      </x:c>
+      <x:c r="K23" s="63" t="str">
+        <x:v>状态UI子组件</x:v>
+      </x:c>
+      <x:c r="L23" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M23" s="63" t="str">
+        <x:v>高于猫耳；无独立计时器/SubViewport</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="38" customHeight="1">
+      <x:c r="A24" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B24" s="63" t="str">
+        <x:v>body_diy</x:v>
+      </x:c>
+      <x:c r="C24" s="63" t="str">
+        <x:v>VisualRoot/Body</x:v>
+      </x:c>
+      <x:c r="D24" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E24" s="63" t="str">
+        <x:v>无独立纹理/程序材质</x:v>
+      </x:c>
+      <x:c r="F24" s="63" t="str">
+        <x:v>4种配色</x:v>
+      </x:c>
+      <x:c r="G24" s="63" t="str">
+        <x:v>沿Body</x:v>
+      </x:c>
+      <x:c r="H24" s="63" t="str">
+        <x:v>随root</x:v>
+      </x:c>
+      <x:c r="I24" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J24" s="63" t="str">
+        <x:v>继承身体动态</x:v>
+      </x:c>
+      <x:c r="K24" s="63" t="str">
+        <x:v>身体外观</x:v>
+      </x:c>
+      <x:c r="L24" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M24" s="63" t="str">
+        <x:v>cat_orange + 旧三色兼容</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="38" customHeight="1">
+      <x:c r="A25" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B25" s="63" t="str">
+        <x:v>head_diy</x:v>
+      </x:c>
+      <x:c r="C25" s="63" t="str">
+        <x:v>VisualRoot/Head</x:v>
+      </x:c>
+      <x:c r="D25" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E25" s="63" t="str">
+        <x:v>无独立纹理/程序材质</x:v>
+      </x:c>
+      <x:c r="F25" s="63" t="str">
+        <x:v>4种配色</x:v>
+      </x:c>
+      <x:c r="G25" s="63" t="str">
+        <x:v>沿Head</x:v>
+      </x:c>
+      <x:c r="H25" s="63" t="str">
+        <x:v>随root</x:v>
+      </x:c>
+      <x:c r="I25" s="63" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J25" s="63" t="str">
+        <x:v>继承头部动态</x:v>
+      </x:c>
+      <x:c r="K25" s="63" t="str">
+        <x:v>头部外观</x:v>
+      </x:c>
+      <x:c r="L25" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M25" s="63" t="str">
+        <x:v>cat_orange + 旧三色兼容；双眼/双耳节点不变</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="38" customHeight="1">
+      <x:c r="A26" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B26" s="63" t="str">
+        <x:v>hand_diy</x:v>
+      </x:c>
+      <x:c r="C26" s="63" t="str">
+        <x:v>VisualRoot/Hand</x:v>
+      </x:c>
+      <x:c r="D26" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E26" s="63" t="str">
+        <x:v>无独立纹理/程序材质</x:v>
+      </x:c>
+      <x:c r="F26" s="63" t="str">
+        <x:v>4种配色</x:v>
+      </x:c>
+      <x:c r="G26" s="63" t="str">
+        <x:v>(0.60,1.10,-0.30)</x:v>
+      </x:c>
+      <x:c r="H26" s="63" t="str">
+        <x:v>随root+同相动作</x:v>
+      </x:c>
+      <x:c r="I26" s="63" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J26" s="63" t="str">
+        <x:v>抓握压缩；与socket同相</x:v>
+      </x:c>
+      <x:c r="K26" s="63" t="str">
+        <x:v>唯一手外观</x:v>
+      </x:c>
+      <x:c r="L26" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M26" s="63" t="str">
+        <x:v>cat_orange + 旧三色兼容</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="38" customHeight="1">
+      <x:c r="A27" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B27" s="63" t="str">
+        <x:v>feet_diy</x:v>
+      </x:c>
+      <x:c r="C27" s="63" t="str">
+        <x:v>VisualRoot/Feet</x:v>
+      </x:c>
+      <x:c r="D27" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E27" s="63" t="str">
+        <x:v>无独立纹理/程序材质</x:v>
+      </x:c>
+      <x:c r="F27" s="63" t="str">
+        <x:v>4种配色</x:v>
+      </x:c>
+      <x:c r="G27" s="63" t="str">
+        <x:v>沿Feet</x:v>
+      </x:c>
+      <x:c r="H27" s="63" t="str">
+        <x:v>随root+交替步态</x:v>
+      </x:c>
+      <x:c r="I27" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J27" s="63" t="str">
+        <x:v>FootL/R交替抬起</x:v>
+      </x:c>
+      <x:c r="K27" s="63" t="str">
+        <x:v>脚部外观</x:v>
+      </x:c>
+      <x:c r="L27" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M27" s="63" t="str">
+        <x:v>cat_orange / boot_sand / boot_cobalt / boot_teal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="38" customHeight="1">
+      <x:c r="A28" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B28" s="63" t="str">
+        <x:v>hat</x:v>
+      </x:c>
+      <x:c r="C28" s="63" t="str">
+        <x:v>VisualRoot/Head/Wearables/Hat*</x:v>
+      </x:c>
+      <x:c r="D28" s="63" t="str">
+        <x:v>head</x:v>
+      </x:c>
+      <x:c r="E28" s="63" t="str">
+        <x:v>无独立纹理/程序网格</x:v>
+      </x:c>
+      <x:c r="F28" s="63" t="str">
+        <x:v>3种帽型</x:v>
+      </x:c>
+      <x:c r="G28" s="63" t="str">
+        <x:v>沿Head</x:v>
+      </x:c>
+      <x:c r="H28" s="63" t="str">
+        <x:v>继承Head</x:v>
+      </x:c>
+      <x:c r="I28" s="63" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J28" s="63" t="str">
+        <x:v>头部滞后/受击/死亡</x:v>
+      </x:c>
+      <x:c r="K28" s="63" t="str">
+        <x:v>头部外戴件</x:v>
+      </x:c>
+      <x:c r="L28" s="63" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="M28" s="63" t="str">
+        <x:v>可选；layer2，禁投影/GI；不得替代猫耳节点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="38" customHeight="1">
+      <x:c r="A29" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B29" s="63" t="str">
+        <x:v>glasses</x:v>
+      </x:c>
+      <x:c r="C29" s="63" t="str">
+        <x:v>VisualRoot/Head/Wearables/Glasses*</x:v>
+      </x:c>
+      <x:c r="D29" s="63" t="str">
+        <x:v>head</x:v>
+      </x:c>
+      <x:c r="E29" s="63" t="str">
+        <x:v>无独立纹理/程序网格</x:v>
+      </x:c>
+      <x:c r="F29" s="63" t="str">
+        <x:v>3种护目件</x:v>
+      </x:c>
+      <x:c r="G29" s="63" t="str">
+        <x:v>沿Head前侧</x:v>
+      </x:c>
+      <x:c r="H29" s="63" t="str">
+        <x:v>继承Head</x:v>
+      </x:c>
+      <x:c r="I29" s="63" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J29" s="63" t="str">
+        <x:v>头部滞后/受击/死亡</x:v>
+      </x:c>
+      <x:c r="K29" s="63" t="str">
+        <x:v>护目件</x:v>
+      </x:c>
+      <x:c r="L29" s="63" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="M29" s="63" t="str">
+        <x:v>可选；layer2，禁投影/GI；不得替代双眼节点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="38" customHeight="1">
+      <x:c r="A30" s="63" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B30" s="63" t="str">
+        <x:v>scarf_legacy</x:v>
+      </x:c>
+      <x:c r="C30" s="63" t="str">
+        <x:v>VisualRoot/Scarf</x:v>
+      </x:c>
+      <x:c r="D30" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E30" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="F30" s="63" t="str">
+        <x:v>隐藏兼容节点</x:v>
+      </x:c>
+      <x:c r="G30" s="63" t="str">
+        <x:v>(0,1.32,0)</x:v>
+      </x:c>
+      <x:c r="H30" s="63" t="str">
+        <x:v>随root</x:v>
+      </x:c>
+      <x:c r="I30" s="63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J30" s="63" t="str">
+        <x:v>不参与当前轮廓</x:v>
+      </x:c>
+      <x:c r="K30" s="63" t="str">
+        <x:v>旧场景兼容</x:v>
+      </x:c>
+      <x:c r="L30" s="63" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="M30" s="63" t="str">
+        <x:v>默认visible=false；不计入四主模块</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11894,7 +13178,7 @@
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>2D/3D 共用六态 ID 与转换白名单；Low HP / Silenced / Invincible / Reloading 为叠加层。Reloading 读取武器唯一计时，新增动画前先查本表</x:v>
+        <x:v>2D/3D 共用六态 ID 与转换白名单；Low HP / Silenced / Invincible / Reloading / Firing / Charging / Knockback 为叠加层。武器与命中是唯一动作来源，新增动画前先查本表</x:v>
       </x:c>
       <x:c r="B3" s="6"/>
       <x:c r="C3" s="6"/>
@@ -12077,25 +13361,25 @@
         <x:v>idle,moving,locked,dead</x:v>
       </x:c>
       <x:c r="F9" s="37" t="str">
-        <x:v>冲击压缩</x:v>
+        <x:v>冲击压缩 + 击退弹性</x:v>
       </x:c>
       <x:c r="G9" s="37" t="str">
-        <x:v>后仰</x:v>
+        <x:v>后仰 + 回弹</x:v>
       </x:c>
       <x:c r="H9" s="37" t="str">
         <x:v>不显示</x:v>
       </x:c>
       <x:c r="I9" s="37" t="str">
-        <x:v>随身体左右镜像</x:v>
+        <x:v>与weapon_socket同相后退/回正</x:v>
       </x:c>
       <x:c r="J9" s="37" t="str">
-        <x:v>抖动</x:v>
+        <x:v>抖动/滞后</x:v>
       </x:c>
       <x:c r="K9" s="37" t="str">
-        <x:v>红闪/屏闪</x:v>
+        <x:v>红闪/击退轨迹</x:v>
       </x:c>
       <x:c r="L9" s="37" t="str">
-        <x:v>2D/3D受击压缩/闪色；握持关系不变</x:v>
+        <x:v>真实命中方向 + 递减XZ冲量；不扩张六态</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -12722,11 +14006,303 @@
         <x:v>终态 + Tween</x:v>
       </x:c>
     </x:row>
+    <x:row r="28" ht="38" customHeight="1">
+      <x:c r="A28" s="81" t="str">
+        <x:v>Player3D 动作覆盖层 × 组件表现（不新增顶层状态）</x:v>
+      </x:c>
+      <x:c r="B28" s="81"/>
+      <x:c r="C28" s="81"/>
+      <x:c r="D28" s="81"/>
+      <x:c r="E28" s="81"/>
+      <x:c r="F28" s="81"/>
+      <x:c r="G28" s="81"/>
+      <x:c r="H28" s="81"/>
+      <x:c r="I28" s="81"/>
+      <x:c r="J28" s="81"/>
+      <x:c r="K28" s="81"/>
+      <x:c r="L28" s="81"/>
+    </x:row>
+    <x:row r="29" ht="38" customHeight="1">
+      <x:c r="A29" s="82" t="str">
+        <x:v>层级｜状态ID｜中文名｜唯一来源｜退出｜Body｜Head｜Hand L（停用）｜Hand（握持）｜Scarf｜VFX/UI｜首版实现</x:v>
+      </x:c>
+      <x:c r="B29" s="82"/>
+      <x:c r="C29" s="82"/>
+      <x:c r="D29" s="82"/>
+      <x:c r="E29" s="82"/>
+      <x:c r="F29" s="82"/>
+      <x:c r="G29" s="82"/>
+      <x:c r="H29" s="82"/>
+      <x:c r="I29" s="82"/>
+      <x:c r="J29" s="82"/>
+      <x:c r="K29" s="82"/>
+      <x:c r="L29" s="82"/>
+    </x:row>
+    <x:row r="30" ht="38" customHeight="1">
+      <x:c r="A30" s="63" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B30" s="63" t="str">
+        <x:v>firing</x:v>
+      </x:c>
+      <x:c r="C30" s="63" t="str">
+        <x:v>射击</x:v>
+      </x:c>
+      <x:c r="D30" s="63" t="str">
+        <x:v>WeaponModel3D.shot_fired</x:v>
+      </x:c>
+      <x:c r="E30" s="63" t="str">
+        <x:v>短时回弹后退出</x:v>
+      </x:c>
+      <x:c r="F30" s="63" t="str">
+        <x:v>前探/压缩/回弹</x:v>
+      </x:c>
+      <x:c r="G30" s="63" t="str">
+        <x:v>小幅前探</x:v>
+      </x:c>
+      <x:c r="H30" s="63" t="str">
+        <x:v>不显示</x:v>
+      </x:c>
+      <x:c r="I30" s="63" t="str">
+        <x:v>与weapon_socket同相后坐</x:v>
+      </x:c>
+      <x:c r="J30" s="63" t="str">
+        <x:v>受冲量轻摆</x:v>
+      </x:c>
+      <x:c r="K30" s="63" t="str">
+        <x:v>枪口闪光/后坐</x:v>
+      </x:c>
+      <x:c r="L30" s="63" t="str">
+        <x:v>真实发射信号；0.14s基础弹性；不独立计时</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="38" customHeight="1">
+      <x:c r="A31" s="63" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B31" s="63" t="str">
+        <x:v>charging</x:v>
+      </x:c>
+      <x:c r="C31" s="63" t="str">
+        <x:v>蓄力</x:v>
+      </x:c>
+      <x:c r="D31" s="63" t="str">
+        <x:v>WeaponModel3D.charge_active / charge_ratio</x:v>
+      </x:c>
+      <x:c r="E31" s="63" t="str">
+        <x:v>释放/取消/换枪/死亡</x:v>
+      </x:c>
+      <x:c r="F31" s="63" t="str">
+        <x:v>下压蓄势</x:v>
+      </x:c>
+      <x:c r="G31" s="63" t="str">
+        <x:v>轻微压低</x:v>
+      </x:c>
+      <x:c r="H31" s="63" t="str">
+        <x:v>不显示</x:v>
+      </x:c>
+      <x:c r="I31" s="63" t="str">
+        <x:v>与weapon_socket同相蓄势</x:v>
+      </x:c>
+      <x:c r="J31" s="63" t="str">
+        <x:v>低频张力摆动</x:v>
+      </x:c>
+      <x:c r="K31" s="63" t="str">
+        <x:v>紫色能量提示（可选）</x:v>
+      </x:c>
+      <x:c r="L31" s="63" t="str">
+        <x:v>读取真实蓄力进度；禁用输入不取消脚本蓄力</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="38" customHeight="1">
+      <x:c r="A32" s="63" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B32" s="63" t="str">
+        <x:v>knockback</x:v>
+      </x:c>
+      <x:c r="C32" s="63" t="str">
+        <x:v>受击击飞</x:v>
+      </x:c>
+      <x:c r="D32" s="63" t="str">
+        <x:v>Player3D 命中方向/强度/时长</x:v>
+      </x:c>
+      <x:c r="E32" s="63" t="str">
+        <x:v>冲量归零或死亡</x:v>
+      </x:c>
+      <x:c r="F32" s="63" t="str">
+        <x:v>反向位移/压缩/弹回</x:v>
+      </x:c>
+      <x:c r="G32" s="63" t="str">
+        <x:v>后仰/回正</x:v>
+      </x:c>
+      <x:c r="H32" s="63" t="str">
+        <x:v>不显示</x:v>
+      </x:c>
+      <x:c r="I32" s="63" t="str">
+        <x:v>与weapon_socket同相后退/回正</x:v>
+      </x:c>
+      <x:c r="J32" s="63" t="str">
+        <x:v>滞后甩动</x:v>
+      </x:c>
+      <x:c r="K32" s="63" t="str">
+        <x:v>红闪/短轨迹</x:v>
+      </x:c>
+      <x:c r="L32" s="63" t="str">
+        <x:v>hurt 消费递减XZ冲量；不新增顶层状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="34" customHeight="1">
+      <x:c r="A34" s="93" t="str">
+        <x:v>Player3D DIY 外观槽 × 动态继承（不影响六态/玩法）</x:v>
+      </x:c>
+      <x:c r="B34" s="93"/>
+      <x:c r="C34" s="93"/>
+      <x:c r="D34" s="93"/>
+      <x:c r="E34" s="93"/>
+      <x:c r="F34" s="93"/>
+      <x:c r="G34" s="93"/>
+      <x:c r="H34" s="93"/>
+      <x:c r="I34" s="93"/>
+      <x:c r="J34" s="93"/>
+      <x:c r="K34" s="93"/>
+      <x:c r="L34" s="93"/>
+    </x:row>
+    <x:row r="35" ht="34" customHeight="1">
+      <x:c r="A35" s="94" t="str">
+        <x:v>槽位｜候选变体｜父组件｜移动｜射击/蓄力｜受击/击飞｜换弹｜死亡｜挂点契约｜验收｜复用范围｜首版实现</x:v>
+      </x:c>
+      <x:c r="B35" s="94"/>
+      <x:c r="C35" s="94"/>
+      <x:c r="D35" s="94"/>
+      <x:c r="E35" s="94"/>
+      <x:c r="F35" s="94"/>
+      <x:c r="G35" s="94"/>
+      <x:c r="H35" s="94"/>
+      <x:c r="I35" s="94"/>
+      <x:c r="J35" s="94"/>
+      <x:c r="K35" s="94"/>
+      <x:c r="L35" s="94"/>
+    </x:row>
+    <x:row r="36" ht="34" customHeight="1">
+      <x:c r="A36" s="63" t="str">
+        <x:v>body/head/hand/feet/hat/glasses</x:v>
+      </x:c>
+      <x:c r="B36" s="63" t="str">
+        <x:v>4+4+4+4+3+3</x:v>
+      </x:c>
+      <x:c r="C36" s="63" t="str">
+        <x:v>Body/Head/Hand/Feet/Wearables</x:v>
+      </x:c>
+      <x:c r="D36" s="63" t="str">
+        <x:v>身体弹性+双脚交替+圆短尾轻摆</x:v>
+      </x:c>
+      <x:c r="E36" s="63" t="str">
+        <x:v>手/枪同相后坐；头前探</x:v>
+      </x:c>
+      <x:c r="F36" s="63" t="str">
+        <x:v>整体后仰/脚随根回正</x:v>
+      </x:c>
+      <x:c r="G36" s="63" t="str">
+        <x:v>Hand+Socket同相</x:v>
+      </x:c>
+      <x:c r="H36" s="63" t="str">
+        <x:v>四主模块随根倾倒</x:v>
+      </x:c>
+      <x:c r="I36" s="63" t="str">
+        <x:v>唯一手/挂点相对向量固定</x:v>
+      </x:c>
+      <x:c r="J36" s="63" t="str">
+        <x:v>四主模块+双眼双耳短尾+六态覆盖</x:v>
+      </x:c>
+      <x:c r="K36" s="63" t="str">
+        <x:v>3D玩家/预览场</x:v>
+      </x:c>
+      <x:c r="L36" s="63" t="str">
+        <x:v>Godot原生方体/三角耳/圆尾；Player3D.set_avatar_customization</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="38" customHeight="1">
+      <x:c r="A38" s="63" t="str">
+        <x:v>PH33 方形猫子组件 × 动作归属（不新增状态）</x:v>
+      </x:c>
+      <x:c r="B38" s="63"/>
+      <x:c r="C38" s="63"/>
+      <x:c r="D38" s="63"/>
+      <x:c r="E38" s="63"/>
+      <x:c r="F38" s="63"/>
+      <x:c r="G38" s="63"/>
+      <x:c r="H38" s="63"/>
+      <x:c r="I38" s="63"/>
+      <x:c r="J38" s="63"/>
+      <x:c r="K38" s="63"/>
+      <x:c r="L38" s="63"/>
+    </x:row>
+    <x:row r="39" ht="38" customHeight="1">
+      <x:c r="A39" s="63" t="str">
+        <x:v>父模块｜子组件｜节点数量｜Idle｜Moving｜Dashing｜Hurt/Knockback｜Reload/Fire｜Dead｜图形语言｜禁止事项｜验收</x:v>
+      </x:c>
+      <x:c r="B39" s="63"/>
+      <x:c r="C39" s="63"/>
+      <x:c r="D39" s="63"/>
+      <x:c r="E39" s="63"/>
+      <x:c r="F39" s="63"/>
+      <x:c r="G39" s="63"/>
+      <x:c r="H39" s="63"/>
+      <x:c r="I39" s="63"/>
+      <x:c r="J39" s="63"/>
+      <x:c r="K39" s="63"/>
+      <x:c r="L39" s="63"/>
+    </x:row>
+    <x:row r="40" ht="38" customHeight="1">
+      <x:c r="A40" s="63" t="str">
+        <x:v>Head / Body / Feet</x:v>
+      </x:c>
+      <x:c r="B40" s="63" t="str">
+        <x:v>Eyes / Ears / TailStub / FootL / FootR</x:v>
+      </x:c>
+      <x:c r="C40" s="63" t="str">
+        <x:v>2 / 2 / 1 / 2</x:v>
+      </x:c>
+      <x:c r="D40" s="63" t="str">
+        <x:v>双眼双耳稳定；短尾微摆</x:v>
+      </x:c>
+      <x:c r="E40" s="63" t="str">
+        <x:v>双脚交替抬起；短尾轻摆</x:v>
+      </x:c>
+      <x:c r="F40" s="63" t="str">
+        <x:v>随VisualRoot压缩</x:v>
+      </x:c>
+      <x:c r="G40" s="63" t="str">
+        <x:v>随父模块后仰回正</x:v>
+      </x:c>
+      <x:c r="H40" s="63" t="str">
+        <x:v>手/枪动作不牵动脚；头部继承</x:v>
+      </x:c>
+      <x:c r="I40" s="63" t="str">
+        <x:v>随父模块倾倒</x:v>
+      </x:c>
+      <x:c r="J40" s="63" t="str">
+        <x:v>方头方身方手方脚；圆尾唯一例外</x:v>
+      </x:c>
+      <x:c r="K40" s="63" t="str">
+        <x:v>嘴/鼻/第二手/长尾/烘焙跨模块</x:v>
+      </x:c>
+      <x:c r="L40" s="63" t="str">
+        <x:v>节点路径+数量+步态+持枪+视觉</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:L2"/>
     <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A16:L16"/>
+    <x:mergeCell ref="A28:L28"/>
+    <x:mergeCell ref="A29:L29"/>
+    <x:mergeCell ref="A34:L34"/>
+    <x:mergeCell ref="A35:L35"/>
+    <x:mergeCell ref="A38:L38"/>
+    <x:mergeCell ref="A39:L39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -13661,6 +15237,78 @@
       <x:c r="M24" s="73"/>
       <x:c r="N24" s="73"/>
     </x:row>
+    <x:row r="25" ht="30" customHeight="1">
+      <x:c r="A25" s="63" t="str">
+        <x:v>独立3D验收场：scenes/Player3DStateGallery.tscn ｜ 真正驱动 Player3D 六态、WeaponModel3D 换弹覆盖、Enemy3D/Boss 九态与 ThemedNPC3D；验证：verify_player3d_state_gallery_flow.tscn / verify_player3d_state_gallery_visual.tscn PASS</x:v>
+      </x:c>
+      <x:c r="B25" s="63"/>
+      <x:c r="C25" s="63"/>
+      <x:c r="D25" s="63"/>
+      <x:c r="E25" s="63"/>
+      <x:c r="F25" s="63"/>
+      <x:c r="G25" s="63"/>
+      <x:c r="H25" s="63"/>
+      <x:c r="I25" s="63"/>
+      <x:c r="J25" s="63"/>
+      <x:c r="K25" s="63"/>
+      <x:c r="L25" s="63"/>
+      <x:c r="M25" s="63"/>
+      <x:c r="N25" s="63"/>
+    </x:row>
+    <x:row r="26" ht="32" customHeight="1">
+      <x:c r="A26" s="83" t="str">
+        <x:v>动作覆盖层：firing 由 WeaponModel3D.shot_fired 启动；charging 读取真实蓄力；knockback 以命中方向驱动 hurt 冲量与弹性回正；唯一 Hand + weapon_socket 全程同相。验证：verify_player3d_state_gallery_flow.tscn PASS</x:v>
+      </x:c>
+      <x:c r="B26" s="83"/>
+      <x:c r="C26" s="83"/>
+      <x:c r="D26" s="83"/>
+      <x:c r="E26" s="83"/>
+      <x:c r="F26" s="83"/>
+      <x:c r="G26" s="83"/>
+      <x:c r="H26" s="83"/>
+      <x:c r="I26" s="83"/>
+      <x:c r="J26" s="83"/>
+      <x:c r="K26" s="83"/>
+      <x:c r="L26" s="83"/>
+      <x:c r="M26" s="83"/>
+      <x:c r="N26" s="83"/>
+    </x:row>
+    <x:row r="28" ht="34" customHeight="1">
+      <x:c r="A28" s="95" t="str">
+        <x:v>DIY 组件：body/head/hand 三组外观变体 + hat/glasses 独立头部配件；真实入口 Player3D.set_avatar_customization()；握持点内收，移动/射击/击飞中 Hand + weapon_socket 同相。验证：verify_player3d_diy_flow.tscn PASS</x:v>
+      </x:c>
+      <x:c r="B28" s="95"/>
+      <x:c r="C28" s="95"/>
+      <x:c r="D28" s="95"/>
+      <x:c r="E28" s="95"/>
+      <x:c r="F28" s="95"/>
+      <x:c r="G28" s="95"/>
+      <x:c r="H28" s="95"/>
+      <x:c r="I28" s="95"/>
+      <x:c r="J28" s="95"/>
+      <x:c r="K28" s="95"/>
+      <x:c r="L28" s="95"/>
+      <x:c r="M28" s="95"/>
+      <x:c r="N28" s="95"/>
+    </x:row>
+    <x:row r="29" ht="38" customHeight="1">
+      <x:c r="A29" t="str">
+        <x:v>PH33 方形猫：复用CHR-PLY-CAPSULE01-3D；Body/Head/Hand/Feet四主模块；Head含双矩形眼与双三角耳，Body含圆短尾；无嘴、无长尾、无第二手；moving双脚交替，手与weapon_socket全动作同相。</x:v>
+      </x:c>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
+      <x:c r="I29"/>
+      <x:c r="J29"/>
+      <x:c r="K29"/>
+      <x:c r="L29"/>
+      <x:c r="M29"/>
+      <x:c r="N29"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:N2"/>
@@ -13669,6 +15317,10 @@
     <x:mergeCell ref="A21:H21"/>
     <x:mergeCell ref="A23:H23"/>
     <x:mergeCell ref="A24:N24"/>
+    <x:mergeCell ref="A25:N25"/>
+    <x:mergeCell ref="A26:N26"/>
+    <x:mergeCell ref="A28:N28"/>
+    <x:mergeCell ref="A29:N29"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -13994,6 +15646,75 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" ht="52" customHeight="1">
+      <x:c r="A17" s="63" t="str">
+        <x:v>v1.11</x:v>
+      </x:c>
+      <x:c r="B17" s="63" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="C17" s="63" t="str">
+        <x:v>3D动作覆盖层登记</x:v>
+      </x:c>
+      <x:c r="D17" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D / WPN-GUN-KIT-3D</x:v>
+      </x:c>
+      <x:c r="E17" s="63" t="str">
+        <x:v>登记 firing/charging/knockback：真实武器/命中来源、手与weapon_socket同相、击飞基础位移与弹性回正；预览场控件和自动验收补齐</x:v>
+      </x:c>
+      <x:c r="F17" s="63" t="str">
+        <x:v>不新增AssetID或贴图；六态保持互斥，动作以既有组件程序组合</x:v>
+      </x:c>
+      <x:c r="G17" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="50" customHeight="1">
+      <x:c r="A18" s="63" t="str">
+        <x:v>v1.12</x:v>
+      </x:c>
+      <x:c r="B18" s="63" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="C18" s="63" t="str">
+        <x:v>3D角色DIY组件登记</x:v>
+      </x:c>
+      <x:c r="D18" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D 及五个子变体</x:v>
+      </x:c>
+      <x:c r="E18" s="63" t="str">
+        <x:v>登记 body/head/hand/hat/glasses 可装配变体、内收握持点、动态继承和预览/自动验收</x:v>
+      </x:c>
+      <x:c r="F18" s="63" t="str">
+        <x:v>新增子AssetID；不增加角色根，不改玩法或六态</x:v>
+      </x:c>
+      <x:c r="G18" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="52" customHeight="1">
+      <x:c r="A19" s="63" t="str">
+        <x:v>v1.13</x:v>
+      </x:c>
+      <x:c r="B19" s="63" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
+      <x:c r="C19" s="63" t="str">
+        <x:v>方形猫3D角色原型登记</x:v>
+      </x:c>
+      <x:c r="D19" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D及脚/眼/耳/短尾子资产</x:v>
+      </x:c>
+      <x:c r="E19" s="63" t="str">
+        <x:v>复用玩家根；登记Body/Head/Hand/Feet四主模块、双矩形眼、双三角耳、圆短尾、feet DIY及交替脚步</x:v>
+      </x:c>
+      <x:c r="F19" s="63" t="str">
+        <x:v>新增5个子AssetID；旧2D胶囊不变；3D旧Scarf隐藏兼容；玩法、碰撞、六态和灯光契约不变</x:v>
+      </x:c>
+      <x:c r="G19" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G2"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8db6a911985d42be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R35b8b0bedd9b4554"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rc39ac0ba6b8d4f2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Re947ec0d70f2431b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R0d468249c12e48b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R07671a5e19124163"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R7cb7398f221e4b8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rb332978a099b43a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R065eab7c384d4218"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R4c498c89f0c34f43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R19ece0f3781d4444"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R710c77a653d74579"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Ra219fef398b0458d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R6c057252c0b94528"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R6fd384406cd24e14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rff4b4e72d114498c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1220,16 +1220,16 @@
     <x:col min="12" max="12" width="8" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="9" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="48" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="38" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="36" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="34" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="26" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="42" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="12" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="34" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="30" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="12" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="13" hidden="0" customWidth="1"/>
     <x:col min="23" max="23" width="16" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="44" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="52" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="25" customHeight="1">
@@ -1443,7 +1443,7 @@
         <x:v>角色|player|player_capsule01|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S6" s="36" t="str">
-        <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$155,R6)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$162,R6)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T6" s="36" t="str"/>
@@ -1517,7 +1517,7 @@
         <x:v>角色|player_component|player_capsule01|head|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S7" s="37" t="str">
-        <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$155,R7)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$162,R7)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T7" s="37" t="str">
@@ -1593,7 +1593,7 @@
         <x:v>角色|player_component|player_capsule01|body|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S8" s="37" t="str">
-        <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$155,R8)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$162,R8)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T8" s="37" t="str">
@@ -1669,7 +1669,7 @@
         <x:v>角色|player_component|player_capsule01|hand_l_source|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S9" s="37" t="str">
-        <x:f>IF(A9="","",IF(COUNTIF($R$6:$R$155,R9)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A9="","",IF(COUNTIF($R$6:$R$162,R9)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T9" s="37" t="str">
@@ -1745,7 +1745,7 @@
         <x:v>角色|player_component|player_capsule01|hand|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S10" s="37" t="str">
-        <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$155,R10)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$162,R10)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T10" s="37" t="str">
@@ -1821,7 +1821,7 @@
         <x:v>角色|player_accessory|player_capsule01|scarf|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S11" s="37" t="str">
-        <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$155,R11)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$162,R11)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T11" s="37" t="str">
@@ -1897,7 +1897,7 @@
         <x:v>角色|review_board|player_capsule01|preview|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S12" s="37" t="str">
-        <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$155,R12)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$162,R12)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T12" s="37" t="str"/>
@@ -1965,7 +1965,7 @@
         <x:v>特效|player_state|player_dash|root|侧面朝右（可水平翻转）|dashing</x:v>
       </x:c>
       <x:c r="S13" s="37" t="str">
-        <x:f>IF(A13="","",IF(COUNTIF($R$6:$R$155,R13)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A13="","",IF(COUNTIF($R$6:$R$162,R13)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T13" s="37" t="str"/>
@@ -2033,7 +2033,7 @@
         <x:v>特效|player_state|player_hurt|root|侧面朝右（可水平翻转）|hurt</x:v>
       </x:c>
       <x:c r="S14" s="37" t="str">
-        <x:f>IF(A14="","",IF(COUNTIF($R$6:$R$155,R14)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A14="","",IF(COUNTIF($R$6:$R$162,R14)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T14" s="37" t="str"/>
@@ -2099,7 +2099,7 @@
         <x:v>特效|player_overlay|player_low_hp|root|侧面朝右（可水平翻转）|low_health</x:v>
       </x:c>
       <x:c r="S15" s="37" t="str">
-        <x:f>IF(A15="","",IF(COUNTIF($R$6:$R$155,R15)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A15="","",IF(COUNTIF($R$6:$R$162,R15)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T15" s="37" t="str"/>
@@ -2165,7 +2165,7 @@
         <x:v>特效|player_overlay|player_silenced|root|侧面朝右（可水平翻转）|silenced</x:v>
       </x:c>
       <x:c r="S16" s="37" t="str">
-        <x:f>IF(A16="","",IF(COUNTIF($R$6:$R$155,R16)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A16="","",IF(COUNTIF($R$6:$R$162,R16)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T16" s="37" t="str"/>
@@ -2233,7 +2233,7 @@
         <x:v>敌人|normal_melee|melee_chaser|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S17" s="37" t="str">
-        <x:f>IF(A17="","",IF(COUNTIF($R$6:$R$155,R17)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A17="","",IF(COUNTIF($R$6:$R$162,R17)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T17" s="37" t="str"/>
@@ -2303,7 +2303,7 @@
         <x:v>敌人|normal_ranged|ranged_caster|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S18" s="37" t="str">
-        <x:f>IF(A18="","",IF(COUNTIF($R$6:$R$155,R18)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A18="","",IF(COUNTIF($R$6:$R$162,R18)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T18" s="37" t="str"/>
@@ -2371,7 +2371,7 @@
         <x:v>敌人|normal_summoner|summoner|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S19" s="37" t="str">
-        <x:f>IF(A19="","",IF(COUNTIF($R$6:$R$155,R19)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A19="","",IF(COUNTIF($R$6:$R$162,R19)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T19" s="37" t="str"/>
@@ -2439,7 +2439,7 @@
         <x:v>敌人|normal_tank|shielded|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S20" s="37" t="str">
-        <x:f>IF(A20="","",IF(COUNTIF($R$6:$R$155,R20)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A20="","",IF(COUNTIF($R$6:$R$162,R20)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T20" s="37" t="str"/>
@@ -2507,7 +2507,7 @@
         <x:v>敌人|normal_bomber|exploder|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S21" s="37" t="str">
-        <x:f>IF(A21="","",IF(COUNTIF($R$6:$R$155,R21)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A21="","",IF(COUNTIF($R$6:$R$162,R21)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T21" s="37" t="str"/>
@@ -2575,7 +2575,7 @@
         <x:v>敌人|normal_ambusher|ambusher|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S22" s="37" t="str">
-        <x:f>IF(A22="","",IF(COUNTIF($R$6:$R$155,R22)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A22="","",IF(COUNTIF($R$6:$R$162,R22)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T22" s="37" t="str"/>
@@ -2643,7 +2643,7 @@
         <x:v>敌人|boss|boss|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S23" s="37" t="str">
-        <x:f>IF(A23="","",IF(COUNTIF($R$6:$R$155,R23)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A23="","",IF(COUNTIF($R$6:$R$162,R23)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T23" s="37" t="str"/>
@@ -2713,7 +2713,7 @@
         <x:v>枪械|gunbody|bp_pistol|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S24" s="37" t="str">
-        <x:f>IF(A24="","",IF(COUNTIF($R$6:$R$155,R24)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A24="","",IF(COUNTIF($R$6:$R$162,R24)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T24" s="37" t="str"/>
@@ -2783,7 +2783,7 @@
         <x:v>枪械|gunbody|bp_shotgun|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S25" s="37" t="str">
-        <x:f>IF(A25="","",IF(COUNTIF($R$6:$R$155,R25)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A25="","",IF(COUNTIF($R$6:$R$162,R25)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T25" s="37" t="str"/>
@@ -2853,7 +2853,7 @@
         <x:v>枪械|gunbody|bp_rifle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S26" s="37" t="str">
-        <x:f>IF(A26="","",IF(COUNTIF($R$6:$R$155,R26)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A26="","",IF(COUNTIF($R$6:$R$162,R26)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T26" s="37" t="str"/>
@@ -2923,7 +2923,7 @@
         <x:v>枪械|gunbody|bp_machinegun|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S27" s="37" t="str">
-        <x:f>IF(A27="","",IF(COUNTIF($R$6:$R$155,R27)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A27="","",IF(COUNTIF($R$6:$R$162,R27)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T27" s="37" t="str"/>
@@ -2993,7 +2993,7 @@
         <x:v>枪械|gunbody|bp_sniper|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S28" s="37" t="str">
-        <x:f>IF(A28="","",IF(COUNTIF($R$6:$R$155,R28)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A28="","",IF(COUNTIF($R$6:$R$162,R28)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T28" s="37" t="str"/>
@@ -3063,7 +3063,7 @@
         <x:v>枪械|gunbody|bp_launcher|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S29" s="37" t="str">
-        <x:f>IF(A29="","",IF(COUNTIF($R$6:$R$155,R29)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A29="","",IF(COUNTIF($R$6:$R$162,R29)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T29" s="37" t="str"/>
@@ -3133,7 +3133,7 @@
         <x:v>枪械|gunbody|bp_charge|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S30" s="37" t="str">
-        <x:f>IF(A30="","",IF(COUNTIF($R$6:$R$155,R30)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A30="","",IF(COUNTIF($R$6:$R$162,R30)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T30" s="37" t="str"/>
@@ -3201,7 +3201,7 @@
         <x:v>枪械|bullet_module|mod_bullet_standard|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S31" s="37" t="str">
-        <x:f>IF(A31="","",IF(COUNTIF($R$6:$R$155,R31)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A31="","",IF(COUNTIF($R$6:$R$162,R31)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T31" s="37" t="str"/>
@@ -3269,7 +3269,7 @@
         <x:v>枪械|bullet_module|mod_bullet_sticky|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S32" s="37" t="str">
-        <x:f>IF(A32="","",IF(COUNTIF($R$6:$R$155,R32)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A32="","",IF(COUNTIF($R$6:$R$162,R32)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T32" s="37" t="str"/>
@@ -3337,7 +3337,7 @@
         <x:v>枪械|bullet_module|mod_bullet_bounce|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S33" s="37" t="str">
-        <x:f>IF(A33="","",IF(COUNTIF($R$6:$R$155,R33)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A33="","",IF(COUNTIF($R$6:$R$162,R33)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T33" s="37" t="str"/>
@@ -3405,7 +3405,7 @@
         <x:v>枪械|bullet_module|mod_bullet_piercing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S34" s="37" t="str">
-        <x:f>IF(A34="","",IF(COUNTIF($R$6:$R$155,R34)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A34="","",IF(COUNTIF($R$6:$R$162,R34)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T34" s="37" t="str"/>
@@ -3473,7 +3473,7 @@
         <x:v>枪械|bullet_module|mod_bullet_explosive|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S35" s="37" t="str">
-        <x:f>IF(A35="","",IF(COUNTIF($R$6:$R$155,R35)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A35="","",IF(COUNTIF($R$6:$R$162,R35)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T35" s="37" t="str"/>
@@ -3541,7 +3541,7 @@
         <x:v>枪械|bullet_module|mod_bullet_homing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S36" s="37" t="str">
-        <x:f>IF(A36="","",IF(COUNTIF($R$6:$R$155,R36)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A36="","",IF(COUNTIF($R$6:$R$162,R36)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T36" s="37" t="str"/>
@@ -3609,7 +3609,7 @@
         <x:v>枪械|bullet_module|mod_bullet_blackhole|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S37" s="37" t="str">
-        <x:f>IF(A37="","",IF(COUNTIF($R$6:$R$155,R37)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A37="","",IF(COUNTIF($R$6:$R$162,R37)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T37" s="37" t="str"/>
@@ -3677,7 +3677,7 @@
         <x:v>枪械|bullet_module|mod_bullet_balloon|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S38" s="37" t="str">
-        <x:f>IF(A38="","",IF(COUNTIF($R$6:$R$155,R38)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A38="","",IF(COUNTIF($R$6:$R$162,R38)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T38" s="37" t="str"/>
@@ -3745,7 +3745,7 @@
         <x:v>枪械|attachment|attach_triple_muzzle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S39" s="37" t="str">
-        <x:f>IF(A39="","",IF(COUNTIF($R$6:$R$155,R39)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A39="","",IF(COUNTIF($R$6:$R$162,R39)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T39" s="37" t="str"/>
@@ -3813,7 +3813,7 @@
         <x:v>枪械|attachment|attach_rubber_stock|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S40" s="37" t="str">
-        <x:f>IF(A40="","",IF(COUNTIF($R$6:$R$155,R40)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A40="","",IF(COUNTIF($R$6:$R$162,R40)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T40" s="37" t="str"/>
@@ -3881,7 +3881,7 @@
         <x:v>枪械|attachment|attach_scope|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S41" s="37" t="str">
-        <x:f>IF(A41="","",IF(COUNTIF($R$6:$R$155,R41)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A41="","",IF(COUNTIF($R$6:$R$162,R41)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T41" s="37" t="str"/>
@@ -3949,7 +3949,7 @@
         <x:v>枪械|attachment|attach_big_mag|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S42" s="37" t="str">
-        <x:f>IF(A42="","",IF(COUNTIF($R$6:$R$155,R42)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A42="","",IF(COUNTIF($R$6:$R$162,R42)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T42" s="37" t="str"/>
@@ -4017,7 +4017,7 @@
         <x:v>枪械|attachment|attach_fan|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S43" s="37" t="str">
-        <x:f>IF(A43="","",IF(COUNTIF($R$6:$R$155,R43)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A43="","",IF(COUNTIF($R$6:$R$162,R43)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T43" s="37" t="str"/>
@@ -4085,7 +4085,7 @@
         <x:v>枪械|attachment|attach_copy_sticker|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S44" s="37" t="str">
-        <x:f>IF(A44="","",IF(COUNTIF($R$6:$R$155,R44)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A44="","",IF(COUNTIF($R$6:$R$162,R44)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T44" s="37" t="str"/>
@@ -4153,7 +4153,7 @@
         <x:v>道具|consumable|item_beacon|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S45" s="37" t="str">
-        <x:f>IF(A45="","",IF(COUNTIF($R$6:$R$155,R45)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A45="","",IF(COUNTIF($R$6:$R$162,R45)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T45" s="37" t="str"/>
@@ -4219,7 +4219,7 @@
         <x:v>道具|key|item_room_key|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S46" s="37" t="str">
-        <x:f>IF(A46="","",IF(COUNTIF($R$6:$R$155,R46)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A46="","",IF(COUNTIF($R$6:$R$162,R46)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T46" s="37" t="str"/>
@@ -4285,7 +4285,7 @@
         <x:v>道具|pickup|soul_orb|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S47" s="37" t="str">
-        <x:f>IF(A47="","",IF(COUNTIF($R$6:$R$155,R47)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A47="","",IF(COUNTIF($R$6:$R$162,R47)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T47" s="37" t="str"/>
@@ -4351,7 +4351,7 @@
         <x:v>道具|container|container|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S48" s="37" t="str">
-        <x:f>IF(A48="","",IF(COUNTIF($R$6:$R$155,R48)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A48="","",IF(COUNTIF($R$6:$R$162,R48)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T48" s="37" t="str"/>
@@ -4417,7 +4417,7 @@
         <x:v>道具|pickup|room_key_pickup|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S49" s="37" t="str">
-        <x:f>IF(A49="","",IF(COUNTIF($R$6:$R$155,R49)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A49="","",IF(COUNTIF($R$6:$R$162,R49)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T49" s="37" t="str"/>
@@ -4485,7 +4485,7 @@
         <x:v>道具|pickup_base|ground_item|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S50" s="37" t="str">
-        <x:f>IF(A50="","",IF(COUNTIF($R$6:$R$155,R50)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A50="","",IF(COUNTIF($R$6:$R$162,R50)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T50" s="37" t="str"/>
@@ -4553,7 +4553,7 @@
         <x:v>场景|biome_kit|base_world|root|顶视|default</x:v>
       </x:c>
       <x:c r="S51" s="37" t="str">
-        <x:f>IF(A51="","",IF(COUNTIF($R$6:$R$155,R51)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A51="","",IF(COUNTIF($R$6:$R$162,R51)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T51" s="37" t="str"/>
@@ -4621,7 +4621,7 @@
         <x:v>场景|biome_kit|iron_frontier|root|顶视|default</x:v>
       </x:c>
       <x:c r="S52" s="37" t="str">
-        <x:f>IF(A52="","",IF(COUNTIF($R$6:$R$155,R52)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A52="","",IF(COUNTIF($R$6:$R$162,R52)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T52" s="37" t="str"/>
@@ -4689,7 +4689,7 @@
         <x:v>场景|biome_kit|rust_foundry|root|顶视|default</x:v>
       </x:c>
       <x:c r="S53" s="37" t="str">
-        <x:f>IF(A53="","",IF(COUNTIF($R$6:$R$155,R53)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A53="","",IF(COUNTIF($R$6:$R$162,R53)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T53" s="37" t="str"/>
@@ -4757,7 +4757,7 @@
         <x:v>场景|biome_kit|spore_depths|root|顶视|default</x:v>
       </x:c>
       <x:c r="S54" s="37" t="str">
-        <x:f>IF(A54="","",IF(COUNTIF($R$6:$R$155,R54)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A54="","",IF(COUNTIF($R$6:$R$162,R54)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T54" s="37" t="str"/>
@@ -4825,7 +4825,7 @@
         <x:v>场景|biome_kit|abyss_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S55" s="37" t="str">
-        <x:f>IF(A55="","",IF(COUNTIF($R$6:$R$155,R55)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A55="","",IF(COUNTIF($R$6:$R$162,R55)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T55" s="37" t="str"/>
@@ -4893,7 +4893,7 @@
         <x:v>场景|biome_kit|training_range|root|顶视|default</x:v>
       </x:c>
       <x:c r="S56" s="37" t="str">
-        <x:f>IF(A56="","",IF(COUNTIF($R$6:$R$155,R56)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A56="","",IF(COUNTIF($R$6:$R$162,R56)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T56" s="37" t="str"/>
@@ -4961,7 +4961,7 @@
         <x:v>场景|room_dressing|room_combat|root|顶视|default</x:v>
       </x:c>
       <x:c r="S57" s="37" t="str">
-        <x:f>IF(A57="","",IF(COUNTIF($R$6:$R$155,R57)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A57="","",IF(COUNTIF($R$6:$R$162,R57)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T57" s="37" t="str"/>
@@ -5029,7 +5029,7 @@
         <x:v>场景|room_dressing|room_elite|root|顶视|default</x:v>
       </x:c>
       <x:c r="S58" s="37" t="str">
-        <x:f>IF(A58="","",IF(COUNTIF($R$6:$R$155,R58)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A58="","",IF(COUNTIF($R$6:$R$162,R58)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T58" s="37" t="str"/>
@@ -5097,7 +5097,7 @@
         <x:v>场景|room_dressing|room_boss|root|顶视|default</x:v>
       </x:c>
       <x:c r="S59" s="37" t="str">
-        <x:f>IF(A59="","",IF(COUNTIF($R$6:$R$155,R59)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A59="","",IF(COUNTIF($R$6:$R$162,R59)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T59" s="37" t="str"/>
@@ -5165,7 +5165,7 @@
         <x:v>场景|room_dressing|room_event|root|顶视|default</x:v>
       </x:c>
       <x:c r="S60" s="37" t="str">
-        <x:f>IF(A60="","",IF(COUNTIF($R$6:$R$155,R60)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A60="","",IF(COUNTIF($R$6:$R$162,R60)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T60" s="37" t="str"/>
@@ -5233,7 +5233,7 @@
         <x:v>场景|room_dressing|room_extraction|root|顶视|default</x:v>
       </x:c>
       <x:c r="S61" s="37" t="str">
-        <x:f>IF(A61="","",IF(COUNTIF($R$6:$R$155,R61)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A61="","",IF(COUNTIF($R$6:$R$162,R61)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T61" s="37" t="str"/>
@@ -5301,7 +5301,7 @@
         <x:v>场景|room_dressing|room_merchant|root|顶视|default</x:v>
       </x:c>
       <x:c r="S62" s="37" t="str">
-        <x:f>IF(A62="","",IF(COUNTIF($R$6:$R$155,R62)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A62="","",IF(COUNTIF($R$6:$R$162,R62)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T62" s="37" t="str"/>
@@ -5369,7 +5369,7 @@
         <x:v>场景|room_dressing|room_scavenge|root|顶视|default</x:v>
       </x:c>
       <x:c r="S63" s="37" t="str">
-        <x:f>IF(A63="","",IF(COUNTIF($R$6:$R$155,R63)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A63="","",IF(COUNTIF($R$6:$R$162,R63)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T63" s="37" t="str"/>
@@ -5437,7 +5437,7 @@
         <x:v>场景|room_dressing|room_storage|root|顶视|default</x:v>
       </x:c>
       <x:c r="S64" s="37" t="str">
-        <x:f>IF(A64="","",IF(COUNTIF($R$6:$R$155,R64)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A64="","",IF(COUNTIF($R$6:$R$162,R64)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T64" s="37" t="str"/>
@@ -5505,7 +5505,7 @@
         <x:v>场景|room_dressing|room_trap|root|顶视|default</x:v>
       </x:c>
       <x:c r="S65" s="37" t="str">
-        <x:f>IF(A65="","",IF(COUNTIF($R$6:$R$155,R65)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A65="","",IF(COUNTIF($R$6:$R$162,R65)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T65" s="37" t="str"/>
@@ -5573,7 +5573,7 @@
         <x:v>场景|room_dressing|room_upgrade|root|顶视|default</x:v>
       </x:c>
       <x:c r="S66" s="37" t="str">
-        <x:f>IF(A66="","",IF(COUNTIF($R$6:$R$155,R66)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A66="","",IF(COUNTIF($R$6:$R$162,R66)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T66" s="37" t="str"/>
@@ -5641,7 +5641,7 @@
         <x:v>场景|room_dressing|room_spawn|root|顶视|default</x:v>
       </x:c>
       <x:c r="S67" s="37" t="str">
-        <x:f>IF(A67="","",IF(COUNTIF($R$6:$R$155,R67)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A67="","",IF(COUNTIF($R$6:$R$162,R67)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T67" s="37" t="str"/>
@@ -5709,7 +5709,7 @@
         <x:v>场景|room_dressing|room_stairs|root|顶视|default</x:v>
       </x:c>
       <x:c r="S68" s="37" t="str">
-        <x:f>IF(A68="","",IF(COUNTIF($R$6:$R$155,R68)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A68="","",IF(COUNTIF($R$6:$R$162,R68)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T68" s="37" t="str"/>
@@ -5777,7 +5777,7 @@
         <x:v>场景道具|facility|base_briefing|root|顶视|default</x:v>
       </x:c>
       <x:c r="S69" s="37" t="str">
-        <x:f>IF(A69="","",IF(COUNTIF($R$6:$R$155,R69)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A69="","",IF(COUNTIF($R$6:$R$162,R69)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T69" s="37" t="str"/>
@@ -5845,7 +5845,7 @@
         <x:v>场景道具|facility|base_workshop|root|顶视|default</x:v>
       </x:c>
       <x:c r="S70" s="37" t="str">
-        <x:f>IF(A70="","",IF(COUNTIF($R$6:$R$155,R70)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A70="","",IF(COUNTIF($R$6:$R$162,R70)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T70" s="37" t="str"/>
@@ -5913,7 +5913,7 @@
         <x:v>场景道具|facility|base_divination|root|顶视|default</x:v>
       </x:c>
       <x:c r="S71" s="37" t="str">
-        <x:f>IF(A71="","",IF(COUNTIF($R$6:$R$155,R71)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A71="","",IF(COUNTIF($R$6:$R$162,R71)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T71" s="37" t="str"/>
@@ -5981,7 +5981,7 @@
         <x:v>场景道具|facility|base_vault|root|顶视|default</x:v>
       </x:c>
       <x:c r="S72" s="37" t="str">
-        <x:f>IF(A72="","",IF(COUNTIF($R$6:$R$155,R72)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A72="","",IF(COUNTIF($R$6:$R$162,R72)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T72" s="37" t="str"/>
@@ -6049,7 +6049,7 @@
         <x:v>场景道具|facility|base_monster_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S73" s="37" t="str">
-        <x:f>IF(A73="","",IF(COUNTIF($R$6:$R$155,R73)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A73="","",IF(COUNTIF($R$6:$R$162,R73)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T73" s="37" t="str"/>
@@ -6117,7 +6117,7 @@
         <x:v>场景道具|facility|base_card_collection|root|顶视|default</x:v>
       </x:c>
       <x:c r="S74" s="37" t="str">
-        <x:f>IF(A74="","",IF(COUNTIF($R$6:$R$155,R74)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A74="","",IF(COUNTIF($R$6:$R$162,R74)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T74" s="37" t="str"/>
@@ -6185,7 +6185,7 @@
         <x:v>场景道具|facility|base_terminal|root|顶视|default</x:v>
       </x:c>
       <x:c r="S75" s="37" t="str">
-        <x:f>IF(A75="","",IF(COUNTIF($R$6:$R$155,R75)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A75="","",IF(COUNTIF($R$6:$R$162,R75)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T75" s="37" t="str"/>
@@ -6253,7 +6253,7 @@
         <x:v>场景道具|facility|dungeon_gate|root|顶视|default</x:v>
       </x:c>
       <x:c r="S76" s="37" t="str">
-        <x:f>IF(A76="","",IF(COUNTIF($R$6:$R$155,R76)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A76="","",IF(COUNTIF($R$6:$R$162,R76)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T76" s="37" t="str"/>
@@ -6321,7 +6321,7 @@
         <x:v>场景道具|facility|workbench|root|顶视|default</x:v>
       </x:c>
       <x:c r="S77" s="37" t="str">
-        <x:f>IF(A77="","",IF(COUNTIF($R$6:$R$155,R77)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A77="","",IF(COUNTIF($R$6:$R$162,R77)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T77" s="37" t="str"/>
@@ -6389,7 +6389,7 @@
         <x:v>场景道具|facility|door|root|顶视|default</x:v>
       </x:c>
       <x:c r="S78" s="37" t="str">
-        <x:f>IF(A78="","",IF(COUNTIF($R$6:$R$155,R78)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A78="","",IF(COUNTIF($R$6:$R$162,R78)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T78" s="37" t="str"/>
@@ -6457,7 +6457,7 @@
         <x:v>ui|screen|hud|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S79" s="37" t="str">
-        <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$155,R79)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$162,R79)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T79" s="37" t="str"/>
@@ -6525,7 +6525,7 @@
         <x:v>ui|screen|inventory|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S80" s="37" t="str">
-        <x:f>IF(A80="","",IF(COUNTIF($R$6:$R$155,R80)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A80="","",IF(COUNTIF($R$6:$R$162,R80)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T80" s="37" t="str"/>
@@ -6593,7 +6593,7 @@
         <x:v>ui|screen|merchant|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S81" s="37" t="str">
-        <x:f>IF(A81="","",IF(COUNTIF($R$6:$R$155,R81)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A81="","",IF(COUNTIF($R$6:$R$162,R81)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T81" s="37" t="str"/>
@@ -6661,7 +6661,7 @@
         <x:v>ui|screen|workshop|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S82" s="37" t="str">
-        <x:f>IF(A82="","",IF(COUNTIF($R$6:$R$155,R82)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A82="","",IF(COUNTIF($R$6:$R$162,R82)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T82" s="37" t="str"/>
@@ -6729,7 +6729,7 @@
         <x:v>ui|screen|workbench|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S83" s="37" t="str">
-        <x:f>IF(A83="","",IF(COUNTIF($R$6:$R$155,R83)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A83="","",IF(COUNTIF($R$6:$R$162,R83)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T83" s="37" t="str"/>
@@ -6797,7 +6797,7 @@
         <x:v>ui|screen|weapon_tree|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S84" s="37" t="str">
-        <x:f>IF(A84="","",IF(COUNTIF($R$6:$R$155,R84)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A84="","",IF(COUNTIF($R$6:$R$162,R84)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T84" s="37" t="str"/>
@@ -6865,7 +6865,7 @@
         <x:v>ui|screen|fate_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S85" s="37" t="str">
-        <x:f>IF(A85="","",IF(COUNTIF($R$6:$R$155,R85)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A85="","",IF(COUNTIF($R$6:$R$162,R85)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T85" s="37" t="str"/>
@@ -6933,7 +6933,7 @@
         <x:v>ui|screen|fate_collection|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S86" s="37" t="str">
-        <x:f>IF(A86="","",IF(COUNTIF($R$6:$R$155,R86)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A86="","",IF(COUNTIF($R$6:$R$162,R86)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T86" s="37" t="str"/>
@@ -7001,7 +7001,7 @@
         <x:v>ui|screen|level_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S87" s="37" t="str">
-        <x:f>IF(A87="","",IF(COUNTIF($R$6:$R$155,R87)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A87="","",IF(COUNTIF($R$6:$R$162,R87)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T87" s="37" t="str"/>
@@ -7069,7 +7069,7 @@
         <x:v>ui|screen|vault|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S88" s="37" t="str">
-        <x:f>IF(A88="","",IF(COUNTIF($R$6:$R$155,R88)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A88="","",IF(COUNTIF($R$6:$R$162,R88)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T88" s="37" t="str"/>
@@ -7137,7 +7137,7 @@
         <x:v>ui|screen|monster_archive|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S89" s="37" t="str">
-        <x:f>IF(A89="","",IF(COUNTIF($R$6:$R$155,R89)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A89="","",IF(COUNTIF($R$6:$R$162,R89)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T89" s="37" t="str"/>
@@ -7205,7 +7205,7 @@
         <x:v>ui|screen|base_menu|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S90" s="37" t="str">
-        <x:f>IF(A90="","",IF(COUNTIF($R$6:$R$155,R90)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A90="","",IF(COUNTIF($R$6:$R$162,R90)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T90" s="37" t="str"/>
@@ -7273,7 +7273,7 @@
         <x:v>ui|screen|mobile_controls|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S91" s="37" t="str">
-        <x:f>IF(A91="","",IF(COUNTIF($R$6:$R$155,R91)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A91="","",IF(COUNTIF($R$6:$R$162,R91)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T91" s="37" t="str"/>
@@ -7341,7 +7341,7 @@
         <x:v>特效|gameplay_vfx|explosion|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S92" s="37" t="str">
-        <x:f>IF(A92="","",IF(COUNTIF($R$6:$R$155,R92)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A92="","",IF(COUNTIF($R$6:$R$162,R92)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T92" s="37" t="str"/>
@@ -7409,7 +7409,7 @@
         <x:v>特效|gameplay_vfx|muzzle_flash|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S93" s="37" t="str">
-        <x:f>IF(A93="","",IF(COUNTIF($R$6:$R$155,R93)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A93="","",IF(COUNTIF($R$6:$R$162,R93)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T93" s="37" t="str"/>
@@ -7477,7 +7477,7 @@
         <x:v>特效|gameplay_vfx|damage_number|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S94" s="37" t="str">
-        <x:f>IF(A94="","",IF(COUNTIF($R$6:$R$155,R94)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A94="","",IF(COUNTIF($R$6:$R$162,R94)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T94" s="37" t="str"/>
@@ -7545,7 +7545,7 @@
         <x:v>特效|gameplay_vfx|spark|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S95" s="37" t="str">
-        <x:f>IF(A95="","",IF(COUNTIF($R$6:$R$155,R95)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A95="","",IF(COUNTIF($R$6:$R$162,R95)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T95" s="37" t="str"/>
@@ -7613,7 +7613,7 @@
         <x:v>特效|gameplay_vfx|room_transition|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S96" s="37" t="str">
-        <x:f>IF(A96="","",IF(COUNTIF($R$6:$R$155,R96)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A96="","",IF(COUNTIF($R$6:$R$162,R96)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T96" s="37" t="str"/>
@@ -7683,7 +7683,7 @@
         <x:v>特效|gameplay_vfx|health_vignette|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S97" s="37" t="str">
-        <x:f>IF(A97="","",IF(COUNTIF($R$6:$R$155,R97)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A97="","",IF(COUNTIF($R$6:$R$162,R97)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T97" s="37" t="str"/>
@@ -7751,7 +7751,7 @@
         <x:v>特效|gameplay_vfx|visibility_light|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S98" s="37" t="str">
-        <x:f>IF(A98="","",IF(COUNTIF($R$6:$R$155,R98)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A98="","",IF(COUNTIF($R$6:$R$162,R98)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T98" s="37" t="str"/>
@@ -7819,7 +7819,7 @@
         <x:v>特效|gameplay_vfx|extraction_beacon|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S99" s="37" t="str">
-        <x:f>IF(A99="","",IF(COUNTIF($R$6:$R$155,R99)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A99="","",IF(COUNTIF($R$6:$R$162,R99)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T99" s="37" t="str"/>
@@ -7887,7 +7887,7 @@
         <x:v>音频|bgm|bgm_wasteland|root|不适用|default</x:v>
       </x:c>
       <x:c r="S100" s="37" t="str">
-        <x:f>IF(A100="","",IF(COUNTIF($R$6:$R$155,R100)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A100="","",IF(COUNTIF($R$6:$R$162,R100)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T100" s="37" t="str"/>
@@ -7953,7 +7953,7 @@
         <x:v>音频|sfx|pistol_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S101" s="37" t="str">
-        <x:f>IF(A101="","",IF(COUNTIF($R$6:$R$155,R101)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A101="","",IF(COUNTIF($R$6:$R$162,R101)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T101" s="37" t="str"/>
@@ -8019,7 +8019,7 @@
         <x:v>音频|sfx|rifle_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S102" s="37" t="str">
-        <x:f>IF(A102="","",IF(COUNTIF($R$6:$R$155,R102)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A102="","",IF(COUNTIF($R$6:$R$162,R102)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T102" s="37" t="str"/>
@@ -8085,7 +8085,7 @@
         <x:v>音频|sfx|shotgun_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S103" s="37" t="str">
-        <x:f>IF(A103="","",IF(COUNTIF($R$6:$R$155,R103)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A103="","",IF(COUNTIF($R$6:$R$162,R103)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T103" s="37" t="str"/>
@@ -8151,7 +8151,7 @@
         <x:v>音频|sfx|smg_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S104" s="37" t="str">
-        <x:f>IF(A104="","",IF(COUNTIF($R$6:$R$155,R104)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A104="","",IF(COUNTIF($R$6:$R$162,R104)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T104" s="37" t="str"/>
@@ -8217,7 +8217,7 @@
         <x:v>音频|sfx|sniper_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S105" s="37" t="str">
-        <x:f>IF(A105="","",IF(COUNTIF($R$6:$R$155,R105)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A105="","",IF(COUNTIF($R$6:$R$162,R105)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T105" s="37" t="str"/>
@@ -8283,7 +8283,7 @@
         <x:v>音频|sfx|player_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S106" s="37" t="str">
-        <x:f>IF(A106="","",IF(COUNTIF($R$6:$R$155,R106)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A106="","",IF(COUNTIF($R$6:$R$162,R106)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T106" s="37" t="str"/>
@@ -8349,7 +8349,7 @@
         <x:v>音频|sfx|player_dash|root|不适用|default</x:v>
       </x:c>
       <x:c r="S107" s="37" t="str">
-        <x:f>IF(A107="","",IF(COUNTIF($R$6:$R$155,R107)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A107="","",IF(COUNTIF($R$6:$R$162,R107)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T107" s="37" t="str"/>
@@ -8415,7 +8415,7 @@
         <x:v>音频|sfx|enemy_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S108" s="37" t="str">
-        <x:f>IF(A108="","",IF(COUNTIF($R$6:$R$155,R108)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A108="","",IF(COUNTIF($R$6:$R$162,R108)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T108" s="37" t="str"/>
@@ -8481,7 +8481,7 @@
         <x:v>音频|sfx|enemy_die|root|不适用|default</x:v>
       </x:c>
       <x:c r="S109" s="37" t="str">
-        <x:f>IF(A109="","",IF(COUNTIF($R$6:$R$155,R109)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A109="","",IF(COUNTIF($R$6:$R$162,R109)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T109" s="37" t="str"/>
@@ -8547,7 +8547,7 @@
         <x:v>音频|sfx|reload|root|不适用|default</x:v>
       </x:c>
       <x:c r="S110" s="37" t="str">
-        <x:f>IF(A110="","",IF(COUNTIF($R$6:$R$155,R110)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A110="","",IF(COUNTIF($R$6:$R$162,R110)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T110" s="37" t="str"/>
@@ -8613,7 +8613,7 @@
         <x:v>音频|sfx|extraction_start|root|不适用|default</x:v>
       </x:c>
       <x:c r="S111" s="37" t="str">
-        <x:f>IF(A111="","",IF(COUNTIF($R$6:$R$155,R111)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A111="","",IF(COUNTIF($R$6:$R$162,R111)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T111" s="37" t="str"/>
@@ -8679,7 +8679,7 @@
         <x:v>音频|sfx|extraction_done|root|不适用|default</x:v>
       </x:c>
       <x:c r="S112" s="37" t="str">
-        <x:f>IF(A112="","",IF(COUNTIF($R$6:$R$155,R112)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A112="","",IF(COUNTIF($R$6:$R$162,R112)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T112" s="37" t="str"/>
@@ -8751,7 +8751,7 @@
         <x:v>角色|player|player_capsule01|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S113" t="str">
-        <x:f>IF(A113="","",IF(COUNTIF($R$6:$R$155,R113)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A113="","",IF(COUNTIF($R$6:$R$162,R113)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T113" t="str">
@@ -8827,7 +8827,7 @@
         <x:v>角色|player|player_capsule01|body_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S114" t="str">
-        <x:f>IF(A114="","",IF(COUNTIF($R$6:$R$155,R114)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A114="","",IF(COUNTIF($R$6:$R$162,R114)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T114" t="str">
@@ -8903,7 +8903,7 @@
         <x:v>角色|player|player_capsule01|head_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S115" t="str">
-        <x:f>IF(A115="","",IF(COUNTIF($R$6:$R$155,R115)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A115="","",IF(COUNTIF($R$6:$R$162,R115)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T115" t="str">
@@ -8979,7 +8979,7 @@
         <x:v>角色|player|player_capsule01|hand_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S116" t="str">
-        <x:f>IF(A116="","",IF(COUNTIF($R$6:$R$155,R116)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A116="","",IF(COUNTIF($R$6:$R$162,R116)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T116" t="str">
@@ -9055,7 +9055,7 @@
         <x:v>角色|player|player_capsule01|scarf_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S117" t="str">
-        <x:f>IF(A117="","",IF(COUNTIF($R$6:$R$155,R117)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A117="","",IF(COUNTIF($R$6:$R$162,R117)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T117" t="str">
@@ -9131,7 +9131,7 @@
         <x:v>角色|player|player_capsule01|weapon_socket_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S118" t="str">
-        <x:f>IF(A118="","",IF(COUNTIF($R$6:$R$155,R118)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A118="","",IF(COUNTIF($R$6:$R$162,R118)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T118" t="str">
@@ -9207,7 +9207,7 @@
         <x:v>场景|base|base_world|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S119" t="str">
-        <x:f>IF(A119="","",IF(COUNTIF($R$6:$R$155,R119)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A119="","",IF(COUNTIF($R$6:$R$162,R119)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T119" t="str">
@@ -9283,7 +9283,7 @@
         <x:v>场景道具|facility|base_facility_module|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S120" t="str">
-        <x:f>IF(A120="","",IF(COUNTIF($R$6:$R$155,R120)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A120="","",IF(COUNTIF($R$6:$R$162,R120)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T120" t="str">
@@ -9359,7 +9359,7 @@
         <x:v>场景道具|door|dungeon_gate|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S121" t="str">
-        <x:f>IF(A121="","",IF(COUNTIF($R$6:$R$155,R121)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A121="","",IF(COUNTIF($R$6:$R$162,R121)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T121" t="str">
@@ -9435,7 +9435,7 @@
         <x:v>场景|review_board|base_world|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S122" t="str">
-        <x:f>IF(A122="","",IF(COUNTIF($R$6:$R$155,R122)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A122="","",IF(COUNTIF($R$6:$R$162,R122)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T122" t="str">
@@ -9509,7 +9509,7 @@
         <x:v>场景|room|dungeon_runtime|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S123" s="63" t="str">
-        <x:f>IF(A123="","",IF(COUNTIF($R$6:$R$155,R123)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A123="","",IF(COUNTIF($R$6:$R$162,R123)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T123" s="63" t="str">
@@ -9585,7 +9585,7 @@
         <x:v>场景|biome|iron_frontier|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S124" s="63" t="str">
-        <x:f>IF(A124="","",IF(COUNTIF($R$6:$R$155,R124)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A124="","",IF(COUNTIF($R$6:$R$162,R124)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T124" s="63" t="str">
@@ -9661,7 +9661,7 @@
         <x:v>场景|biome|rust_foundry|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S125" s="63" t="str">
-        <x:f>IF(A125="","",IF(COUNTIF($R$6:$R$155,R125)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A125="","",IF(COUNTIF($R$6:$R$162,R125)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T125" s="63" t="str">
@@ -9737,7 +9737,7 @@
         <x:v>场景|biome|spore_depths|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S126" s="63" t="str">
-        <x:f>IF(A126="","",IF(COUNTIF($R$6:$R$155,R126)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A126="","",IF(COUNTIF($R$6:$R$162,R126)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T126" s="63" t="str">
@@ -9813,7 +9813,7 @@
         <x:v>场景|biome|abyss_archive|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S127" s="63" t="str">
-        <x:f>IF(A127="","",IF(COUNTIF($R$6:$R$155,R127)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A127="","",IF(COUNTIF($R$6:$R$162,R127)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T127" s="63" t="str">
@@ -9889,7 +9889,7 @@
         <x:v>场景道具|light|wasteland_light|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S128" s="63" t="str">
-        <x:f>IF(A128="","",IF(COUNTIF($R$6:$R$155,R128)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A128="","",IF(COUNTIF($R$6:$R$162,R128)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T128" s="63" t="str">
@@ -9965,7 +9965,7 @@
         <x:v>场景道具|furniture|room_furniture|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S129" s="63" t="str">
-        <x:f>IF(A129="","",IF(COUNTIF($R$6:$R$155,R129)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A129="","",IF(COUNTIF($R$6:$R$162,R129)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T129" s="63" t="str">
@@ -10041,7 +10041,7 @@
         <x:v>场景道具|container|search_container|root_3d|俯视3d|closed_opened</x:v>
       </x:c>
       <x:c r="S130" s="63" t="str">
-        <x:f>IF(A130="","",IF(COUNTIF($R$6:$R$155,R130)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A130="","",IF(COUNTIF($R$6:$R$162,R130)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T130" s="63" t="str">
@@ -10117,7 +10117,7 @@
         <x:v>场景道具|facility|service_station|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S131" s="63" t="str">
-        <x:f>IF(A131="","",IF(COUNTIF($R$6:$R$155,R131)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A131="","",IF(COUNTIF($R$6:$R$162,R131)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T131" s="63" t="str">
@@ -10193,7 +10193,7 @@
         <x:v>场景道具|facility|extraction_beacon|root_3d|俯视3d|locked_active_done</x:v>
       </x:c>
       <x:c r="S132" s="63" t="str">
-        <x:f>IF(A132="","",IF(COUNTIF($R$6:$R$155,R132)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A132="","",IF(COUNTIF($R$6:$R$162,R132)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T132" s="63" t="str">
@@ -10269,7 +10269,7 @@
         <x:v>特效|environment|hazard_field|root_3d|俯视3d|active</x:v>
       </x:c>
       <x:c r="S133" s="63" t="str">
-        <x:f>IF(A133="","",IF(COUNTIF($R$6:$R$155,R133)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A133="","",IF(COUNTIF($R$6:$R$162,R133)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T133" s="63" t="str">
@@ -10343,7 +10343,7 @@
         <x:v>枪械|gunbody|blueprint_gun_catalog|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S134" s="63" t="str">
-        <x:f>IF(A134="","",IF(COUNTIF($R$6:$R$155,R134)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A134="","",IF(COUNTIF($R$6:$R$162,R134)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T134" s="63" t="str">
@@ -10417,7 +10417,7 @@
         <x:v>敌人|normal_elite_boss|enemy_ecosystem|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S135" s="63" t="str">
-        <x:f>IF(A135="","",IF(COUNTIF($R$6:$R$155,R135)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A135="","",IF(COUNTIF($R$6:$R$162,R135)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T135" s="63" t="str">
@@ -10491,7 +10491,7 @@
         <x:v>特效|combat|combat_feedback|root_3d|俯视3d|muzzle_impact_damage_explosion</x:v>
       </x:c>
       <x:c r="S136" s="63" t="str">
-        <x:f>IF(A136="","",IF(COUNTIF($R$6:$R$155,R136)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A136="","",IF(COUNTIF($R$6:$R$162,R136)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T136" s="63" t="str">
@@ -10565,7 +10565,7 @@
         <x:v>场景|training_range|training_range|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S137" s="63" t="str">
-        <x:f>IF(A137="","",IF(COUNTIF($R$6:$R$155,R137)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A137="","",IF(COUNTIF($R$6:$R$162,R137)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T137" s="63" t="str">
@@ -10641,7 +10641,7 @@
         <x:v>场景|review_board|dungeon_runtime|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S138" s="63" t="str">
-        <x:f>IF(A138="","",IF(COUNTIF($R$6:$R$155,R138)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A138="","",IF(COUNTIF($R$6:$R$162,R138)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T138" s="63" t="str">
@@ -10717,7 +10717,7 @@
         <x:v>场景|review_board|training_range|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S139" s="63" t="str">
-        <x:f>IF(A139="","",IF(COUNTIF($R$6:$R$155,R139)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A139="","",IF(COUNTIF($R$6:$R$162,R139)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T139" s="63" t="str">
@@ -10793,7 +10793,7 @@
         <x:v>特效|gameplay_vfx|visibility_field|field_mesh_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S140" t="str">
-        <x:f>IF(A140="","",IF(COUNTIF($R$6:$R$155,R140)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A140="","",IF(COUNTIF($R$6:$R$162,R140)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T140" t="str">
@@ -10869,7 +10869,7 @@
         <x:v>ui|screen|inventory|root_3d|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S141" t="str">
-        <x:f>IF(A141="","",IF(COUNTIF($R$6:$R$155,R141)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A141="","",IF(COUNTIF($R$6:$R$162,R141)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T141" t="str">
@@ -10943,7 +10943,7 @@
         <x:v>ui|screen|pause|root_3d|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S142" t="str">
-        <x:f>IF(A142="","",IF(COUNTIF($R$6:$R$155,R142)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A142="","",IF(COUNTIF($R$6:$R$162,R142)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T142" t="str">
@@ -11019,7 +11019,7 @@
         <x:v>场景道具|facility|room_light_switch|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S143" t="str">
-        <x:f>IF(A143="","",IF(COUNTIF($R$6:$R$155,R143)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A143="","",IF(COUNTIF($R$6:$R$162,R143)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T143" t="str">
@@ -11095,7 +11095,7 @@
         <x:v>特效|gameplay_vfx|player_flashlight|light_rig_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S144" t="str">
-        <x:f>IF(A144="","",IF(COUNTIF($R$6:$R$155,R144)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A144="","",IF(COUNTIF($R$6:$R$162,R144)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T144" t="str">
@@ -11171,7 +11171,7 @@
         <x:v>ui|icon|item_model_icon|root_3d|屏幕空间/3d投影|default</x:v>
       </x:c>
       <x:c r="S145" t="str">
-        <x:f>IF(A145="","",IF(COUNTIF($R$6:$R$155,R145)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A145="","",IF(COUNTIF($R$6:$R$162,R145)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T145" t="str">
@@ -11247,7 +11247,7 @@
         <x:v>角色|player_variant|player_capsule01|body_diy_3d|俯视3d|diy</x:v>
       </x:c>
       <x:c r="S146" s="63" t="str">
-        <x:f>IF(A146="","",IF(COUNTIF($R$6:$R$155,R146)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A146="","",IF(COUNTIF($R$6:$R$162,R146)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T146" s="63" t="str">
@@ -11323,7 +11323,7 @@
         <x:v>角色|player_variant|player_capsule01|head_diy_3d|俯视3d|diy</x:v>
       </x:c>
       <x:c r="S147" s="63" t="str">
-        <x:f>IF(A147="","",IF(COUNTIF($R$6:$R$155,R147)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A147="","",IF(COUNTIF($R$6:$R$162,R147)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T147" s="63" t="str">
@@ -11399,7 +11399,7 @@
         <x:v>角色|player_variant|player_capsule01|hand_diy_3d|俯视3d|diy</x:v>
       </x:c>
       <x:c r="S148" s="63" t="str">
-        <x:f>IF(A148="","",IF(COUNTIF($R$6:$R$155,R148)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A148="","",IF(COUNTIF($R$6:$R$162,R148)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T148" s="63" t="str">
@@ -11475,7 +11475,7 @@
         <x:v>角色|player_accessory|player_capsule01|hat_diy_3d|俯视3d|diy</x:v>
       </x:c>
       <x:c r="S149" s="63" t="str">
-        <x:f>IF(A149="","",IF(COUNTIF($R$6:$R$155,R149)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A149="","",IF(COUNTIF($R$6:$R$162,R149)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T149" s="63" t="str">
@@ -11551,7 +11551,7 @@
         <x:v>角色|player_accessory|player_capsule01|glasses_diy_3d|俯视3d|diy</x:v>
       </x:c>
       <x:c r="S150" s="63" t="str">
-        <x:f>IF(A150="","",IF(COUNTIF($R$6:$R$155,R150)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A150="","",IF(COUNTIF($R$6:$R$162,R150)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T150" s="63" t="str">
@@ -11627,7 +11627,7 @@
         <x:v>角色|player|player_capsule01|feet_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S151" s="63" t="str">
-        <x:f>IF(A151="","",IF(COUNTIF($R$6:$R$155,R151)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A151="","",IF(COUNTIF($R$6:$R$162,R151)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T151" s="63" t="str">
@@ -11703,7 +11703,7 @@
         <x:v>角色|player_accessory|player_capsule01|eyes_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S152" s="63" t="str">
-        <x:f>IF(A152="","",IF(COUNTIF($R$6:$R$155,R152)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A152="","",IF(COUNTIF($R$6:$R$162,R152)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T152" s="63" t="str">
@@ -11779,7 +11779,7 @@
         <x:v>角色|player_accessory|player_capsule01|ears_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S153" s="63" t="str">
-        <x:f>IF(A153="","",IF(COUNTIF($R$6:$R$155,R153)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A153="","",IF(COUNTIF($R$6:$R$162,R153)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T153" s="63" t="str">
@@ -11855,7 +11855,7 @@
         <x:v>角色|player_accessory|player_capsule01|tail_stub_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S154" s="63" t="str">
-        <x:f>IF(A154="","",IF(COUNTIF($R$6:$R$155,R154)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A154="","",IF(COUNTIF($R$6:$R$162,R154)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T154" s="63" t="str">
@@ -11931,7 +11931,7 @@
         <x:v>角色|player_variant|player_capsule01|feet_diy_3d|俯视3d|diy</x:v>
       </x:c>
       <x:c r="S155" s="63" t="str">
-        <x:f>IF(A155="","",IF(COUNTIF($R$6:$R$155,R155)&gt;1,"重复","唯一"))</x:f>
+        <x:f>IF(A155="","",IF(COUNTIF($R$6:$R$162,R155)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T155" s="63" t="str">
@@ -11948,6 +11948,538 @@
       </x:c>
       <x:c r="X155" s="63" t="str">
         <x:v>方形猫角色3D脚部DIY变体；复用CHR-PLY-CAPSULE01-3D玩家根；方形主语言，TailStub为用户指定圆尾例外；自动与视觉验收PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="88" customHeight="1">
+      <x:c r="A156" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
+      </x:c>
+      <x:c r="B156" s="63" t="str">
+        <x:v>兔子主角3D根变体</x:v>
+      </x:c>
+      <x:c r="C156" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D156" s="63" t="str">
+        <x:v>player_variant</x:v>
+      </x:c>
+      <x:c r="E156" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F156" s="63" t="str">
+        <x:v>root_3d_bunny01</x:v>
+      </x:c>
+      <x:c r="G156" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="H156" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I156" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J156" s="63" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K156" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L156" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M156" s="63" t="str">
+        <x:v>v004</x:v>
+      </x:c>
+      <x:c r="N156" s="63" t="str">
+        <x:v>1.705×2.475×1.064 m</x:v>
+      </x:c>
+      <x:c r="O156" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v004.tscn</x:v>
+      </x:c>
+      <x:c r="P156" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
+      </x:c>
+      <x:c r="Q156" s="63" t="str">
+        <x:v>兔子;主角;兔耳;3D;Blender;bunny01</x:v>
+      </x:c>
+      <x:c r="R156" s="63" t="str">
+        <x:f>LOWER(TRIM(C156)&amp;"|"&amp;TRIM(D156)&amp;"|"&amp;TRIM(E156)&amp;"|"&amp;TRIM(F156)&amp;"|"&amp;TRIM(H156)&amp;"|"&amp;TRIM(I156))</x:f>
+        <x:v>角色|player_variant|player_capsule01|root_3d_bunny01|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S156" s="63" t="str">
+        <x:f>IF(A156="","",IF(COUNTIF($R$6:$R$162,R156)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T156" s="63" t="str">
+        <x:v>2c34f9d637b480321fc287cb9a72d8d5d633a3aa3976ff0fbb21d3d7c8f9e621</x:v>
+      </x:c>
+      <x:c r="U156" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V156" s="63" t="str">
+        <x:v>2026-07-29</x:v>
+      </x:c>
+      <x:c r="W156" s="63" t="str">
+        <x:v>用户提供 Blender 源文件 / Codex 模块化拆分</x:v>
+      </x:c>
+      <x:c r="X156" s="63" t="str">
+        <x:v>v004 行为契约修正（网格、源文件与 AssetID 不变）：手部圆环定义为近端手腕轴心，球体为远端手掌；手枪在角色右侧单手握持，长枪右手握把、左手托举；hold/run/fire/reload/charge 由武器姿势状态机分离，七种枪体使用数据化差异后坐。六态状态机既有 idle 现驱动约 2.38s 站立循环：呼吸挤压、慢速重心换脚、头部反向滞后、双耳错相与偶发耳弹，移动输入出现即退出，停止后恢复。模型层级零碰撞；Player3D 根节点使用不可见 BoxShape3D 0.86×1.80×0.72m，顶部 1.80m ≤ 无耳头顶 1.820592m。自动与视觉验收 PASS。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="58" customHeight="1">
+      <x:c r="A157" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-BODY</x:v>
+      </x:c>
+      <x:c r="B157" s="63" t="str">
+        <x:v>兔子主角3D身体</x:v>
+      </x:c>
+      <x:c r="C157" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D157" s="63" t="str">
+        <x:v>player_component</x:v>
+      </x:c>
+      <x:c r="E157" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F157" s="63" t="str">
+        <x:v>body_3d_bunny01</x:v>
+      </x:c>
+      <x:c r="G157" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
+      </x:c>
+      <x:c r="H157" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I157" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J157" s="63" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K157" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L157" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M157" s="63" t="str">
+        <x:v>v004</x:v>
+      </x:c>
+      <x:c r="N157" s="63" t="str">
+        <x:v>GLB / 1,958 verts / pivot-local</x:v>
+      </x:c>
+      <x:c r="O157" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="P157" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
+      </x:c>
+      <x:c r="Q157" s="63" t="str">
+        <x:v>兔子;身体;服装;body;bunny01</x:v>
+      </x:c>
+      <x:c r="R157" s="63" t="str">
+        <x:f>LOWER(TRIM(C157)&amp;"|"&amp;TRIM(D157)&amp;"|"&amp;TRIM(E157)&amp;"|"&amp;TRIM(F157)&amp;"|"&amp;TRIM(H157)&amp;"|"&amp;TRIM(I157))</x:f>
+        <x:v>角色|player_component|player_capsule01|body_3d_bunny01|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S157" s="63" t="str">
+        <x:f>IF(A157="","",IF(COUNTIF($R$6:$R$162,R157)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T157" s="63" t="str">
+        <x:v>632b9e9832d5fbd367d3b4682035732ec43cfc02b797cb4f09a309099c9e42c1</x:v>
+      </x:c>
+      <x:c r="U157" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V157" s="63" t="str">
+        <x:v>2026-07-29</x:v>
+      </x:c>
+      <x:c r="W157" s="63" t="str">
+        <x:v>用户提供 Blender 源文件</x:v>
+      </x:c>
+      <x:c r="X157" s="63" t="str">
+        <x:v>BunnyRig/BodyJoint；底部中心原点；支持呼吸、突进压缩、完整翻滚和受击挤压回弹。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="58" customHeight="1">
+      <x:c r="A158" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-HEAD</x:v>
+      </x:c>
+      <x:c r="B158" s="63" t="str">
+        <x:v>兔子主角3D头部</x:v>
+      </x:c>
+      <x:c r="C158" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D158" s="63" t="str">
+        <x:v>player_component</x:v>
+      </x:c>
+      <x:c r="E158" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F158" s="63" t="str">
+        <x:v>head_3d_bunny01</x:v>
+      </x:c>
+      <x:c r="G158" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
+      </x:c>
+      <x:c r="H158" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I158" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J158" s="63" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K158" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L158" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M158" s="63" t="str">
+        <x:v>v004</x:v>
+      </x:c>
+      <x:c r="N158" s="63" t="str">
+        <x:v>GLB / 5,936 verts / pivot-local</x:v>
+      </x:c>
+      <x:c r="O158" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="P158" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
+      </x:c>
+      <x:c r="Q158" s="63" t="str">
+        <x:v>兔子;头部;head;bunny01</x:v>
+      </x:c>
+      <x:c r="R158" s="63" t="str">
+        <x:f>LOWER(TRIM(C158)&amp;"|"&amp;TRIM(D158)&amp;"|"&amp;TRIM(E158)&amp;"|"&amp;TRIM(F158)&amp;"|"&amp;TRIM(H158)&amp;"|"&amp;TRIM(I158))</x:f>
+        <x:v>角色|player_component|player_capsule01|head_3d_bunny01|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S158" s="63" t="str">
+        <x:f>IF(A158="","",IF(COUNTIF($R$6:$R$162,R158)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T158" s="63" t="str">
+        <x:v>4255cfdc374dc97a75d3386444edbd8c523ca174b9fc32b5c5fe48b9aedb4d1c</x:v>
+      </x:c>
+      <x:c r="U158" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V158" s="63" t="str">
+        <x:v>2026-07-29</x:v>
+      </x:c>
+      <x:c r="W158" s="63" t="str">
+        <x:v>用户提供 Blender 源文件</x:v>
+      </x:c>
+      <x:c r="X158" s="63" t="str">
+        <x:v>BunnyRig/HeadJoint；头部下沿中心原点；耳朵通过 Head 子挂点装配；受击时承担夸张甩头和过冲回正。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="58" customHeight="1">
+      <x:c r="A159" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-EARS</x:v>
+      </x:c>
+      <x:c r="B159" s="63" t="str">
+        <x:v>兔子主角3D双耳配件</x:v>
+      </x:c>
+      <x:c r="C159" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D159" s="63" t="str">
+        <x:v>player_accessory</x:v>
+      </x:c>
+      <x:c r="E159" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F159" s="63" t="str">
+        <x:v>ears_3d_bunny01</x:v>
+      </x:c>
+      <x:c r="G159" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-HEAD</x:v>
+      </x:c>
+      <x:c r="H159" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I159" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J159" s="63" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K159" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L159" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M159" s="63" t="str">
+        <x:v>v004</x:v>
+      </x:c>
+      <x:c r="N159" s="63" t="str">
+        <x:v>单 GLB / 1,536 verts / pivot-local</x:v>
+      </x:c>
+      <x:c r="O159" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="P159" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
+      </x:c>
+      <x:c r="Q159" s="63" t="str">
+        <x:v>兔耳;耳朵;耳部配件;EarSocketL;EarSocketR;bunny01</x:v>
+      </x:c>
+      <x:c r="R159" s="63" t="str">
+        <x:f>LOWER(TRIM(C159)&amp;"|"&amp;TRIM(D159)&amp;"|"&amp;TRIM(E159)&amp;"|"&amp;TRIM(F159)&amp;"|"&amp;TRIM(H159)&amp;"|"&amp;TRIM(I159))</x:f>
+        <x:v>角色|player_accessory|player_capsule01|ears_3d_bunny01|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S159" s="63" t="str">
+        <x:f>IF(A159="","",IF(COUNTIF($R$6:$R$162,R159)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T159" s="63" t="str">
+        <x:v>c768ac511df6636ba66ca3153b06a5348bffd2e6bfeed0f49c922ada982393ef</x:v>
+      </x:c>
+      <x:c r="U159" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V159" s="63" t="str">
+        <x:v>2026-07-29</x:v>
+      </x:c>
+      <x:c r="W159" s="63" t="str">
+        <x:v>用户提供 Blender 源文件</x:v>
+      </x:c>
+      <x:c r="X159" s="63" t="str">
+        <x:v>单个语义右耳局部模型；Godot EarSocketR 直接复用，EarSocketL 运行时 -X 镜像；耳根原点用于后压、收耳和甩动。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="72" customHeight="1">
+      <x:c r="A160" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-HAND</x:v>
+      </x:c>
+      <x:c r="B160" s="63" t="str">
+        <x:v>兔子主角3D双爪表现组件</x:v>
+      </x:c>
+      <x:c r="C160" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D160" s="63" t="str">
+        <x:v>player_component</x:v>
+      </x:c>
+      <x:c r="E160" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F160" s="63" t="str">
+        <x:v>hand_3d_bunny01</x:v>
+      </x:c>
+      <x:c r="G160" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
+      </x:c>
+      <x:c r="H160" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I160" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J160" s="63" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K160" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L160" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M160" s="63" t="str">
+        <x:v>v004</x:v>
+      </x:c>
+      <x:c r="N160" s="63" t="str">
+        <x:v>双 GLB / 左右各 1,058 verts / pivot-local</x:v>
+      </x:c>
+      <x:c r="O160" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v004.glb; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_r_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="P160" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
+      </x:c>
+      <x:c r="Q160" s="63" t="str">
+        <x:v>兔爪;手;握持;weapon_socket;bunny01</x:v>
+      </x:c>
+      <x:c r="R160" s="63" t="str">
+        <x:f>LOWER(TRIM(C160)&amp;"|"&amp;TRIM(D160)&amp;"|"&amp;TRIM(E160)&amp;"|"&amp;TRIM(F160)&amp;"|"&amp;TRIM(H160)&amp;"|"&amp;TRIM(I160))</x:f>
+        <x:v>角色|player_component|player_capsule01|hand_3d_bunny01|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S160" s="63" t="str">
+        <x:f>IF(A160="","",IF(COUNTIF($R$6:$R$162,R160)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T160" s="63" t="str">
+        <x:v>6171ea35985b712446983d7c5fa27ae8c248e4516f487c709a302de6e845d088 / d421b98ded85d9580ad41189ab6fd3095f579447c1ef64ef659e87b6ec72581e</x:v>
+      </x:c>
+      <x:c r="U160" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V160" s="63" t="str">
+        <x:v>2026-07-29</x:v>
+      </x:c>
+      <x:c r="W160" s="63" t="str">
+        <x:v>用户提供 Blender 源文件</x:v>
+      </x:c>
+      <x:c r="X160" s="63" t="str">
+        <x:v>BunnyRig/HandRoot/HandJointL/R；圆环=近端手腕/动画轴心，球体=远端手掌。手枪仅右手握持且置于角色右侧，左手自由摆动；长枪右手握把、左手托举；跑步、射击、换弹、蓄力分别由武器姿势状态管理，手枪/霰弹/步枪/机枪/狙击/发射器/蓄力枪具备差异后坐参数。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="58" customHeight="1">
+      <x:c r="A161" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-FOOT-L</x:v>
+      </x:c>
+      <x:c r="B161" s="63" t="str">
+        <x:v>兔子主角3D左脚</x:v>
+      </x:c>
+      <x:c r="C161" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D161" s="63" t="str">
+        <x:v>player_component</x:v>
+      </x:c>
+      <x:c r="E161" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F161" s="63" t="str">
+        <x:v>foot_l_3d_bunny01</x:v>
+      </x:c>
+      <x:c r="G161" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
+      </x:c>
+      <x:c r="H161" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I161" s="63" t="str">
+        <x:v>moving</x:v>
+      </x:c>
+      <x:c r="J161" s="63" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K161" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L161" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M161" s="63" t="str">
+        <x:v>v004</x:v>
+      </x:c>
+      <x:c r="N161" s="63" t="str">
+        <x:v>GLB / 5,396 verts / pivot-local</x:v>
+      </x:c>
+      <x:c r="O161" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="P161" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
+      </x:c>
+      <x:c r="Q161" s="63" t="str">
+        <x:v>兔脚;左脚;步态;FootL;bunny01</x:v>
+      </x:c>
+      <x:c r="R161" s="63" t="str">
+        <x:f>LOWER(TRIM(C161)&amp;"|"&amp;TRIM(D161)&amp;"|"&amp;TRIM(E161)&amp;"|"&amp;TRIM(F161)&amp;"|"&amp;TRIM(H161)&amp;"|"&amp;TRIM(I161))</x:f>
+        <x:v>角色|player_component|player_capsule01|foot_l_3d_bunny01|俯视3d|moving</x:v>
+      </x:c>
+      <x:c r="S161" s="63" t="str">
+        <x:f>IF(A161="","",IF(COUNTIF($R$6:$R$162,R161)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T161" s="63" t="str">
+        <x:v>ba37215c7a03dae202dd03c6b2151b179dae0bfca345142bf7b0bd6268203251</x:v>
+      </x:c>
+      <x:c r="U161" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V161" s="63" t="str">
+        <x:v>2026-07-29</x:v>
+      </x:c>
+      <x:c r="W161" s="63" t="str">
+        <x:v>用户提供 Blender 源文件</x:v>
+      </x:c>
+      <x:c r="X161" s="63" t="str">
+        <x:v>BunnyRig/FeetRoot/FootJointL；脚底中心原点；支持交替步态、翻滚收腿、受击甩脚和落地挤压。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="58" customHeight="1">
+      <x:c r="A162" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-FOOT-R</x:v>
+      </x:c>
+      <x:c r="B162" s="63" t="str">
+        <x:v>兔子主角3D右脚</x:v>
+      </x:c>
+      <x:c r="C162" s="63" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D162" s="63" t="str">
+        <x:v>player_component</x:v>
+      </x:c>
+      <x:c r="E162" s="63" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F162" s="63" t="str">
+        <x:v>foot_r_3d_bunny01</x:v>
+      </x:c>
+      <x:c r="G162" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
+      </x:c>
+      <x:c r="H162" s="63" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I162" s="63" t="str">
+        <x:v>moving</x:v>
+      </x:c>
+      <x:c r="J162" s="63" t="str">
+        <x:v>3D玩家场景</x:v>
+      </x:c>
+      <x:c r="K162" s="63" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L162" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M162" s="63" t="str">
+        <x:v>v004</x:v>
+      </x:c>
+      <x:c r="N162" s="63" t="str">
+        <x:v>GLB / 5,396 verts / pivot-local</x:v>
+      </x:c>
+      <x:c r="O162" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="P162" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
+      </x:c>
+      <x:c r="Q162" s="63" t="str">
+        <x:v>兔脚;右脚;步态;FootR;bunny01</x:v>
+      </x:c>
+      <x:c r="R162" s="63" t="str">
+        <x:f>LOWER(TRIM(C162)&amp;"|"&amp;TRIM(D162)&amp;"|"&amp;TRIM(E162)&amp;"|"&amp;TRIM(F162)&amp;"|"&amp;TRIM(H162)&amp;"|"&amp;TRIM(I162))</x:f>
+        <x:v>角色|player_component|player_capsule01|foot_r_3d_bunny01|俯视3d|moving</x:v>
+      </x:c>
+      <x:c r="S162" s="63" t="str">
+        <x:f>IF(A162="","",IF(COUNTIF($R$6:$R$162,R162)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T162" s="63" t="str">
+        <x:v>9afad545f5f7f1ffa13db7d33bb71ba6df913c9072b6b9a32d673f5c4b24438a</x:v>
+      </x:c>
+      <x:c r="U162" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V162" s="63" t="str">
+        <x:v>2026-07-29</x:v>
+      </x:c>
+      <x:c r="W162" s="63" t="str">
+        <x:v>用户提供 Blender 源文件</x:v>
+      </x:c>
+      <x:c r="X162" s="63" t="str">
+        <x:v>BunnyRig/FeetRoot/FootJointR；脚底中心原点；与左脚独立交替并参与翻滚/受击关键姿势。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11975,7 +12507,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54ff6c904d8a485a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51196272a3c247a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11986,17 +12518,17 @@
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="52" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="44" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="19" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="6" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="30" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="8" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="36" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="25" customHeight="1">
@@ -13112,6 +13644,375 @@
       </x:c>
       <x:c r="M30" s="63" t="str">
         <x:v>默认visible=false；不计入四主模块</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="62" customHeight="1">
+      <x:c r="A31" s="63" t="str">
+        <x:v>player_capsule01_bunny01_3d</x:v>
+      </x:c>
+      <x:c r="B31" s="63" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="C31" s="63" t="str">
+        <x:v>Avatar3D/VisualRoot/BunnyRig</x:v>
+      </x:c>
+      <x:c r="D31" s="63" t="str">
+        <x:v>player_root</x:v>
+      </x:c>
+      <x:c r="E31" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v004.tscn</x:v>
+      </x:c>
+      <x:c r="F31" s="63" t="str">
+        <x:v>Node3D刚性骨架</x:v>
+      </x:c>
+      <x:c r="G31" s="63" t="str">
+        <x:v>(0,0,0)</x:v>
+      </x:c>
+      <x:c r="H31" s="63" t="str">
+        <x:v>整体随准星绕Y轴</x:v>
+      </x:c>
+      <x:c r="I31" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J31" s="63" t="str">
+        <x:v>六态整体 + 动作覆盖</x:v>
+      </x:c>
+      <x:c r="K31" s="63" t="str">
+        <x:v>Godot骨架根</x:v>
+      </x:c>
+      <x:c r="L31" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M31" s="63" t="str">
+        <x:v>v004：模型为 pivot-local；导出器断言 Blender +X → Godot -Z；装配坐标由 Godot 关节节点提供；视觉层级 CollisionShape3D/CollisionObject3D 数量均为 0。玩法碰撞仅使用 Player3D/VirtualCollisionBox（0.86×1.80×0.72m），不包含耳朵。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="54" customHeight="1">
+      <x:c r="A32" s="63" t="str">
+        <x:v>player_capsule01_bunny01_3d</x:v>
+      </x:c>
+      <x:c r="B32" s="63" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="C32" s="63" t="str">
+        <x:v>VisualRoot/BunnyRig/BodyJoint/Model</x:v>
+      </x:c>
+      <x:c r="D32" s="63" t="str">
+        <x:v>BunnyRig</x:v>
+      </x:c>
+      <x:c r="E32" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="F32" s="63" t="str">
+        <x:v>pivot-local GLB</x:v>
+      </x:c>
+      <x:c r="G32" s="63" t="str">
+        <x:v>(-0.00005,0.255786,-0.001047)</x:v>
+      </x:c>
+      <x:c r="H32" s="63" t="str">
+        <x:v>BodyJoint</x:v>
+      </x:c>
+      <x:c r="I32" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J32" s="63" t="str">
+        <x:v>呼吸/移动挤压/突进翻滚/受击</x:v>
+      </x:c>
+      <x:c r="K32" s="63" t="str">
+        <x:v>身体组件</x:v>
+      </x:c>
+      <x:c r="L32" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M32" s="63" t="str">
+        <x:v>Blender 原点：身体底部中心</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="54" customHeight="1">
+      <x:c r="A33" s="63" t="str">
+        <x:v>player_capsule01_bunny01_3d</x:v>
+      </x:c>
+      <x:c r="B33" s="63" t="str">
+        <x:v>head</x:v>
+      </x:c>
+      <x:c r="C33" s="63" t="str">
+        <x:v>VisualRoot/BunnyRig/HeadJoint/Model</x:v>
+      </x:c>
+      <x:c r="D33" s="63" t="str">
+        <x:v>BunnyRig</x:v>
+      </x:c>
+      <x:c r="E33" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="F33" s="63" t="str">
+        <x:v>pivot-local GLB</x:v>
+      </x:c>
+      <x:c r="G33" s="63" t="str">
+        <x:v>(-0.000046,0.787232,0.043611)</x:v>
+      </x:c>
+      <x:c r="H33" s="63" t="str">
+        <x:v>HeadJoint</x:v>
+      </x:c>
+      <x:c r="I33" s="63" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J33" s="63" t="str">
+        <x:v>移动反相滞后/后坐/受击甩头</x:v>
+      </x:c>
+      <x:c r="K33" s="63" t="str">
+        <x:v>头部组件</x:v>
+      </x:c>
+      <x:c r="L33" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M33" s="63" t="str">
+        <x:v>Blender 原点：头部下沿中心</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="54" customHeight="1">
+      <x:c r="A34" s="63" t="str">
+        <x:v>player_capsule01_bunny01_3d</x:v>
+      </x:c>
+      <x:c r="B34" s="63" t="str">
+        <x:v>ear_l</x:v>
+      </x:c>
+      <x:c r="C34" s="63" t="str">
+        <x:v>VisualRoot/BunnyRig/HeadJoint/Ears/EarSocketL/EarAccessory</x:v>
+      </x:c>
+      <x:c r="D34" s="63" t="str">
+        <x:v>head</x:v>
+      </x:c>
+      <x:c r="E34" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="F34" s="63" t="str">
+        <x:v>pivot-local GLB × -X</x:v>
+      </x:c>
+      <x:c r="G34" s="63" t="str">
+        <x:v>Head local (-0.404343,0.824427,-0.002757)</x:v>
+      </x:c>
+      <x:c r="H34" s="63" t="str">
+        <x:v>继承HeadJoint</x:v>
+      </x:c>
+      <x:c r="I34" s="63" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J34" s="63" t="str">
+        <x:v>移动跟随/冲刺后压/受击收耳</x:v>
+      </x:c>
+      <x:c r="K34" s="63" t="str">
+        <x:v>头部配件</x:v>
+      </x:c>
+      <x:c r="L34" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M34" s="63" t="str">
+        <x:v>复用语义右耳资产并在左挂点镜像；原点位于耳根</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="54" customHeight="1">
+      <x:c r="A35" s="63" t="str">
+        <x:v>player_capsule01_bunny01_3d</x:v>
+      </x:c>
+      <x:c r="B35" s="63" t="str">
+        <x:v>ear_r</x:v>
+      </x:c>
+      <x:c r="C35" s="63" t="str">
+        <x:v>VisualRoot/BunnyRig/HeadJoint/Ears/EarSocketR/EarAccessory</x:v>
+      </x:c>
+      <x:c r="D35" s="63" t="str">
+        <x:v>head</x:v>
+      </x:c>
+      <x:c r="E35" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="F35" s="63" t="str">
+        <x:v>pivot-local GLB</x:v>
+      </x:c>
+      <x:c r="G35" s="63" t="str">
+        <x:v>Head local (0.404435,0.824427,-0.002757)</x:v>
+      </x:c>
+      <x:c r="H35" s="63" t="str">
+        <x:v>继承HeadJoint</x:v>
+      </x:c>
+      <x:c r="I35" s="63" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J35" s="63" t="str">
+        <x:v>移动跟随/冲刺后压/受击收耳</x:v>
+      </x:c>
+      <x:c r="K35" s="63" t="str">
+        <x:v>头部配件</x:v>
+      </x:c>
+      <x:c r="L35" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M35" s="63" t="str">
+        <x:v>语义右耳标准实例；原点位于耳根</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="62" customHeight="1">
+      <x:c r="A36" s="63" t="str">
+        <x:v>player_capsule01_bunny01_3d</x:v>
+      </x:c>
+      <x:c r="B36" s="63" t="str">
+        <x:v>hand_l</x:v>
+      </x:c>
+      <x:c r="C36" s="63" t="str">
+        <x:v>VisualRoot/BunnyRig/HandRoot/HandJointL/Model</x:v>
+      </x:c>
+      <x:c r="D36" s="63" t="str">
+        <x:v>BunnyRig</x:v>
+      </x:c>
+      <x:c r="E36" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="F36" s="63" t="str">
+        <x:v>pivot-local GLB</x:v>
+      </x:c>
+      <x:c r="G36" s="63" t="str">
+        <x:v>Authored (-0.471625,0.530925,-0.023818); longgun support (0.20,0.52,-0.64)</x:v>
+      </x:c>
+      <x:c r="H36" s="63" t="str">
+        <x:v>HandRoot 独立左腕</x:v>
+      </x:c>
+      <x:c r="I36" s="63" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J36" s="63" t="str">
+        <x:v>手枪自由摆臂；长枪托举；换弹服务；双手枪后坐</x:v>
+      </x:c>
+      <x:c r="K36" s="63" t="str">
+        <x:v>左手组件</x:v>
+      </x:c>
+      <x:c r="L36" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M36" s="63" t="str">
+        <x:v>Blender 原点位于手腕圆环近端轴心，球体为远端手掌；手枪姿势不计入握持手，长枪左手跨中线托住护木下方并绕本地 Y 负向转入托举。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="62" customHeight="1">
+      <x:c r="A37" s="63" t="str">
+        <x:v>player_capsule01_bunny01_3d</x:v>
+      </x:c>
+      <x:c r="B37" s="63" t="str">
+        <x:v>hand_r</x:v>
+      </x:c>
+      <x:c r="C37" s="63" t="str">
+        <x:v>VisualRoot/BunnyRig/HandRoot/HandJointR/Model</x:v>
+      </x:c>
+      <x:c r="D37" s="63" t="str">
+        <x:v>BunnyRig</x:v>
+      </x:c>
+      <x:c r="E37" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_r_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="F37" s="63" t="str">
+        <x:v>pivot-local GLB</x:v>
+      </x:c>
+      <x:c r="G37" s="63" t="str">
+        <x:v>Authored (0.471625,0.530925,-0.023818); sidearm (0.08,0.56,-0.49)+socket X0.24; longgun (0.13,0.56,-0.49)</x:v>
+      </x:c>
+      <x:c r="H37" s="63" t="str">
+        <x:v>HandRoot 独立右腕 / WeaponSocket 跟随</x:v>
+      </x:c>
+      <x:c r="I37" s="63" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J37" s="63" t="str">
+        <x:v>手枪/长枪主握把；独立跑步；武器差异射击后坐</x:v>
+      </x:c>
+      <x:c r="K37" s="63" t="str">
+        <x:v>右手组件</x:v>
+      </x:c>
+      <x:c r="L37" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M37" s="63" t="str">
+        <x:v>Blender 原点位于手腕圆环近端轴心，球体为远端手掌；角色右侧单手枪绕本地 Y 正向对齐，长枪与左手托举共同锁定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="54" customHeight="1">
+      <x:c r="A38" s="63" t="str">
+        <x:v>player_capsule01_bunny01_3d</x:v>
+      </x:c>
+      <x:c r="B38" s="63" t="str">
+        <x:v>foot_l</x:v>
+      </x:c>
+      <x:c r="C38" s="63" t="str">
+        <x:v>VisualRoot/BunnyRig/FeetRoot/FootJointL/Model</x:v>
+      </x:c>
+      <x:c r="D38" s="63" t="str">
+        <x:v>FeetRoot</x:v>
+      </x:c>
+      <x:c r="E38" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="F38" s="63" t="str">
+        <x:v>pivot-local GLB</x:v>
+      </x:c>
+      <x:c r="G38" s="63" t="str">
+        <x:v>(-0.212854,0,-0.017964)</x:v>
+      </x:c>
+      <x:c r="H38" s="63" t="str">
+        <x:v>独立FootJointL</x:v>
+      </x:c>
+      <x:c r="I38" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J38" s="63" t="str">
+        <x:v>moving左脚/翻滚收腿/受击甩脚</x:v>
+      </x:c>
+      <x:c r="K38" s="63" t="str">
+        <x:v>左脚组件</x:v>
+      </x:c>
+      <x:c r="L38" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M38" s="63" t="str">
+        <x:v>Blender 原点：脚底中心</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="54" customHeight="1">
+      <x:c r="A39" s="63" t="str">
+        <x:v>player_capsule01_bunny01_3d</x:v>
+      </x:c>
+      <x:c r="B39" s="63" t="str">
+        <x:v>foot_r</x:v>
+      </x:c>
+      <x:c r="C39" s="63" t="str">
+        <x:v>VisualRoot/BunnyRig/FeetRoot/FootJointR/Model</x:v>
+      </x:c>
+      <x:c r="D39" s="63" t="str">
+        <x:v>FeetRoot</x:v>
+      </x:c>
+      <x:c r="E39" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="F39" s="63" t="str">
+        <x:v>pivot-local GLB</x:v>
+      </x:c>
+      <x:c r="G39" s="63" t="str">
+        <x:v>(0.212854,0,-0.017964)</x:v>
+      </x:c>
+      <x:c r="H39" s="63" t="str">
+        <x:v>独立FootJointR</x:v>
+      </x:c>
+      <x:c r="I39" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J39" s="63" t="str">
+        <x:v>moving右脚/翻滚收腿/受击甩脚</x:v>
+      </x:c>
+      <x:c r="K39" s="63" t="str">
+        <x:v>右脚组件</x:v>
+      </x:c>
+      <x:c r="L39" s="63" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M39" s="63" t="str">
+        <x:v>Blender 原点：脚底中心</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13137,13 +14038,13 @@
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="34" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="25" customHeight="1">
@@ -13178,7 +14079,7 @@
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>2D/3D 共用六态 ID 与转换白名单；Low HP / Silenced / Invincible / Reloading / Firing / Charging / Knockback 为叠加层。武器与命中是唯一动作来源，新增动画前先查本表</x:v>
+        <x:v>2D/3D 共用六态 ID 与转换白名单；Low HP / Silenced / Invincible / Reloading / Firing / Charging / Knockback 为叠加层。兔子另有武器姿势状态机：unarmed、sidearm/longgun × hold/run/fire/reload/charge。武器与命中是唯一动作来源，新增动画前先查本表</x:v>
       </x:c>
       <x:c r="B3" s="6"/>
       <x:c r="C3" s="6"/>
@@ -13215,10 +14116,10 @@
         <x:v>Head</x:v>
       </x:c>
       <x:c r="H5" s="29" t="str">
-        <x:v>Hand L（停用）</x:v>
+        <x:v>Hand L</x:v>
       </x:c>
       <x:c r="I5" s="29" t="str">
-        <x:v>Hand（握持）</x:v>
+        <x:v>Hand R / WeaponSocket</x:v>
       </x:c>
       <x:c r="J5" s="29" t="str">
         <x:v>Scarf</x:v>
@@ -13230,7 +14131,7 @@
         <x:v>首版实现</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="58" customHeight="1">
       <x:c r="A6" s="36" t="str">
         <x:v>顶层</x:v>
       </x:c>
@@ -13247,25 +14148,25 @@
         <x:v>moving,dashing,hurt,locked,dead</x:v>
       </x:c>
       <x:c r="F6" s="36" t="str">
-        <x:v>低频呼吸</x:v>
+        <x:v>约2.38s呼吸挤压；半速重心换脚；躯干轻微侧移</x:v>
       </x:c>
       <x:c r="G6" s="36" t="str">
-        <x:v>轻微滞后</x:v>
+        <x:v>与身体反相缩放；反向滞后保持头重感</x:v>
       </x:c>
       <x:c r="H6" s="36" t="str">
-        <x:v>不显示</x:v>
+        <x:v>手枪自由左手轻摆；长枪左手保持托举</x:v>
       </x:c>
       <x:c r="I6" s="36" t="str">
-        <x:v>随身体左右镜像</x:v>
+        <x:v>握持手与 WeaponSocket 同步稳定呼吸，不脱离握把</x:v>
       </x:c>
       <x:c r="J6" s="36" t="str">
-        <x:v>轻摆</x:v>
+        <x:v>低频错相轻摆</x:v>
       </x:c>
       <x:c r="K6" s="36" t="str">
-        <x:v>HUD 待命</x:v>
+        <x:v>HUD 待命；无新增VFX</x:v>
       </x:c>
       <x:c r="L6" s="36" t="str">
-        <x:v>2D/3D组件变换；单手保持局部挂点</x:v>
+        <x:v>六态 StateMachine 的 idle 唯一驱动；idle_cycle 推进呼吸/换脚；双耳错相并偶发单耳轻弹；moving 本帧归零，停下后恢复</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -13291,10 +14192,10 @@
         <x:v>较小反相滞后</x:v>
       </x:c>
       <x:c r="H7" s="37" t="str">
-        <x:v>不显示</x:v>
+        <x:v>手枪自由左手大幅反摆；长枪左手锁定托举</x:v>
       </x:c>
       <x:c r="I7" s="37" t="str">
-        <x:v>与挂点同相移动</x:v>
+        <x:v>手枪右手与右侧挂点紧凑起伏；长枪双手/挂点收胸跑</x:v>
       </x:c>
       <x:c r="J7" s="37" t="str">
         <x:v>周期滞后</x:v>
@@ -13303,10 +14204,10 @@
         <x:v>地面划痕</x:v>
       </x:c>
       <x:c r="L7" s="37" t="str">
-        <x:v>2D/3D组件变换；独立moving循环；整体根随准星；手与挂点局部关系固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>位移驱动独立循环；WeaponPoseFSM 进入 sidearm_run 或 longgun_run；双脚交替，单手/双手剪影分离</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="56" customHeight="1">
       <x:c r="A8" s="37" t="str">
         <x:v>顶层</x:v>
       </x:c>
@@ -13323,28 +14224,28 @@
         <x:v>idle,moving,hurt,locked,dead</x:v>
       </x:c>
       <x:c r="F8" s="37" t="str">
-        <x:v>横向压缩</x:v>
+        <x:v>压缩成团并绕半高轴完整前滚</x:v>
       </x:c>
       <x:c r="G8" s="37" t="str">
-        <x:v>随整体压缩</x:v>
+        <x:v>随整体轴心翻滚，耳朵大幅后压</x:v>
       </x:c>
       <x:c r="H8" s="37" t="str">
-        <x:v>不显示</x:v>
+        <x:v>按当前武器握持数收束；自由左手随整体抱团</x:v>
       </x:c>
       <x:c r="I8" s="37" t="str">
-        <x:v>随身体左右镜像</x:v>
+        <x:v>右手握把与 WeaponSocket 同轴完整翻滚</x:v>
       </x:c>
       <x:c r="J8" s="37" t="str">
-        <x:v>顺风</x:v>
+        <x:v>随整体收束</x:v>
       </x:c>
       <x:c r="K8" s="37" t="str">
         <x:v>青色尾迹</x:v>
       </x:c>
       <x:c r="L8" s="37" t="str">
-        <x:v>2D/3D组件变换 + 程序尾迹；握持关系不变</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+        <x:v>0.17s 内完成 360° 本地X前滚；用半高轴心补偿避免钻地；夸张压缩与抛物线位移</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="56" customHeight="1">
       <x:c r="A9" s="37" t="str">
         <x:v>顶层</x:v>
       </x:c>
@@ -13361,25 +14262,25 @@
         <x:v>idle,moving,locked,dead</x:v>
       </x:c>
       <x:c r="F9" s="37" t="str">
-        <x:v>冲击压缩 + 击退弹性</x:v>
+        <x:v>三段压扁/抬起/过冲回正</x:v>
       </x:c>
       <x:c r="G9" s="37" t="str">
-        <x:v>后仰 + 回弹</x:v>
+        <x:v>大幅后仰甩头 + 反向过冲</x:v>
       </x:c>
       <x:c r="H9" s="37" t="str">
-        <x:v>不显示</x:v>
+        <x:v>手枪左手自由外甩；长枪左手回护木</x:v>
       </x:c>
       <x:c r="I9" s="37" t="str">
-        <x:v>与weapon_socket同相后退/回正</x:v>
+        <x:v>右手/WeaponSocket 同相后退，握把不脱离</x:v>
       </x:c>
       <x:c r="J9" s="37" t="str">
-        <x:v>抖动/滞后</x:v>
+        <x:v>冲击滞后</x:v>
       </x:c>
       <x:c r="K9" s="37" t="str">
         <x:v>红闪/击退轨迹</x:v>
       </x:c>
       <x:c r="L9" s="37" t="str">
-        <x:v>真实命中方向 + 递减XZ冲量；不扩张六态</x:v>
+        <x:v>真实命中方向 + 受击进度关键姿势；头、双脚、双耳使用独立夸张回弹</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -13405,10 +14306,10 @@
         <x:v>稳定</x:v>
       </x:c>
       <x:c r="H10" s="37" t="str">
-        <x:v>不显示</x:v>
+        <x:v>稳定</x:v>
       </x:c>
       <x:c r="I10" s="37" t="str">
-        <x:v>随身体左右镜像</x:v>
+        <x:v>保持握持</x:v>
       </x:c>
       <x:c r="J10" s="37" t="str">
         <x:v>低摆</x:v>
@@ -13417,7 +14318,7 @@
         <x:v>琥珀锁定环</x:v>
       </x:c>
       <x:c r="L10" s="37" t="str">
-        <x:v>2D/3D降亮 + 锁定环；输入锁转换一致</x:v>
+        <x:v>降亮 + 锁定环；保持刚性层级</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -13443,7 +14344,7 @@
         <x:v>随整体倾倒</x:v>
       </x:c>
       <x:c r="H11" s="37" t="str">
-        <x:v>不显示</x:v>
+        <x:v>随整体倾倒</x:v>
       </x:c>
       <x:c r="I11" s="37" t="str">
         <x:v>随整体倾倒</x:v>
@@ -13455,7 +14356,7 @@
         <x:v>HUD 终止</x:v>
       </x:c>
       <x:c r="L11" s="37" t="str">
-        <x:v>2D/3D终态守卫 + 整体倾倒</x:v>
+        <x:v>整体倾倒；耳朵与肢体跟随关节</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -13481,10 +14382,10 @@
         <x:v>不变</x:v>
       </x:c>
       <x:c r="H12" s="37" t="str">
-        <x:v>不显示</x:v>
+        <x:v>保持当前动作</x:v>
       </x:c>
       <x:c r="I12" s="37" t="str">
-        <x:v>保持当前朝向</x:v>
+        <x:v>保持当前动作</x:v>
       </x:c>
       <x:c r="J12" s="37" t="str">
         <x:v>不变</x:v>
@@ -13519,10 +14420,10 @@
         <x:v>传感器干扰</x:v>
       </x:c>
       <x:c r="H13" s="37" t="str">
-        <x:v>不显示</x:v>
+        <x:v>保持当前动作</x:v>
       </x:c>
       <x:c r="I13" s="37" t="str">
-        <x:v>保持当前朝向</x:v>
+        <x:v>保持当前动作</x:v>
       </x:c>
       <x:c r="J13" s="37" t="str">
         <x:v>不变</x:v>
@@ -13557,10 +14458,10 @@
         <x:v>闪烁</x:v>
       </x:c>
       <x:c r="H14" s="37" t="str">
-        <x:v>不显示</x:v>
+        <x:v>保持当前动作</x:v>
       </x:c>
       <x:c r="I14" s="37" t="str">
-        <x:v>保持当前朝向</x:v>
+        <x:v>保持当前动作</x:v>
       </x:c>
       <x:c r="J14" s="37" t="str">
         <x:v>闪烁</x:v>
@@ -13572,7 +14473,7 @@
         <x:v>InvincibleTimer 唯一解除</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="34" customHeight="1">
+    <x:row r="15" ht="56" customHeight="1">
       <x:c r="A15" s="63" t="str">
         <x:v>叠加</x:v>
       </x:c>
@@ -13595,10 +14496,10 @@
         <x:v>保持当前顶层</x:v>
       </x:c>
       <x:c r="H15" s="63" t="str">
-        <x:v>不显示</x:v>
+        <x:v>手枪左手近身取弹但不计握持；长枪左手离开护木服务</x:v>
       </x:c>
       <x:c r="I15" s="63" t="str">
-        <x:v>与weapon_socket同相下压/操作/回位</x:v>
+        <x:v>右手持续握把并跟随 WeaponSocket 下压/回位</x:v>
       </x:c>
       <x:c r="J15" s="63" t="str">
         <x:v>保持当前顶层</x:v>
@@ -13607,7 +14508,7 @@
         <x:v>3D头顶billboard进度条；2D弹药栏</x:v>
       </x:c>
       <x:c r="L15" s="63" t="str">
-        <x:v>WeaponModel3D唯一计时源；0→1；换枪/补弹/清空/死亡取消</x:v>
+        <x:v>WeaponModel3D 唯一计时源；WeaponPoseFSM 进入 sidearm_reload/longgun_reload；右手保持握把，左手按武器类型服务</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="28" customHeight="1">
@@ -14038,7 +14939,7 @@
       <x:c r="K29" s="82"/>
       <x:c r="L29" s="82"/>
     </x:row>
-    <x:row r="30" ht="38" customHeight="1">
+    <x:row r="30" ht="56" customHeight="1">
       <x:c r="A30" s="63" t="str">
         <x:v>叠加</x:v>
       </x:c>
@@ -14055,16 +14956,16 @@
         <x:v>短时回弹后退出</x:v>
       </x:c>
       <x:c r="F30" s="63" t="str">
-        <x:v>前探/压缩/回弹</x:v>
+        <x:v>前探/压缩/弹性回弹</x:v>
       </x:c>
       <x:c r="G30" s="63" t="str">
         <x:v>小幅前探</x:v>
       </x:c>
       <x:c r="H30" s="63" t="str">
-        <x:v>不显示</x:v>
+        <x:v>手枪左手不继承后坐；长枪左手托举并小幅刚性回弹</x:v>
       </x:c>
       <x:c r="I30" s="63" t="str">
-        <x:v>与weapon_socket同相后坐</x:v>
+        <x:v>右手握把跟随 WeaponSocket；手枪单腕上挑，长枪双手与躯干共同吃后坐</x:v>
       </x:c>
       <x:c r="J30" s="63" t="str">
         <x:v>受冲量轻摆</x:v>
@@ -14073,10 +14974,10 @@
         <x:v>枪口闪光/后坐</x:v>
       </x:c>
       <x:c r="L30" s="63" t="str">
-        <x:v>真实发射信号；0.14s基础弹性；不独立计时</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="38" customHeight="1">
+        <x:v>真实 shot_fired 信号；WeaponPoseFSM 进入 sidearm_fire/longgun_fire；七种枪体读取独立 fire_style、kick、pitch、roll、lift 参数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="56" customHeight="1">
       <x:c r="A31" s="63" t="str">
         <x:v>叠加</x:v>
       </x:c>
@@ -14099,10 +15000,10 @@
         <x:v>轻微压低</x:v>
       </x:c>
       <x:c r="H31" s="63" t="str">
-        <x:v>不显示</x:v>
+        <x:v>长枪左手向内压入形成张力；手枪保持自由手</x:v>
       </x:c>
       <x:c r="I31" s="63" t="str">
-        <x:v>与weapon_socket同相蓄势</x:v>
+        <x:v>右手握把与 WeaponSocket 同相蓄势</x:v>
       </x:c>
       <x:c r="J31" s="63" t="str">
         <x:v>低频张力摆动</x:v>
@@ -14111,10 +15012,10 @@
         <x:v>紫色能量提示（可选）</x:v>
       </x:c>
       <x:c r="L31" s="63" t="str">
-        <x:v>读取真实蓄力进度；禁用输入不取消脚本蓄力</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="38" customHeight="1">
+        <x:v>读取真实蓄力进度；WeaponPoseFSM 进入对应 charge 状态；释放后按枪体 profile 回弹</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="56" customHeight="1">
       <x:c r="A32" s="63" t="str">
         <x:v>叠加</x:v>
       </x:c>
@@ -14134,13 +15035,13 @@
         <x:v>反向位移/压缩/弹回</x:v>
       </x:c>
       <x:c r="G32" s="63" t="str">
-        <x:v>后仰/回正</x:v>
+        <x:v>夸张后仰甩头/回正</x:v>
       </x:c>
       <x:c r="H32" s="63" t="str">
-        <x:v>不显示</x:v>
+        <x:v>手枪自由左手外甩；长枪左手回护木</x:v>
       </x:c>
       <x:c r="I32" s="63" t="str">
-        <x:v>与weapon_socket同相后退/回正</x:v>
+        <x:v>右手与 WeaponSocket 同相后退/回正</x:v>
       </x:c>
       <x:c r="J32" s="63" t="str">
         <x:v>滞后甩动</x:v>
@@ -14149,7 +15050,7 @@
         <x:v>红闪/短轨迹</x:v>
       </x:c>
       <x:c r="L32" s="63" t="str">
-        <x:v>hurt 消费递减XZ冲量；不新增顶层状态</x:v>
+        <x:v>hurt 消费递减XZ冲量；双耳/双脚/双手分层过冲，不新增顶层状态</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
@@ -15715,6 +16616,52 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="20" ht="90" customHeight="1">
+      <x:c r="A20" s="63" t="str">
+        <x:v>v1.14</x:v>
+      </x:c>
+      <x:c r="B20" s="63" t="str">
+        <x:v>2026-07-29</x:v>
+      </x:c>
+      <x:c r="C20" s="63" t="str">
+        <x:v>兔子武器姿势与虚拟碰撞契约</x:v>
+      </x:c>
+      <x:c r="D20" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01 / PlayerAvatar3D / Player3D</x:v>
+      </x:c>
+      <x:c r="E20" s="63" t="str">
+        <x:v>登记圆环近端手腕轴心；手枪右侧单手、长枪右手握把+左手托举；hold/run/fire/reload/charge 武器姿势状态机；七枪差异后坐；模型零碰撞，根节点 1.80m 无耳虚拟盒</x:v>
+      </x:c>
+      <x:c r="F20" s="63" t="str">
+        <x:v>不新增 AssetID、不复制 GLB、不改 v004 Blender 源网格；仅更新运行时姿势、碰撞职责与验收契约</x:v>
+      </x:c>
+      <x:c r="G20" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="86" customHeight="1">
+      <x:c r="A21" s="63" t="str">
+        <x:v>v1.15</x:v>
+      </x:c>
+      <x:c r="B21" s="63" t="str">
+        <x:v>2026-07-29</x:v>
+      </x:c>
+      <x:c r="C21" s="63" t="str">
+        <x:v>兔子站立待机动画登记</x:v>
+      </x:c>
+      <x:c r="D21" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01 / PlayerAvatar3D / Player3DIdleState</x:v>
+      </x:c>
+      <x:c r="E21" s="63" t="str">
+        <x:v>复用既有六态 idle：登记约2.38s站立循环、呼吸挤压、重心换脚、头部滞后、双耳错相/偶发耳弹及持枪呼吸；移动时立即退出，停下后恢复</x:v>
+      </x:c>
+      <x:c r="F21" s="63" t="str">
+        <x:v>不新增顶层状态、不新增 AssetID、不改 Blender/GLB；仅强化 v004 运行时组件动画与自动验收</x:v>
+      </x:c>
+      <x:c r="G21" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G2"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8012e6c98da341e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R2690ce1b18a4437b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Ra74e98fe9d4b44de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R0d1b316386cb4d6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rde2f7627bc9f4bdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R05aaa99b8eed4ce5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R9ed6945929714d85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rd87daef3738f4d84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rfa174e7ffc124add"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R47d248961f194341"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R12e429ef18d940e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rc8c0553e1fd04b64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R48cd160bc7884cd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Refa81424dd8f4e53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R7b37cf83ba384acf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R33db02dcbd4d4d7e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -319,7 +319,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="96">
+  <x:cellXfs count="105">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -527,6 +527,33 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="22" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -900,7 +927,7 @@
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
         <x:f>COUNTIF('资产主表'!$K$6:$K$200,"待制作")+COUNTIF('资产主表'!$K$6:$K$200,"程序占位")</x:f>
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F6" s="43"/>
       <x:c r="G6" s="45" t="n">
@@ -1067,11 +1094,11 @@
       </x:c>
       <x:c r="B14" s="52" t="n">
         <x:f>COUNTIF('资产主表'!$C$6:$C$200,A14)</x:f>
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C14" s="52" t="n">
         <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A14,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A14,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D14" s="43"/>
       <x:c r="E14" s="51" t="str">
@@ -1097,7 +1124,7 @@
       </x:c>
       <x:c r="C15" s="52" t="n">
         <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A15,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A15,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D15" s="43"/>
       <x:c r="E15" s="43"/>
@@ -6406,72 +6433,72 @@
         <x:v>状态变体使用同一 AssetID + state，不复制新命名根</x:v>
       </x:c>
     </x:row>
-    <x:row r="79">
-      <x:c r="A79" s="37" t="str">
+    <x:row r="79" ht="155" customHeight="1">
+      <x:c r="A79" s="101" t="str">
         <x:v>UI-SCREEN-HUD</x:v>
       </x:c>
-      <x:c r="B79" s="37" t="str">
+      <x:c r="B79" s="101" t="str">
         <x:v>战斗 HUD</x:v>
       </x:c>
-      <x:c r="C79" s="37" t="str">
+      <x:c r="C79" s="101" t="str">
         <x:v>UI</x:v>
       </x:c>
-      <x:c r="D79" s="37" t="str">
+      <x:c r="D79" s="101" t="str">
         <x:v>screen</x:v>
       </x:c>
-      <x:c r="E79" s="37" t="str">
+      <x:c r="E79" s="101" t="str">
         <x:v>hud</x:v>
       </x:c>
-      <x:c r="F79" s="37" t="str">
+      <x:c r="F79" s="101" t="str">
         <x:v>root</x:v>
       </x:c>
-      <x:c r="G79" s="37" t="str"/>
-      <x:c r="H79" s="37" t="str">
+      <x:c r="G79" s="101" t="str"/>
+      <x:c r="H79" s="101" t="str">
         <x:v>屏幕空间</x:v>
       </x:c>
-      <x:c r="I79" s="37" t="str">
+      <x:c r="I79" s="101" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J79" s="37" t="str">
+      <x:c r="J79" s="101" t="str">
         <x:v>跨分辨率</x:v>
       </x:c>
-      <x:c r="K79" s="37" t="str">
-        <x:v>程序占位</x:v>
-      </x:c>
-      <x:c r="L79" s="37" t="str">
+      <x:c r="K79" s="101" t="str">
+        <x:v>已接入</x:v>
+      </x:c>
+      <x:c r="L79" s="101" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M79" s="37" t="str">
-        <x:v>v001</x:v>
-      </x:c>
-      <x:c r="N79" s="37" t="str">
+      <x:c r="M79" s="101" t="str">
+        <x:v>v002</x:v>
+      </x:c>
+      <x:c r="N79" s="101" t="str">
         <x:v>1280×720 基准；九宫格/矢量优先</x:v>
       </x:c>
-      <x:c r="O79" s="37" t="str"/>
-      <x:c r="P79" s="37" t="str">
+      <x:c r="O79" s="101" t="str"/>
+      <x:c r="P79" s="101" t="str">
         <x:v>src/ui/GameUIManager.gd</x:v>
       </x:c>
-      <x:c r="Q79" s="37" t="str"/>
-      <x:c r="R79" s="37" t="str">
+      <x:c r="Q79" s="101" t="str"/>
+      <x:c r="R79" s="101" t="str">
         <x:f>LOWER(TRIM(C79)&amp;"|"&amp;TRIM(D79)&amp;"|"&amp;TRIM(E79)&amp;"|"&amp;TRIM(F79)&amp;"|"&amp;TRIM(H79)&amp;"|"&amp;TRIM(I79))</x:f>
         <x:v>ui|screen|hud|root|屏幕空间|default</x:v>
       </x:c>
-      <x:c r="S79" s="37" t="str">
+      <x:c r="S79" s="101" t="str">
         <x:f>IF(A79="","",IF(COUNTIF($R$6:$R$162,R79)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T79" s="37" t="str"/>
-      <x:c r="U79" s="37" t="str">
+      <x:c r="T79" s="101" t="str"/>
+      <x:c r="U79" s="101" t="str">
         <x:v>待分配</x:v>
       </x:c>
-      <x:c r="V79" s="54" t="n">
-        <x:v>46224</x:v>
-      </x:c>
-      <x:c r="W79" s="37" t="str">
+      <x:c r="V79" s="104" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W79" s="101" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
-      <x:c r="X79" s="37" t="str">
-        <x:v>先建组件库，再做页面，避免每页重复画按钮/面板</x:v>
+      <x:c r="X79" s="101" t="str">
+        <x:v>PH49：主游戏HUD升级为深色半透明青色全息面板，危险/撤离信息使用琥珀与绿色分层；小地图以20Hz实时更新当前楼层，显示玩家位置与朝向、扫描扇区、脉冲环、透视网格、已发现房间/连线和楼层纵向索引。</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -8694,80 +8721,80 @@
       </x:c>
       <x:c r="X112" s="37" t="str"/>
     </x:row>
-    <x:row r="113">
-      <x:c r="A113" t="str">
+    <x:row r="113" ht="155" customHeight="1">
+      <x:c r="A113" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D</x:v>
       </x:c>
-      <x:c r="B113" t="str">
+      <x:c r="B113" s="70" t="str">
         <x:v>方形猫角色3D根组件</x:v>
       </x:c>
-      <x:c r="C113" t="str">
+      <x:c r="C113" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D113" t="str">
+      <x:c r="D113" s="70" t="str">
         <x:v>player</x:v>
       </x:c>
-      <x:c r="E113" t="str">
+      <x:c r="E113" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F113" t="str">
+      <x:c r="F113" s="70" t="str">
         <x:v>root_3d</x:v>
       </x:c>
-      <x:c r="G113" t="str">
+      <x:c r="G113" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01</x:v>
       </x:c>
-      <x:c r="H113" t="str">
+      <x:c r="H113" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I113" t="str">
+      <x:c r="I113" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J113" t="str">
+      <x:c r="J113" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K113" t="str">
+      <x:c r="K113" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L113" t="str">
+      <x:c r="L113" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M113" t="str">
+      <x:c r="M113" s="70" t="str">
         <x:v>v001</x:v>
       </x:c>
-      <x:c r="N113" t="str">
+      <x:c r="N113" s="70" t="str">
         <x:v>PackedScene/程序材质</x:v>
       </x:c>
-      <x:c r="O113" t="str">
+      <x:c r="O113" s="70" t="str">
         <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:v>
       </x:c>
-      <x:c r="P113" t="str">
+      <x:c r="P113" s="70" t="str">
         <x:v>scenes/Player3D.tscn</x:v>
       </x:c>
-      <x:c r="Q113" t="str">
+      <x:c r="Q113" s="70" t="str">
         <x:v>胶囊;防护服;3D;模块角色</x:v>
       </x:c>
-      <x:c r="R113" t="str">
+      <x:c r="R113" s="70" t="str">
         <x:f>LOWER(TRIM(C113)&amp;"|"&amp;TRIM(D113)&amp;"|"&amp;TRIM(E113)&amp;"|"&amp;TRIM(F113)&amp;"|"&amp;TRIM(H113)&amp;"|"&amp;TRIM(I113))</x:f>
         <x:v>角色|player|player_capsule01|root_3d|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S113" t="str">
+      <x:c r="S113" s="70" t="str">
         <x:f>IF(A113="","",IF(COUNTIF($R$6:$R$162,R113)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T113" t="str">
+      <x:c r="T113" s="70" t="str">
         <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
       </x:c>
-      <x:c r="U113" t="str">
+      <x:c r="U113" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V113" s="62" t="str">
-        <x:v>2026-07-25</x:v>
-      </x:c>
-      <x:c r="W113" t="str">
+      <x:c r="V113" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W113" s="70" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
-      <x:c r="X113" s="63" t="str">
-        <x:v>VisualRoot四主模块；方头/方身/方手/方脚；双眼双耳；圆短尾；六态与动作覆盖保持；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
+      <x:c r="X113" s="70" t="str">
+        <x:v>PH49：原先项目外shellstorm2-art/blender中的三份角色Blender源已按稳定命名归档到assets/art/characters/player/chr_player_capsule01_3d/source/，SHA-256与原件一致；运行时场景路径不变，后续不再依赖仓库外资产。</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -9226,80 +9253,80 @@
         <x:v>保留原2D布局语义；首张3D迁移地图</x:v>
       </x:c>
     </x:row>
-    <x:row r="120">
-      <x:c r="A120" t="str">
+    <x:row r="120" ht="155" customHeight="1">
+      <x:c r="A120" s="70" t="str">
         <x:v>PRP-BASE-FACILITY-3D</x:v>
       </x:c>
-      <x:c r="B120" t="str">
+      <x:c r="B120" s="70" t="str">
         <x:v>基地设施3D通用模块</x:v>
       </x:c>
-      <x:c r="C120" t="str">
+      <x:c r="C120" s="70" t="str">
         <x:v>场景道具</x:v>
       </x:c>
-      <x:c r="D120" t="str">
+      <x:c r="D120" s="70" t="str">
         <x:v>facility</x:v>
       </x:c>
-      <x:c r="E120" t="str">
+      <x:c r="E120" s="70" t="str">
         <x:v>base_facility_module</x:v>
       </x:c>
-      <x:c r="F120" t="str">
+      <x:c r="F120" s="70" t="str">
         <x:v>root_3d</x:v>
       </x:c>
-      <x:c r="G120" t="str">
+      <x:c r="G120" s="70" t="str">
         <x:v>ENV-BASE-WORLD-KIT-3D</x:v>
       </x:c>
-      <x:c r="H120" t="str">
+      <x:c r="H120" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I120" t="str">
+      <x:c r="I120" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J120" t="str">
+      <x:c r="J120" s="70" t="str">
         <x:v>8类基地设施</x:v>
       </x:c>
-      <x:c r="K120" t="str">
-        <x:v>原型已接入</x:v>
-      </x:c>
-      <x:c r="L120" t="str">
+      <x:c r="K120" s="70" t="str">
+        <x:v>已接入</x:v>
+      </x:c>
+      <x:c r="L120" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M120" t="str">
+      <x:c r="M120" s="70" t="str">
         <x:v>v001</x:v>
       </x:c>
-      <x:c r="N120" t="str">
+      <x:c r="N120" s="70" t="str">
         <x:v>PackedScene/材质变体</x:v>
       </x:c>
-      <x:c r="O120" t="str">
+      <x:c r="O120" s="70" t="str">
         <x:v>assets/art/props/base_world_3d/prp_base_facility_root_top3d_v001.tscn</x:v>
       </x:c>
-      <x:c r="P120" t="str">
+      <x:c r="P120" s="70" t="str">
         <x:v>src/base3d/BaseFacility3D.gd</x:v>
       </x:c>
-      <x:c r="Q120" t="str">
+      <x:c r="Q120" s="70" t="str">
         <x:v>设施;交互;信标;3D</x:v>
       </x:c>
-      <x:c r="R120" t="str">
+      <x:c r="R120" s="70" t="str">
         <x:f>LOWER(TRIM(C120)&amp;"|"&amp;TRIM(D120)&amp;"|"&amp;TRIM(E120)&amp;"|"&amp;TRIM(F120)&amp;"|"&amp;TRIM(H120)&amp;"|"&amp;TRIM(I120))</x:f>
         <x:v>场景道具|facility|base_facility_module|root_3d|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S120" t="str">
+      <x:c r="S120" s="70" t="str">
         <x:f>IF(A120="","",IF(COUNTIF($R$6:$R$162,R120)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T120" t="str">
+      <x:c r="T120" s="70" t="str">
         <x:v>18921dbda4e5997f5c49c6efa66b7af030310d5d086b60fe476e8f0e664e104e</x:v>
       </x:c>
-      <x:c r="U120" t="str">
+      <x:c r="U120" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V120" s="62" t="n">
-        <x:v>46224</x:v>
-      </x:c>
-      <x:c r="W120" t="str">
+      <x:c r="V120" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W120" s="70" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
-      <x:c r="X120" t="str">
-        <x:v>由配置生成8个设施变体；复用同一场景</x:v>
+      <x:c r="X120" s="70" t="str">
+        <x:v>PH49：BaseFacility3D复用于五个独立电梯设施（99—95层各一处），设施挂在走廊设施层级而非房间内部，放置在基地房间墙边或楼层走廊边。电梯解锁、目标楼层和到达点从邻接的elevator_access房间读取。</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -9454,78 +9481,78 @@
         <x:v>用于检查3D布局、镜头、组件比例与交互可读性</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="34" customHeight="1">
-      <x:c r="A123" s="63" t="str">
+    <x:row r="123" ht="155" customHeight="1">
+      <x:c r="A123" s="70" t="str">
         <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
       </x:c>
-      <x:c r="B123" s="63" t="str">
+      <x:c r="B123" s="70" t="str">
         <x:v>3D随机关卡通用房间套件</x:v>
       </x:c>
-      <x:c r="C123" s="63" t="str">
+      <x:c r="C123" s="70" t="str">
         <x:v>场景</x:v>
       </x:c>
-      <x:c r="D123" s="63" t="str">
+      <x:c r="D123" s="70" t="str">
         <x:v>room</x:v>
       </x:c>
-      <x:c r="E123" s="63" t="str">
+      <x:c r="E123" s="70" t="str">
         <x:v>dungeon_runtime</x:v>
       </x:c>
-      <x:c r="F123" s="63" t="str">
+      <x:c r="F123" s="70" t="str">
         <x:v>root_3d</x:v>
       </x:c>
-      <x:c r="G123" s="63"/>
-      <x:c r="H123" s="63" t="str">
+      <x:c r="G123" s="70"/>
+      <x:c r="H123" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I123" s="63" t="str">
+      <x:c r="I123" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J123" s="63" t="str">
+      <x:c r="J123" s="70" t="str">
         <x:v>四主题副本/随机房间</x:v>
       </x:c>
-      <x:c r="K123" s="63" t="str">
-        <x:v>原型已接入</x:v>
-      </x:c>
-      <x:c r="L123" s="63" t="str">
+      <x:c r="K123" s="70" t="str">
+        <x:v>已接入</x:v>
+      </x:c>
+      <x:c r="L123" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M123" s="63" t="str">
+      <x:c r="M123" s="70" t="str">
         <x:v>v001</x:v>
       </x:c>
-      <x:c r="N123" s="63" t="str">
+      <x:c r="N123" s="70" t="str">
         <x:v>PackedScene/三档程序几何</x:v>
       </x:c>
-      <x:c r="O123" s="63" t="str">
+      <x:c r="O123" s="70" t="str">
         <x:v>assets/art/environments/dungeon_3d/env_dungeon_runtime_kit_top3d_v001.tscn</x:v>
       </x:c>
-      <x:c r="P123" s="63" t="str">
+      <x:c r="P123" s="70" t="str">
         <x:v>src/world3d/DungeonRoom3D.gd</x:v>
       </x:c>
-      <x:c r="Q123" s="63" t="str">
+      <x:c r="Q123" s="70" t="str">
         <x:v>房间;门洞;走廊;随机地图;3D</x:v>
       </x:c>
-      <x:c r="R123" s="63" t="str">
+      <x:c r="R123" s="70" t="str">
         <x:f>LOWER(TRIM(C123)&amp;"|"&amp;TRIM(D123)&amp;"|"&amp;TRIM(E123)&amp;"|"&amp;TRIM(F123)&amp;"|"&amp;TRIM(H123)&amp;"|"&amp;TRIM(I123))</x:f>
         <x:v>场景|room|dungeon_runtime|root_3d|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S123" s="63" t="str">
+      <x:c r="S123" s="70" t="str">
         <x:f>IF(A123="","",IF(COUNTIF($R$6:$R$162,R123)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T123" s="63" t="str">
+      <x:c r="T123" s="70" t="str">
         <x:v>fc33ac084150c3e3cbba89505b3e04f35712abbceaa5cec297c94fe4d7dcc2f3</x:v>
       </x:c>
-      <x:c r="U123" s="63" t="str">
+      <x:c r="U123" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V123" s="64" t="n">
-        <x:v>46232</x:v>
-      </x:c>
-      <x:c r="W123" s="63" t="str">
+      <x:c r="V123" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W123" s="70" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
-      <x:c r="X123" s="63" t="str">
-        <x:v>small/medium/large；四向门；家具、搜索、服务、危险区共用根；PH34复用塔楼层。2026-07-29楼梯最终修正：TowerGeometry3D统一米制（门/楼道/梯宽4.0m、门外平台3.0m、第一跑10.0m、两跑中心距5.2m、护栏端部净口2.4m、楼板厚0.24m、层高6.0m）；十段路径重做为七节点U形模块；路径Y定义为可走顶面，修复入口+0.12m台阶；测试角色从屋顶门内真实走完整楼梯并进入设施层。验证：verify_tower_descent_flow.tscn与Apple M1 OpenGL实机画面通过（1819节点）。 PH35 Blender重制待确认：目标层高9m、楼顶111.803m见方、设施/战斗层67.082m见方；固定6m净宽三组件楼梯。确认前现有PH34 Godot运行时仍保持6m层高与50/30m楼层，不提前替换。</x:v>
+      <x:c r="X123" s="70" t="str">
+        <x:v>PH49：塔楼98—95层形成可闭环的搜打撤流程；普通层每层同时含战斗房和搜刮房，容器按种子掉落。Boss房清理后现在按房间类型正确解锁撤离，不再依赖固定room_id。生成快照增加门连通与全息小地图实时状态，测试覆盖100→99→98实机楼梯路径、95层Boss和撤离完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="34" customHeight="1">
@@ -9832,80 +9859,80 @@
         <x:v>复用通用房间根；主题资源不复制玩法规则</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="34" customHeight="1">
-      <x:c r="A128" s="63" t="str">
+    <x:row r="128" ht="155" customHeight="1">
+      <x:c r="A128" s="70" t="str">
         <x:v>PRP-WASTELAND-LIGHT-3D</x:v>
       </x:c>
-      <x:c r="B128" s="63" t="str">
+      <x:c r="B128" s="70" t="str">
         <x:v>废土灯具3D通用模块（街灯/顶灯）</x:v>
       </x:c>
-      <x:c r="C128" s="63" t="str">
+      <x:c r="C128" s="70" t="str">
         <x:v>场景道具</x:v>
       </x:c>
-      <x:c r="D128" s="63" t="str">
+      <x:c r="D128" s="70" t="str">
         <x:v>light</x:v>
       </x:c>
-      <x:c r="E128" s="63" t="str">
+      <x:c r="E128" s="70" t="str">
         <x:v>wasteland_light</x:v>
       </x:c>
-      <x:c r="F128" s="63" t="str">
+      <x:c r="F128" s="70" t="str">
         <x:v>root_3d</x:v>
       </x:c>
-      <x:c r="G128" s="63" t="str">
+      <x:c r="G128" s="70" t="str">
         <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
       </x:c>
-      <x:c r="H128" s="63" t="str">
+      <x:c r="H128" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I128" s="63" t="str">
+      <x:c r="I128" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J128" s="63" t="str">
+      <x:c r="J128" s="70" t="str">
         <x:v>关卡/靶场/房间中央照明</x:v>
       </x:c>
-      <x:c r="K128" s="63" t="str">
-        <x:v>原型已接入</x:v>
-      </x:c>
-      <x:c r="L128" s="63" t="str">
+      <x:c r="K128" s="70" t="str">
+        <x:v>已接入</x:v>
+      </x:c>
+      <x:c r="L128" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M128" s="63" t="str">
+      <x:c r="M128" s="70" t="str">
         <x:v>v001</x:v>
       </x:c>
-      <x:c r="N128" s="63" t="str">
+      <x:c r="N128" s="70" t="str">
         <x:v>PackedScene/OmniLight3D</x:v>
       </x:c>
-      <x:c r="O128" s="63" t="str">
+      <x:c r="O128" s="70" t="str">
         <x:v>assets/art/props/dungeon_3d/prp_wasteland_light_root_top3d_v001.tscn</x:v>
       </x:c>
-      <x:c r="P128" s="63" t="str">
+      <x:c r="P128" s="70" t="str">
         <x:v>src/world3d/WastelandLight3D.gd</x:v>
       </x:c>
-      <x:c r="Q128" s="63" t="str">
+      <x:c r="Q128" s="70" t="str">
         <x:v>灯具;街灯;中央顶灯;故障灯;废土</x:v>
       </x:c>
-      <x:c r="R128" s="63" t="str">
+      <x:c r="R128" s="70" t="str">
         <x:f>LOWER(TRIM(C128)&amp;"|"&amp;TRIM(D128)&amp;"|"&amp;TRIM(E128)&amp;"|"&amp;TRIM(F128)&amp;"|"&amp;TRIM(H128)&amp;"|"&amp;TRIM(I128))</x:f>
         <x:v>场景道具|light|wasteland_light|root_3d|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S128" s="63" t="str">
+      <x:c r="S128" s="70" t="str">
         <x:f>IF(A128="","",IF(COUNTIF($R$6:$R$162,R128)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T128" s="63" t="str">
+      <x:c r="T128" s="70" t="str">
         <x:v>0a6ec0add8b6e01b83f4dbaae421ff0dc69ed08648d304bac061f540af27d99b</x:v>
       </x:c>
-      <x:c r="U128" s="63" t="str">
+      <x:c r="U128" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V128" s="64" t="n">
-        <x:v>46225</x:v>
-      </x:c>
-      <x:c r="W128" s="63" t="str">
+      <x:c r="V128" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W128" s="70" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
-      <x:c r="X128" s="63" t="str">
-        <x:v>同根支持street/ceiling；房间只实例化唯一中央顶灯，默认关闭并由墙面开关控制；PH28开启能量较旧基线提高约22%</x:v>
+      <x:c r="X128" s="70" t="str">
+        <x:v>PH49：灯具最大作用范围提升到64m；普通房按房间短边约94%设置可感知范围并提高能量。基地采用四盏冷暖混合顶灯、26m范围；95层90m Boss区采用四区顶灯。两者默认开启但都保留墙边总开关，楼梯大厅也提供基础照明。</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="34" customHeight="1">
@@ -10962,80 +10989,80 @@
         <x:v>三张3D地图共用；Esc先关闭最上层模态，再进入真实暂停</x:v>
       </x:c>
     </x:row>
-    <x:row r="143">
-      <x:c r="A143" t="str">
+    <x:row r="143" ht="155" customHeight="1">
+      <x:c r="A143" s="70" t="str">
         <x:v>PRP-ROOM-LIGHT-SWITCH-3D</x:v>
       </x:c>
-      <x:c r="B143" t="str">
+      <x:c r="B143" s="70" t="str">
         <x:v>房间中央灯墙面开关3D</x:v>
       </x:c>
-      <x:c r="C143" t="str">
+      <x:c r="C143" s="70" t="str">
         <x:v>场景道具</x:v>
       </x:c>
-      <x:c r="D143" t="str">
+      <x:c r="D143" s="70" t="str">
         <x:v>facility</x:v>
       </x:c>
-      <x:c r="E143" t="str">
+      <x:c r="E143" s="70" t="str">
         <x:v>room_light_switch</x:v>
       </x:c>
-      <x:c r="F143" t="str">
+      <x:c r="F143" s="70" t="str">
         <x:v>root_3d</x:v>
       </x:c>
-      <x:c r="G143" t="str">
+      <x:c r="G143" s="70" t="str">
         <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
       </x:c>
-      <x:c r="H143" t="str">
+      <x:c r="H143" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I143" t="str">
+      <x:c r="I143" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J143" t="str">
+      <x:c r="J143" s="70" t="str">
         <x:v>随机关卡房间/四主题复用</x:v>
       </x:c>
-      <x:c r="K143" t="str">
-        <x:v>原型已接入</x:v>
-      </x:c>
-      <x:c r="L143" t="str">
+      <x:c r="K143" s="70" t="str">
+        <x:v>已接入</x:v>
+      </x:c>
+      <x:c r="L143" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M143" t="str">
+      <x:c r="M143" s="70" t="str">
         <x:v>v001</x:v>
       </x:c>
-      <x:c r="N143" t="str">
+      <x:c r="N143" s="70" t="str">
         <x:v>PackedScene/Area3D</x:v>
       </x:c>
-      <x:c r="O143" t="str">
+      <x:c r="O143" s="70" t="str">
         <x:v>assets/art/props/dungeon_3d/prp_room_light_switch_root_top3d_v001.tscn</x:v>
       </x:c>
-      <x:c r="P143" t="str">
+      <x:c r="P143" s="70" t="str">
         <x:v>src/world3d/RoomLightSwitch3D.gd</x:v>
       </x:c>
-      <x:c r="Q143" t="str">
+      <x:c r="Q143" s="70" t="str">
         <x:v>房灯开关;墙面交互;中央顶灯;E键</x:v>
       </x:c>
-      <x:c r="R143" t="str">
+      <x:c r="R143" s="70" t="str">
         <x:f>LOWER(TRIM(C143)&amp;"|"&amp;TRIM(D143)&amp;"|"&amp;TRIM(E143)&amp;"|"&amp;TRIM(F143)&amp;"|"&amp;TRIM(H143)&amp;"|"&amp;TRIM(I143))</x:f>
         <x:v>场景道具|facility|room_light_switch|root_3d|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S143" t="str">
+      <x:c r="S143" s="70" t="str">
         <x:f>IF(A143="","",IF(COUNTIF($R$6:$R$162,R143)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T143" t="str">
+      <x:c r="T143" s="70" t="str">
         <x:v>7802bc3a71d892072e43962875e26b60443d19de35bcc77fe0cbedcfa6dd5d94</x:v>
       </x:c>
-      <x:c r="U143" t="str">
+      <x:c r="U143" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V143" s="62" t="n">
-        <x:v>46225</x:v>
-      </x:c>
-      <x:c r="W143" t="str">
+      <x:c r="V143" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W143" s="70" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
-      <x:c r="X143" t="str">
-        <x:v>每个房间共用一件；E键切换唯一中央顶灯；禁止复制到各主题局部目录</x:v>
+      <x:c r="X143" s="70" t="str">
+        <x:v>PH49：开关新增灯组控制，同一开关可统一切换多盏房间灯；基地四灯共用一个墙边开关并在快照中报告控制灯数量。单灯房继续兼容原接口。</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -11950,611 +11977,1058 @@
         <x:v>方形猫角色3D脚部DIY变体；复用CHR-PLY-CAPSULE01-3D玩家根；方形主语言，TailStub为用户指定圆尾例外；自动与视觉验收PASS</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="88" customHeight="1">
-      <x:c r="A156" s="63" t="str">
+    <x:row r="156" ht="132" customHeight="1">
+      <x:c r="A156" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
       </x:c>
-      <x:c r="B156" s="63" t="str">
+      <x:c r="B156" s="70" t="str">
         <x:v>兔子主角3D根变体</x:v>
       </x:c>
-      <x:c r="C156" s="63" t="str">
+      <x:c r="C156" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D156" s="63" t="str">
+      <x:c r="D156" s="70" t="str">
         <x:v>player_variant</x:v>
       </x:c>
-      <x:c r="E156" s="63" t="str">
+      <x:c r="E156" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F156" s="63" t="str">
+      <x:c r="F156" s="70" t="str">
         <x:v>root_3d_bunny01</x:v>
       </x:c>
-      <x:c r="G156" s="63" t="str">
+      <x:c r="G156" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D</x:v>
       </x:c>
-      <x:c r="H156" s="63" t="str">
+      <x:c r="H156" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I156" s="63" t="str">
+      <x:c r="I156" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J156" s="63" t="str">
+      <x:c r="J156" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K156" s="63" t="str">
+      <x:c r="K156" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L156" s="63" t="str">
+      <x:c r="L156" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M156" s="63" t="str">
-        <x:v>v004</x:v>
-      </x:c>
-      <x:c r="N156" s="63" t="str">
-        <x:v>1.705×2.475×1.064 m</x:v>
-      </x:c>
-      <x:c r="O156" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v004.tscn</x:v>
-      </x:c>
-      <x:c r="P156" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
-      </x:c>
-      <x:c r="Q156" s="63" t="str">
+      <x:c r="M156" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N156" s="70" t="str">
+        <x:v>1.034×1.500×0.645 m / 完整视觉含耳</x:v>
+      </x:c>
+      <x:c r="O156" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v006.tscn</x:v>
+      </x:c>
+      <x:c r="P156" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="Q156" s="70" t="str">
         <x:v>兔子;主角;兔耳;3D;Blender;bunny01</x:v>
       </x:c>
-      <x:c r="R156" s="63" t="str">
+      <x:c r="R156" s="70" t="str">
         <x:f>LOWER(TRIM(C156)&amp;"|"&amp;TRIM(D156)&amp;"|"&amp;TRIM(E156)&amp;"|"&amp;TRIM(F156)&amp;"|"&amp;TRIM(H156)&amp;"|"&amp;TRIM(I156))</x:f>
         <x:v>角色|player_variant|player_capsule01|root_3d_bunny01|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S156" s="63" t="str">
+      <x:c r="S156" s="70" t="str">
         <x:f>IF(A156="","",IF(COUNTIF($R$6:$R$162,R156)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T156" s="63" t="str">
-        <x:v>2c34f9d637b480321fc287cb9a72d8d5d633a3aa3976ff0fbb21d3d7c8f9e621</x:v>
-      </x:c>
-      <x:c r="U156" s="63" t="str">
+      <x:c r="T156" s="70" t="str">
+        <x:v>b88839fbe76eedddd48933ac1807867e7a4efbd683de36475215679d26e84998</x:v>
+      </x:c>
+      <x:c r="U156" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V156" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="W156" s="63" t="str">
+      <x:c r="V156" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W156" s="70" t="str">
         <x:v>用户提供 Blender 源文件 / Codex 模块化拆分</x:v>
       </x:c>
-      <x:c r="X156" s="63" t="str">
-        <x:v>v004 行为契约修正（网格、源文件与 AssetID 不变）：手部圆环定义为近端手腕轴心，球体为远端手掌；手枪在角色右侧单手握持，长枪右手握把、左手托举；hold/run/fire/reload/charge 由武器姿势状态机分离，七种枪体使用数据化差异后坐。六态状态机既有 idle 现驱动约 2.38s 站立循环：呼吸挤压、慢速重心换脚、头部反向滞后、双耳错相与偶发耳弹，移动输入出现即退出，停止后恢复。模型层级零碰撞；Player3D 根节点使用不可见 BoxShape3D 0.86×1.80×0.72m，顶部 1.80m ≤ 无耳头顶 1.820592m。自动与视觉验收 PASS。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157" ht="58" customHeight="1">
-      <x:c r="A157" s="63" t="str">
+      <x:c r="X156" s="70" t="str">
+        <x:v>PH43：继续复用v006 1.5m模型与稳定AssetID；Player3D玩法碰撞升级为高1.5m、半径0.34m的VirtualCollisionCapsule。顶层状态扩展为idle/moving/dashing/hurt/locked/falling/landing/dead；下落收腿、耳后扬与落地压缩/回弹均由既有刚性节点程序驱动，不新增GLB或贴图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="118" customHeight="1">
+      <x:c r="A157" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-BODY</x:v>
       </x:c>
-      <x:c r="B157" s="63" t="str">
+      <x:c r="B157" s="70" t="str">
         <x:v>兔子主角3D身体</x:v>
       </x:c>
-      <x:c r="C157" s="63" t="str">
+      <x:c r="C157" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D157" s="63" t="str">
+      <x:c r="D157" s="70" t="str">
         <x:v>player_component</x:v>
       </x:c>
-      <x:c r="E157" s="63" t="str">
+      <x:c r="E157" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F157" s="63" t="str">
+      <x:c r="F157" s="70" t="str">
         <x:v>body_3d_bunny01</x:v>
       </x:c>
-      <x:c r="G157" s="63" t="str">
+      <x:c r="G157" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
       </x:c>
-      <x:c r="H157" s="63" t="str">
+      <x:c r="H157" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I157" s="63" t="str">
+      <x:c r="I157" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J157" s="63" t="str">
+      <x:c r="J157" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K157" s="63" t="str">
+      <x:c r="K157" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L157" s="63" t="str">
+      <x:c r="L157" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M157" s="63" t="str">
-        <x:v>v004</x:v>
-      </x:c>
-      <x:c r="N157" s="63" t="str">
-        <x:v>GLB / 1,958 verts / pivot-local</x:v>
-      </x:c>
-      <x:c r="O157" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="P157" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
-      </x:c>
-      <x:c r="Q157" s="63" t="str">
+      <x:c r="M157" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N157" s="70" t="str">
+        <x:v>GLB / 1,958 verts / pivot-local / 1.5m总高比例</x:v>
+      </x:c>
+      <x:c r="O157" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="P157" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="Q157" s="70" t="str">
         <x:v>兔子;身体;服装;body;bunny01</x:v>
       </x:c>
-      <x:c r="R157" s="63" t="str">
+      <x:c r="R157" s="70" t="str">
         <x:f>LOWER(TRIM(C157)&amp;"|"&amp;TRIM(D157)&amp;"|"&amp;TRIM(E157)&amp;"|"&amp;TRIM(F157)&amp;"|"&amp;TRIM(H157)&amp;"|"&amp;TRIM(I157))</x:f>
         <x:v>角色|player_component|player_capsule01|body_3d_bunny01|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S157" s="63" t="str">
+      <x:c r="S157" s="70" t="str">
         <x:f>IF(A157="","",IF(COUNTIF($R$6:$R$162,R157)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T157" s="63" t="str">
-        <x:v>632b9e9832d5fbd367d3b4682035732ec43cfc02b797cb4f09a309099c9e42c1</x:v>
-      </x:c>
-      <x:c r="U157" s="63" t="str">
+      <x:c r="T157" s="70" t="str">
+        <x:v>c574d76e0f19c1aaa4bee5f427a81028d7b3f0f50299f67b4dbf02a60fc5668d</x:v>
+      </x:c>
+      <x:c r="U157" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V157" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="W157" s="63" t="str">
+      <x:c r="V157" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W157" s="70" t="str">
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
-      <x:c r="X157" s="63" t="str">
-        <x:v>BunnyRig/BodyJoint；底部中心原点；支持呼吸、突进压缩、完整翻滚和受击挤压回弹。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158" ht="58" customHeight="1">
-      <x:c r="A158" s="63" t="str">
+      <x:c r="X157" s="70" t="str">
+        <x:v>PH41 v006：身体网格与底部中心原点从v005等比放大1.5倍；Godot BodyJoint=(-0.000030,0.155022,-0.000635)。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="118" customHeight="1">
+      <x:c r="A158" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-HEAD</x:v>
       </x:c>
-      <x:c r="B158" s="63" t="str">
+      <x:c r="B158" s="70" t="str">
         <x:v>兔子主角3D头部</x:v>
       </x:c>
-      <x:c r="C158" s="63" t="str">
+      <x:c r="C158" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D158" s="63" t="str">
+      <x:c r="D158" s="70" t="str">
         <x:v>player_component</x:v>
       </x:c>
-      <x:c r="E158" s="63" t="str">
+      <x:c r="E158" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F158" s="63" t="str">
+      <x:c r="F158" s="70" t="str">
         <x:v>head_3d_bunny01</x:v>
       </x:c>
-      <x:c r="G158" s="63" t="str">
+      <x:c r="G158" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
       </x:c>
-      <x:c r="H158" s="63" t="str">
+      <x:c r="H158" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I158" s="63" t="str">
+      <x:c r="I158" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J158" s="63" t="str">
+      <x:c r="J158" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K158" s="63" t="str">
+      <x:c r="K158" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L158" s="63" t="str">
+      <x:c r="L158" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M158" s="63" t="str">
-        <x:v>v004</x:v>
-      </x:c>
-      <x:c r="N158" s="63" t="str">
-        <x:v>GLB / 5,936 verts / pivot-local</x:v>
-      </x:c>
-      <x:c r="O158" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="P158" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
-      </x:c>
-      <x:c r="Q158" s="63" t="str">
+      <x:c r="M158" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N158" s="70" t="str">
+        <x:v>GLB / 5,936 verts / pivot-local / 头顶1.103390m</x:v>
+      </x:c>
+      <x:c r="O158" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="P158" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="Q158" s="70" t="str">
         <x:v>兔子;头部;head;bunny01</x:v>
       </x:c>
-      <x:c r="R158" s="63" t="str">
+      <x:c r="R158" s="70" t="str">
         <x:f>LOWER(TRIM(C158)&amp;"|"&amp;TRIM(D158)&amp;"|"&amp;TRIM(E158)&amp;"|"&amp;TRIM(F158)&amp;"|"&amp;TRIM(H158)&amp;"|"&amp;TRIM(I158))</x:f>
         <x:v>角色|player_component|player_capsule01|head_3d_bunny01|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S158" s="63" t="str">
+      <x:c r="S158" s="70" t="str">
         <x:f>IF(A158="","",IF(COUNTIF($R$6:$R$162,R158)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T158" s="63" t="str">
-        <x:v>4255cfdc374dc97a75d3386444edbd8c523ca174b9fc32b5c5fe48b9aedb4d1c</x:v>
-      </x:c>
-      <x:c r="U158" s="63" t="str">
+      <x:c r="T158" s="70" t="str">
+        <x:v>b8db86c722bb2ae4d760b8219051f492251f6b9fa29882c8e32453b020973c24</x:v>
+      </x:c>
+      <x:c r="U158" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V158" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="W158" s="63" t="str">
+      <x:c r="V158" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W158" s="70" t="str">
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
-      <x:c r="X158" s="63" t="str">
-        <x:v>BunnyRig/HeadJoint；头部下沿中心原点；耳朵通过 Head 子挂点装配；受击时承担夸张甩头和过冲回正。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159" ht="58" customHeight="1">
-      <x:c r="A159" s="63" t="str">
+      <x:c r="X158" s="70" t="str">
+        <x:v>PH41 v006：头部与下沿中心原点真实1.5倍；不含耳头顶1.103390m，完整双耳顶部1.500m。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="118" customHeight="1">
+      <x:c r="A159" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-EARS</x:v>
       </x:c>
-      <x:c r="B159" s="63" t="str">
+      <x:c r="B159" s="70" t="str">
         <x:v>兔子主角3D双耳配件</x:v>
       </x:c>
-      <x:c r="C159" s="63" t="str">
+      <x:c r="C159" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D159" s="63" t="str">
+      <x:c r="D159" s="70" t="str">
         <x:v>player_accessory</x:v>
       </x:c>
-      <x:c r="E159" s="63" t="str">
+      <x:c r="E159" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F159" s="63" t="str">
+      <x:c r="F159" s="70" t="str">
         <x:v>ears_3d_bunny01</x:v>
       </x:c>
-      <x:c r="G159" s="63" t="str">
+      <x:c r="G159" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-HEAD</x:v>
       </x:c>
-      <x:c r="H159" s="63" t="str">
+      <x:c r="H159" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I159" s="63" t="str">
+      <x:c r="I159" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J159" s="63" t="str">
+      <x:c r="J159" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K159" s="63" t="str">
+      <x:c r="K159" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L159" s="63" t="str">
+      <x:c r="L159" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M159" s="63" t="str">
-        <x:v>v004</x:v>
-      </x:c>
-      <x:c r="N159" s="63" t="str">
-        <x:v>单 GLB / 1,536 verts / pivot-local</x:v>
-      </x:c>
-      <x:c r="O159" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="P159" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
-      </x:c>
-      <x:c r="Q159" s="63" t="str">
+      <x:c r="M159" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N159" s="70" t="str">
+        <x:v>单 GLB / 1,536 verts / pivot-local / 双实例</x:v>
+      </x:c>
+      <x:c r="O159" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="P159" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="Q159" s="70" t="str">
         <x:v>兔耳;耳朵;耳部配件;EarSocketL;EarSocketR;bunny01</x:v>
       </x:c>
-      <x:c r="R159" s="63" t="str">
+      <x:c r="R159" s="70" t="str">
         <x:f>LOWER(TRIM(C159)&amp;"|"&amp;TRIM(D159)&amp;"|"&amp;TRIM(E159)&amp;"|"&amp;TRIM(F159)&amp;"|"&amp;TRIM(H159)&amp;"|"&amp;TRIM(I159))</x:f>
         <x:v>角色|player_accessory|player_capsule01|ears_3d_bunny01|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S159" s="63" t="str">
+      <x:c r="S159" s="70" t="str">
         <x:f>IF(A159="","",IF(COUNTIF($R$6:$R$162,R159)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T159" s="63" t="str">
-        <x:v>c768ac511df6636ba66ca3153b06a5348bffd2e6bfeed0f49c922ada982393ef</x:v>
-      </x:c>
-      <x:c r="U159" s="63" t="str">
+      <x:c r="T159" s="70" t="str">
+        <x:v>ed3c7abe283166648fafb43373c1dc2222bf9134f3d7bb8e0ebd8d3a05242ebf</x:v>
+      </x:c>
+      <x:c r="U159" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V159" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="W159" s="63" t="str">
+      <x:c r="V159" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W159" s="70" t="str">
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
-      <x:c r="X159" s="63" t="str">
-        <x:v>单个语义右耳局部模型；Godot EarSocketR 直接复用，EarSocketL 运行时 -X 镜像；耳根原点用于后压、收耳和甩动。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" ht="72" customHeight="1">
-      <x:c r="A160" s="63" t="str">
+      <x:c r="X159" s="70" t="str">
+        <x:v>PH41 v006：耳朵网格与耳根原点真实1.5倍；左右挂点复用单资产，装配后最高点严格1.500m。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="118" customHeight="1">
+      <x:c r="A160" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-HAND</x:v>
       </x:c>
-      <x:c r="B160" s="63" t="str">
+      <x:c r="B160" s="70" t="str">
         <x:v>兔子主角3D双爪表现组件</x:v>
       </x:c>
-      <x:c r="C160" s="63" t="str">
+      <x:c r="C160" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D160" s="63" t="str">
+      <x:c r="D160" s="70" t="str">
         <x:v>player_component</x:v>
       </x:c>
-      <x:c r="E160" s="63" t="str">
+      <x:c r="E160" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F160" s="63" t="str">
+      <x:c r="F160" s="70" t="str">
         <x:v>hand_3d_bunny01</x:v>
       </x:c>
-      <x:c r="G160" s="63" t="str">
+      <x:c r="G160" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
       </x:c>
-      <x:c r="H160" s="63" t="str">
+      <x:c r="H160" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I160" s="63" t="str">
+      <x:c r="I160" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J160" s="63" t="str">
+      <x:c r="J160" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K160" s="63" t="str">
+      <x:c r="K160" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L160" s="63" t="str">
+      <x:c r="L160" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M160" s="63" t="str">
-        <x:v>v004</x:v>
-      </x:c>
-      <x:c r="N160" s="63" t="str">
-        <x:v>双 GLB / 左右各 1,058 verts / pivot-local</x:v>
-      </x:c>
-      <x:c r="O160" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v004.glb; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_r_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="P160" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
-      </x:c>
-      <x:c r="Q160" s="63" t="str">
+      <x:c r="M160" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N160" s="70" t="str">
+        <x:v>双 GLB / 左右各1,058 verts / pivot-local / 1.5m角色比例</x:v>
+      </x:c>
+      <x:c r="O160" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v006.glb; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_r_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="P160" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="Q160" s="70" t="str">
         <x:v>兔爪;手;握持;weapon_socket;bunny01</x:v>
       </x:c>
-      <x:c r="R160" s="63" t="str">
+      <x:c r="R160" s="70" t="str">
         <x:f>LOWER(TRIM(C160)&amp;"|"&amp;TRIM(D160)&amp;"|"&amp;TRIM(E160)&amp;"|"&amp;TRIM(F160)&amp;"|"&amp;TRIM(H160)&amp;"|"&amp;TRIM(I160))</x:f>
         <x:v>角色|player_component|player_capsule01|hand_3d_bunny01|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S160" s="63" t="str">
+      <x:c r="S160" s="70" t="str">
         <x:f>IF(A160="","",IF(COUNTIF($R$6:$R$162,R160)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T160" s="63" t="str">
-        <x:v>6171ea35985b712446983d7c5fa27ae8c248e4516f487c709a302de6e845d088 / d421b98ded85d9580ad41189ab6fd3095f579447c1ef64ef659e87b6ec72581e</x:v>
-      </x:c>
-      <x:c r="U160" s="63" t="str">
+      <x:c r="T160" s="70" t="str">
+        <x:v>2c6647c0e4f234e9312ba65e7c73f55c02627be9b7a2c35d1591d86a20cb5f16 / b3ada7b67d0224156d1c39af0bdc0e53af02cb5d26ba68d4746b7859a84a1d10</x:v>
+      </x:c>
+      <x:c r="U160" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V160" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="W160" s="63" t="str">
+      <x:c r="V160" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W160" s="70" t="str">
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
-      <x:c r="X160" s="63" t="str">
-        <x:v>BunnyRig/HandRoot/HandJointL/R；圆环=近端手腕/动画轴心，球体=远端手掌。手枪仅右手握持且置于角色右侧，左手自由摆动；长枪右手握把、左手托举；跑步、射击、换弹、蓄力分别由武器姿势状态管理，手枪/霰弹/步枪/机枪/狙击/发射器/蓄力枪具备差异后坐参数。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" ht="58" customHeight="1">
-      <x:c r="A161" s="63" t="str">
+      <x:c r="X160" s="70" t="str">
+        <x:v>PH41 v006：左右手、手腕原点、单/双手握持目标和动作平移统一改用0.606060606米制比例；持枪外观与确认预览一致。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="132" customHeight="1">
+      <x:c r="A161" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-FOOT-L</x:v>
       </x:c>
-      <x:c r="B161" s="63" t="str">
+      <x:c r="B161" s="70" t="str">
         <x:v>兔子主角3D左脚</x:v>
       </x:c>
-      <x:c r="C161" s="63" t="str">
+      <x:c r="C161" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D161" s="63" t="str">
+      <x:c r="D161" s="70" t="str">
         <x:v>player_component</x:v>
       </x:c>
-      <x:c r="E161" s="63" t="str">
+      <x:c r="E161" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F161" s="63" t="str">
+      <x:c r="F161" s="70" t="str">
         <x:v>foot_l_3d_bunny01</x:v>
       </x:c>
-      <x:c r="G161" s="63" t="str">
+      <x:c r="G161" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
       </x:c>
-      <x:c r="H161" s="63" t="str">
+      <x:c r="H161" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I161" s="63" t="str">
+      <x:c r="I161" s="70" t="str">
         <x:v>moving</x:v>
       </x:c>
-      <x:c r="J161" s="63" t="str">
+      <x:c r="J161" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K161" s="63" t="str">
+      <x:c r="K161" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L161" s="63" t="str">
+      <x:c r="L161" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M161" s="63" t="str">
-        <x:v>v004</x:v>
-      </x:c>
-      <x:c r="N161" s="63" t="str">
-        <x:v>GLB / 5,396 verts / pivot-local</x:v>
-      </x:c>
-      <x:c r="O161" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="P161" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
-      </x:c>
-      <x:c r="Q161" s="63" t="str">
+      <x:c r="M161" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N161" s="70" t="str">
+        <x:v>GLB / 5,396 verts / pivot-local / 1.5m角色比例</x:v>
+      </x:c>
+      <x:c r="O161" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="P161" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="Q161" s="70" t="str">
         <x:v>兔脚;左脚;步态;FootL;bunny01</x:v>
       </x:c>
-      <x:c r="R161" s="63" t="str">
+      <x:c r="R161" s="70" t="str">
         <x:f>LOWER(TRIM(C161)&amp;"|"&amp;TRIM(D161)&amp;"|"&amp;TRIM(E161)&amp;"|"&amp;TRIM(F161)&amp;"|"&amp;TRIM(H161)&amp;"|"&amp;TRIM(I161))</x:f>
         <x:v>角色|player_component|player_capsule01|foot_l_3d_bunny01|俯视3d|moving</x:v>
       </x:c>
-      <x:c r="S161" s="63" t="str">
+      <x:c r="S161" s="70" t="str">
         <x:f>IF(A161="","",IF(COUNTIF($R$6:$R$162,R161)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T161" s="63" t="str">
-        <x:v>ba37215c7a03dae202dd03c6b2151b179dae0bfca345142bf7b0bd6268203251</x:v>
-      </x:c>
-      <x:c r="U161" s="63" t="str">
+      <x:c r="T161" s="70" t="str">
+        <x:v>52051cba0db701d977c8baa8d7ed9899825b10406803ac63e6a3f66efbd80b64</x:v>
+      </x:c>
+      <x:c r="U161" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V161" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="W161" s="63" t="str">
+      <x:c r="V161" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W161" s="70" t="str">
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
-      <x:c r="X161" s="63" t="str">
-        <x:v>BunnyRig/FeetRoot/FootJointL；脚底中心原点；支持交替步态、翻滚收腿、受击甩脚和落地挤压。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162" ht="58" customHeight="1">
-      <x:c r="A162" s="63" t="str">
+      <x:c r="X161" s="70" t="str">
+        <x:v>PH43：v006网格与AssetID不变；FootJointL除moving步态外新增falling收腿与landing压缩恢复职责，动作由PlayerAvatar3D程序变换驱动。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="132" customHeight="1">
+      <x:c r="A162" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-FOOT-R</x:v>
       </x:c>
-      <x:c r="B162" s="63" t="str">
+      <x:c r="B162" s="70" t="str">
         <x:v>兔子主角3D右脚</x:v>
       </x:c>
-      <x:c r="C162" s="63" t="str">
+      <x:c r="C162" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D162" s="63" t="str">
+      <x:c r="D162" s="70" t="str">
         <x:v>player_component</x:v>
       </x:c>
-      <x:c r="E162" s="63" t="str">
+      <x:c r="E162" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F162" s="63" t="str">
+      <x:c r="F162" s="70" t="str">
         <x:v>foot_r_3d_bunny01</x:v>
       </x:c>
-      <x:c r="G162" s="63" t="str">
+      <x:c r="G162" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
       </x:c>
-      <x:c r="H162" s="63" t="str">
+      <x:c r="H162" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I162" s="63" t="str">
+      <x:c r="I162" s="70" t="str">
         <x:v>moving</x:v>
       </x:c>
-      <x:c r="J162" s="63" t="str">
+      <x:c r="J162" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K162" s="63" t="str">
+      <x:c r="K162" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L162" s="63" t="str">
+      <x:c r="L162" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M162" s="63" t="str">
-        <x:v>v004</x:v>
-      </x:c>
-      <x:c r="N162" s="63" t="str">
-        <x:v>GLB / 5,396 verts / pivot-local</x:v>
-      </x:c>
-      <x:c r="O162" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="P162" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
-      </x:c>
-      <x:c r="Q162" s="63" t="str">
+      <x:c r="M162" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N162" s="70" t="str">
+        <x:v>GLB / 5,396 verts / pivot-local / 1.5m角色比例</x:v>
+      </x:c>
+      <x:c r="O162" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="P162" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="Q162" s="70" t="str">
         <x:v>兔脚;右脚;步态;FootR;bunny01</x:v>
       </x:c>
-      <x:c r="R162" s="63" t="str">
+      <x:c r="R162" s="70" t="str">
         <x:f>LOWER(TRIM(C162)&amp;"|"&amp;TRIM(D162)&amp;"|"&amp;TRIM(E162)&amp;"|"&amp;TRIM(F162)&amp;"|"&amp;TRIM(H162)&amp;"|"&amp;TRIM(I162))</x:f>
         <x:v>角色|player_component|player_capsule01|foot_r_3d_bunny01|俯视3d|moving</x:v>
       </x:c>
-      <x:c r="S162" s="63" t="str">
+      <x:c r="S162" s="70" t="str">
         <x:f>IF(A162="","",IF(COUNTIF($R$6:$R$162,R162)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T162" s="63" t="str">
-        <x:v>9afad545f5f7f1ffa13db7d33bb71ba6df913c9072b6b9a32d673f5c4b24438a</x:v>
-      </x:c>
-      <x:c r="U162" s="63" t="str">
+      <x:c r="T162" s="70" t="str">
+        <x:v>d81e840f5c087b349fd6e19b4cb7e65eb79294edb937fdc75192b66967c29e2e</x:v>
+      </x:c>
+      <x:c r="U162" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V162" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="W162" s="63" t="str">
+      <x:c r="V162" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W162" s="70" t="str">
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
-      <x:c r="X162" s="63" t="str">
-        <x:v>BunnyRig/FeetRoot/FootJointR；脚底中心原点；与左脚独立交替并参与翻滚/受击关键姿势。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163">
-      <x:c r="A163" t="str">
+      <x:c r="X162" s="70" t="str">
+        <x:v>PH43：v006网格与AssetID不变；FootJointR除moving步态外新增falling收腿与landing压缩恢复职责，动作由PlayerAvatar3D程序变换驱动。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="155" customHeight="1">
+      <x:c r="A163" s="70" t="str">
         <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
       </x:c>
-      <x:c r="B163" t="str">
-        <x:v>向下爬楼塔楼3D模块化母版</x:v>
-      </x:c>
-      <x:c r="C163" t="str">
+      <x:c r="B163" s="70" t="str">
+        <x:v>向下爬楼塔楼3D五米模块化母版</x:v>
+      </x:c>
+      <x:c r="C163" s="70" t="str">
         <x:v>场景</x:v>
       </x:c>
-      <x:c r="D163" t="str">
+      <x:c r="D163" s="70" t="str">
         <x:v>room_kit</x:v>
       </x:c>
-      <x:c r="E163" t="str">
+      <x:c r="E163" s="70" t="str">
         <x:v>tower_descent</x:v>
       </x:c>
-      <x:c r="F163" t="str">
+      <x:c r="F163" s="70" t="str">
         <x:v>root_3d</x:v>
       </x:c>
-      <x:c r="G163" t="str">
+      <x:c r="G163" s="70" t="str">
         <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
       </x:c>
-      <x:c r="H163" t="str">
+      <x:c r="H163" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I163" t="str">
-        <x:v>blender_review</x:v>
-      </x:c>
-      <x:c r="J163" t="str">
-        <x:v>楼顶/设施层/五层战斗层/通用楼梯间</x:v>
-      </x:c>
-      <x:c r="K163" t="str">
-        <x:v>待制作</x:v>
-      </x:c>
-      <x:c r="L163" t="str">
+      <x:c r="I163" s="70" t="str">
+        <x:v>godot_runtime</x:v>
+      </x:c>
+      <x:c r="J163" s="70" t="str">
+        <x:v>250×250m整层；99层30×30m/6×6格基地；98—95层终局路线；2.2×2.5m门</x:v>
+      </x:c>
+      <x:c r="K163" s="70" t="str">
+        <x:v>已接入</x:v>
+      </x:c>
+      <x:c r="L163" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M163" t="str">
+      <x:c r="M163" s="70" t="str">
+        <x:v>v007</x:v>
+      </x:c>
+      <x:c r="N163" s="70" t="str">
+        <x:v>Blender 4.2源文件/1单位=1m/PH49运行时布局审阅集合</x:v>
+      </x:c>
+      <x:c r="O163" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/source/env_tower_descent_kit_top3d_v007.blend</x:v>
+      </x:c>
+      <x:c r="P163" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/source/sync_env_tower_descent_kit_top3d_v007.py; assets/art/environments/tower_descent_3d/source/validate_env_tower_descent_kit_top3d_v007.py; outputs/019fb2a5-6bc8-7d10-a214-90288a5f7e80/previews/env_tower_descent_v007_base99.png; outputs/019fb2a5-6bc8-7d10-a214-90288a5f7e80/previews/env_tower_descent_v007_floors98_95.png</x:v>
+      </x:c>
+      <x:c r="Q163" s="70" t="str">
+        <x:v>塔楼;向下爬楼;楼顶;基地层;战斗层;特殊楼梯;通用楼梯;五米网格;模块化地砖;模块化墙;模块化门;Blender</x:v>
+      </x:c>
+      <x:c r="R163" s="70" t="str">
+        <x:v>场景|room_kit|tower_descent|root_3d|俯视3d|blender_review</x:v>
+      </x:c>
+      <x:c r="S163" s="70" t="str">
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T163" s="70" t="str">
+        <x:v>ef19c00e61478f0b3268edd9746e7fcf6704a2865aac0b4121474ab9b98e7552</x:v>
+      </x:c>
+      <x:c r="U163" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V163" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W163" s="70" t="str">
+        <x:v>用户楼梯资产 + Codex PH49运行时同步</x:v>
+      </x:c>
+      <x:c r="X163" s="70" t="str">
+        <x:v>PH49：保留99→98楼梯间位置，并在99层基地墙边补17.5m连接走廊；基地改为精确30×30m、6×6个5m地砖。98层入口门位于楼梯间左侧语义方向，关卡改刷在门的内侧而不是对侧。98—95层均含探索、搜刮、战斗、撤离及种子化随机房间/掉落；五处电梯为房间树之外的独立墙边设施。v007 Blender母版同步了基地、两条走廊、46个房间占位、5个独立电梯与2.2×2.5m门合同。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="132" customHeight="1">
+      <x:c r="A164" s="70" t="str">
+        <x:v>ENV-TOWER-FLOOR-TILE-5M</x:v>
+      </x:c>
+      <x:c r="B164" s="70" t="str">
+        <x:v>塔楼5米地砖模块</x:v>
+      </x:c>
+      <x:c r="C164" s="70" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D164" s="70" t="str">
+        <x:v>room_kit</x:v>
+      </x:c>
+      <x:c r="E164" s="70" t="str">
+        <x:v>tower_descent</x:v>
+      </x:c>
+      <x:c r="F164" s="70" t="str">
+        <x:v>floor_tile_5m</x:v>
+      </x:c>
+      <x:c r="G164" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H164" s="70" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I164" s="70" t="str">
+        <x:v>godot_runtime</x:v>
+      </x:c>
+      <x:c r="J164" s="70" t="str">
+        <x:v>塔楼六个物理层楼板/335m MultiMesh网格</x:v>
+      </x:c>
+      <x:c r="K164" s="70" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L164" s="70" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M164" s="70" t="str">
         <x:v>v001</x:v>
       </x:c>
-      <x:c r="N163" t="str">
-        <x:v>Blender 4.2源文件/1单位=1m/122 Mesh</x:v>
-      </x:c>
-      <x:c r="O163" t="str">
-        <x:v>assets/art/environments/tower_descent_3d/source/env_tower_descent_kit_top3d_v001.blend</x:v>
-      </x:c>
-      <x:c r="P163" t="str">
-        <x:v>待用户确认后导出components/*.glb并接入TowerDescent3D</x:v>
-      </x:c>
-      <x:c r="Q163" t="str">
-        <x:v>塔楼;向下爬楼;楼顶;基地层;战斗层;门口走道;折角走道;斜坡楼梯;Blender</x:v>
-      </x:c>
-      <x:c r="R163" t="str">
-        <x:f>LOWER(TRIM(C163)&amp;"|"&amp;TRIM(D163)&amp;"|"&amp;TRIM(E163)&amp;"|"&amp;TRIM(F163)&amp;"|"&amp;TRIM(H163)&amp;"|"&amp;TRIM(I163))</x:f>
-        <x:v>场景|room_kit|tower_descent|root_3d|俯视3d|blender_review</x:v>
-      </x:c>
-      <x:c r="S163" t="str">
+      <x:c r="N164" s="70" t="str">
+        <x:v>GLB / 5×5×0.30m / 共享Mesh / MultiMesh平铺</x:v>
+      </x:c>
+      <x:c r="O164" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_floor_tile_5m_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="P164" s="70" t="str">
+        <x:v>Blender集合=10A_MOD_FLOOR_TILE_5M_U01; export_env_tower_5m_modules_v001.py; TowerFloorStage3D.gd; verify_tower_descent_flow.tscn</x:v>
+      </x:c>
+      <x:c r="Q164" s="70" t="str">
+        <x:v>塔楼;地砖;楼板;5米;模块化;平铺;四向接口</x:v>
+      </x:c>
+      <x:c r="R164" s="70" t="str">
+        <x:v>场景|room_kit|tower_descent|floor_tile_5m|俯视3d|blender_review</x:v>
+      </x:c>
+      <x:c r="S164" s="70" t="str">
+        <x:v>母版子集合</x:v>
+      </x:c>
+      <x:c r="T164" s="70" t="str">
+        <x:v>987b220bef57c4176590caf7568c909d90768450c00f7e4e27c4c61986e6ef2d</x:v>
+      </x:c>
+      <x:c r="U164" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V164" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W164" s="70" t="str">
+        <x:v>程序生成Blender源集合</x:v>
+      </x:c>
+      <x:c r="X164" s="70" t="str">
+        <x:v>PH44：整层由67×67调整为50×50个5m模块，物理尺寸250×250m、满铺2500块；地板仍由模块化MultiMesh渲染并保留独立StaticBody承重。四向楼梯洞口改用对齐5m世界矩形换算网格，避免尺寸与位移单位错位。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="132" customHeight="1">
+      <x:c r="A165" s="70" t="str">
+        <x:v>ENV-TOWER-WALL-SOLID-5M</x:v>
+      </x:c>
+      <x:c r="B165" s="70" t="str">
+        <x:v>塔楼5米满高实墙模块</x:v>
+      </x:c>
+      <x:c r="C165" s="70" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D165" s="70" t="str">
+        <x:v>room_kit</x:v>
+      </x:c>
+      <x:c r="E165" s="70" t="str">
+        <x:v>tower_descent</x:v>
+      </x:c>
+      <x:c r="F165" s="70" t="str">
+        <x:v>wall_solid_5m</x:v>
+      </x:c>
+      <x:c r="G165" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H165" s="70" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I165" s="70" t="str">
+        <x:v>godot_runtime</x:v>
+      </x:c>
+      <x:c r="J165" s="70" t="str">
+        <x:v>整层外墙/65m核心/探索房内墙/5m正交走廊</x:v>
+      </x:c>
+      <x:c r="K165" s="70" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L165" s="70" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M165" s="70" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N165" s="70" t="str">
+        <x:v>GLB / 5×0.30×9m / 共享Mesh / 可旋转</x:v>
+      </x:c>
+      <x:c r="O165" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_wall_solid_5m_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="P165" s="70" t="str">
+        <x:v>Blender集合=10B_MOD_WALL_SOLID_5M_U01; export_env_tower_5m_modules_v001.py; DungeonRoom3D.gd; TowerFloorStage3D.gd</x:v>
+      </x:c>
+      <x:c r="Q165" s="70" t="str">
+        <x:v>塔楼;实墙;满高墙;5米;模块化;室内隔墙;核心外墙</x:v>
+      </x:c>
+      <x:c r="R165" s="70" t="str">
+        <x:v>场景|room_kit|tower_descent|wall_solid_5m|俯视3d|blender_review</x:v>
+      </x:c>
+      <x:c r="S165" s="70" t="str">
+        <x:v>母版子集合</x:v>
+      </x:c>
+      <x:c r="T165" s="70" t="str">
+        <x:v>5680bf2dedc964fcbfd5e5ee7d5ba86af5ba8a2c77c64a02151aee19a7f2cc33</x:v>
+      </x:c>
+      <x:c r="U165" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V165" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W165" s="70" t="str">
+        <x:v>程序生成Blender源集合</x:v>
+      </x:c>
+      <x:c r="X165" s="70" t="str">
+        <x:v>PH44：继续复用同一5m实墙模块；45m战斗房每边按9个模块拼接。为控制250m楼层节点量，同方向连续实墙改为单个MultiMeshInstance3D批量渲染，碰撞按门洞两侧合并成长条StaticBody形状；视觉仍保持逐5m模块拼缝与命名语义。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="132" customHeight="1">
+      <x:c r="A166" s="70" t="str">
+        <x:v>ENV-TOWER-WALL-PARAPET-5M</x:v>
+      </x:c>
+      <x:c r="B166" s="70" t="str">
+        <x:v>塔楼5米楼顶女儿墙模块</x:v>
+      </x:c>
+      <x:c r="C166" s="70" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D166" s="70" t="str">
+        <x:v>room_kit</x:v>
+      </x:c>
+      <x:c r="E166" s="70" t="str">
+        <x:v>tower_descent</x:v>
+      </x:c>
+      <x:c r="F166" s="70" t="str">
+        <x:v>wall_parapet_5m</x:v>
+      </x:c>
+      <x:c r="G166" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H166" s="70" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I166" s="70" t="str">
+        <x:v>godot_runtime</x:v>
+      </x:c>
+      <x:c r="J166" s="70" t="str">
+        <x:v>335m楼顶四周边界/268段MultiMesh围栏</x:v>
+      </x:c>
+      <x:c r="K166" s="70" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L166" s="70" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M166" s="70" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N166" s="70" t="str">
+        <x:v>GLB / 5×0.30×1.50m / 共享Mesh</x:v>
+      </x:c>
+      <x:c r="O166" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_wall_parapet_5m_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="P166" s="70" t="str">
+        <x:v>Blender集合=10C_MOD_WALL_PARAPET_5M_U01; export_env_tower_5m_modules_v001.py; TowerFloorStage3D.gd; verify_tower_descent_visual.tscn</x:v>
+      </x:c>
+      <x:c r="Q166" s="70" t="str">
+        <x:v>塔楼;女儿墙;护栏;5米;模块化;楼顶边界</x:v>
+      </x:c>
+      <x:c r="R166" s="70" t="str">
+        <x:v>场景|room_kit|tower_descent|wall_parapet_5m|俯视3d|blender_review</x:v>
+      </x:c>
+      <x:c r="S166" s="70" t="str">
+        <x:v>母版子集合</x:v>
+      </x:c>
+      <x:c r="T166" s="70" t="str">
+        <x:v>44fdb663487a9bf010d8fa249a2f9811843409c35d9f7ce8d09c48f7de7bf808</x:v>
+      </x:c>
+      <x:c r="U166" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V166" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W166" s="70" t="str">
+        <x:v>程序生成Blender源集合</x:v>
+      </x:c>
+      <x:c r="X166" s="70" t="str">
+        <x:v>PH44：继续复用同一5m围栏模块，按50×50网格环绕250×250m楼顶与整层边界，不新增大块整体网格；普通楼顶由统一太阳照明，楼梯口局部阴影不再靠提高全局环境亮度解决。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="155" customHeight="1">
+      <x:c r="A167" s="70" t="str">
+        <x:v>ENV-TOWER-WALL-DOOR-5M</x:v>
+      </x:c>
+      <x:c r="B167" s="70" t="str">
+        <x:v>塔楼5米带门墙模块</x:v>
+      </x:c>
+      <x:c r="C167" s="70" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D167" s="70" t="str">
+        <x:v>room_kit</x:v>
+      </x:c>
+      <x:c r="E167" s="70" t="str">
+        <x:v>tower_descent</x:v>
+      </x:c>
+      <x:c r="F167" s="70" t="str">
+        <x:v>wall_door_5m</x:v>
+      </x:c>
+      <x:c r="G167" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H167" s="70" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I167" s="70" t="str">
+        <x:v>godot_runtime</x:v>
+      </x:c>
+      <x:c r="J167" s="70" t="str">
+        <x:v>5m墙位/2.2m净宽/2.5m净高/独立门扇</x:v>
+      </x:c>
+      <x:c r="K167" s="70" t="str">
+        <x:v>已接入</x:v>
+      </x:c>
+      <x:c r="L167" s="70" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M167" s="70" t="str">
+        <x:v>v002</x:v>
+      </x:c>
+      <x:c r="N167" s="70" t="str">
+        <x:v>Blender 4.2 GLB/7个Mesh部件/2.2×2.5m净开口</x:v>
+      </x:c>
+      <x:c r="O167" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_wall_door_5m_top3d_v002.glb</x:v>
+      </x:c>
+      <x:c r="P167" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/source/export_env_tower_door_5m_v002.py; assets/art/environments/tower_descent_3d/source/env_tower_descent_kit_top3d_v007.blend</x:v>
+      </x:c>
+      <x:c r="Q167" s="70" t="str">
+        <x:v>塔楼;门;门洞;5米;模块化;肉鸽触发;独立门扇</x:v>
+      </x:c>
+      <x:c r="R167" s="70" t="str">
+        <x:v>场景|room_kit|tower_descent|wall_door_5m|俯视3d|blender_review</x:v>
+      </x:c>
+      <x:c r="S167" s="70" t="str">
+        <x:v>母版子集合</x:v>
+      </x:c>
+      <x:c r="T167" s="70" t="str">
+        <x:v>75f03e2bc785b0d957df9e27940ac9a024097ce6f2c371ae947b2c48cce69ca1</x:v>
+      </x:c>
+      <x:c r="U167" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V167" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W167" s="70" t="str">
+        <x:v>Codex Blender导出 + Godot运行时接入</x:v>
+      </x:c>
+      <x:c r="X167" s="70" t="str">
+        <x:v>PH49：门洞合同统一为2.2m宽、2.5m高；RoomDoor3D门扇、碰撞、开门抬升距离和四向墙垛均按同一尺寸更新。门开启后禁用门扇碰撞，角色可通过；98—95层全部逻辑门执行双向目标验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="132" customHeight="1">
+      <x:c r="A168" s="70" t="str">
+        <x:v>ENV-TOWER-STAIRWELL-GENERIC-9M</x:v>
+      </x:c>
+      <x:c r="B168" s="70" t="str">
+        <x:v>塔楼9米通用双跑楼梯间</x:v>
+      </x:c>
+      <x:c r="C168" s="70" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D168" s="70" t="str">
+        <x:v>room_kit</x:v>
+      </x:c>
+      <x:c r="E168" s="70" t="str">
+        <x:v>tower_descent</x:v>
+      </x:c>
+      <x:c r="F168" s="70" t="str">
+        <x:v>stairwell_generic_9m</x:v>
+      </x:c>
+      <x:c r="G168" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H168" s="70" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I168" s="70" t="str">
+        <x:v>godot_runtime</x:v>
+      </x:c>
+      <x:c r="J168" s="70" t="str">
+        <x:v>99层以下通用楼梯/四向旋转/上下楼交通</x:v>
+      </x:c>
+      <x:c r="K168" s="70" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L168" s="70" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M168" s="70" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N168" s="70" t="str">
+        <x:v>GLB / 14.751×27.617×约18.41m包围 / 9m层差 / 48子对象</x:v>
+      </x:c>
+      <x:c r="O168" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_stairwell_generic_9m_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="P168" s="70" t="str">
+        <x:v>Blender根=Stair_Generic_Rotatable_ROOT; env_tower_descent_kit_top3d_v006.blend; export_env_tower_stairwells_v001.py; TowerDescent3D.gd; verify_tower_descent_flow.tscn</x:v>
+      </x:c>
+      <x:c r="Q168" s="70" t="str">
+        <x:v>塔楼;通用楼梯;双跑楼梯;折角平台;9米层高;四向旋转;Blender直出</x:v>
+      </x:c>
+      <x:c r="R168" s="70" t="str">
+        <x:f>LOWER(TRIM(C168)&amp;"|"&amp;TRIM(D168)&amp;"|"&amp;TRIM(E168)&amp;"|"&amp;TRIM(F168)&amp;"|"&amp;TRIM(H168)&amp;"|"&amp;TRIM(I168))</x:f>
+        <x:v>场景|room_kit|tower_descent|stairwell_generic_9m|俯视3d|godot_runtime</x:v>
+      </x:c>
+      <x:c r="S168" s="70" t="str">
+        <x:f>IF(COUNTIF($R:$R,R168)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T163" t="str">
-        <x:v>654d76f4f80ae41f183edf50e606ac4891b7cfe2cb76d01453fe07f25a810f1b</x:v>
-      </x:c>
-      <x:c r="U163" t="str">
+      <x:c r="T168" s="70" t="str">
+        <x:v>b0416e02b70673bb4cc38a58436210ff04343f6d68b4f5b80f8e1a0c5daaf844</x:v>
+      </x:c>
+      <x:c r="U168" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V163" t="n">
-        <x:v>46232</x:v>
-      </x:c>
-      <x:c r="W163" t="str">
-        <x:v>原创Blender程序建模</x:v>
-      </x:c>
-      <x:c r="X163" t="str">
-        <x:v>PH35评审母版：楼顶111.803×111.803m（12,500㎡）；设施/战斗层67.082×67.082m（4,500㎡）；层高9m。组件为6×6m门口走道、15×6m/下降4.5m固定斜坡、6×14m折角走道和27×14×9m双跑总成。已完成Blender尺寸/命名/接口QA与三张评审图；确认前不导出GLB、不修改Godot运行时。</x:v>
+      <x:c r="V168" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W168" s="70" t="str">
+        <x:v>用户手工Blender模型</x:v>
+      </x:c>
+      <x:c r="X168" s="70" t="str">
+        <x:v>PH44：继续直接复用用户v006通用9m楼梯视觉与六块Walkable同形常驻碰撞；按5m世界矩形对齐250m整层中的四向楼梯洞口，可旋转通用。上下端门侧分别记录，避免楼梯开口朝向改变后沿用同一侧导致错位。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="132" customHeight="1">
+      <x:c r="A169" s="70" t="str">
+        <x:v>ENV-TOWER-STAIRWELL-ROOFTOP-9M</x:v>
+      </x:c>
+      <x:c r="B169" s="70" t="str">
+        <x:v>塔楼楼顶特殊双跑楼梯间</x:v>
+      </x:c>
+      <x:c r="C169" s="70" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D169" s="70" t="str">
+        <x:v>room_kit</x:v>
+      </x:c>
+      <x:c r="E169" s="70" t="str">
+        <x:v>tower_descent</x:v>
+      </x:c>
+      <x:c r="F169" s="70" t="str">
+        <x:v>stairwell_rooftop_9m</x:v>
+      </x:c>
+      <x:c r="G169" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H169" s="70" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I169" s="70" t="str">
+        <x:v>godot_runtime</x:v>
+      </x:c>
+      <x:c r="J169" s="70" t="str">
+        <x:v>楼顶至99层特殊交通/保留手调墙高</x:v>
+      </x:c>
+      <x:c r="K169" s="70" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L169" s="70" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M169" s="70" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N169" s="70" t="str">
+        <x:v>GLB / 14.751×27.617×约15.36m包围 / 9m层差 / 47子对象</x:v>
+      </x:c>
+      <x:c r="O169" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_stairwell_rooftop_9m_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="P169" s="70" t="str">
+        <x:v>Blender根=Stair_Special_Rooftop_ROOT; env_tower_descent_kit_top3d_v006.blend; export_env_tower_stairwells_v001.py; TowerDescent3D.gd; verify_tower_descent_flow.tscn</x:v>
+      </x:c>
+      <x:c r="Q169" s="70" t="str">
+        <x:v>塔楼;楼顶楼梯;特殊楼梯;双跑楼梯;特殊墙高;9米层高;Blender直出</x:v>
+      </x:c>
+      <x:c r="R169" s="70" t="str">
+        <x:f>LOWER(TRIM(C169)&amp;"|"&amp;TRIM(D169)&amp;"|"&amp;TRIM(E169)&amp;"|"&amp;TRIM(F169)&amp;"|"&amp;TRIM(H169)&amp;"|"&amp;TRIM(I169))</x:f>
+        <x:v>场景|room_kit|tower_descent|stairwell_rooftop_9m|俯视3d|godot_runtime</x:v>
+      </x:c>
+      <x:c r="S169" s="70" t="str">
+        <x:f>IF(COUNTIF($R:$R,R169)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T169" s="70" t="str">
+        <x:v>88198a579cc846974f17f5203b46b568b7ab2421fd7bb63c0b7868ddd05684a2</x:v>
+      </x:c>
+      <x:c r="U169" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V169" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W169" s="70" t="str">
+        <x:v>用户手工Blender模型</x:v>
+      </x:c>
+      <x:c r="X169" s="70" t="str">
+        <x:v>PH44：继续复用用户v006楼顶特殊楼梯、加高墙体及常驻Walkable/EnclosureWall碰撞。楼顶纯黑问题确认为固定斜俯视镜头被门墙整段遮挡；现仅剖切遮挡角色的墙体渲染，并联动同方向5m墙段，物理碰撞、门和楼梯围护保持有效；天空反弹光降至1.25，仅补兼容渲染器缺少实时天空GI。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -12582,7 +13056,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a1b9535d3ec4a02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2debb88dbbb542fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13721,373 +14195,373 @@
         <x:v>默认visible=false；不计入四主模块</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="62" customHeight="1">
-      <x:c r="A31" s="63" t="str">
+    <x:row r="31" ht="104" customHeight="1">
+      <x:c r="A31" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B31" s="63" t="str">
+      <x:c r="B31" s="70" t="str">
         <x:v>root</x:v>
       </x:c>
-      <x:c r="C31" s="63" t="str">
+      <x:c r="C31" s="70" t="str">
         <x:v>Avatar3D/VisualRoot/BunnyRig</x:v>
       </x:c>
-      <x:c r="D31" s="63" t="str">
+      <x:c r="D31" s="70" t="str">
         <x:v>player_root</x:v>
       </x:c>
-      <x:c r="E31" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v004.tscn</x:v>
-      </x:c>
-      <x:c r="F31" s="63" t="str">
-        <x:v>Node3D刚性骨架</x:v>
-      </x:c>
-      <x:c r="G31" s="63" t="str">
+      <x:c r="E31" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v006.tscn</x:v>
+      </x:c>
+      <x:c r="F31" s="70" t="str">
+        <x:v>Node3D刚性骨架 / 完整视觉1.500m</x:v>
+      </x:c>
+      <x:c r="G31" s="70" t="str">
         <x:v>(0,0,0)</x:v>
       </x:c>
-      <x:c r="H31" s="63" t="str">
+      <x:c r="H31" s="70" t="str">
         <x:v>整体随准星绕Y轴</x:v>
       </x:c>
-      <x:c r="I31" s="63" t="n">
+      <x:c r="I31" s="70" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J31" s="63" t="str">
-        <x:v>六态整体 + 动作覆盖</x:v>
-      </x:c>
-      <x:c r="K31" s="63" t="str">
+      <x:c r="J31" s="70" t="str">
+        <x:v>八态整体 + falling收束/landing压缩回弹 + 动作覆盖</x:v>
+      </x:c>
+      <x:c r="K31" s="70" t="str">
         <x:v>Godot骨架根</x:v>
       </x:c>
-      <x:c r="L31" s="63" t="str">
+      <x:c r="L31" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M31" s="63" t="str">
-        <x:v>v004：模型为 pivot-local；导出器断言 Blender +X → Godot -Z；装配坐标由 Godot 关节节点提供；视觉层级 CollisionShape3D/CollisionObject3D 数量均为 0。玩法碰撞仅使用 Player3D/VirtualCollisionBox（0.86×1.80×0.72m），不包含耳朵。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="54" customHeight="1">
-      <x:c r="A32" s="63" t="str">
+      <x:c r="M31" s="70" t="str">
+        <x:v>PH43：v006真实1.5m分体网格与AssetID不变；玩法碰撞位于Player3D/VirtualCollisionCapsule（height=1.5m、radius=0.34m）。falling/landing复用既有Body/Head/Hands/Feet/EarSocket关节。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="104" customHeight="1">
+      <x:c r="A32" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B32" s="63" t="str">
+      <x:c r="B32" s="70" t="str">
         <x:v>body</x:v>
       </x:c>
-      <x:c r="C32" s="63" t="str">
+      <x:c r="C32" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/BodyJoint/Model</x:v>
       </x:c>
-      <x:c r="D32" s="63" t="str">
+      <x:c r="D32" s="70" t="str">
         <x:v>BunnyRig</x:v>
       </x:c>
-      <x:c r="E32" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F32" s="63" t="str">
-        <x:v>pivot-local GLB</x:v>
-      </x:c>
-      <x:c r="G32" s="63" t="str">
-        <x:v>(-0.00005,0.255786,-0.001047)</x:v>
-      </x:c>
-      <x:c r="H32" s="63" t="str">
+      <x:c r="E32" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F32" s="70" t="str">
+        <x:v>pivot-local GLB / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G32" s="70" t="str">
+        <x:v>(-0.000030,0.155022,-0.000635)</x:v>
+      </x:c>
+      <x:c r="H32" s="70" t="str">
         <x:v>BodyJoint</x:v>
       </x:c>
-      <x:c r="I32" s="63" t="n">
+      <x:c r="I32" s="70" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J32" s="63" t="str">
+      <x:c r="J32" s="70" t="str">
         <x:v>呼吸/移动挤压/突进翻滚/受击</x:v>
       </x:c>
-      <x:c r="K32" s="63" t="str">
+      <x:c r="K32" s="70" t="str">
         <x:v>身体组件</x:v>
       </x:c>
-      <x:c r="L32" s="63" t="str">
+      <x:c r="L32" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M32" s="63" t="str">
-        <x:v>Blender 原点：身体底部中心</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="54" customHeight="1">
-      <x:c r="A33" s="63" t="str">
+      <x:c r="M32" s="70" t="str">
+        <x:v>Blender原点：身体底部中心；v006真实1.5m几何。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="104" customHeight="1">
+      <x:c r="A33" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B33" s="63" t="str">
+      <x:c r="B33" s="70" t="str">
         <x:v>head</x:v>
       </x:c>
-      <x:c r="C33" s="63" t="str">
+      <x:c r="C33" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/HeadJoint/Model</x:v>
       </x:c>
-      <x:c r="D33" s="63" t="str">
+      <x:c r="D33" s="70" t="str">
         <x:v>BunnyRig</x:v>
       </x:c>
-      <x:c r="E33" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F33" s="63" t="str">
-        <x:v>pivot-local GLB</x:v>
-      </x:c>
-      <x:c r="G33" s="63" t="str">
-        <x:v>(-0.000046,0.787232,0.043611)</x:v>
-      </x:c>
-      <x:c r="H33" s="63" t="str">
+      <x:c r="E33" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F33" s="70" t="str">
+        <x:v>pivot-local GLB / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G33" s="70" t="str">
+        <x:v>(-0.000028,0.477110,0.026431)</x:v>
+      </x:c>
+      <x:c r="H33" s="70" t="str">
         <x:v>HeadJoint</x:v>
       </x:c>
-      <x:c r="I33" s="63" t="n">
+      <x:c r="I33" s="70" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J33" s="63" t="str">
+      <x:c r="J33" s="70" t="str">
         <x:v>移动反相滞后/后坐/受击甩头</x:v>
       </x:c>
-      <x:c r="K33" s="63" t="str">
+      <x:c r="K33" s="70" t="str">
         <x:v>头部组件</x:v>
       </x:c>
-      <x:c r="L33" s="63" t="str">
+      <x:c r="L33" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M33" s="63" t="str">
-        <x:v>Blender 原点：头部下沿中心</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="54" customHeight="1">
-      <x:c r="A34" s="63" t="str">
+      <x:c r="M33" s="70" t="str">
+        <x:v>Blender原点：头部下沿中心；不含耳头顶1.103390m。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="104" customHeight="1">
+      <x:c r="A34" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B34" s="63" t="str">
+      <x:c r="B34" s="70" t="str">
         <x:v>ear_l</x:v>
       </x:c>
-      <x:c r="C34" s="63" t="str">
+      <x:c r="C34" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/HeadJoint/Ears/EarSocketL/EarAccessory</x:v>
       </x:c>
-      <x:c r="D34" s="63" t="str">
+      <x:c r="D34" s="70" t="str">
         <x:v>head</x:v>
       </x:c>
-      <x:c r="E34" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F34" s="63" t="str">
-        <x:v>pivot-local GLB × -X</x:v>
-      </x:c>
-      <x:c r="G34" s="63" t="str">
-        <x:v>Head local (-0.404343,0.824427,-0.002757)</x:v>
-      </x:c>
-      <x:c r="H34" s="63" t="str">
+      <x:c r="E34" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F34" s="70" t="str">
+        <x:v>pivot-local GLB × -X / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G34" s="70" t="str">
+        <x:v>Head local (-0.245056,0.499653,-0.001671)</x:v>
+      </x:c>
+      <x:c r="H34" s="70" t="str">
         <x:v>继承HeadJoint</x:v>
       </x:c>
-      <x:c r="I34" s="63" t="n">
+      <x:c r="I34" s="70" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J34" s="63" t="str">
+      <x:c r="J34" s="70" t="str">
         <x:v>移动跟随/冲刺后压/受击收耳</x:v>
       </x:c>
-      <x:c r="K34" s="63" t="str">
+      <x:c r="K34" s="70" t="str">
         <x:v>头部配件</x:v>
       </x:c>
-      <x:c r="L34" s="63" t="str">
+      <x:c r="L34" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M34" s="63" t="str">
-        <x:v>复用语义右耳资产并在左挂点镜像；原点位于耳根</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="54" customHeight="1">
-      <x:c r="A35" s="63" t="str">
+      <x:c r="M34" s="70" t="str">
+        <x:v>复用语义右耳并在左挂点镜像；完整视觉顶部1.500m。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="104" customHeight="1">
+      <x:c r="A35" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B35" s="63" t="str">
+      <x:c r="B35" s="70" t="str">
         <x:v>ear_r</x:v>
       </x:c>
-      <x:c r="C35" s="63" t="str">
+      <x:c r="C35" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/HeadJoint/Ears/EarSocketR/EarAccessory</x:v>
       </x:c>
-      <x:c r="D35" s="63" t="str">
+      <x:c r="D35" s="70" t="str">
         <x:v>head</x:v>
       </x:c>
-      <x:c r="E35" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F35" s="63" t="str">
-        <x:v>pivot-local GLB</x:v>
-      </x:c>
-      <x:c r="G35" s="63" t="str">
-        <x:v>Head local (0.404435,0.824427,-0.002757)</x:v>
-      </x:c>
-      <x:c r="H35" s="63" t="str">
+      <x:c r="E35" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F35" s="70" t="str">
+        <x:v>pivot-local GLB / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G35" s="70" t="str">
+        <x:v>Head local (0.245112,0.499653,-0.001671)</x:v>
+      </x:c>
+      <x:c r="H35" s="70" t="str">
         <x:v>继承HeadJoint</x:v>
       </x:c>
-      <x:c r="I35" s="63" t="n">
+      <x:c r="I35" s="70" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J35" s="63" t="str">
+      <x:c r="J35" s="70" t="str">
         <x:v>移动跟随/冲刺后压/受击收耳</x:v>
       </x:c>
-      <x:c r="K35" s="63" t="str">
+      <x:c r="K35" s="70" t="str">
         <x:v>头部配件</x:v>
       </x:c>
-      <x:c r="L35" s="63" t="str">
+      <x:c r="L35" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M35" s="63" t="str">
-        <x:v>语义右耳标准实例；原点位于耳根</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="62" customHeight="1">
-      <x:c r="A36" s="63" t="str">
+      <x:c r="M35" s="70" t="str">
+        <x:v>语义右耳标准实例；完整视觉顶部1.500m。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="104" customHeight="1">
+      <x:c r="A36" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B36" s="63" t="str">
+      <x:c r="B36" s="70" t="str">
         <x:v>hand_l</x:v>
       </x:c>
-      <x:c r="C36" s="63" t="str">
+      <x:c r="C36" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/HandRoot/HandJointL/Model</x:v>
       </x:c>
-      <x:c r="D36" s="63" t="str">
+      <x:c r="D36" s="70" t="str">
         <x:v>BunnyRig</x:v>
       </x:c>
-      <x:c r="E36" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F36" s="63" t="str">
-        <x:v>pivot-local GLB</x:v>
-      </x:c>
-      <x:c r="G36" s="63" t="str">
-        <x:v>Authored (-0.471625,0.530925,-0.023818); longgun support (0.20,0.52,-0.64)</x:v>
-      </x:c>
-      <x:c r="H36" s="63" t="str">
+      <x:c r="E36" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F36" s="70" t="str">
+        <x:v>pivot-local GLB / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G36" s="70" t="str">
+        <x:v>Authored (-0.285833,0.321773,-0.014435); longgun support (0.121212,0.315152,-0.387879)</x:v>
+      </x:c>
+      <x:c r="H36" s="70" t="str">
         <x:v>HandRoot 独立左腕</x:v>
       </x:c>
-      <x:c r="I36" s="63" t="n">
+      <x:c r="I36" s="70" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J36" s="63" t="str">
+      <x:c r="J36" s="70" t="str">
         <x:v>手枪自由摆臂；长枪托举；换弹服务；双手枪后坐</x:v>
       </x:c>
-      <x:c r="K36" s="63" t="str">
+      <x:c r="K36" s="70" t="str">
         <x:v>左手组件</x:v>
       </x:c>
-      <x:c r="L36" s="63" t="str">
+      <x:c r="L36" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M36" s="63" t="str">
-        <x:v>Blender 原点位于手腕圆环近端轴心，球体为远端手掌；手枪姿势不计入握持手，长枪左手跨中线托住护木下方并绕本地 Y 负向转入托举。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="62" customHeight="1">
-      <x:c r="A37" s="63" t="str">
+      <x:c r="M36" s="70" t="str">
+        <x:v>手腕圆环近端轴心；网格、挂点与动作米制平移使用0.606060606比例。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="104" customHeight="1">
+      <x:c r="A37" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B37" s="63" t="str">
+      <x:c r="B37" s="70" t="str">
         <x:v>hand_r</x:v>
       </x:c>
-      <x:c r="C37" s="63" t="str">
+      <x:c r="C37" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/HandRoot/HandJointR/Model</x:v>
       </x:c>
-      <x:c r="D37" s="63" t="str">
+      <x:c r="D37" s="70" t="str">
         <x:v>BunnyRig</x:v>
       </x:c>
-      <x:c r="E37" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_r_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F37" s="63" t="str">
-        <x:v>pivot-local GLB</x:v>
-      </x:c>
-      <x:c r="G37" s="63" t="str">
-        <x:v>Authored (0.471625,0.530925,-0.023818); sidearm (0.08,0.56,-0.49)+socket X0.24; longgun (0.13,0.56,-0.49)</x:v>
-      </x:c>
-      <x:c r="H37" s="63" t="str">
+      <x:c r="E37" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_r_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F37" s="70" t="str">
+        <x:v>pivot-local GLB / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G37" s="70" t="str">
+        <x:v>Authored (0.285833,0.321773,-0.014435); sidearm (0.048485,0.339394,-0.296970)+socket X0.145455; longgun (0.078788,0.339394,-0.296970)</x:v>
+      </x:c>
+      <x:c r="H37" s="70" t="str">
         <x:v>HandRoot 独立右腕 / WeaponSocket 跟随</x:v>
       </x:c>
-      <x:c r="I37" s="63" t="n">
+      <x:c r="I37" s="70" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J37" s="63" t="str">
+      <x:c r="J37" s="70" t="str">
         <x:v>手枪/长枪主握把；独立跑步；武器差异射击后坐</x:v>
       </x:c>
-      <x:c r="K37" s="63" t="str">
+      <x:c r="K37" s="70" t="str">
         <x:v>右手组件</x:v>
       </x:c>
-      <x:c r="L37" s="63" t="str">
+      <x:c r="L37" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M37" s="63" t="str">
-        <x:v>Blender 原点位于手腕圆环近端轴心，球体为远端手掌；角色右侧单手枪绕本地 Y 正向对齐，长枪与左手托举共同锁定。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="54" customHeight="1">
-      <x:c r="A38" s="63" t="str">
+      <x:c r="M37" s="70" t="str">
+        <x:v>右手主握把；持枪视觉与手/挂点使用同一0.606060606比例。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="104" customHeight="1">
+      <x:c r="A38" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B38" s="63" t="str">
+      <x:c r="B38" s="70" t="str">
         <x:v>foot_l</x:v>
       </x:c>
-      <x:c r="C38" s="63" t="str">
+      <x:c r="C38" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/FeetRoot/FootJointL/Model</x:v>
       </x:c>
-      <x:c r="D38" s="63" t="str">
+      <x:c r="D38" s="70" t="str">
         <x:v>FeetRoot</x:v>
       </x:c>
-      <x:c r="E38" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F38" s="63" t="str">
-        <x:v>pivot-local GLB</x:v>
-      </x:c>
-      <x:c r="G38" s="63" t="str">
-        <x:v>(-0.212854,0,-0.017964)</x:v>
-      </x:c>
-      <x:c r="H38" s="63" t="str">
+      <x:c r="E38" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F38" s="70" t="str">
+        <x:v>pivot-local GLB / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G38" s="70" t="str">
+        <x:v>(-0.129002,0,-0.010887)</x:v>
+      </x:c>
+      <x:c r="H38" s="70" t="str">
         <x:v>独立FootJointL</x:v>
       </x:c>
-      <x:c r="I38" s="63" t="n">
+      <x:c r="I38" s="70" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J38" s="63" t="str">
-        <x:v>moving左脚/翻滚收腿/受击甩脚</x:v>
-      </x:c>
-      <x:c r="K38" s="63" t="str">
+      <x:c r="J38" s="70" t="str">
+        <x:v>moving左脚/翻滚收腿/受击甩脚/falling收腿/landing压缩</x:v>
+      </x:c>
+      <x:c r="K38" s="70" t="str">
         <x:v>左脚组件</x:v>
       </x:c>
-      <x:c r="L38" s="63" t="str">
+      <x:c r="L38" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M38" s="63" t="str">
-        <x:v>Blender 原点：脚底中心</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="54" customHeight="1">
-      <x:c r="A39" s="63" t="str">
+      <x:c r="M38" s="70" t="str">
+        <x:v>Blender原点：脚底中心；静态最低点Y=0；PH43复用同一v006网格增加下落与落地程序动作。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="104" customHeight="1">
+      <x:c r="A39" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B39" s="63" t="str">
+      <x:c r="B39" s="70" t="str">
         <x:v>foot_r</x:v>
       </x:c>
-      <x:c r="C39" s="63" t="str">
+      <x:c r="C39" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/FeetRoot/FootJointR/Model</x:v>
       </x:c>
-      <x:c r="D39" s="63" t="str">
+      <x:c r="D39" s="70" t="str">
         <x:v>FeetRoot</x:v>
       </x:c>
-      <x:c r="E39" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F39" s="63" t="str">
-        <x:v>pivot-local GLB</x:v>
-      </x:c>
-      <x:c r="G39" s="63" t="str">
-        <x:v>(0.212854,0,-0.017964)</x:v>
-      </x:c>
-      <x:c r="H39" s="63" t="str">
+      <x:c r="E39" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F39" s="70" t="str">
+        <x:v>pivot-local GLB / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G39" s="70" t="str">
+        <x:v>(0.129002,0,-0.010887)</x:v>
+      </x:c>
+      <x:c r="H39" s="70" t="str">
         <x:v>独立FootJointR</x:v>
       </x:c>
-      <x:c r="I39" s="63" t="n">
+      <x:c r="I39" s="70" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J39" s="63" t="str">
-        <x:v>moving右脚/翻滚收腿/受击甩脚</x:v>
-      </x:c>
-      <x:c r="K39" s="63" t="str">
+      <x:c r="J39" s="70" t="str">
+        <x:v>moving右脚/翻滚收腿/受击甩脚/falling收腿/landing压缩</x:v>
+      </x:c>
+      <x:c r="K39" s="70" t="str">
         <x:v>右脚组件</x:v>
       </x:c>
-      <x:c r="L39" s="63" t="str">
+      <x:c r="L39" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M39" s="63" t="str">
-        <x:v>Blender 原点：脚底中心</x:v>
+      <x:c r="M39" s="70" t="str">
+        <x:v>Blender原点：脚底中心；静态最低点Y=0；PH43复用同一v006网格增加下落与落地程序动作。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14152,21 +14626,35 @@
       <x:c r="K2" s="3"/>
       <x:c r="L2" s="3"/>
     </x:row>
-    <x:row r="3" ht="23" customHeight="1">
-      <x:c r="A3" s="6" t="str">
-        <x:v>2D/3D 共用六态 ID 与转换白名单；Low HP / Silenced / Invincible / Reloading / Firing / Charging / Knockback 为叠加层。兔子另有武器姿势状态机：unarmed、sidearm/longgun × hold/run/fire/reload/charge。武器与命中是唯一动作来源，新增动画前先查本表</x:v>
-      </x:c>
-      <x:c r="B3" s="6"/>
-      <x:c r="C3" s="6"/>
-      <x:c r="D3" s="6"/>
-      <x:c r="E3" s="6"/>
-      <x:c r="F3" s="6"/>
-      <x:c r="G3" s="6"/>
-      <x:c r="H3" s="6"/>
-      <x:c r="I3" s="6"/>
-      <x:c r="J3" s="6"/>
-      <x:c r="K3" s="6"/>
-      <x:c r="L3" s="6"/>
+    <x:row r="3" ht="74" customHeight="1">
+      <x:c r="A3" s="96" t="str">
+        <x:v>Player3D 八态状态机 × 组件表现（falling/landing为真实垂直物理顶层状态）</x:v>
+      </x:c>
+      <x:c r="B3" s="96"/>
+      <x:c r="C3" s="96"/>
+      <x:c r="D3" s="96"/>
+      <x:c r="E3" s="96"/>
+      <x:c r="F3" s="96"/>
+      <x:c r="G3" s="96"/>
+      <x:c r="H3" s="96"/>
+      <x:c r="I3" s="96"/>
+      <x:c r="J3" s="96"/>
+      <x:c r="K3" s="96"/>
+      <x:c r="L3" s="96"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="70"/>
+      <x:c r="B4" s="70"/>
+      <x:c r="C4" s="70"/>
+      <x:c r="D4" s="70"/>
+      <x:c r="E4" s="70"/>
+      <x:c r="F4" s="70"/>
+      <x:c r="G4" s="70"/>
+      <x:c r="H4" s="70"/>
+      <x:c r="I4" s="70"/>
+      <x:c r="J4" s="70"/>
+      <x:c r="K4" s="70"/>
+      <x:c r="L4" s="70"/>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
       <x:c r="A5" s="28" t="str">
@@ -14207,1064 +14695,1182 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
-      <x:c r="A6" s="36" t="str">
+      <x:c r="A6" s="100" t="str">
         <x:v>顶层</x:v>
       </x:c>
-      <x:c r="B6" s="36" t="str">
+      <x:c r="B6" s="100" t="str">
         <x:v>idle</x:v>
       </x:c>
-      <x:c r="C6" s="36" t="str">
+      <x:c r="C6" s="100" t="str">
         <x:v>待命</x:v>
       </x:c>
-      <x:c r="D6" s="36" t="str">
-        <x:v>start/moving/hurt/locked</x:v>
-      </x:c>
-      <x:c r="E6" s="36" t="str">
-        <x:v>moving,dashing,hurt,locked,dead</x:v>
-      </x:c>
-      <x:c r="F6" s="36" t="str">
+      <x:c r="D6" s="100" t="str">
+        <x:v>start/moving/hurt/locked/landing</x:v>
+      </x:c>
+      <x:c r="E6" s="100" t="str">
+        <x:v>moving,dashing,hurt,locked,falling,dead</x:v>
+      </x:c>
+      <x:c r="F6" s="100" t="str">
         <x:v>约2.38s呼吸挤压；半速重心换脚；躯干轻微侧移</x:v>
       </x:c>
-      <x:c r="G6" s="36" t="str">
+      <x:c r="G6" s="100" t="str">
         <x:v>与身体反相缩放；反向滞后保持头重感</x:v>
       </x:c>
-      <x:c r="H6" s="36" t="str">
+      <x:c r="H6" s="100" t="str">
         <x:v>手枪自由左手轻摆；长枪左手保持托举</x:v>
       </x:c>
-      <x:c r="I6" s="36" t="str">
+      <x:c r="I6" s="100" t="str">
         <x:v>握持手与 WeaponSocket 同步稳定呼吸，不脱离握把</x:v>
       </x:c>
-      <x:c r="J6" s="36" t="str">
+      <x:c r="J6" s="100" t="str">
         <x:v>低频错相轻摆</x:v>
       </x:c>
-      <x:c r="K6" s="36" t="str">
+      <x:c r="K6" s="100" t="str">
         <x:v>HUD 待命；无新增VFX</x:v>
       </x:c>
-      <x:c r="L6" s="36" t="str">
-        <x:v>六态 StateMachine 的 idle 唯一驱动；idle_cycle 推进呼吸/换脚；双耳错相并偶发单耳轻弹；moving 本帧归零，停下后恢复</x:v>
+      <x:c r="L6" s="100" t="str">
+        <x:v>八态 StateMachine 的 idle 唯一驱动；idle_cycle 推进呼吸/换脚；双耳错相并偶发单耳轻弹；moving 本帧归零，停下后恢复</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="37" t="str">
+      <x:c r="A7" s="101" t="str">
         <x:v>顶层</x:v>
       </x:c>
-      <x:c r="B7" s="37" t="str">
+      <x:c r="B7" s="101" t="str">
         <x:v>moving</x:v>
       </x:c>
-      <x:c r="C7" s="37" t="str">
+      <x:c r="C7" s="101" t="str">
         <x:v>机动</x:v>
       </x:c>
-      <x:c r="D7" s="37" t="str">
-        <x:v>idle/dashing/hurt/locked</x:v>
-      </x:c>
-      <x:c r="E7" s="37" t="str">
-        <x:v>idle,dashing,hurt,locked,dead</x:v>
-      </x:c>
-      <x:c r="F7" s="37" t="str">
+      <x:c r="D7" s="101" t="str">
+        <x:v>idle/dashing/hurt/locked/landing</x:v>
+      </x:c>
+      <x:c r="E7" s="101" t="str">
+        <x:v>idle,dashing,hurt,locked,falling,dead</x:v>
+      </x:c>
+      <x:c r="F7" s="101" t="str">
         <x:v>位移驱动弹跳/压缩回弹</x:v>
       </x:c>
-      <x:c r="G7" s="37" t="str">
+      <x:c r="G7" s="101" t="str">
         <x:v>较小反相滞后</x:v>
       </x:c>
-      <x:c r="H7" s="37" t="str">
+      <x:c r="H7" s="101" t="str">
         <x:v>手枪自由左手大幅反摆；长枪左手锁定托举</x:v>
       </x:c>
-      <x:c r="I7" s="37" t="str">
+      <x:c r="I7" s="101" t="str">
         <x:v>手枪右手与右侧挂点紧凑起伏；长枪双手/挂点收胸跑</x:v>
       </x:c>
-      <x:c r="J7" s="37" t="str">
+      <x:c r="J7" s="101" t="str">
         <x:v>周期滞后</x:v>
       </x:c>
-      <x:c r="K7" s="37" t="str">
+      <x:c r="K7" s="101" t="str">
         <x:v>地面划痕</x:v>
       </x:c>
-      <x:c r="L7" s="37" t="str">
+      <x:c r="L7" s="101" t="str">
         <x:v>位移驱动独立循环；WeaponPoseFSM 进入 sidearm_run 或 longgun_run；双脚交替，单手/双手剪影分离</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="56" customHeight="1">
-      <x:c r="A8" s="37" t="str">
+      <x:c r="A8" s="101" t="str">
         <x:v>顶层</x:v>
       </x:c>
-      <x:c r="B8" s="37" t="str">
+      <x:c r="B8" s="101" t="str">
         <x:v>dashing</x:v>
       </x:c>
-      <x:c r="C8" s="37" t="str">
+      <x:c r="C8" s="101" t="str">
         <x:v>突进</x:v>
       </x:c>
-      <x:c r="D8" s="37" t="str">
+      <x:c r="D8" s="101" t="str">
         <x:v>idle/moving</x:v>
       </x:c>
-      <x:c r="E8" s="37" t="str">
-        <x:v>idle,moving,hurt,locked,dead</x:v>
-      </x:c>
-      <x:c r="F8" s="37" t="str">
+      <x:c r="E8" s="101" t="str">
+        <x:v>idle,moving,hurt,locked,falling,dead</x:v>
+      </x:c>
+      <x:c r="F8" s="101" t="str">
         <x:v>压缩成团并绕半高轴完整前滚</x:v>
       </x:c>
-      <x:c r="G8" s="37" t="str">
+      <x:c r="G8" s="101" t="str">
         <x:v>随整体轴心翻滚，耳朵大幅后压</x:v>
       </x:c>
-      <x:c r="H8" s="37" t="str">
+      <x:c r="H8" s="101" t="str">
         <x:v>按当前武器握持数收束；自由左手随整体抱团</x:v>
       </x:c>
-      <x:c r="I8" s="37" t="str">
+      <x:c r="I8" s="101" t="str">
         <x:v>右手握把与 WeaponSocket 同轴完整翻滚</x:v>
       </x:c>
-      <x:c r="J8" s="37" t="str">
+      <x:c r="J8" s="101" t="str">
         <x:v>随整体收束</x:v>
       </x:c>
-      <x:c r="K8" s="37" t="str">
+      <x:c r="K8" s="101" t="str">
         <x:v>青色尾迹</x:v>
       </x:c>
-      <x:c r="L8" s="37" t="str">
+      <x:c r="L8" s="101" t="str">
         <x:v>0.17s 内完成 360° 本地X前滚；用半高轴心补偿避免钻地；夸张压缩与抛物线位移</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="56" customHeight="1">
-      <x:c r="A9" s="37" t="str">
+      <x:c r="A9" s="101" t="str">
         <x:v>顶层</x:v>
       </x:c>
-      <x:c r="B9" s="37" t="str">
+      <x:c r="B9" s="101" t="str">
         <x:v>hurt</x:v>
       </x:c>
-      <x:c r="C9" s="37" t="str">
+      <x:c r="C9" s="101" t="str">
         <x:v>受创</x:v>
       </x:c>
-      <x:c r="D9" s="37" t="str">
+      <x:c r="D9" s="101" t="str">
         <x:v>任意存活态</x:v>
       </x:c>
-      <x:c r="E9" s="37" t="str">
-        <x:v>idle,moving,locked,dead</x:v>
-      </x:c>
-      <x:c r="F9" s="37" t="str">
+      <x:c r="E9" s="101" t="str">
+        <x:v>idle,moving,locked,falling,dead</x:v>
+      </x:c>
+      <x:c r="F9" s="101" t="str">
         <x:v>三段压扁/抬起/过冲回正</x:v>
       </x:c>
-      <x:c r="G9" s="37" t="str">
+      <x:c r="G9" s="101" t="str">
         <x:v>大幅后仰甩头 + 反向过冲</x:v>
       </x:c>
-      <x:c r="H9" s="37" t="str">
+      <x:c r="H9" s="101" t="str">
         <x:v>手枪左手自由外甩；长枪左手回护木</x:v>
       </x:c>
-      <x:c r="I9" s="37" t="str">
+      <x:c r="I9" s="101" t="str">
         <x:v>右手/WeaponSocket 同相后退，握把不脱离</x:v>
       </x:c>
-      <x:c r="J9" s="37" t="str">
+      <x:c r="J9" s="101" t="str">
         <x:v>冲击滞后</x:v>
       </x:c>
-      <x:c r="K9" s="37" t="str">
+      <x:c r="K9" s="101" t="str">
         <x:v>红闪/击退轨迹</x:v>
       </x:c>
-      <x:c r="L9" s="37" t="str">
+      <x:c r="L9" s="101" t="str">
         <x:v>真实命中方向 + 受击进度关键姿势；头、双脚、双耳使用独立夸张回弹</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="37" t="str">
+      <x:c r="A10" s="101" t="str">
         <x:v>顶层</x:v>
       </x:c>
-      <x:c r="B10" s="37" t="str">
+      <x:c r="B10" s="101" t="str">
         <x:v>locked</x:v>
       </x:c>
-      <x:c r="C10" s="37" t="str">
+      <x:c r="C10" s="101" t="str">
         <x:v>交互锁定</x:v>
       </x:c>
-      <x:c r="D10" s="37" t="str">
+      <x:c r="D10" s="101" t="str">
+        <x:v>任意存活态/landing</x:v>
+      </x:c>
+      <x:c r="E10" s="101" t="str">
+        <x:v>idle,moving,hurt,falling,dead</x:v>
+      </x:c>
+      <x:c r="F10" s="101" t="str">
+        <x:v>降亮稳定</x:v>
+      </x:c>
+      <x:c r="G10" s="101" t="str">
+        <x:v>稳定</x:v>
+      </x:c>
+      <x:c r="H10" s="101" t="str">
+        <x:v>稳定</x:v>
+      </x:c>
+      <x:c r="I10" s="101" t="str">
+        <x:v>保持握持</x:v>
+      </x:c>
+      <x:c r="J10" s="101" t="str">
+        <x:v>低摆</x:v>
+      </x:c>
+      <x:c r="K10" s="101" t="str">
+        <x:v>琥珀锁定环</x:v>
+      </x:c>
+      <x:c r="L10" s="101" t="str">
+        <x:v>降亮 + 锁定环；保持刚性层级</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="92" customHeight="1">
+      <x:c r="A11" s="101" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B11" s="101" t="str">
+        <x:v>falling</x:v>
+      </x:c>
+      <x:c r="C11" s="101" t="str">
+        <x:v>下落</x:v>
+      </x:c>
+      <x:c r="D11" s="101" t="str">
+        <x:v>idle/moving/dashing/hurt/locked</x:v>
+      </x:c>
+      <x:c r="E11" s="101" t="str">
+        <x:v>landing,hurt,dead</x:v>
+      </x:c>
+      <x:c r="F11" s="101" t="str">
+        <x:v>随下落速度轻微纵向拉长</x:v>
+      </x:c>
+      <x:c r="G11" s="101" t="str">
+        <x:v>滞后上扬，保持头重感</x:v>
+      </x:c>
+      <x:c r="H11" s="101" t="str">
+        <x:v>手枪自由手收束；长枪托举手不脱离</x:v>
+      </x:c>
+      <x:c r="I11" s="101" t="str">
+        <x:v>握持手与WeaponSocket保持同相</x:v>
+      </x:c>
+      <x:c r="J11" s="101" t="str">
+        <x:v>向上滞后</x:v>
+      </x:c>
+      <x:c r="K11" s="101" t="str">
+        <x:v>无新增VFX</x:v>
+      </x:c>
+      <x:c r="L11" s="101" t="str">
+        <x:v>真实重力+0.10s离地容错；双脚收起、双耳后压；楼梯接缝不误触发</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="92" customHeight="1">
+      <x:c r="A12" s="101" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B12" s="101" t="str">
+        <x:v>landing</x:v>
+      </x:c>
+      <x:c r="C12" s="101" t="str">
+        <x:v>落地</x:v>
+      </x:c>
+      <x:c r="D12" s="101" t="str">
+        <x:v>falling</x:v>
+      </x:c>
+      <x:c r="E12" s="101" t="str">
+        <x:v>idle,moving,locked,falling,hurt,dead</x:v>
+      </x:c>
+      <x:c r="F12" s="101" t="str">
+        <x:v>按冲击速度压缩并回弹</x:v>
+      </x:c>
+      <x:c r="G12" s="101" t="str">
+        <x:v>轻微下压后恢复</x:v>
+      </x:c>
+      <x:c r="H12" s="101" t="str">
+        <x:v>随整体吸收冲击</x:v>
+      </x:c>
+      <x:c r="I12" s="101" t="str">
+        <x:v>握持手与WeaponSocket同相稳定</x:v>
+      </x:c>
+      <x:c r="J12" s="101" t="str">
+        <x:v>短促回摆</x:v>
+      </x:c>
+      <x:c r="K12" s="101" t="str">
+        <x:v>落地停顿</x:v>
+      </x:c>
+      <x:c r="L12" s="101" t="str">
+        <x:v>冲击速度映射0.12—0.30s硬直；状态计时结束后恢复地面移动</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="101" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B13" s="101" t="str">
+        <x:v>dead</x:v>
+      </x:c>
+      <x:c r="C13" s="101" t="str">
+        <x:v>生命终止</x:v>
+      </x:c>
+      <x:c r="D13" s="101" t="str">
         <x:v>任意存活态</x:v>
       </x:c>
-      <x:c r="E10" s="37" t="str">
-        <x:v>idle,moving,hurt,dead</x:v>
-      </x:c>
-      <x:c r="F10" s="37" t="str">
-        <x:v>降亮稳定</x:v>
-      </x:c>
-      <x:c r="G10" s="37" t="str">
+      <x:c r="E13" s="101" t="str">
+        <x:v>无（终态）</x:v>
+      </x:c>
+      <x:c r="F13" s="101" t="str">
+        <x:v>倾倒熄灭</x:v>
+      </x:c>
+      <x:c r="G13" s="101" t="str">
+        <x:v>随整体倾倒</x:v>
+      </x:c>
+      <x:c r="H13" s="101" t="str">
+        <x:v>随整体倾倒</x:v>
+      </x:c>
+      <x:c r="I13" s="101" t="str">
+        <x:v>随整体倾倒</x:v>
+      </x:c>
+      <x:c r="J13" s="101" t="str">
+        <x:v>停止</x:v>
+      </x:c>
+      <x:c r="K13" s="101" t="str">
+        <x:v>HUD 终止</x:v>
+      </x:c>
+      <x:c r="L13" s="101" t="str">
+        <x:v>整体倾倒；耳朵与肢体跟随关节</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="101" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B14" s="101" t="str">
+        <x:v>low_health</x:v>
+      </x:c>
+      <x:c r="C14" s="101" t="str">
+        <x:v>低血</x:v>
+      </x:c>
+      <x:c r="D14" s="101" t="str">
+        <x:v>任意存活态</x:v>
+      </x:c>
+      <x:c r="E14" s="101" t="str">
+        <x:v>不改变顶层</x:v>
+      </x:c>
+      <x:c r="F14" s="101" t="str">
+        <x:v>不变</x:v>
+      </x:c>
+      <x:c r="G14" s="101" t="str">
+        <x:v>不变</x:v>
+      </x:c>
+      <x:c r="H14" s="101" t="str">
+        <x:v>保持当前动作</x:v>
+      </x:c>
+      <x:c r="I14" s="101" t="str">
+        <x:v>保持当前动作</x:v>
+      </x:c>
+      <x:c r="J14" s="101" t="str">
+        <x:v>不变</x:v>
+      </x:c>
+      <x:c r="K14" s="101" t="str">
+        <x:v>红色呼吸环</x:v>
+      </x:c>
+      <x:c r="L14" s="101" t="str">
+        <x:v>HP≤30%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="56" customHeight="1">
+      <x:c r="A15" s="70" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B15" s="70" t="str">
+        <x:v>silenced</x:v>
+      </x:c>
+      <x:c r="C15" s="70" t="str">
+        <x:v>沉默</x:v>
+      </x:c>
+      <x:c r="D15" s="70" t="str">
+        <x:v>任意存活态</x:v>
+      </x:c>
+      <x:c r="E15" s="70" t="str">
+        <x:v>不改变顶层</x:v>
+      </x:c>
+      <x:c r="F15" s="70" t="str">
+        <x:v>降饱和可选</x:v>
+      </x:c>
+      <x:c r="G15" s="70" t="str">
+        <x:v>传感器干扰</x:v>
+      </x:c>
+      <x:c r="H15" s="70" t="str">
+        <x:v>保持当前动作</x:v>
+      </x:c>
+      <x:c r="I15" s="70" t="str">
+        <x:v>保持当前动作</x:v>
+      </x:c>
+      <x:c r="J15" s="70" t="str">
+        <x:v>不变</x:v>
+      </x:c>
+      <x:c r="K15" s="70" t="str">
+        <x:v>紫色干扰环</x:v>
+      </x:c>
+      <x:c r="L15" s="70" t="str">
+        <x:v>计时标志</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="28" customHeight="1">
+      <x:c r="A16" s="97" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B16" s="97" t="str">
+        <x:v>invincible</x:v>
+      </x:c>
+      <x:c r="C16" s="97" t="str">
+        <x:v>无敌</x:v>
+      </x:c>
+      <x:c r="D16" s="97" t="str">
+        <x:v>dash/hurt</x:v>
+      </x:c>
+      <x:c r="E16" s="97" t="str">
+        <x:v>不改变顶层</x:v>
+      </x:c>
+      <x:c r="F16" s="97" t="str">
+        <x:v>闪烁</x:v>
+      </x:c>
+      <x:c r="G16" s="97" t="str">
+        <x:v>闪烁</x:v>
+      </x:c>
+      <x:c r="H16" s="97" t="str">
+        <x:v>保持当前动作</x:v>
+      </x:c>
+      <x:c r="I16" s="97" t="str">
+        <x:v>保持当前动作</x:v>
+      </x:c>
+      <x:c r="J16" s="97" t="str">
+        <x:v>闪烁</x:v>
+      </x:c>
+      <x:c r="K16" s="97" t="str">
+        <x:v>透明闪烁</x:v>
+      </x:c>
+      <x:c r="L16" s="97" t="str">
+        <x:v>InvincibleTimer 唯一解除</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="70" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B17" s="70" t="str">
+        <x:v>reloading</x:v>
+      </x:c>
+      <x:c r="C17" s="70" t="str">
+        <x:v>换弹</x:v>
+      </x:c>
+      <x:c r="D17" s="70" t="str">
+        <x:v>任意持枪存活态</x:v>
+      </x:c>
+      <x:c r="E17" s="70" t="str">
+        <x:v>不改变顶层；完成/取消退出</x:v>
+      </x:c>
+      <x:c r="F17" s="70" t="str">
+        <x:v>保持当前顶层</x:v>
+      </x:c>
+      <x:c r="G17" s="70" t="str">
+        <x:v>保持当前顶层</x:v>
+      </x:c>
+      <x:c r="H17" s="70" t="str">
+        <x:v>手枪左手近身取弹但不计握持；长枪左手离开护木服务</x:v>
+      </x:c>
+      <x:c r="I17" s="70" t="str">
+        <x:v>右手持续握把并跟随 WeaponSocket 下压/回位</x:v>
+      </x:c>
+      <x:c r="J17" s="70" t="str">
+        <x:v>保持当前顶层</x:v>
+      </x:c>
+      <x:c r="K17" s="70" t="str">
+        <x:v>3D头顶billboard进度条；2D弹药栏</x:v>
+      </x:c>
+      <x:c r="L17" s="70" t="str">
+        <x:v>WeaponModel3D 唯一计时源；WeaponPoseFSM 进入 sidearm_reload/longgun_reload；右手保持握把，左手按武器类型服务</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="70" t="str">
+        <x:v>Enemy3D 九态状态机 × 模块表现 × 模型轮廓碰撞</x:v>
+      </x:c>
+      <x:c r="B18" s="70"/>
+      <x:c r="C18" s="70"/>
+      <x:c r="D18" s="70"/>
+      <x:c r="E18" s="70"/>
+      <x:c r="F18" s="70"/>
+      <x:c r="G18" s="70"/>
+      <x:c r="H18" s="70"/>
+      <x:c r="I18" s="70"/>
+      <x:c r="J18" s="70"/>
+      <x:c r="K18" s="70"/>
+      <x:c r="L18" s="70"/>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="A19" s="70" t="str">
+        <x:v>层级</x:v>
+      </x:c>
+      <x:c r="B19" s="70" t="str">
+        <x:v>状态ID</x:v>
+      </x:c>
+      <x:c r="C19" s="70" t="str">
+        <x:v>中文名</x:v>
+      </x:c>
+      <x:c r="D19" s="70" t="str">
+        <x:v>允许来源</x:v>
+      </x:c>
+      <x:c r="E19" s="70" t="str">
+        <x:v>允许去向</x:v>
+      </x:c>
+      <x:c r="F19" s="70" t="str">
+        <x:v>Core</x:v>
+      </x:c>
+      <x:c r="G19" s="70" t="str">
+        <x:v>Shell</x:v>
+      </x:c>
+      <x:c r="H19" s="70" t="str">
+        <x:v>Appendages</x:v>
+      </x:c>
+      <x:c r="I19" s="70" t="str">
+        <x:v>StateVFX</x:v>
+      </x:c>
+      <x:c r="J19" s="70" t="str">
+        <x:v>行为职责</x:v>
+      </x:c>
+      <x:c r="K19" s="70" t="str">
+        <x:v>验收</x:v>
+      </x:c>
+      <x:c r="L19" s="70" t="str">
+        <x:v>首版实现</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="A20" s="70" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B20" s="70" t="str">
+        <x:v>idle</x:v>
+      </x:c>
+      <x:c r="C20" s="70" t="str">
+        <x:v>待机</x:v>
+      </x:c>
+      <x:c r="D20" s="70" t="str">
+        <x:v>start/patrol/stagger</x:v>
+      </x:c>
+      <x:c r="E20" s="70" t="str">
+        <x:v>patrol/alert/dead</x:v>
+      </x:c>
+      <x:c r="F20" s="70" t="str">
+        <x:v>低频脉冲</x:v>
+      </x:c>
+      <x:c r="G20" s="70" t="str">
+        <x:v>轻浮动</x:v>
+      </x:c>
+      <x:c r="H20" s="70" t="str">
+        <x:v>低速</x:v>
+      </x:c>
+      <x:c r="I20" s="70" t="str">
+        <x:v>关闭</x:v>
+      </x:c>
+      <x:c r="J20" s="70" t="str">
+        <x:v>等待目标</x:v>
+      </x:c>
+      <x:c r="K20" s="70" t="str">
+        <x:v>静态轮廓可读</x:v>
+      </x:c>
+      <x:c r="L20" s="70" t="str">
+        <x:v>模块变换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="70" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B21" s="70" t="str">
+        <x:v>patrol</x:v>
+      </x:c>
+      <x:c r="C21" s="70" t="str">
+        <x:v>巡逻</x:v>
+      </x:c>
+      <x:c r="D21" s="70" t="str">
+        <x:v>idle/search</x:v>
+      </x:c>
+      <x:c r="E21" s="70" t="str">
+        <x:v>idle/alert/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F21" s="70" t="str">
+        <x:v>低频脉冲</x:v>
+      </x:c>
+      <x:c r="G21" s="70" t="str">
+        <x:v>朝巡逻点</x:v>
+      </x:c>
+      <x:c r="H21" s="70" t="str">
+        <x:v>慢速步态</x:v>
+      </x:c>
+      <x:c r="I21" s="70" t="str">
+        <x:v>关闭</x:v>
+      </x:c>
+      <x:c r="J21" s="70" t="str">
+        <x:v>出生点附近巡逻</x:v>
+      </x:c>
+      <x:c r="K21" s="70" t="str">
+        <x:v>无目标不原地僵住</x:v>
+      </x:c>
+      <x:c r="L21" s="70" t="str">
+        <x:v>CharacterBody3D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="A22" s="70" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B22" s="70" t="str">
+        <x:v>alert</x:v>
+      </x:c>
+      <x:c r="C22" s="70" t="str">
+        <x:v>警觉</x:v>
+      </x:c>
+      <x:c r="D22" s="70" t="str">
+        <x:v>idle/patrol/search</x:v>
+      </x:c>
+      <x:c r="E22" s="70" t="str">
+        <x:v>chase/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F22" s="70" t="str">
+        <x:v>加速</x:v>
+      </x:c>
+      <x:c r="G22" s="70" t="str">
+        <x:v>抬升</x:v>
+      </x:c>
+      <x:c r="H22" s="70" t="str">
+        <x:v>展开</x:v>
+      </x:c>
+      <x:c r="I22" s="70" t="str">
+        <x:v>关闭</x:v>
+      </x:c>
+      <x:c r="J22" s="70" t="str">
+        <x:v>发现玩家</x:v>
+      </x:c>
+      <x:c r="K22" s="70" t="str">
+        <x:v>0.28s响应</x:v>
+      </x:c>
+      <x:c r="L22" s="70" t="str">
+        <x:v>模块变换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="70" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B23" s="70" t="str">
+        <x:v>chase</x:v>
+      </x:c>
+      <x:c r="C23" s="70" t="str">
+        <x:v>追击</x:v>
+      </x:c>
+      <x:c r="D23" s="70" t="str">
+        <x:v>alert/attack/stagger</x:v>
+      </x:c>
+      <x:c r="E23" s="70" t="str">
+        <x:v>search/telegraph/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F23" s="70" t="str">
         <x:v>稳定</x:v>
       </x:c>
-      <x:c r="H10" s="37" t="str">
+      <x:c r="G23" s="70" t="str">
+        <x:v>朝目标</x:v>
+      </x:c>
+      <x:c r="H23" s="70" t="str">
+        <x:v>步态</x:v>
+      </x:c>
+      <x:c r="I23" s="70" t="str">
+        <x:v>关闭</x:v>
+      </x:c>
+      <x:c r="J23" s="70" t="str">
+        <x:v>距离控制</x:v>
+      </x:c>
+      <x:c r="K23" s="70" t="str">
+        <x:v>七类速度差</x:v>
+      </x:c>
+      <x:c r="L23" s="70" t="str">
+        <x:v>CharacterBody3D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="A24" s="70" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B24" s="70" t="str">
+        <x:v>search</x:v>
+      </x:c>
+      <x:c r="C24" s="70" t="str">
+        <x:v>搜索</x:v>
+      </x:c>
+      <x:c r="D24" s="70" t="str">
+        <x:v>chase</x:v>
+      </x:c>
+      <x:c r="E24" s="70" t="str">
+        <x:v>patrol/alert/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F24" s="70" t="str">
+        <x:v>渐缓</x:v>
+      </x:c>
+      <x:c r="G24" s="70" t="str">
+        <x:v>朝最后位置</x:v>
+      </x:c>
+      <x:c r="H24" s="70" t="str">
+        <x:v>搜索步态</x:v>
+      </x:c>
+      <x:c r="I24" s="70" t="str">
+        <x:v>搜索提示</x:v>
+      </x:c>
+      <x:c r="J24" s="70" t="str">
+        <x:v>失去视线后搜索</x:v>
+      </x:c>
+      <x:c r="K24" s="70" t="str">
+        <x:v>2.4s后回巡逻</x:v>
+      </x:c>
+      <x:c r="L24" s="70" t="str">
+        <x:v>射线+最后位置</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="70" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B25" s="70" t="str">
+        <x:v>telegraph</x:v>
+      </x:c>
+      <x:c r="C25" s="70" t="str">
+        <x:v>预警</x:v>
+      </x:c>
+      <x:c r="D25" s="70" t="str">
+        <x:v>chase</x:v>
+      </x:c>
+      <x:c r="E25" s="70" t="str">
+        <x:v>attack/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F25" s="70" t="str">
+        <x:v>高频脉冲</x:v>
+      </x:c>
+      <x:c r="G25" s="70" t="str">
         <x:v>稳定</x:v>
       </x:c>
-      <x:c r="I10" s="37" t="str">
-        <x:v>保持握持</x:v>
-      </x:c>
-      <x:c r="J10" s="37" t="str">
-        <x:v>低摆</x:v>
-      </x:c>
-      <x:c r="K10" s="37" t="str">
-        <x:v>琥珀锁定环</x:v>
-      </x:c>
-      <x:c r="L10" s="37" t="str">
-        <x:v>降亮 + 锁定环；保持刚性层级</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="37" t="str">
+      <x:c r="H25" s="70" t="str">
+        <x:v>蓄势</x:v>
+      </x:c>
+      <x:c r="I25" s="70" t="str">
+        <x:v>红色预警环</x:v>
+      </x:c>
+      <x:c r="J25" s="70" t="str">
+        <x:v>攻击前摇</x:v>
+      </x:c>
+      <x:c r="K25" s="70" t="str">
+        <x:v>不可省略</x:v>
+      </x:c>
+      <x:c r="L25" s="70" t="str">
+        <x:v>计时状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="70" t="str">
         <x:v>顶层</x:v>
       </x:c>
-      <x:c r="B11" s="37" t="str">
+      <x:c r="B26" s="70" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="C26" s="70" t="str">
+        <x:v>攻击</x:v>
+      </x:c>
+      <x:c r="D26" s="70" t="str">
+        <x:v>telegraph</x:v>
+      </x:c>
+      <x:c r="E26" s="70" t="str">
+        <x:v>chase/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F26" s="70" t="str">
+        <x:v>峰值</x:v>
+      </x:c>
+      <x:c r="G26" s="70" t="str">
+        <x:v>反冲</x:v>
+      </x:c>
+      <x:c r="H26" s="70" t="str">
+        <x:v>执行</x:v>
+      </x:c>
+      <x:c r="I26" s="70" t="str">
+        <x:v>按攻击类型</x:v>
+      </x:c>
+      <x:c r="J26" s="70" t="str">
+        <x:v>近战/远程/召唤/爆炸</x:v>
+      </x:c>
+      <x:c r="K26" s="70" t="str">
+        <x:v>七类差异</x:v>
+      </x:c>
+      <x:c r="L26" s="70" t="str">
+        <x:v>profile策略</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="70" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B27" s="70" t="str">
+        <x:v>stagger</x:v>
+      </x:c>
+      <x:c r="C27" s="70" t="str">
+        <x:v>硬直</x:v>
+      </x:c>
+      <x:c r="D27" s="70" t="str">
+        <x:v>任意存活态</x:v>
+      </x:c>
+      <x:c r="E27" s="70" t="str">
+        <x:v>chase/dead</x:v>
+      </x:c>
+      <x:c r="F27" s="70" t="str">
+        <x:v>闪色</x:v>
+      </x:c>
+      <x:c r="G27" s="70" t="str">
+        <x:v>冲击</x:v>
+      </x:c>
+      <x:c r="H27" s="70" t="str">
+        <x:v>暂停</x:v>
+      </x:c>
+      <x:c r="I27" s="70" t="str">
+        <x:v>伤害反馈</x:v>
+      </x:c>
+      <x:c r="J27" s="70" t="str">
+        <x:v>受击窗口</x:v>
+      </x:c>
+      <x:c r="K27" s="70" t="str">
+        <x:v>方向可读</x:v>
+      </x:c>
+      <x:c r="L27" s="70" t="str">
+        <x:v>统一伤害入口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="38" customHeight="1">
+      <x:c r="A28" s="102" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B28" s="102" t="str">
         <x:v>dead</x:v>
       </x:c>
-      <x:c r="C11" s="37" t="str">
-        <x:v>生命终止</x:v>
-      </x:c>
-      <x:c r="D11" s="37" t="str">
+      <x:c r="C28" s="102" t="str">
+        <x:v>死亡</x:v>
+      </x:c>
+      <x:c r="D28" s="102" t="str">
         <x:v>任意存活态</x:v>
       </x:c>
-      <x:c r="E11" s="37" t="str">
+      <x:c r="E28" s="102" t="str">
         <x:v>无（终态）</x:v>
       </x:c>
-      <x:c r="F11" s="37" t="str">
-        <x:v>倾倒熄灭</x:v>
-      </x:c>
-      <x:c r="G11" s="37" t="str">
-        <x:v>随整体倾倒</x:v>
-      </x:c>
-      <x:c r="H11" s="37" t="str">
-        <x:v>随整体倾倒</x:v>
-      </x:c>
-      <x:c r="I11" s="37" t="str">
-        <x:v>随整体倾倒</x:v>
-      </x:c>
-      <x:c r="J11" s="37" t="str">
+      <x:c r="F28" s="102" t="str">
+        <x:v>熄灭</x:v>
+      </x:c>
+      <x:c r="G28" s="102" t="str">
+        <x:v>压扁</x:v>
+      </x:c>
+      <x:c r="H28" s="102" t="str">
         <x:v>停止</x:v>
       </x:c>
-      <x:c r="K11" s="37" t="str">
-        <x:v>HUD 终止</x:v>
-      </x:c>
-      <x:c r="L11" s="37" t="str">
-        <x:v>整体倾倒；耳朵与肢体跟随关节</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="37" t="str">
+      <x:c r="I28" s="102" t="str">
+        <x:v>爆散/淡出</x:v>
+      </x:c>
+      <x:c r="J28" s="102" t="str">
+        <x:v>掉落与计数</x:v>
+      </x:c>
+      <x:c r="K28" s="102" t="str">
+        <x:v>不可回存活态</x:v>
+      </x:c>
+      <x:c r="L28" s="102" t="str">
+        <x:v>终态 + Tween</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="38" customHeight="1">
+      <x:c r="A29" s="103"/>
+      <x:c r="B29" s="103"/>
+      <x:c r="C29" s="103"/>
+      <x:c r="D29" s="103"/>
+      <x:c r="E29" s="103"/>
+      <x:c r="F29" s="103"/>
+      <x:c r="G29" s="103"/>
+      <x:c r="H29" s="103"/>
+      <x:c r="I29" s="103"/>
+      <x:c r="J29" s="103"/>
+      <x:c r="K29" s="103"/>
+      <x:c r="L29" s="103"/>
+    </x:row>
+    <x:row r="30" ht="56" customHeight="1">
+      <x:c r="A30" s="70" t="str">
+        <x:v>Player3D 动作覆盖层 × 组件表现（不新增顶层状态）</x:v>
+      </x:c>
+      <x:c r="B30" s="70"/>
+      <x:c r="C30" s="70"/>
+      <x:c r="D30" s="70"/>
+      <x:c r="E30" s="70"/>
+      <x:c r="F30" s="70"/>
+      <x:c r="G30" s="70"/>
+      <x:c r="H30" s="70"/>
+      <x:c r="I30" s="70"/>
+      <x:c r="J30" s="70"/>
+      <x:c r="K30" s="70"/>
+      <x:c r="L30" s="70"/>
+    </x:row>
+    <x:row r="31" ht="56" customHeight="1">
+      <x:c r="A31" s="70" t="str">
+        <x:v>层级｜状态ID｜中文名｜唯一来源｜退出｜Body｜Head｜Hand L（停用）｜Hand（握持）｜Scarf｜VFX/UI｜首版实现</x:v>
+      </x:c>
+      <x:c r="B31" s="70"/>
+      <x:c r="C31" s="70"/>
+      <x:c r="D31" s="70"/>
+      <x:c r="E31" s="70"/>
+      <x:c r="F31" s="70"/>
+      <x:c r="G31" s="70"/>
+      <x:c r="H31" s="70"/>
+      <x:c r="I31" s="70"/>
+      <x:c r="J31" s="70"/>
+      <x:c r="K31" s="70"/>
+      <x:c r="L31" s="70"/>
+    </x:row>
+    <x:row r="32" ht="56" customHeight="1">
+      <x:c r="A32" s="70" t="str">
         <x:v>叠加</x:v>
       </x:c>
-      <x:c r="B12" s="37" t="str">
-        <x:v>low_health</x:v>
-      </x:c>
-      <x:c r="C12" s="37" t="str">
-        <x:v>低血</x:v>
-      </x:c>
-      <x:c r="D12" s="37" t="str">
-        <x:v>任意存活态</x:v>
-      </x:c>
-      <x:c r="E12" s="37" t="str">
-        <x:v>不改变顶层</x:v>
-      </x:c>
-      <x:c r="F12" s="37" t="str">
-        <x:v>不变</x:v>
-      </x:c>
-      <x:c r="G12" s="37" t="str">
-        <x:v>不变</x:v>
-      </x:c>
-      <x:c r="H12" s="37" t="str">
-        <x:v>保持当前动作</x:v>
-      </x:c>
-      <x:c r="I12" s="37" t="str">
-        <x:v>保持当前动作</x:v>
-      </x:c>
-      <x:c r="J12" s="37" t="str">
-        <x:v>不变</x:v>
-      </x:c>
-      <x:c r="K12" s="37" t="str">
-        <x:v>红色呼吸环</x:v>
-      </x:c>
-      <x:c r="L12" s="37" t="str">
-        <x:v>HP≤30%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="37" t="str">
+      <x:c r="B32" s="70" t="str">
+        <x:v>firing</x:v>
+      </x:c>
+      <x:c r="C32" s="70" t="str">
+        <x:v>射击</x:v>
+      </x:c>
+      <x:c r="D32" s="70" t="str">
+        <x:v>WeaponModel3D.shot_fired</x:v>
+      </x:c>
+      <x:c r="E32" s="70" t="str">
+        <x:v>短时回弹后退出</x:v>
+      </x:c>
+      <x:c r="F32" s="70" t="str">
+        <x:v>前探/压缩/弹性回弹</x:v>
+      </x:c>
+      <x:c r="G32" s="70" t="str">
+        <x:v>小幅前探</x:v>
+      </x:c>
+      <x:c r="H32" s="70" t="str">
+        <x:v>手枪左手不继承后坐；长枪左手托举并小幅刚性回弹</x:v>
+      </x:c>
+      <x:c r="I32" s="70" t="str">
+        <x:v>右手握把跟随 WeaponSocket；手枪单腕上挑，长枪双手与躯干共同吃后坐</x:v>
+      </x:c>
+      <x:c r="J32" s="70" t="str">
+        <x:v>受冲量轻摆</x:v>
+      </x:c>
+      <x:c r="K32" s="70" t="str">
+        <x:v>枪口闪光/后坐</x:v>
+      </x:c>
+      <x:c r="L32" s="70" t="str">
+        <x:v>真实 shot_fired 信号；WeaponPoseFSM 进入 sidearm_fire/longgun_fire；七种枪体读取独立 fire_style、kick、pitch、roll、lift 参数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="70" t="str">
         <x:v>叠加</x:v>
       </x:c>
-      <x:c r="B13" s="37" t="str">
-        <x:v>silenced</x:v>
-      </x:c>
-      <x:c r="C13" s="37" t="str">
-        <x:v>沉默</x:v>
-      </x:c>
-      <x:c r="D13" s="37" t="str">
-        <x:v>任意存活态</x:v>
-      </x:c>
-      <x:c r="E13" s="37" t="str">
-        <x:v>不改变顶层</x:v>
-      </x:c>
-      <x:c r="F13" s="37" t="str">
-        <x:v>降饱和可选</x:v>
-      </x:c>
-      <x:c r="G13" s="37" t="str">
-        <x:v>传感器干扰</x:v>
-      </x:c>
-      <x:c r="H13" s="37" t="str">
-        <x:v>保持当前动作</x:v>
-      </x:c>
-      <x:c r="I13" s="37" t="str">
-        <x:v>保持当前动作</x:v>
-      </x:c>
-      <x:c r="J13" s="37" t="str">
-        <x:v>不变</x:v>
-      </x:c>
-      <x:c r="K13" s="37" t="str">
-        <x:v>紫色干扰环</x:v>
-      </x:c>
-      <x:c r="L13" s="37" t="str">
-        <x:v>计时标志</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="37" t="str">
+      <x:c r="B33" s="70" t="str">
+        <x:v>charging</x:v>
+      </x:c>
+      <x:c r="C33" s="70" t="str">
+        <x:v>蓄力</x:v>
+      </x:c>
+      <x:c r="D33" s="70" t="str">
+        <x:v>WeaponModel3D.charge_active / charge_ratio</x:v>
+      </x:c>
+      <x:c r="E33" s="70" t="str">
+        <x:v>释放/取消/换枪/死亡</x:v>
+      </x:c>
+      <x:c r="F33" s="70" t="str">
+        <x:v>下压蓄势</x:v>
+      </x:c>
+      <x:c r="G33" s="70" t="str">
+        <x:v>轻微压低</x:v>
+      </x:c>
+      <x:c r="H33" s="70" t="str">
+        <x:v>长枪左手向内压入形成张力；手枪保持自由手</x:v>
+      </x:c>
+      <x:c r="I33" s="70" t="str">
+        <x:v>右手握把与 WeaponSocket 同相蓄势</x:v>
+      </x:c>
+      <x:c r="J33" s="70" t="str">
+        <x:v>低频张力摆动</x:v>
+      </x:c>
+      <x:c r="K33" s="70" t="str">
+        <x:v>紫色能量提示（可选）</x:v>
+      </x:c>
+      <x:c r="L33" s="70" t="str">
+        <x:v>读取真实蓄力进度；WeaponPoseFSM 进入对应 charge 状态；释放后按枪体 profile 回弹</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="34" customHeight="1">
+      <x:c r="A34" s="102" t="str">
         <x:v>叠加</x:v>
       </x:c>
-      <x:c r="B14" s="37" t="str">
-        <x:v>invincible</x:v>
-      </x:c>
-      <x:c r="C14" s="37" t="str">
-        <x:v>无敌</x:v>
-      </x:c>
-      <x:c r="D14" s="37" t="str">
-        <x:v>dash/hurt</x:v>
-      </x:c>
-      <x:c r="E14" s="37" t="str">
-        <x:v>不改变顶层</x:v>
-      </x:c>
-      <x:c r="F14" s="37" t="str">
-        <x:v>闪烁</x:v>
-      </x:c>
-      <x:c r="G14" s="37" t="str">
-        <x:v>闪烁</x:v>
-      </x:c>
-      <x:c r="H14" s="37" t="str">
-        <x:v>保持当前动作</x:v>
-      </x:c>
-      <x:c r="I14" s="37" t="str">
-        <x:v>保持当前动作</x:v>
-      </x:c>
-      <x:c r="J14" s="37" t="str">
-        <x:v>闪烁</x:v>
-      </x:c>
-      <x:c r="K14" s="37" t="str">
-        <x:v>透明闪烁</x:v>
-      </x:c>
-      <x:c r="L14" s="37" t="str">
-        <x:v>InvincibleTimer 唯一解除</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="56" customHeight="1">
-      <x:c r="A15" s="63" t="str">
-        <x:v>叠加</x:v>
-      </x:c>
-      <x:c r="B15" s="63" t="str">
-        <x:v>reloading</x:v>
-      </x:c>
-      <x:c r="C15" s="63" t="str">
-        <x:v>换弹</x:v>
-      </x:c>
-      <x:c r="D15" s="63" t="str">
-        <x:v>任意持枪存活态</x:v>
-      </x:c>
-      <x:c r="E15" s="63" t="str">
-        <x:v>不改变顶层；完成/取消退出</x:v>
-      </x:c>
-      <x:c r="F15" s="63" t="str">
-        <x:v>保持当前顶层</x:v>
-      </x:c>
-      <x:c r="G15" s="63" t="str">
-        <x:v>保持当前顶层</x:v>
-      </x:c>
-      <x:c r="H15" s="63" t="str">
-        <x:v>手枪左手近身取弹但不计握持；长枪左手离开护木服务</x:v>
-      </x:c>
-      <x:c r="I15" s="63" t="str">
-        <x:v>右手持续握把并跟随 WeaponSocket 下压/回位</x:v>
-      </x:c>
-      <x:c r="J15" s="63" t="str">
-        <x:v>保持当前顶层</x:v>
-      </x:c>
-      <x:c r="K15" s="63" t="str">
-        <x:v>3D头顶billboard进度条；2D弹药栏</x:v>
-      </x:c>
-      <x:c r="L15" s="63" t="str">
-        <x:v>WeaponModel3D 唯一计时源；WeaponPoseFSM 进入 sidearm_reload/longgun_reload；右手保持握把，左手按武器类型服务</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="28" customHeight="1">
-      <x:c r="A16" s="69" t="str">
-        <x:v>Enemy3D 九态状态机 × 模块表现 × 模型轮廓碰撞</x:v>
-      </x:c>
-      <x:c r="B16" s="69"/>
-      <x:c r="C16" s="69"/>
-      <x:c r="D16" s="69"/>
-      <x:c r="E16" s="69"/>
-      <x:c r="F16" s="69"/>
-      <x:c r="G16" s="69"/>
-      <x:c r="H16" s="69"/>
-      <x:c r="I16" s="69"/>
-      <x:c r="J16" s="69"/>
-      <x:c r="K16" s="69"/>
-      <x:c r="L16" s="69"/>
-    </x:row>
-    <x:row r="17" ht="36" customHeight="1">
-      <x:c r="A17" s="63" t="str">
-        <x:v>层级</x:v>
-      </x:c>
-      <x:c r="B17" s="63" t="str">
-        <x:v>状态ID</x:v>
-      </x:c>
-      <x:c r="C17" s="63" t="str">
-        <x:v>中文名</x:v>
-      </x:c>
-      <x:c r="D17" s="63" t="str">
-        <x:v>允许来源</x:v>
-      </x:c>
-      <x:c r="E17" s="63" t="str">
-        <x:v>允许去向</x:v>
-      </x:c>
-      <x:c r="F17" s="63" t="str">
-        <x:v>Core</x:v>
-      </x:c>
-      <x:c r="G17" s="63" t="str">
-        <x:v>Shell</x:v>
-      </x:c>
-      <x:c r="H17" s="63" t="str">
-        <x:v>Appendages</x:v>
-      </x:c>
-      <x:c r="I17" s="63" t="str">
-        <x:v>StateVFX</x:v>
-      </x:c>
-      <x:c r="J17" s="63" t="str">
-        <x:v>行为职责</x:v>
-      </x:c>
-      <x:c r="K17" s="63" t="str">
-        <x:v>验收</x:v>
-      </x:c>
-      <x:c r="L17" s="63" t="str">
-        <x:v>首版实现</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="42" customHeight="1">
-      <x:c r="A18" s="63" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B18" s="63" t="str">
-        <x:v>idle</x:v>
-      </x:c>
-      <x:c r="C18" s="63" t="str">
-        <x:v>待机</x:v>
-      </x:c>
-      <x:c r="D18" s="63" t="str">
-        <x:v>start/patrol/stagger</x:v>
-      </x:c>
-      <x:c r="E18" s="63" t="str">
-        <x:v>patrol/alert/dead</x:v>
-      </x:c>
-      <x:c r="F18" s="63" t="str">
-        <x:v>低频脉冲</x:v>
-      </x:c>
-      <x:c r="G18" s="63" t="str">
-        <x:v>轻浮动</x:v>
-      </x:c>
-      <x:c r="H18" s="63" t="str">
-        <x:v>低速</x:v>
-      </x:c>
-      <x:c r="I18" s="63" t="str">
-        <x:v>关闭</x:v>
-      </x:c>
-      <x:c r="J18" s="63" t="str">
-        <x:v>等待目标</x:v>
-      </x:c>
-      <x:c r="K18" s="63" t="str">
-        <x:v>静态轮廓可读</x:v>
-      </x:c>
-      <x:c r="L18" s="63" t="str">
-        <x:v>模块变换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="42" customHeight="1">
-      <x:c r="A19" s="63" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B19" s="63" t="str">
-        <x:v>patrol</x:v>
-      </x:c>
-      <x:c r="C19" s="63" t="str">
-        <x:v>巡逻</x:v>
-      </x:c>
-      <x:c r="D19" s="63" t="str">
-        <x:v>idle/search</x:v>
-      </x:c>
-      <x:c r="E19" s="63" t="str">
-        <x:v>idle/alert/stagger/dead</x:v>
-      </x:c>
-      <x:c r="F19" s="63" t="str">
-        <x:v>低频脉冲</x:v>
-      </x:c>
-      <x:c r="G19" s="63" t="str">
-        <x:v>朝巡逻点</x:v>
-      </x:c>
-      <x:c r="H19" s="63" t="str">
-        <x:v>慢速步态</x:v>
-      </x:c>
-      <x:c r="I19" s="63" t="str">
-        <x:v>关闭</x:v>
-      </x:c>
-      <x:c r="J19" s="63" t="str">
-        <x:v>出生点附近巡逻</x:v>
-      </x:c>
-      <x:c r="K19" s="63" t="str">
-        <x:v>无目标不原地僵住</x:v>
-      </x:c>
-      <x:c r="L19" s="63" t="str">
-        <x:v>CharacterBody3D</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="42" customHeight="1">
-      <x:c r="A20" s="63" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B20" s="63" t="str">
-        <x:v>alert</x:v>
-      </x:c>
-      <x:c r="C20" s="63" t="str">
-        <x:v>警觉</x:v>
-      </x:c>
-      <x:c r="D20" s="63" t="str">
-        <x:v>idle/patrol/search</x:v>
-      </x:c>
-      <x:c r="E20" s="63" t="str">
-        <x:v>chase/stagger/dead</x:v>
-      </x:c>
-      <x:c r="F20" s="63" t="str">
-        <x:v>加速</x:v>
-      </x:c>
-      <x:c r="G20" s="63" t="str">
-        <x:v>抬升</x:v>
-      </x:c>
-      <x:c r="H20" s="63" t="str">
-        <x:v>展开</x:v>
-      </x:c>
-      <x:c r="I20" s="63" t="str">
-        <x:v>关闭</x:v>
-      </x:c>
-      <x:c r="J20" s="63" t="str">
-        <x:v>发现玩家</x:v>
-      </x:c>
-      <x:c r="K20" s="63" t="str">
-        <x:v>0.28s响应</x:v>
-      </x:c>
-      <x:c r="L20" s="63" t="str">
-        <x:v>模块变换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="63" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B21" s="63" t="str">
-        <x:v>chase</x:v>
-      </x:c>
-      <x:c r="C21" s="63" t="str">
-        <x:v>追击</x:v>
-      </x:c>
-      <x:c r="D21" s="63" t="str">
-        <x:v>alert/attack/stagger</x:v>
-      </x:c>
-      <x:c r="E21" s="63" t="str">
-        <x:v>search/telegraph/stagger/dead</x:v>
-      </x:c>
-      <x:c r="F21" s="63" t="str">
-        <x:v>稳定</x:v>
-      </x:c>
-      <x:c r="G21" s="63" t="str">
-        <x:v>朝目标</x:v>
-      </x:c>
-      <x:c r="H21" s="63" t="str">
-        <x:v>步态</x:v>
-      </x:c>
-      <x:c r="I21" s="63" t="str">
-        <x:v>关闭</x:v>
-      </x:c>
-      <x:c r="J21" s="63" t="str">
-        <x:v>距离控制</x:v>
-      </x:c>
-      <x:c r="K21" s="63" t="str">
-        <x:v>七类速度差</x:v>
-      </x:c>
-      <x:c r="L21" s="63" t="str">
-        <x:v>CharacterBody3D</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="42" customHeight="1">
-      <x:c r="A22" s="63" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B22" s="63" t="str">
-        <x:v>search</x:v>
-      </x:c>
-      <x:c r="C22" s="63" t="str">
-        <x:v>搜索</x:v>
-      </x:c>
-      <x:c r="D22" s="63" t="str">
-        <x:v>chase</x:v>
-      </x:c>
-      <x:c r="E22" s="63" t="str">
-        <x:v>patrol/alert/stagger/dead</x:v>
-      </x:c>
-      <x:c r="F22" s="63" t="str">
-        <x:v>渐缓</x:v>
-      </x:c>
-      <x:c r="G22" s="63" t="str">
-        <x:v>朝最后位置</x:v>
-      </x:c>
-      <x:c r="H22" s="63" t="str">
-        <x:v>搜索步态</x:v>
-      </x:c>
-      <x:c r="I22" s="63" t="str">
-        <x:v>搜索提示</x:v>
-      </x:c>
-      <x:c r="J22" s="63" t="str">
-        <x:v>失去视线后搜索</x:v>
-      </x:c>
-      <x:c r="K22" s="63" t="str">
-        <x:v>2.4s后回巡逻</x:v>
-      </x:c>
-      <x:c r="L22" s="63" t="str">
-        <x:v>射线+最后位置</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="42" customHeight="1">
-      <x:c r="A23" s="63" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B23" s="63" t="str">
-        <x:v>telegraph</x:v>
-      </x:c>
-      <x:c r="C23" s="63" t="str">
-        <x:v>预警</x:v>
-      </x:c>
-      <x:c r="D23" s="63" t="str">
-        <x:v>chase</x:v>
-      </x:c>
-      <x:c r="E23" s="63" t="str">
-        <x:v>attack/stagger/dead</x:v>
-      </x:c>
-      <x:c r="F23" s="63" t="str">
-        <x:v>高频脉冲</x:v>
-      </x:c>
-      <x:c r="G23" s="63" t="str">
-        <x:v>稳定</x:v>
-      </x:c>
-      <x:c r="H23" s="63" t="str">
-        <x:v>蓄势</x:v>
-      </x:c>
-      <x:c r="I23" s="63" t="str">
-        <x:v>红色预警环</x:v>
-      </x:c>
-      <x:c r="J23" s="63" t="str">
-        <x:v>攻击前摇</x:v>
-      </x:c>
-      <x:c r="K23" s="63" t="str">
-        <x:v>不可省略</x:v>
-      </x:c>
-      <x:c r="L23" s="63" t="str">
-        <x:v>计时状态</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="42" customHeight="1">
-      <x:c r="A24" s="63" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B24" s="63" t="str">
-        <x:v>attack</x:v>
-      </x:c>
-      <x:c r="C24" s="63" t="str">
-        <x:v>攻击</x:v>
-      </x:c>
-      <x:c r="D24" s="63" t="str">
-        <x:v>telegraph</x:v>
-      </x:c>
-      <x:c r="E24" s="63" t="str">
-        <x:v>chase/stagger/dead</x:v>
-      </x:c>
-      <x:c r="F24" s="63" t="str">
-        <x:v>峰值</x:v>
-      </x:c>
-      <x:c r="G24" s="63" t="str">
-        <x:v>反冲</x:v>
-      </x:c>
-      <x:c r="H24" s="63" t="str">
-        <x:v>执行</x:v>
-      </x:c>
-      <x:c r="I24" s="63" t="str">
-        <x:v>按攻击类型</x:v>
-      </x:c>
-      <x:c r="J24" s="63" t="str">
-        <x:v>近战/远程/召唤/爆炸</x:v>
-      </x:c>
-      <x:c r="K24" s="63" t="str">
-        <x:v>七类差异</x:v>
-      </x:c>
-      <x:c r="L24" s="63" t="str">
-        <x:v>profile策略</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B25" t="str">
-        <x:v>stagger</x:v>
-      </x:c>
-      <x:c r="C25" t="str">
-        <x:v>硬直</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
-        <x:v>任意存活态</x:v>
-      </x:c>
-      <x:c r="E25" t="str">
-        <x:v>chase/dead</x:v>
-      </x:c>
-      <x:c r="F25" t="str">
-        <x:v>闪色</x:v>
-      </x:c>
-      <x:c r="G25" t="str">
-        <x:v>冲击</x:v>
-      </x:c>
-      <x:c r="H25" t="str">
-        <x:v>暂停</x:v>
-      </x:c>
-      <x:c r="I25" t="str">
-        <x:v>伤害反馈</x:v>
-      </x:c>
-      <x:c r="J25" t="str">
-        <x:v>受击窗口</x:v>
-      </x:c>
-      <x:c r="K25" t="str">
-        <x:v>方向可读</x:v>
-      </x:c>
-      <x:c r="L25" t="str">
-        <x:v>统一伤害入口</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B26" t="str">
-        <x:v>dead</x:v>
-      </x:c>
-      <x:c r="C26" t="str">
-        <x:v>死亡</x:v>
-      </x:c>
-      <x:c r="D26" t="str">
-        <x:v>任意存活态</x:v>
-      </x:c>
-      <x:c r="E26" t="str">
-        <x:v>无（终态）</x:v>
-      </x:c>
-      <x:c r="F26" t="str">
-        <x:v>熄灭</x:v>
-      </x:c>
-      <x:c r="G26" t="str">
-        <x:v>压扁</x:v>
-      </x:c>
-      <x:c r="H26" t="str">
-        <x:v>停止</x:v>
-      </x:c>
-      <x:c r="I26" t="str">
-        <x:v>爆散/淡出</x:v>
-      </x:c>
-      <x:c r="J26" t="str">
-        <x:v>掉落与计数</x:v>
-      </x:c>
-      <x:c r="K26" t="str">
-        <x:v>不可回存活态</x:v>
-      </x:c>
-      <x:c r="L26" t="str">
-        <x:v>终态 + Tween</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="38" customHeight="1">
-      <x:c r="A28" s="81" t="str">
-        <x:v>Player3D 动作覆盖层 × 组件表现（不新增顶层状态）</x:v>
-      </x:c>
-      <x:c r="B28" s="81"/>
-      <x:c r="C28" s="81"/>
-      <x:c r="D28" s="81"/>
-      <x:c r="E28" s="81"/>
-      <x:c r="F28" s="81"/>
-      <x:c r="G28" s="81"/>
-      <x:c r="H28" s="81"/>
-      <x:c r="I28" s="81"/>
-      <x:c r="J28" s="81"/>
-      <x:c r="K28" s="81"/>
-      <x:c r="L28" s="81"/>
-    </x:row>
-    <x:row r="29" ht="38" customHeight="1">
-      <x:c r="A29" s="82" t="str">
-        <x:v>层级｜状态ID｜中文名｜唯一来源｜退出｜Body｜Head｜Hand L（停用）｜Hand（握持）｜Scarf｜VFX/UI｜首版实现</x:v>
-      </x:c>
-      <x:c r="B29" s="82"/>
-      <x:c r="C29" s="82"/>
-      <x:c r="D29" s="82"/>
-      <x:c r="E29" s="82"/>
-      <x:c r="F29" s="82"/>
-      <x:c r="G29" s="82"/>
-      <x:c r="H29" s="82"/>
-      <x:c r="I29" s="82"/>
-      <x:c r="J29" s="82"/>
-      <x:c r="K29" s="82"/>
-      <x:c r="L29" s="82"/>
-    </x:row>
-    <x:row r="30" ht="56" customHeight="1">
-      <x:c r="A30" s="63" t="str">
-        <x:v>叠加</x:v>
-      </x:c>
-      <x:c r="B30" s="63" t="str">
-        <x:v>firing</x:v>
-      </x:c>
-      <x:c r="C30" s="63" t="str">
-        <x:v>射击</x:v>
-      </x:c>
-      <x:c r="D30" s="63" t="str">
-        <x:v>WeaponModel3D.shot_fired</x:v>
-      </x:c>
-      <x:c r="E30" s="63" t="str">
-        <x:v>短时回弹后退出</x:v>
-      </x:c>
-      <x:c r="F30" s="63" t="str">
-        <x:v>前探/压缩/弹性回弹</x:v>
-      </x:c>
-      <x:c r="G30" s="63" t="str">
-        <x:v>小幅前探</x:v>
-      </x:c>
-      <x:c r="H30" s="63" t="str">
-        <x:v>手枪左手不继承后坐；长枪左手托举并小幅刚性回弹</x:v>
-      </x:c>
-      <x:c r="I30" s="63" t="str">
-        <x:v>右手握把跟随 WeaponSocket；手枪单腕上挑，长枪双手与躯干共同吃后坐</x:v>
-      </x:c>
-      <x:c r="J30" s="63" t="str">
-        <x:v>受冲量轻摆</x:v>
-      </x:c>
-      <x:c r="K30" s="63" t="str">
-        <x:v>枪口闪光/后坐</x:v>
-      </x:c>
-      <x:c r="L30" s="63" t="str">
-        <x:v>真实 shot_fired 信号；WeaponPoseFSM 进入 sidearm_fire/longgun_fire；七种枪体读取独立 fire_style、kick、pitch、roll、lift 参数</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="56" customHeight="1">
-      <x:c r="A31" s="63" t="str">
-        <x:v>叠加</x:v>
-      </x:c>
-      <x:c r="B31" s="63" t="str">
-        <x:v>charging</x:v>
-      </x:c>
-      <x:c r="C31" s="63" t="str">
-        <x:v>蓄力</x:v>
-      </x:c>
-      <x:c r="D31" s="63" t="str">
-        <x:v>WeaponModel3D.charge_active / charge_ratio</x:v>
-      </x:c>
-      <x:c r="E31" s="63" t="str">
-        <x:v>释放/取消/换枪/死亡</x:v>
-      </x:c>
-      <x:c r="F31" s="63" t="str">
-        <x:v>下压蓄势</x:v>
-      </x:c>
-      <x:c r="G31" s="63" t="str">
-        <x:v>轻微压低</x:v>
-      </x:c>
-      <x:c r="H31" s="63" t="str">
-        <x:v>长枪左手向内压入形成张力；手枪保持自由手</x:v>
-      </x:c>
-      <x:c r="I31" s="63" t="str">
-        <x:v>右手握把与 WeaponSocket 同相蓄势</x:v>
-      </x:c>
-      <x:c r="J31" s="63" t="str">
-        <x:v>低频张力摆动</x:v>
-      </x:c>
-      <x:c r="K31" s="63" t="str">
-        <x:v>紫色能量提示（可选）</x:v>
-      </x:c>
-      <x:c r="L31" s="63" t="str">
-        <x:v>读取真实蓄力进度；WeaponPoseFSM 进入对应 charge 状态；释放后按枪体 profile 回弹</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="56" customHeight="1">
-      <x:c r="A32" s="63" t="str">
-        <x:v>叠加</x:v>
-      </x:c>
-      <x:c r="B32" s="63" t="str">
+      <x:c r="B34" s="102" t="str">
         <x:v>knockback</x:v>
       </x:c>
-      <x:c r="C32" s="63" t="str">
+      <x:c r="C34" s="102" t="str">
         <x:v>受击击飞</x:v>
       </x:c>
-      <x:c r="D32" s="63" t="str">
+      <x:c r="D34" s="102" t="str">
         <x:v>Player3D 命中方向/强度/时长</x:v>
       </x:c>
-      <x:c r="E32" s="63" t="str">
+      <x:c r="E34" s="102" t="str">
         <x:v>冲量归零或死亡</x:v>
       </x:c>
-      <x:c r="F32" s="63" t="str">
+      <x:c r="F34" s="102" t="str">
         <x:v>反向位移/压缩/弹回</x:v>
       </x:c>
-      <x:c r="G32" s="63" t="str">
+      <x:c r="G34" s="102" t="str">
         <x:v>夸张后仰甩头/回正</x:v>
       </x:c>
-      <x:c r="H32" s="63" t="str">
+      <x:c r="H34" s="102" t="str">
         <x:v>手枪自由左手外甩；长枪左手回护木</x:v>
       </x:c>
-      <x:c r="I32" s="63" t="str">
+      <x:c r="I34" s="102" t="str">
         <x:v>右手与 WeaponSocket 同相后退/回正</x:v>
       </x:c>
-      <x:c r="J32" s="63" t="str">
+      <x:c r="J34" s="102" t="str">
         <x:v>滞后甩动</x:v>
       </x:c>
-      <x:c r="K32" s="63" t="str">
+      <x:c r="K34" s="102" t="str">
         <x:v>红闪/短轨迹</x:v>
       </x:c>
-      <x:c r="L32" s="63" t="str">
+      <x:c r="L34" s="102" t="str">
         <x:v>hurt 消费递减XZ冲量；双耳/双脚/双手分层过冲，不新增顶层状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="34" customHeight="1">
-      <x:c r="A34" s="93" t="str">
-        <x:v>Player3D DIY 外观槽 × 动态继承（不影响六态/玩法）</x:v>
-      </x:c>
-      <x:c r="B34" s="93"/>
-      <x:c r="C34" s="93"/>
-      <x:c r="D34" s="93"/>
-      <x:c r="E34" s="93"/>
-      <x:c r="F34" s="93"/>
-      <x:c r="G34" s="93"/>
-      <x:c r="H34" s="93"/>
-      <x:c r="I34" s="93"/>
-      <x:c r="J34" s="93"/>
-      <x:c r="K34" s="93"/>
-      <x:c r="L34" s="93"/>
-    </x:row>
     <x:row r="35" ht="34" customHeight="1">
-      <x:c r="A35" s="94" t="str">
+      <x:c r="A35" s="103"/>
+      <x:c r="B35" s="103"/>
+      <x:c r="C35" s="103"/>
+      <x:c r="D35" s="103"/>
+      <x:c r="E35" s="103"/>
+      <x:c r="F35" s="103"/>
+      <x:c r="G35" s="103"/>
+      <x:c r="H35" s="103"/>
+      <x:c r="I35" s="103"/>
+      <x:c r="J35" s="103"/>
+      <x:c r="K35" s="103"/>
+      <x:c r="L35" s="103"/>
+    </x:row>
+    <x:row r="36" ht="34" customHeight="1">
+      <x:c r="A36" s="70" t="str">
+        <x:v>Player3D DIY 外观槽 × 动态继承（不影响八态/玩法）</x:v>
+      </x:c>
+      <x:c r="B36" s="70"/>
+      <x:c r="C36" s="70"/>
+      <x:c r="D36" s="70"/>
+      <x:c r="E36" s="70"/>
+      <x:c r="F36" s="70"/>
+      <x:c r="G36" s="70"/>
+      <x:c r="H36" s="70"/>
+      <x:c r="I36" s="70"/>
+      <x:c r="J36" s="70"/>
+      <x:c r="K36" s="70"/>
+      <x:c r="L36" s="70"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="70" t="str">
         <x:v>槽位｜候选变体｜父组件｜移动｜射击/蓄力｜受击/击飞｜换弹｜死亡｜挂点契约｜验收｜复用范围｜首版实现</x:v>
       </x:c>
-      <x:c r="B35" s="94"/>
-      <x:c r="C35" s="94"/>
-      <x:c r="D35" s="94"/>
-      <x:c r="E35" s="94"/>
-      <x:c r="F35" s="94"/>
-      <x:c r="G35" s="94"/>
-      <x:c r="H35" s="94"/>
-      <x:c r="I35" s="94"/>
-      <x:c r="J35" s="94"/>
-      <x:c r="K35" s="94"/>
-      <x:c r="L35" s="94"/>
-    </x:row>
-    <x:row r="36" ht="34" customHeight="1">
-      <x:c r="A36" s="63" t="str">
+      <x:c r="B37" s="70"/>
+      <x:c r="C37" s="70"/>
+      <x:c r="D37" s="70"/>
+      <x:c r="E37" s="70"/>
+      <x:c r="F37" s="70"/>
+      <x:c r="G37" s="70"/>
+      <x:c r="H37" s="70"/>
+      <x:c r="I37" s="70"/>
+      <x:c r="J37" s="70"/>
+      <x:c r="K37" s="70"/>
+      <x:c r="L37" s="70"/>
+    </x:row>
+    <x:row r="38" ht="38" customHeight="1">
+      <x:c r="A38" s="70" t="str">
         <x:v>body/head/hand/feet/hat/glasses</x:v>
       </x:c>
-      <x:c r="B36" s="63" t="str">
+      <x:c r="B38" s="70" t="str">
         <x:v>4+4+4+4+3+3</x:v>
       </x:c>
-      <x:c r="C36" s="63" t="str">
+      <x:c r="C38" s="70" t="str">
         <x:v>Body/Head/Hand/Feet/Wearables</x:v>
       </x:c>
-      <x:c r="D36" s="63" t="str">
+      <x:c r="D38" s="70" t="str">
         <x:v>身体弹性+双脚交替+圆短尾轻摆</x:v>
       </x:c>
-      <x:c r="E36" s="63" t="str">
+      <x:c r="E38" s="70" t="str">
         <x:v>手/枪同相后坐；头前探</x:v>
       </x:c>
-      <x:c r="F36" s="63" t="str">
+      <x:c r="F38" s="70" t="str">
         <x:v>整体后仰/脚随根回正</x:v>
       </x:c>
-      <x:c r="G36" s="63" t="str">
+      <x:c r="G38" s="70" t="str">
         <x:v>Hand+Socket同相</x:v>
       </x:c>
-      <x:c r="H36" s="63" t="str">
+      <x:c r="H38" s="70" t="str">
         <x:v>四主模块随根倾倒</x:v>
       </x:c>
-      <x:c r="I36" s="63" t="str">
+      <x:c r="I38" s="70" t="str">
         <x:v>唯一手/挂点相对向量固定</x:v>
       </x:c>
-      <x:c r="J36" s="63" t="str">
-        <x:v>四主模块+双眼双耳短尾+六态覆盖</x:v>
-      </x:c>
-      <x:c r="K36" s="63" t="str">
+      <x:c r="J38" s="70" t="str">
+        <x:v>四主模块+双眼双耳短尾+八态覆盖</x:v>
+      </x:c>
+      <x:c r="K38" s="70" t="str">
         <x:v>3D玩家/预览场</x:v>
       </x:c>
-      <x:c r="L36" s="63" t="str">
+      <x:c r="L38" s="70" t="str">
         <x:v>Godot原生方体/三角耳/圆尾；Player3D.set_avatar_customization</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="38" customHeight="1">
-      <x:c r="A38" s="63" t="str">
+    <x:row r="39" ht="38" customHeight="1">
+      <x:c r="A39" s="70"/>
+      <x:c r="B39" s="70"/>
+      <x:c r="C39" s="70"/>
+      <x:c r="D39" s="70"/>
+      <x:c r="E39" s="70"/>
+      <x:c r="F39" s="70"/>
+      <x:c r="G39" s="70"/>
+      <x:c r="H39" s="70"/>
+      <x:c r="I39" s="70"/>
+      <x:c r="J39" s="70"/>
+      <x:c r="K39" s="70"/>
+      <x:c r="L39" s="70"/>
+    </x:row>
+    <x:row r="40" ht="38" customHeight="1">
+      <x:c r="A40" s="70" t="str">
         <x:v>PH33 方形猫子组件 × 动作归属（不新增状态）</x:v>
       </x:c>
-      <x:c r="B38" s="63"/>
-      <x:c r="C38" s="63"/>
-      <x:c r="D38" s="63"/>
-      <x:c r="E38" s="63"/>
-      <x:c r="F38" s="63"/>
-      <x:c r="G38" s="63"/>
-      <x:c r="H38" s="63"/>
-      <x:c r="I38" s="63"/>
-      <x:c r="J38" s="63"/>
-      <x:c r="K38" s="63"/>
-      <x:c r="L38" s="63"/>
-    </x:row>
-    <x:row r="39" ht="38" customHeight="1">
-      <x:c r="A39" s="63" t="str">
+      <x:c r="B40" s="70"/>
+      <x:c r="C40" s="70"/>
+      <x:c r="D40" s="70"/>
+      <x:c r="E40" s="70"/>
+      <x:c r="F40" s="70"/>
+      <x:c r="G40" s="70"/>
+      <x:c r="H40" s="70"/>
+      <x:c r="I40" s="70"/>
+      <x:c r="J40" s="70"/>
+      <x:c r="K40" s="70"/>
+      <x:c r="L40" s="70"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="70" t="str">
         <x:v>父模块｜子组件｜节点数量｜Idle｜Moving｜Dashing｜Hurt/Knockback｜Reload/Fire｜Dead｜图形语言｜禁止事项｜验收</x:v>
       </x:c>
-      <x:c r="B39" s="63"/>
-      <x:c r="C39" s="63"/>
-      <x:c r="D39" s="63"/>
-      <x:c r="E39" s="63"/>
-      <x:c r="F39" s="63"/>
-      <x:c r="G39" s="63"/>
-      <x:c r="H39" s="63"/>
-      <x:c r="I39" s="63"/>
-      <x:c r="J39" s="63"/>
-      <x:c r="K39" s="63"/>
-      <x:c r="L39" s="63"/>
-    </x:row>
-    <x:row r="40" ht="38" customHeight="1">
-      <x:c r="A40" s="63" t="str">
+      <x:c r="B41" s="70"/>
+      <x:c r="C41" s="70"/>
+      <x:c r="D41" s="70"/>
+      <x:c r="E41" s="70"/>
+      <x:c r="F41" s="70"/>
+      <x:c r="G41" s="70"/>
+      <x:c r="H41" s="70"/>
+      <x:c r="I41" s="70"/>
+      <x:c r="J41" s="70"/>
+      <x:c r="K41" s="70"/>
+      <x:c r="L41" s="70"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="70" t="str">
         <x:v>Head / Body / Feet</x:v>
       </x:c>
-      <x:c r="B40" s="63" t="str">
+      <x:c r="B42" s="70" t="str">
         <x:v>Eyes / Ears / TailStub / FootL / FootR</x:v>
       </x:c>
-      <x:c r="C40" s="63" t="str">
+      <x:c r="C42" s="70" t="str">
         <x:v>2 / 2 / 1 / 2</x:v>
       </x:c>
-      <x:c r="D40" s="63" t="str">
+      <x:c r="D42" s="70" t="str">
         <x:v>双眼双耳稳定；短尾微摆</x:v>
       </x:c>
-      <x:c r="E40" s="63" t="str">
+      <x:c r="E42" s="70" t="str">
         <x:v>双脚交替抬起；短尾轻摆</x:v>
       </x:c>
-      <x:c r="F40" s="63" t="str">
+      <x:c r="F42" s="70" t="str">
         <x:v>随VisualRoot压缩</x:v>
       </x:c>
-      <x:c r="G40" s="63" t="str">
+      <x:c r="G42" s="70" t="str">
         <x:v>随父模块后仰回正</x:v>
       </x:c>
-      <x:c r="H40" s="63" t="str">
+      <x:c r="H42" s="70" t="str">
         <x:v>手/枪动作不牵动脚；头部继承</x:v>
       </x:c>
-      <x:c r="I40" s="63" t="str">
+      <x:c r="I42" s="70" t="str">
         <x:v>随父模块倾倒</x:v>
       </x:c>
-      <x:c r="J40" s="63" t="str">
+      <x:c r="J42" s="70" t="str">
         <x:v>方头方身方手方脚；圆尾唯一例外</x:v>
       </x:c>
-      <x:c r="K40" s="63" t="str">
+      <x:c r="K42" s="70" t="str">
         <x:v>嘴/鼻/第二手/长尾/烘焙跨模块</x:v>
       </x:c>
-      <x:c r="L40" s="63" t="str">
+      <x:c r="L42" s="70" t="str">
         <x:v>节点路径+数量+步态+持枪+视觉</x:v>
       </x:c>
     </x:row>
@@ -15272,13 +15878,13 @@
   <x:mergeCells>
     <x:mergeCell ref="A1:L2"/>
     <x:mergeCell ref="A3:L3"/>
-    <x:mergeCell ref="A16:L16"/>
-    <x:mergeCell ref="A28:L28"/>
-    <x:mergeCell ref="A29:L29"/>
-    <x:mergeCell ref="A34:L34"/>
-    <x:mergeCell ref="A35:L35"/>
-    <x:mergeCell ref="A38:L38"/>
-    <x:mergeCell ref="A39:L39"/>
+    <x:mergeCell ref="A18:L18"/>
+    <x:mergeCell ref="A30:L30"/>
+    <x:mergeCell ref="A31:L31"/>
+    <x:mergeCell ref="A36:L36"/>
+    <x:mergeCell ref="A37:L37"/>
+    <x:mergeCell ref="A40:L40"/>
+    <x:mergeCell ref="A41:L41"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -16737,6 +17343,282 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="22" ht="72" customHeight="1">
+      <x:c r="A22" s="63" t="str">
+        <x:v>v1.16</x:v>
+      </x:c>
+      <x:c r="B22" s="64" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="C22" s="63" t="str">
+        <x:v>塔楼Blender三层堆叠版登记</x:v>
+      </x:c>
+      <x:c r="D22" s="63" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="E22" s="63" t="str">
+        <x:v>将旧v001横向组件评审板保留为历史版本；登记独立v002三层真实堆叠文件，含楼板、外墙、室内隔墙、15扇门及西/东两段实际楼梯，并修复同名文件覆盖导致的评审图不一致。</x:v>
+      </x:c>
+      <x:c r="F22" s="63" t="str">
+        <x:v>AssetID不变；只升级Blender评审源文件版本；确认前不导出GLB、不接入Godot。</x:v>
+      </x:c>
+      <x:c r="G22" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="78" customHeight="1">
+      <x:c r="A23" s="63" t="str">
+        <x:v>v1.17</x:v>
+      </x:c>
+      <x:c r="B23" s="64" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C23" s="63" t="str">
+        <x:v>塔楼双楼梯与五倍边长地图登记</x:v>
+      </x:c>
+      <x:c r="D23" s="63" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="E23" s="63" t="str">
+        <x:v>将用户手工v003保存为快照；登记v004特殊楼顶梯与通用旋转梯、02_STAIRWELLS集合层级、核心门口连接板、335.410m总占地、67.082m中央核心和空外围楼板。</x:v>
+      </x:c>
+      <x:c r="F23" s="63" t="str">
+        <x:v>AssetID不变；v003可回退；只升级Blender评审源文件，确认前不导出GLB、不接入Godot。</x:v>
+      </x:c>
+      <x:c r="G23" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="100" customHeight="1">
+      <x:c r="A24" s="63" t="str">
+        <x:v>v1.18</x:v>
+      </x:c>
+      <x:c r="B24" s="64" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C24" s="63" t="str">
+        <x:v>塔楼整层外壳五倍边长修正</x:v>
+      </x:c>
+      <x:c r="D24" s="63" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="E24" s="63" t="str">
+        <x:v>登记v005：楼顶女儿墙、基地外墙、战斗层外墙全部移到335.410m总楼层边界；旧核心满高外墙取消，67.082m中央核心、楼梯、门、设施和内部隔墙保持原尺寸。</x:v>
+      </x:c>
+      <x:c r="F24" s="63" t="str">
+        <x:v>AssetID不变；v004可回退；只修正Blender评审母版，确认前不导出GLB、不接入Godot。</x:v>
+      </x:c>
+      <x:c r="G24" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="115" customHeight="1">
+      <x:c r="A25" s="63" t="str">
+        <x:v>v1.19</x:v>
+      </x:c>
+      <x:c r="B25" s="64" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C25" s="63" t="str">
+        <x:v>塔楼五米模块化楼层与墙体</x:v>
+      </x:c>
+      <x:c r="D25" s="63" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D; ENV-TOWER-FLOOR-TILE-5M; ENV-TOWER-WALL-SOLID-5M; ENV-TOWER-WALL-PARAPET-5M; ENV-TOWER-WALL-DOOR-5M</x:v>
+      </x:c>
+      <x:c r="E25" s="63" t="str">
+        <x:v>登记v006：335m整层与65m基地/战斗核心全部对齐5m网格；地砖、满高墙、楼顶女儿墙、带门墙成为四个稳定子资产，基地完整围合，战斗内墙和门可独立拼装。</x:v>
+      </x:c>
+      <x:c r="F25" s="63" t="str">
+        <x:v>v005用户内存状态另存快照；楼梯手调结构不重做。四个子资产当前仅为Blender程序占位，未导出GLB、未接入Godot。</x:v>
+      </x:c>
+      <x:c r="G25" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="118" customHeight="1">
+      <x:c r="A26" s="70" t="str">
+        <x:v>v1.20</x:v>
+      </x:c>
+      <x:c r="B26" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C26" s="70" t="str">
+        <x:v>塔楼5m GLB与99—95层Godot首批关卡接入</x:v>
+      </x:c>
+      <x:c r="D26" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D及四个5m子资产</x:v>
+      </x:c>
+      <x:c r="E26" s="70" t="str">
+        <x:v>四个Blender模块导出独立GLB并接入335m楼顶、99层基地、98—95层五房+电梯探索关卡；登记9m双跑楼梯、门后命运、Boss/撤离、城市日照、智能剖切与≤5层流送验收。</x:v>
+      </x:c>
+      <x:c r="F26" s="70" t="str">
+        <x:v>AssetID与v006 Blender母版不变；子资产状态由程序占位升级为原型已接入；旧四主题Dungeon3D玩法继续共用。</x:v>
+      </x:c>
+      <x:c r="G26" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="118" customHeight="1">
+      <x:c r="A27" s="70" t="str">
+        <x:v>v1.21</x:v>
+      </x:c>
+      <x:c r="B27" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C27" s="70" t="str">
+        <x:v>Blender楼梯直入与99—95层种子化关卡</x:v>
+      </x:c>
+      <x:c r="D27" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D; ENV-TOWER-STAIRWELL-GENERIC-9M; ENV-TOWER-STAIRWELL-ROOFTOP-9M</x:v>
+      </x:c>
+      <x:c r="E27" s="70" t="str">
+        <x:v>两套用户手调楼梯从v006根节点直接导出GLB并接入Godot；登记前三段门禁差异、四类种子化房间模板、固定电梯、95层Boss、城市/室内光、智能遮挡与≤5层流送。</x:v>
+      </x:c>
+      <x:c r="F27" s="70" t="str">
+        <x:v>新增两个楼梯子AssetID，不复制程序踏步；四个5m模块ID和母版ID不变；运行时碰撞/吸附与Blender视觉职责分离。</x:v>
+      </x:c>
+      <x:c r="G27" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="118" customHeight="1">
+      <x:c r="A28" s="70" t="str">
+        <x:v>v1.22</x:v>
+      </x:c>
+      <x:c r="B28" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C28" s="70" t="str">
+        <x:v>bunny01完整视觉与碰撞统一为1米</x:v>
+      </x:c>
+      <x:c r="D28" s="70" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01及六个稳定组件AssetID</x:v>
+      </x:c>
+      <x:c r="E28" s="70" t="str">
+        <x:v>从v004派生真实1m Blender v005与七个pivot-local GLB；Godot改用v005装配，碰撞体高1m，持枪视觉、挂点、可穿戴、VFX和全部米制动作平移同步缩放。</x:v>
+      </x:c>
+      <x:c r="F28" s="70" t="str">
+        <x:v>不新增角色AssetID；v004保留回退。静态AABB、六态、武器姿势、碰撞、DIY、换弹、塔楼与性能验收通过。</x:v>
+      </x:c>
+      <x:c r="G28" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="84" hidden="0" customHeight="1">
+      <x:c r="A29" s="70" t="str">
+        <x:v>v1.23</x:v>
+      </x:c>
+      <x:c r="B29" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C29" s="70" t="str">
+        <x:v>bunny01正式定版为1.5米</x:v>
+      </x:c>
+      <x:c r="D29" s="70" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01及六个稳定组件AssetID</x:v>
+      </x:c>
+      <x:c r="E29" s="70" t="str">
+        <x:v>从一米v005等比烘焙真实1.5m Blender v006、七个pivot-local GLB与Godot v006装配；取消Avatar3D临时1.5倍缩放，碰撞、挂点、附件与米制动画固定为1.5m契约。</x:v>
+      </x:c>
+      <x:c r="F29" s="70" t="str">
+        <x:v>不新增AssetID；v005保留回退。Blender/Godot AABB、武器姿势、碰撞、六态、DIY、换弹、塔楼楼梯和PH40镜头验收通过。</x:v>
+      </x:c>
+      <x:c r="G29" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="118" customHeight="1">
+      <x:c r="A30" s="70" t="str">
+        <x:v>v1.24</x:v>
+      </x:c>
+      <x:c r="B30" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C30" s="70" t="str">
+        <x:v>PH43楼梯承重、下落落地与屋顶可读性</x:v>
+      </x:c>
+      <x:c r="D30" s="70" t="str">
+        <x:v>Player3D / bunny01 v006 / 两套9m楼梯 / 楼顶洞口与镜头</x:v>
+      </x:c>
+      <x:c r="E30" s="70" t="str">
+        <x:v>六态扩展为八态falling/landing；1.5m玩法碰撞改胶囊；楼梯取消Y吸附并合并连续三角承重面；掉落/钥匙向下找承重面；导入墙补同形碰撞；楼顶洞口收紧、8m镜头侧向避障并加物理天空反弹光；进入特殊楼梯围护体立即启用角色探照灯。</x:v>
+      </x:c>
+      <x:c r="F30" s="70" t="str">
+        <x:v>不新增角色/楼梯AssetID、GLB或贴图；v006模型尺寸和单太阳参数不变；原战斗/命运/枪械/流送兼容。</x:v>
+      </x:c>
+      <x:c r="G30" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="118" customHeight="1">
+      <x:c r="A31" s="70" t="str">
+        <x:v>v1.25</x:v>
+      </x:c>
+      <x:c r="B31" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C31" s="70" t="str">
+        <x:v>PH43楼梯Walkable根因修复与固定镜头</x:v>
+      </x:c>
+      <x:c r="D31" s="70" t="str">
+        <x:v>Player3D / bunny01 v006 / 两套9m楼梯 / 楼顶洞口与镜头</x:v>
+      </x:c>
+      <x:c r="E31" s="70" t="str">
+        <x:v>六态扩展为八态falling/landing；1.5m玩法碰撞改胶囊；楼梯取消Y吸附与程序路径承重面，直接采用v006每套六块*Walkable网格同形常驻碰撞；掉落/钥匙向下找承重面；EnclosureWall补围护碰撞；楼顶洞口收紧并加物理天空反弹光；镜头固定(0,8,5.5)、FOV 55°，每物理帧覆盖外部位移与旋转；进入特殊楼梯围护体立即启用角色探照灯。</x:v>
+      </x:c>
+      <x:c r="F31" s="70" t="str">
+        <x:v>不新增角色/楼梯AssetID、GLB或贴图；v006模型尺寸和单太阳参数不变；原战斗/命运/枪械/流送兼容。</x:v>
+      </x:c>
+      <x:c r="G31" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="118" customHeight="1">
+      <x:c r="A32" s="70" t="str">
+        <x:v>v1.26</x:v>
+      </x:c>
+      <x:c r="B32" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C32" s="70" t="str">
+        <x:v>PH44二百五十米塔楼与四乘四战斗层重构</x:v>
+      </x:c>
+      <x:c r="D32" s="70" t="str">
+        <x:v>塔楼整层 / 5m地砖与墙体 / 两套9m楼梯 / 固定镜头局部剖切</x:v>
+      </x:c>
+      <x:c r="E32" s="70" t="str">
+        <x:v>整层统一50×50格（250×250m、2500砖）；65×65m基地核心不变并偏移2.5m对齐；普通层12个45×45m房间，Boss层90×90m Boss区+9个普通房；实墙按方向MultiMesh批渲染并合并碰撞；上下楼梯分别记录两端门侧；固定8m镜头只剖切挡住角色的墙体渲染；楼顶天空反弹光降至1.25。</x:v>
+      </x:c>
+      <x:c r="F32" s="70" t="str">
+        <x:v>不新增AssetID、GLB或贴图；v006楼梯与既有5m模块继续复用；碰撞、房门、命运卡、刷怪、流送和固定镜头角度保持兼容。完整探索节点数2783。</x:v>
+      </x:c>
+      <x:c r="G32" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="128" customHeight="1">
+      <x:c r="A33" s="70" t="str">
+        <x:v>v1.27</x:v>
+      </x:c>
+      <x:c r="B33" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C33" s="70" t="str">
+        <x:v>PH49九十八至九十五层终局关卡与全局系统验收</x:v>
+      </x:c>
+      <x:c r="D33" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D; ENV-TOWER-WALL-DOOR-5M; ENV-DUNGEON-RUNTIME-3D; PRP-BASE-FACILITY-3D; PRP-WASTELAND-LIGHT-3D; PRP-ROOM-LIGHT-SWITCH-3D; UI-SCREEN-HUD; CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="E33" s="70" t="str">
+        <x:v>完成98—95层怪物、搜刮、随机房间/掉落与95层Boss撤离闭环；基地30×30m/6×6格；修正98层入口内外侧；电梯改为墙边独立设施；门统一2.2×2.5m；环境光改为全局固定；关闭会让墙体概率消失的相机材质淡出；基地四灯组和开关；实时3D全息小地图与游戏化HUD。</x:v>
+      </x:c>
+      <x:c r="F33" s="70" t="str">
+        <x:v>Blender v007与Godot布局同步；导出门v002 GLB；三份仓库外角色Blender源归档进项目且不新增重复AssetID。主流程、全部楼层门、实际楼梯、灯光开关、随机种子、Boss撤离、相机遮挡和性能预算均有自动验收。</x:v>
+      </x:c>
+      <x:c r="G33" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G2"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R218cf9748d8b4aed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R073888a90f714d22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R5f820dbf49c74ee1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Raf6cce13e4144cd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R935bbfa5dcee4864"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Ra417ce902b7c4a92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Raddac6b3c69e4a0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rd3ef4d61aa654bfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf84ca10cd5ed4d24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rf5a2a1a12f2c4332"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rb2bd3d1075a745c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R8df505db60d1424e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Reeff2b36bfb14845"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R4f9e39ce2b484273"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R686a524d7a334e8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R602a90e65fc44325"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11134,11 +11134,11 @@
       <x:c r="V144" s="62" t="n">
         <x:v>46225</x:v>
       </x:c>
-      <x:c r="W144" t="n">
+      <x:c r="W144" s="62" t="n">
         <x:v>46235</x:v>
       </x:c>
       <x:c r="X144" t="str">
-        <x:v>PH50：前向SpotLight仅命中环境layer1并允许环境/怪物投影；玩家、穿戴物与手持枪固定在layer2，因此不会被自己的前向灯自投影。layer2只接受微弱无阴影正面补光；房间灯与太阳仍覆盖layer1+2，使玩家正常向地面投影。</x:v>
+        <x:v>PH50：前向SpotLight仅命中环境layer1并保留环境/怪物投影；玩家、穿戴物与手持枪统一位于layer2且cast_shadow=OFF，不进入随身灯shadow map。layer2只接受无阴影正面补光；已通过真实渲染与自投影专项验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -12046,11 +12046,11 @@
       <x:c r="V156" s="71" t="n">
         <x:v>46233</x:v>
       </x:c>
-      <x:c r="W156" s="70" t="str">
-        <x:v>用户提供 Blender 源文件 / Codex 模块化拆分</x:v>
+      <x:c r="W156" s="71" t="n">
+        <x:v>46235</x:v>
       </x:c>
       <x:c r="X156" s="70" t="str">
-        <x:v>PH43：继续复用v006 1.5m模型与稳定AssetID；Player3D玩法碰撞升级为高1.5m、半径0.34m的VirtualCollisionCapsule。顶层状态扩展为idle/moving/dashing/hurt/locked/falling/landing/dead；下落收腿、耳后扬与落地压缩/回弹均由既有刚性节点程序驱动，不新增GLB或贴图。</x:v>
+        <x:v>PH50：bunny01主体、耳朵、手脚、DIY穿戴物与WeaponSocket下手持武器统一使用render layer2、GI关闭、cast_shadow=OFF；角色仍接收专用无阴影柔光，但不会在玩家随身灯前方产生放大自投影。</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="118" customHeight="1">
@@ -12576,11 +12576,11 @@
       <x:c r="V163" s="71" t="n">
         <x:v>46233</x:v>
       </x:c>
-      <x:c r="W163" s="70" t="n">
+      <x:c r="W163" s="71" t="n">
         <x:v>46235</x:v>
       </x:c>
       <x:c r="X163" s="70" t="str">
-        <x:v>PH50：基地墙体与楼顶/战斗房统一为5m实墙、5m门墙和独立L拐角Mesh组件，删除整条Box拉伸墙路径。98—96层普通房固定30×25m（6×5格），按5m走廊间距重排为紧凑环线；95层保留90×90m Boss区并同步压缩前置房。全层通过无重叠、双向门、实际通行、楼梯钥匙门、随机种子与撤离回归。</x:v>
+        <x:v>PH50：250m整层与65m核心不变；99层30×30m基地、98—96层30×25m/6×5房间和95层Boss区均以5m格线边界生成。门墙组件、RoomDoor3D与走廊端点按两端真实门槽求交；楼梯只在上层楼板开15×30m模块洞，落地层保持完整覆盖。</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="132" customHeight="1">
@@ -13056,7 +13056,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra77edd0bfb8843dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18073fb8f3f14812"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17619,26 +17619,49 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
-      <x:c r="A34" t="str">
+    <x:row r="34" ht="96" customHeight="1">
+      <x:c r="A34" s="63" t="str">
         <x:v>v1.28</x:v>
       </x:c>
-      <x:c r="B34" t="str">
+      <x:c r="B34" s="63" t="str">
         <x:v>2026-08-01</x:v>
       </x:c>
-      <x:c r="C34" t="str">
+      <x:c r="C34" s="63" t="str">
         <x:v>PH50三十乘二十五房间、模块化基地墙与分层投影修复</x:v>
       </x:c>
-      <x:c r="D34" t="str">
+      <x:c r="D34" s="63" t="str">
         <x:v>ENV-TOWER-DESCENT-KIT-3D; ENV-TOWER-WALL-SOLID-5M; ENV-TOWER-WALL-DOOR-5M; PRP-WASTELAND-LIGHT-3D; VFX-PLAYER-FLASHLIGHT-3D; ENV-DUNGEON-RUNTIME-3D</x:v>
       </x:c>
-      <x:c r="E34" t="str">
+      <x:c r="E34" s="63" t="str">
         <x:v>98—96层普通房统一30×25m/6×5格并紧凑重排；基地删除整墙拉伸路径，改用独立5m墙、门墙和L拐角组件；墙段A/B材质交替；房间灯递归流送并让玩家/怪物投影；前向灯只照环境层，不对玩家自投影；普通行动区恢复初始1钥匙与唯一STANDARD信标。</x:v>
       </x:c>
-      <x:c r="F34" t="str">
+      <x:c r="F34" s="63" t="str">
         <x:v>不新增AssetID、GLB或贴图；复用既有5m模块与两套墙材质。塔楼、94门物理通行、3D核心、四主题完整流程、房灯、视野输入、背包武器、换弹、撤离、运行安全和性能预算全部通过，并完成真实渲染复核。</x:v>
       </x:c>
-      <x:c r="G34" t="str">
+      <x:c r="G34" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="108" customHeight="1">
+      <x:c r="A35" s="63" t="str">
+        <x:v>v1.29</x:v>
+      </x:c>
+      <x:c r="B35" s="64" t="n">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C35" s="63" t="str">
+        <x:v>PH50 五米组件坐标与玩家灯光自投影修复</x:v>
+      </x:c>
+      <x:c r="D35" s="63" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D / ENV-TOWER-FLOOR-TILE-5M / ENV-TOWER-WALL-SOLID-5M / ENV-TOWER-STAIRWELL-GENERIC-9M / CHR-PLY-CAPSULE01-BUNNY01 / WPN-GUN-KIT-3D</x:v>
+      </x:c>
+      <x:c r="E35" s="63" t="str">
+        <x:v>基底层改为合法6×6组件边界；98—95层30×25房间按5m格线重排；门墙、交互门与走廊端点由两端真实门槽求交；楼梯只挖上层楼板；玩家/配件/手持武器禁投影，前向灯仍保留环境与怪物阴影。</x:v>
+      </x:c>
+      <x:c r="F35" s="63" t="str">
+        <x:v>AssetID与GLB不变；Godot关卡坐标、楼板覆盖和渲染属性更新；TOWER_GRID_COMPONENT_ALIGNMENT_OK、TOWER_DESCENT_FLOW_OK、94门通行、灯光/性能/视觉回归通过。</x:v>
+      </x:c>
+      <x:c r="G35" s="63" t="str">
         <x:v>Codex</x:v>
       </x:c>
     </x:row>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf84ca10cd5ed4d24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rf5a2a1a12f2c4332"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rb2bd3d1075a745c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R8df505db60d1424e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Reeff2b36bfb14845"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R4f9e39ce2b484273"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R686a524d7a334e8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R602a90e65fc44325"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rcaaab8bdaaa2428d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rc281819524a44e50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rd6466099b9344e9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rca9e7a8f8f724486"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rbe08f792abae40ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rd228f9c63d8147d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R21176932c385478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R5f70b6e6332a46e7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8788,13 +8788,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V113" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46236</x:v>
       </x:c>
       <x:c r="W113" s="70" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X113" s="70" t="str">
-        <x:v>PH49：原先项目外shellstorm2-art/blender中的三份角色Blender源已按稳定命名归档到assets/art/characters/player/chr_player_capsule01_3d/source/，SHA-256与原件一致；运行时场景路径不变，后续不再依赖仓库外资产。</x:v>
+        <x:v>玩家随身三灯通过 layer 1/2 隔离避免自身投影；角色网格恢复外部太阳光/室内灯投影，GI保持关闭；verify_tower_lighting_wall_combat_regressions.tscn</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -12648,13 +12648,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V164" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46236</x:v>
       </x:c>
       <x:c r="W164" s="70" t="str">
         <x:v>程序生成Blender源集合</x:v>
       </x:c>
       <x:c r="X164" s="70" t="str">
-        <x:v>PH44：整层由67×67调整为50×50个5m模块，物理尺寸250×250m、满铺2500块；地板仍由模块化MultiMesh渲染并保留独立StaticBody承重。四向楼梯洞口改用对齐5m世界矩形换算网格，避免尺寸与位移单位错位。</x:v>
+        <x:v>塔楼地砖统一低金属0.08/高粗糙0.90，降低太阳与室内灯高光；A/B双色交替保留；verify_tower_lighting_wall_combat_regressions.tscn</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="132" customHeight="1">
@@ -12722,13 +12722,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V165" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46236</x:v>
       </x:c>
       <x:c r="W165" s="70" t="n">
         <x:v>46235</x:v>
       </x:c>
       <x:c r="X165" s="70" t="str">
-        <x:v>PH50：99层基地和30×25m战斗房的每个5m墙位均实例化为独立MeshInstance3D；相邻墙段按绝对段号交替使用A/B两套材质，门墙和四个L拐角沿用同一交替规则。门洞两侧碰撞按5m网格合并，外层250m楼体仍保留MultiMesh批渲染以满足性能预算。</x:v>
+        <x:v>实墙、门墙、L拐角统一0—9m高度；仅南面朝北墙标记摄像机交互；隐藏连接器不保留阻挡碰撞；verify_tower_lighting_wall_combat_regressions.tscn</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="132" customHeight="1">
@@ -13056,7 +13056,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18073fb8f3f14812"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3993304e8f974db9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17665,6 +17665,29 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="36" ht="72" customHeight="1">
+      <x:c r="A36" t="str">
+        <x:v>v1.30</x:v>
+      </x:c>
+      <x:c r="B36" s="62" t="n">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C36" s="63" t="str">
+        <x:v>PH51 灯光投影、地砖反光、9m南墙与刷怪软锁修复</x:v>
+      </x:c>
+      <x:c r="D36" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D / ENV-TOWER-FLOOR-TILE-5M / ENV-TOWER-WALL-SOLID-5M / Dungeon3D</x:v>
+      </x:c>
+      <x:c r="E36" s="63" t="str">
+        <x:v>角色恢复太阳/室内灯投影但三盏随身灯不自投影；地砖降反光；实墙/门墙/拐角统一9m并仅南墙参与摄像机交互；隐藏连接器碰撞随显隐；敌对房间增加生成兜底与旧状态修复。</x:v>
+      </x:c>
+      <x:c r="F36" s="63" t="str">
+        <x:v>不新增AssetID；仅修正既有组件配置与生成/碰撞逻辑；全量回归PASS</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G2"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rcaaab8bdaaa2428d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rc281819524a44e50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rd6466099b9344e9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rca9e7a8f8f724486"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rbe08f792abae40ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rd228f9c63d8147d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R21176932c385478e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R5f70b6e6332a46e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0a8841f7c7484ec9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R4a9ad332e3514442"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R8a9ca5ec05d94bc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R66a38b32129e4722"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R8ce0f4a8cebf490c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rfa43cc9bf7fb4ec6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R5dab1cd4fc1046eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R2075c7f791c24df8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -157,7 +157,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="23">
+  <x:fills count="24">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -269,6 +269,11 @@
         <x:fgColor rgb="FF24495D"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF246583"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="6">
     <x:border/>
@@ -319,7 +324,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="105">
+  <x:cellXfs count="109">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -554,6 +559,14 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -842,7 +855,7 @@
   <x:sheetData>
     <x:row r="1" ht="25" customHeight="1">
       <x:c r="A1" s="41" t="str">
-        <x:v>SHELLSTORM 2 · 美术资产中枢</x:v>
+        <x:v>SHELLSTORM 2 · 美术资产中枢 v0.1</x:v>
       </x:c>
       <x:c r="B1" s="41"/>
       <x:c r="C1" s="41"/>
@@ -868,7 +881,7 @@
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="42" t="str">
-        <x:v>先查重 → 归类 → 领取 AssetID → 制作组件 → 验收 → 登记哈希；本表是唯一资产台账</x:v>
+        <x:v>查重 → 归类 → 领取 AssetID → 组件制作 → 游戏内验收 → 回填哈希；本表是唯一资产登记源</x:v>
       </x:c>
       <x:c r="B3" s="42"/>
       <x:c r="C3" s="42"/>
@@ -918,28 +931,30 @@
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="45" t="n">
-        <x:v>155</x:v>
+        <x:f>COUNTA('资产主表'!$A$6:$A$205)</x:f>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B6" s="43"/>
       <x:c r="C6" s="45" t="n">
-        <x:v>59</x:v>
+        <x:f>COUNTIF('资产主表'!$K$6:$K$205,"已完成")+COUNTIF('资产主表'!$K$6:$K$205,"原型已接入")</x:f>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
-        <x:f>COUNTIF('资产主表'!$K$6:$K$200,"待制作")+COUNTIF('资产主表'!$K$6:$K$200,"程序占位")</x:f>
+        <x:f>COUNTIF('资产主表'!$K$6:$K$205,"待制作")+COUNTIF('资产主表'!$K$6:$K$205,"程序占位")</x:f>
         <x:v>94</x:v>
       </x:c>
       <x:c r="F6" s="43"/>
       <x:c r="G6" s="45" t="n">
-        <x:f>COUNTIF('资产主表'!$S$6:$S$200,"重复")</x:f>
+        <x:f>COUNTIF('资产主表'!$S$6:$S$205,"重复")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="43"/>
       <x:c r="I6" s="46" t="str">
-        <x:v>PH33 方形猫：头/身/单手/脚四模块；双眼双耳；圆短尾</x:v>
+        <x:v>v0.1 3D塔楼：5m组件网格 / 30×25m战斗房 / 9m层高</x:v>
       </x:c>
       <x:c r="J6" s="46" t="str">
-        <x:v>基地 + 四主题副本 + 独立靶场 + 角色与遭遇预览场</x:v>
+        <x:v>楼顶 → 99层基地 → 98—95层战斗与撤离</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -991,10 +1006,12 @@
         <x:v>角色</x:v>
       </x:c>
       <x:c r="B10" s="50" t="n">
-        <x:v>28</x:v>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$205,A10)</x:f>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C10" s="50" t="n">
-        <x:v>27</x:v>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$205,A10,'资产主表'!$K$6:$K$205,"已完成")+COUNTIFS('资产主表'!$C$6:$C$205,A10,'资产主表'!$K$6:$K$205,"原型已接入")</x:f>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D10" s="43"/>
       <x:c r="E10" s="51" t="str">
@@ -1015,11 +1032,11 @@
         <x:v>敌人</x:v>
       </x:c>
       <x:c r="B11" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A11)</x:f>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$205,A11)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A11,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A11,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$205,A11,'资产主表'!$K$6:$K$205,"已完成")+COUNTIFS('资产主表'!$C$6:$C$205,A11,'资产主表'!$K$6:$K$205,"原型已接入")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D11" s="43"/>
@@ -1041,11 +1058,11 @@
         <x:v>枪械</x:v>
       </x:c>
       <x:c r="B12" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A12)</x:f>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$205,A12)</x:f>
         <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A12,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A12,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$205,A12,'资产主表'!$K$6:$K$205,"已完成")+COUNTIFS('资产主表'!$C$6:$C$205,A12,'资产主表'!$K$6:$K$205,"原型已接入")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D12" s="43"/>
@@ -1067,11 +1084,11 @@
         <x:v>道具</x:v>
       </x:c>
       <x:c r="B13" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A13)</x:f>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$205,A13)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="C13" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A13,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A13,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$205,A13,'资产主表'!$K$6:$K$205,"已完成")+COUNTIFS('资产主表'!$C$6:$C$205,A13,'资产主表'!$K$6:$K$205,"原型已接入")</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="D13" s="43"/>
@@ -1093,12 +1110,12 @@
         <x:v>场景</x:v>
       </x:c>
       <x:c r="B14" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A14)</x:f>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$205,A14)</x:f>
         <x:v>35</x:v>
       </x:c>
       <x:c r="C14" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A14,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A14,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>14</x:v>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$205,A14,'资产主表'!$K$6:$K$205,"已完成")+COUNTIFS('资产主表'!$C$6:$C$205,A14,'资产主表'!$K$6:$K$205,"原型已接入")</x:f>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D14" s="43"/>
       <x:c r="E14" s="51" t="str">
@@ -1119,12 +1136,12 @@
         <x:v>场景道具</x:v>
       </x:c>
       <x:c r="B15" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A15)</x:f>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$205,A15)</x:f>
         <x:v>18</x:v>
       </x:c>
       <x:c r="C15" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A15,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A15,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>5</x:v>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$205,A15,'资产主表'!$K$6:$K$205,"已完成")+COUNTIFS('资产主表'!$C$6:$C$205,A15,'资产主表'!$K$6:$K$205,"原型已接入")</x:f>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D15" s="43"/>
       <x:c r="E15" s="43"/>
@@ -1139,12 +1156,12 @@
         <x:v>UI</x:v>
       </x:c>
       <x:c r="B16" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A16)</x:f>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$205,A16)</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="C16" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A16,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A16,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>4</x:v>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$205,A16,'资产主表'!$K$6:$K$205,"已完成")+COUNTIFS('资产主表'!$C$6:$C$205,A16,'资产主表'!$K$6:$K$205,"原型已接入")</x:f>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D16" s="43"/>
       <x:c r="E16" s="43"/>
@@ -1159,11 +1176,11 @@
         <x:v>特效</x:v>
       </x:c>
       <x:c r="B17" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A17)</x:f>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$205,A17)</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="C17" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A17,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A17,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$205,A17,'资产主表'!$K$6:$K$205,"已完成")+COUNTIFS('资产主表'!$C$6:$C$205,A17,'资产主表'!$K$6:$K$205,"原型已接入")</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="D17" s="43"/>
@@ -1179,11 +1196,11 @@
         <x:v>音频</x:v>
       </x:c>
       <x:c r="B18" s="52" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$200,A18)</x:f>
+        <x:f>COUNTIF('资产主表'!$C$6:$C$205,A18)</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="C18" s="52" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A18,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A18,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
+        <x:f>COUNTIFS('资产主表'!$C$6:$C$205,A18,'资产主表'!$K$6:$K$205,"已完成")+COUNTIFS('资产主表'!$C$6:$C$205,A18,'资产主表'!$K$6:$K$205,"原型已接入")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D18" s="43"/>
@@ -1914,7 +1931,7 @@
         <x:v>assets/art/characters/player/chr_player_capsule01/chr_player_capsule01_states_preview_v001.png</x:v>
       </x:c>
       <x:c r="P12" s="37" t="str">
-        <x:v>verify_player_pixel_art_flow.tscn</x:v>
+        <x:v>tests/verification/verify_player_pixel_art_flow.tscn</x:v>
       </x:c>
       <x:c r="Q12" s="37" t="str">
         <x:v>六态; 验收板</x:v>
@@ -6463,7 +6480,7 @@
         <x:v>跨分辨率</x:v>
       </x:c>
       <x:c r="K79" s="101" t="str">
-        <x:v>已接入</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L79" s="101" t="str">
         <x:v>P0</x:v>
@@ -6498,7 +6515,7 @@
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X79" s="101" t="str">
-        <x:v>PH49：主游戏HUD升级为深色半透明青色全息面板，危险/撤离信息使用琥珀与绿色分层；小地图以20Hz实时更新当前楼层，显示玩家位置与朝向、扫描扇区、脉冲环、透视网格、已发现房间/连线和楼层纵向索引。</x:v>
+        <x:v>v0.1：主游戏HUD升级为深色半透明青色全息面板，危险/撤离信息使用琥珀与绿色分层；小地图以20Hz实时更新当前楼层，显示玩家位置与朝向、扫描扇区、脉冲环、透视网格、已发现房间/连线和楼层纵向索引。</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -8794,7 +8811,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X113" s="70" t="str">
-        <x:v>玩家随身三灯通过 layer 1/2 隔离避免自身投影；角色网格恢复外部太阳光/室内灯投影，GI保持关闭；verify_tower_lighting_wall_combat_regressions.tscn</x:v>
+        <x:v>玩家随身三灯通过 layer 1/2 隔离避免自身投影；角色网格恢复外部太阳光/室内灯投影，GI保持关闭；tests/verification/verify_tower_lighting_wall_combat_regressions.tscn</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -8870,7 +8887,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X114" t="str">
-        <x:v>VisualRoot/Body：BoxMesh身躯、BellyPatch、圆形TailStub；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
+        <x:v>VisualRoot/Body：BoxMesh身躯、BellyPatch、圆形TailStub；v0.1方形猫原型；tests/verification/verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -8946,7 +8963,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X115" t="str">
-        <x:v>VisualRoot/Head：BoxMesh方头；Eyes双矩形眼；Ears双三角耳；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
+        <x:v>VisualRoot/Head：BoxMesh方头；Eyes双矩形眼；Ears双三角耳；v0.1方形猫原型；tests/verification/verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -9022,7 +9039,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X116" t="str">
-        <x:v>VisualRoot/Hand：单个BoxMesh悬浮握持手；全动作与weapon_socket同相；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
+        <x:v>VisualRoot/Hand：单个BoxMesh悬浮握持手；全动作与weapon_socket同相；v0.1方形猫原型；tests/verification/verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -9098,7 +9115,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X117" t="str">
-        <x:v>VisualRoot/Scarf默认隐藏，仅为旧场景兼容；当前四主模块不计入scarf；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
+        <x:v>VisualRoot/Scarf默认隐藏，仅为旧场景兼容；当前四主模块不计入scarf；v0.1方形猫原型；tests/verification/verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -9174,7 +9191,7 @@
         <x:v>原创逻辑挂点</x:v>
       </x:c>
       <x:c r="X118" t="str">
-        <x:v>VisualRoot/WeaponSocket：(0.60,1.15,-0.42)，与唯一手固定相对向量；PH33方形猫原型；verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
+        <x:v>VisualRoot/WeaponSocket：(0.60,1.15,-0.42)，与唯一手固定相对向量；v0.1方形猫原型；tests/verification/verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -9285,7 +9302,7 @@
         <x:v>8类基地设施</x:v>
       </x:c>
       <x:c r="K120" s="70" t="str">
-        <x:v>已接入</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L120" s="70" t="str">
         <x:v>P0</x:v>
@@ -9326,7 +9343,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X120" s="70" t="str">
-        <x:v>PH49：BaseFacility3D复用于五个独立电梯设施（99—95层各一处），设施挂在走廊设施层级而非房间内部，放置在基地房间墙边或楼层走廊边。电梯解锁、目标楼层和到达点从邻接的elevator_access房间读取。</x:v>
+        <x:v>v0.1：BaseFacility3D复用于五个独立电梯设施（99—95层各一处），设施挂在走廊设施层级而非房间内部，放置在基地房间墙边或楼层走廊边。电梯解锁、目标楼层和到达点从邻接的elevator_access房间读取。</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -9452,7 +9469,7 @@
         <x:v>assets/art/environments/base_world_3d/env_base_world_preview_top3d_v001.png</x:v>
       </x:c>
       <x:c r="P122" t="str">
-        <x:v>verify_base_world_3d_visual.tscn</x:v>
+        <x:v>tests/verification/verify_base_world_3d_visual.tscn</x:v>
       </x:c>
       <x:c r="Q122" t="str">
         <x:v>3D预览;评审;入口地图</x:v>
@@ -9511,7 +9528,7 @@
         <x:v>四主题副本/随机房间</x:v>
       </x:c>
       <x:c r="K123" s="70" t="str">
-        <x:v>已接入</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L123" s="70" t="str">
         <x:v>P0</x:v>
@@ -9552,7 +9569,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X123" s="70" t="str">
-        <x:v>PH49：塔楼98—95层形成可闭环的搜打撤流程；普通层每层同时含战斗房和搜刮房，容器按种子掉落。Boss房清理后现在按房间类型正确解锁撤离，不再依赖固定room_id。生成快照增加门连通与全息小地图实时状态，测试覆盖100→99→98实机楼梯路径、95层Boss和撤离完成。</x:v>
+        <x:v>v0.1：塔楼98—95层形成可闭环的搜打撤流程；普通层每层同时含战斗房和搜刮房，容器按种子掉落。Boss房清理后现在按房间类型正确解锁撤离，不再依赖固定room_id。生成快照增加门连通与全息小地图实时状态，测试覆盖100→99→98实机楼梯路径、95层Boss和撤离完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="34" customHeight="1">
@@ -9891,7 +9908,7 @@
         <x:v>关卡/靶场/房间中央照明</x:v>
       </x:c>
       <x:c r="K128" s="70" t="str">
-        <x:v>已接入</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L128" s="70" t="str">
         <x:v>P0</x:v>
@@ -9928,11 +9945,11 @@
       <x:c r="V128" s="71" t="n">
         <x:v>46233</x:v>
       </x:c>
-      <x:c r="W128" s="70" t="n">
-        <x:v>46235</x:v>
+      <x:c r="W128" s="70" t="str">
+        <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X128" s="70" t="str">
-        <x:v>PH50：房间灯统一覆盖环境layer1与角色layer2；普通房中央灯与基地四灯组各只保留一盏投影主灯，其余灯无阴影以控制预算。流送状态改为递归同步嵌套灯具，玩家与怪物均可在开灯房间产生投影。</x:v>
+        <x:v>v0.1：房间灯统一覆盖环境layer1与角色layer2；普通房中央灯与基地四灯组各只保留一盏投影主灯，其余灯无阴影以控制预算。流送状态改为递归同步嵌套灯具，玩家与怪物均可在开灯房间产生投影。</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="34" customHeight="1">
@@ -10658,7 +10675,7 @@
         <x:v>assets/art/environments/dungeon_3d/env_dungeon_runtime_preview_top3d_v001.png</x:v>
       </x:c>
       <x:c r="P138" s="63" t="str">
-        <x:v>verify_full_3d_visual.tscn</x:v>
+        <x:v>tests/verification/verify_full_3d_visual.tscn</x:v>
       </x:c>
       <x:c r="Q138" s="63" t="str">
         <x:v>3D关卡;预览;灯光;战斗;QA</x:v>
@@ -10684,7 +10701,7 @@
         <x:v>项目运行截图</x:v>
       </x:c>
       <x:c r="X138" s="63" t="str">
-        <x:v>实际GPU窗口确认360°遮挡逻辑与96°定向表现；PH28三层玩家灯去除头顶溢光，角色正面柔光、增强中央灯与战斗轮廓通过验收</x:v>
+        <x:v>实际GPU窗口确认360°遮挡逻辑与96°定向表现；v0.1三层玩家灯去除头顶溢光，角色正面柔光、增强中央灯与战斗轮廓通过验收</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="34" customHeight="1">
@@ -10734,7 +10751,7 @@
         <x:v>assets/art/environments/training_range_3d/env_training_range_preview_top3d_v001.png</x:v>
       </x:c>
       <x:c r="P139" s="63" t="str">
-        <x:v>verify_training_range_3d_visual.tscn</x:v>
+        <x:v>tests/verification/verify_training_range_3d_visual.tscn</x:v>
       </x:c>
       <x:c r="Q139" s="63" t="str">
         <x:v>3D靶场;预览;射击道;目标;QA</x:v>
@@ -11021,7 +11038,7 @@
         <x:v>随机关卡房间/四主题复用</x:v>
       </x:c>
       <x:c r="K143" s="70" t="str">
-        <x:v>已接入</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L143" s="70" t="str">
         <x:v>P0</x:v>
@@ -11062,7 +11079,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X143" s="70" t="str">
-        <x:v>PH49：开关新增灯组控制，同一开关可统一切换多盏房间灯；基地四灯共用一个墙边开关并在快照中报告控制灯数量。单灯房继续兼容原接口。</x:v>
+        <x:v>v0.1：开关新增灯组控制，同一开关可统一切换多盏房间灯；基地四灯共用一个墙边开关并在快照中报告控制灯数量。单灯房继续兼容原接口。</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -11134,11 +11151,11 @@
       <x:c r="V144" s="62" t="n">
         <x:v>46225</x:v>
       </x:c>
-      <x:c r="W144" s="62" t="n">
-        <x:v>46235</x:v>
+      <x:c r="W144" s="62" t="str">
+        <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X144" t="str">
-        <x:v>PH50：前向SpotLight仅命中环境layer1并保留环境/怪物投影；玩家、穿戴物与手持枪统一位于layer2且cast_shadow=OFF，不进入随身灯shadow map。layer2只接受无阴影正面补光；已通过真实渲染与自投影专项验收。</x:v>
+        <x:v>v0.1：前向SpotLight仅命中环境layer1并保留环境/怪物投影；玩家、穿戴物与手持枪统一位于layer2且cast_shadow=OFF，不进入随身灯shadow map。layer2只接受无阴影正面补光；已通过真实渲染与自投影专项验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -11290,7 +11307,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X146" s="63" t="str">
-        <x:v>胶囊防护体3D身体DIY变体；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+        <x:v>胶囊防护体3D身体DIY变体；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；tests/verification/verify_player3d_diy_flow PASS ｜ v0.1：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="44" customHeight="1">
@@ -11366,7 +11383,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X147" s="63" t="str">
-        <x:v>胶囊防护体3D头部DIY变体；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+        <x:v>胶囊防护体3D头部DIY变体；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；tests/verification/verify_player3d_diy_flow PASS ｜ v0.1：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="44" customHeight="1">
@@ -11442,7 +11459,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X148" s="63" t="str">
-        <x:v>胶囊防护体3D手部DIY变体；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+        <x:v>胶囊防护体3D手部DIY变体；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；tests/verification/verify_player3d_diy_flow PASS ｜ v0.1：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="44" customHeight="1">
@@ -11518,7 +11535,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X149" s="63" t="str">
-        <x:v>胶囊防护体3D帽子DIY组件；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH32灯光修正：角色专用层2；禁用投影/GI，仅接收AvatarFrontFill，不遮挡头壳传感器或探照灯 ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+        <x:v>胶囊防护体3D帽子DIY组件；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；tests/verification/verify_player3d_diy_flow PASS ｜ v0.1灯光修正：角色专用层2；禁用投影/GI，仅接收AvatarFrontFill，不遮挡头壳传感器或探照灯 ｜ v0.1：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="44" customHeight="1">
@@ -11594,7 +11611,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X150" s="63" t="str">
-        <x:v>胶囊防护体3D眼镜DIY组件；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；verify_player3d_diy_flow PASS ｜ PH32灯光修正：角色专用层2；禁用投影/GI，仅接收AvatarFrontFill，不遮挡头壳传感器或探照灯 ｜ PH33：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+        <x:v>胶囊防护体3D眼镜DIY组件；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；tests/verification/verify_player3d_diy_flow PASS ｜ v0.1灯光修正：角色专用层2；禁用投影/GI，仅接收AvatarFrontFill，不遮挡头壳传感器或探照灯 ｜ v0.1：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="44" customHeight="1">
@@ -12046,11 +12063,11 @@
       <x:c r="V156" s="71" t="n">
         <x:v>46233</x:v>
       </x:c>
-      <x:c r="W156" s="71" t="n">
-        <x:v>46235</x:v>
+      <x:c r="W156" s="71" t="str">
+        <x:v>原创 Blender/Godot 组合</x:v>
       </x:c>
       <x:c r="X156" s="70" t="str">
-        <x:v>PH50：bunny01主体、耳朵、手脚、DIY穿戴物与WeaponSocket下手持武器统一使用render layer2、GI关闭、cast_shadow=OFF；角色仍接收专用无阴影柔光，但不会在玩家随身灯前方产生放大自投影。</x:v>
+        <x:v>v0.1：玩家网格位于 layer2，允许太阳与室内灯产生外部投影；玩家随身三盏灯不对角色自身投影；GI关闭。</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="118" customHeight="1">
@@ -12126,7 +12143,7 @@
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
       <x:c r="X157" s="70" t="str">
-        <x:v>PH41 v006：身体网格与底部中心原点从v005等比放大1.5倍；Godot BodyJoint=(-0.000030,0.155022,-0.000635)。</x:v>
+        <x:v>v0.1 v006：身体网格与底部中心原点从v005等比放大1.5倍；Godot BodyJoint=(-0.000030,0.155022,-0.000635)。</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="118" customHeight="1">
@@ -12202,7 +12219,7 @@
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
       <x:c r="X158" s="70" t="str">
-        <x:v>PH41 v006：头部与下沿中心原点真实1.5倍；不含耳头顶1.103390m，完整双耳顶部1.500m。</x:v>
+        <x:v>v0.1 v006：头部与下沿中心原点真实1.5倍；不含耳头顶1.103390m，完整双耳顶部1.500m。</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="118" customHeight="1">
@@ -12278,7 +12295,7 @@
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
       <x:c r="X159" s="70" t="str">
-        <x:v>PH41 v006：耳朵网格与耳根原点真实1.5倍；左右挂点复用单资产，装配后最高点严格1.500m。</x:v>
+        <x:v>v0.1 v006：耳朵网格与耳根原点真实1.5倍；左右挂点复用单资产，装配后最高点严格1.500m。</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="118" customHeight="1">
@@ -12354,7 +12371,7 @@
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
       <x:c r="X160" s="70" t="str">
-        <x:v>PH41 v006：左右手、手腕原点、单/双手握持目标和动作平移统一改用0.606060606米制比例；持枪外观与确认预览一致。</x:v>
+        <x:v>v0.1 v006：左右手、手腕原点、单/双手握持目标和动作平移统一改用0.606060606米制比例；持枪外观与确认预览一致。</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="132" customHeight="1">
@@ -12430,7 +12447,7 @@
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
       <x:c r="X161" s="70" t="str">
-        <x:v>PH43：v006网格与AssetID不变；FootJointL除moving步态外新增falling收腿与landing压缩恢复职责，动作由PlayerAvatar3D程序变换驱动。</x:v>
+        <x:v>v0.1：v006网格与AssetID不变；FootJointL除moving步态外新增falling收腿与landing压缩恢复职责，动作由PlayerAvatar3D程序变换驱动。</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="132" customHeight="1">
@@ -12506,7 +12523,7 @@
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
       <x:c r="X162" s="70" t="str">
-        <x:v>PH43：v006网格与AssetID不变；FootJointR除moving步态外新增falling收腿与landing压缩恢复职责，动作由PlayerAvatar3D程序变换驱动。</x:v>
+        <x:v>v0.1：v006网格与AssetID不变；FootJointR除moving步态外新增falling收腿与landing压缩恢复职责，动作由PlayerAvatar3D程序变换驱动。</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="155" customHeight="1">
@@ -12541,7 +12558,7 @@
         <x:v>250×250m整层；99层30×30m/6×6格基地；98—95层终局路线；2.2×2.5m门</x:v>
       </x:c>
       <x:c r="K163" s="70" t="str">
-        <x:v>已接入</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L163" s="70" t="str">
         <x:v>P0</x:v>
@@ -12556,7 +12573,7 @@
         <x:v>assets/art/environments/tower_descent_3d/source/env_tower_descent_kit_top3d_v007.blend</x:v>
       </x:c>
       <x:c r="P163" s="70" t="str">
-        <x:v>assets/art/environments/tower_descent_3d/source/sync_env_tower_descent_kit_top3d_v007.py; assets/art/environments/tower_descent_3d/source/validate_env_tower_descent_kit_top3d_v007.py; outputs/019fb2a5-6bc8-7d10-a214-90288a5f7e80/previews/env_tower_descent_v007_base99.png; outputs/019fb2a5-6bc8-7d10-a214-90288a5f7e80/previews/env_tower_descent_v007_floors98_95.png</x:v>
+        <x:v>assets/art/environments/tower_descent_3d/source/validate_env_tower_descent_kit_top3d_v007.py; assets/art/environments/tower_descent_3d/source/render_env_tower_descent_kit_top3d_v007.py; docs/v0.1/03_关卡与场景设计.md</x:v>
       </x:c>
       <x:c r="Q163" s="70" t="str">
         <x:v>塔楼;向下爬楼;楼顶;基地层;战斗层;特殊楼梯;通用楼梯;五米网格;模块化地砖;模块化墙;模块化门;Blender</x:v>
@@ -12576,11 +12593,11 @@
       <x:c r="V163" s="71" t="n">
         <x:v>46233</x:v>
       </x:c>
-      <x:c r="W163" s="71" t="n">
-        <x:v>46235</x:v>
+      <x:c r="W163" s="71" t="str">
+        <x:v>程序生成 Blender 源集合</x:v>
       </x:c>
       <x:c r="X163" s="70" t="str">
-        <x:v>PH50：250m整层与65m核心不变；99层30×30m基地、98—96层30×25m/6×5房间和95层Boss区均以5m格线边界生成。门墙组件、RoomDoor3D与走廊端点按两端真实门槽求交；楼梯只在上层楼板开15×30m模块洞，落地层保持完整覆盖。</x:v>
+        <x:v>v0.1：250m整层与65m核心使用5m组件；99层30×30m基地，98—96层30×25m房间，95层Boss区；门、地砖、墙和楼梯按组件坐标装配。</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="132" customHeight="1">
@@ -12630,7 +12647,7 @@
         <x:v>assets/art/environments/tower_descent_3d/components/env_tower_floor_tile_5m_top3d_v001.glb</x:v>
       </x:c>
       <x:c r="P164" s="70" t="str">
-        <x:v>Blender集合=10A_MOD_FLOOR_TILE_5M_U01; export_env_tower_5m_modules_v001.py; TowerFloorStage3D.gd; verify_tower_descent_flow.tscn</x:v>
+        <x:v>Blender集合=10A_MOD_FLOOR_TILE_5M_U01; export_env_tower_5m_modules_v001.py; TowerFloorStage3D.gd; tests/verification/verify_tower_descent_flow.tscn</x:v>
       </x:c>
       <x:c r="Q164" s="70" t="str">
         <x:v>塔楼;地砖;楼板;5米;模块化;平铺;四向接口</x:v>
@@ -12654,7 +12671,7 @@
         <x:v>程序生成Blender源集合</x:v>
       </x:c>
       <x:c r="X164" s="70" t="str">
-        <x:v>塔楼地砖统一低金属0.08/高粗糙0.90，降低太阳与室内灯高光；A/B双色交替保留；verify_tower_lighting_wall_combat_regressions.tscn</x:v>
+        <x:v>塔楼地砖统一低金属0.08/高粗糙0.90，降低太阳与室内灯高光；A/B双色交替保留；tests/verification/verify_tower_lighting_wall_combat_regressions.tscn</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="132" customHeight="1">
@@ -12704,7 +12721,7 @@
         <x:v>assets/art/environments/tower_descent_3d/components/env_tower_wall_solid_5m_top3d_v001.glb</x:v>
       </x:c>
       <x:c r="P165" s="70" t="str">
-        <x:v>Blender集合=10B_MOD_WALL_SOLID_5M_U01; export_env_tower_5m_modules_v001.py; DungeonRoom3D.gd; TowerFloorStage3D.gd; mat_tower_wall_solid_a_v001.tres; mat_tower_wall_solid_b_v001.tres; verify_tower_descent_flow.tscn</x:v>
+        <x:v>Blender集合=10B_MOD_WALL_SOLID_5M_U01; export_env_tower_5m_modules_v001.py; DungeonRoom3D.gd; TowerFloorStage3D.gd; mat_tower_wall_solid_a_v001.tres; mat_tower_wall_solid_b_v001.tres; tests/verification/verify_tower_descent_flow.tscn</x:v>
       </x:c>
       <x:c r="Q165" s="70" t="str">
         <x:v>塔楼;实墙;满高墙;5米;模块化;室内隔墙;核心外墙</x:v>
@@ -12724,11 +12741,11 @@
       <x:c r="V165" s="71" t="n">
         <x:v>46236</x:v>
       </x:c>
-      <x:c r="W165" s="70" t="n">
-        <x:v>46235</x:v>
+      <x:c r="W165" s="70" t="str">
+        <x:v>程序生成 Blender 源集合</x:v>
       </x:c>
       <x:c r="X165" s="70" t="str">
-        <x:v>实墙、门墙、L拐角统一0—9m高度；仅南面朝北墙标记摄像机交互；隐藏连接器不保留阻挡碰撞；verify_tower_lighting_wall_combat_regressions.tscn</x:v>
+        <x:v>v0.1：实墙、门墙与拐角统一0—9m；仅南侧朝北墙参与镜头交互；隐藏连接器不保留阻挡碰撞；A/B材质按网格交替。</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="132" customHeight="1">
@@ -12778,7 +12795,7 @@
         <x:v>assets/art/environments/tower_descent_3d/components/env_tower_wall_parapet_5m_top3d_v001.glb</x:v>
       </x:c>
       <x:c r="P166" s="70" t="str">
-        <x:v>Blender集合=10C_MOD_WALL_PARAPET_5M_U01; export_env_tower_5m_modules_v001.py; TowerFloorStage3D.gd; verify_tower_descent_visual.tscn</x:v>
+        <x:v>Blender集合=10C_MOD_WALL_PARAPET_5M_U01; export_env_tower_5m_modules_v001.py; TowerFloorStage3D.gd; tests/verification/verify_tower_descent_visual.tscn</x:v>
       </x:c>
       <x:c r="Q166" s="70" t="str">
         <x:v>塔楼;女儿墙;护栏;5米;模块化;楼顶边界</x:v>
@@ -12802,7 +12819,7 @@
         <x:v>程序生成Blender源集合</x:v>
       </x:c>
       <x:c r="X166" s="70" t="str">
-        <x:v>PH44：继续复用同一5m围栏模块，按50×50网格环绕250×250m楼顶与整层边界，不新增大块整体网格；普通楼顶由统一太阳照明，楼梯口局部阴影不再靠提高全局环境亮度解决。</x:v>
+        <x:v>v0.1：继续复用同一5m围栏模块，按50×50网格环绕250×250m楼顶与整层边界，不新增大块整体网格；普通楼顶由统一太阳照明，楼梯口局部阴影不再靠提高全局环境亮度解决。</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="155" customHeight="1">
@@ -12837,7 +12854,7 @@
         <x:v>5m墙位/2.2m净宽/2.5m净高/独立门扇</x:v>
       </x:c>
       <x:c r="K167" s="70" t="str">
-        <x:v>已接入</x:v>
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="L167" s="70" t="str">
         <x:v>P0</x:v>
@@ -12872,11 +12889,11 @@
       <x:c r="V167" s="71" t="n">
         <x:v>46233</x:v>
       </x:c>
-      <x:c r="W167" s="70" t="n">
-        <x:v>46235</x:v>
+      <x:c r="W167" s="70" t="str">
+        <x:v>程序生成 Blender 源集合</x:v>
       </x:c>
       <x:c r="X167" s="70" t="str">
-        <x:v>PH50：基地、楼顶和战斗房复用同一5m门墙模块与2.2×2.5m净开口；门位由墙段索引生成，触发体、门扇表现和碰撞共用同一目标边。94扇门完成配置、关闭阻挡、开启放行、文案、物理通行与楼顶→基地首次交互验收。</x:v>
+        <x:v>v0.1：基地、楼顶和战斗房复用同一5m门墙与2.2×2.5m净空；门扇、触发体、碰撞和目标边共用同一组件坐标。</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="132" customHeight="1">
@@ -12926,7 +12943,7 @@
         <x:v>assets/art/environments/tower_descent_3d/components/env_tower_stairwell_generic_9m_top3d_v001.glb</x:v>
       </x:c>
       <x:c r="P168" s="70" t="str">
-        <x:v>Blender根=Stair_Generic_Rotatable_ROOT; env_tower_descent_kit_top3d_v006.blend; export_env_tower_stairwells_v001.py; TowerDescent3D.gd; verify_tower_descent_flow.tscn</x:v>
+        <x:v>Blender根=Stair_Generic_Rotatable_ROOT; env_tower_descent_kit_top3d_v007.blend; export_env_tower_stairwells_v001.py; TowerDescent3D.gd; tests/verification/verify_tower_descent_flow.tscn</x:v>
       </x:c>
       <x:c r="Q168" s="70" t="str">
         <x:v>塔楼;通用楼梯;双跑楼梯;折角平台;9米层高;四向旋转;Blender直出</x:v>
@@ -12952,7 +12969,7 @@
         <x:v>用户手工Blender模型</x:v>
       </x:c>
       <x:c r="X168" s="70" t="str">
-        <x:v>PH44：继续直接复用用户v006通用9m楼梯视觉与六块Walkable同形常驻碰撞；按5m世界矩形对齐250m整层中的四向楼梯洞口，可旋转通用。上下端门侧分别记录，避免楼梯开口朝向改变后沿用同一侧导致错位。</x:v>
+        <x:v>v0.1：继续直接复用用户v006通用9m楼梯视觉与六块Walkable同形常驻碰撞；按5m世界矩形对齐250m整层中的四向楼梯洞口，可旋转通用。上下端门侧分别记录，避免楼梯开口朝向改变后沿用同一侧导致错位。</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="132" customHeight="1">
@@ -13002,7 +13019,7 @@
         <x:v>assets/art/environments/tower_descent_3d/components/env_tower_stairwell_rooftop_9m_top3d_v001.glb</x:v>
       </x:c>
       <x:c r="P169" s="70" t="str">
-        <x:v>Blender根=Stair_Special_Rooftop_ROOT; env_tower_descent_kit_top3d_v006.blend; export_env_tower_stairwells_v001.py; TowerDescent3D.gd; verify_tower_descent_flow.tscn</x:v>
+        <x:v>Blender根=Stair_Special_Rooftop_ROOT; env_tower_descent_kit_top3d_v007.blend; export_env_tower_stairwells_v001.py; TowerDescent3D.gd; tests/verification/verify_tower_descent_flow.tscn</x:v>
       </x:c>
       <x:c r="Q169" s="70" t="str">
         <x:v>塔楼;楼顶楼梯;特殊楼梯;双跑楼梯;特殊墙高;9米层高;Blender直出</x:v>
@@ -13028,7 +13045,7 @@
         <x:v>用户手工Blender模型</x:v>
       </x:c>
       <x:c r="X169" s="70" t="str">
-        <x:v>PH44：继续复用用户v006楼顶特殊楼梯、加高墙体及常驻Walkable/EnclosureWall碰撞。楼顶纯黑问题确认为固定斜俯视镜头被门墙整段遮挡；现仅剖切遮挡角色的墙体渲染，并联动同方向5m墙段，物理碰撞、门和楼梯围护保持有效；天空反弹光降至1.25，仅补兼容渲染器缺少实时天空GI。</x:v>
+        <x:v>v0.1：继续复用用户v006楼顶特殊楼梯、加高墙体及常驻Walkable/EnclosureWall碰撞。楼顶纯黑问题确认为固定斜俯视镜头被门墙整段遮挡；现仅剖切遮挡角色的墙体渲染，并联动同方向5m墙段，物理碰撞、门和楼梯围护保持有效；天空反弹光降至1.25，仅补兼容渲染器缺少实时天空GI。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13056,7 +13073,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3993304e8f974db9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4a77b1d5b2e42fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14151,7 +14168,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="M29" s="63" t="str">
-        <x:v>可选；layer2，禁投影/GI；不得替代双眼节点</x:v>
+        <x:v>可选；layer2；允许太阳/室内灯外部投影；玩家三灯不产生自身投影；GI禁用。</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="38" customHeight="1">
@@ -14192,7 +14209,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="M30" s="63" t="str">
-        <x:v>默认visible=false；不计入四主模块</x:v>
+        <x:v>可选；layer2；允许太阳/室内灯外部投影；玩家三灯不产生自身投影；GI禁用。</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="104" customHeight="1">
@@ -14233,7 +14250,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M31" s="70" t="str">
-        <x:v>PH43：v006真实1.5m分体网格与AssetID不变；玩法碰撞位于Player3D/VirtualCollisionCapsule（height=1.5m、radius=0.34m）。falling/landing复用既有Body/Head/Hands/Feet/EarSocket关节。</x:v>
+        <x:v>v0.1：v006真实1.5m分体网格与AssetID不变；玩法碰撞位于Player3D/VirtualCollisionCapsule（height=1.5m、radius=0.34m）。falling/landing复用既有Body/Head/Hands/Feet/EarSocket关节。</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="104" customHeight="1">
@@ -14520,7 +14537,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M38" s="70" t="str">
-        <x:v>Blender原点：脚底中心；静态最低点Y=0；PH43复用同一v006网格增加下落与落地程序动作。</x:v>
+        <x:v>Blender原点：脚底中心；静态最低点Y=0；v0.1复用同一v006网格增加下落与落地程序动作。</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="104" customHeight="1">
@@ -14561,7 +14578,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M39" s="70" t="str">
-        <x:v>Blender原点：脚底中心；静态最低点Y=0；PH43复用同一v006网格增加下落与落地程序动作。</x:v>
+        <x:v>Blender原点：脚底中心；静态最低点Y=0；v0.1复用同一v006网格增加下落与落地程序动作。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -15806,7 +15823,7 @@
     </x:row>
     <x:row r="40" ht="38" customHeight="1">
       <x:c r="A40" s="70" t="str">
-        <x:v>PH33 方形猫子组件 × 动作归属（不新增状态）</x:v>
+        <x:v>v0.1 兔子组件与动作归属（不新增状态）</x:v>
       </x:c>
       <x:c r="B40" s="70"/>
       <x:c r="C40" s="70"/>
@@ -16448,10 +16465,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="36" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="54" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="58" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
@@ -16459,7 +16476,7 @@
   <x:sheetData>
     <x:row r="1" ht="25" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>首个角色原型 · 胶囊防护体</x:v>
+        <x:v>当前角色原型 · 兔子组件角色</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -16493,7 +16510,7 @@
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>侧面朝右，可水平翻转；无腿、无人脸、无手臂；单手随身体朝向在 x=±19 镜像，枪械挂点在 x=±24 同步换边且枪械独立瞄准；红围巾为独立身份组件</x:v>
+        <x:v>1.5m 俯视3D角色；逻辑根、虚拟碰撞胶囊、视觉组件和 WeaponSocket 相互独立</x:v>
       </x:c>
       <x:c r="B3" s="6"/>
       <x:c r="C3" s="6"/>
@@ -16529,145 +16546,197 @@
         <x:v>哈希前12位</x:v>
       </x:c>
       <x:c r="G5" s="29" t="str">
-        <x:v>动画方式</x:v>
+        <x:v>动作方式</x:v>
       </x:c>
       <x:c r="H5" s="30" t="str">
         <x:v>验收</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="36" t="str">
-        <x:v>head</x:v>
+        <x:v>root</x:v>
       </x:c>
       <x:c r="B6" s="36" t="str">
-        <x:v>CHR-PLY-CAPSULE01-HEAD-SIDE</x:v>
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
       </x:c>
       <x:c r="C6" s="36" t="str">
-        <x:v>28×24</x:v>
+        <x:v>1.034×1.500×0.645m</x:v>
       </x:c>
       <x:c r="D6" s="36" t="str">
-        <x:v>头壳/单传感器</x:v>
+        <x:v>视觉组件根</x:v>
       </x:c>
       <x:c r="E6" s="36" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01/components/chr_player_capsule01_head_side_v001.png</x:v>
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v006.tscn</x:v>
       </x:c>
       <x:c r="F6" s="36" t="str">
-        <x:v>6035db0c8d18</x:v>
+        <x:v>b88839fbe76e</x:v>
       </x:c>
       <x:c r="G6" s="36" t="str">
-        <x:v>flip_h + 滞后</x:v>
+        <x:v>八态 + 动作覆盖层</x:v>
       </x:c>
       <x:c r="H6" s="36" t="str">
         <x:v>通过</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="42" customHeight="1">
       <x:c r="A7" s="37" t="str">
         <x:v>body</x:v>
       </x:c>
       <x:c r="B7" s="37" t="str">
-        <x:v>CHR-PLY-CAPSULE01-BODY-SIDE</x:v>
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-BODY</x:v>
       </x:c>
       <x:c r="C7" s="37" t="str">
-        <x:v>32×35</x:v>
+        <x:v>1.5m角色比例</x:v>
       </x:c>
       <x:c r="D7" s="37" t="str">
-        <x:v>胶囊防护服躯干</x:v>
+        <x:v>身体组件</x:v>
       </x:c>
       <x:c r="E7" s="37" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01/components/chr_player_capsule01_body_side_v001.png</x:v>
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v006.glb</x:v>
       </x:c>
       <x:c r="F7" s="37" t="str">
-        <x:v>653190cbcd99</x:v>
+        <x:v>c574d76e0f19</x:v>
       </x:c>
       <x:c r="G7" s="37" t="str">
-        <x:v>呼吸/压缩/倾倒</x:v>
+        <x:v>呼吸/移动/受击</x:v>
       </x:c>
       <x:c r="H7" s="37" t="str">
         <x:v>通过</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="37" t="str">
-        <x:v>hand_l_source</x:v>
+        <x:v>head</x:v>
       </x:c>
       <x:c r="B8" s="37" t="str">
-        <x:v>CHR-PLY-CAPSULE01-HAND-L-SIDE</x:v>
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-HEAD</x:v>
       </x:c>
       <x:c r="C8" s="37" t="str">
-        <x:v>22×21</x:v>
+        <x:v>头顶1.103390m</x:v>
       </x:c>
       <x:c r="D8" s="37" t="str">
-        <x:v>停用的副手源</x:v>
+        <x:v>头部组件</x:v>
       </x:c>
       <x:c r="E8" s="37" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01/components/chr_player_capsule01_hand_l_side_v001.png</x:v>
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v006.glb</x:v>
       </x:c>
       <x:c r="F8" s="37" t="str">
-        <x:v>6270855f57a2</x:v>
+        <x:v>b8db86c722bb</x:v>
       </x:c>
       <x:c r="G8" s="37" t="str">
-        <x:v>不进运行时</x:v>
+        <x:v>延迟跟随/受击</x:v>
       </x:c>
       <x:c r="H8" s="37" t="str">
-        <x:v>停用</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+        <x:v>通过</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="37" t="str">
-        <x:v>hand</x:v>
+        <x:v>ears</x:v>
       </x:c>
       <x:c r="B9" s="37" t="str">
-        <x:v>CHR-PLY-CAPSULE01-HAND-R-SIDE</x:v>
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-EARS</x:v>
       </x:c>
       <x:c r="C9" s="37" t="str">
-        <x:v>22×17</x:v>
+        <x:v>单GLB双实例</x:v>
       </x:c>
       <x:c r="D9" s="37" t="str">
-        <x:v>唯一镜像握持手</x:v>
+        <x:v>双耳配件</x:v>
       </x:c>
       <x:c r="E9" s="37" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01/components/chr_player_capsule01_hand_r_side_v001.png</x:v>
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v006.glb</x:v>
       </x:c>
       <x:c r="F9" s="37" t="str">
-        <x:v>69c2529cbd27</x:v>
+        <x:v>ed3c7abe2831</x:v>
       </x:c>
       <x:c r="G9" s="37" t="str">
-        <x:v>随身体左右镜像；不随准星连续旋转</x:v>
+        <x:v>跟随/摆动</x:v>
       </x:c>
       <x:c r="H9" s="37" t="str">
         <x:v>通过</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="37" t="str">
-        <x:v>scarf</x:v>
+        <x:v>hands</x:v>
       </x:c>
       <x:c r="B10" s="37" t="str">
-        <x:v>CHR-PLY-CAPSULE01-SCARF-SIDE</x:v>
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-HAND</x:v>
       </x:c>
       <x:c r="C10" s="37" t="str">
-        <x:v>26×14</x:v>
+        <x:v>左右独立GLB</x:v>
       </x:c>
       <x:c r="D10" s="37" t="str">
-        <x:v>红色身份配件</x:v>
+        <x:v>握持与支撑手</x:v>
       </x:c>
       <x:c r="E10" s="37" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01/components/chr_player_capsule01_scarf_side_v001.png</x:v>
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v006.glb; ...hand_r...v006.glb</x:v>
       </x:c>
       <x:c r="F10" s="37" t="str">
-        <x:v>d3a7b1bb5e2a</x:v>
+        <x:v>2c6647c0e4f2</x:v>
       </x:c>
       <x:c r="G10" s="37" t="str">
-        <x:v>轻摆/翻转</x:v>
+        <x:v>单手/双手握持</x:v>
       </x:c>
       <x:c r="H10" s="37" t="str">
         <x:v>通过</x:v>
       </x:c>
     </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" t="str">
+        <x:v>foot_l</x:v>
+      </x:c>
+      <x:c r="B11" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-FOOT-L</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>1.5m角色比例</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>左脚组件</x:v>
+      </x:c>
+      <x:c r="E11" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>52051cba0db7</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>步态/下落/落地</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" t="str">
+        <x:v>foot_r</x:v>
+      </x:c>
+      <x:c r="B12" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-FOOT-R</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>1.5m角色比例</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>右脚组件</x:v>
+      </x:c>
+      <x:c r="E12" s="63" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>d81e840f5c08</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>步态/下落/落地</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+    </x:row>
     <x:row r="13">
       <x:c r="A13" s="57" t="str">
-        <x:v>六态游戏内验收预览（Idle / Moving / Dashing / Hurt / Locked / Dead）</x:v>
+        <x:v>八态游戏内验收（Idle / Moving / Dashing / Hurt / Locked / Falling / Landing / Dead）</x:v>
       </x:c>
       <x:c r="B13" s="57"/>
       <x:c r="C13" s="57"/>
@@ -16694,6 +16763,12 @@
         <x:v>LOCKED</x:v>
       </x:c>
       <x:c r="F15" s="30" t="str">
+        <x:v>FALLING</x:v>
+      </x:c>
+      <x:c r="G15" s="108" t="str">
+        <x:v>LANDING</x:v>
+      </x:c>
+      <x:c r="H15" s="108" t="str">
         <x:v>DEAD</x:v>
       </x:c>
     </x:row>
@@ -16702,7 +16777,7 @@
         <x:v>待命</x:v>
       </x:c>
       <x:c r="B16" s="36" t="str">
-        <x:v>机动</x:v>
+        <x:v>移动</x:v>
       </x:c>
       <x:c r="C16" s="36" t="str">
         <x:v>突进</x:v>
@@ -16714,72 +16789,96 @@
         <x:v>交互锁定</x:v>
       </x:c>
       <x:c r="F16" s="36" t="str">
+        <x:v>下落</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>落地</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
         <x:v>生命终止</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="37" t="str">
-        <x:v>低频呼吸</x:v>
+        <x:v>呼吸/重心</x:v>
       </x:c>
       <x:c r="B17" s="37" t="str">
-        <x:v>上下弹性</x:v>
+        <x:v>双脚交替</x:v>
       </x:c>
       <x:c r="C17" s="37" t="str">
-        <x:v>横向压缩</x:v>
+        <x:v>翻滚收束</x:v>
       </x:c>
       <x:c r="D17" s="37" t="str">
-        <x:v>冲击压缩</x:v>
+        <x:v>反向冲击</x:v>
       </x:c>
       <x:c r="E17" s="37" t="str">
-        <x:v>降亮稳定</x:v>
+        <x:v>姿态稳定</x:v>
       </x:c>
       <x:c r="F17" s="37" t="str">
-        <x:v>倾倒熄灭</x:v>
+        <x:v>收腿下落</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>压缩回弹</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>整体倒伏</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="37" t="str">
-        <x:v>随向镜像</x:v>
+        <x:v>可进移动/突进</x:v>
       </x:c>
       <x:c r="B18" s="37" t="str">
-        <x:v>随向镜像</x:v>
+        <x:v>可进待命/突进</x:v>
       </x:c>
       <x:c r="C18" s="37" t="str">
-        <x:v>随向镜像</x:v>
+        <x:v>回到待命或移动</x:v>
       </x:c>
       <x:c r="D18" s="37" t="str">
-        <x:v>随向镜像</x:v>
+        <x:v>恢复原状态</x:v>
       </x:c>
       <x:c r="E18" s="37" t="str">
-        <x:v>随向镜像</x:v>
+        <x:v>由交互释放</x:v>
       </x:c>
       <x:c r="F18" s="37" t="str">
-        <x:v>随整体倾倒</x:v>
+        <x:v>只进落地或死亡</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>回到可控态</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>终态</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="37" t="str">
-        <x:v>无</x:v>
+        <x:v>允许射击覆盖</x:v>
       </x:c>
       <x:c r="B19" s="37" t="str">
-        <x:v>地面划痕</x:v>
+        <x:v>允许射击覆盖</x:v>
       </x:c>
       <x:c r="C19" s="37" t="str">
-        <x:v>青色尾迹</x:v>
+        <x:v>无敌窗</x:v>
       </x:c>
       <x:c r="D19" s="37" t="str">
-        <x:v>红闪</x:v>
+        <x:v>受击反馈</x:v>
       </x:c>
       <x:c r="E19" s="37" t="str">
-        <x:v>琥珀环</x:v>
+        <x:v>输入锁定</x:v>
       </x:c>
       <x:c r="F19" s="37" t="str">
-        <x:v>终态守卫</x:v>
+        <x:v>关闭地面步态</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>短时落地冲击</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>停止动作</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="58" t="str">
-        <x:v>预览图：assets/art/characters/player/chr_player_capsule01/chr_player_capsule01_states_preview_v001.png</x:v>
+        <x:v>视觉输出：outputs/verification/player3d_state_gallery.png</x:v>
       </x:c>
       <x:c r="B21" s="58"/>
       <x:c r="C21" s="58"/>
@@ -16791,7 +16890,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="61" t="str">
-        <x:v>验证命令：godot --path . verify_player_pixel_art_flow.tscn ｜ 结果：单手随身体镜像 / 枪械独立连续瞄准 PASS</x:v>
+        <x:v>验证命令：./scripts/run_verification_suite.sh scene verify_player3d_state_gallery_flow</x:v>
       </x:c>
       <x:c r="B23" s="61"/>
       <x:c r="C23" s="61"/>
@@ -16803,7 +16902,7 @@
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="73" t="str">
-        <x:v>换弹覆盖层：唯一手 + weapon_socket 同相三阶段动作；头顶 billboard 读取真实 0→1 进度；verify_3d_reload_state_flow.tscn PASS</x:v>
+        <x:v>换弹覆盖层：唯一手 + WeaponSocket 同相动作；测试 tests/verification/verify_3d_reload_state_flow.tscn</x:v>
       </x:c>
       <x:c r="B24" s="73"/>
       <x:c r="C24" s="73"/>
@@ -16821,7 +16920,7 @@
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
       <x:c r="A25" s="63" t="str">
-        <x:v>独立3D验收场：scenes/Player3DStateGallery.tscn ｜ 真正驱动 Player3D 六态、WeaponModel3D 换弹覆盖、Enemy3D/Boss 九态与 ThemedNPC3D；验证：verify_player3d_state_gallery_flow.tscn / verify_player3d_state_gallery_visual.tscn PASS</x:v>
+        <x:v>独立3D验收：scenes/Player3DStateGallery.tscn；验证位于 tests/verification/</x:v>
       </x:c>
       <x:c r="B25" s="63"/>
       <x:c r="C25" s="63"/>
@@ -16839,7 +16938,7 @@
     </x:row>
     <x:row r="26" ht="32" customHeight="1">
       <x:c r="A26" s="83" t="str">
-        <x:v>动作覆盖层：firing 由 WeaponModel3D.shot_fired 启动；charging 读取真实蓄力；knockback 以命中方向驱动 hurt 冲量与弹性回正；唯一 Hand + weapon_socket 全程同相。验证：verify_player3d_state_gallery_flow.tscn PASS</x:v>
+        <x:v>动作覆盖层：firing / charging / knockback 不新增顶层状态；测试 tests/verification/verify_player3d_state_gallery_flow.tscn</x:v>
       </x:c>
       <x:c r="B26" s="83"/>
       <x:c r="C26" s="83"/>
@@ -16855,9 +16954,12 @@
       <x:c r="M26" s="83"/>
       <x:c r="N26" s="83"/>
     </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+    </x:row>
     <x:row r="28" ht="34" customHeight="1">
       <x:c r="A28" s="95" t="str">
-        <x:v>DIY 组件：body/head/hand 三组外观变体 + hat/glasses 独立头部配件；真实入口 Player3D.set_avatar_customization()；握持点内收，移动/射击/击飞中 Hand + weapon_socket 同相。验证：verify_player3d_diy_flow.tscn PASS</x:v>
+        <x:v>DIY：body / head / hand / feet / hat / glasses 只改表现；测试 tests/verification/verify_player3d_diy_flow.tscn</x:v>
       </x:c>
       <x:c r="B28" s="95"/>
       <x:c r="C28" s="95"/>
@@ -16875,7 +16977,7 @@
     </x:row>
     <x:row r="29" ht="38" customHeight="1">
       <x:c r="A29" t="str">
-        <x:v>PH33 方形猫：复用CHR-PLY-CAPSULE01-3D；Body/Head/Hand/Feet四主模块；Head含双矩形眼与双三角耳，Body含圆短尾；无嘴、无长尾、无第二手；moving双脚交替，手与weapon_socket全动作同相。</x:v>
+        <x:v>v0.1 兔子组件：Body / Head / Ears / HandL / HandR / FootL / FootR；视觉根不含玩法碰撞。</x:v>
       </x:c>
       <x:c r="B29"/>
       <x:c r="C29"/>
@@ -16923,7 +17025,7 @@
   <x:sheetData>
     <x:row r="1" ht="25" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>资产台账版本记录</x:v>
+        <x:v>资产台账版本记录 · 游戏设计文档 v0.1</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -16943,7 +17045,7 @@
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>只记录影响规范、分类、ID 或批量资产状态的变更；单张资产更新在主表版本列追踪</x:v>
+        <x:v>只记录当前有效基线；历史变更通过版本控制追溯</x:v>
       </x:c>
       <x:c r="B3" s="6"/>
       <x:c r="C3" s="6"/>
@@ -16977,716 +17079,296 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="36" t="str">
-        <x:v>v1.0</x:v>
+        <x:v>v0.1.0</x:v>
       </x:c>
       <x:c r="B6" s="53" t="n">
-        <x:v>46224</x:v>
+        <x:v>46236</x:v>
       </x:c>
       <x:c r="C6" s="36" t="str">
-        <x:v>首次建立</x:v>
+        <x:v>游戏设计文档 v0.1</x:v>
       </x:c>
       <x:c r="D6" s="36" t="str">
         <x:v>全项目</x:v>
       </x:c>
       <x:c r="E6" s="36" t="str">
-        <x:v>建立分类、查重、角色组件、状态映射；登记胶囊防护体 v001</x:v>
+        <x:v>统一3D塔楼主线、测试目录、当前资产路径、状态口径和投影契约；清理历史制作版本。</x:v>
       </x:c>
       <x:c r="F6" s="36" t="str">
-        <x:v>基线</x:v>
+        <x:v>只保留当前运行资产；历史追溯使用版本控制。</x:v>
       </x:c>
       <x:c r="G6" s="36" t="str">
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>v1.1</x:v>
-      </x:c>
-      <x:c r="B7" s="62" t="n">
-        <x:v>46224</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>组件契约修正</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>player_capsule01</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>停用左手运行时表现；唯一握持手固定在 (23,0)，准星只驱动枪械旋转</x:v>
-      </x:c>
-      <x:c r="F7" t="str">
-        <x:v>保留旧 AssetID/源文件</x:v>
-      </x:c>
-      <x:c r="G7" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>v1.2</x:v>
-      </x:c>
-      <x:c r="B8" s="62" t="n">
-        <x:v>46224</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>朝向与挂点契约修正</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>player_capsule01</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
-        <x:v>握持手改为随身体在 x=±19 镜像；枪械挂点同步 x=±24；垂直瞄准保持上次左右朝向</x:v>
-      </x:c>
-      <x:c r="F8" t="str">
-        <x:v>不改纹理与 AssetID</x:v>
-      </x:c>
-      <x:c r="G8" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A8"/>
+      <x:c r="B8"/>
+      <x:c r="C8"/>
+      <x:c r="D8"/>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="63" t="str">
-        <x:v>v1.3</x:v>
-      </x:c>
-      <x:c r="B9" s="64" t="n">
-        <x:v>46224</x:v>
-      </x:c>
-      <x:c r="C9" s="63" t="str">
-        <x:v>3D变体登记</x:v>
-      </x:c>
-      <x:c r="D9" s="63" t="str">
-        <x:v>入口基地 / player_capsule01</x:v>
-      </x:c>
-      <x:c r="E9" s="63" t="str">
-        <x:v>登记首张3D入口地图、设施/入口模块、3D角色root/body/head/hand/scarf/socket；六态ID与2D保持一致</x:v>
-      </x:c>
-      <x:c r="F9" s="63" t="str">
-        <x:v>保留原2D资产与场景作为基线</x:v>
-      </x:c>
-      <x:c r="G9" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A9"/>
+      <x:c r="B9"/>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
-      <x:c r="A10" s="63" t="str">
-        <x:v>v1.4</x:v>
-      </x:c>
-      <x:c r="B10" s="64" t="n">
-        <x:v>46224</x:v>
-      </x:c>
-      <x:c r="C10" s="63" t="str">
-        <x:v>全游戏3D原型登记</x:v>
-      </x:c>
-      <x:c r="D10" s="63" t="str">
-        <x:v>四主题副本 / 靶场 / 战斗 / 共用资产</x:v>
-      </x:c>
-      <x:c r="E10" s="63" t="str">
-        <x:v>登记通用房间、4主题、灯具、三档家具与搜索、服务/撤离、枪械、七怪、战斗VFX、3D靶场和两张GPU验收预览</x:v>
-      </x:c>
-      <x:c r="F10" s="63" t="str">
-        <x:v>复用原玩法ID与BlueprintRegistry；保留2D基线</x:v>
-      </x:c>
-      <x:c r="G10" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A10"/>
+      <x:c r="B10"/>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
-      <x:c r="A11" s="63" t="str">
-        <x:v>v1.5</x:v>
-      </x:c>
-      <x:c r="B11" s="64" t="n">
-        <x:v>46225</x:v>
-      </x:c>
-      <x:c r="C11" s="63" t="str">
-        <x:v>真实视野与3D输入验收登记</x:v>
-      </x:c>
-      <x:c r="D11" s="63" t="str">
-        <x:v>3D视野 / 背包 / 暂停 / Enemy3D</x:v>
-      </x:c>
-      <x:c r="E11" s="63" t="str">
-        <x:v>登记真实视野场、3D背包子变体和共用暂停UI；低血暗角完成接入；Enemy3D状态表由七态修正为九态</x:v>
-      </x:c>
-      <x:c r="F11" s="63" t="str">
-        <x:v>复用既有视野/背包/VFX根身份；新增暂停根；不改变2D资产ID</x:v>
-      </x:c>
-      <x:c r="G11" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A11"/>
+      <x:c r="B11"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="63" t="str">
-        <x:v>v1.6</x:v>
-      </x:c>
-      <x:c r="B12" s="64" t="n">
-        <x:v>46225</x:v>
-      </x:c>
-      <x:c r="C12" s="63" t="str">
-        <x:v>暗室照明与战斗生态登记</x:v>
-      </x:c>
-      <x:c r="D12" s="63" t="str">
-        <x:v>3D视野 / 房灯 / 怪物 / 枪械组合</x:v>
-      </x:c>
-      <x:c r="E12" s="63" t="str">
-        <x:v>登记柔边视野与表现层探照灯、中央顶灯与墙面开关；七类怪碰撞随模型轮廓；枪械/子弹3D适配与开局副枪完成</x:v>
-      </x:c>
-      <x:c r="F12" s="63" t="str">
-        <x:v>新增一个房灯开关根；其余复用既有根ID；玩法逻辑与表现解耦</x:v>
-      </x:c>
-      <x:c r="G12" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
     </x:row>
     <x:row r="13" ht="60" customHeight="1">
-      <x:c r="A13" s="70" t="str">
-        <x:v>v1.7</x:v>
-      </x:c>
-      <x:c r="B13" s="71" t="n">
-        <x:v>46225</x:v>
-      </x:c>
-      <x:c r="C13" s="70" t="str">
-        <x:v>真实灯光与3D背包投影登记</x:v>
-      </x:c>
-      <x:c r="D13" s="70" t="str">
-        <x:v>玩家探照灯 / 3D背包 / 世界道具模型</x:v>
-      </x:c>
-      <x:c r="E13" s="70" t="str">
-        <x:v>登记独立真实探照灯和共用3D道具投影；视野不再持有灯光；实际槽位点击换枪纳入资产验收</x:v>
-      </x:c>
-      <x:c r="F13" s="70" t="str">
-        <x:v>新增两个可复用子资产；不复制每个道具图标；玩法视野与灯光继续解耦</x:v>
-      </x:c>
-      <x:c r="G13" s="70" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
-      <x:c r="A14" s="63" t="str">
-        <x:v>v1.8</x:v>
-      </x:c>
-      <x:c r="B14" s="64" t="n">
-        <x:v>46225</x:v>
-      </x:c>
-      <x:c r="C14" s="63" t="str">
-        <x:v>360°逻辑视野契约修正</x:v>
-      </x:c>
-      <x:c r="D14" s="63" t="str">
-        <x:v>VFX-VISIBILITY-FIELD-3D / PlayerVision3D</x:v>
-      </x:c>
-      <x:c r="E14" s="63" t="str">
-        <x:v>目标显隐改为21m内360°物理遮挡；保留96°柔边目光场与探照灯表现。</x:v>
-      </x:c>
-      <x:c r="F14" s="63" t="str">
-        <x:v>AssetID和路径不变；只更新玩法角度契约、诊断字段与验收。</x:v>
-      </x:c>
-      <x:c r="G14" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
     </x:row>
     <x:row r="15" ht="72" customHeight="1">
-      <x:c r="A15" s="70" t="str">
-        <x:v>v1.9</x:v>
-      </x:c>
-      <x:c r="B15" s="71" t="n">
-        <x:v>46225</x:v>
-      </x:c>
-      <x:c r="C15" s="70" t="str">
-        <x:v>3D战斗生命、AI与反馈闭环</x:v>
-      </x:c>
-      <x:c r="D15" s="70" t="str">
-        <x:v>Enemy3D / 玩家状态动画 / 三层灯组 / 钥匙与掉落</x:v>
-      </x:c>
-      <x:c r="E15" s="70" t="str">
-        <x:v>修复AI视线与3D HP倍率；moving独立动画；环境/角色灯分层；中央灯增强；拾取上弹旋转；钥匙近距生成、查重与补发</x:v>
-      </x:c>
-      <x:c r="F15" s="70" t="str">
-        <x:v>不新增AssetID或复制模型；更新既有根资产行为、哈希、状态职责与验收契约</x:v>
-      </x:c>
-      <x:c r="G15" s="70" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
     </x:row>
     <x:row r="16" ht="72" customHeight="1">
-      <x:c r="A16" s="63" t="str">
-        <x:v>v1.10</x:v>
-      </x:c>
-      <x:c r="B16" s="64" t="n">
-        <x:v>46225</x:v>
-      </x:c>
-      <x:c r="C16" s="63" t="str">
-        <x:v>3D换弹覆盖状态登记</x:v>
-      </x:c>
-      <x:c r="D16" s="63" t="str">
-        <x:v>CHR-PLY-CAPSULE01-3D / WPN-GUN-KIT-3D / 玩家状态机</x:v>
-      </x:c>
-      <x:c r="E16" s="63" t="str">
-        <x:v>换弹成为可与移动并存的覆盖态；武器唯一计时驱动单手/枪同相动画和头顶billboard进度条；完成/补弹/换枪/死亡清理</x:v>
-      </x:c>
-      <x:c r="F16" s="63" t="str">
-        <x:v>不新增AssetID；六态白名单与56组合不变；复用既有角色根和枪械套件</x:v>
-      </x:c>
-      <x:c r="G16" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
     </x:row>
     <x:row r="17" ht="52" customHeight="1">
-      <x:c r="A17" s="63" t="str">
-        <x:v>v1.11</x:v>
-      </x:c>
-      <x:c r="B17" s="63" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="C17" s="63" t="str">
-        <x:v>3D动作覆盖层登记</x:v>
-      </x:c>
-      <x:c r="D17" s="63" t="str">
-        <x:v>CHR-PLY-CAPSULE01-3D / WPN-GUN-KIT-3D</x:v>
-      </x:c>
-      <x:c r="E17" s="63" t="str">
-        <x:v>登记 firing/charging/knockback：真实武器/命中来源、手与weapon_socket同相、击飞基础位移与弹性回正；预览场控件和自动验收补齐</x:v>
-      </x:c>
-      <x:c r="F17" s="63" t="str">
-        <x:v>不新增AssetID或贴图；六态保持互斥，动作以既有组件程序组合</x:v>
-      </x:c>
-      <x:c r="G17" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
     </x:row>
     <x:row r="18" ht="50" customHeight="1">
-      <x:c r="A18" s="63" t="str">
-        <x:v>v1.12</x:v>
-      </x:c>
-      <x:c r="B18" s="63" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="C18" s="63" t="str">
-        <x:v>3D角色DIY组件登记</x:v>
-      </x:c>
-      <x:c r="D18" s="63" t="str">
-        <x:v>CHR-PLY-CAPSULE01-3D 及五个子变体</x:v>
-      </x:c>
-      <x:c r="E18" s="63" t="str">
-        <x:v>登记 body/head/hand/hat/glasses 可装配变体、内收握持点、动态继承和预览/自动验收</x:v>
-      </x:c>
-      <x:c r="F18" s="63" t="str">
-        <x:v>新增子AssetID；不增加角色根，不改玩法或六态</x:v>
-      </x:c>
-      <x:c r="G18" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
     </x:row>
     <x:row r="19" ht="52" customHeight="1">
-      <x:c r="A19" s="63" t="str">
-        <x:v>v1.13</x:v>
-      </x:c>
-      <x:c r="B19" s="63" t="str">
-        <x:v>2026-07-25</x:v>
-      </x:c>
-      <x:c r="C19" s="63" t="str">
-        <x:v>方形猫3D角色原型登记</x:v>
-      </x:c>
-      <x:c r="D19" s="63" t="str">
-        <x:v>CHR-PLY-CAPSULE01-3D及脚/眼/耳/短尾子资产</x:v>
-      </x:c>
-      <x:c r="E19" s="63" t="str">
-        <x:v>复用玩家根；登记Body/Head/Hand/Feet四主模块、双矩形眼、双三角耳、圆短尾、feet DIY及交替脚步</x:v>
-      </x:c>
-      <x:c r="F19" s="63" t="str">
-        <x:v>新增5个子AssetID；旧2D胶囊不变；3D旧Scarf隐藏兼容；玩法、碰撞、六态和灯光契约不变</x:v>
-      </x:c>
-      <x:c r="G19" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
     </x:row>
     <x:row r="20" ht="90" customHeight="1">
-      <x:c r="A20" s="63" t="str">
-        <x:v>v1.14</x:v>
-      </x:c>
-      <x:c r="B20" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="C20" s="63" t="str">
-        <x:v>兔子武器姿势与虚拟碰撞契约</x:v>
-      </x:c>
-      <x:c r="D20" s="63" t="str">
-        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01 / PlayerAvatar3D / Player3D</x:v>
-      </x:c>
-      <x:c r="E20" s="63" t="str">
-        <x:v>登记圆环近端手腕轴心；手枪右侧单手、长枪右手握把+左手托举；hold/run/fire/reload/charge 武器姿势状态机；七枪差异后坐；模型零碰撞，根节点 1.80m 无耳虚拟盒</x:v>
-      </x:c>
-      <x:c r="F20" s="63" t="str">
-        <x:v>不新增 AssetID、不复制 GLB、不改 v004 Blender 源网格；仅更新运行时姿势、碰撞职责与验收契约</x:v>
-      </x:c>
-      <x:c r="G20" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
     </x:row>
     <x:row r="21" ht="86" customHeight="1">
-      <x:c r="A21" s="63" t="str">
-        <x:v>v1.15</x:v>
-      </x:c>
-      <x:c r="B21" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="C21" s="63" t="str">
-        <x:v>兔子站立待机动画登记</x:v>
-      </x:c>
-      <x:c r="D21" s="63" t="str">
-        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01 / PlayerAvatar3D / Player3DIdleState</x:v>
-      </x:c>
-      <x:c r="E21" s="63" t="str">
-        <x:v>复用既有六态 idle：登记约2.38s站立循环、呼吸挤压、重心换脚、头部滞后、双耳错相/偶发耳弹及持枪呼吸；移动时立即退出，停下后恢复</x:v>
-      </x:c>
-      <x:c r="F21" s="63" t="str">
-        <x:v>不新增顶层状态、不新增 AssetID、不改 Blender/GLB；仅强化 v004 运行时组件动画与自动验收</x:v>
-      </x:c>
-      <x:c r="G21" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
     </x:row>
     <x:row r="22" ht="72" customHeight="1">
-      <x:c r="A22" s="63" t="str">
-        <x:v>v1.16</x:v>
-      </x:c>
-      <x:c r="B22" s="64" t="n">
-        <x:v>46232</x:v>
-      </x:c>
-      <x:c r="C22" s="63" t="str">
-        <x:v>塔楼Blender三层堆叠版登记</x:v>
-      </x:c>
-      <x:c r="D22" s="63" t="str">
-        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
-      </x:c>
-      <x:c r="E22" s="63" t="str">
-        <x:v>将旧v001横向组件评审板保留为历史版本；登记独立v002三层真实堆叠文件，含楼板、外墙、室内隔墙、15扇门及西/东两段实际楼梯，并修复同名文件覆盖导致的评审图不一致。</x:v>
-      </x:c>
-      <x:c r="F22" s="63" t="str">
-        <x:v>AssetID不变；只升级Blender评审源文件版本；确认前不导出GLB、不接入Godot。</x:v>
-      </x:c>
-      <x:c r="G22" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
     </x:row>
     <x:row r="23" ht="78" customHeight="1">
-      <x:c r="A23" s="63" t="str">
-        <x:v>v1.17</x:v>
-      </x:c>
-      <x:c r="B23" s="64" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="C23" s="63" t="str">
-        <x:v>塔楼双楼梯与五倍边长地图登记</x:v>
-      </x:c>
-      <x:c r="D23" s="63" t="str">
-        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
-      </x:c>
-      <x:c r="E23" s="63" t="str">
-        <x:v>将用户手工v003保存为快照；登记v004特殊楼顶梯与通用旋转梯、02_STAIRWELLS集合层级、核心门口连接板、335.410m总占地、67.082m中央核心和空外围楼板。</x:v>
-      </x:c>
-      <x:c r="F23" s="63" t="str">
-        <x:v>AssetID不变；v003可回退；只升级Blender评审源文件，确认前不导出GLB、不接入Godot。</x:v>
-      </x:c>
-      <x:c r="G23" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
+      <x:c r="G23"/>
     </x:row>
     <x:row r="24" ht="100" customHeight="1">
-      <x:c r="A24" s="63" t="str">
-        <x:v>v1.18</x:v>
-      </x:c>
-      <x:c r="B24" s="64" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="C24" s="63" t="str">
-        <x:v>塔楼整层外壳五倍边长修正</x:v>
-      </x:c>
-      <x:c r="D24" s="63" t="str">
-        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
-      </x:c>
-      <x:c r="E24" s="63" t="str">
-        <x:v>登记v005：楼顶女儿墙、基地外墙、战斗层外墙全部移到335.410m总楼层边界；旧核心满高外墙取消，67.082m中央核心、楼梯、门、设施和内部隔墙保持原尺寸。</x:v>
-      </x:c>
-      <x:c r="F24" s="63" t="str">
-        <x:v>AssetID不变；v004可回退；只修正Blender评审母版，确认前不导出GLB、不接入Godot。</x:v>
-      </x:c>
-      <x:c r="G24" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+      <x:c r="G24"/>
     </x:row>
     <x:row r="25" ht="115" customHeight="1">
-      <x:c r="A25" s="63" t="str">
-        <x:v>v1.19</x:v>
-      </x:c>
-      <x:c r="B25" s="64" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="C25" s="63" t="str">
-        <x:v>塔楼五米模块化楼层与墙体</x:v>
-      </x:c>
-      <x:c r="D25" s="63" t="str">
-        <x:v>ENV-TOWER-DESCENT-KIT-3D; ENV-TOWER-FLOOR-TILE-5M; ENV-TOWER-WALL-SOLID-5M; ENV-TOWER-WALL-PARAPET-5M; ENV-TOWER-WALL-DOOR-5M</x:v>
-      </x:c>
-      <x:c r="E25" s="63" t="str">
-        <x:v>登记v006：335m整层与65m基地/战斗核心全部对齐5m网格；地砖、满高墙、楼顶女儿墙、带门墙成为四个稳定子资产，基地完整围合，战斗内墙和门可独立拼装。</x:v>
-      </x:c>
-      <x:c r="F25" s="63" t="str">
-        <x:v>v005用户内存状态另存快照；楼梯手调结构不重做。四个子资产当前仅为Blender程序占位，未导出GLB、未接入Godot。</x:v>
-      </x:c>
-      <x:c r="G25" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+      <x:c r="G25"/>
     </x:row>
     <x:row r="26" ht="118" customHeight="1">
-      <x:c r="A26" s="70" t="str">
-        <x:v>v1.20</x:v>
-      </x:c>
-      <x:c r="B26" s="71" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="C26" s="70" t="str">
-        <x:v>塔楼5m GLB与99—95层Godot首批关卡接入</x:v>
-      </x:c>
-      <x:c r="D26" s="70" t="str">
-        <x:v>ENV-TOWER-DESCENT-KIT-3D及四个5m子资产</x:v>
-      </x:c>
-      <x:c r="E26" s="70" t="str">
-        <x:v>四个Blender模块导出独立GLB并接入335m楼顶、99层基地、98—95层五房+电梯探索关卡；登记9m双跑楼梯、门后命运、Boss/撤离、城市日照、智能剖切与≤5层流送验收。</x:v>
-      </x:c>
-      <x:c r="F26" s="70" t="str">
-        <x:v>AssetID与v006 Blender母版不变；子资产状态由程序占位升级为原型已接入；旧四主题Dungeon3D玩法继续共用。</x:v>
-      </x:c>
-      <x:c r="G26" s="70" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+      <x:c r="G26"/>
     </x:row>
     <x:row r="27" ht="118" customHeight="1">
-      <x:c r="A27" s="70" t="str">
-        <x:v>v1.21</x:v>
-      </x:c>
-      <x:c r="B27" s="71" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="C27" s="70" t="str">
-        <x:v>Blender楼梯直入与99—95层种子化关卡</x:v>
-      </x:c>
-      <x:c r="D27" s="70" t="str">
-        <x:v>ENV-TOWER-DESCENT-KIT-3D; ENV-TOWER-STAIRWELL-GENERIC-9M; ENV-TOWER-STAIRWELL-ROOFTOP-9M</x:v>
-      </x:c>
-      <x:c r="E27" s="70" t="str">
-        <x:v>两套用户手调楼梯从v006根节点直接导出GLB并接入Godot；登记前三段门禁差异、四类种子化房间模板、固定电梯、95层Boss、城市/室内光、智能遮挡与≤5层流送。</x:v>
-      </x:c>
-      <x:c r="F27" s="70" t="str">
-        <x:v>新增两个楼梯子AssetID，不复制程序踏步；四个5m模块ID和母版ID不变；运行时碰撞/吸附与Blender视觉职责分离。</x:v>
-      </x:c>
-      <x:c r="G27" s="70" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
     </x:row>
     <x:row r="28" ht="118" customHeight="1">
-      <x:c r="A28" s="70" t="str">
-        <x:v>v1.22</x:v>
-      </x:c>
-      <x:c r="B28" s="71" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="C28" s="70" t="str">
-        <x:v>bunny01完整视觉与碰撞统一为1米</x:v>
-      </x:c>
-      <x:c r="D28" s="70" t="str">
-        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01及六个稳定组件AssetID</x:v>
-      </x:c>
-      <x:c r="E28" s="70" t="str">
-        <x:v>从v004派生真实1m Blender v005与七个pivot-local GLB；Godot改用v005装配，碰撞体高1m，持枪视觉、挂点、可穿戴、VFX和全部米制动作平移同步缩放。</x:v>
-      </x:c>
-      <x:c r="F28" s="70" t="str">
-        <x:v>不新增角色AssetID；v004保留回退。静态AABB、六态、武器姿势、碰撞、DIY、换弹、塔楼与性能验收通过。</x:v>
-      </x:c>
-      <x:c r="G28" s="70" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
+      <x:c r="G28"/>
     </x:row>
     <x:row r="29" ht="84" hidden="0" customHeight="1">
-      <x:c r="A29" s="70" t="str">
-        <x:v>v1.23</x:v>
-      </x:c>
-      <x:c r="B29" s="71" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="C29" s="70" t="str">
-        <x:v>bunny01正式定版为1.5米</x:v>
-      </x:c>
-      <x:c r="D29" s="70" t="str">
-        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01及六个稳定组件AssetID</x:v>
-      </x:c>
-      <x:c r="E29" s="70" t="str">
-        <x:v>从一米v005等比烘焙真实1.5m Blender v006、七个pivot-local GLB与Godot v006装配；取消Avatar3D临时1.5倍缩放，碰撞、挂点、附件与米制动画固定为1.5m契约。</x:v>
-      </x:c>
-      <x:c r="F29" s="70" t="str">
-        <x:v>不新增AssetID；v005保留回退。Blender/Godot AABB、武器姿势、碰撞、六态、DIY、换弹、塔楼楼梯和PH40镜头验收通过。</x:v>
-      </x:c>
-      <x:c r="G29" s="70" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
     </x:row>
     <x:row r="30" ht="118" customHeight="1">
-      <x:c r="A30" s="70" t="str">
-        <x:v>v1.24</x:v>
-      </x:c>
-      <x:c r="B30" s="71" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="C30" s="70" t="str">
-        <x:v>PH43楼梯承重、下落落地与屋顶可读性</x:v>
-      </x:c>
-      <x:c r="D30" s="70" t="str">
-        <x:v>Player3D / bunny01 v006 / 两套9m楼梯 / 楼顶洞口与镜头</x:v>
-      </x:c>
-      <x:c r="E30" s="70" t="str">
-        <x:v>六态扩展为八态falling/landing；1.5m玩法碰撞改胶囊；楼梯取消Y吸附并合并连续三角承重面；掉落/钥匙向下找承重面；导入墙补同形碰撞；楼顶洞口收紧、8m镜头侧向避障并加物理天空反弹光；进入特殊楼梯围护体立即启用角色探照灯。</x:v>
-      </x:c>
-      <x:c r="F30" s="70" t="str">
-        <x:v>不新增角色/楼梯AssetID、GLB或贴图；v006模型尺寸和单太阳参数不变；原战斗/命运/枪械/流送兼容。</x:v>
-      </x:c>
-      <x:c r="G30" s="70" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
     </x:row>
     <x:row r="31" ht="118" customHeight="1">
-      <x:c r="A31" s="70" t="str">
-        <x:v>v1.25</x:v>
-      </x:c>
-      <x:c r="B31" s="71" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="C31" s="70" t="str">
-        <x:v>PH43楼梯Walkable根因修复与固定镜头</x:v>
-      </x:c>
-      <x:c r="D31" s="70" t="str">
-        <x:v>Player3D / bunny01 v006 / 两套9m楼梯 / 楼顶洞口与镜头</x:v>
-      </x:c>
-      <x:c r="E31" s="70" t="str">
-        <x:v>六态扩展为八态falling/landing；1.5m玩法碰撞改胶囊；楼梯取消Y吸附与程序路径承重面，直接采用v006每套六块*Walkable网格同形常驻碰撞；掉落/钥匙向下找承重面；EnclosureWall补围护碰撞；楼顶洞口收紧并加物理天空反弹光；镜头固定(0,8,5.5)、FOV 55°，每物理帧覆盖外部位移与旋转；进入特殊楼梯围护体立即启用角色探照灯。</x:v>
-      </x:c>
-      <x:c r="F31" s="70" t="str">
-        <x:v>不新增角色/楼梯AssetID、GLB或贴图；v006模型尺寸和单太阳参数不变；原战斗/命运/枪械/流送兼容。</x:v>
-      </x:c>
-      <x:c r="G31" s="70" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
     </x:row>
     <x:row r="32" ht="118" customHeight="1">
-      <x:c r="A32" s="70" t="str">
-        <x:v>v1.26</x:v>
-      </x:c>
-      <x:c r="B32" s="71" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="C32" s="70" t="str">
-        <x:v>PH44二百五十米塔楼与四乘四战斗层重构</x:v>
-      </x:c>
-      <x:c r="D32" s="70" t="str">
-        <x:v>塔楼整层 / 5m地砖与墙体 / 两套9m楼梯 / 固定镜头局部剖切</x:v>
-      </x:c>
-      <x:c r="E32" s="70" t="str">
-        <x:v>整层统一50×50格（250×250m、2500砖）；65×65m基地核心不变并偏移2.5m对齐；普通层12个45×45m房间，Boss层90×90m Boss区+9个普通房；实墙按方向MultiMesh批渲染并合并碰撞；上下楼梯分别记录两端门侧；固定8m镜头只剖切挡住角色的墙体渲染；楼顶天空反弹光降至1.25。</x:v>
-      </x:c>
-      <x:c r="F32" s="70" t="str">
-        <x:v>不新增AssetID、GLB或贴图；v006楼梯与既有5m模块继续复用；碰撞、房门、命运卡、刷怪、流送和固定镜头角度保持兼容。完整探索节点数2783。</x:v>
-      </x:c>
-      <x:c r="G32" s="70" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
     </x:row>
     <x:row r="33" ht="128" customHeight="1">
-      <x:c r="A33" s="70" t="str">
-        <x:v>v1.27</x:v>
-      </x:c>
-      <x:c r="B33" s="71" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="C33" s="70" t="str">
-        <x:v>PH49九十八至九十五层终局关卡与全局系统验收</x:v>
-      </x:c>
-      <x:c r="D33" s="70" t="str">
-        <x:v>ENV-TOWER-DESCENT-KIT-3D; ENV-TOWER-WALL-DOOR-5M; ENV-DUNGEON-RUNTIME-3D; PRP-BASE-FACILITY-3D; PRP-WASTELAND-LIGHT-3D; PRP-ROOM-LIGHT-SWITCH-3D; UI-SCREEN-HUD; CHR-PLY-CAPSULE01-3D</x:v>
-      </x:c>
-      <x:c r="E33" s="70" t="str">
-        <x:v>完成98—95层怪物、搜刮、随机房间/掉落与95层Boss撤离闭环；基地30×30m/6×6格；修正98层入口内外侧；电梯改为墙边独立设施；门统一2.2×2.5m；环境光改为全局固定；关闭会让墙体概率消失的相机材质淡出；基地四灯组和开关；实时3D全息小地图与游戏化HUD。</x:v>
-      </x:c>
-      <x:c r="F33" s="70" t="str">
-        <x:v>Blender v007与Godot布局同步；导出门v002 GLB；三份仓库外角色Blender源归档进项目且不新增重复AssetID。主流程、全部楼层门、实际楼梯、灯光开关、随机种子、Boss撤离、相机遮挡和性能预算均有自动验收。</x:v>
-      </x:c>
-      <x:c r="G33" s="70" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
     </x:row>
     <x:row r="34" ht="96" customHeight="1">
-      <x:c r="A34" s="63" t="str">
-        <x:v>v1.28</x:v>
-      </x:c>
-      <x:c r="B34" s="63" t="str">
-        <x:v>2026-08-01</x:v>
-      </x:c>
-      <x:c r="C34" s="63" t="str">
-        <x:v>PH50三十乘二十五房间、模块化基地墙与分层投影修复</x:v>
-      </x:c>
-      <x:c r="D34" s="63" t="str">
-        <x:v>ENV-TOWER-DESCENT-KIT-3D; ENV-TOWER-WALL-SOLID-5M; ENV-TOWER-WALL-DOOR-5M; PRP-WASTELAND-LIGHT-3D; VFX-PLAYER-FLASHLIGHT-3D; ENV-DUNGEON-RUNTIME-3D</x:v>
-      </x:c>
-      <x:c r="E34" s="63" t="str">
-        <x:v>98—96层普通房统一30×25m/6×5格并紧凑重排；基地删除整墙拉伸路径，改用独立5m墙、门墙和L拐角组件；墙段A/B材质交替；房间灯递归流送并让玩家/怪物投影；前向灯只照环境层，不对玩家自投影；普通行动区恢复初始1钥匙与唯一STANDARD信标。</x:v>
-      </x:c>
-      <x:c r="F34" s="63" t="str">
-        <x:v>不新增AssetID、GLB或贴图；复用既有5m模块与两套墙材质。塔楼、94门物理通行、3D核心、四主题完整流程、房灯、视野输入、背包武器、换弹、撤离、运行安全和性能预算全部通过，并完成真实渲染复核。</x:v>
-      </x:c>
-      <x:c r="G34" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A34"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+      <x:c r="G34"/>
     </x:row>
     <x:row r="35" ht="108" customHeight="1">
-      <x:c r="A35" s="63" t="str">
-        <x:v>v1.29</x:v>
-      </x:c>
-      <x:c r="B35" s="64" t="n">
-        <x:v>46235</x:v>
-      </x:c>
-      <x:c r="C35" s="63" t="str">
-        <x:v>PH50 五米组件坐标与玩家灯光自投影修复</x:v>
-      </x:c>
-      <x:c r="D35" s="63" t="str">
-        <x:v>ENV-TOWER-DESCENT-KIT-3D / ENV-TOWER-FLOOR-TILE-5M / ENV-TOWER-WALL-SOLID-5M / ENV-TOWER-STAIRWELL-GENERIC-9M / CHR-PLY-CAPSULE01-BUNNY01 / WPN-GUN-KIT-3D</x:v>
-      </x:c>
-      <x:c r="E35" s="63" t="str">
-        <x:v>基底层改为合法6×6组件边界；98—95层30×25房间按5m格线重排；门墙、交互门与走廊端点由两端真实门槽求交；楼梯只挖上层楼板；玩家/配件/手持武器禁投影，前向灯仍保留环境与怪物阴影。</x:v>
-      </x:c>
-      <x:c r="F35" s="63" t="str">
-        <x:v>AssetID与GLB不变；Godot关卡坐标、楼板覆盖和渲染属性更新；TOWER_GRID_COMPONENT_ALIGNMENT_OK、TOWER_DESCENT_FLOW_OK、94门通行、灯光/性能/视觉回归通过。</x:v>
-      </x:c>
-      <x:c r="G35" s="63" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A35"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
+      <x:c r="G35"/>
     </x:row>
     <x:row r="36" ht="72" customHeight="1">
-      <x:c r="A36" t="str">
-        <x:v>v1.30</x:v>
-      </x:c>
-      <x:c r="B36" s="62" t="n">
-        <x:v>46236</x:v>
-      </x:c>
-      <x:c r="C36" s="63" t="str">
-        <x:v>PH51 灯光投影、地砖反光、9m南墙与刷怪软锁修复</x:v>
-      </x:c>
-      <x:c r="D36" s="63" t="str">
-        <x:v>CHR-PLY-CAPSULE01-3D / ENV-TOWER-FLOOR-TILE-5M / ENV-TOWER-WALL-SOLID-5M / Dungeon3D</x:v>
-      </x:c>
-      <x:c r="E36" s="63" t="str">
-        <x:v>角色恢复太阳/室内灯投影但三盏随身灯不自投影；地砖降反光；实墙/门墙/拐角统一9m并仅南墙参与摄像机交互；隐藏连接器碰撞随显隐；敌对房间增加生成兜底与旧状态修复。</x:v>
-      </x:c>
-      <x:c r="F36" s="63" t="str">
-        <x:v>不新增AssetID；仅修正既有组件配置与生成/碰撞逻辑；全量回归PASS</x:v>
-      </x:c>
-      <x:c r="G36" t="str">
-        <x:v>Codex</x:v>
-      </x:c>
+      <x:c r="A36"/>
+      <x:c r="B36"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
+      <x:c r="G36"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0a8841f7c7484ec9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R4a9ad332e3514442"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R8a9ca5ec05d94bc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R66a38b32129e4722"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R8ce0f4a8cebf490c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rfa43cc9bf7fb4ec6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R5dab1cd4fc1046eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R2075c7f791c24df8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re146b146528e4695"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Re058249dcb6f45a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R11460df5f28f4241"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rf98cafef292844de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R705bdb1888b249b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R9e46c897485f438f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Rbf01b378a3c04efe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R27e531a01c9c46fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11155,7 +11155,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X144" t="str">
-        <x:v>v0.1：前向SpotLight仅命中环境layer1并保留环境/怪物投影；玩家、穿戴物与手持枪统一位于layer2且cast_shadow=OFF，不进入随身灯shadow map。layer2只接受无阴影正面补光；已通过真实渲染与自投影专项验收。</x:v>
+        <x:v>v0.1：ForwardBeam仅照环境layer1，shadow_caster_mask也仅包含layer1，明确排除玩家、穿戴物与手持枪layer2；AvatarFrontFill无阴影。玩家网格保留cast_shadow=ON，由太阳和室内灯产生外部投影；准星禁用投影。曝光预算固定为主聚光7.2、环境溢光0.7、角色柔光2.8，并通过真实渲染验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -11535,7 +11535,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X149" s="63" t="str">
-        <x:v>胶囊防护体3D帽子DIY组件；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；tests/verification/verify_player3d_diy_flow PASS ｜ v0.1灯光修正：角色专用层2；禁用投影/GI，仅接收AvatarFrontFill，不遮挡头壳传感器或探照灯 ｜ v0.1：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+        <x:v>胶囊防护体3D帽子DIY组件；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；tests/verification/verify_player3d_diy_flow PASS ｜ v0.1灯光修正：角色专用layer2、GI关闭；保留太阳/室内灯外部投影，玩家随身灯以shadow_caster_mask排除layer2；不遮挡头壳传感器或探照灯 ｜ v0.1：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="44" customHeight="1">
@@ -11611,7 +11611,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X150" s="63" t="str">
-        <x:v>胶囊防护体3D眼镜DIY组件；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；tests/verification/verify_player3d_diy_flow PASS ｜ v0.1灯光修正：角色专用层2；禁用投影/GI，仅接收AvatarFrontFill，不遮挡头壳传感器或探照灯 ｜ v0.1：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
+        <x:v>胶囊防护体3D眼镜DIY组件；作为 CHR-PLY-CAPSULE01-3D 子变体，由 Player3D.set_avatar_customization() 驱动；不改玩法。手/挂点内收并在移动、换弹、射击、蓄力、击飞中保持同相；tests/verification/verify_player3d_diy_flow PASS ｜ v0.1灯光修正：角色专用layer2、GI关闭；保留太阳/室内灯外部投影，玩家随身灯以shadow_caster_mask排除layer2；不遮挡头壳传感器或探照灯 ｜ v0.1：适配方形猫四模块与feet槽；双眼/双耳/圆短尾保持父组件归属</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="44" customHeight="1">
@@ -12067,7 +12067,7 @@
         <x:v>原创 Blender/Godot 组合</x:v>
       </x:c>
       <x:c r="X156" s="70" t="str">
-        <x:v>v0.1：玩家网格位于 layer2，允许太阳与室内灯产生外部投影；玩家随身三盏灯不对角色自身投影；GI关闭。</x:v>
+        <x:v>v0.1：玩家网格位于layer2并保持cast_shadow=ON；太阳与室内灯的shadow_caster_mask包含layer1|layer2，可产生正常外部投影。玩家随身三盏灯的阴影图排除layer2，不对角色自身投影；GI关闭。</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="118" customHeight="1">
@@ -12745,7 +12745,7 @@
         <x:v>程序生成 Blender 源集合</x:v>
       </x:c>
       <x:c r="X165" s="70" t="str">
-        <x:v>v0.1：实墙、门墙与拐角统一0—9m；仅南侧朝北墙参与镜头交互；隐藏连接器不保留阻挡碰撞；A/B材质按网格交替。</x:v>
+        <x:v>v0.1：实墙、门墙与拐角统一0—9m；仅南侧朝北墙参与镜头交互。水平隔间南墙统一注册镜头墙；南侧门洞使用5×9m相机专用代理碰撞（layer16），开门后仍触发抬升/收镜，但代理不阻挡角色、怪物或子弹。镜头使用从角色前侧穿过角色的三条横向探针并允许内部起点命中；隐藏连接器不保留阻挡碰撞；A/B材质按网格交替。</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="132" customHeight="1">
@@ -12887,13 +12887,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V167" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46236</x:v>
       </x:c>
       <x:c r="W167" s="70" t="str">
         <x:v>程序生成 Blender 源集合</x:v>
       </x:c>
       <x:c r="X167" s="70" t="str">
-        <x:v>v0.1：基地、楼顶和战斗房复用同一5m门墙与2.2×2.5m净空；门扇、触发体、碰撞和目标边共用同一组件坐标。</x:v>
+        <x:v>v0.1：门墙保持5m模块坐标和9m总高；南侧门洞拥有独立5×9m相机专用代理碰撞（layer16），门扇开启或禁用实体碰撞时仍触发镜头抬升/收回。代理仅供相机探针查询，不参与角色、怪物、子弹或导航阻挡。</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="132" customHeight="1">
@@ -13073,7 +13073,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4a77b1d5b2e42fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc128da19cc44bf2"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re146b146528e4695"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Re058249dcb6f45a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R11460df5f28f4241"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rf98cafef292844de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R705bdb1888b249b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R9e46c897485f438f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Rbf01b378a3c04efe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R27e531a01c9c46fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Recdf561dd38e4307"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R87b35accb2ff4162"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R12b2ef04f01e45c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rb92e61661b894992"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rd4ae00453da34079"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R3f397cfdc2384a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Re66f83729f474423"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R8b883a573c824769"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -12591,13 +12591,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V163" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46236</x:v>
       </x:c>
       <x:c r="W163" s="71" t="str">
         <x:v>程序生成 Blender 源集合</x:v>
       </x:c>
       <x:c r="X163" s="70" t="str">
-        <x:v>v0.1：250m整层与65m核心使用5m组件；99层30×30m基地，98—96层30×25m房间，95层Boss区；门、地砖、墙和楼梯按组件坐标装配。</x:v>
+        <x:v>2026-08-02：99层楼梯间至基地西侧入口补齐15m模块化走廊，基地东侧出口至下层楼梯补齐20m模块化走廊；仅复用5m地砖/墙体组件，走廊外空间保持实体封闭；基地灯开关固定在西侧入口墙并离门4m。</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="132" customHeight="1">
@@ -12671,7 +12671,7 @@
         <x:v>程序生成Blender源集合</x:v>
       </x:c>
       <x:c r="X164" s="70" t="str">
-        <x:v>塔楼地砖统一低金属0.08/高粗糙0.90，降低太阳与室内灯高光；A/B双色交替保留；tests/verification/verify_tower_lighting_wall_combat_regressions.tscn</x:v>
+        <x:v>2026-08-02：复用于99层楼梯间—基地房间的15m/20m接驳走廊地面，继续遵守5m网格与不透明材质规范。</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="132" customHeight="1">
@@ -12745,7 +12745,7 @@
         <x:v>程序生成 Blender 源集合</x:v>
       </x:c>
       <x:c r="X165" s="70" t="str">
-        <x:v>v0.1：实墙、门墙与拐角统一0—9m；仅南侧朝北墙参与镜头交互。水平隔间南墙统一注册镜头墙；南侧门洞使用5×9m相机专用代理碰撞（layer16），开门后仍触发抬升/收镜，但代理不阻挡角色、怪物或子弹。镜头使用从角色前侧穿过角色的三条横向探针并允许内部起点命中；隐藏连接器不保留阻挡碰撞；A/B材质按网格交替。</x:v>
+        <x:v>2026-08-02：南北向水平共享墙统一注册相机抬升判定，楼梯南侧墙纳入同一规则；墙体始终不透明，取消运行时墙体透明度改写。</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="132" customHeight="1">
@@ -12893,7 +12893,7 @@
         <x:v>程序生成 Blender 源集合</x:v>
       </x:c>
       <x:c r="X167" s="70" t="str">
-        <x:v>v0.1：门墙保持5m模块坐标和9m总高；南侧门洞拥有独立5×9m相机专用代理碰撞（layer16），门扇开启或禁用实体碰撞时仍触发镜头抬升/收回。代理仅供相机探针查询，不参与角色、怪物、子弹或导航阻挡。</x:v>
+        <x:v>2026-08-02：南北门墙统一使用仅限相机层的门洞代理，开门不再全局绕过后墙检测；代理不阻挡玩家、怪物或子弹。</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="132" customHeight="1">
@@ -13039,13 +13039,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V169" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46236</x:v>
       </x:c>
       <x:c r="W169" s="70" t="str">
         <x:v>用户手工Blender模型</x:v>
       </x:c>
       <x:c r="X169" s="70" t="str">
-        <x:v>v0.1：继续复用用户v006楼顶特殊楼梯、加高墙体及常驻Walkable/EnclosureWall碰撞。楼顶纯黑问题确认为固定斜俯视镜头被门墙整段遮挡；现仅剖切遮挡角色的墙体渲染，并联动同方向5m墙段，物理碰撞、门和楼梯围护保持有效；天空反弹光降至1.25，仅补兼容渲染器缺少实时天空GI。</x:v>
+        <x:v>2026-08-02：楼梯间南侧围墙补齐相机抬升元数据；与99层基地之间使用5m地砖及墙体组件拼接可见封闭走廊。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13073,7 +13073,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc128da19cc44bf2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65ff60d9dcd649f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Recdf561dd38e4307"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R87b35accb2ff4162"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R12b2ef04f01e45c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rb92e61661b894992"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rd4ae00453da34079"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R3f397cfdc2384a4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Re66f83729f474423"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R8b883a573c824769"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R2e0966da1d6c4ef3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Ra3187969b8aa4319"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rb3b4612fb4c844d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Re827b1ebaf3847c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R9ac5c7846717426c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rea908fe98f294f53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Reffb2108cfe54994"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rf19968f8f8534dd5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9943,13 +9943,14 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V128" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46237</x:v>
       </x:c>
       <x:c r="W128" s="70" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X128" s="70" t="str">
-        <x:v>v0.1：房间灯统一覆盖环境layer1与角色layer2；普通房中央灯与基地四灯组各只保留一盏投影主灯，其余灯无阴影以控制预算。流送状态改为递归同步嵌套灯具，玩家与怪物均可在开灯房间产生投影。</x:v>
+        <x:v>v0.1：房间灯统一覆盖环境layer1与角色layer2；普通房中央灯与基地四灯组各只保留一盏投影主灯，其余灯无阴影以控制预算。流送状态改为递归同步嵌套灯具，玩家与怪物均可在开灯房间产生投影。
+2026-08-03：failing=false 稳定灯不进入慢波/微波亮度调制；房灯开关仅切换 0/配置能量并保留 Compatibility 渲染实例，固定机位初始开灯与复明后的地面采样一致。</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="34" customHeight="1">
@@ -10247,13 +10248,14 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V132" s="64" t="n">
-        <x:v>46224</x:v>
+        <x:v>46237</x:v>
       </x:c>
       <x:c r="W132" s="63" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X132" s="63" t="str">
-        <x:v>锁定/同步/取消/完成四段生命周期</x:v>
+        <x:v>锁定/同步/取消/完成四段生命周期
+2026-08-03：待机/锁定 STANDARD 信标局部光固定为 2.2；仅正式撤离倒计时允许能量脉冲，避免干扰基地房灯的地面反馈。</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="34" customHeight="1">
@@ -11073,13 +11075,14 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V143" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46237</x:v>
       </x:c>
       <x:c r="W143" s="70" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X143" s="70" t="str">
-        <x:v>v0.1：开关新增灯组控制，同一开关可统一切换多盏房间灯；基地四灯共用一个墙边开关并在快照中报告控制灯数量。单灯房继续兼容原接口。</x:v>
+        <x:v>v0.1：开关新增灯组控制，同一开关可统一切换多盏房间灯；基地四灯共用一个墙边开关并在快照中报告控制灯数量。单灯房继续兼容原接口。
+2026-08-03：基地四灯总开关不再移除 OmniLight3D 渲染实例；关灯能量归零，复明恢复配置能量、范围与阴影，真实 GPU 双区域像素差验收通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -12591,13 +12594,14 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V163" s="71" t="n">
-        <x:v>46236</x:v>
+        <x:v>46237</x:v>
       </x:c>
       <x:c r="W163" s="71" t="str">
         <x:v>程序生成 Blender 源集合</x:v>
       </x:c>
       <x:c r="X163" s="70" t="str">
-        <x:v>2026-08-02：99层楼梯间至基地西侧入口补齐15m模块化走廊，基地东侧出口至下层楼梯补齐20m模块化走廊；仅复用5m地砖/墙体组件，走廊外空间保持实体封闭；基地灯开关固定在西侧入口墙并离门4m。</x:v>
+        <x:v>2026-08-02：99层楼梯间至基地西侧入口补齐15m模块化走廊，基地东侧出口至下层楼梯补齐20m模块化走廊；仅复用5m地砖/墙体组件，走廊外空间保持实体封闭；基地灯开关固定在西侧入口墙并离门4m。
+2026-08-03：移除楼梯路径包围盒式不可见围护碰撞；98层安全房南向通道与99层基地入口北向通道通过无空气墙物理射线验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="132" customHeight="1">
@@ -12963,13 +12967,14 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V168" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46237</x:v>
       </x:c>
       <x:c r="W168" s="70" t="str">
         <x:v>用户手工Blender模型</x:v>
       </x:c>
       <x:c r="X168" s="70" t="str">
-        <x:v>v0.1：继续直接复用用户v006通用9m楼梯视觉与六块Walkable同形常驻碰撞；按5m世界矩形对齐250m整层中的四向楼梯洞口，可旋转通用。上下端门侧分别记录，避免楼梯开口朝向改变后沿用同一侧导致错位。</x:v>
+        <x:v>v0.1：继续直接复用用户v006通用9m楼梯视觉与六块Walkable同形常驻碰撞；按5m世界矩形对齐250m整层中的四向楼梯洞口，可旋转通用。上下端门侧分别记录，避免楼梯开口朝向改变后沿用同一侧导致错位。
+2026-08-03：四面围护墙全部直接从可视Mesh生成同形ConcavePolygon碰撞，碰撞不再越过楼梯接口伸入相邻房间。</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="132" customHeight="1">
@@ -13039,13 +13044,14 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V169" s="71" t="n">
-        <x:v>46236</x:v>
+        <x:v>46237</x:v>
       </x:c>
       <x:c r="W169" s="70" t="str">
         <x:v>用户手工Blender模型</x:v>
       </x:c>
       <x:c r="X169" s="70" t="str">
-        <x:v>2026-08-02：楼梯间南侧围墙补齐相机抬升元数据；与99层基地之间使用5m地砖及墙体组件拼接可见封闭走廊。</x:v>
+        <x:v>2026-08-02：楼梯间南侧围墙补齐相机抬升元数据；与99层基地之间使用5m地砖及墙体组件拼接可见封闭走廊。
+2026-08-03：四面围护墙全部直接从可视Mesh生成同形ConcavePolygon碰撞；南侧可视墙继续承担相机抬升判定。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13073,7 +13079,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65ff60d9dcd649f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cb35fb9dcc64cbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R2e0966da1d6c4ef3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Ra3187969b8aa4319"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rb3b4612fb4c844d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Re827b1ebaf3847c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R9ac5c7846717426c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rea908fe98f294f53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Reffb2108cfe54994"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rf19968f8f8534dd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re1c4750dddce4157"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R539f00cb558747e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Reb8a47642c0b4ff5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rcfa9c3631db84e8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R4c084c6dd44240fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb56ebbb0bf3b4b38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Ra77c69430f474a65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R833ffce7681d439a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -12601,7 +12601,9 @@
       </x:c>
       <x:c r="X163" s="70" t="str">
         <x:v>2026-08-02：99层楼梯间至基地西侧入口补齐15m模块化走廊，基地东侧出口至下层楼梯补齐20m模块化走廊；仅复用5m地砖/墙体组件，走廊外空间保持实体封闭；基地灯开关固定在西侧入口墙并离门4m。
-2026-08-03：移除楼梯路径包围盒式不可见围护碰撞；98层安全房南向通道与99层基地入口北向通道通过无空气墙物理射线验收。</x:v>
+2026-08-03：移除楼梯路径包围盒式不可见围护碰撞；98层安全房南向通道与99层基地入口北向通道通过无空气墙物理射线验收。
+2026-08-03：战斗层改为首触发整层冻结组件坐标、门轴、通道与上下楼梯接口；房间Mesh继续邻接流送。房间矩形、保守楼梯占位与真实导入楼梯Mesh三重验收为零重叠；98—96层主环/支路及95层Boss区已重排到5m网格安全区。
+2026-08-03：所有水平通道改为按真实门距计算N=长度/5m，动态复用N块地砖与左右各N块实墙；可视覆盖和双侧连续碰撞同长，完整塔楼流程节点数3063/预算3500。</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="132" customHeight="1">
@@ -12633,7 +12635,7 @@
         <x:v>godot_runtime</x:v>
       </x:c>
       <x:c r="J164" s="70" t="str">
-        <x:v>塔楼六个物理层楼板/335m MultiMesh网格</x:v>
+        <x:v>塔楼六个物理层楼板/335m MultiMesh网格/动态水平通道</x:v>
       </x:c>
       <x:c r="K164" s="70" t="str">
         <x:v>原型已接入</x:v>
@@ -12669,13 +12671,14 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V164" s="71" t="n">
-        <x:v>46236</x:v>
+        <x:v>46237</x:v>
       </x:c>
       <x:c r="W164" s="70" t="str">
         <x:v>程序生成Blender源集合</x:v>
       </x:c>
       <x:c r="X164" s="70" t="str">
-        <x:v>2026-08-02：复用于99层楼梯间—基地房间的15m/20m接驳走廊地面，继续遵守5m网格与不透明材质规范。</x:v>
+        <x:v>2026-08-02：复用于99层楼梯间—基地房间的15m/20m接驳走廊地面，继续遵守5m网格与不透明材质规范。
+2026-08-03：水平通道按每5m一块动态生成地砖实例；使用MultiMesh批量提交但保留逐格坐标，禁止拉伸单块Mesh代替模块拼接。</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="132" customHeight="1">
@@ -12743,13 +12746,16 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V165" s="71" t="n">
-        <x:v>46236</x:v>
+        <x:v>46237</x:v>
       </x:c>
       <x:c r="W165" s="70" t="str">
         <x:v>程序生成 Blender 源集合</x:v>
       </x:c>
       <x:c r="X165" s="70" t="str">
-        <x:v>2026-08-02：南北向水平共享墙统一注册相机抬升判定，楼梯南侧墙纳入同一规则；墙体始终不透明，取消运行时墙体透明度改写。</x:v>
+        <x:v>2026-08-02：南北向水平共享墙统一注册相机抬升判定，楼梯南侧墙纳入同一规则；墙体始终不透明，取消运行时墙体透明度改写。
+2026-08-03：东西向5m房间连接通道的无门南侧实墙增加独立camera_lower_wall碰撞标记；南北向通道的东/西墙保持不触发。真实98层侧门通道相机回归通过。
+2026-08-03：水平通道按每5m左右各一块动态生成9m实墙实例；墙体可视覆盖与连续碰撞严格等长，东西向通道南墙继续承担相机抬升判定。
+2026-08-03：动态水平通道按实墙Mesh包围盒底面自动贴合楼面；GLB几何保持Y=0..9m，可视原点不再误用碰撞盒4.5m中心。新增墙底高度与9m墙高自动回归。</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="132" customHeight="1">
@@ -12974,7 +12980,8 @@
       </x:c>
       <x:c r="X168" s="70" t="str">
         <x:v>v0.1：继续直接复用用户v006通用9m楼梯视觉与六块Walkable同形常驻碰撞；按5m世界矩形对齐250m整层中的四向楼梯洞口，可旋转通用。上下端门侧分别记录，避免楼梯开口朝向改变后沿用同一侧导致错位。
-2026-08-03：四面围护墙全部直接从可视Mesh生成同形ConcavePolygon碰撞，碰撞不再越过楼梯接口伸入相邻房间。</x:v>
+2026-08-03：四面围护墙全部直接从可视Mesh生成同形ConcavePolygon碰撞，碰撞不再越过楼梯接口伸入相邻房间。
+2026-08-03：整层布局把楼梯折返空间登记为排他占位，并用导入Mesh世界AABB复核非接口房间；随机支路、普通房和Boss区不得侵入。</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="132" customHeight="1">
@@ -13079,7 +13086,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cb35fb9dcc64cbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde612d2613ce4ab3"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re1c4750dddce4157"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R539f00cb558747e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Reb8a47642c0b4ff5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rcfa9c3631db84e8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R4c084c6dd44240fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb56ebbb0bf3b4b38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Ra77c69430f474a65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R833ffce7681d439a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb891d57361b143fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rf0bfffabc55d4391"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R1265a59f80ae4cce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rc3ebc3e777444b5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rcb04521b862e4d84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R37afdea5f1b4426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R263ba332a8f5418a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rbee54b4adc664436"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11158,7 +11158,8 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X144" t="str">
-        <x:v>v0.1：ForwardBeam仅照环境layer1，shadow_caster_mask也仅包含layer1，明确排除玩家、穿戴物与手持枪layer2；AvatarFrontFill无阴影。玩家网格保留cast_shadow=ON，由太阳和室内灯产生外部投影；准星禁用投影。曝光预算固定为主聚光7.2、环境溢光0.7、角色柔光2.8，并通过真实渲染验收。</x:v>
+        <x:v>v0.1：ForwardBeam仅照环境layer1，shadow_caster_mask也仅包含layer1，明确排除玩家、穿戴物与手持枪layer2；AvatarFrontFill无阴影。玩家网格保留cast_shadow=ON，由太阳和室内灯产生外部投影；准星禁用投影。曝光预算固定为主聚光7.2、环境溢光0.7、角色柔光2.8，并通过真实渲染验收。
+2026-08-03：主聚光保持能量7.2/范围25m/角度66°与环境层隔离；Compatibility阴影采样固定 bias=0.18、normal_bias=1.6、blur=1.2，消除远处斜角墙面横纹，不改变玩家自身不投影契约；已通过近25m真GPU画面验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -12603,7 +12604,8 @@
         <x:v>2026-08-02：99层楼梯间至基地西侧入口补齐15m模块化走廊，基地东侧出口至下层楼梯补齐20m模块化走廊；仅复用5m地砖/墙体组件，走廊外空间保持实体封闭；基地灯开关固定在西侧入口墙并离门4m。
 2026-08-03：移除楼梯路径包围盒式不可见围护碰撞；98层安全房南向通道与99层基地入口北向通道通过无空气墙物理射线验收。
 2026-08-03：战斗层改为首触发整层冻结组件坐标、门轴、通道与上下楼梯接口；房间Mesh继续邻接流送。房间矩形、保守楼梯占位与真实导入楼梯Mesh三重验收为零重叠；98—96层主环/支路及95层Boss区已重排到5m网格安全区。
-2026-08-03：所有水平通道改为按真实门距计算N=长度/5m，动态复用N块地砖与左右各N块实墙；可视覆盖和双侧连续碰撞同长，完整塔楼流程节点数3063/预算3500。</x:v>
+2026-08-03：所有水平通道改为按真实门距计算N=长度/5m，动态复用N块地砖与左右各N块实墙；可视覆盖和双侧连续碰撞同长，完整塔楼流程节点数3063/预算3500。
+2026-08-03：已开门邻房在房间显现时创建首波敌人，进房前仅暂停物理AI且保留视野/遮挡判定资格；进房激活同一instance ID，不重复生成，不扩大21m可见规则。</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="132" customHeight="1">
@@ -13086,7 +13088,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde612d2613ce4ab3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R515bb317b86c414c"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb891d57361b143fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rf0bfffabc55d4391"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R1265a59f80ae4cce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rc3ebc3e777444b5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rcb04521b862e4d84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R37afdea5f1b4426b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R263ba332a8f5418a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rbee54b4adc664436"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb903f49eae684872"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R189a5e59c0cd4f57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rce3b2737aa7b4110"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R3903b8a6eedd45f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R742c45ab38904062"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R6fedb916435a41b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R8b6b8c4ff131414a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R45f35b754aad4bd2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8799,7 +8799,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T113" s="70" t="str">
-        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+        <x:v>cf0b3b648d56590f1e024553d224df35007358452ea16ad1651ae9af4a7dde49</x:v>
       </x:c>
       <x:c r="U113" s="70" t="str">
         <x:v>Codex</x:v>
@@ -8875,7 +8875,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T114" t="str">
-        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+        <x:v>cf0b3b648d56590f1e024553d224df35007358452ea16ad1651ae9af4a7dde49</x:v>
       </x:c>
       <x:c r="U114" t="str">
         <x:v>Codex</x:v>
@@ -8951,7 +8951,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T115" t="str">
-        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+        <x:v>cf0b3b648d56590f1e024553d224df35007358452ea16ad1651ae9af4a7dde49</x:v>
       </x:c>
       <x:c r="U115" t="str">
         <x:v>Codex</x:v>
@@ -9027,7 +9027,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T116" t="str">
-        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+        <x:v>cf0b3b648d56590f1e024553d224df35007358452ea16ad1651ae9af4a7dde49</x:v>
       </x:c>
       <x:c r="U116" t="str">
         <x:v>Codex</x:v>
@@ -9103,7 +9103,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T117" t="str">
-        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+        <x:v>cf0b3b648d56590f1e024553d224df35007358452ea16ad1651ae9af4a7dde49</x:v>
       </x:c>
       <x:c r="U117" t="str">
         <x:v>Codex</x:v>
@@ -9179,7 +9179,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T118" t="str">
-        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+        <x:v>cf0b3b648d56590f1e024553d224df35007358452ea16ad1651ae9af4a7dde49</x:v>
       </x:c>
       <x:c r="U118" t="str">
         <x:v>Codex</x:v>
@@ -9191,7 +9191,7 @@
         <x:v>原创逻辑挂点</x:v>
       </x:c>
       <x:c r="X118" t="str">
-        <x:v>VisualRoot/WeaponSocket：(0.60,1.15,-0.42)，与唯一手固定相对向量；v0.1方形猫原型；tests/verification/verify_player3d_diy_flow / gallery flow / visual PASS</x:v>
+        <x:v>VisualRoot/WeaponSocket：(0.60,1.15,-0.42)，与唯一手固定相对向量；v0.1方形猫原型；tests/verification/verify_player3d_diy_flow / gallery flow / visual PASS ｜ 2026-08-06：复用本AssetID扩展主/副武器背部语义挂点；主武器槽0在左、副武器槽1在右，枪模local -Z枪口轴统一转向世界下方；verify_dual_weapon_quick_map_fate_flow / verify_player3d_weapon_grip_visual PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -11679,7 +11679,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T151" s="63" t="str">
-        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+        <x:v>cf0b3b648d56590f1e024553d224df35007358452ea16ad1651ae9af4a7dde49</x:v>
       </x:c>
       <x:c r="U151" s="63" t="str">
         <x:v>Codex</x:v>
@@ -11755,7 +11755,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T152" s="63" t="str">
-        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+        <x:v>cf0b3b648d56590f1e024553d224df35007358452ea16ad1651ae9af4a7dde49</x:v>
       </x:c>
       <x:c r="U152" s="63" t="str">
         <x:v>Codex</x:v>
@@ -11831,7 +11831,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T153" s="63" t="str">
-        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+        <x:v>cf0b3b648d56590f1e024553d224df35007358452ea16ad1651ae9af4a7dde49</x:v>
       </x:c>
       <x:c r="U153" s="63" t="str">
         <x:v>Codex</x:v>
@@ -11907,7 +11907,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T154" s="63" t="str">
-        <x:v>0a15194d68ecc0490ecd3910d2e51901a006ec6ac28e093e2aba48c6f67fec64</x:v>
+        <x:v>cf0b3b648d56590f1e024553d224df35007358452ea16ad1651ae9af4a7dde49</x:v>
       </x:c>
       <x:c r="U154" s="63" t="str">
         <x:v>Codex</x:v>
@@ -12059,7 +12059,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T156" s="70" t="str">
-        <x:v>b88839fbe76eedddd48933ac1807867e7a4efbd683de36475215679d26e84998</x:v>
+        <x:v>3aeed15ba17514e5e92ddda3b7303f9f29f576abe826d3039a7b8fc080c320bb</x:v>
       </x:c>
       <x:c r="U156" s="70" t="str">
         <x:v>Codex</x:v>
@@ -13088,7 +13088,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R515bb317b86c414c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77a69cc18bf84bde"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14594,6 +14594,88 @@
       </x:c>
       <x:c r="M39" s="70" t="str">
         <x:v>Blender原点：脚底中心；静态最低点Y=0；v0.1复用同一v006网格增加下落与落地程序动作。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>weapon_stow_primary</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>VisualRoot/BunnyRig/StowedWeaponSocketPrimary</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>无纹理</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>Marker3D</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>(-0.42,1.12,0.25)</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>随root；local -Z枪口轴转向世界下方</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>主武器未激活时背部左侧收纳</x:v>
+      </x:c>
+      <x:c r="K40" t="str">
+        <x:v>武器系统</x:v>
+      </x:c>
+      <x:c r="L40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>主武器槽0专属；枪口朝下；回退节点VisualRoot/StowedWeaponSocketPrimary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>weapon_stow_secondary</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>VisualRoot/BunnyRig/StowedWeaponSocketSecondary</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>无纹理</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>Marker3D</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>(0.42,1.12,0.25)</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>随root；local -Z枪口轴转向世界下方</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>副武器未激活时背部右侧收纳</x:v>
+      </x:c>
+      <x:c r="K41" t="str">
+        <x:v>武器系统</x:v>
+      </x:c>
+      <x:c r="L41" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M41" t="str">
+        <x:v>副武器槽1专属；枪口朝下；回退节点VisualRoot/StowedWeaponSocketSecondary</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -17116,13 +17198,27 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7"/>
-      <x:c r="B7"/>
-      <x:c r="C7"/>
-      <x:c r="D7"/>
-      <x:c r="E7"/>
-      <x:c r="F7"/>
-      <x:c r="G7"/>
+      <x:c r="A7" t="str">
+        <x:v>v0.1.1</x:v>
+      </x:c>
+      <x:c r="B7" s="62" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>角色武器表现调整</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>新增主左/副右背部收纳挂点，枪口统一朝下；复用既有武器模型与AssetID。</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>不改武器实例、碰撞、伤害或切枪规则。</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb903f49eae684872"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R189a5e59c0cd4f57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rce3b2737aa7b4110"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R3903b8a6eedd45f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R742c45ab38904062"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R6fedb916435a41b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R8b6b8c4ff131414a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R45f35b754aad4bd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R75d4eac042494d63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rffc421c440ba4260"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R38cb38a55a0043b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rb5585ae8e5354959"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R6d0966278a3d49dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R4461a72bf5304843"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Ra5ec9800d3be472b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R9e7e2e12ebc346cd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -932,22 +932,22 @@
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="45" t="n">
         <x:f>COUNTA('资产主表'!$A$6:$A$205)</x:f>
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B6" s="43"/>
       <x:c r="C6" s="45" t="n">
         <x:f>COUNTIF('资产主表'!$K$6:$K$205,"已完成")+COUNTIF('资产主表'!$K$6:$K$205,"原型已接入")</x:f>
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
         <x:f>COUNTIF('资产主表'!$K$6:$K$205,"待制作")+COUNTIF('资产主表'!$K$6:$K$205,"程序占位")</x:f>
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F6" s="43"/>
       <x:c r="G6" s="45" t="n">
         <x:f>COUNTIF('资产主表'!$S$6:$S$205,"重复")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="43"/>
       <x:c r="I6" s="46" t="str">
@@ -1007,11 +1007,11 @@
       </x:c>
       <x:c r="B10" s="50" t="n">
         <x:f>COUNTIF('资产主表'!$C$6:$C$205,A10)</x:f>
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="50" t="n">
         <x:f>COUNTIFS('资产主表'!$C$6:$C$205,A10,'资产主表'!$K$6:$K$205,"已完成")+COUNTIFS('资产主表'!$C$6:$C$205,A10,'资产主表'!$K$6:$K$205,"原型已接入")</x:f>
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="43"/>
       <x:c r="E10" s="51" t="str">
@@ -1085,7 +1085,7 @@
       </x:c>
       <x:c r="B13" s="52" t="n">
         <x:f>COUNTIF('资产主表'!$C$6:$C$205,A13)</x:f>
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C13" s="52" t="n">
         <x:f>COUNTIFS('资产主表'!$C$6:$C$205,A13,'资产主表'!$K$6:$K$205,"已完成")+COUNTIFS('资产主表'!$C$6:$C$205,A13,'资产主表'!$K$6:$K$205,"原型已接入")</x:f>
@@ -13044,7 +13044,7 @@
       </x:c>
       <x:c r="S169" s="70" t="str">
         <x:f>IF(COUNTIF($R:$R,R169)&gt;1,"重复","唯一")</x:f>
-        <x:v>唯一</x:v>
+        <x:v>重复</x:v>
       </x:c>
       <x:c r="T169" s="70" t="str">
         <x:v>88198a579cc846974f17f5203b46b568b7ab2421fd7bb63c0b7868ddd05684a2</x:v>
@@ -13061,6 +13061,150 @@
       <x:c r="X169" s="70" t="str">
         <x:v>2026-08-02：楼梯间南侧围墙补齐相机抬升元数据；与99层基地之间使用5m地砖及墙体组件拼接可见封闭走廊。
 2026-08-03：四面围护墙全部直接从可视Mesh生成同形ConcavePolygon碰撞；南侧可视墙继续承担相机抬升判定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" t="str">
+        <x:v>CHR-PLY-CAPSULE01-BACKPACK-SOCKET-3D</x:v>
+      </x:c>
+      <x:c r="B170" t="str">
+        <x:v>玩家背包装备挂点</x:v>
+      </x:c>
+      <x:c r="C170" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D170" t="str">
+        <x:v>player_accessory_socket</x:v>
+      </x:c>
+      <x:c r="E170" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F170" t="str">
+        <x:v>backpack_socket_3d</x:v>
+      </x:c>
+      <x:c r="G170" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D</x:v>
+      </x:c>
+      <x:c r="H170" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I170" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J170" t="str">
+        <x:v>3D玩家场景/可装备背包</x:v>
+      </x:c>
+      <x:c r="K170" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L170" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M170" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N170" t="str">
+        <x:v>Marker3D；bunny=(0,0.74,0.30)；fallback=(0,1.25,0.48)</x:v>
+      </x:c>
+      <x:c r="O170" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v006.tscn</x:v>
+      </x:c>
+      <x:c r="P170" t="str">
+        <x:v>src/player3d/PlayerAvatar3D.gd; tests/verification/verify_backpack_equipment_flow.tscn</x:v>
+      </x:c>
+      <x:c r="Q170" t="str">
+        <x:v>背包挂点;BackpackSocket;背部装备;wearable;capacity</x:v>
+      </x:c>
+      <x:c r="R170" t="str">
+        <x:f>LOWER(TRIM(C170)&amp;"|"&amp;TRIM(D170)&amp;"|"&amp;TRIM(E170)&amp;"|"&amp;TRIM(F170)&amp;"|"&amp;TRIM(H170)&amp;"|"&amp;TRIM(I170))</x:f>
+        <x:v>角色|player_accessory_socket|player_capsule01|backpack_socket_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S170" t="str">
+        <x:f>IF(COUNTIF($R:$R,R170)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T170"/>
+      <x:c r="U170" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V170" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W170" t="str">
+        <x:v>原创程序挂点</x:v>
+      </x:c>
+      <x:c r="X170" t="str">
+        <x:v>独立于左右武器收纳挂点；只承载表现，不改变角色碰撞。装备/卸下由backpack_equipment_changed同步；专项与Metal/OpenGL战术背包画面通过。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" t="str">
+        <x:v>ITM-EQUIPMENT-BACKPACK-3D</x:v>
+      </x:c>
+      <x:c r="B171" t="str">
+        <x:v>可装备背包3D占位模型</x:v>
+      </x:c>
+      <x:c r="C171" t="str">
+        <x:v>道具</x:v>
+      </x:c>
+      <x:c r="D171" t="str">
+        <x:v>equipment</x:v>
+      </x:c>
+      <x:c r="E171" t="str">
+        <x:v>equipment_backpack</x:v>
+      </x:c>
+      <x:c r="F171" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G171"/>
+      <x:c r="H171" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I171" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J171" t="str">
+        <x:v>地面拾取/UI图标/角色背部共用</x:v>
+      </x:c>
+      <x:c r="K171" t="str">
+        <x:v>程序占位</x:v>
+      </x:c>
+      <x:c r="L171" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M171" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N171" t="str">
+        <x:v>BoxMesh组件；2/4/8格三档体积、主色与1/2/3附袋</x:v>
+      </x:c>
+      <x:c r="O171"/>
+      <x:c r="P171" t="str">
+        <x:v>src/world3d/ItemModelFactory3D.gd; src/base/ItemRegistry.gd; tests/verification/verify_backpack_equipment_flow.tscn</x:v>
+      </x:c>
+      <x:c r="Q171" t="str">
+        <x:v>轻型腰包;战术背包;远征背包;backpack;2格;4格;8格</x:v>
+      </x:c>
+      <x:c r="R171" t="str">
+        <x:f>LOWER(TRIM(C171)&amp;"|"&amp;TRIM(D171)&amp;"|"&amp;TRIM(E171)&amp;"|"&amp;TRIM(F171)&amp;"|"&amp;TRIM(H171)&amp;"|"&amp;TRIM(I171))</x:f>
+        <x:v>道具|equipment|equipment_backpack|root_3d|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S171" t="str">
+        <x:f>IF(COUNTIF($R:$R,R171)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T171"/>
+      <x:c r="U171" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V171" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W171" t="str">
+        <x:v>原创程序几何</x:v>
+      </x:c>
+      <x:c r="X171" t="str">
+        <x:v>同一模型工厂服务equipment_backpack_2/4/8，避免世界物、UI图标和背部表现重复资产；无玩法碰撞，正式模型完成前保持程序占位状态。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13088,7 +13232,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77a69cc18bf84bde"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R559a8883ce7d4927"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14676,6 +14820,47 @@
       </x:c>
       <x:c r="M41" t="str">
         <x:v>副武器槽1专属；枪口朝下；回退节点VisualRoot/StowedWeaponSocketSecondary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>player_capsule01_3d</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>backpack_socket</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>VisualRoot/BunnyRig/BackpackSocket（fallback: VisualRoot/BackpackSocket）</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>无纹理；子模型来自ItemModelFactory3D</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>Marker3D + 程序Mesh</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>bunny (0,0.74,0.30)；fallback (0,1.25,0.48)</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>继承VisualRoot朝向</x:v>
+      </x:c>
+      <x:c r="I42" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>装备时生成背包占位Mesh；卸下时移除</x:v>
+      </x:c>
+      <x:c r="K42" t="str">
+        <x:v>背包装备系统</x:v>
+      </x:c>
+      <x:c r="L42" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>与StowedWeaponSocketPrimary/Secondary分离；2/4/8格共用模型工厂；无碰撞；verify_backpack_equipment_flow与Metal/OpenGL实机渲染通过。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R75d4eac042494d63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rffc421c440ba4260"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R38cb38a55a0043b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rb5585ae8e5354959"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R6d0966278a3d49dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R4461a72bf5304843"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Ra5ec9800d3be472b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R9e7e2e12ebc346cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R456445caedda4b33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rf8a96cdab32843ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rec49a9ae1aa94645"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rd3e68439d7114a4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R34dcc169b3e0480d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rd8c1759590d04f83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R5d6edb9fe09c46a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R7ee6e7fe10f94022"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="23">
+  <x:fonts count="26">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -156,8 +156,25 @@
       <x:color rgb="FFE2F8FF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF15383E"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17563A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF15383E"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="24">
+  <x:fills count="28">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -274,8 +291,28 @@
         <x:fgColor rgb="FF246583"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE4F2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD7EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE4F2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD7EEE5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="6">
+  <x:borders count="8">
     <x:border/>
     <x:border>
       <x:left style="medium">
@@ -320,11 +357,39 @@
         <x:color rgb="FFB9CBD2"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFAFC9CD"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFAFC9CD"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAFC9CD"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFAFC9CD"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF8FC3A1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF8FC3A1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF8FC3A1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF8FC3A1"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="109">
+  <x:cellXfs count="124">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -567,6 +632,45 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="23" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="25" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="26" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="26" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="27" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="27" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="27" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -932,12 +1036,12 @@
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="45" t="n">
         <x:f>COUNTA('资产主表'!$A$6:$A$205)</x:f>
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B6" s="43"/>
       <x:c r="C6" s="45" t="n">
         <x:f>COUNTIF('资产主表'!$K$6:$K$205,"已完成")+COUNTIF('资产主表'!$K$6:$K$205,"原型已接入")</x:f>
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
@@ -947,7 +1051,7 @@
       <x:c r="F6" s="43"/>
       <x:c r="G6" s="45" t="n">
         <x:f>COUNTIF('资产主表'!$S$6:$S$205,"重复")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="43"/>
       <x:c r="I6" s="46" t="str">
@@ -1157,11 +1261,11 @@
       </x:c>
       <x:c r="B16" s="52" t="n">
         <x:f>COUNTIF('资产主表'!$C$6:$C$205,A16)</x:f>
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="52" t="n">
         <x:f>COUNTIFS('资产主表'!$C$6:$C$205,A16,'资产主表'!$K$6:$K$205,"已完成")+COUNTIFS('资产主表'!$C$6:$C$205,A16,'资产主表'!$K$6:$K$205,"原型已接入")</x:f>
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D16" s="43"/>
       <x:c r="E16" s="43"/>
@@ -9299,7 +9403,7 @@
         <x:v>default</x:v>
       </x:c>
       <x:c r="J120" s="70" t="str">
-        <x:v>8类基地设施</x:v>
+        <x:v>8类基地设施/统一状态牌</x:v>
       </x:c>
       <x:c r="K120" s="70" t="str">
         <x:v>原型已接入</x:v>
@@ -9311,16 +9415,16 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="N120" s="70" t="str">
-        <x:v>PackedScene/材质变体</x:v>
+        <x:v>PackedScene/材质变体/名称与实时摘要共用Label3D</x:v>
       </x:c>
       <x:c r="O120" s="70" t="str">
         <x:v>assets/art/props/base_world_3d/prp_base_facility_root_top3d_v001.tscn</x:v>
       </x:c>
       <x:c r="P120" s="70" t="str">
-        <x:v>src/base3d/BaseFacility3D.gd</x:v>
+        <x:v>src/base3d/BaseFacility3D.gd; src/base/BaseFacilityCatalog.gd; src/base/BaseFacilityService.gd; src/world3d/TowerDescent3D.gd; tests/verification/verify_base_facility_framework.tscn; tests/verification/verify_base_world_3d_visual.tscn</x:v>
       </x:c>
       <x:c r="Q120" s="70" t="str">
-        <x:v>设施;交互;信标;3D</x:v>
+        <x:v>设施;交互;信标;3D;facility_id;实时摘要;状态牌;共享目录</x:v>
       </x:c>
       <x:c r="R120" s="70" t="str">
         <x:f>LOWER(TRIM(C120)&amp;"|"&amp;TRIM(D120)&amp;"|"&amp;TRIM(E120)&amp;"|"&amp;TRIM(F120)&amp;"|"&amp;TRIM(H120)&amp;"|"&amp;TRIM(I120))</x:f>
@@ -9337,13 +9441,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V120" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46240</x:v>
       </x:c>
       <x:c r="W120" s="70" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X120" s="70" t="str">
-        <x:v>v0.1：BaseFacility3D复用于五个独立电梯设施（99—95层各一处），设施挂在走廊设施层级而非房间内部，放置在基地房间墙边或楼层走廊边。电梯解锁、目标楼层和到达点从邻接的elevator_access房间读取。</x:v>
+        <x:v>2026-08-06：确认该根资产服务正式基地8项设施；颜色材质、名称、交互提示与实时摘要均由稳定facility_id驱动，基地大世界与塔内99层同类设施共用。复用原NameLabel显示名称+状态，不增加节点和碰撞；注意态为金色、正常态为青绿色、不可用态为红色。管理终端与3D设施读取同一快照；Metal/OpenGL 1280×720基地和终端画面验收通过。塔楼电梯只复用外壳，保持独立交通身份。</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -13044,7 +13148,7 @@
       </x:c>
       <x:c r="S169" s="70" t="str">
         <x:f>IF(COUNTIF($R:$R,R169)&gt;1,"重复","唯一")</x:f>
-        <x:v>重复</x:v>
+        <x:v>唯一</x:v>
       </x:c>
       <x:c r="T169" s="70" t="str">
         <x:v>88198a579cc846974f17f5203b46b568b7ab2421fd7bb63c0b7868ddd05684a2</x:v>
@@ -13205,6 +13309,154 @@
       </x:c>
       <x:c r="X171" t="str">
         <x:v>同一模型工厂服务equipment_backpack_2/4/8，避免世界物、UI图标和背部表现重复资产；无玩法碰撞，正式模型完成前保持程序占位状态。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="42" customHeight="1">
+      <x:c r="A172" s="123" t="str">
+        <x:v>PRP-BASE-VENDING-MACHINE-3D</x:v>
+      </x:c>
+      <x:c r="B172" s="118" t="str">
+        <x:v>基地自动贩卖机长方体模型</x:v>
+      </x:c>
+      <x:c r="C172" s="118" t="str">
+        <x:v>3D道具</x:v>
+      </x:c>
+      <x:c r="D172" s="118" t="str">
+        <x:v>base_facility</x:v>
+      </x:c>
+      <x:c r="E172" s="118" t="str">
+        <x:v>base_vending</x:v>
+      </x:c>
+      <x:c r="F172" s="118" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="G172" s="118" t="str">
+        <x:v>PRP-BASE-FACILITY-3D</x:v>
+      </x:c>
+      <x:c r="H172" s="118" t="str">
+        <x:v>Top3D</x:v>
+      </x:c>
+      <x:c r="I172" s="118" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J172" s="118" t="str">
+        <x:v>BaseWorld3D/TowerDescent99F</x:v>
+      </x:c>
+      <x:c r="K172" s="118" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L172" s="118" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M172" s="118" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N172" s="118" t="str">
+        <x:v>2.5×3.35×1.35m</x:v>
+      </x:c>
+      <x:c r="O172" s="118" t="str">
+        <x:v>assets/art/props/base_world_3d/prp_base_vending_machine_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P172" s="118" t="str">
+        <x:v>用户设计+docs/v0.1/07_技术施工_基地设施.md</x:v>
+      </x:c>
+      <x:c r="Q172" s="118" t="str">
+        <x:v>自动贩卖机; 长方体; 基地; 出口墙边</x:v>
+      </x:c>
+      <x:c r="R172" s="118" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C172,D172,E172,F172,H172,I172)</x:f>
+        <x:v>3D道具|base_facility|base_vending|root|Top3D|default</x:v>
+      </x:c>
+      <x:c r="S172" s="118" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$200,R172)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T172" s="118"/>
+      <x:c r="U172" s="118" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V172" s="118" t="str">
+        <x:v>2026-08-06</x:v>
+      </x:c>
+      <x:c r="W172" s="118" t="str">
+        <x:v>程序基础网格/原创</x:v>
+      </x:c>
+      <x:c r="X172" s="118" t="str">
+        <x:v>代码网格与材质，无图片；独立碰撞、正面货窗、屏幕、灯带和交互区</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="42" customHeight="1">
+      <x:c r="A173" s="123" t="str">
+        <x:v>UI-SCREEN-BASE-VENDING</x:v>
+      </x:c>
+      <x:c r="B173" s="118" t="str">
+        <x:v>基地自动贩卖机商店界面</x:v>
+      </x:c>
+      <x:c r="C173" s="118" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="D173" s="118" t="str">
+        <x:v>base_facility</x:v>
+      </x:c>
+      <x:c r="E173" s="118" t="str">
+        <x:v>base_vending_shop</x:v>
+      </x:c>
+      <x:c r="F173" s="118" t="str">
+        <x:v>screen</x:v>
+      </x:c>
+      <x:c r="G173" s="118" t="str">
+        <x:v>UI-SCREEN-MERCHANT</x:v>
+      </x:c>
+      <x:c r="H173" s="118" t="str">
+        <x:v>Screen</x:v>
+      </x:c>
+      <x:c r="I173" s="118" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J173" s="118" t="str">
+        <x:v>基地自动贩卖机</x:v>
+      </x:c>
+      <x:c r="K173" s="118" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L173" s="118" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M173" s="118" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N173" s="118" t="str">
+        <x:v>1280×720自适应</x:v>
+      </x:c>
+      <x:c r="O173" s="118" t="str">
+        <x:v>scenes/BaseVendingMenu.tscn; src/ui/BaseVendingMenu.gd</x:v>
+      </x:c>
+      <x:c r="P173" s="118" t="str">
+        <x:v>用户设计+docs/v0.1/07_技术施工_基地设施.md</x:v>
+      </x:c>
+      <x:c r="Q173" s="118" t="str">
+        <x:v>基地商店; 购买; 出售; 3D物品图标</x:v>
+      </x:c>
+      <x:c r="R173" s="118" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C173,D173,E173,F173,H173,I173)</x:f>
+        <x:v>UI|base_facility|base_vending_shop|screen|Screen|default</x:v>
+      </x:c>
+      <x:c r="S173" s="118" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$200,R173)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T173" s="118"/>
+      <x:c r="U173" s="118" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V173" s="118" t="str">
+        <x:v>2026-08-06</x:v>
+      </x:c>
+      <x:c r="W173" s="118" t="str">
+        <x:v>程序控件/原创</x:v>
+      </x:c>
+      <x:c r="X173" s="118" t="str">
+        <x:v>左右买卖双栏；复用ItemModelIcon3D；资源与容量常驻；Esc退出</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13232,7 +13484,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R559a8883ce7d4927"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd19abecd5a6b443e"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R456445caedda4b33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rf8a96cdab32843ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rec49a9ae1aa94645"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rd3e68439d7114a4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R34dcc169b3e0480d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rd8c1759590d04f83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R5d6edb9fe09c46a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R7ee6e7fe10f94022"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0551494b974f4ac6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R1c003ec036f64218"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rb22758f0ce214e86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R7a7260dbbd2f4e5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rd9c3cd43d45f4cf7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R0ec45979b76c47ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R75e66154a0234179"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rb32e9d61309f4aba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1036,12 +1036,12 @@
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="45" t="n">
         <x:f>COUNTA('资产主表'!$A$6:$A$205)</x:f>
-        <x:v>168</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B6" s="43"/>
       <x:c r="C6" s="45" t="n">
         <x:f>COUNTIF('资产主表'!$K$6:$K$205,"已完成")+COUNTIF('资产主表'!$K$6:$K$205,"原型已接入")</x:f>
-        <x:v>72</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
@@ -1301,11 +1301,11 @@
       </x:c>
       <x:c r="B18" s="52" t="n">
         <x:f>COUNTIF('资产主表'!$C$6:$C$205,A18)</x:f>
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C18" s="52" t="n">
         <x:f>COUNTIFS('资产主表'!$C$6:$C$205,A18,'资产主表'!$K$6:$K$205,"已完成")+COUNTIFS('资产主表'!$C$6:$C$205,A18,'资产主表'!$K$6:$K$205,"原型已接入")</x:f>
-        <x:v>1</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D18" s="43"/>
       <x:c r="E18" s="43"/>
@@ -11000,7 +11000,7 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="M141" t="str">
-        <x:v>v001</x:v>
+        <x:v>v002</x:v>
       </x:c>
       <x:c r="N141" t="str">
         <x:v>全屏Control/12+2槽/96×96投影</x:v>
@@ -11035,7 +11035,7 @@
         <x:v>原创程序UI</x:v>
       </x:c>
       <x:c r="X141" t="str">
-        <x:v>复用背包根身份的3D子变体；I/Tab；打开时锁输入；道具共用 ItemModelFactory3D；实际 ItemSlot 信号完成换枪</x:v>
+        <x:v>复用背包根身份的3D子变体；I/Tab；打开时锁输入；道具共用 ItemModelFactory3D；实际 ItemSlot 信号完成换枪 ｜ 2026-08-07：左角色装备/右包裹网格；主副武器、背包装备、快捷物、物品与保险格统一正方形图标；深蓝黑+霓虹青+生命红语言。</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -13423,7 +13423,7 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="M173" s="118" t="str">
-        <x:v>v001</x:v>
+        <x:v>v002</x:v>
       </x:c>
       <x:c r="N173" s="118" t="str">
         <x:v>1280×720自适应</x:v>
@@ -13456,7 +13456,2301 @@
         <x:v>程序控件/原创</x:v>
       </x:c>
       <x:c r="X173" s="118" t="str">
-        <x:v>左右买卖双栏；复用ItemModelIcon3D；资源与容量常驻；Esc退出</x:v>
+        <x:v>左右买卖双栏；复用ItemModelIcon3D；资源与容量常驻；Esc退出 ｜ 2026-08-07：购买/出售改为3列商品卡网格，正方形ItemModelIcon3D，与I键背包同源；统一主HUD配色和按钮状态。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="44" customHeight="1">
+      <x:c r="A174" s="63" t="str">
+        <x:v>AUD-SFX-AMMO-EMPTY</x:v>
+      </x:c>
+      <x:c r="B174" s="63" t="str">
+        <x:v>空仓扳机音效</x:v>
+      </x:c>
+      <x:c r="C174" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D174" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E174" s="63" t="str">
+        <x:v>ammo_empty</x:v>
+      </x:c>
+      <x:c r="F174" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G174" s="63"/>
+      <x:c r="H174" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I174" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J174" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K174" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L174" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M174" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N174" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O174" s="63" t="str">
+        <x:v>src/assets/audio/sfx/ammo_empty_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P174" s="63" t="str">
+        <x:v>src/assets/audio/sfx/ammo_empty.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q174" s="63" t="str">
+        <x:v>ammo_empty; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R174" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C174,D174,E174,F174,H174,I174)</x:f>
+        <x:v>音频|sfx|ammo_empty|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S174" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R174)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T174" s="63" t="str">
+        <x:v>f5d0339c3c7fce8227970163bd773a11f15faffa57a878ec41111308657a000c</x:v>
+      </x:c>
+      <x:c r="U174" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V174" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W174" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X174" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=ammo_empty；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="44" customHeight="1">
+      <x:c r="A175" s="63" t="str">
+        <x:v>AUD-SFX-BOSS-DEFEAT</x:v>
+      </x:c>
+      <x:c r="B175" s="63" t="str">
+        <x:v>Boss击败音效</x:v>
+      </x:c>
+      <x:c r="C175" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D175" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E175" s="63" t="str">
+        <x:v>boss_defeat</x:v>
+      </x:c>
+      <x:c r="F175" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G175" s="63"/>
+      <x:c r="H175" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I175" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J175" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K175" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L175" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M175" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N175" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O175" s="63" t="str">
+        <x:v>src/assets/audio/sfx/boss_defeat_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P175" s="63" t="str">
+        <x:v>src/assets/audio/sfx/boss_defeat.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q175" s="63" t="str">
+        <x:v>boss_defeat; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R175" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C175,D175,E175,F175,H175,I175)</x:f>
+        <x:v>音频|sfx|boss_defeat|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S175" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R175)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T175" s="63" t="str">
+        <x:v>245b27a482a9166c6bc09cdabae3094f4a2bb1e67956f8a8f54b767eb15fefba</x:v>
+      </x:c>
+      <x:c r="U175" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V175" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W175" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X175" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=boss_defeat；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="44" customHeight="1">
+      <x:c r="A176" s="63" t="str">
+        <x:v>AUD-SFX-BOSS-INTRO</x:v>
+      </x:c>
+      <x:c r="B176" s="63" t="str">
+        <x:v>Boss入场音效</x:v>
+      </x:c>
+      <x:c r="C176" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D176" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E176" s="63" t="str">
+        <x:v>boss_intro</x:v>
+      </x:c>
+      <x:c r="F176" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G176" s="63"/>
+      <x:c r="H176" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I176" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J176" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K176" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L176" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M176" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N176" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O176" s="63" t="str">
+        <x:v>src/assets/audio/sfx/boss_intro_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P176" s="63" t="str">
+        <x:v>src/assets/audio/sfx/boss_intro.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q176" s="63" t="str">
+        <x:v>boss_intro; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R176" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C176,D176,E176,F176,H176,I176)</x:f>
+        <x:v>音频|sfx|boss_intro|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S176" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R176)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T176" s="63" t="str">
+        <x:v>4e18a3afe9c7b804e6fb6905fbf05b62cba70d9b15a324c650a04d04a981d5ff</x:v>
+      </x:c>
+      <x:c r="U176" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V176" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W176" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X176" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=boss_intro；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="44" customHeight="1">
+      <x:c r="A177" s="63" t="str">
+        <x:v>AUD-SFX-BOSS-PHASE</x:v>
+      </x:c>
+      <x:c r="B177" s="63" t="str">
+        <x:v>Boss阶段切换音效</x:v>
+      </x:c>
+      <x:c r="C177" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D177" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E177" s="63" t="str">
+        <x:v>boss_phase</x:v>
+      </x:c>
+      <x:c r="F177" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G177" s="63"/>
+      <x:c r="H177" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I177" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J177" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K177" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L177" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M177" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N177" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O177" s="63" t="str">
+        <x:v>src/assets/audio/sfx/boss_phase_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P177" s="63" t="str">
+        <x:v>src/assets/audio/sfx/boss_phase.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q177" s="63" t="str">
+        <x:v>boss_phase; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R177" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C177,D177,E177,F177,H177,I177)</x:f>
+        <x:v>音频|sfx|boss_phase|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S177" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R177)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T177" s="63" t="str">
+        <x:v>804457fc13cb83e18bdc1e7e84d1b9a27414be72128f82811e016c17fc331ad3</x:v>
+      </x:c>
+      <x:c r="U177" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V177" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W177" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X177" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=boss_phase；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="44" customHeight="1">
+      <x:c r="A178" s="63" t="str">
+        <x:v>AUD-SFX-CONTAINER-OPEN</x:v>
+      </x:c>
+      <x:c r="B178" s="63" t="str">
+        <x:v>搜索容器开启音效</x:v>
+      </x:c>
+      <x:c r="C178" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D178" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E178" s="63" t="str">
+        <x:v>container_open</x:v>
+      </x:c>
+      <x:c r="F178" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G178" s="63"/>
+      <x:c r="H178" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I178" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J178" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K178" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L178" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M178" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N178" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O178" s="63" t="str">
+        <x:v>src/assets/audio/sfx/container_open_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P178" s="63" t="str">
+        <x:v>src/assets/audio/sfx/container_open.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q178" s="63" t="str">
+        <x:v>container_open; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R178" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C178,D178,E178,F178,H178,I178)</x:f>
+        <x:v>音频|sfx|container_open|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S178" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R178)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T178" s="63" t="str">
+        <x:v>8e9d9e0a773ab0daf850734913302212a2f279dc7afb0f457a193300325840d0</x:v>
+      </x:c>
+      <x:c r="U178" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V178" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W178" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X178" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=container_open；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="44" customHeight="1">
+      <x:c r="A179" s="63" t="str">
+        <x:v>AUD-SFX-CRIT-HIT</x:v>
+      </x:c>
+      <x:c r="B179" s="63" t="str">
+        <x:v>暴击命中音效</x:v>
+      </x:c>
+      <x:c r="C179" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D179" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E179" s="63" t="str">
+        <x:v>crit_hit</x:v>
+      </x:c>
+      <x:c r="F179" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G179" s="63"/>
+      <x:c r="H179" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I179" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J179" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K179" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L179" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M179" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N179" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O179" s="63" t="str">
+        <x:v>src/assets/audio/sfx/crit_hit_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P179" s="63" t="str">
+        <x:v>src/assets/audio/sfx/crit_hit.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q179" s="63" t="str">
+        <x:v>crit_hit; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R179" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C179,D179,E179,F179,H179,I179)</x:f>
+        <x:v>音频|sfx|crit_hit|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S179" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R179)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T179" s="63" t="str">
+        <x:v>9228e4544dc5472afe0dfaa53df5be2ec8c95bd253ea7ffd9b6136c6dd19069f</x:v>
+      </x:c>
+      <x:c r="U179" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V179" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W179" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X179" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=crit_hit；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="44" customHeight="1">
+      <x:c r="A180" s="63" t="str">
+        <x:v>AUD-SFX-DOOR-LOCKED</x:v>
+      </x:c>
+      <x:c r="B180" s="63" t="str">
+        <x:v>门锁定音效</x:v>
+      </x:c>
+      <x:c r="C180" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D180" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E180" s="63" t="str">
+        <x:v>door_locked</x:v>
+      </x:c>
+      <x:c r="F180" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G180" s="63"/>
+      <x:c r="H180" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I180" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J180" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K180" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L180" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M180" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N180" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O180" s="63" t="str">
+        <x:v>src/assets/audio/sfx/door_locked_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P180" s="63" t="str">
+        <x:v>src/assets/audio/sfx/door_locked.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q180" s="63" t="str">
+        <x:v>door_locked; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R180" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C180,D180,E180,F180,H180,I180)</x:f>
+        <x:v>音频|sfx|door_locked|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S180" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R180)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T180" s="63" t="str">
+        <x:v>db9ece4cf6a904b8c23319b0d3bc83bce2d48ea69d7ebd246dd2bb30f2587e74</x:v>
+      </x:c>
+      <x:c r="U180" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V180" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W180" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X180" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=door_locked；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="44" customHeight="1">
+      <x:c r="A181" s="63" t="str">
+        <x:v>AUD-SFX-DOOR-OPEN</x:v>
+      </x:c>
+      <x:c r="B181" s="63" t="str">
+        <x:v>门开启音效</x:v>
+      </x:c>
+      <x:c r="C181" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D181" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E181" s="63" t="str">
+        <x:v>door_open</x:v>
+      </x:c>
+      <x:c r="F181" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G181" s="63"/>
+      <x:c r="H181" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I181" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J181" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K181" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L181" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M181" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N181" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O181" s="63" t="str">
+        <x:v>src/assets/audio/sfx/door_open_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P181" s="63" t="str">
+        <x:v>src/assets/audio/sfx/door_open.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q181" s="63" t="str">
+        <x:v>door_open; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R181" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C181,D181,E181,F181,H181,I181)</x:f>
+        <x:v>音频|sfx|door_open|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S181" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R181)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T181" s="63" t="str">
+        <x:v>6b3044e0231f425a54103d7a4e44c2a1f21f895310841347ea9ceb76485a5565</x:v>
+      </x:c>
+      <x:c r="U181" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V181" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W181" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X181" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=door_open；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="44" customHeight="1">
+      <x:c r="A182" s="63" t="str">
+        <x:v>AUD-SFX-ENEMY-DIE</x:v>
+      </x:c>
+      <x:c r="B182" s="63" t="str">
+        <x:v>敌人死亡音效</x:v>
+      </x:c>
+      <x:c r="C182" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D182" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E182" s="63" t="str">
+        <x:v>enemy_die</x:v>
+      </x:c>
+      <x:c r="F182" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G182" s="63"/>
+      <x:c r="H182" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I182" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J182" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K182" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L182" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M182" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N182" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O182" s="63" t="str">
+        <x:v>src/assets/audio/sfx/enemy_die_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P182" s="63" t="str">
+        <x:v>src/assets/audio/sfx/enemy_die.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q182" s="63" t="str">
+        <x:v>enemy_die; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R182" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C182,D182,E182,F182,H182,I182)</x:f>
+        <x:v>音频|sfx|enemy_die|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S182" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R182)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T182" s="63" t="str">
+        <x:v>eba3495cc7bf7a301a526a8131c3ee989fd8bfa162e9fafca2c5f923936e4c36</x:v>
+      </x:c>
+      <x:c r="U182" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V182" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W182" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X182" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=enemy_die；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="44" customHeight="1">
+      <x:c r="A183" s="63" t="str">
+        <x:v>AUD-SFX-ENEMY-HIT</x:v>
+      </x:c>
+      <x:c r="B183" s="63" t="str">
+        <x:v>敌人受击音效</x:v>
+      </x:c>
+      <x:c r="C183" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D183" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E183" s="63" t="str">
+        <x:v>enemy_hit</x:v>
+      </x:c>
+      <x:c r="F183" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G183" s="63"/>
+      <x:c r="H183" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I183" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J183" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K183" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L183" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M183" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N183" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O183" s="63" t="str">
+        <x:v>src/assets/audio/sfx/enemy_hit_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P183" s="63" t="str">
+        <x:v>src/assets/audio/sfx/enemy_hit.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q183" s="63" t="str">
+        <x:v>enemy_hit; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R183" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C183,D183,E183,F183,H183,I183)</x:f>
+        <x:v>音频|sfx|enemy_hit|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S183" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R183)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T183" s="63" t="str">
+        <x:v>167495a122c9f30351c44c8d4ad7a46d6324703dddf91305adf550037f429ba4</x:v>
+      </x:c>
+      <x:c r="U183" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V183" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W183" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X183" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=enemy_hit；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="44" customHeight="1">
+      <x:c r="A184" s="63" t="str">
+        <x:v>AUD-SFX-EXTRACTION-ABORT</x:v>
+      </x:c>
+      <x:c r="B184" s="63" t="str">
+        <x:v>撤离中断音效</x:v>
+      </x:c>
+      <x:c r="C184" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D184" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E184" s="63" t="str">
+        <x:v>extraction_abort</x:v>
+      </x:c>
+      <x:c r="F184" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G184" s="63"/>
+      <x:c r="H184" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I184" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J184" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K184" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L184" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M184" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N184" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O184" s="63" t="str">
+        <x:v>src/assets/audio/sfx/extraction_abort_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P184" s="63" t="str">
+        <x:v>src/assets/audio/sfx/extraction_abort.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q184" s="63" t="str">
+        <x:v>extraction_abort; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R184" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C184,D184,E184,F184,H184,I184)</x:f>
+        <x:v>音频|sfx|extraction_abort|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S184" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R184)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T184" s="63" t="str">
+        <x:v>2b29c153f38d8115cdfae413ad3c4054923c65060341d26b2509e617d7c11de0</x:v>
+      </x:c>
+      <x:c r="U184" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V184" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W184" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X184" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=extraction_abort；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="44" customHeight="1">
+      <x:c r="A185" s="63" t="str">
+        <x:v>AUD-SFX-EXTRACTION-DONE</x:v>
+      </x:c>
+      <x:c r="B185" s="63" t="str">
+        <x:v>撤离成功音效</x:v>
+      </x:c>
+      <x:c r="C185" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D185" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E185" s="63" t="str">
+        <x:v>extraction_done</x:v>
+      </x:c>
+      <x:c r="F185" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G185" s="63"/>
+      <x:c r="H185" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I185" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J185" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K185" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L185" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M185" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N185" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O185" s="63" t="str">
+        <x:v>src/assets/audio/sfx/extraction_done_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P185" s="63" t="str">
+        <x:v>src/assets/audio/sfx/extraction_done.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q185" s="63" t="str">
+        <x:v>extraction_done; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R185" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C185,D185,E185,F185,H185,I185)</x:f>
+        <x:v>音频|sfx|extraction_done|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S185" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R185)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T185" s="63" t="str">
+        <x:v>c6eef279ec7a88822b2554799f0a49e4549576ee4c682ef5a3440ea53279df70</x:v>
+      </x:c>
+      <x:c r="U185" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V185" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W185" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X185" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=extraction_done；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="44" customHeight="1">
+      <x:c r="A186" s="63" t="str">
+        <x:v>AUD-SFX-EXTRACTION-START</x:v>
+      </x:c>
+      <x:c r="B186" s="63" t="str">
+        <x:v>撤离开始音效</x:v>
+      </x:c>
+      <x:c r="C186" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D186" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E186" s="63" t="str">
+        <x:v>extraction_start</x:v>
+      </x:c>
+      <x:c r="F186" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G186" s="63"/>
+      <x:c r="H186" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I186" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J186" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K186" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L186" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M186" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N186" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O186" s="63" t="str">
+        <x:v>src/assets/audio/sfx/extraction_start_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P186" s="63" t="str">
+        <x:v>src/assets/audio/sfx/extraction_start.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q186" s="63" t="str">
+        <x:v>extraction_start; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R186" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C186,D186,E186,F186,H186,I186)</x:f>
+        <x:v>音频|sfx|extraction_start|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S186" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R186)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T186" s="63" t="str">
+        <x:v>e44385e009738b96dac7aa7106bd489ccf55fe700332359407e0663f826c7daa</x:v>
+      </x:c>
+      <x:c r="U186" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V186" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W186" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X186" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=extraction_start；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="44" customHeight="1">
+      <x:c r="A187" s="63" t="str">
+        <x:v>AUD-SFX-FATE-CARD</x:v>
+      </x:c>
+      <x:c r="B187" s="63" t="str">
+        <x:v>命运卡生效音效</x:v>
+      </x:c>
+      <x:c r="C187" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D187" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E187" s="63" t="str">
+        <x:v>fate_card</x:v>
+      </x:c>
+      <x:c r="F187" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G187" s="63"/>
+      <x:c r="H187" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I187" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J187" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K187" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L187" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M187" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N187" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O187" s="63" t="str">
+        <x:v>src/assets/audio/sfx/fate_card_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P187" s="63" t="str">
+        <x:v>src/assets/audio/sfx/fate_card.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q187" s="63" t="str">
+        <x:v>fate_card; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R187" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C187,D187,E187,F187,H187,I187)</x:f>
+        <x:v>音频|sfx|fate_card|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S187" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R187)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T187" s="63" t="str">
+        <x:v>7cdce8d37b6308c0df873f4f20e80d319e546cb24ab5d860ea0cef5bd4ae3488</x:v>
+      </x:c>
+      <x:c r="U187" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V187" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W187" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X187" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=fate_card；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="44" customHeight="1">
+      <x:c r="A188" s="63" t="str">
+        <x:v>AUD-SFX-ITEM-PICKUP</x:v>
+      </x:c>
+      <x:c r="B188" s="63" t="str">
+        <x:v>物品拾取音效</x:v>
+      </x:c>
+      <x:c r="C188" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D188" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E188" s="63" t="str">
+        <x:v>item_pickup</x:v>
+      </x:c>
+      <x:c r="F188" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G188" s="63"/>
+      <x:c r="H188" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I188" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J188" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K188" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L188" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M188" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N188" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O188" s="63" t="str">
+        <x:v>src/assets/audio/sfx/item_pickup_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P188" s="63" t="str">
+        <x:v>src/assets/audio/sfx/item_pickup.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q188" s="63" t="str">
+        <x:v>item_pickup; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R188" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C188,D188,E188,F188,H188,I188)</x:f>
+        <x:v>音频|sfx|item_pickup|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S188" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R188)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T188" s="63" t="str">
+        <x:v>7114f2ac9b0dc6ee500f5176b315b5f8a84f9ec7e3c5168dc342febdb747c290</x:v>
+      </x:c>
+      <x:c r="U188" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V188" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W188" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X188" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=item_pickup；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="44" customHeight="1">
+      <x:c r="A189" s="63" t="str">
+        <x:v>AUD-SFX-LASER-FIRE</x:v>
+      </x:c>
+      <x:c r="B189" s="63" t="str">
+        <x:v>能量武器射击音效</x:v>
+      </x:c>
+      <x:c r="C189" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D189" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E189" s="63" t="str">
+        <x:v>laser_fire</x:v>
+      </x:c>
+      <x:c r="F189" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G189" s="63"/>
+      <x:c r="H189" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I189" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J189" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K189" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L189" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M189" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N189" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O189" s="63" t="str">
+        <x:v>src/assets/audio/sfx/laser_fire_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P189" s="63" t="str">
+        <x:v>src/assets/audio/sfx/laser_fire.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q189" s="63" t="str">
+        <x:v>laser_fire; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R189" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C189,D189,E189,F189,H189,I189)</x:f>
+        <x:v>音频|sfx|laser_fire|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S189" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R189)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T189" s="63" t="str">
+        <x:v>b9fa5b0e0835a0e18b5a0bb29bff7fcc94944020f3eb9a8424343786ab845191</x:v>
+      </x:c>
+      <x:c r="U189" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V189" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W189" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X189" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=laser_fire；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="44" customHeight="1">
+      <x:c r="A190" s="63" t="str">
+        <x:v>AUD-SFX-MERCHANT-PURCHASE</x:v>
+      </x:c>
+      <x:c r="B190" s="63" t="str">
+        <x:v>交易成功音效</x:v>
+      </x:c>
+      <x:c r="C190" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D190" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E190" s="63" t="str">
+        <x:v>merchant_purchase</x:v>
+      </x:c>
+      <x:c r="F190" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G190" s="63"/>
+      <x:c r="H190" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I190" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J190" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K190" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L190" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M190" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N190" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O190" s="63" t="str">
+        <x:v>src/assets/audio/sfx/merchant_purchase_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P190" s="63" t="str">
+        <x:v>src/assets/audio/sfx/merchant_purchase.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q190" s="63" t="str">
+        <x:v>merchant_purchase; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R190" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C190,D190,E190,F190,H190,I190)</x:f>
+        <x:v>音频|sfx|merchant_purchase|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S190" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R190)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T190" s="63" t="str">
+        <x:v>ff71a229a012ea8ed985ab286ea01672af277dd33a62549dd080f1e9026d53c2</x:v>
+      </x:c>
+      <x:c r="U190" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V190" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W190" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X190" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=merchant_purchase；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="44" customHeight="1">
+      <x:c r="A191" s="63" t="str">
+        <x:v>AUD-SFX-PISTOL-FIRE</x:v>
+      </x:c>
+      <x:c r="B191" s="63" t="str">
+        <x:v>手枪射击音效</x:v>
+      </x:c>
+      <x:c r="C191" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D191" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E191" s="63" t="str">
+        <x:v>pistol_fire</x:v>
+      </x:c>
+      <x:c r="F191" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G191" s="63"/>
+      <x:c r="H191" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I191" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J191" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K191" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L191" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M191" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N191" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O191" s="63" t="str">
+        <x:v>src/assets/audio/sfx/pistol_fire_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P191" s="63" t="str">
+        <x:v>src/assets/audio/sfx/pistol_fire.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q191" s="63" t="str">
+        <x:v>pistol_fire; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R191" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C191,D191,E191,F191,H191,I191)</x:f>
+        <x:v>音频|sfx|pistol_fire|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S191" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R191)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T191" s="63" t="str">
+        <x:v>b2c39d4579cf13e32f98e79eb57b6ea0efeb5af7a497c60dc1acf94e8dd16937</x:v>
+      </x:c>
+      <x:c r="U191" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V191" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W191" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X191" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=pistol_fire；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="44" customHeight="1">
+      <x:c r="A192" s="63" t="str">
+        <x:v>AUD-SFX-PLAYER-DASH</x:v>
+      </x:c>
+      <x:c r="B192" s="63" t="str">
+        <x:v>玩家冲刺音效</x:v>
+      </x:c>
+      <x:c r="C192" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D192" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E192" s="63" t="str">
+        <x:v>player_dash</x:v>
+      </x:c>
+      <x:c r="F192" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G192" s="63"/>
+      <x:c r="H192" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I192" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J192" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K192" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L192" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M192" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N192" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O192" s="63" t="str">
+        <x:v>src/assets/audio/sfx/player_dash_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P192" s="63" t="str">
+        <x:v>src/assets/audio/sfx/player_dash.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q192" s="63" t="str">
+        <x:v>player_dash; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R192" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C192,D192,E192,F192,H192,I192)</x:f>
+        <x:v>音频|sfx|player_dash|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S192" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R192)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T192" s="63" t="str">
+        <x:v>5d437b11f4b79d593ded0045cf202542b44ac0eb7344561ec96c659ad9ea6930</x:v>
+      </x:c>
+      <x:c r="U192" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V192" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W192" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X192" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=player_dash；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="44" customHeight="1">
+      <x:c r="A193" s="63" t="str">
+        <x:v>AUD-SFX-PLAYER-HIT</x:v>
+      </x:c>
+      <x:c r="B193" s="63" t="str">
+        <x:v>玩家受击音效</x:v>
+      </x:c>
+      <x:c r="C193" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D193" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E193" s="63" t="str">
+        <x:v>player_hit</x:v>
+      </x:c>
+      <x:c r="F193" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G193" s="63"/>
+      <x:c r="H193" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I193" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J193" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K193" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L193" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M193" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N193" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O193" s="63" t="str">
+        <x:v>src/assets/audio/sfx/player_hit_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P193" s="63" t="str">
+        <x:v>src/assets/audio/sfx/player_hit.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q193" s="63" t="str">
+        <x:v>player_hit; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R193" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C193,D193,E193,F193,H193,I193)</x:f>
+        <x:v>音频|sfx|player_hit|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S193" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R193)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T193" s="63" t="str">
+        <x:v>aa5bec92c2734e64ae75245c0fcb165c915981cf77d107c579649c228fc50eb2</x:v>
+      </x:c>
+      <x:c r="U193" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V193" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W193" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X193" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=player_hit；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="44" customHeight="1">
+      <x:c r="A194" s="63" t="str">
+        <x:v>AUD-SFX-RELOAD</x:v>
+      </x:c>
+      <x:c r="B194" s="63" t="str">
+        <x:v>换弹音效</x:v>
+      </x:c>
+      <x:c r="C194" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D194" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E194" s="63" t="str">
+        <x:v>reload</x:v>
+      </x:c>
+      <x:c r="F194" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G194" s="63"/>
+      <x:c r="H194" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I194" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J194" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K194" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L194" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M194" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N194" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O194" s="63" t="str">
+        <x:v>src/assets/audio/sfx/reload_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P194" s="63" t="str">
+        <x:v>src/assets/audio/sfx/reload.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q194" s="63" t="str">
+        <x:v>reload; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R194" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C194,D194,E194,F194,H194,I194)</x:f>
+        <x:v>音频|sfx|reload|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S194" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R194)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T194" s="63" t="str">
+        <x:v>0d60be5b4b3e9955d34c69e5719ae8d3147d6e87d3ffa58beae8d2beae42d0c7</x:v>
+      </x:c>
+      <x:c r="U194" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V194" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W194" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X194" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=reload；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="44" customHeight="1">
+      <x:c r="A195" s="63" t="str">
+        <x:v>AUD-SFX-RIFLE-FIRE</x:v>
+      </x:c>
+      <x:c r="B195" s="63" t="str">
+        <x:v>步枪射击音效</x:v>
+      </x:c>
+      <x:c r="C195" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D195" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E195" s="63" t="str">
+        <x:v>rifle_fire</x:v>
+      </x:c>
+      <x:c r="F195" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G195" s="63"/>
+      <x:c r="H195" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I195" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J195" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K195" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L195" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M195" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N195" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O195" s="63" t="str">
+        <x:v>src/assets/audio/sfx/rifle_fire_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P195" s="63" t="str">
+        <x:v>src/assets/audio/sfx/rifle_fire.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q195" s="63" t="str">
+        <x:v>rifle_fire; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R195" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C195,D195,E195,F195,H195,I195)</x:f>
+        <x:v>音频|sfx|rifle_fire|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S195" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R195)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T195" s="63" t="str">
+        <x:v>c5b6cc8c2beb44f22c72c1d201b750dd79dc877ae88f0067ef246103948e0e33</x:v>
+      </x:c>
+      <x:c r="U195" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V195" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W195" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X195" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=rifle_fire；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="44" customHeight="1">
+      <x:c r="A196" s="63" t="str">
+        <x:v>AUD-SFX-SHOTGUN-FIRE</x:v>
+      </x:c>
+      <x:c r="B196" s="63" t="str">
+        <x:v>霰弹枪射击音效</x:v>
+      </x:c>
+      <x:c r="C196" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D196" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E196" s="63" t="str">
+        <x:v>shotgun_fire</x:v>
+      </x:c>
+      <x:c r="F196" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G196" s="63"/>
+      <x:c r="H196" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I196" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J196" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K196" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L196" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M196" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N196" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O196" s="63" t="str">
+        <x:v>src/assets/audio/sfx/shotgun_fire_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P196" s="63" t="str">
+        <x:v>src/assets/audio/sfx/shotgun_fire.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q196" s="63" t="str">
+        <x:v>shotgun_fire; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R196" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C196,D196,E196,F196,H196,I196)</x:f>
+        <x:v>音频|sfx|shotgun_fire|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S196" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R196)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T196" s="63" t="str">
+        <x:v>e4b8feb67d9a438892183fa3a2e4afec8e3131235be342c02b1ce72e25767466</x:v>
+      </x:c>
+      <x:c r="U196" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V196" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W196" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X196" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=shotgun_fire；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="44" customHeight="1">
+      <x:c r="A197" s="63" t="str">
+        <x:v>AUD-SFX-SMG-FIRE</x:v>
+      </x:c>
+      <x:c r="B197" s="63" t="str">
+        <x:v>冲锋枪射击音效</x:v>
+      </x:c>
+      <x:c r="C197" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D197" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E197" s="63" t="str">
+        <x:v>smg_fire</x:v>
+      </x:c>
+      <x:c r="F197" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G197" s="63"/>
+      <x:c r="H197" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I197" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J197" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K197" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L197" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M197" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N197" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O197" s="63" t="str">
+        <x:v>src/assets/audio/sfx/smg_fire_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P197" s="63" t="str">
+        <x:v>src/assets/audio/sfx/smg_fire.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q197" s="63" t="str">
+        <x:v>smg_fire; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R197" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C197,D197,E197,F197,H197,I197)</x:f>
+        <x:v>音频|sfx|smg_fire|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S197" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R197)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T197" s="63" t="str">
+        <x:v>282379aa6850e03dd6109928a22ad7792563768414ece93374c7cff725d306fa</x:v>
+      </x:c>
+      <x:c r="U197" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V197" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W197" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X197" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=smg_fire；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="44" customHeight="1">
+      <x:c r="A198" s="63" t="str">
+        <x:v>AUD-SFX-SNIPER-FIRE</x:v>
+      </x:c>
+      <x:c r="B198" s="63" t="str">
+        <x:v>狙击枪射击音效</x:v>
+      </x:c>
+      <x:c r="C198" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D198" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E198" s="63" t="str">
+        <x:v>sniper_fire</x:v>
+      </x:c>
+      <x:c r="F198" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G198" s="63"/>
+      <x:c r="H198" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I198" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J198" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K198" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L198" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M198" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N198" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O198" s="63" t="str">
+        <x:v>src/assets/audio/sfx/sniper_fire_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P198" s="63" t="str">
+        <x:v>src/assets/audio/sfx/sniper_fire.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q198" s="63" t="str">
+        <x:v>sniper_fire; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R198" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C198,D198,E198,F198,H198,I198)</x:f>
+        <x:v>音频|sfx|sniper_fire|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S198" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R198)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T198" s="63" t="str">
+        <x:v>0d5161b3b8faece3024ad618916c203cd3d274d3b373af7bcbbd22baa0ab3968</x:v>
+      </x:c>
+      <x:c r="U198" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V198" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W198" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X198" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=sniper_fire；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="44" customHeight="1">
+      <x:c r="A199" s="63" t="str">
+        <x:v>AUD-SFX-SOUL-PICKUP</x:v>
+      </x:c>
+      <x:c r="B199" s="63" t="str">
+        <x:v>魂球拾取音效</x:v>
+      </x:c>
+      <x:c r="C199" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D199" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E199" s="63" t="str">
+        <x:v>soul_pickup</x:v>
+      </x:c>
+      <x:c r="F199" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G199" s="63"/>
+      <x:c r="H199" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I199" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J199" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K199" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L199" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M199" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N199" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O199" s="63" t="str">
+        <x:v>src/assets/audio/sfx/soul_pickup_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P199" s="63" t="str">
+        <x:v>src/assets/audio/sfx/soul_pickup.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q199" s="63" t="str">
+        <x:v>soul_pickup; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R199" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C199,D199,E199,F199,H199,I199)</x:f>
+        <x:v>音频|sfx|soul_pickup|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S199" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R199)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T199" s="63" t="str">
+        <x:v>c9f24f23f1c4e8ad28a5ee97e9b11efd00e53bf706faa0655cba4f78b68e76ff</x:v>
+      </x:c>
+      <x:c r="U199" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V199" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W199" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X199" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=soul_pickup；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="44" customHeight="1">
+      <x:c r="A200" s="63" t="str">
+        <x:v>AUD-SFX-UI-CLICK</x:v>
+      </x:c>
+      <x:c r="B200" s="63" t="str">
+        <x:v>UI点击音效</x:v>
+      </x:c>
+      <x:c r="C200" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D200" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E200" s="63" t="str">
+        <x:v>ui_click</x:v>
+      </x:c>
+      <x:c r="F200" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G200" s="63"/>
+      <x:c r="H200" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I200" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J200" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K200" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L200" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M200" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N200" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O200" s="63" t="str">
+        <x:v>src/assets/audio/sfx/ui_click_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P200" s="63" t="str">
+        <x:v>src/assets/audio/sfx/ui_click.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q200" s="63" t="str">
+        <x:v>ui_click; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R200" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C200,D200,E200,F200,H200,I200)</x:f>
+        <x:v>音频|sfx|ui_click|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S200" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R200)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T200" s="63" t="str">
+        <x:v>a19f1bec70959ea5fd4715ee292080f9932fc3835b060b713a00fc19822fc3a5</x:v>
+      </x:c>
+      <x:c r="U200" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V200" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W200" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X200" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=ui_click；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="44" customHeight="1">
+      <x:c r="A201" s="63" t="str">
+        <x:v>AUD-SFX-UI-ERROR</x:v>
+      </x:c>
+      <x:c r="B201" s="63" t="str">
+        <x:v>UI错误音效</x:v>
+      </x:c>
+      <x:c r="C201" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D201" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E201" s="63" t="str">
+        <x:v>ui_error</x:v>
+      </x:c>
+      <x:c r="F201" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G201" s="63"/>
+      <x:c r="H201" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I201" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J201" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K201" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L201" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M201" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N201" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O201" s="63" t="str">
+        <x:v>src/assets/audio/sfx/ui_error_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P201" s="63" t="str">
+        <x:v>src/assets/audio/sfx/ui_error.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q201" s="63" t="str">
+        <x:v>ui_error; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R201" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C201,D201,E201,F201,H201,I201)</x:f>
+        <x:v>音频|sfx|ui_error|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S201" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R201)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T201" s="63" t="str">
+        <x:v>eeb07b8cc575869b8d560c929431d8beb43eb533c9900403df6beb9bb83b9b5e</x:v>
+      </x:c>
+      <x:c r="U201" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V201" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W201" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X201" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=ui_error；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="44" customHeight="1">
+      <x:c r="A202" s="63" t="str">
+        <x:v>AUD-SFX-UI-HOVER</x:v>
+      </x:c>
+      <x:c r="B202" s="63" t="str">
+        <x:v>UI悬停音效</x:v>
+      </x:c>
+      <x:c r="C202" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D202" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E202" s="63" t="str">
+        <x:v>ui_hover</x:v>
+      </x:c>
+      <x:c r="F202" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G202" s="63"/>
+      <x:c r="H202" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I202" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J202" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K202" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L202" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M202" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N202" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O202" s="63" t="str">
+        <x:v>src/assets/audio/sfx/ui_hover_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P202" s="63" t="str">
+        <x:v>src/assets/audio/sfx/ui_hover.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q202" s="63" t="str">
+        <x:v>ui_hover; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R202" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C202,D202,E202,F202,H202,I202)</x:f>
+        <x:v>音频|sfx|ui_hover|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S202" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R202)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T202" s="63" t="str">
+        <x:v>edb43f0a80a9833364555c052e01e898d39396bef925566cbadf34e009877bcb</x:v>
+      </x:c>
+      <x:c r="U202" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V202" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W202" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X202" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=ui_hover；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="44" customHeight="1">
+      <x:c r="A203" s="63" t="str">
+        <x:v>AUD-SFX-WAVE-CLEAR</x:v>
+      </x:c>
+      <x:c r="B203" s="63" t="str">
+        <x:v>波次完成音效</x:v>
+      </x:c>
+      <x:c r="C203" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D203" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E203" s="63" t="str">
+        <x:v>wave_clear</x:v>
+      </x:c>
+      <x:c r="F203" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G203" s="63"/>
+      <x:c r="H203" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I203" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J203" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K203" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L203" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M203" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N203" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O203" s="63" t="str">
+        <x:v>src/assets/audio/sfx/wave_clear_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P203" s="63" t="str">
+        <x:v>src/assets/audio/sfx/wave_clear.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q203" s="63" t="str">
+        <x:v>wave_clear; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R203" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C203,D203,E203,F203,H203,I203)</x:f>
+        <x:v>音频|sfx|wave_clear|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S203" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R203)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T203" s="63" t="str">
+        <x:v>aa4d315fd2914681fc9a44533dc4470186f3b3349e88782a9d4a00730b5377a2</x:v>
+      </x:c>
+      <x:c r="U203" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V203" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W203" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X203" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=wave_clear；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="44" customHeight="1">
+      <x:c r="A204" s="63" t="str">
+        <x:v>AUD-SFX-WAVE-START</x:v>
+      </x:c>
+      <x:c r="B204" s="63" t="str">
+        <x:v>波次开始音效</x:v>
+      </x:c>
+      <x:c r="C204" s="63" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D204" s="63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E204" s="63" t="str">
+        <x:v>wave_start</x:v>
+      </x:c>
+      <x:c r="F204" s="63" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G204" s="63"/>
+      <x:c r="H204" s="63" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I204" s="63" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J204" s="63" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K204" s="63" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L204" s="63" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M204" s="63" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N204" s="63" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O204" s="63" t="str">
+        <x:v>src/assets/audio/sfx/wave_start_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P204" s="63" t="str">
+        <x:v>src/assets/audio/sfx/wave_start.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q204" s="63" t="str">
+        <x:v>wave_start; 音效; OGG; Android; 移动端</x:v>
+      </x:c>
+      <x:c r="R204" s="63" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C204,D204,E204,F204,H204,I204)</x:f>
+        <x:v>音频|sfx|wave_start|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S204" s="63" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$204,R204)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T204" s="63" t="str">
+        <x:v>be26cec7935eda95510b606cfc8bbebc5fe6f6d4310008a363d889f4bbef6083</x:v>
+      </x:c>
+      <x:c r="U204" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V204" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="W204" s="63" t="str">
+        <x:v>项目WAV母版转码</x:v>
+      </x:c>
+      <x:c r="X204" s="63" t="str">
+        <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=wave_start；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13484,7 +15778,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd19abecd5a6b443e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3916b222ff134eef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15528,25 +17822,25 @@
         <x:v>无（终态）</x:v>
       </x:c>
       <x:c r="F13" s="101" t="str">
-        <x:v>倾倒熄灭</x:v>
+        <x:v>按最后受击方向水平击飞并上抛；落地弹起一次后侧倒</x:v>
       </x:c>
       <x:c r="G13" s="101" t="str">
-        <x:v>随整体倾倒</x:v>
+        <x:v>随身体滞后后仰，回弹后贴地</x:v>
       </x:c>
       <x:c r="H13" s="101" t="str">
-        <x:v>随整体倾倒</x:v>
+        <x:v>随击飞惯性展开，回弹时收束</x:v>
       </x:c>
       <x:c r="I13" s="101" t="str">
-        <x:v>随整体倾倒</x:v>
+        <x:v>武器握持层随整体击飞/回弹/侧倒</x:v>
       </x:c>
       <x:c r="J13" s="101" t="str">
-        <x:v>停止</x:v>
+        <x:v>惯性拖尾后停止</x:v>
       </x:c>
       <x:c r="K13" s="101" t="str">
-        <x:v>HUD 终止</x:v>
+        <x:v>1.35秒后显示点击返99F确认框</x:v>
       </x:c>
       <x:c r="L13" s="101" t="str">
-        <x:v>整体倾倒；耳朵与肢体跟随关节</x:v>
+        <x:v>真实CharacterBody3D速度+重力；death_animation_finished仅通知表现完成，点击后结算</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -16672,13 +18966,13 @@
         <x:v>bgm / sfx / ambience / ui</x:v>
       </x:c>
       <x:c r="D14" s="37" t="str">
-        <x:v>assets/audio/</x:v>
+        <x:v>src/assets/audio/sfx/</x:v>
       </x:c>
       <x:c r="E14" s="37" t="str">
-        <x:v>aud_{type}_{event}_{variant}_v{nnn}.wav</x:v>
+        <x:v>{event}_v{nnn}.{ogg|wav}</x:v>
       </x:c>
       <x:c r="F14" s="37" t="str">
-        <x:v>AUD-SFX-PLAYER-DASH-A</x:v>
+        <x:v>AUD-SFX-PLAYER-DASH</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -17550,11 +19844,11 @@
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="58" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="60" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="25" customHeight="1">
@@ -17611,7 +19905,7 @@
         <x:v>负责人</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="46" customHeight="1">
       <x:c r="A6" s="36" t="str">
         <x:v>v0.1.0</x:v>
       </x:c>
@@ -17634,37 +19928,51 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
+    <x:row r="7" ht="46" customHeight="1">
+      <x:c r="A7" s="63" t="str">
         <x:v>v0.1.1</x:v>
       </x:c>
-      <x:c r="B7" s="62" t="n">
+      <x:c r="B7" s="64" t="n">
         <x:v>46240</x:v>
       </x:c>
-      <x:c r="C7" t="str">
+      <x:c r="C7" s="63" t="str">
         <x:v>角色武器表现调整</x:v>
       </x:c>
-      <x:c r="D7" t="str">
+      <x:c r="D7" s="63" t="str">
         <x:v>player_capsule01_3d</x:v>
       </x:c>
-      <x:c r="E7" t="str">
+      <x:c r="E7" s="63" t="str">
         <x:v>新增主左/副右背部收纳挂点，枪口统一朝下；复用既有武器模型与AssetID。</x:v>
       </x:c>
-      <x:c r="F7" t="str">
+      <x:c r="F7" s="63" t="str">
         <x:v>不改武器实例、碰撞、伤害或切枪规则。</x:v>
       </x:c>
-      <x:c r="G7" t="str">
+      <x:c r="G7" s="63" t="str">
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8"/>
-      <x:c r="B8"/>
-      <x:c r="C8"/>
-      <x:c r="D8"/>
-      <x:c r="E8"/>
-      <x:c r="F8"/>
-      <x:c r="G8"/>
+    <x:row r="8" ht="46" customHeight="1">
+      <x:c r="A8" s="63" t="str">
+        <x:v>v0.1.2</x:v>
+      </x:c>
+      <x:c r="B8" s="64" t="n">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C8" s="63" t="str">
+        <x:v>音频与体验一致性</x:v>
+      </x:c>
+      <x:c r="D8" s="63" t="str">
+        <x:v>31项音效/UI/玩家死亡</x:v>
+      </x:c>
+      <x:c r="E8" s="63" t="str">
+        <x:v>登记OGG运行资产与哈希；更新包裹/贩卖机UI版本和死亡击飞回弹状态。</x:v>
+      </x:c>
+      <x:c r="F8" s="63" t="str">
+        <x:v>WAV母版保留；运行时改用版本化OGG；不改变稳定事件键和AssetID。</x:v>
+      </x:c>
+      <x:c r="G8" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0551494b974f4ac6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R1c003ec036f64218"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rb22758f0ce214e86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R7a7260dbbd2f4e5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rd9c3cd43d45f4cf7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R0ec45979b76c47ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R75e66154a0234179"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rb32e9d61309f4aba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf445afed255f4c27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rcc0afe7668354274"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R6275beb9a61741b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Ra1da56055e89475a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R1ad8686139e64aaa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R56a8f7b5b15f412e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R2846fd3d7c8040a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R57ed26890ba14e7e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1036,17 +1036,17 @@
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="45" t="n">
         <x:f>COUNTA('资产主表'!$A$6:$A$205)</x:f>
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B6" s="43"/>
       <x:c r="C6" s="45" t="n">
         <x:f>COUNTIF('资产主表'!$K$6:$K$205,"已完成")+COUNTIF('资产主表'!$K$6:$K$205,"原型已接入")</x:f>
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
         <x:f>COUNTIF('资产主表'!$K$6:$K$205,"待制作")+COUNTIF('资产主表'!$K$6:$K$205,"程序占位")</x:f>
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F6" s="43"/>
       <x:c r="G6" s="45" t="n">
@@ -1111,11 +1111,11 @@
       </x:c>
       <x:c r="B10" s="50" t="n">
         <x:f>COUNTIF('资产主表'!$C$6:$C$205,A10)</x:f>
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="50" t="n">
         <x:f>COUNTIFS('资产主表'!$C$6:$C$205,A10,'资产主表'!$K$6:$K$205,"已完成")+COUNTIFS('资产主表'!$C$6:$C$205,A10,'资产主表'!$K$6:$K$205,"原型已接入")</x:f>
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D10" s="43"/>
       <x:c r="E10" s="51" t="str">
@@ -1557,13 +1557,13 @@
       </x:c>
       <x:c r="G6" s="36" t="str"/>
       <x:c r="H6" s="36" t="str">
-        <x:v>侧面朝右（可水平翻转）</x:v>
+        <x:v>俯视3D</x:v>
       </x:c>
       <x:c r="I6" s="36" t="str">
         <x:v>default</x:v>
       </x:c>
       <x:c r="J6" s="36" t="str">
-        <x:v>全模式玩家</x:v>
+        <x:v>正式3D玩家</x:v>
       </x:c>
       <x:c r="K6" s="36" t="str">
         <x:v>原型已接入</x:v>
@@ -1572,23 +1572,23 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="M6" s="36" t="str">
-        <x:v>v001</x:v>
+        <x:v>v006</x:v>
       </x:c>
       <x:c r="N6" s="36" t="str">
-        <x:v>组装后约 56×64 px</x:v>
+        <x:v>稳定逻辑身份；当前表现约1.5m高</x:v>
       </x:c>
       <x:c r="O6" s="36" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01/</x:v>
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v006.tscn</x:v>
       </x:c>
       <x:c r="P6" s="36" t="str">
-        <x:v>src/player/PlayerAvatarRenderer.gd</x:v>
+        <x:v>src/player3d/Player3D.gd; src/player3d/PlayerAvatar3D.gd</x:v>
       </x:c>
       <x:c r="Q6" s="36" t="str">
         <x:v>玩家; 胶囊体; 防护服; 主角</x:v>
       </x:c>
       <x:c r="R6" s="36" t="str">
         <x:f>LOWER(TRIM(C6)&amp;"|"&amp;TRIM(D6)&amp;"|"&amp;TRIM(E6)&amp;"|"&amp;TRIM(F6)&amp;"|"&amp;TRIM(H6)&amp;"|"&amp;TRIM(I6))</x:f>
-        <x:v>角色|player|player_capsule01|root|侧面朝右（可水平翻转）|default</x:v>
+        <x:v>角色|player|player_capsule01|root|俯视3d|default</x:v>
       </x:c>
       <x:c r="S6" s="36" t="str">
         <x:f>IF(A6="","",IF(COUNTIF($R$6:$R$162,R6)&gt;1,"重复","唯一"))</x:f>
@@ -1599,13 +1599,13 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V6" s="53" t="n">
-        <x:v>46224</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="W6" s="36" t="str">
-        <x:v>原创/待确认</x:v>
+        <x:v>稳定玩法根 AssetID</x:v>
       </x:c>
       <x:c r="X6" s="36" t="str">
-        <x:v>非人类抽象体；无腿；单手随身体朝向左右镜像；红围巾识别色</x:v>
+        <x:v>2026-08-09：旧2D胶囊表现已退役并删除；正式表现只使用 CHR-PLY-CAPSULE01-3D-BUNNY01 v006。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1634,13 +1634,13 @@
         <x:v>侧面朝右（可水平翻转）</x:v>
       </x:c>
       <x:c r="I7" s="37" t="str">
-        <x:v>default</x:v>
+        <x:v>deprecated</x:v>
       </x:c>
       <x:c r="J7" s="37" t="str">
         <x:v>单资产</x:v>
       </x:c>
       <x:c r="K7" s="37" t="str">
-        <x:v>已完成</x:v>
+        <x:v>弃用</x:v>
       </x:c>
       <x:c r="L7" s="37" t="str">
         <x:v>P0</x:v>
@@ -1651,18 +1651,14 @@
       <x:c r="N7" s="37" t="str">
         <x:v>28×24 px</x:v>
       </x:c>
-      <x:c r="O7" s="37" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01/components/chr_player_capsule01_head_side_v001.png</x:v>
-      </x:c>
-      <x:c r="P7" s="37" t="str">
-        <x:v>AI 母版 + 色键裁切</x:v>
-      </x:c>
+      <x:c r="O7" s="37"/>
+      <x:c r="P7" s="37"/>
       <x:c r="Q7" s="37" t="str">
         <x:v>头; 头盔; 传感器</x:v>
       </x:c>
       <x:c r="R7" s="37" t="str">
         <x:f>LOWER(TRIM(C7)&amp;"|"&amp;TRIM(D7)&amp;"|"&amp;TRIM(E7)&amp;"|"&amp;TRIM(F7)&amp;"|"&amp;TRIM(H7)&amp;"|"&amp;TRIM(I7))</x:f>
-        <x:v>角色|player_component|player_capsule01|head|侧面朝右（可水平翻转）|default</x:v>
+        <x:v>角色|player_component|player_capsule01|head|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S7" s="37" t="str">
         <x:f>IF(A7="","",IF(COUNTIF($R$6:$R$162,R7)&gt;1,"重复","唯一"))</x:f>
@@ -1675,13 +1671,13 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V7" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="W7" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X7" s="37" t="str">
-        <x:v>侧面单传感器；无脸；禁止补嘴</x:v>
+        <x:v>2026-08-09：旧2D玩家像素表现文件已从仓库删除；仅保留AssetID/哈希作为历史记录，替代项为 CHR-PLY-CAPSULE01-3D-BUNNY01。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1710,13 +1706,13 @@
         <x:v>侧面朝右（可水平翻转）</x:v>
       </x:c>
       <x:c r="I8" s="37" t="str">
-        <x:v>default</x:v>
+        <x:v>deprecated</x:v>
       </x:c>
       <x:c r="J8" s="37" t="str">
         <x:v>单资产</x:v>
       </x:c>
       <x:c r="K8" s="37" t="str">
-        <x:v>已完成</x:v>
+        <x:v>弃用</x:v>
       </x:c>
       <x:c r="L8" s="37" t="str">
         <x:v>P0</x:v>
@@ -1727,18 +1723,14 @@
       <x:c r="N8" s="37" t="str">
         <x:v>32×35 px</x:v>
       </x:c>
-      <x:c r="O8" s="37" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01/components/chr_player_capsule01_body_side_v001.png</x:v>
-      </x:c>
-      <x:c r="P8" s="37" t="str">
-        <x:v>AI 母版 + 色键裁切</x:v>
-      </x:c>
+      <x:c r="O8" s="37"/>
+      <x:c r="P8" s="37"/>
       <x:c r="Q8" s="37" t="str">
         <x:v>身子; 躯干; 防护服</x:v>
       </x:c>
       <x:c r="R8" s="37" t="str">
         <x:f>LOWER(TRIM(C8)&amp;"|"&amp;TRIM(D8)&amp;"|"&amp;TRIM(E8)&amp;"|"&amp;TRIM(F8)&amp;"|"&amp;TRIM(H8)&amp;"|"&amp;TRIM(I8))</x:f>
-        <x:v>角色|player_component|player_capsule01|body|侧面朝右（可水平翻转）|default</x:v>
+        <x:v>角色|player_component|player_capsule01|body|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S8" s="37" t="str">
         <x:f>IF(A8="","",IF(COUNTIF($R$6:$R$162,R8)&gt;1,"重复","唯一"))</x:f>
@@ -1751,13 +1743,13 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V8" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="W8" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X8" s="37" t="str">
-        <x:v>身体不含腿、脚、手臂</x:v>
+        <x:v>2026-08-09：旧2D玩家像素表现文件已从仓库删除；仅保留AssetID/哈希作为历史记录，替代项为 CHR-PLY-CAPSULE01-3D-BUNNY01。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1803,12 +1795,8 @@
       <x:c r="N9" s="37" t="str">
         <x:v>22×21 px</x:v>
       </x:c>
-      <x:c r="O9" s="37" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01/components/chr_player_capsule01_hand_l_side_v001.png</x:v>
-      </x:c>
-      <x:c r="P9" s="37" t="str">
-        <x:v>AI 母版 + 色键裁切</x:v>
-      </x:c>
+      <x:c r="O9" s="37"/>
+      <x:c r="P9" s="37"/>
       <x:c r="Q9" s="37" t="str">
         <x:v>左手; 辅助手</x:v>
       </x:c>
@@ -1827,13 +1815,13 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V9" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="W9" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X9" s="37" t="str">
-        <x:v>单手持枪方案不再实例化；保留源文件与历史 AssetID，运行时改用 CHR-PLY-CAPSULE01-HAND-R-SIDE</x:v>
+        <x:v>2026-08-09：旧2D玩家像素表现文件已从仓库删除；仅保留AssetID/哈希作为历史记录，替代项为 CHR-PLY-CAPSULE01-3D-BUNNY01。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1862,13 +1850,13 @@
         <x:v>侧面朝右（可水平翻转）</x:v>
       </x:c>
       <x:c r="I10" s="37" t="str">
-        <x:v>default</x:v>
+        <x:v>deprecated</x:v>
       </x:c>
       <x:c r="J10" s="37" t="str">
         <x:v>单资产</x:v>
       </x:c>
       <x:c r="K10" s="37" t="str">
-        <x:v>已完成</x:v>
+        <x:v>弃用</x:v>
       </x:c>
       <x:c r="L10" s="37" t="str">
         <x:v>P0</x:v>
@@ -1879,18 +1867,14 @@
       <x:c r="N10" s="37" t="str">
         <x:v>22×17 px</x:v>
       </x:c>
-      <x:c r="O10" s="37" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01/components/chr_player_capsule01_hand_r_side_v001.png</x:v>
-      </x:c>
-      <x:c r="P10" s="37" t="str">
-        <x:v>AI 母版 + 色键裁切</x:v>
-      </x:c>
+      <x:c r="O10" s="37"/>
+      <x:c r="P10" s="37"/>
       <x:c r="Q10" s="37" t="str">
         <x:v>右手; 主手; 枪手; 镜像握持</x:v>
       </x:c>
       <x:c r="R10" s="37" t="str">
         <x:f>LOWER(TRIM(C10)&amp;"|"&amp;TRIM(D10)&amp;"|"&amp;TRIM(E10)&amp;"|"&amp;TRIM(F10)&amp;"|"&amp;TRIM(H10)&amp;"|"&amp;TRIM(I10))</x:f>
-        <x:v>角色|player_component|player_capsule01|hand|侧面朝右（可水平翻转）|default</x:v>
+        <x:v>角色|player_component|player_capsule01|hand|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S10" s="37" t="str">
         <x:f>IF(A10="","",IF(COUNTIF($R$6:$R$162,R10)&gt;1,"重复","唯一"))</x:f>
@@ -1903,13 +1887,13 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V10" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="W10" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X10" s="37" t="str">
-        <x:v>运行时唯一可见手；随身体朝向在 (-19,0)/(19,0) 两个插槽镜像，不随准星连续旋转；枪械挂点同步在 x=±24 换边，枪械视觉独立读取 aim_direction</x:v>
+        <x:v>2026-08-09：旧2D玩家像素表现文件已从仓库删除；仅保留AssetID/哈希作为历史记录，替代项为 CHR-PLY-CAPSULE01-3D-BUNNY01。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1938,13 +1922,13 @@
         <x:v>侧面朝右（可水平翻转）</x:v>
       </x:c>
       <x:c r="I11" s="37" t="str">
-        <x:v>default</x:v>
+        <x:v>deprecated</x:v>
       </x:c>
       <x:c r="J11" s="37" t="str">
         <x:v>单资产</x:v>
       </x:c>
       <x:c r="K11" s="37" t="str">
-        <x:v>已完成</x:v>
+        <x:v>弃用</x:v>
       </x:c>
       <x:c r="L11" s="37" t="str">
         <x:v>P0</x:v>
@@ -1955,18 +1939,14 @@
       <x:c r="N11" s="37" t="str">
         <x:v>26×14 px</x:v>
       </x:c>
-      <x:c r="O11" s="37" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01/components/chr_player_capsule01_scarf_side_v001.png</x:v>
-      </x:c>
-      <x:c r="P11" s="37" t="str">
-        <x:v>AI 母版 + 色键裁切</x:v>
-      </x:c>
+      <x:c r="O11" s="37"/>
+      <x:c r="P11" s="37"/>
       <x:c r="Q11" s="37" t="str">
         <x:v>红围巾; 牛仔围巾; 识别色</x:v>
       </x:c>
       <x:c r="R11" s="37" t="str">
         <x:f>LOWER(TRIM(C11)&amp;"|"&amp;TRIM(D11)&amp;"|"&amp;TRIM(E11)&amp;"|"&amp;TRIM(F11)&amp;"|"&amp;TRIM(H11)&amp;"|"&amp;TRIM(I11))</x:f>
-        <x:v>角色|player_accessory|player_capsule01|scarf|侧面朝右（可水平翻转）|default</x:v>
+        <x:v>角色|player_accessory|player_capsule01|scarf|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S11" s="37" t="str">
         <x:f>IF(A11="","",IF(COUNTIF($R$6:$R$162,R11)&gt;1,"重复","唯一"))</x:f>
@@ -1979,13 +1959,13 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V11" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="W11" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X11" s="37" t="str">
-        <x:v>独立配件；位于头壳与躯干之间</x:v>
+        <x:v>2026-08-09：旧2D玩家像素表现文件已从仓库删除；仅保留AssetID/哈希作为历史记录，替代项为 CHR-PLY-CAPSULE01-3D-BUNNY01。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2014,13 +1994,13 @@
         <x:v>侧面朝右（可水平翻转）</x:v>
       </x:c>
       <x:c r="I12" s="37" t="str">
-        <x:v>default</x:v>
+        <x:v>deprecated</x:v>
       </x:c>
       <x:c r="J12" s="37" t="str">
         <x:v>评审/回归</x:v>
       </x:c>
       <x:c r="K12" s="37" t="str">
-        <x:v>已完成</x:v>
+        <x:v>弃用</x:v>
       </x:c>
       <x:c r="L12" s="37" t="str">
         <x:v>P0</x:v>
@@ -2031,18 +2011,14 @@
       <x:c r="N12" s="37" t="str">
         <x:v>1280×720 px</x:v>
       </x:c>
-      <x:c r="O12" s="37" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01/chr_player_capsule01_states_preview_v001.png</x:v>
-      </x:c>
-      <x:c r="P12" s="37" t="str">
-        <x:v>tests/verification/verify_player_pixel_art_flow.tscn</x:v>
-      </x:c>
+      <x:c r="O12" s="37"/>
+      <x:c r="P12" s="37"/>
       <x:c r="Q12" s="37" t="str">
         <x:v>六态; 验收板</x:v>
       </x:c>
       <x:c r="R12" s="37" t="str">
         <x:f>LOWER(TRIM(C12)&amp;"|"&amp;TRIM(D12)&amp;"|"&amp;TRIM(E12)&amp;"|"&amp;TRIM(F12)&amp;"|"&amp;TRIM(H12)&amp;"|"&amp;TRIM(I12))</x:f>
-        <x:v>角色|review_board|player_capsule01|preview|侧面朝右（可水平翻转）|default</x:v>
+        <x:v>角色|review_board|player_capsule01|preview|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S12" s="37" t="str">
         <x:f>IF(A12="","",IF(COUNTIF($R$6:$R$162,R12)&gt;1,"重复","唯一"))</x:f>
@@ -2053,13 +2029,13 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V12" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="W12" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X12" s="37" t="str">
-        <x:v>非运行时纹理</x:v>
+        <x:v>2026-08-09：旧2D玩家像素表现文件已从仓库删除；仅保留AssetID/哈希作为历史记录，替代项为 CHR-PLY-CAPSULE01-3D-BUNNY01。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2092,7 +2068,7 @@
         <x:v>玩家状态</x:v>
       </x:c>
       <x:c r="K13" s="37" t="str">
-        <x:v>程序占位</x:v>
+        <x:v>弃用</x:v>
       </x:c>
       <x:c r="L13" s="37" t="str">
         <x:v>P1</x:v>
@@ -2104,9 +2080,7 @@
         <x:v>待定</x:v>
       </x:c>
       <x:c r="O13" s="37" t="str"/>
-      <x:c r="P13" s="37" t="str">
-        <x:v>src/player/PlayerAvatarRenderer.gd</x:v>
-      </x:c>
+      <x:c r="P13" s="37"/>
       <x:c r="Q13" s="37" t="str"/>
       <x:c r="R13" s="37" t="str">
         <x:f>LOWER(TRIM(C13)&amp;"|"&amp;TRIM(D13)&amp;"|"&amp;TRIM(E13)&amp;"|"&amp;TRIM(F13)&amp;"|"&amp;TRIM(H13)&amp;"|"&amp;TRIM(I13))</x:f>
@@ -2121,13 +2095,13 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V13" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="W13" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
       <x:c r="X13" s="37" t="str">
-        <x:v>正式像素特效可替换绘制线段</x:v>
+        <x:v>2026-08-09：旧2D PlayerAvatarRenderer专用表现已删除；当前3D状态表现由 PlayerAvatar3D / WeaponModel3D 持有。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2160,7 +2134,7 @@
         <x:v>玩家状态</x:v>
       </x:c>
       <x:c r="K14" s="37" t="str">
-        <x:v>程序占位</x:v>
+        <x:v>弃用</x:v>
       </x:c>
       <x:c r="L14" s="37" t="str">
         <x:v>P1</x:v>
@@ -2172,9 +2146,7 @@
         <x:v>待定</x:v>
       </x:c>
       <x:c r="O14" s="37" t="str"/>
-      <x:c r="P14" s="37" t="str">
-        <x:v>src/player/PlayerAvatarRenderer.gd</x:v>
-      </x:c>
+      <x:c r="P14" s="37"/>
       <x:c r="Q14" s="37" t="str"/>
       <x:c r="R14" s="37" t="str">
         <x:f>LOWER(TRIM(C14)&amp;"|"&amp;TRIM(D14)&amp;"|"&amp;TRIM(E14)&amp;"|"&amp;TRIM(F14)&amp;"|"&amp;TRIM(H14)&amp;"|"&amp;TRIM(I14))</x:f>
@@ -2189,12 +2161,14 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V14" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="W14" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
-      <x:c r="X14" s="37" t="str"/>
+      <x:c r="X14" s="37" t="str">
+        <x:v>2026-08-09：旧2D PlayerAvatarRenderer专用表现已删除；当前3D状态表现由 PlayerAvatar3D / WeaponModel3D 持有。</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="37" t="str">
@@ -2226,7 +2200,7 @@
         <x:v>叠加状态</x:v>
       </x:c>
       <x:c r="K15" s="37" t="str">
-        <x:v>程序占位</x:v>
+        <x:v>弃用</x:v>
       </x:c>
       <x:c r="L15" s="37" t="str">
         <x:v>P2</x:v>
@@ -2238,9 +2212,7 @@
         <x:v>待定</x:v>
       </x:c>
       <x:c r="O15" s="37" t="str"/>
-      <x:c r="P15" s="37" t="str">
-        <x:v>src/player/PlayerAvatarRenderer.gd</x:v>
-      </x:c>
+      <x:c r="P15" s="37"/>
       <x:c r="Q15" s="37" t="str"/>
       <x:c r="R15" s="37" t="str">
         <x:f>LOWER(TRIM(C15)&amp;"|"&amp;TRIM(D15)&amp;"|"&amp;TRIM(E15)&amp;"|"&amp;TRIM(F15)&amp;"|"&amp;TRIM(H15)&amp;"|"&amp;TRIM(I15))</x:f>
@@ -2255,12 +2227,14 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V15" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="W15" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
-      <x:c r="X15" s="37" t="str"/>
+      <x:c r="X15" s="37" t="str">
+        <x:v>2026-08-09：旧2D PlayerAvatarRenderer专用表现已删除；当前3D状态表现由 PlayerAvatar3D / WeaponModel3D 持有。</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="37" t="str">
@@ -2292,7 +2266,7 @@
         <x:v>叠加状态</x:v>
       </x:c>
       <x:c r="K16" s="37" t="str">
-        <x:v>程序占位</x:v>
+        <x:v>弃用</x:v>
       </x:c>
       <x:c r="L16" s="37" t="str">
         <x:v>P2</x:v>
@@ -2304,9 +2278,7 @@
         <x:v>待定</x:v>
       </x:c>
       <x:c r="O16" s="37" t="str"/>
-      <x:c r="P16" s="37" t="str">
-        <x:v>src/player/PlayerAvatarRenderer.gd</x:v>
-      </x:c>
+      <x:c r="P16" s="37"/>
       <x:c r="Q16" s="37" t="str"/>
       <x:c r="R16" s="37" t="str">
         <x:f>LOWER(TRIM(C16)&amp;"|"&amp;TRIM(D16)&amp;"|"&amp;TRIM(E16)&amp;"|"&amp;TRIM(F16)&amp;"|"&amp;TRIM(H16)&amp;"|"&amp;TRIM(I16))</x:f>
@@ -2321,12 +2293,14 @@
         <x:v>待分配</x:v>
       </x:c>
       <x:c r="V16" s="54" t="n">
-        <x:v>46224</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="W16" s="37" t="str">
         <x:v>原创/待确认</x:v>
       </x:c>
-      <x:c r="X16" s="37" t="str"/>
+      <x:c r="X16" s="37" t="str">
+        <x:v>2026-08-09：旧2D PlayerAvatarRenderer专用表现已删除；当前3D状态表现由 PlayerAvatar3D / WeaponModel3D 持有。</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="37" t="str">
@@ -12163,19 +12137,19 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T156" s="70" t="str">
-        <x:v>3aeed15ba17514e5e92ddda3b7303f9f29f576abe826d3039a7b8fc080c320bb</x:v>
+        <x:v>b894e9fe05f8898bf035b7b383c27407cf027208ccf8fec65a2ba22c1f390624</x:v>
       </x:c>
       <x:c r="U156" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V156" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="W156" s="71" t="str">
         <x:v>原创 Blender/Godot 组合</x:v>
       </x:c>
       <x:c r="X156" s="70" t="str">
-        <x:v>v0.1：玩家网格位于layer2并保持cast_shadow=ON；太阳与室内灯的shadow_caster_mask包含layer1|layer2，可产生正常外部投影。玩家随身三盏灯的阴影图排除layer2，不对角色自身投影；GI关闭。</x:v>
+        <x:v>v0.1 v006：正式BunnyRig保持双手武器姿势；新增BodyJoint/LowerBodySocket；DIY body/head/hand/feet直接映射可见GLB材质；状态画廊覆盖层读数兼容结构化flashlight快照。角色网格保持layer2与现有外部灯光投影契约。</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="118" customHeight="1">
@@ -12245,13 +12219,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V157" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="W157" s="70" t="str">
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
       <x:c r="X157" s="70" t="str">
-        <x:v>v0.1 v006：身体网格与底部中心原点从v005等比放大1.5倍；Godot BodyJoint=(-0.000030,0.155022,-0.000635)。</x:v>
+        <x:v>v0.1 v006：身体网格与底部中心原点保持不变；BodyJoint新增LowerBodySocket local=(0,0.14,0)，用于裙摆/腰甲/下摆并继承全部身体程序动画。</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="118" customHeight="1">
@@ -15751,6 +15725,80 @@
       </x:c>
       <x:c r="X204" s="63" t="str">
         <x:v>正式运行OGG；WAV仅作母版；AudioManager事件=wave_start；Android/桌面统一版本化路径，禁止旧音效回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-LOWER-BODY-SOCKET</x:v>
+      </x:c>
+      <x:c r="B205" t="str">
+        <x:v>兔子主角下身配件挂点</x:v>
+      </x:c>
+      <x:c r="C205" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D205" t="str">
+        <x:v>player_accessory_socket</x:v>
+      </x:c>
+      <x:c r="E205" t="str">
+        <x:v>player_capsule01</x:v>
+      </x:c>
+      <x:c r="F205" t="str">
+        <x:v>lower_body_socket_3d_bunny01</x:v>
+      </x:c>
+      <x:c r="G205" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-BODY</x:v>
+      </x:c>
+      <x:c r="H205" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I205" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J205" t="str">
+        <x:v>3D玩家下身配件</x:v>
+      </x:c>
+      <x:c r="K205" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L205" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M205" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N205" t="str">
+        <x:v>Marker3D；BodyJoint local=(0,0.14,0)</x:v>
+      </x:c>
+      <x:c r="O205" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v006.tscn</x:v>
+      </x:c>
+      <x:c r="P205" t="str">
+        <x:v>src/player3d/PlayerAvatar3D.gd; tests/verification/verify_player3d_lower_body_socket_flow.tscn</x:v>
+      </x:c>
+      <x:c r="Q205" t="str">
+        <x:v>下身挂点;腰部挂点;裙子;裙摆;腰甲;LowerBodySocket;lower_body</x:v>
+      </x:c>
+      <x:c r="R205" t="str">
+        <x:f>LOWER(TRIM(C205)&amp;"|"&amp;TRIM(D205)&amp;"|"&amp;TRIM(E205)&amp;"|"&amp;TRIM(F205)&amp;"|"&amp;TRIM(H205)&amp;"|"&amp;TRIM(I205))</x:f>
+        <x:v>角色|player_accessory_socket|player_capsule01|lower_body_socket_3d_bunny01|俯视3d|default</x:v>
+      </x:c>
+      <x:c r="S205" t="str">
+        <x:f>IF(A205="","",IF(COUNTIF($R:$R,R205)&gt;1,"重复","唯一"))</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T205"/>
+      <x:c r="U205" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V205" s="62" t="n">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="W205" t="str">
+        <x:v>原创程序挂点</x:v>
+      </x:c>
+      <x:c r="X205" t="str">
+        <x:v>BodyJoint子节点；只承载裙摆、腰甲和下摆等表现附件；继承身体位置/旋转/缩放，不改变碰撞、移动、伤害或状态机。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -15778,7 +15826,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3916b222ff134eef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd6065c28e844407"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15930,7 +15978,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M6" s="36" t="str">
-        <x:v>无腿、无脚、无手臂</x:v>
+        <x:v>已退役（2026-08-09）：旧2D节点/纹理/Marker2D已删除；仅作历史组件记录，禁止运行时引用。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -15971,7 +16019,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="M7" s="37" t="str">
-        <x:v>红色识别色；可换其他颈部配件</x:v>
+        <x:v>已退役（2026-08-09）：旧2D节点/纹理/Marker2D已删除；仅作历史组件记录，禁止运行时引用。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -16012,7 +16060,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M8" s="37" t="str">
-        <x:v>单传感器，无人脸</x:v>
+        <x:v>已退役（2026-08-09）：旧2D节点/纹理/Marker2D已删除；仅作历史组件记录，禁止运行时引用。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -16053,7 +16101,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="M9" s="37" t="str">
-        <x:v>单手方案不进入运行时；替代项为 hand</x:v>
+        <x:v>已退役（2026-08-09）：旧2D节点/纹理/Marker2D已删除；仅作历史组件记录，禁止运行时引用。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -16094,7 +16142,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M10" s="37" t="str">
-        <x:v>手读取身体左右朝向，不读取准星连续角度</x:v>
+        <x:v>已退役（2026-08-09）：旧2D节点/纹理/Marker2D已删除；仅作历史组件记录，禁止运行时引用。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -16135,7 +16183,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M11" s="37" t="str">
-        <x:v>逻辑挂点无 PNG；垂直瞄准沿用上次左右朝向</x:v>
+        <x:v>已退役（2026-08-09）：旧2D节点/纹理/Marker2D已删除；仅作历史组件记录，禁止运行时引用。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -16258,7 +16306,7 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="M14" s="63" t="str">
-        <x:v>四主模块：Body/Head/Hand/Feet；2D旧胶囊不在本次迁移范围</x:v>
+        <x:v>正式3D表现根；旧2D胶囊已完成退役，不再属于兼容范围。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="38" customHeight="1">
@@ -17407,6 +17455,47 @@
       </x:c>
       <x:c r="M42" t="str">
         <x:v>与StowedWeaponSocketPrimary/Secondary分离；2/4/8格共用模型工厂；无碰撞；verify_backpack_equipment_flow与Metal/OpenGL实机渲染通过。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>player_capsule01_bunny01_3d</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>lower_body_socket</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>VisualRoot/BunnyRig/BodyJoint/LowerBodySocket（fallback: VisualRoot/Body/LowerBodySocket）</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>body</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>无纹理</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>Marker3D</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>bunny Body local (0,0.14,0)；fallback Body local (0,-0.36,0)</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>继承BodyJoint位置/旋转/缩放</x:v>
+      </x:c>
+      <x:c r="I43" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>裙摆/腰甲/下摆继承全部身体状态与动作覆盖</x:v>
+      </x:c>
+      <x:c r="K43" t="str">
+        <x:v>下身配件挂点</x:v>
+      </x:c>
+      <x:c r="L43" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>presentation_only；无碰撞；不改变玩法；专项验证 verify_player3d_lower_body_socket_flow.tscn。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -17989,7 +18078,7 @@
         <x:v>保持当前顶层</x:v>
       </x:c>
       <x:c r="K17" s="70" t="str">
-        <x:v>3D头顶billboard进度条；2D弹药栏</x:v>
+        <x:v>3D头顶billboard进度条；HUD弹药栏</x:v>
       </x:c>
       <x:c r="L17" s="70" t="str">
         <x:v>WeaponModel3D 唯一计时源；WeaponPoseFSM 进入 sidearm_reload/longgun_reload；右手保持握把，左手按武器类型服务</x:v>
@@ -18602,37 +18691,37 @@
         <x:v>body/head/hand/feet/hat/glasses</x:v>
       </x:c>
       <x:c r="B38" s="70" t="str">
-        <x:v>4+4+4+4+3+3</x:v>
+        <x:v>5+5+5+5+4+4</x:v>
       </x:c>
       <x:c r="C38" s="70" t="str">
-        <x:v>Body/Head/Hand/Feet/Wearables</x:v>
+        <x:v>BunnyRig Body/Head/Hands/Feet/Wearables</x:v>
       </x:c>
       <x:c r="D38" s="70" t="str">
-        <x:v>身体弹性+双脚交替+圆短尾轻摆</x:v>
+        <x:v>身体弹性+双脚交替+双耳摆动</x:v>
       </x:c>
       <x:c r="E38" s="70" t="str">
-        <x:v>手/枪同相后坐；头前探</x:v>
+        <x:v>按武器类型单/双手后坐；头前探</x:v>
       </x:c>
       <x:c r="F38" s="70" t="str">
         <x:v>整体后仰/脚随根回正</x:v>
       </x:c>
       <x:c r="G38" s="70" t="str">
-        <x:v>Hand+Socket同相</x:v>
+        <x:v>主握手+WeaponSocket同相；长枪左手托举</x:v>
       </x:c>
       <x:c r="H38" s="70" t="str">
-        <x:v>四主模块随根倾倒</x:v>
+        <x:v>全部模块随根倾倒</x:v>
       </x:c>
       <x:c r="I38" s="70" t="str">
-        <x:v>唯一手/挂点相对向量固定</x:v>
+        <x:v>LowerBodySocket随BodyJoint；武器握持按枪型</x:v>
       </x:c>
       <x:c r="J38" s="70" t="str">
-        <x:v>四主模块+双眼双耳短尾+八态覆盖</x:v>
+        <x:v>可见GLB材质+双耳+双手+双脚+八态覆盖</x:v>
       </x:c>
       <x:c r="K38" s="70" t="str">
         <x:v>3D玩家/预览场</x:v>
       </x:c>
       <x:c r="L38" s="70" t="str">
-        <x:v>Godot原生方体/三角耳/圆尾；Player3D.set_avatar_customization</x:v>
+        <x:v>Bunny GLB材质/程序挂点；Player3D.set_avatar_customization</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="38" customHeight="1">
@@ -18683,40 +18772,40 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="70" t="str">
-        <x:v>Head / Body / Feet</x:v>
+        <x:v>Head / Body / Hands / Feet</x:v>
       </x:c>
       <x:c r="B42" s="70" t="str">
-        <x:v>Eyes / Ears / TailStub / FootL / FootR</x:v>
+        <x:v>Ears / LowerBodySocket / HandL / HandR / FootL / FootR</x:v>
       </x:c>
       <x:c r="C42" s="70" t="str">
-        <x:v>2 / 2 / 1 / 2</x:v>
+        <x:v>2 / 1 / 1 / 1 / 1 / 1</x:v>
       </x:c>
       <x:c r="D42" s="70" t="str">
-        <x:v>双眼双耳稳定；短尾微摆</x:v>
+        <x:v>双耳错相呼吸；下身挂点随Body</x:v>
       </x:c>
       <x:c r="E42" s="70" t="str">
-        <x:v>双脚交替抬起；短尾轻摆</x:v>
+        <x:v>双脚交替；双手按武器类型；挂点随Body</x:v>
       </x:c>
       <x:c r="F42" s="70" t="str">
-        <x:v>随VisualRoot压缩</x:v>
+        <x:v>随VisualRoot压缩翻滚</x:v>
       </x:c>
       <x:c r="G42" s="70" t="str">
-        <x:v>随父模块后仰回正</x:v>
+        <x:v>手/耳/脚分别回弹；挂点继承Body</x:v>
       </x:c>
       <x:c r="H42" s="70" t="str">
-        <x:v>手/枪动作不牵动脚；头部继承</x:v>
+        <x:v>手枪右手/长枪双手；下身挂件不参与枪姿</x:v>
       </x:c>
       <x:c r="I42" s="70" t="str">
-        <x:v>随父模块倾倒</x:v>
+        <x:v>全部随VisualRoot倾倒</x:v>
       </x:c>
       <x:c r="J42" s="70" t="str">
-        <x:v>方头方身方手方脚；圆尾唯一例外</x:v>
+        <x:v>兔子刚性节点骨架；GLB分件</x:v>
       </x:c>
       <x:c r="K42" s="70" t="str">
-        <x:v>嘴/鼻/第二手/长尾/烘焙跨模块</x:v>
+        <x:v>禁止把下身附件烘焙进Body或加入玩法碰撞</x:v>
       </x:c>
       <x:c r="L42" s="70" t="str">
-        <x:v>节点路径+数量+步态+持枪+视觉</x:v>
+        <x:v>节点路径+材质换色+步态+持枪+LowerBodySocket专项验证</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -19397,7 +19486,7 @@
         <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v006.tscn</x:v>
       </x:c>
       <x:c r="F6" s="36" t="str">
-        <x:v>b88839fbe76e</x:v>
+        <x:v>b894e9fe05f8</x:v>
       </x:c>
       <x:c r="G6" s="36" t="str">
         <x:v>八态 + 动作覆盖层</x:v>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf445afed255f4c27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rcc0afe7668354274"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R6275beb9a61741b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Ra1da56055e89475a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R1ad8686139e64aaa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R56a8f7b5b15f412e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R2846fd3d7c8040a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R57ed26890ba14e7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R76479236688e4a35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rce3b18a56dc94948"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rf338650557d94cb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rbc845000e62e489a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R3dce54b2fe5c47a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rc831b419f7ea4426"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Rf2b614d2fec84cd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R20deda5459a44404"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10584,10 +10584,10 @@
         <x:v>俯视3D</x:v>
       </x:c>
       <x:c r="I136" s="63" t="str">
-        <x:v>muzzle_impact_damage_explosion</x:v>
+        <x:v>muzzle_impact_damage_explosion_slash_melee_impact</x:v>
       </x:c>
       <x:c r="J136" s="63" t="str">
-        <x:v>枪械/敌人/关卡</x:v>
+        <x:v>枪械/近战/敌人/关卡</x:v>
       </x:c>
       <x:c r="K136" s="63" t="str">
         <x:v>原型已接入</x:v>
@@ -10605,14 +10605,14 @@
         <x:v>assets/art/vfx/combat_3d/vfx_combat_kit_root_top3d_v001.tscn</x:v>
       </x:c>
       <x:c r="P136" s="63" t="str">
-        <x:v>src/combat3d/CombatEffect3D.gd</x:v>
+        <x:v>src/combat3d/CombatEffect3D.gd; src/combat3d/CombatEffectPool3D.gd; src/player3d/melee/PlayerMeleeCombat3D.gd</x:v>
       </x:c>
       <x:c r="Q136" s="63" t="str">
-        <x:v>枪口;命中;伤害;爆炸;3D</x:v>
+        <x:v>枪口;命中;伤害;爆炸;挥砍;近战冲击;slash;melee_impact;3D</x:v>
       </x:c>
       <x:c r="R136" s="63" t="str">
         <x:f>LOWER(TRIM(C136)&amp;"|"&amp;TRIM(D136)&amp;"|"&amp;TRIM(E136)&amp;"|"&amp;TRIM(F136)&amp;"|"&amp;TRIM(H136)&amp;"|"&amp;TRIM(I136))</x:f>
-        <x:v>特效|combat|combat_feedback|root_3d|俯视3d|muzzle_impact_damage_explosion</x:v>
+        <x:v>特效|combat|combat_feedback|root_3d|俯视3d|muzzle_impact_damage_explosion_slash_melee_impact</x:v>
       </x:c>
       <x:c r="S136" s="63" t="str">
         <x:f>IF(A136="","",IF(COUNTIF($R$6:$R$162,R136)&gt;1,"重复","唯一"))</x:f>
@@ -10631,7 +10631,7 @@
         <x:v>原创程序特效</x:v>
       </x:c>
       <x:c r="X136" s="63" t="str">
-        <x:v>effect kind、颜色与尺寸参数化，避免每把枪复制特效</x:v>
+        <x:v>effect kind、颜色、尺寸、方向与连段参数化；新增slash/melee_impact无碰撞池化种类，复用同一战斗VFX根；近战专项验证一段一弧光、逐目标爆点。</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="34" customHeight="1">
@@ -10682,7 +10682,7 @@
         <x:v>scenes/TrainingRange3D.tscn</x:v>
       </x:c>
       <x:c r="Q137" s="63" t="str">
-        <x:v>靶场;射击道;货架;56组合;三类靶</x:v>
+        <x:v>靶场;射击道;货架;59组合;三类靶</x:v>
       </x:c>
       <x:c r="R137" s="63" t="str">
         <x:f>LOWER(TRIM(C137)&amp;"|"&amp;TRIM(D137)&amp;"|"&amp;TRIM(E137)&amp;"|"&amp;TRIM(F137)&amp;"|"&amp;TRIM(H137)&amp;"|"&amp;TRIM(I137))</x:f>
@@ -10705,7 +10705,7 @@
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X137" s="63" t="str">
-        <x:v>15货架、三射击道、三靶标、重置与返回；BaseData隔离</x:v>
+        <x:v>18货架（7远程+3近战+8子弹）、三射击道、三靶标、重置与返回；BaseData隔离</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="34" customHeight="1">
@@ -15799,6 +15799,365 @@
       </x:c>
       <x:c r="X205" t="str">
         <x:v>BodyJoint子节点；只承载裙摆、腰甲和下摆等表现附件；继承身体位置/旋转/缩放，不改变碰撞、移动、伤害或状态机。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206" t="str">
+        <x:v>WPN-MELEE-BP-GREATBLADE</x:v>
+      </x:c>
+      <x:c r="B206" t="str">
+        <x:v>巨型工业断刃程序原型</x:v>
+      </x:c>
+      <x:c r="C206" t="str">
+        <x:v>武器</x:v>
+      </x:c>
+      <x:c r="D206" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="E206" t="str">
+        <x:v>bp_greatblade</x:v>
+      </x:c>
+      <x:c r="F206" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="G206"/>
+      <x:c r="H206" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I206" t="str">
+        <x:v>default / three_step_combo</x:v>
+      </x:c>
+      <x:c r="J206" t="str">
+        <x:v>手持/背负/地面/背包图标/表现页</x:v>
+      </x:c>
+      <x:c r="K206" t="str">
+        <x:v>程序占位</x:v>
+      </x:c>
+      <x:c r="L206" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M206" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N206" t="str">
+        <x:v>程序Mesh；0.82×0.30×2.42m；无碰撞</x:v>
+      </x:c>
+      <x:c r="O206" t="str">
+        <x:v>assets/art/weapons/melee_3d/wpn_melee_greatblade_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P206" t="str">
+        <x:v>src/combat3d/MeleeWeaponVisual3D.gd; src/player3d/melee/PlayerMeleeCombat3D.gd</x:v>
+      </x:c>
+      <x:c r="Q206" t="str">
+        <x:v>近战;大型武器;工业断刃;三段连击;greatblade;melee</x:v>
+      </x:c>
+      <x:c r="R206" t="str">
+        <x:v>武器|melee|bp_greatblade|root|俯视3d|default / three_step_combo</x:v>
+      </x:c>
+      <x:c r="S206" t="str">
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T206"/>
+      <x:c r="U206" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V206" s="62" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="W206" t="str">
+        <x:v>原创程序原型</x:v>
+      </x:c>
+      <x:c r="X206" t="str">
+        <x:v>总长2.42m；双手重型持握；四态动作子状态机；三段池化弧光/命中爆点与专属挥砍/冲击音频已接入；最终美术替换保留握柄原点/local -Z与稳定ID。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" t="str">
+        <x:v>WPN-MELEE-BP-WARAXE</x:v>
+      </x:c>
+      <x:c r="B207" t="str">
+        <x:v>攻城裂甲斧程序原型</x:v>
+      </x:c>
+      <x:c r="C207" t="str">
+        <x:v>武器</x:v>
+      </x:c>
+      <x:c r="D207" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="E207" t="str">
+        <x:v>bp_waraxe</x:v>
+      </x:c>
+      <x:c r="F207" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="G207"/>
+      <x:c r="H207" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I207" t="str">
+        <x:v>default / three_step_combo</x:v>
+      </x:c>
+      <x:c r="J207" t="str">
+        <x:v>手持/背负/地面/背包图标/表现页</x:v>
+      </x:c>
+      <x:c r="K207" t="str">
+        <x:v>程序占位</x:v>
+      </x:c>
+      <x:c r="L207" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M207" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N207" t="str">
+        <x:v>程序Mesh；1.18×0.34×2.62m；无碰撞</x:v>
+      </x:c>
+      <x:c r="O207" t="str">
+        <x:v>assets/art/weapons/melee_3d/wpn_melee_waraxe_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P207" t="str">
+        <x:v>src/combat3d/MeleeWeaponVisual3D.gd; src/player3d/melee/PlayerMeleeCombat3D.gd</x:v>
+      </x:c>
+      <x:c r="Q207" t="str">
+        <x:v>近战;大型武器;攻城斧;三段连击;waraxe;melee</x:v>
+      </x:c>
+      <x:c r="R207" t="str">
+        <x:v>武器|melee|bp_waraxe|root|俯视3d|default / three_step_combo</x:v>
+      </x:c>
+      <x:c r="S207" t="str">
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T207"/>
+      <x:c r="U207" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V207" s="62" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="W207" t="str">
+        <x:v>原创程序原型</x:v>
+      </x:c>
+      <x:c r="X207" t="str">
+        <x:v>总长2.62m；高伤高击退；四态动作子状态机；第三段最大弧光并降低音高/提高冲击响度；最终美术替换保留握柄原点/local -Z与稳定ID。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" t="str">
+        <x:v>AUD-SFX-MELEE-IMPACT</x:v>
+      </x:c>
+      <x:c r="B208" t="str">
+        <x:v>近战命中主层音效</x:v>
+      </x:c>
+      <x:c r="C208" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D208" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E208" t="str">
+        <x:v>melee_impact</x:v>
+      </x:c>
+      <x:c r="F208" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G208"/>
+      <x:c r="H208" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I208" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J208" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K208" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L208" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M208" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N208" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O208" t="str">
+        <x:v>src/assets/audio/sfx/melee_impact_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P208" t="str">
+        <x:v>src/assets/audio/sfx/melee_impact.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q208" t="str">
+        <x:v>melee_impact; 近战命中; 打击; 冲击; OGG; Android</x:v>
+      </x:c>
+      <x:c r="R208" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C208,D208,E208,F208,H208,I208)</x:f>
+        <x:v>音频|sfx|melee_impact|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S208" t="str">
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T208" t="str">
+        <x:v>adef9ec927d3d54967c605bfd3b779237e4f2b2b4430c30b4b656d4a204db8f8</x:v>
+      </x:c>
+      <x:c r="U208" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V208" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="W208" t="str">
+        <x:v>原创程序合成母版</x:v>
+      </x:c>
+      <x:c r="X208" t="str">
+        <x:v>正式运行OGG；WAV为原创程序合成母版；AudioManager事件=melee_impact；攻击级单次播放，敌人enemy_hit/crit_hit仍逐目标负责材质接触层。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" t="str">
+        <x:v>AUD-SFX-MELEE-SWING</x:v>
+      </x:c>
+      <x:c r="B209" t="str">
+        <x:v>近战挥砍空气层音效</x:v>
+      </x:c>
+      <x:c r="C209" t="str">
+        <x:v>音频</x:v>
+      </x:c>
+      <x:c r="D209" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="E209" t="str">
+        <x:v>melee_swing</x:v>
+      </x:c>
+      <x:c r="F209" t="str">
+        <x:v>runtime</x:v>
+      </x:c>
+      <x:c r="G209"/>
+      <x:c r="H209" t="str">
+        <x:v>全局/非空间</x:v>
+      </x:c>
+      <x:c r="I209" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J209" t="str">
+        <x:v>桌面与Android正式运行</x:v>
+      </x:c>
+      <x:c r="K209" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L209" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M209" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N209" t="str">
+        <x:v>44.1kHz / OGG Vorbis / stereo</x:v>
+      </x:c>
+      <x:c r="O209" t="str">
+        <x:v>src/assets/audio/sfx/melee_swing_v001.ogg</x:v>
+      </x:c>
+      <x:c r="P209" t="str">
+        <x:v>src/assets/audio/sfx/melee_swing.wav; src/音效接入说明.md</x:v>
+      </x:c>
+      <x:c r="Q209" t="str">
+        <x:v>melee_swing; 近战挥砍; 切风; 空气层; OGG; Android</x:v>
+      </x:c>
+      <x:c r="R209" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C209,D209,E209,F209,H209,I209)</x:f>
+        <x:v>音频|sfx|melee_swing|runtime|全局/非空间|default</x:v>
+      </x:c>
+      <x:c r="S209" t="str">
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T209" t="str">
+        <x:v>a3deeeeae55f1944ccf5df07167dad6c5cc4ac2869cf7b397383ce9828cfdad4</x:v>
+      </x:c>
+      <x:c r="U209" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V209" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="W209" t="str">
+        <x:v>原创程序合成母版</x:v>
+      </x:c>
+      <x:c r="X209" t="str">
+        <x:v>正式运行OGG；WAV为原创程序合成母版；AudioManager事件=melee_swing；每段active一次，按连段与武器类型固定调整音高/响度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" t="str">
+        <x:v>WPN-MELEE-BP-BASEBALL-BAT</x:v>
+      </x:c>
+      <x:c r="B210" t="str">
+        <x:v>废土棒球棍程序原型</x:v>
+      </x:c>
+      <x:c r="C210" t="str">
+        <x:v>武器</x:v>
+      </x:c>
+      <x:c r="D210" t="str">
+        <x:v>melee</x:v>
+      </x:c>
+      <x:c r="E210" t="str">
+        <x:v>bp_baseball_bat</x:v>
+      </x:c>
+      <x:c r="F210" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="G210"/>
+      <x:c r="H210" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I210" t="str">
+        <x:v>default / three_step_combo</x:v>
+      </x:c>
+      <x:c r="J210" t="str">
+        <x:v>手持/背负/地面/背包图标/表现页/基地贩卖机</x:v>
+      </x:c>
+      <x:c r="K210" t="str">
+        <x:v>程序占位</x:v>
+      </x:c>
+      <x:c r="L210" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M210" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N210" t="str">
+        <x:v>程序Mesh；0.28×0.28×1.48m；无碰撞</x:v>
+      </x:c>
+      <x:c r="O210" t="str">
+        <x:v>assets/art/weapons/melee_3d/wpn_melee_baseball_bat_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P210" t="str">
+        <x:v>src/combat3d/MeleeWeaponVisual3D.gd; src/player3d/melee/PlayerMeleeCombat3D.gd; tests/verification/verify_weapon_attachment_inventory_flow.gd</x:v>
+      </x:c>
+      <x:c r="Q210" t="str">
+        <x:v>近战;初级武器;棒球棍;三段连击;baseball_bat;melee;基地贩卖机</x:v>
+      </x:c>
+      <x:c r="R210" t="str">
+        <x:f>LOWER(TRIM(C210)&amp;"|"&amp;TRIM(D210)&amp;"|"&amp;TRIM(E210)&amp;"|"&amp;TRIM(F210)&amp;"|"&amp;TRIM(H210)&amp;"|"&amp;TRIM(I210))</x:f>
+        <x:v>武器|melee|bp_baseball_bat|root|俯视3d|default / three_step_combo</x:v>
+      </x:c>
+      <x:c r="S210" t="str">
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T210" t="str">
+        <x:v>700ecf26ca26d653967db40dbe48f8572387ae63b43a1428aa54721c25ca7b0a</x:v>
+      </x:c>
+      <x:c r="U210" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V210" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="W210" t="str">
+        <x:v>原创程序原型</x:v>
+      </x:c>
+      <x:c r="X210" t="str">
+        <x:v>基地45魂初级近战；三段快速挥击、第三段强化击退；复用近战四态、弧光/命中VFX和版本化音频。最终美术替换须保留握柄原点/local -Z与稳定ID。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -15826,7 +16185,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd6065c28e844407"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R805cc8c5bb994aa5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18808,6 +19167,190 @@
         <x:v>节点路径+材质换色+步态+持枪+LowerBodySocket专项验证</x:v>
       </x:c>
     </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>Player3D 近战动作子状态机 × 三段上下文（不新增顶层状态）</x:v>
+      </x:c>
+      <x:c r="B44"/>
+      <x:c r="C44"/>
+      <x:c r="D44"/>
+      <x:c r="E44"/>
+      <x:c r="F44"/>
+      <x:c r="G44"/>
+      <x:c r="H44"/>
+      <x:c r="I44"/>
+      <x:c r="J44"/>
+      <x:c r="K44"/>
+      <x:c r="L44"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>层级｜状态ID｜中文名｜唯一来源｜退出｜Body｜Head｜Hand L｜Hand R / WeaponSocket｜Scarf｜VFX/UI｜首版实现</x:v>
+      </x:c>
+      <x:c r="B45"/>
+      <x:c r="C45"/>
+      <x:c r="D45"/>
+      <x:c r="E45"/>
+      <x:c r="F45"/>
+      <x:c r="G45"/>
+      <x:c r="H45"/>
+      <x:c r="I45"/>
+      <x:c r="J45"/>
+      <x:c r="K45"/>
+      <x:c r="L45"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>动作子状态</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>ready</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>近战就绪</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>PlayerMeleeCombat3D</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>主攻击→windup</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>保持当前idle/moving</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>保持瞄准</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>双手重型握持</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>WeaponSocket稳定持械</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>低频随动</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>HUD显示近战·三段</x:v>
+      </x:c>
+      <x:c r="L46" t="str">
+        <x:v>近战动作机初态/复位态；连段=-1；无命中许可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>动作子状态</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>windup</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>挥砍前摇</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>ready或连段recovery</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>计时结束→active；非法顶层→ready</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>侧拧/下压蓄势</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>随躯干反向预备</x:v>
+      </x:c>
+      <x:c r="H47" t="str">
+        <x:v>前手锁住长柄</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>后手带WeaponSocket蓄势</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>滞后拉伸</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>动作阶段/连段编号</x:v>
+      </x:c>
+      <x:c r="L47" t="str">
+        <x:v>三段分别为左横斩、右回斩、过顶重劈前摇；输入可缓存下一段</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>动作子状态</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>active</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>命中窗口</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>windup计时完成</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>计时结束→recovery；非法顶层→ready</x:v>
+      </x:c>
+      <x:c r="F48" t="str">
+        <x:v>跨侧扭转/第三段前压</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>跟随挥砍方向</x:v>
+      </x:c>
+      <x:c r="H48" t="str">
+        <x:v>双手沿长柄同步扫过</x:v>
+      </x:c>
+      <x:c r="I48" t="str">
+        <x:v>WeaponSocket执行横扫或过顶弧</x:v>
+      </x:c>
+      <x:c r="J48" t="str">
+        <x:v>受冲量甩动</x:v>
+      </x:c>
+      <x:c r="K48" t="str">
+        <x:v>池化slash弧光/逐目标melee_impact/伤害飘字/挥砍与冲击音频</x:v>
+      </x:c>
+      <x:c r="L48" t="str">
+        <x:v>进入时唯一一次扇区查询；每段一弧光一挥砍音；逐目标爆点，多目标冲击主音去重；距离+夹角+墙体+目标去重</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>动作子状态</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>recovery</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>挥砍后摇</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>active计时完成</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>有缓存→下一段windup；否则→ready</x:v>
+      </x:c>
+      <x:c r="F49" t="str">
+        <x:v>重心回收</x:v>
+      </x:c>
+      <x:c r="G49" t="str">
+        <x:v>回正</x:v>
+      </x:c>
+      <x:c r="H49" t="str">
+        <x:v>双手恢复握持间距</x:v>
+      </x:c>
+      <x:c r="I49" t="str">
+        <x:v>WeaponSocket回到持械位</x:v>
+      </x:c>
+      <x:c r="J49" t="str">
+        <x:v>余振衰减</x:v>
+      </x:c>
+      <x:c r="K49" t="str">
+        <x:v>连段缓存提示</x:v>
+      </x:c>
+      <x:c r="L49" t="str">
+        <x:v>第三段结束强制复位；受伤/冲刺/坠落/锁定/死亡/换武器全部取消</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:L2"/>
@@ -18819,6 +19362,8 @@
     <x:mergeCell ref="A37:L37"/>
     <x:mergeCell ref="A40:L40"/>
     <x:mergeCell ref="A41:L41"/>
+    <x:mergeCell ref="A44:L44"/>
+    <x:mergeCell ref="A45:L45"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -18929,10 +19474,10 @@
         <x:v>WPN</x:v>
       </x:c>
       <x:c r="B8" s="37" t="str">
-        <x:v>枪械</x:v>
+        <x:v>武器</x:v>
       </x:c>
       <x:c r="C8" s="37" t="str">
-        <x:v>gunbody / bullet / attachment</x:v>
+        <x:v>gunbody / melee / bullet / attachment</x:v>
       </x:c>
       <x:c r="D8" s="37" t="str">
         <x:v>assets/art/weapons/</x:v>
@@ -18941,7 +19486,7 @@
         <x:v>wpn_{family}_{logic_id}_{view}_v{nnn}.{png|glb|tscn}</x:v>
       </x:c>
       <x:c r="F8" s="37" t="str">
-        <x:v>WPN-GUN-BP-PISTOL-SIDE</x:v>
+        <x:v>WPN-MELEE-BP-GREATBLADE</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -19271,7 +19816,7 @@
         <x:v>large可搜索柜</x:v>
       </x:c>
       <x:c r="G10" s="37" t="str">
-        <x:v>复用RoomFurniture3D + size=large</x:v>
+        <x:v>seed/暗室开关/遮挡视野/七怪/59组合/撤离 PASS</x:v>
       </x:c>
       <x:c r="H10" s="37" t="str">
         <x:v>F/N/O/X</x:v>
@@ -20064,31 +20609,73 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9"/>
-      <x:c r="B9"/>
-      <x:c r="C9"/>
-      <x:c r="D9"/>
-      <x:c r="E9"/>
-      <x:c r="F9"/>
-      <x:c r="G9"/>
+      <x:c r="A9" t="str">
+        <x:v>v0.1.6</x:v>
+      </x:c>
+      <x:c r="B9" s="62" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>大型近战与动作状态机</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>2武器/4动作态/三段连击</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>登记巨型工业断刃、攻城裂甲斧程序原型；新增近战ready/windup/active/recovery动作契约与专项验收。</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>不改变玩家八态移动机、碰撞体或WeaponInstance稳定身份；近战根无子弹槽。</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
-      <x:c r="A10"/>
-      <x:c r="B10"/>
-      <x:c r="C10"/>
-      <x:c r="D10"/>
-      <x:c r="E10"/>
-      <x:c r="F10"/>
-      <x:c r="G10"/>
+      <x:c r="A10" t="str">
+        <x:v>v0.1.7</x:v>
+      </x:c>
+      <x:c r="B10" s="62" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>近战打击VFX与音频反馈</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>战斗VFX/2音频/2近战</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>复用VFX-COMBAT-KIT-3D扩展slash/melee_impact；登记melee_swing/melee_impact OGG与母版哈希；同步动作状态、武器反馈和专项验收。</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>不改命中判定、伤害或稳定武器ID；VFX无碰撞；多目标冲击主音去重。</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
-      <x:c r="A11"/>
-      <x:c r="B11"/>
-      <x:c r="C11"/>
-      <x:c r="D11"/>
-      <x:c r="E11"/>
-      <x:c r="F11"/>
-      <x:c r="G11"/>
+      <x:c r="A11" t="str">
+        <x:v>v0.1.8</x:v>
+      </x:c>
+      <x:c r="B11" s="62" t="n">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>初级近战与统一枪械配件槽</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>1武器/6公共槽/7枪兼容矩阵</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>登记基地初级棒球棍；所有枪显示瞄具/枪口/弹匣/枪托/战术/特性统一位置，不支持槽禁用；配件可单拆，整枪移动保留装配树。</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>WeaponInstance schema v2兼容v1 MOUNT旧快照；不改命运永久槽或内部递归挂载。</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12"/>
@@ -20315,6 +20902,15 @@
       <x:c r="F36"/>
       <x:c r="G36"/>
     </x:row>
+    <x:row r="37">
+      <x:c r="A37"/>
+      <x:c r="B37" s="62"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
+      <x:c r="G37"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G2"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -25395,7 +25395,7 @@
       </c>
       <c r="E222" s="118" t="inlineStr">
         <is>
-          <t>future_locker_station</t>
+          <t>vault</t>
         </is>
       </c>
       <c r="F222" s="118" t="inlineStr">
@@ -25415,17 +25415,17 @@
       </c>
       <c r="I222" s="118" t="inlineStr">
         <is>
-          <t>default / 独立交互场景</t>
+          <t>default / ??????</t>
         </is>
       </c>
       <c r="J222" s="118" t="inlineStr">
         <is>
-          <t>未来基地设施池</t>
+          <t>99??????????</t>
         </is>
       </c>
       <c r="K222" s="118" t="inlineStr">
         <is>
-          <t>正式美术已入库/待玩法映射</t>
+          <t>????/???</t>
         </is>
       </c>
       <c r="L222" s="118" t="inlineStr">
@@ -25435,7 +25435,7 @@
       </c>
       <c r="M222" s="118" t="inlineStr">
         <is>
-          <t>v002</t>
+          <t>v004</t>
         </is>
       </c>
       <c r="N222" s="118" t="inlineStr">
@@ -25450,12 +25450,12 @@
       </c>
       <c r="P222" s="118" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/locker_station/prp_base_locker_station_source_v002.blend</t>
+          <t>assets/art/props/base_world_3d/source/locker_station/prp_base_locker_station_source_v004.blend</t>
         </is>
       </c>
       <c r="Q222" s="118" t="inlineStr">
         <is>
-          <t>future_locker_station; 赛博储物站; 基地设施; 未开放</t>
+          <t>vault; ???; ?????; ????</t>
         </is>
       </c>
       <c r="R222" s="118">
@@ -25469,7 +25469,7 @@
       </c>
       <c r="T222" s="118" t="inlineStr">
         <is>
-          <t>c1a89d68b72f0ce9dfbafb20526fb13ba781e0a4743cf2a5d20cf094f0f38571</t>
+          <t>b4aa2b142d31798ba8d040f4a3bbc4f0abbdbb69e070ab422d0be6bc9e48ade2</t>
         </is>
       </c>
       <c r="U222" s="118" t="inlineStr">
@@ -25478,7 +25478,7 @@
         </is>
       </c>
       <c r="V222" s="133" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="W222" s="118" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
       </c>
       <c r="X222" s="118" t="inlineStr">
         <is>
-          <t>v002按5米地板模数整体等比例强化；仅作为墙边装饰入库，不绑定当前未开放设施功能。</t>
+          <t>2026-08-11????99?????????BaseFacility3D??vault?VaultMenu???????????Visual??180?????-Z???</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="E223" s="118" t="inlineStr">
         <is>
-          <t>future_retro_tv_station</t>
+          <t>fate_collection</t>
         </is>
       </c>
       <c r="F223" s="118" t="inlineStr">
@@ -25534,17 +25534,17 @@
       </c>
       <c r="I223" s="118" t="inlineStr">
         <is>
-          <t>default / 独立交互场景</t>
+          <t>default / ??????</t>
         </is>
       </c>
       <c r="J223" s="118" t="inlineStr">
         <is>
-          <t>未来基地设施池</t>
+          <t>99?????????????</t>
         </is>
       </c>
       <c r="K223" s="118" t="inlineStr">
         <is>
-          <t>正式美术已入库/待玩法映射</t>
+          <t>????/???</t>
         </is>
       </c>
       <c r="L223" s="118" t="inlineStr">
@@ -25554,7 +25554,7 @@
       </c>
       <c r="M223" s="118" t="inlineStr">
         <is>
-          <t>v002</t>
+          <t>v004</t>
         </is>
       </c>
       <c r="N223" s="118" t="inlineStr">
@@ -25569,12 +25569,12 @@
       </c>
       <c r="P223" s="118" t="inlineStr">
         <is>
-          <t>assets/art/props/base_world_3d/source/retro_tv_station/prp_base_retro_tv_station_source_v002.blend</t>
+          <t>assets/art/props/base_world_3d/source/retro_tv_station/prp_base_retro_tv_station_source_v004.blend</t>
         </is>
       </c>
       <c r="Q223" s="118" t="inlineStr">
         <is>
-          <t>future_retro_tv_station; 复古游戏电视站; 基地设施; 未开放</t>
+          <t>fate_collection; ??????; ???????; ????</t>
         </is>
       </c>
       <c r="R223" s="118">
@@ -25588,7 +25588,7 @@
       </c>
       <c r="T223" s="118" t="inlineStr">
         <is>
-          <t>d2f8acc46acad8734487476dc5c35f6ae132f58a4b4be89a0f235edfb74122bd</t>
+          <t>fed2c5ff578efd3771f369126bd5c57f7cf2904db5faf4c8071d1802c749ba52</t>
         </is>
       </c>
       <c r="U223" s="118" t="inlineStr">
@@ -25597,7 +25597,7 @@
         </is>
       </c>
       <c r="V223" s="133" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="W223" s="118" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
       </c>
       <c r="X223" s="118" t="inlineStr">
         <is>
-          <t>v002按5米地板模数整体等比例强化；仅作为墙边装饰入库，不绑定当前未开放设施功能。</t>
+          <t>2026-08-11????99????????????BaseFacility3D??fate_collection?FateCardCollectionMenu???????????Visual??180?????-Z???</t>
         </is>
       </c>
     </row>
@@ -32365,7 +32365,41 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1"/>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>v0.1.8</t>
+        </is>
+      </c>
+      <c r="B13" s="134" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>??????????</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>vault / fate_collection</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>????????????????????????????????????????????????</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>??facility_id???????????????????????</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
     <row r="14" ht="54" customHeight="1"/>
     <row r="15" ht="72" customHeight="1"/>
     <row r="16" ht="72" customHeight="1"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,24 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0033ffb156114670"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rc2e26be926194451"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R919242f66d28405d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R96894b7af6f74d57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R4dc0ce92ceaf4b90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R5b609f4666504e34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R64425a64d5f5461e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R85665a8bc8ab484b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="R94d5c1e9369945d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R4c781f017df340fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="Rf7316a874c414a46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="Rb8ab70d28fbf4b5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R81fa0f2348c6451f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R28fc8ccd5b464580"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="Rad159b3f60d84d20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="Raf05cdbbf3944f31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R2b22935282ac4505"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="R3522b38eab424760"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0127ac44682d4feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R7e1e467d3eb045cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rcf071e60b0814c5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rf4c20de826454a01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R7da4dd0fe97f4e9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R0496e026e72a4888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Rf80ac4b71a2d49ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rba66325e1ff6496c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="R35820ff189dd4719"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R24ffccdbd22349b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R6a70d1f70e76411c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R116530e24c78471b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R78d22c4d378b42e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R16db15341bda4c23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="Rba3ee9eef5ed43a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R1e8880fac14749cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R6b6ab662236848a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Rb95333a1b9864b12"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2456,7 +2456,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="145" t="str">
-        <x:v>关卡结构、地板、墙体、走廊、楼梯、楼板与环境套件；当前 51 个独立Prefab。</x:v>
+        <x:v>关卡结构、地板、墙体、走廊、楼梯、楼板与环境套件；当前 52 个独立Prefab。</x:v>
       </x:c>
       <x:c r="B2" s="145"/>
       <x:c r="C2" s="145"/>
@@ -4623,7 +4623,7 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="P49" s="136" t="str">
-        <x:v>GLB无玩法碰撞；receive_light_no_cast；替换同路径GLB不改变功能。</x:v>
+        <x:v>GLB无玩法碰撞；cast_and_receive；替换同路径GLB不改变功能。</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -4673,7 +4673,7 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="P50" s="136" t="str">
-        <x:v>GLB无玩法碰撞；receive_light_no_cast；替换同路径GLB不改变功能。</x:v>
+        <x:v>GLB无玩法碰撞；cast_and_receive；替换同路径GLB不改变功能。</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -4723,7 +4723,7 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="P51" s="136" t="str">
-        <x:v>GLB无玩法碰撞；receive_light_no_cast；替换同路径GLB不改变功能。</x:v>
+        <x:v>GLB无玩法碰撞；cast_and_receive；替换同路径GLB不改变功能。</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -4771,7 +4771,7 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="P52" s="136" t="str">
-        <x:v>GLB仅表现；receive_light_no_cast；99层使用数量必须为0。</x:v>
+        <x:v>GLB仅表现；cast_and_receive；99层使用数量必须为0。</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -4922,6 +4922,54 @@
       </x:c>
       <x:c r="P55" s="136" t="str">
         <x:v>不使用踏步Trimesh；位置和旋转由布局tscn管理。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str">
+        <x:v>ENV-BASE100-UPPER-SHELL-30X30-H9</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>基地100层上层围护与18米封顶</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base100_upper_shell_30x30_h9/env_base100_upper_shell_30x30_h9_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="D56"/>
+      <x:c r="E56" t="str">
+        <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_source_v001.blend</x:v>
+      </x:c>
+      <x:c r="F56" t="str">
+        <x:v>可编辑组合Prefab；24块围护墙与36块封顶模块；统一挡光并投影</x:v>
+      </x:c>
+      <x:c r="G56" t="str">
+        <x:v>src/world3d/Base100UpperShell3D.gd</x:v>
+      </x:c>
+      <x:c r="H56" t="str">
+        <x:v>开</x:v>
+      </x:c>
+      <x:c r="I56" t="str">
+        <x:v>Prefab脚本</x:v>
+      </x:c>
+      <x:c r="J56" t="str">
+        <x:v>9个BoxShape3D（连续墙/东侧门洞框/屋顶）</x:v>
+      </x:c>
+      <x:c r="K56" t="str">
+        <x:v>30×30×9m上层围护；墙底9m；屋顶底18m；东门洞2.2×2.5m</x:v>
+      </x:c>
+      <x:c r="L56" t="str">
+        <x:v>room_center；local -Z为北；根缩放1</x:v>
+      </x:c>
+      <x:c r="M56" t="str">
+        <x:v>基地100层及18米屋顶</x:v>
+      </x:c>
+      <x:c r="N56" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="O56" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="P56" t="str">
+        <x:v>子Prefab=60；北墙两端普通+中间4窗；其余19普通墙，东侧1门墙；复用现有墙/地板资产，cast_and_receive；18米屋顶阻挡室外光；不恢复99/100层中间36块。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5785,7 +5833,7 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="P19" s="136" t="str">
-        <x:v>GLB无玩法碰撞；receive_light_no_cast；替换同路径GLB不改变功能。</x:v>
+        <x:v>GLB无玩法碰撞；cast_and_receive；替换同路径GLB不改变门功能。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8633,7 +8681,7 @@
         <x:v>角色|player|player_capsule01|root|俯视3d|default</x:v>
       </x:c>
       <x:c r="S6" s="301" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R6)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R6)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T6" s="301" t="str"/>
@@ -8739,7 +8787,7 @@
         <x:v>角色|player_component|player_capsule01|head|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S7" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R7)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R7)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T7" s="138" t="inlineStr">
@@ -8849,7 +8897,7 @@
         <x:v>角色|player_component|player_capsule01|body|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S8" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R8)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R8)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T8" s="138" t="inlineStr">
@@ -8959,7 +9007,7 @@
         <x:v>角色|player_component|player_capsule01|hand_l_source|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S9" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R9)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R9)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T9" s="138" t="inlineStr">
@@ -9069,7 +9117,7 @@
         <x:v>角色|player_component|player_capsule01|hand|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S10" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R10)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R10)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T10" s="138" t="inlineStr">
@@ -9179,7 +9227,7 @@
         <x:v>角色|player_accessory|player_capsule01|scarf|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S11" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R11)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R11)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T11" s="138" t="inlineStr">
@@ -9289,7 +9337,7 @@
         <x:v>角色|review_board|player_capsule01|preview|侧面朝右（可水平翻转）|deprecated</x:v>
       </x:c>
       <x:c r="S12" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R12)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R12)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T12" s="138" t="str"/>
@@ -9387,7 +9435,7 @@
         <x:v>特效|player_state|player_dash|root|侧面朝右（可水平翻转）|dashing</x:v>
       </x:c>
       <x:c r="S13" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R13)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R13)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T13" s="138" t="str"/>
@@ -9485,7 +9533,7 @@
         <x:v>特效|player_state|player_hurt|root|侧面朝右（可水平翻转）|hurt</x:v>
       </x:c>
       <x:c r="S14" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R14)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R14)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T14" s="138" t="str"/>
@@ -9583,7 +9631,7 @@
         <x:v>特效|player_overlay|player_low_hp|root|侧面朝右（可水平翻转）|low_health</x:v>
       </x:c>
       <x:c r="S15" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R15)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R15)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T15" s="138" t="str"/>
@@ -9681,7 +9729,7 @@
         <x:v>特效|player_overlay|player_silenced|root|侧面朝右（可水平翻转）|silenced</x:v>
       </x:c>
       <x:c r="S16" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R16)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R16)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T16" s="138" t="str"/>
@@ -9787,7 +9835,7 @@
         <x:v>敌人|normal_melee|melee_chaser|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S17" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R17)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R17)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T17" s="138" t="str"/>
@@ -9893,7 +9941,7 @@
         <x:v>敌人|normal_ranged|ranged_caster|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S18" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R18)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R18)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T18" s="138" t="str"/>
@@ -9995,7 +10043,7 @@
         <x:v>敌人|normal_summoner|summoner|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S19" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R19)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R19)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T19" s="138" t="str"/>
@@ -10097,7 +10145,7 @@
         <x:v>敌人|normal_tank|shielded|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S20" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R20)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R20)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T20" s="138" t="str"/>
@@ -10199,7 +10247,7 @@
         <x:v>敌人|normal_bomber|exploder|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S21" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R21)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R21)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T21" s="138" t="str"/>
@@ -10301,7 +10349,7 @@
         <x:v>敌人|normal_ambusher|ambusher|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S22" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R22)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R22)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T22" s="138" t="str"/>
@@ -10403,7 +10451,7 @@
         <x:v>敌人|boss|boss|root|侧面朝右（可水平翻转）|default</x:v>
       </x:c>
       <x:c r="S23" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R23)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R23)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T23" s="138" t="str"/>
@@ -10513,7 +10561,7 @@
         <x:v>枪械|gunbody|bp_pistol|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S24" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R24)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R24)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T24" s="138" t="inlineStr">
@@ -10627,7 +10675,7 @@
         <x:v>枪械|gunbody|bp_shotgun|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S25" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R25)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R25)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T25" s="138" t="inlineStr">
@@ -10741,7 +10789,7 @@
         <x:v>枪械|gunbody|bp_rifle|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S26" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R26)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R26)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T26" s="138" t="inlineStr">
@@ -10855,7 +10903,7 @@
         <x:v>枪械|gunbody|bp_machinegun|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S27" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R27)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R27)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T27" s="138" t="inlineStr">
@@ -10969,7 +11017,7 @@
         <x:v>枪械|gunbody|bp_sniper|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S28" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R28)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R28)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T28" s="138" t="inlineStr">
@@ -11083,7 +11131,7 @@
         <x:v>枪械|gunbody|bp_launcher|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S29" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R29)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R29)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T29" s="138" t="inlineStr">
@@ -11197,7 +11245,7 @@
         <x:v>枪械|gunbody|bp_charge|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S30" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R30)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R30)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T30" s="138" t="inlineStr">
@@ -11303,7 +11351,7 @@
         <x:v>枪械|bullet_module|mod_bullet_standard|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S31" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R31)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R31)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T31" s="138" t="str"/>
@@ -11405,7 +11453,7 @@
         <x:v>枪械|bullet_module|mod_bullet_sticky|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S32" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R32)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R32)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T32" s="138" t="str"/>
@@ -11507,7 +11555,7 @@
         <x:v>枪械|bullet_module|mod_bullet_bounce|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S33" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R33)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R33)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T33" s="138" t="str"/>
@@ -11609,7 +11657,7 @@
         <x:v>枪械|bullet_module|mod_bullet_piercing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S34" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R34)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R34)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T34" s="138" t="str"/>
@@ -11711,7 +11759,7 @@
         <x:v>枪械|bullet_module|mod_bullet_explosive|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S35" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R35)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R35)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T35" s="138" t="str"/>
@@ -11813,7 +11861,7 @@
         <x:v>枪械|bullet_module|mod_bullet_homing|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S36" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R36)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R36)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T36" s="138" t="str"/>
@@ -11915,7 +11963,7 @@
         <x:v>枪械|bullet_module|mod_bullet_blackhole|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S37" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R37)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R37)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T37" s="138" t="str"/>
@@ -12017,7 +12065,7 @@
         <x:v>枪械|bullet_module|mod_bullet_balloon|root|顶视/方向无关|default</x:v>
       </x:c>
       <x:c r="S38" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R38)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R38)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T38" s="138" t="str"/>
@@ -12119,7 +12167,7 @@
         <x:v>枪械|attachment|attach_triple_muzzle|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S39" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R39)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R39)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T39" s="138" t="str"/>
@@ -12221,7 +12269,7 @@
         <x:v>枪械|attachment|attach_rubber_stock|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S40" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R40)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R40)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T40" s="138" t="str"/>
@@ -12323,7 +12371,7 @@
         <x:v>枪械|attachment|attach_scope|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S41" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R41)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R41)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T41" s="138" t="str"/>
@@ -12425,7 +12473,7 @@
         <x:v>枪械|attachment|attach_big_mag|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S42" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R42)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R42)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T42" s="138" t="str"/>
@@ -12527,7 +12575,7 @@
         <x:v>枪械|attachment|attach_fan|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S43" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R43)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R43)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T43" s="138" t="str"/>
@@ -12629,7 +12677,7 @@
         <x:v>枪械|attachment|attach_copy_sticker|root|侧面朝右|default</x:v>
       </x:c>
       <x:c r="S44" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R44)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R44)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T44" s="138" t="str"/>
@@ -12731,7 +12779,7 @@
         <x:v>道具|consumable|item_beacon|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S45" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R45)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R45)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T45" s="138" t="str"/>
@@ -12829,7 +12877,7 @@
         <x:v>道具|key|item_room_key|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S46" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R46)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R46)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T46" s="138" t="str"/>
@@ -12927,7 +12975,7 @@
         <x:v>道具|pickup|soul_orb|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S47" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R47)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R47)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T47" s="138" t="str"/>
@@ -13025,7 +13073,7 @@
         <x:v>道具|container|container|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S48" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R48)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R48)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T48" s="138" t="str"/>
@@ -13123,7 +13171,7 @@
         <x:v>道具|pickup|room_key_pickup|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S49" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R49)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R49)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T49" s="138" t="str"/>
@@ -13225,7 +13273,7 @@
         <x:v>道具|pickup_base|ground_item|root|顶视/图标|default</x:v>
       </x:c>
       <x:c r="S50" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R50)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R50)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T50" s="138" t="str"/>
@@ -13327,7 +13375,7 @@
         <x:v>场景|biome_kit|base_world|root|顶视|default</x:v>
       </x:c>
       <x:c r="S51" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R51)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R51)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T51" s="138" t="str"/>
@@ -13429,7 +13477,7 @@
         <x:v>场景|biome_kit|iron_frontier|root|顶视|default</x:v>
       </x:c>
       <x:c r="S52" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R52)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R52)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T52" s="138" t="str"/>
@@ -13531,7 +13579,7 @@
         <x:v>场景|biome_kit|rust_foundry|root|顶视|default</x:v>
       </x:c>
       <x:c r="S53" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R53)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R53)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T53" s="138" t="str"/>
@@ -13633,7 +13681,7 @@
         <x:v>场景|biome_kit|spore_depths|root|顶视|default</x:v>
       </x:c>
       <x:c r="S54" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R54)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R54)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T54" s="138" t="str"/>
@@ -13735,7 +13783,7 @@
         <x:v>场景|biome_kit|abyss_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S55" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R55)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R55)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T55" s="138" t="str"/>
@@ -13837,7 +13885,7 @@
         <x:v>场景|biome_kit|training_range|root|顶视|default</x:v>
       </x:c>
       <x:c r="S56" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R56)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R56)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T56" s="138" t="str"/>
@@ -13939,7 +13987,7 @@
         <x:v>场景|room_dressing|room_combat|root|顶视|default</x:v>
       </x:c>
       <x:c r="S57" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R57)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R57)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T57" s="138" t="str"/>
@@ -14041,7 +14089,7 @@
         <x:v>场景|room_dressing|room_elite|root|顶视|default</x:v>
       </x:c>
       <x:c r="S58" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R58)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R58)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T58" s="138" t="str"/>
@@ -14143,7 +14191,7 @@
         <x:v>场景|room_dressing|room_boss|root|顶视|default</x:v>
       </x:c>
       <x:c r="S59" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R59)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R59)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T59" s="138" t="str"/>
@@ -14245,7 +14293,7 @@
         <x:v>场景|room_dressing|room_event|root|顶视|default</x:v>
       </x:c>
       <x:c r="S60" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R60)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R60)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T60" s="138" t="str"/>
@@ -14347,7 +14395,7 @@
         <x:v>场景|room_dressing|room_extraction|root|顶视|default</x:v>
       </x:c>
       <x:c r="S61" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R61)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R61)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T61" s="138" t="str"/>
@@ -14449,7 +14497,7 @@
         <x:v>场景|room_dressing|room_merchant|root|顶视|default</x:v>
       </x:c>
       <x:c r="S62" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R62)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R62)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T62" s="138" t="str"/>
@@ -14551,7 +14599,7 @@
         <x:v>场景|room_dressing|room_scavenge|root|顶视|default</x:v>
       </x:c>
       <x:c r="S63" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R63)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R63)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T63" s="138" t="str"/>
@@ -14653,7 +14701,7 @@
         <x:v>场景|room_dressing|room_storage|root|顶视|default</x:v>
       </x:c>
       <x:c r="S64" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R64)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R64)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T64" s="138" t="str"/>
@@ -14755,7 +14803,7 @@
         <x:v>场景|room_dressing|room_trap|root|顶视|default</x:v>
       </x:c>
       <x:c r="S65" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R65)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R65)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T65" s="138" t="str"/>
@@ -14857,7 +14905,7 @@
         <x:v>场景|room_dressing|room_upgrade|root|顶视|default</x:v>
       </x:c>
       <x:c r="S66" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R66)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R66)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T66" s="138" t="str"/>
@@ -14959,7 +15007,7 @@
         <x:v>场景|room_dressing|room_spawn|root|顶视|default</x:v>
       </x:c>
       <x:c r="S67" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R67)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R67)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T67" s="138" t="str"/>
@@ -15061,7 +15109,7 @@
         <x:v>场景|room_dressing|room_stairs|root|顶视|default</x:v>
       </x:c>
       <x:c r="S68" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R68)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R68)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T68" s="138" t="str"/>
@@ -15171,7 +15219,7 @@
         <x:v>3d道具|base_facility|mission_operations|root|top3d / local -z 正面|default / 独立交互场景</x:v>
       </x:c>
       <x:c r="S69" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R69)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R69)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T69" s="138" t="inlineStr">
@@ -15285,7 +15333,7 @@
         <x:v>3d道具|base_facility|weapon_workshop|root|top3d / local -z 正面|default / 独立交互场景</x:v>
       </x:c>
       <x:c r="S70" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R70)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R70)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T70" s="138" t="inlineStr">
@@ -15391,7 +15439,7 @@
         <x:v>场景道具|facility|base_divination|root|顶视|default</x:v>
       </x:c>
       <x:c r="S71" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R71)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R71)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T71" s="138" t="str"/>
@@ -15493,7 +15541,7 @@
         <x:v>场景道具|facility|base_vault|root|顶视|default</x:v>
       </x:c>
       <x:c r="S72" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R72)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R72)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T72" s="138" t="str"/>
@@ -15595,7 +15643,7 @@
         <x:v>场景道具|facility|base_monster_archive|root|顶视|default</x:v>
       </x:c>
       <x:c r="S73" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R73)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R73)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T73" s="138" t="str"/>
@@ -15697,7 +15745,7 @@
         <x:v>场景道具|facility|base_card_collection|root|顶视|default</x:v>
       </x:c>
       <x:c r="S74" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R74)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R74)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T74" s="138" t="str"/>
@@ -15799,7 +15847,7 @@
         <x:v>场景道具|facility|base_terminal|root|顶视|default</x:v>
       </x:c>
       <x:c r="S75" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R75)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R75)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T75" s="138" t="str"/>
@@ -15901,7 +15949,7 @@
         <x:v>场景道具|facility|dungeon_gate|root|顶视|default</x:v>
       </x:c>
       <x:c r="S76" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R76)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R76)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T76" s="138" t="str"/>
@@ -16003,7 +16051,7 @@
         <x:v>场景道具|facility|workbench|root|顶视|default</x:v>
       </x:c>
       <x:c r="S77" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R77)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R77)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T77" s="138" t="str"/>
@@ -16105,7 +16153,7 @@
         <x:v>场景道具|facility|door|root|顶视|default</x:v>
       </x:c>
       <x:c r="S78" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R78)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R78)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T78" s="138" t="str"/>
@@ -16207,7 +16255,7 @@
         <x:v>ui|screen|hud|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S79" s="304" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R79)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R79)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T79" s="304" t="str"/>
@@ -16309,7 +16357,7 @@
         <x:v>ui|screen|inventory|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S80" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R80)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R80)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T80" s="138" t="str"/>
@@ -16411,7 +16459,7 @@
         <x:v>ui|screen|merchant|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S81" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R81)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R81)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T81" s="138" t="str"/>
@@ -16513,7 +16561,7 @@
         <x:v>ui|screen|workshop|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S82" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R82)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R82)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T82" s="138" t="str"/>
@@ -16615,7 +16663,7 @@
         <x:v>ui|screen|workbench|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S83" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R83)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R83)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T83" s="138" t="str"/>
@@ -16717,7 +16765,7 @@
         <x:v>ui|screen|weapon_tree|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S84" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R84)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R84)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T84" s="138" t="str"/>
@@ -16819,7 +16867,7 @@
         <x:v>ui|screen|fate_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S85" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R85)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R85)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T85" s="138" t="str"/>
@@ -16921,7 +16969,7 @@
         <x:v>ui|screen|fate_collection|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S86" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R86)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R86)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T86" s="138" t="str"/>
@@ -17023,7 +17071,7 @@
         <x:v>ui|screen|level_select|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S87" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R87)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R87)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T87" s="138" t="str"/>
@@ -17125,7 +17173,7 @@
         <x:v>ui|screen|vault|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S88" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R88)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R88)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T88" s="138" t="str"/>
@@ -17227,7 +17275,7 @@
         <x:v>ui|screen|monster_archive|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S89" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R89)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R89)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T89" s="138" t="str"/>
@@ -17329,7 +17377,7 @@
         <x:v>ui|screen|base_menu|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S90" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R90)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R90)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T90" s="138" t="str"/>
@@ -17431,7 +17479,7 @@
         <x:v>ui|screen|mobile_controls|root|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S91" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R91)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R91)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T91" s="138" t="str"/>
@@ -17533,7 +17581,7 @@
         <x:v>特效|gameplay_vfx|explosion|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S92" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R92)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R92)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T92" s="138" t="str"/>
@@ -17635,7 +17683,7 @@
         <x:v>特效|gameplay_vfx|muzzle_flash|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S93" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R93)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R93)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T93" s="138" t="str"/>
@@ -17737,7 +17785,7 @@
         <x:v>特效|gameplay_vfx|damage_number|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S94" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R94)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R94)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T94" s="138" t="str"/>
@@ -17839,7 +17887,7 @@
         <x:v>特效|gameplay_vfx|spark|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S95" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R95)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R95)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T95" s="138" t="str"/>
@@ -17941,7 +17989,7 @@
         <x:v>特效|gameplay_vfx|room_transition|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S96" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R96)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R96)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T96" s="138" t="str"/>
@@ -18047,7 +18095,7 @@
         <x:v>特效|gameplay_vfx|health_vignette|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S97" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R97)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R97)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T97" s="138" t="str"/>
@@ -18149,7 +18197,7 @@
         <x:v>特效|gameplay_vfx|visibility_light|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S98" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R98)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R98)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T98" s="138" t="str"/>
@@ -18251,7 +18299,7 @@
         <x:v>特效|gameplay_vfx|extraction_beacon|root|顶视/屏幕空间|default</x:v>
       </x:c>
       <x:c r="S99" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R99)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R99)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T99" s="138" t="str"/>
@@ -18353,7 +18401,7 @@
         <x:v>音频|bgm|bgm_wasteland|root|不适用|default</x:v>
       </x:c>
       <x:c r="S100" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R100)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R100)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T100" s="138" t="str"/>
@@ -18451,7 +18499,7 @@
         <x:v>音频|sfx|pistol_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S101" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R101)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R101)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T101" s="138" t="str"/>
@@ -18549,7 +18597,7 @@
         <x:v>音频|sfx|rifle_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S102" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R102)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R102)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T102" s="138" t="str"/>
@@ -18647,7 +18695,7 @@
         <x:v>音频|sfx|shotgun_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S103" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R103)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R103)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T103" s="138" t="str"/>
@@ -18745,7 +18793,7 @@
         <x:v>音频|sfx|smg_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S104" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R104)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R104)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T104" s="138" t="str"/>
@@ -18843,7 +18891,7 @@
         <x:v>音频|sfx|sniper_fire|root|不适用|default</x:v>
       </x:c>
       <x:c r="S105" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R105)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R105)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T105" s="138" t="str"/>
@@ -18941,7 +18989,7 @@
         <x:v>音频|sfx|player_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S106" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R106)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R106)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T106" s="138" t="str"/>
@@ -19039,7 +19087,7 @@
         <x:v>音频|sfx|player_dash|root|不适用|default</x:v>
       </x:c>
       <x:c r="S107" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R107)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R107)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T107" s="138" t="str"/>
@@ -19137,7 +19185,7 @@
         <x:v>音频|sfx|enemy_hit|root|不适用|default</x:v>
       </x:c>
       <x:c r="S108" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R108)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R108)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T108" s="138" t="str"/>
@@ -19235,7 +19283,7 @@
         <x:v>音频|sfx|enemy_die|root|不适用|default</x:v>
       </x:c>
       <x:c r="S109" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R109)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R109)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T109" s="138" t="str"/>
@@ -19333,7 +19381,7 @@
         <x:v>音频|sfx|reload|root|不适用|default</x:v>
       </x:c>
       <x:c r="S110" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R110)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R110)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T110" s="138" t="str"/>
@@ -19431,7 +19479,7 @@
         <x:v>音频|sfx|extraction_start|root|不适用|default</x:v>
       </x:c>
       <x:c r="S111" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R111)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R111)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T111" s="138" t="str"/>
@@ -19529,7 +19577,7 @@
         <x:v>音频|sfx|extraction_done|root|不适用|default</x:v>
       </x:c>
       <x:c r="S112" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R112)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R112)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T112" s="138" t="str"/>
@@ -19639,7 +19687,7 @@
         <x:v>角色|player|player_capsule01|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S113" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R113)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R113)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T113" s="306" t="inlineStr">
@@ -19757,7 +19805,7 @@
         <x:v>角色|player|player_capsule01|body_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S114" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R114)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R114)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T114" s="136" t="inlineStr">
@@ -19877,7 +19925,7 @@
         <x:v>角色|player|player_capsule01|head_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S115" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R115)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R115)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T115" s="136" t="inlineStr">
@@ -19997,7 +20045,7 @@
         <x:v>角色|player|player_capsule01|hand_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S116" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R116)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R116)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T116" s="136" t="inlineStr">
@@ -20117,7 +20165,7 @@
         <x:v>角色|player|player_capsule01|scarf_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S117" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R117)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R117)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T117" s="136" t="inlineStr">
@@ -20237,7 +20285,7 @@
         <x:v>角色|player|player_capsule01|weapon_socket_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S118" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R118)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R118)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T118" s="136" t="inlineStr">
@@ -20357,7 +20405,7 @@
         <x:v>场景|base|base_world|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S119" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R119)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R119)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T119" s="136" t="inlineStr">
@@ -20475,7 +20523,7 @@
         <x:v>场景道具|facility|base_facility_module|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S120" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R120)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R120)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T120" s="306" t="inlineStr">
@@ -20593,7 +20641,7 @@
         <x:v>场景道具|door|dungeon_gate|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S121" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R121)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R121)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T121" s="136" t="inlineStr">
@@ -20711,7 +20759,7 @@
         <x:v>场景|review_board|base_world|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S122" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R122)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R122)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T122" s="136" t="inlineStr">
@@ -20825,7 +20873,7 @@
         <x:v>场景|room|dungeon_runtime|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S123" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R123)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R123)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T123" s="306" t="inlineStr">
@@ -20943,7 +20991,7 @@
         <x:v>场景|biome|iron_frontier|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S124" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R124)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R124)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T124" s="136" t="inlineStr">
@@ -21061,7 +21109,7 @@
         <x:v>场景|biome|rust_foundry|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S125" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R125)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R125)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T125" s="136" t="inlineStr">
@@ -21179,7 +21227,7 @@
         <x:v>场景|biome|spore_depths|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S126" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R126)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R126)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T126" s="136" t="inlineStr">
@@ -21297,7 +21345,7 @@
         <x:v>场景|biome|abyss_archive|theme_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S127" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R127)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R127)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T127" s="136" t="inlineStr">
@@ -21415,7 +21463,7 @@
         <x:v>场景道具|light|wasteland_light|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S128" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R128)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R128)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T128" s="306" t="inlineStr">
@@ -21534,7 +21582,7 @@
         <x:v>场景道具|furniture|room_furniture|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S129" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R129)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R129)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T129" s="136" t="inlineStr">
@@ -21652,7 +21700,7 @@
         <x:v>场景道具|container|search_container|root_3d|俯视3d|closed_opened</x:v>
       </x:c>
       <x:c r="S130" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R130)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R130)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T130" s="136" t="inlineStr">
@@ -21770,7 +21818,7 @@
         <x:v>场景道具|facility|service_station|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S131" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R131)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R131)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T131" s="136" t="inlineStr">
@@ -21888,7 +21936,7 @@
         <x:v>场景道具|facility|extraction_beacon|root_3d|俯视3d|locked_active_done</x:v>
       </x:c>
       <x:c r="S132" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R132)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R132)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T132" s="136" t="inlineStr">
@@ -22007,7 +22055,7 @@
         <x:v>特效|environment|hazard_field|root_3d|俯视3d|active</x:v>
       </x:c>
       <x:c r="S133" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R133)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R133)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T133" s="136" t="inlineStr">
@@ -22121,7 +22169,7 @@
         <x:v>枪械|gunbody|blueprint_gun_catalog|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S134" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R134)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R134)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T134" s="136" t="inlineStr">
@@ -22235,7 +22283,7 @@
         <x:v>敌人|normal_elite_boss|enemy_ecosystem|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S135" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R135)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R135)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T135" s="136" t="inlineStr">
@@ -22349,7 +22397,7 @@
         <x:v>特效|combat|combat_feedback|root_3d|俯视3d|muzzle_impact_damage_explosion_slash_melee_impact</x:v>
       </x:c>
       <x:c r="S136" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R136)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R136)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T136" s="136" t="inlineStr">
@@ -22463,7 +22511,7 @@
         <x:v>场景|training_range|training_range|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S137" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R137)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R137)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T137" s="136" t="inlineStr">
@@ -22581,7 +22629,7 @@
         <x:v>场景|review_board|dungeon_runtime|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S138" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R138)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R138)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T138" s="136" t="inlineStr">
@@ -22699,7 +22747,7 @@
         <x:v>场景|review_board|training_range|preview_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S139" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R139)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R139)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T139" s="136" t="inlineStr">
@@ -22817,7 +22865,7 @@
         <x:v>特效|gameplay_vfx|visibility_field|field_mesh_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S140" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R140)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R140)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T140" s="136" t="inlineStr">
@@ -22935,7 +22983,7 @@
         <x:v>ui|screen|inventory|root_3d|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S141" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R141)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R141)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T141" s="136" t="inlineStr">
@@ -23049,7 +23097,7 @@
         <x:v>ui|screen|pause|root_3d|屏幕空间|default</x:v>
       </x:c>
       <x:c r="S142" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R142)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R142)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T142" s="136" t="inlineStr">
@@ -23167,7 +23215,7 @@
         <x:v>场景道具|facility|room_light_switch|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S143" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R143)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R143)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T143" s="306" t="inlineStr">
@@ -23286,7 +23334,7 @@
         <x:v>特效|gameplay_vfx|player_flashlight|light_rig_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S144" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R144)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R144)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T144" s="136" t="inlineStr">
@@ -23405,7 +23453,7 @@
         <x:v>ui|icon|item_model_icon|root_3d|屏幕空间/3d投影|default</x:v>
       </x:c>
       <x:c r="S145" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R145)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R145)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T145" s="136" t="inlineStr">
@@ -23523,7 +23571,7 @@
         <x:v>角色|player_variant|player_capsule01|body_diy_3d|俯视3d|diy</x:v>
       </x:c>
       <x:c r="S146" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R146)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R146)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T146" s="136" t="inlineStr">
@@ -23643,7 +23691,7 @@
         <x:v>角色|player_variant|player_capsule01|head_diy_3d|俯视3d|diy</x:v>
       </x:c>
       <x:c r="S147" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R147)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R147)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T147" s="136" t="inlineStr">
@@ -23763,7 +23811,7 @@
         <x:v>角色|player_variant|player_capsule01|hand_diy_3d|俯视3d|diy</x:v>
       </x:c>
       <x:c r="S148" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R148)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R148)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T148" s="136" t="inlineStr">
@@ -23883,7 +23931,7 @@
         <x:v>角色|player_accessory|player_capsule01|hat_diy_3d|俯视3d|diy</x:v>
       </x:c>
       <x:c r="S149" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R149)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R149)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T149" s="136" t="inlineStr">
@@ -24003,7 +24051,7 @@
         <x:v>角色|player_accessory|player_capsule01|glasses_diy_3d|俯视3d|diy</x:v>
       </x:c>
       <x:c r="S150" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R150)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R150)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T150" s="136" t="inlineStr">
@@ -24123,7 +24171,7 @@
         <x:v>角色|player|player_capsule01|feet_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S151" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R151)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R151)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T151" s="136" t="inlineStr">
@@ -24243,7 +24291,7 @@
         <x:v>角色|player_accessory|player_capsule01|eyes_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S152" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R152)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R152)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T152" s="136" t="inlineStr">
@@ -24363,7 +24411,7 @@
         <x:v>角色|player_accessory|player_capsule01|ears_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S153" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R153)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R153)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T153" s="136" t="inlineStr">
@@ -24483,7 +24531,7 @@
         <x:v>角色|player_accessory|player_capsule01|tail_stub_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S154" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R154)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R154)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T154" s="136" t="inlineStr">
@@ -24603,7 +24651,7 @@
         <x:v>角色|player_variant|player_capsule01|feet_diy_3d|俯视3d|diy</x:v>
       </x:c>
       <x:c r="S155" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R155)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R155)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T155" s="136" t="inlineStr">
@@ -24723,7 +24771,7 @@
         <x:v>角色|player_variant|player_capsule01|root_3d_bunny01|俯视3d|default</x:v>
       </x:c>
       <x:c r="S156" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R156)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R156)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T156" s="306" t="inlineStr">
@@ -24841,7 +24889,7 @@
         <x:v>角色|player_component|player_capsule01|body_3d_bunny01|俯视3d|default</x:v>
       </x:c>
       <x:c r="S157" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R157)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R157)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T157" s="306" t="inlineStr">
@@ -24959,7 +25007,7 @@
         <x:v>角色|player_component|player_capsule01|head_3d_bunny01|俯视3d|default</x:v>
       </x:c>
       <x:c r="S158" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R158)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R158)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T158" s="306" t="inlineStr">
@@ -25077,7 +25125,7 @@
         <x:v>角色|player_accessory|player_capsule01|ears_3d_bunny01|俯视3d|default</x:v>
       </x:c>
       <x:c r="S159" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R159)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R159)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T159" s="306" t="inlineStr">
@@ -25195,7 +25243,7 @@
         <x:v>角色|player_component|player_capsule01|hand_3d_bunny01|俯视3d|default</x:v>
       </x:c>
       <x:c r="S160" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R160)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R160)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T160" s="306" t="inlineStr">
@@ -25313,7 +25361,7 @@
         <x:v>角色|player_component|player_capsule01|foot_l_3d_bunny01|俯视3d|moving</x:v>
       </x:c>
       <x:c r="S161" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R161)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R161)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T161" s="306" t="inlineStr">
@@ -25431,7 +25479,7 @@
         <x:v>角色|player_component|player_capsule01|foot_r_3d_bunny01|俯视3d|moving</x:v>
       </x:c>
       <x:c r="S162" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R162)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R162)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T162" s="306" t="inlineStr">
@@ -25550,7 +25598,7 @@
         </x:is>
       </x:c>
       <x:c r="S163" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R163)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R163)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T163" s="306" t="inlineStr">
@@ -25673,7 +25721,7 @@
         </x:is>
       </x:c>
       <x:c r="S164" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R164)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R164)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T164" s="306" t="inlineStr">
@@ -25792,7 +25840,7 @@
         </x:is>
       </x:c>
       <x:c r="S165" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R165)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R165)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T165" s="306" t="inlineStr">
@@ -25914,7 +25962,7 @@
         </x:is>
       </x:c>
       <x:c r="S166" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R166)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R166)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T166" s="306" t="inlineStr">
@@ -26033,7 +26081,7 @@
         </x:is>
       </x:c>
       <x:c r="S167" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R167)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R167)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T167" s="306" t="inlineStr">
@@ -26151,7 +26199,7 @@
         <x:v>场景|room_kit|tower_descent|stairwell_generic_9m|俯视3d|godot_runtime</x:v>
       </x:c>
       <x:c r="S168" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R168)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R168)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T168" s="306" t="inlineStr">
@@ -26271,7 +26319,7 @@
         <x:v>场景|room_kit|tower_descent|stairwell_rooftop_9m|俯视3d|godot_runtime</x:v>
       </x:c>
       <x:c r="S169" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R169)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R169)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T169" s="306" t="inlineStr">
@@ -26390,7 +26438,7 @@
         <x:v>角色|player_accessory_socket|player_capsule01|backpack_socket_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S170" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R170)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R170)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T170" s="136"/>
@@ -26496,7 +26544,7 @@
         <x:v>道具|equipment|equipment_backpack|root_3d|俯视3d|default</x:v>
       </x:c>
       <x:c r="S171" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R171)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R171)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T171" s="136"/>
@@ -26610,7 +26658,7 @@
         <x:v>3d道具|base_facility|base_vending|root|top3d / local -z 正面|default / 独立交互场景</x:v>
       </x:c>
       <x:c r="S172" s="309" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R172)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R172)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T172" s="309" t="inlineStr">
@@ -26728,7 +26776,7 @@
         <x:v>UI|base_facility|base_vending_shop|screen|Screen|default</x:v>
       </x:c>
       <x:c r="S173" s="309" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R173)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R173)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T173" s="309" t="n"/>
@@ -26840,7 +26888,7 @@
         <x:v>音频|sfx|ammo_empty|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S174" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R174)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R174)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T174" s="136" t="inlineStr">
@@ -26954,7 +27002,7 @@
         <x:v>音频|sfx|boss_defeat|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S175" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R175)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R175)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T175" s="136" t="inlineStr">
@@ -27068,7 +27116,7 @@
         <x:v>音频|sfx|boss_intro|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S176" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R176)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R176)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T176" s="136" t="inlineStr">
@@ -27182,7 +27230,7 @@
         <x:v>音频|sfx|boss_phase|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S177" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R177)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R177)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T177" s="136" t="inlineStr">
@@ -27296,7 +27344,7 @@
         <x:v>音频|sfx|container_open|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S178" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R178)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R178)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T178" s="136" t="inlineStr">
@@ -27410,7 +27458,7 @@
         <x:v>音频|sfx|crit_hit|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S179" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R179)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R179)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T179" s="136" t="inlineStr">
@@ -27524,7 +27572,7 @@
         <x:v>音频|sfx|door_locked|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S180" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R180)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R180)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T180" s="136" t="inlineStr">
@@ -27638,7 +27686,7 @@
         <x:v>音频|sfx|door_open|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S181" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R181)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R181)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T181" s="136" t="inlineStr">
@@ -27752,7 +27800,7 @@
         <x:v>音频|sfx|enemy_die|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S182" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R182)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R182)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T182" s="136" t="inlineStr">
@@ -27866,7 +27914,7 @@
         <x:v>音频|sfx|enemy_hit|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S183" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R183)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R183)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T183" s="136" t="inlineStr">
@@ -27980,7 +28028,7 @@
         <x:v>音频|sfx|extraction_abort|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S184" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R184)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R184)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T184" s="136" t="inlineStr">
@@ -28094,7 +28142,7 @@
         <x:v>音频|sfx|extraction_done|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S185" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R185)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R185)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T185" s="136" t="inlineStr">
@@ -28208,7 +28256,7 @@
         <x:v>音频|sfx|extraction_start|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S186" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R186)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R186)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T186" s="136" t="inlineStr">
@@ -28322,7 +28370,7 @@
         <x:v>音频|sfx|fate_card|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S187" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R187)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R187)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T187" s="136" t="inlineStr">
@@ -28436,7 +28484,7 @@
         <x:v>音频|sfx|item_pickup|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S188" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R188)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R188)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T188" s="136" t="inlineStr">
@@ -28550,7 +28598,7 @@
         <x:v>音频|sfx|laser_fire|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S189" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R189)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R189)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T189" s="136" t="inlineStr">
@@ -28664,7 +28712,7 @@
         <x:v>音频|sfx|merchant_purchase|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S190" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R190)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R190)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T190" s="136" t="inlineStr">
@@ -28778,7 +28826,7 @@
         <x:v>音频|sfx|pistol_fire|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S191" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R191)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R191)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T191" s="136" t="inlineStr">
@@ -28892,7 +28940,7 @@
         <x:v>音频|sfx|player_dash|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S192" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R192)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R192)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T192" s="136" t="inlineStr">
@@ -29006,7 +29054,7 @@
         <x:v>音频|sfx|player_hit|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S193" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R193)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R193)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T193" s="136" t="inlineStr">
@@ -29120,7 +29168,7 @@
         <x:v>音频|sfx|reload|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S194" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R194)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R194)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T194" s="136" t="inlineStr">
@@ -29234,7 +29282,7 @@
         <x:v>音频|sfx|rifle_fire|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S195" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R195)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R195)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T195" s="136" t="inlineStr">
@@ -29348,7 +29396,7 @@
         <x:v>音频|sfx|shotgun_fire|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S196" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R196)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R196)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T196" s="136" t="inlineStr">
@@ -29462,7 +29510,7 @@
         <x:v>音频|sfx|smg_fire|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S197" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R197)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R197)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T197" s="136" t="inlineStr">
@@ -29576,7 +29624,7 @@
         <x:v>音频|sfx|sniper_fire|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S198" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R198)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R198)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T198" s="136" t="inlineStr">
@@ -29690,7 +29738,7 @@
         <x:v>音频|sfx|soul_pickup|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S199" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R199)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R199)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T199" s="136" t="inlineStr">
@@ -29804,7 +29852,7 @@
         <x:v>音频|sfx|ui_click|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S200" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R200)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R200)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T200" s="136" t="inlineStr">
@@ -29918,7 +29966,7 @@
         <x:v>音频|sfx|ui_error|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S201" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R201)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R201)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T201" s="136" t="inlineStr">
@@ -30032,7 +30080,7 @@
         <x:v>音频|sfx|ui_hover|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S202" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R202)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R202)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T202" s="136" t="inlineStr">
@@ -30146,7 +30194,7 @@
         <x:v>音频|sfx|wave_clear|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S203" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R203)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R203)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T203" s="136" t="inlineStr">
@@ -30260,7 +30308,7 @@
         <x:v>音频|sfx|wave_start|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S204" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R204)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R204)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T204" s="136" t="inlineStr">
@@ -30378,7 +30426,7 @@
         <x:v>角色|player_accessory_socket|player_capsule01|lower_body_socket_3d_bunny01|俯视3d|default</x:v>
       </x:c>
       <x:c r="S205" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R205)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R205)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T205" s="136"/>
@@ -30489,7 +30537,7 @@
         </x:is>
       </x:c>
       <x:c r="S206" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R206)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R206)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T206" s="136"/>
@@ -30600,7 +30648,7 @@
         </x:is>
       </x:c>
       <x:c r="S207" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R207)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R207)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T207" s="136"/>
@@ -30710,7 +30758,7 @@
         <x:v>音频|sfx|melee_impact|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S208" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R208)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R208)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T208" s="136" t="inlineStr">
@@ -30824,7 +30872,7 @@
         <x:v>音频|sfx|melee_swing|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S209" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R209)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R209)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T209" s="136" t="inlineStr">
@@ -30938,7 +30986,7 @@
         <x:v>武器|melee|bp_baseball_bat|root|俯视3d|default / three_step_combo</x:v>
       </x:c>
       <x:c r="S210" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R210)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R210)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T210" s="136" t="inlineStr">
@@ -31052,7 +31100,7 @@
         <x:v>武器|gunbody|future_megaphone_cannon|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S211" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R211)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R211)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T211" s="138" t="inlineStr">
@@ -31166,7 +31214,7 @@
         <x:v>武器|gunbody|future_guitar_blaster|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S212" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R212)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R212)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T212" s="138" t="inlineStr">
@@ -31280,7 +31328,7 @@
         <x:v>武器|gunbody|future_spatula_rifle|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S213" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R213)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R213)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T213" s="138" t="inlineStr">
@@ -31394,7 +31442,7 @@
         <x:v>武器|gunbody|future_frying_pan_cannon|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S214" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R214)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R214)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T214" s="138" t="inlineStr">
@@ -31508,7 +31556,7 @@
         <x:v>武器|gunbody|future_scope_cannon|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S215" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R215)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R215)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T215" s="138" t="inlineStr">
@@ -31622,7 +31670,7 @@
         <x:v>武器|gunbody|future_popcorn_blaster|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S216" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R216)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R216)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T216" s="138" t="inlineStr">
@@ -31736,7 +31784,7 @@
         <x:v>武器|gunbody|future_soda_straw_blaster|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S217" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R217)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R217)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T217" s="138" t="inlineStr">
@@ -31850,7 +31898,7 @@
         <x:v>武器|gunbody|future_crocodile_cannon|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S218" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R218)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R218)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T218" s="138" t="inlineStr">
@@ -31964,7 +32012,7 @@
         <x:v>武器|gunbody|future_camera_blaster|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S219" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R219)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R219)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T219" s="138" t="inlineStr">
@@ -32078,7 +32126,7 @@
         <x:v>武器|gunbody|future_tissue_box_cannon|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S220" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R220)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R220)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T220" s="138" t="inlineStr">
@@ -32192,7 +32240,7 @@
         <x:v>武器|gunbody|future_fan_blaster|root|俯视3d / local -z 枪口|default / 标准握把与8类挂点</x:v>
       </x:c>
       <x:c r="S221" s="138" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R221)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R221)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T221" s="138" t="inlineStr">
@@ -32302,7 +32350,7 @@
         <x:v>3d道具|base_facility|vault|root|top3d / local -z 正面|default / 正式交互设施</x:v>
       </x:c>
       <x:c r="S222" s="309" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R222)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R222)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T222" s="309" t="inlineStr">
@@ -32410,7 +32458,7 @@
         <x:v>3d道具|base_facility|fate_collection|root|top3d / local -z 正面|default / 正式交互设施</x:v>
       </x:c>
       <x:c r="S223" s="309" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R223)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R223)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T223" s="309" t="inlineStr">
@@ -32522,7 +32570,7 @@
         <x:v>3d道具|decor_prop|workshop_stool|root|top3d / local -z 正面|default / 独立装饰场景</x:v>
       </x:c>
       <x:c r="S224" s="309" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R224)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R224)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T224" s="309" t="inlineStr">
@@ -32636,7 +32684,7 @@
         <x:v>3d道具|decor_prop|mission_command_chair|root|top3d / local -z 正面|default / 独立装饰场景</x:v>
       </x:c>
       <x:c r="S225" s="309" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R225)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R225)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T225" s="309" t="inlineStr">
@@ -32718,7 +32766,7 @@
         <x:v>敌人|boss|boss_abyss_archivist_95|root|top3d|default / 三阶段</x:v>
       </x:c>
       <x:c r="S226" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R226)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R226)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T226" s="136" t="str">
@@ -32792,7 +32840,7 @@
         <x:v>敌人|boss|boss_furnace_warden_90|root|top3d|default / 三阶段</x:v>
       </x:c>
       <x:c r="S227" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R227)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R227)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T227" s="136" t="str">
@@ -32866,7 +32914,7 @@
         <x:v>敌人|boss|boss_hollow_choir_85|root|top3d|default / 三阶段</x:v>
       </x:c>
       <x:c r="S228" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R228)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R228)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T228" s="136" t="str">
@@ -32940,7 +32988,7 @@
         <x:v>场景|boss_arena|arena_archive_95|dressing|top3d|default / 高模流式</x:v>
       </x:c>
       <x:c r="S229" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R229)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R229)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T229" s="136" t="str">
@@ -33014,7 +33062,7 @@
         <x:v>场景|boss_arena|arena_furnace_90|dressing|top3d|default / 高模流式</x:v>
       </x:c>
       <x:c r="S230" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R230)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R230)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T230" s="136" t="str">
@@ -33088,7 +33136,7 @@
         <x:v>场景|boss_arena|arena_choir_85|dressing|top3d|default / 高模流式</x:v>
       </x:c>
       <x:c r="S231" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R231)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R231)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T231" s="136" t="str">
@@ -33162,7 +33210,7 @@
         <x:v>音频|sfx|flashlight_charge_up|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S232" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R232)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R232)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T232" s="136" t="str">
@@ -33236,7 +33284,7 @@
         <x:v>音频|sfx|flashlight_depleted|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S233" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R233)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R233)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T233" s="136" t="str">
@@ -33310,7 +33358,7 @@
         <x:v>音频|sfx|flashlight_low_battery|runtime|全局/非空间|default</x:v>
       </x:c>
       <x:c r="S234" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R234)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R234)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T234" s="136" t="str">
@@ -33386,7 +33434,7 @@
         <x:v>场景|environment_kit_3d|base99_modular_room|root_3d|top3d / local -z 正面|default / modular</x:v>
       </x:c>
       <x:c r="S235" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R235)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R235)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T235" s="136" t="str">
@@ -33455,14 +33503,14 @@
         <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v001.blend; scripts/blender/export_base99_runtime_modules.py; src/world3d/DungeonRoom3D.gd</x:v>
       </x:c>
       <x:c r="Q236" s="136" t="str">
-        <x:v>基地99层普通墙体5×9米;base99;PaletteUV;receive_light_no_cast</x:v>
+        <x:v>基地99层普通墙体5×9米;base99;PaletteUV;cast_and_receive</x:v>
       </x:c>
       <x:c r="R236" s="136" t="str">
         <x:f>LOWER(TRIM(C236)&amp;"|"&amp;TRIM(D236)&amp;"|"&amp;TRIM(E236)&amp;"|"&amp;TRIM(F236)&amp;"|"&amp;TRIM(H236)&amp;"|"&amp;TRIM(I236))</x:f>
         <x:v>场景|environment_module_3d|base99_wall_plain_5x9|wall_plain|top3d / local -z 正面|default / visual_only</x:v>
       </x:c>
       <x:c r="S236" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R236)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R236)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T236" s="136" t="str">
@@ -33478,7 +33526,7 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X236" s="136" t="str">
-        <x:v>99层运行时14段普通墙；不放窗墙；0.30m结构碰撞归DungeonRoom3D；视觉不投影。</x:v>
+        <x:v>99层运行时14段普通墙；不放窗墙；0.30m结构碰撞归DungeonRoom3D；模型参与挡光与投影。</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
@@ -33531,14 +33579,14 @@
         <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v001.blend; scripts/blender/export_base99_runtime_modules.py; src/world3d/DungeonRoom3D.gd</x:v>
       </x:c>
       <x:c r="Q237" s="136" t="str">
-        <x:v>基地99层带门墙体5×9米;base99;PaletteUV;receive_light_no_cast</x:v>
+        <x:v>基地99层带门墙体5×9米;base99;PaletteUV;cast_and_receive</x:v>
       </x:c>
       <x:c r="R237" s="136" t="str">
         <x:f>LOWER(TRIM(C237)&amp;"|"&amp;TRIM(D237)&amp;"|"&amp;TRIM(E237)&amp;"|"&amp;TRIM(F237)&amp;"|"&amp;TRIM(H237)&amp;"|"&amp;TRIM(I237))</x:f>
         <x:v>场景|environment_module_3d|base99_wall_door_5x9|wall_door|top3d / local -z 正面|default / visual_only</x:v>
       </x:c>
       <x:c r="S237" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R237)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R237)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T237" s="136" t="str">
@@ -33554,7 +33602,7 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X237" s="136" t="str">
-        <x:v>运行时2段独立门墙；门扇、门状态机、提示、碰撞和寻路仍由Godot原系统拥有。</x:v>
+        <x:v>运行时2段独立门墙；墙体模型投影；门扇、门状态机、提示、碰撞和寻路仍由Godot原系统拥有。</x:v>
       </x:c>
     </x:row>
     <x:row r="238">
@@ -33607,14 +33655,14 @@
         <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v001.blend; scripts/blender/export_base99_runtime_modules.py; src/world3d/DungeonRoom3D.gd</x:v>
       </x:c>
       <x:c r="Q238" s="136" t="str">
-        <x:v>基地99层普通地板5×5米;base99;PaletteUV;receive_light_no_cast</x:v>
+        <x:v>基地99层普通地板5×5米;base99;PaletteUV;cast_and_receive</x:v>
       </x:c>
       <x:c r="R238" s="136" t="str">
         <x:f>LOWER(TRIM(C238)&amp;"|"&amp;TRIM(D238)&amp;"|"&amp;TRIM(E238)&amp;"|"&amp;TRIM(F238)&amp;"|"&amp;TRIM(H238)&amp;"|"&amp;TRIM(I238))</x:f>
         <x:v>场景|environment_module_3d|base99_floor_plain_5m|floor_plain|top3d / local -z 正面|default / visual_only</x:v>
       </x:c>
       <x:c r="S238" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R238)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R238)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T238" s="136" t="str">
@@ -33630,7 +33678,7 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X238" s="136" t="str">
-        <x:v>运行时18块；承重仍由TowerFloorStage地面碰撞负责；视觉不投影。</x:v>
+        <x:v>运行时18块；承重仍由TowerFloorStage地面碰撞负责；模型参与挡光与投影。</x:v>
       </x:c>
     </x:row>
     <x:row r="239">
@@ -33683,14 +33731,14 @@
         <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v001.blend; scripts/blender/export_base99_runtime_modules.py; src/world3d/DungeonRoom3D.gd</x:v>
       </x:c>
       <x:c r="Q239" s="136" t="str">
-        <x:v>基地99层铆钉铁皮带地板5×5米;base99;PaletteUV;receive_light_no_cast</x:v>
+        <x:v>基地99层铆钉铁皮带地板5×5米;base99;PaletteUV;cast_and_receive</x:v>
       </x:c>
       <x:c r="R239" s="136" t="str">
         <x:f>LOWER(TRIM(C239)&amp;"|"&amp;TRIM(D239)&amp;"|"&amp;TRIM(E239)&amp;"|"&amp;TRIM(F239)&amp;"|"&amp;TRIM(H239)&amp;"|"&amp;TRIM(I239))</x:f>
         <x:v>场景|environment_module_3d|base99_floor_rivet_5m|floor_rivet|top3d / local -z 正面|default / visual_only</x:v>
       </x:c>
       <x:c r="S239" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R239)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R239)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T239" s="136" t="str">
@@ -33706,7 +33754,7 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X239" s="136" t="str">
-        <x:v>运行时18块，与普通基地地板棋盘式互用；承重碰撞不变；视觉不投影。</x:v>
+        <x:v>运行时18块，与普通基地地板棋盘式互用；承重碰撞不变；模型参与挡光与投影。</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -33765,7 +33813,7 @@
         <x:v>场景|environment_module_3d|base_facility_art_layout|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S240" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R240)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R240)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T240" s="136" t="str">
@@ -33840,7 +33888,7 @@
         <x:v>场景|environment_module_3d|corner_L_5m|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S241" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R241)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R241)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T241" s="136" t="str">
@@ -33915,7 +33963,7 @@
         <x:v>场景|environment_module_3d|corner_L_parapet_5m|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S242" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R242)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R242)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T242" s="136" t="str">
@@ -33990,7 +34038,7 @@
         <x:v>场景|environment_module_3d|corner_T_5m|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S243" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R243)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R243)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T243" s="136" t="str">
@@ -34065,7 +34113,7 @@
         <x:v>场景|environment_module_3d|corner_X_5m|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S244" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R244)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R244)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T244" s="136" t="str">
@@ -34140,7 +34188,7 @@
         <x:v>场景|environment_module_3d|corridor_ceiling_segment|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S245" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R245)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R245)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T245" s="136" t="str">
@@ -34215,7 +34263,7 @@
         <x:v>场景|environment_module_3d|corridor_floor_segment|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S246" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R246)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R246)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T246" s="136" t="str">
@@ -34290,7 +34338,7 @@
         <x:v>场景|environment_module_3d|corridor_stair_tread|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S247" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R247)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R247)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T247" s="136" t="str">
@@ -34365,7 +34413,7 @@
         <x:v>场景|environment_module_3d|corridor_wall_segment|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S248" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R248)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R248)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T248" s="136" t="str">
@@ -34440,7 +34488,7 @@
         <x:v>场景|environment_module_3d|room_access_step|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S249" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R249)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R249)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T249" s="136" t="str">
@@ -34515,7 +34563,7 @@
         <x:v>场景|environment_module_3d|room_corner_post|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S250" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R250)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R250)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T250" s="136" t="str">
@@ -34590,7 +34638,7 @@
         <x:v>场景|environment_module_3d|room_door_lintel|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S251" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R251)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R251)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T251" s="136" t="str">
@@ -34665,7 +34713,7 @@
         <x:v>场景|environment_module_3d|room_facility_base_wall_door_side|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S252" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R252)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R252)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T252" s="136" t="str">
@@ -34740,7 +34788,7 @@
         <x:v>场景|environment_module_3d|room_facility_base_wall_lintel|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S253" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R253)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R253)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T253" s="136" t="str">
@@ -34815,7 +34863,7 @@
         <x:v>场景|environment_module_3d|room_facility_base_wall|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S254" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R254)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R254)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T254" s="136" t="str">
@@ -34890,7 +34938,7 @@
         <x:v>场景|environment_module_3d|room_floor_inset|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S255" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R255)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R255)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T255" s="136" t="str">
@@ -34965,7 +35013,7 @@
         <x:v>场景|environment_module_3d|room_floor_partition_horizontal|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S256" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R256)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R256)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T256" s="136" t="str">
@@ -35040,7 +35088,7 @@
         <x:v>场景|environment_module_3d|room_floor_partition_vertical|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S257" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R257)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R257)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T257" s="136" t="str">
@@ -35115,7 +35163,7 @@
         <x:v>场景|environment_module_3d|room_floor_seam_strip|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S258" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R258)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R258)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T258" s="136" t="str">
@@ -35190,7 +35238,7 @@
         <x:v>场景|environment_module_3d|room_floor|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S259" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R259)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R259)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T259" s="136" t="str">
@@ -35265,7 +35313,7 @@
         <x:v>场景|environment_module_3d|room_rooftop_descent_marker|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S260" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R260)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R260)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T260" s="136" t="str">
@@ -35340,7 +35388,7 @@
         <x:v>场景|environment_module_3d|room_rooftop_facade_band|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S261" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R261)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R261)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T261" s="136" t="str">
@@ -35415,7 +35463,7 @@
         <x:v>场景|environment_module_3d|room_rooftop_facade|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S262" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R262)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R262)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T262" s="136" t="str">
@@ -35490,7 +35538,7 @@
         <x:v>场景|environment_module_3d|room_rooftop_rail_post|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S263" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R263)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R263)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T263" s="136" t="str">
@@ -35565,7 +35613,7 @@
         <x:v>场景|environment_module_3d|room_rooftop_railing_lower|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S264" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R264)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R264)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T264" s="136" t="str">
@@ -35640,7 +35688,7 @@
         <x:v>场景|environment_module_3d|room_rooftop_railing_upper|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S265" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R265)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R265)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T265" s="136" t="str">
@@ -35715,7 +35763,7 @@
         <x:v>场景|environment_module_3d|room_rooftop_stair_frame_lintel|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S266" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R266)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R266)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T266" s="136" t="str">
@@ -35790,7 +35838,7 @@
         <x:v>场景|environment_module_3d|room_rooftop_stair_frame_post|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S267" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R267)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R267)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T267" s="136" t="str">
@@ -35865,7 +35913,7 @@
         <x:v>场景|environment_module_3d|room_stair_lobby_route_guide|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S268" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R268)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R268)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T268" s="136" t="str">
@@ -35940,7 +35988,7 @@
         <x:v>场景|environment_module_3d|room_stair_lobby_threshold_guide|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S269" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R269)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R269)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T269" s="136" t="str">
@@ -36015,7 +36063,7 @@
         <x:v>场景|environment_module_3d|room_vertical_access_marker_label|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S270" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R270)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R270)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T270" s="136" t="str">
@@ -36090,7 +36138,7 @@
         <x:v>场景|environment_module_3d|room_wall_door_segment|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S271" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R271)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R271)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T271" s="136" t="str">
@@ -36165,7 +36213,7 @@
         <x:v>场景|environment_module_3d|room_wall_segment|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S272" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R272)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R272)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T272" s="136" t="str">
@@ -36240,7 +36288,7 @@
         <x:v>场景|environment_module_3d|tower_wall_parapet_door_5m|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S273" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R273)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R273)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T273" s="136" t="str">
@@ -36315,7 +36363,7 @@
         <x:v>场景道具|facility|base_facility_light_grid|root_3d|top3d / local -z 正面|default / prefab</x:v>
       </x:c>
       <x:c r="S274" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R274)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R274)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T274" s="136" t="str">
@@ -36384,14 +36432,14 @@
         <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v001.blend; scripts/blender/export_base99_runtime_modules.py; src/world3d/DungeonRoom3D.gd</x:v>
       </x:c>
       <x:c r="Q275" s="136" t="str">
-        <x:v>基地99层带窗墙体5×9米;base99;PaletteUV;receive_light_no_cast</x:v>
+        <x:v>基地99层带窗墙体5×9米;base99;PaletteUV;cast_and_receive</x:v>
       </x:c>
       <x:c r="R275" s="136" t="str">
         <x:f>LOWER(TRIM(C275)&amp;"|"&amp;TRIM(D275)&amp;"|"&amp;TRIM(E275)&amp;"|"&amp;TRIM(F275)&amp;"|"&amp;TRIM(H275)&amp;"|"&amp;TRIM(I275))</x:f>
         <x:v>场景|environment_module_3d|base99_wall_window_5x9|wall_window|top3d / local -z 正面|default / visual_only</x:v>
       </x:c>
       <x:c r="S275" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R275)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R275)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T275" s="136" t="str">
@@ -36407,7 +36455,7 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X275" s="136" t="str">
-        <x:v>100层上层围护专用窗墙；99层实例数为0；视觉不投影，禁止混入99层9米普通墙圈。</x:v>
+        <x:v>100层上层围护专用窗墙；99层实例数为0；模型参与挡光与投影，禁止混入99层9米普通墙圈。</x:v>
       </x:c>
     </x:row>
     <x:row r="276">
@@ -36460,14 +36508,14 @@
         <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v001.blend; scripts/blender/export_base99_runtime_modules.py; src/world3d/DungeonRoom3D.gd</x:v>
       </x:c>
       <x:c r="Q276" s="136" t="str">
-        <x:v>基地99层7米楼中楼楼板;base99;PaletteUV;receive_light_no_cast</x:v>
+        <x:v>基地99层7米楼中楼楼板;base99;PaletteUV;cast_and_receive</x:v>
       </x:c>
       <x:c r="R276" s="136" t="str">
         <x:f>LOWER(TRIM(C276)&amp;"|"&amp;TRIM(D276)&amp;"|"&amp;TRIM(E276)&amp;"|"&amp;TRIM(F276)&amp;"|"&amp;TRIM(H276)&amp;"|"&amp;TRIM(I276))</x:f>
         <x:v>场景|environment_module_3d|base99_mezzanine_20x10_z7|mezzanine|top3d / local -z 正面|default / visual_only</x:v>
       </x:c>
       <x:c r="S276" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R276)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R276)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T276" s="136" t="str">
@@ -36483,7 +36531,7 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X276" s="136" t="str">
-        <x:v>实例位于基地美术布局tscn；Prefab自带简化楼板承重面与camera_stair_slab，移动实例时碰撞同步。</x:v>
+        <x:v>实例位于基地美术布局tscn；Prefab自带简化楼板承重面与camera_stair_slab；模型投影，移动实例时碰撞同步。</x:v>
       </x:c>
     </x:row>
     <x:row r="277">
@@ -36536,14 +36584,14 @@
         <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v001.blend; scripts/blender/export_base99_runtime_modules.py; src/world3d/DungeonRoom3D.gd</x:v>
       </x:c>
       <x:c r="Q277" s="136" t="str">
-        <x:v>基地99层7米L型楼梯;base99;PaletteUV;receive_light_no_cast</x:v>
+        <x:v>基地99层7米L型楼梯;base99;PaletteUV;cast_and_receive</x:v>
       </x:c>
       <x:c r="R277" s="136" t="str">
         <x:f>LOWER(TRIM(C277)&amp;"|"&amp;TRIM(D277)&amp;"|"&amp;TRIM(E277)&amp;"|"&amp;TRIM(F277)&amp;"|"&amp;TRIM(H277)&amp;"|"&amp;TRIM(I277))</x:f>
         <x:v>场景|environment_module_3d|base99_stair_l_z7|stair_l|top3d / local -z 正面|default / visual_only</x:v>
       </x:c>
       <x:c r="S277" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R277)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R277)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T277" s="136" t="str">
@@ -36559,7 +36607,7 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X277" s="136" t="str">
-        <x:v>实例位于基地美术布局tscn；Prefab自带两段斜坡+转角平台碰撞，避免踏步Trimesh卡住角色。</x:v>
+        <x:v>实例位于基地美术布局tscn；可行走坡面与camera_stair_slab保持原规则；模型参与挡光与投影。</x:v>
       </x:c>
     </x:row>
     <x:row r="278">
@@ -36612,14 +36660,14 @@
         <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v001.blend; scripts/blender/export_base99_runtime_modules.py; src/world3d/DungeonRoom3D.gd</x:v>
       </x:c>
       <x:c r="Q278" s="136" t="str">
-        <x:v>基地99层二楼外门2米小楼梯;base99;PaletteUV;receive_light_no_cast</x:v>
+        <x:v>基地99层二楼外门2米小楼梯;base99;PaletteUV;cast_and_receive</x:v>
       </x:c>
       <x:c r="R278" s="136" t="str">
         <x:f>LOWER(TRIM(C278)&amp;"|"&amp;TRIM(D278)&amp;"|"&amp;TRIM(E278)&amp;"|"&amp;TRIM(F278)&amp;"|"&amp;TRIM(H278)&amp;"|"&amp;TRIM(I278))</x:f>
         <x:v>场景|environment_module_3d|base99_stair_exterior_h2|stair_exterior|top3d / local -z 正面|default / visual_only</x:v>
       </x:c>
       <x:c r="S278" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R278)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R278)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T278" s="136" t="str">
@@ -36635,7 +36683,7 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X278" s="136" t="str">
-        <x:v>实例位于基地美术布局tscn；Prefab自带可行走斜坡碰撞，从7米完成面通向9米门槛。</x:v>
+        <x:v>实例位于基地美术布局tscn；简化坡面与camera_stair_slab保持原规则；模型参与挡光与投影。</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
@@ -36688,14 +36736,14 @@
         <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v001.blend; scripts/blender/export_base99_runtime_modules.py; src/world3d/RoomDoor3D.gd</x:v>
       </x:c>
       <x:c r="Q279" s="136" t="str">
-        <x:v>基地99层2.2×2.5米滑升门扇;base99;PaletteUV;receive_light_no_cast</x:v>
+        <x:v>基地99层2.2×2.5米滑升门扇;base99;PaletteUV;cast_and_receive</x:v>
       </x:c>
       <x:c r="R279" s="136" t="str">
         <x:f>LOWER(TRIM(C279)&amp;"|"&amp;TRIM(D279)&amp;"|"&amp;TRIM(E279)&amp;"|"&amp;TRIM(F279)&amp;"|"&amp;TRIM(H279)&amp;"|"&amp;TRIM(I279))</x:f>
         <x:v>场景|facility_visual_3d|base99_door_lift_2p2x2p5|door_leaf|top3d / local -z 正面|default / visual_only</x:v>
       </x:c>
       <x:c r="S279" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$279,R279)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$280,R279)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T279" s="136" t="str">
@@ -36711,7 +36759,83 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X279" s="136" t="str">
-        <x:v>只替换RoomDoor3D动画视觉；碰撞、锁定、提示和信号不变；视觉不投影。</x:v>
+        <x:v>只替换RoomDoor3D动画视觉；模型投影；碰撞、锁定、提示和信号不变。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" t="str">
+        <x:v>ENV-BASE100-UPPER-SHELL-30X30-H9</x:v>
+      </x:c>
+      <x:c r="B280" t="str">
+        <x:v>基地100层上层围护与18米封顶</x:v>
+      </x:c>
+      <x:c r="C280" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D280" t="str">
+        <x:v>environment_kit_3d</x:v>
+      </x:c>
+      <x:c r="E280" t="str">
+        <x:v>base100_upper_shell_30x30_h9</x:v>
+      </x:c>
+      <x:c r="F280" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G280" t="str">
+        <x:v>ENV-BASE99-MODULAR-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H280" t="str">
+        <x:v>Top3D / local -Z 正面</x:v>
+      </x:c>
+      <x:c r="I280" t="str">
+        <x:v>default / prefab</x:v>
+      </x:c>
+      <x:c r="J280" t="str">
+        <x:v>场景通用组件</x:v>
+      </x:c>
+      <x:c r="K280" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="L280" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M280" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N280" t="str">
+        <x:v>30×30m围护；本地9—18m墙体；18m封顶</x:v>
+      </x:c>
+      <x:c r="O280" t="str">
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base100_upper_shell_30x30_h9/env_base100_upper_shell_30x30_h9_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P280" t="str">
+        <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_source_v001.blend; src/world3d/Base100UpperShell3D.gd; assets/art/3D模型资产目录与命名规范.md</x:v>
+      </x:c>
+      <x:c r="Q280" t="str">
+        <x:v>基地100层;上层围护;北侧窗墙;18米封顶;可编辑Prefab;cast_and_receive</x:v>
+      </x:c>
+      <x:c r="R280" t="str">
+        <x:f>LOWER(TRIM(C280)&amp;"|"&amp;TRIM(D280)&amp;"|"&amp;TRIM(E280)&amp;"|"&amp;TRIM(F280)&amp;"|"&amp;TRIM(H280)&amp;"|"&amp;TRIM(I280))</x:f>
+        <x:v>场景|environment_kit_3d|base100_upper_shell_30x30_h9|root_3d|top3d / local -z 正面|default / prefab</x:v>
+      </x:c>
+      <x:c r="S280" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$280,R280)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T280" t="str">
+        <x:v>127b01c6d9f554621c84eb06b028133665042ca3ce57b3c938c533b6d5877bc1</x:v>
+      </x:c>
+      <x:c r="U280" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V280" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="W280" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X280" t="str">
+        <x:v>北墙两端普通+中间4窗；其余19普通墙，东侧1门墙；18米屋顶挡光；围护与封顶统一投影；不恢复99/100层中间36块。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -36739,7 +36863,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9046dc71eaf43a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R312686a395b54d32"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43528,22 +43652,50 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="86" customHeight="1">
-      <x:c r="A21" s="136"/>
-      <x:c r="B21" s="136"/>
-      <x:c r="C21" s="136"/>
-      <x:c r="D21" s="136"/>
-      <x:c r="E21" s="136"/>
-      <x:c r="F21" s="136"/>
-      <x:c r="G21" s="136"/>
+      <x:c r="A21" s="136" t="str">
+        <x:v>v0.1.17</x:v>
+      </x:c>
+      <x:c r="B21" s="136" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C21" s="136" t="str">
+        <x:v>基地100层上层围护与18米封顶</x:v>
+      </x:c>
+      <x:c r="D21" s="136" t="str">
+        <x:v>1个组合Prefab/24块墙/36块封顶/9片结构碰撞</x:v>
+      </x:c>
+      <x:c r="E21" s="136" t="str">
+        <x:v>按Blender母版加入9—18米上层围护：北侧中间4窗、其余19普通墙、东侧1门墙；18米复用5米地板模块封顶。</x:v>
+      </x:c>
+      <x:c r="F21" s="136" t="str">
+        <x:v>新增组合仅负责表现与结构碰撞；99层14普通墙、2功能门、设施、中庭开洞和摄像机规则不变；全部不投影。</x:v>
+      </x:c>
+      <x:c r="G21" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="72" customHeight="1">
-      <x:c r="A22" s="136"/>
-      <x:c r="B22" s="136"/>
-      <x:c r="C22" s="136"/>
-      <x:c r="D22" s="136"/>
-      <x:c r="E22" s="136"/>
-      <x:c r="F22" s="136"/>
-      <x:c r="G22" s="136"/>
+      <x:c r="A22" s="136" t="str">
+        <x:v>v0.1.18</x:v>
+      </x:c>
+      <x:c r="B22" s="136" t="n">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C22" s="136" t="str">
+        <x:v>场景组件真实投影规则</x:v>
+      </x:c>
+      <x:c r="D22" s="136" t="str">
+        <x:v>基地墙/地板/门/楼板/楼梯/封顶/设施模型</x:v>
+      </x:c>
+      <x:c r="E22" s="136" t="str">
+        <x:v>统一cast_shadow=ON；封顶阻挡室外光；中央灯开关形成真实明暗切换。</x:v>
+      </x:c>
+      <x:c r="F22" s="136" t="str">
+        <x:v>只改渲染投影，不改碰撞、门、设施、楼层功能；纯VFX/光池/玩家/UI不纳入场景模型规则。</x:v>
+      </x:c>
+      <x:c r="G22" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="78" customHeight="1">
       <x:c r="A23" s="136"/>
@@ -43814,16 +43966,16 @@
         <x:v>3D-场景通用</x:v>
       </x:c>
       <x:c r="C5" s="277" t="n">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D5" s="277" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="277" t="n">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F5" s="277" t="n">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G5" s="278" t="str">
         <x:v>关卡结构、地板、墙体、走廊、楼梯、楼板与环境套件</x:v>
@@ -44139,19 +44291,19 @@
         <x:v>9个分类分页</x:v>
       </x:c>
       <x:c r="C14" s="315" t="n">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D14" s="315" t="n">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E14" s="315" t="n">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F14" s="315" t="n">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G14" s="316" t="str">
-        <x:v>更新日期：2026-08-18；基地99层九件正式接入</x:v>
+        <x:v>更新日期：2026-08-18；基地100层上层围护与18米封顶接入</x:v>
       </x:c>
       <x:c r="H14" s="136"/>
       <x:c r="I14" s="136"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,24 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0127ac44682d4feb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R7e1e467d3eb045cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rcf071e60b0814c5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rf4c20de826454a01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R7da4dd0fe97f4e9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R0496e026e72a4888"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Rf80ac4b71a2d49ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rba66325e1ff6496c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="R35820ff189dd4719"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R24ffccdbd22349b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R6a70d1f70e76411c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R116530e24c78471b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R78d22c4d378b42e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R16db15341bda4c23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="Rba3ee9eef5ed43a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R1e8880fac14749cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R6b6ab662236848a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Rb95333a1b9864b12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R111badf2faa4436f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rf7216e33164d410c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rfa13bef7b1204d3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R34782d7f354d4ad7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rb2f49475948646de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R0d1a957fa8294355"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R86ee98e9878f4cf7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R5b7fd96b0adc47c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Re43a9b6df2714656"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R2ee6d32d33184c32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R4b1b60d4f0e7483d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R810920693ae24707"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R1511a47ea7da471f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="Rcb69e40406de4a78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="R798ba1463c1c478a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R258657c401384f9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R4219a7cdcc414a13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Rfde33724019b4035"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R6e5bf74ed43240d8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -214,7 +215,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="41">
+  <x:fills count="44">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -416,8 +417,23 @@
         <x:fgColor rgb="FFE2E8F0"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17324D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE6F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F75B5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="40">
+  <x:borders count="41">
     <x:border/>
     <x:border>
       <x:left style="medium">
@@ -815,11 +831,25 @@
         <x:color rgb="FFD9E2F3"/>
       </x:top>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="333">
+  <x:cellXfs count="347">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -1607,6 +1637,34 @@
     <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="43" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="43" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="43" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="43" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="28" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -2456,7 +2514,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="145" t="str">
-        <x:v>关卡结构、地板、墙体、走廊、楼梯、楼板与环境套件；当前 52 个独立Prefab。</x:v>
+        <x:v>关卡结构、地板、墙体、走廊、楼梯、楼板与环境套件；当前 55 个独立Prefab。</x:v>
       </x:c>
       <x:c r="B2" s="145"/>
       <x:c r="C2" s="145"/>
@@ -4970,6 +5028,156 @@
       </x:c>
       <x:c r="P56" t="str">
         <x:v>子Prefab=60；北墙两端普通+中间4窗；其余19普通墙，东侧1门墙；复用现有墙/地板资产，cast_and_receive；18米屋顶阻挡室外光；不恢复99/100层中间36块。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="78" customHeight="1">
+      <x:c r="A57" s="136" t="str">
+        <x:v>ENV-BASE99-MEZZANINE-20X10-Z5</x:v>
+      </x:c>
+      <x:c r="B57" s="136" t="str">
+        <x:v>基地99层5米楼中楼楼板</x:v>
+      </x:c>
+      <x:c r="C57" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_mezzanine_20x10_z5/env_base99_mezzanine_20x10_z5_root_top3d_v002.tscn</x:v>
+      </x:c>
+      <x:c r="D57" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/components/env_base99_mezzanine_20x10_z5/env_base99_mezzanine_20x10_z5_visual_top3d_v002.glb</x:v>
+      </x:c>
+      <x:c r="E57" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v002.blend</x:v>
+      </x:c>
+      <x:c r="F57" s="136" t="str">
+        <x:v>5米承重楼板；连续栏杆阻挡；真实投影</x:v>
+      </x:c>
+      <x:c r="G57" s="136" t="str">
+        <x:v>src/world3d/Base99WalkableModule3D.gd</x:v>
+      </x:c>
+      <x:c r="H57" s="136" t="str">
+        <x:v>开</x:v>
+      </x:c>
+      <x:c r="I57" s="136" t="str">
+        <x:v>Prefab自身</x:v>
+      </x:c>
+      <x:c r="J57" s="136" t="str">
+        <x:v>连续Box楼板+独立栏杆Box</x:v>
+      </x:c>
+      <x:c r="K57" s="136" t="str">
+        <x:v>20.2475×10.2475×5.93m；台面5m</x:v>
+      </x:c>
+      <x:c r="L57" s="136" t="str">
+        <x:v>底面中心；Blender -Y / Godot -Z</x:v>
+      </x:c>
+      <x:c r="M57" s="136" t="str">
+        <x:v>99层基地楼中楼</x:v>
+      </x:c>
+      <x:c r="N57" s="136" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="O57" s="136" t="str">
+        <x:v>v002</x:v>
+      </x:c>
+      <x:c r="P57" s="136" t="str">
+        <x:v>根缩放1；替代Z7版本；视觉/碰撞/功能分离</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="78" customHeight="1">
+      <x:c r="A58" s="136" t="str">
+        <x:v>ENV-BASE99-STAIR-L-Z5</x:v>
+      </x:c>
+      <x:c r="B58" s="136" t="str">
+        <x:v>基地99层5米L型楼梯</x:v>
+      </x:c>
+      <x:c r="C58" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_stair_l_z5/env_base99_stair_l_z5_root_top3d_v002.tscn</x:v>
+      </x:c>
+      <x:c r="D58" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/components/env_base99_stair_l_z5/env_base99_stair_l_z5_visual_top3d_v002.glb</x:v>
+      </x:c>
+      <x:c r="E58" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v002.blend</x:v>
+      </x:c>
+      <x:c r="F58" s="136" t="str">
+        <x:v>0→2.5→5米双跑L梯；扶手真实投影与阻挡</x:v>
+      </x:c>
+      <x:c r="G58" s="136" t="str">
+        <x:v>src/world3d/Base99WalkableModule3D.gd</x:v>
+      </x:c>
+      <x:c r="H58" s="136" t="str">
+        <x:v>开</x:v>
+      </x:c>
+      <x:c r="I58" s="136" t="str">
+        <x:v>Prefab自身</x:v>
+      </x:c>
+      <x:c r="J58" s="136" t="str">
+        <x:v>两段连续斜坡+平台+独立扶手Box</x:v>
+      </x:c>
+      <x:c r="K58" s="136" t="str">
+        <x:v>9.2176×10.538×5.91015m；终点5m</x:v>
+      </x:c>
+      <x:c r="L58" s="136" t="str">
+        <x:v>底面中心；Blender -Y / Godot -Z</x:v>
+      </x:c>
+      <x:c r="M58" s="136" t="str">
+        <x:v>99层基地一楼至楼中楼</x:v>
+      </x:c>
+      <x:c r="N58" s="136" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="O58" s="136" t="str">
+        <x:v>v002</x:v>
+      </x:c>
+      <x:c r="P58" s="136" t="str">
+        <x:v>不用逐级碰撞；坡脚/平台/坡顶连续；替代Z7版本</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="78" customHeight="1">
+      <x:c r="A59" s="136" t="str">
+        <x:v>ENV-BASE99-STAIR-EXTERIOR-H4</x:v>
+      </x:c>
+      <x:c r="B59" s="136" t="str">
+        <x:v>基地99至100层4米外门楼梯</x:v>
+      </x:c>
+      <x:c r="C59" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_stair_exterior_h4/env_base99_stair_exterior_h4_root_top3d_v002.tscn</x:v>
+      </x:c>
+      <x:c r="D59" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/components/env_base99_stair_exterior_h4/env_base99_stair_exterior_h4_visual_top3d_v002.glb</x:v>
+      </x:c>
+      <x:c r="E59" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v002.blend</x:v>
+      </x:c>
+      <x:c r="F59" s="136" t="str">
+        <x:v>平台5米至100层9米；两段原生楼梯组合；真实投影</x:v>
+      </x:c>
+      <x:c r="G59" s="136" t="str">
+        <x:v>src/world3d/Base99WalkableModule3D.gd</x:v>
+      </x:c>
+      <x:c r="H59" s="136" t="str">
+        <x:v>开</x:v>
+      </x:c>
+      <x:c r="I59" s="136" t="str">
+        <x:v>Prefab自身</x:v>
+      </x:c>
+      <x:c r="J59" s="136" t="str">
+        <x:v>覆盖8.515米包络的连续斜坡+双侧护栏</x:v>
+      </x:c>
+      <x:c r="K59" s="136" t="str">
+        <x:v>8.515×2.8×4m；高差4m</x:v>
+      </x:c>
+      <x:c r="L59" s="136" t="str">
+        <x:v>底面中心；Blender -Y / Godot -Z</x:v>
+      </x:c>
+      <x:c r="M59" s="136" t="str">
+        <x:v>基地楼中楼至100层出口</x:v>
+      </x:c>
+      <x:c r="N59" s="136" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="O59" s="136" t="str">
+        <x:v>v002</x:v>
+      </x:c>
+      <x:c r="P59" s="136" t="str">
+        <x:v>不做纵向拉伸；替代H2版本</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5036,7 +5244,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="145" t="str">
-        <x:v>门扇、灯具、开关、终端、工作台、储物与服务设施；当前 15 个独立Prefab。</x:v>
+        <x:v>门扇、灯具、开关、终端、工作台、储物与服务设施；当前 17 个独立Prefab。</x:v>
       </x:c>
       <x:c r="B2" s="145"/>
       <x:c r="C2" s="145"/>
@@ -5834,6 +6042,102 @@
       </x:c>
       <x:c r="P19" s="136" t="str">
         <x:v>GLB无玩法碰撞；cast_and_receive；替换同路径GLB不改变门功能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="78" customHeight="1">
+      <x:c r="A20" s="136" t="str">
+        <x:v>PRP-BASE-RECOVERY-STATION-3D</x:v>
+      </x:c>
+      <x:c r="B20" s="136" t="str">
+        <x:v>基地状态恢复舱</x:v>
+      </x:c>
+      <x:c r="C20" s="136" t="str">
+        <x:v>assets/art/props/base_world_3d/runtime/recovery_station/prp_base_recovery_station_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="D20" s="136"/>
+      <x:c r="E20" s="136"/>
+      <x:c r="F20" s="136" t="str">
+        <x:v>消耗基地电量恢复HP与手电电量</x:v>
+      </x:c>
+      <x:c r="G20" s="136" t="str">
+        <x:v>src/base3d/BaseFacility3D.gd; src/ui/BaseRecoveryMenu.gd; src/base/BaseEnergyService.gd</x:v>
+      </x:c>
+      <x:c r="H20" s="136" t="str">
+        <x:v>开</x:v>
+      </x:c>
+      <x:c r="I20" s="136" t="str">
+        <x:v>Prefab自身</x:v>
+      </x:c>
+      <x:c r="J20" s="136" t="str">
+        <x:v>Area3D交互+BoxShape3D实体</x:v>
+      </x:c>
+      <x:c r="K20" s="136" t="str">
+        <x:v>设施根缩放1；程序占位视觉</x:v>
+      </x:c>
+      <x:c r="L20" s="136" t="str">
+        <x:v>底面中心；-Z</x:v>
+      </x:c>
+      <x:c r="M20" s="136" t="str">
+        <x:v>BaseWorld3D/TowerDescent99F</x:v>
+      </x:c>
+      <x:c r="N20" s="136" t="str">
+        <x:v>功能已接入/正式模型待补</x:v>
+      </x:c>
+      <x:c r="O20" s="136" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="P20" s="136" t="str">
+        <x:v>手电在基地只暂停耗电；补电仅走恢复舱或电池</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="78" customHeight="1">
+      <x:c r="A21" s="136" t="str">
+        <x:v>PRP-BASE-AVATAR-WARDROBE-001</x:v>
+      </x:c>
+      <x:c r="B21" s="136" t="str">
+        <x:v>基地角色衣柜</x:v>
+      </x:c>
+      <x:c r="C21" s="136" t="str">
+        <x:v>assets/art/props/base_world_3d/runtime/avatar_wardrobe/prp_base_avatar_wardrobe_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="D21" s="136" t="str">
+        <x:v>assets/art/props/base_world_3d/components/locker_station/prp_base_locker_station_visual_top3d_v004.glb</x:v>
+      </x:c>
+      <x:c r="E21" s="136" t="str">
+        <x:v>assets/art/props/base_world_3d/source/locker_station/prp_base_locker_station_source_v004.blend</x:v>
+      </x:c>
+      <x:c r="F21" s="136" t="str">
+        <x:v>激活衣柜UI并预览/保存角色外观</x:v>
+      </x:c>
+      <x:c r="G21" s="136" t="str">
+        <x:v>src/base3d/wardrobe/WardrobeFacility3D.gd; src/ui/wardrobe/WardrobeMenu3D.gd</x:v>
+      </x:c>
+      <x:c r="H21" s="136" t="str">
+        <x:v>开</x:v>
+      </x:c>
+      <x:c r="I21" s="136" t="str">
+        <x:v>Prefab自身</x:v>
+      </x:c>
+      <x:c r="J21" s="136" t="str">
+        <x:v>Area3D交互+BoxShape3D实体；复用储物站视觉</x:v>
+      </x:c>
+      <x:c r="K21" s="136" t="str">
+        <x:v>5×3.9×1.63m碰撞；根缩放1</x:v>
+      </x:c>
+      <x:c r="L21" s="136" t="str">
+        <x:v>底面中心；-Z</x:v>
+      </x:c>
+      <x:c r="M21" s="136" t="str">
+        <x:v>BaseWorld3D/TowerDescent99F</x:v>
+      </x:c>
+      <x:c r="N21" s="136" t="str">
+        <x:v>功能已接入/复用模型</x:v>
+      </x:c>
+      <x:c r="O21" s="136" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="P21" s="136" t="str">
+        <x:v>6类方形物品格；每类≥3款；只改表现，不改碰撞与功能</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6174,7 +6478,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="250" t="str">
-        <x:v>玩家、NPC与角色表现/玩法根；本次扫描 3 个独立Prefab。</x:v>
+        <x:v>玩家、NPC与角色表现/玩法根及制作母版；当前 4 个登记项。</x:v>
       </x:c>
       <x:c r="B2" s="250"/>
       <x:c r="C2" s="250"/>
@@ -6380,6 +6684,52 @@
       </x:c>
       <x:c r="P7" s="196" t="str">
         <x:v>根节点=Player3D(CharacterBody3D)；子Prefab=2；资产主表当前Prefab=assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v006.tscn</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="78" customHeight="1">
+      <x:c r="A8" s="136" t="str">
+        <x:v>CHR-PLAYER-AVATAR-TEMPLATE-001</x:v>
+      </x:c>
+      <x:c r="B8" s="136" t="str">
+        <x:v>玩家角色1.5米Blender制作母版</x:v>
+      </x:c>
+      <x:c r="C8" s="136"/>
+      <x:c r="D8" s="136"/>
+      <x:c r="E8" s="136" t="str">
+        <x:v>assets/art/characters/player/chr_player_avatar_template_3d/source/chr_player_avatar_template_source_v001.blend</x:v>
+      </x:c>
+      <x:c r="F8" s="136" t="str">
+        <x:v>角色与配件制作尺寸/方向/挂点模板；非运行时Prefab</x:v>
+      </x:c>
+      <x:c r="G8" s="136" t="str">
+        <x:v>scripts/blender/validate_player_avatar_asset_template.py</x:v>
+      </x:c>
+      <x:c r="H8" s="136" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="I8" s="136" t="str">
+        <x:v>Player3D玩法根</x:v>
+      </x:c>
+      <x:c r="J8" s="136" t="str">
+        <x:v>母版只提供表现包络与挂点；CapsuleShape3D不变</x:v>
+      </x:c>
+      <x:c r="K8" s="136" t="str">
+        <x:v>总高1.50m；根缩放1</x:v>
+      </x:c>
+      <x:c r="L8" s="136" t="str">
+        <x:v>脚底中心Z0；Blender -Y / Godot -Z</x:v>
+      </x:c>
+      <x:c r="M8" s="136" t="str">
+        <x:v>玩家角色与换装资产制作</x:v>
+      </x:c>
+      <x:c r="N8" s="136" t="str">
+        <x:v>正式制作母版</x:v>
+      </x:c>
+      <x:c r="O8" s="136" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="P8" s="136" t="str">
+        <x:v>7槽位/9挂点；角色玩法碰撞仍由scenes/Player3D.tscn拥有</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8330,6 +8680,219 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="58" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="38" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="335" t="str">
+        <x:v>ShellStorm2 · 资产制作与带入 Skill 清单</x:v>
+      </x:c>
+      <x:c r="B1" s="335"/>
+      <x:c r="C1" s="335"/>
+      <x:c r="D1" s="335"/>
+      <x:c r="E1" s="335"/>
+      <x:c r="F1" s="335"/>
+      <x:c r="G1" s="335"/>
+      <x:c r="H1" s="335"/>
+      <x:c r="I1" s="335"/>
+      <x:c r="J1" s="335"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="338" t="str">
+        <x:v>只登记实际使用或项目预备的Skill；项目草稿不等于已安装。</x:v>
+      </x:c>
+      <x:c r="B2" s="338"/>
+      <x:c r="C2" s="338"/>
+      <x:c r="D2" s="338"/>
+      <x:c r="E2" s="338"/>
+      <x:c r="F2" s="338"/>
+      <x:c r="G2" s="338"/>
+      <x:c r="H2" s="338"/>
+      <x:c r="I2" s="338"/>
+      <x:c r="J2" s="338"/>
+    </x:row>
+    <x:row r="4" ht="34" customHeight="1">
+      <x:c r="A4" s="344" t="str">
+        <x:v>SkillID</x:v>
+      </x:c>
+      <x:c r="B4" s="344" t="str">
+        <x:v>名称</x:v>
+      </x:c>
+      <x:c r="C4" s="344" t="str">
+        <x:v>用途</x:v>
+      </x:c>
+      <x:c r="D4" s="344" t="str">
+        <x:v>路径</x:v>
+      </x:c>
+      <x:c r="E4" s="344" t="str">
+        <x:v>安装状态</x:v>
+      </x:c>
+      <x:c r="F4" s="344" t="str">
+        <x:v>触发范围</x:v>
+      </x:c>
+      <x:c r="G4" s="344" t="str">
+        <x:v>版本</x:v>
+      </x:c>
+      <x:c r="H4" s="344" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+      <x:c r="I4" s="344" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="J4" s="344" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="56" customHeight="1">
+      <x:c r="A5" s="345" t="str">
+        <x:v>SKILL-SHELLSTORM-ART-ASSETS</x:v>
+      </x:c>
+      <x:c r="B5" s="345" t="str">
+        <x:v>ShellStorm2美术资产管理</x:v>
+      </x:c>
+      <x:c r="C5" s="345" t="str">
+        <x:v>资产分类、命名、查重、登记与QA</x:v>
+      </x:c>
+      <x:c r="D5" s="345" t="str">
+        <x:v>/Users/summercards/.codex/skills/shellstorm-art-assets/SKILL.md</x:v>
+      </x:c>
+      <x:c r="E5" s="345" t="str">
+        <x:v>已安装</x:v>
+      </x:c>
+      <x:c r="F5" s="345" t="str">
+        <x:v>ShellStorm2全类别美术资产</x:v>
+      </x:c>
+      <x:c r="G5" s="345" t="str">
+        <x:v>current</x:v>
+      </x:c>
+      <x:c r="H5" s="345" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+      <x:c r="I5" s="346" t="n">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="J5" s="345" t="str">
+        <x:v>项目资产总流程</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="56" customHeight="1">
+      <x:c r="A6" s="345" t="str">
+        <x:v>SKILL-BLENDER-GAME-PROP</x:v>
+      </x:c>
+      <x:c r="B6" s="345" t="str">
+        <x:v>Blender游戏资产制作规范</x:v>
+      </x:c>
+      <x:c r="C6" s="345" t="str">
+        <x:v>单物件与模块化建筑制作/验收</x:v>
+      </x:c>
+      <x:c r="D6" s="345" t="str">
+        <x:v>.codex/skills/blender-game-prop-standard/SKILL.md</x:v>
+      </x:c>
+      <x:c r="E6" s="345" t="str">
+        <x:v>项目内已安装</x:v>
+      </x:c>
+      <x:c r="F6" s="345" t="str">
+        <x:v>设施、道具、墙、楼板、楼梯、栏杆</x:v>
+      </x:c>
+      <x:c r="G6" s="345" t="str">
+        <x:v>current</x:v>
+      </x:c>
+      <x:c r="H6" s="345" t="str">
+        <x:v>本轮已迭代</x:v>
+      </x:c>
+      <x:c r="I6" s="346" t="n">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="J6" s="345" t="str">
+        <x:v>新增连接模块、高度、坡面、栏杆和投影规则</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="56" customHeight="1">
+      <x:c r="A7" s="345" t="str">
+        <x:v>SKILL-GODOT-MODEL-IMPORT</x:v>
+      </x:c>
+      <x:c r="B7" s="345" t="str">
+        <x:v>Godot模型资产导入规范</x:v>
+      </x:c>
+      <x:c r="C7" s="345" t="str">
+        <x:v>GLB、PackedScene、引用替换、台账和验收</x:v>
+      </x:c>
+      <x:c r="D7" s="345" t="str">
+        <x:v>.codex/skills/godot-model-asset-import-standard/SKILL.md</x:v>
+      </x:c>
+      <x:c r="E7" s="345" t="str">
+        <x:v>项目内已安装</x:v>
+      </x:c>
+      <x:c r="F7" s="345" t="str">
+        <x:v>所有3D模型导入与替换</x:v>
+      </x:c>
+      <x:c r="G7" s="345" t="str">
+        <x:v>current</x:v>
+      </x:c>
+      <x:c r="H7" s="345" t="str">
+        <x:v>本轮已迭代</x:v>
+      </x:c>
+      <x:c r="I7" s="346" t="n">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="J7" s="345" t="str">
+        <x:v>新增Prefab台账、结构碰撞和物理楼层规则</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="56" customHeight="1">
+      <x:c r="A8" s="345" t="str">
+        <x:v>SKILL-PLAYER-AVATAR-DRAFT</x:v>
+      </x:c>
+      <x:c r="B8" s="345" t="str">
+        <x:v>玩家角色资产制作与带入规范</x:v>
+      </x:c>
+      <x:c r="C8" s="345" t="str">
+        <x:v>1.5米角色母版、槽位、挂点、换装与导入</x:v>
+      </x:c>
+      <x:c r="D8" s="345" t="str">
+        <x:v>skills_drafts/player-avatar-asset-standard/SKILL.md</x:v>
+      </x:c>
+      <x:c r="E8" s="345" t="str">
+        <x:v>未安装（项目草稿）</x:v>
+      </x:c>
+      <x:c r="F8" s="345" t="str">
+        <x:v>玩家角色与配件</x:v>
+      </x:c>
+      <x:c r="G8" s="345" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="H8" s="345" t="str">
+        <x:v>预备完成</x:v>
+      </x:c>
+      <x:c r="I8" s="346" t="n">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="J8" s="345" t="str">
+        <x:v>等待用户未来明确授权后再安装</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -36838,6 +37401,446 @@
         <x:v>北墙两端普通+中间4窗；其余19普通墙，东侧1门墙；18米屋顶挡光；围护与封顶统一投影；不恢复99/100层中间36块。</x:v>
       </x:c>
     </x:row>
+    <x:row r="281" ht="66" customHeight="1">
+      <x:c r="A281" s="136" t="str">
+        <x:v>ENV-BASE99-MEZZANINE-20X10-Z5</x:v>
+      </x:c>
+      <x:c r="B281" s="136" t="str">
+        <x:v>基地99层5米楼中楼楼板</x:v>
+      </x:c>
+      <x:c r="C281" s="136" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D281" s="136" t="str">
+        <x:v>environment_module</x:v>
+      </x:c>
+      <x:c r="E281" s="136" t="str">
+        <x:v>base99_mezzanine_20x10_z5</x:v>
+      </x:c>
+      <x:c r="F281" s="136" t="str">
+        <x:v>platform</x:v>
+      </x:c>
+      <x:c r="G281" s="136" t="str">
+        <x:v>ENV-BASE99-MODULAR-ROOM</x:v>
+      </x:c>
+      <x:c r="H281" s="136" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I281" s="136" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J281" s="136" t="str">
+        <x:v>基地99F</x:v>
+      </x:c>
+      <x:c r="K281" s="136" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="L281" s="136" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M281" s="136" t="str">
+        <x:v>v002</x:v>
+      </x:c>
+      <x:c r="N281" s="136" t="str">
+        <x:v>台面5m；20.2475×10.2475m</x:v>
+      </x:c>
+      <x:c r="O281" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_mezzanine_20x10_z5/env_base99_mezzanine_20x10_z5_root_top3d_v002.tscn</x:v>
+      </x:c>
+      <x:c r="P281" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v002.blend</x:v>
+      </x:c>
+      <x:c r="Q281" s="136" t="str">
+        <x:v>5米楼板; 栏杆; 投影</x:v>
+      </x:c>
+      <x:c r="R281" s="136" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C281,D281,E281,F281,H281,I281)</x:f>
+        <x:v>场景|environment_module|base99_mezzanine_20x10_z5|platform|俯视3D|default</x:v>
+      </x:c>
+      <x:c r="S281" s="136" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$400,R281)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T281" s="136"/>
+      <x:c r="U281" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V281" s="137" t="n">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="W281" s="136" t="str">
+        <x:v>用户自制/项目内资产</x:v>
+      </x:c>
+      <x:c r="X281" s="136" t="str">
+        <x:v>2026-08-20：本轮基地系统、角色母版与资产流程登记。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" ht="66" customHeight="1">
+      <x:c r="A282" s="136" t="str">
+        <x:v>ENV-BASE99-STAIR-L-Z5</x:v>
+      </x:c>
+      <x:c r="B282" s="136" t="str">
+        <x:v>基地99层5米L型楼梯</x:v>
+      </x:c>
+      <x:c r="C282" s="136" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D282" s="136" t="str">
+        <x:v>environment_module</x:v>
+      </x:c>
+      <x:c r="E282" s="136" t="str">
+        <x:v>base99_stair_l_z5</x:v>
+      </x:c>
+      <x:c r="F282" s="136" t="str">
+        <x:v>stair</x:v>
+      </x:c>
+      <x:c r="G282" s="136" t="str">
+        <x:v>ENV-BASE99-MODULAR-ROOM</x:v>
+      </x:c>
+      <x:c r="H282" s="136" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I282" s="136" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J282" s="136" t="str">
+        <x:v>基地99F</x:v>
+      </x:c>
+      <x:c r="K282" s="136" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="L282" s="136" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M282" s="136" t="str">
+        <x:v>v002</x:v>
+      </x:c>
+      <x:c r="N282" s="136" t="str">
+        <x:v>0→2.5→5m</x:v>
+      </x:c>
+      <x:c r="O282" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_stair_l_z5/env_base99_stair_l_z5_root_top3d_v002.tscn</x:v>
+      </x:c>
+      <x:c r="P282" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v002.blend</x:v>
+      </x:c>
+      <x:c r="Q282" s="136" t="str">
+        <x:v>L梯; 连续坡面; 扶手</x:v>
+      </x:c>
+      <x:c r="R282" s="136" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C282,D282,E282,F282,H282,I282)</x:f>
+        <x:v>场景|environment_module|base99_stair_l_z5|stair|俯视3D|default</x:v>
+      </x:c>
+      <x:c r="S282" s="136" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$400,R282)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T282" s="136"/>
+      <x:c r="U282" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V282" s="137" t="n">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="W282" s="136" t="str">
+        <x:v>用户自制/项目内资产</x:v>
+      </x:c>
+      <x:c r="X282" s="136" t="str">
+        <x:v>2026-08-20：本轮基地系统、角色母版与资产流程登记。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" ht="66" customHeight="1">
+      <x:c r="A283" s="136" t="str">
+        <x:v>ENV-BASE99-STAIR-EXTERIOR-H4</x:v>
+      </x:c>
+      <x:c r="B283" s="136" t="str">
+        <x:v>基地99至100层4米外梯</x:v>
+      </x:c>
+      <x:c r="C283" s="136" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D283" s="136" t="str">
+        <x:v>environment_module</x:v>
+      </x:c>
+      <x:c r="E283" s="136" t="str">
+        <x:v>base99_stair_exterior_h4</x:v>
+      </x:c>
+      <x:c r="F283" s="136" t="str">
+        <x:v>stair_exterior</x:v>
+      </x:c>
+      <x:c r="G283" s="136" t="str">
+        <x:v>ENV-BASE99-MODULAR-ROOM</x:v>
+      </x:c>
+      <x:c r="H283" s="136" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I283" s="136" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J283" s="136" t="str">
+        <x:v>基地99F/100F</x:v>
+      </x:c>
+      <x:c r="K283" s="136" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="L283" s="136" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M283" s="136" t="str">
+        <x:v>v002</x:v>
+      </x:c>
+      <x:c r="N283" s="136" t="str">
+        <x:v>5→9m；8.515m包络</x:v>
+      </x:c>
+      <x:c r="O283" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_stair_exterior_h4/env_base99_stair_exterior_h4_root_top3d_v002.tscn</x:v>
+      </x:c>
+      <x:c r="P283" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v002.blend</x:v>
+      </x:c>
+      <x:c r="Q283" s="136" t="str">
+        <x:v>外梯; H4; 连续坡面</x:v>
+      </x:c>
+      <x:c r="R283" s="136" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C283,D283,E283,F283,H283,I283)</x:f>
+        <x:v>场景|environment_module|base99_stair_exterior_h4|stair_exterior|俯视3D|default</x:v>
+      </x:c>
+      <x:c r="S283" s="136" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$400,R283)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T283" s="136"/>
+      <x:c r="U283" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V283" s="137" t="n">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="W283" s="136" t="str">
+        <x:v>用户自制/项目内资产</x:v>
+      </x:c>
+      <x:c r="X283" s="136" t="str">
+        <x:v>2026-08-20：本轮基地系统、角色母版与资产流程登记。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" ht="66" customHeight="1">
+      <x:c r="A284" s="136" t="str">
+        <x:v>PRP-BASE-RECOVERY-STATION-3D</x:v>
+      </x:c>
+      <x:c r="B284" s="136" t="str">
+        <x:v>基地状态恢复舱</x:v>
+      </x:c>
+      <x:c r="C284" s="136" t="str">
+        <x:v>设施</x:v>
+      </x:c>
+      <x:c r="D284" s="136" t="str">
+        <x:v>base_facility</x:v>
+      </x:c>
+      <x:c r="E284" s="136" t="str">
+        <x:v>base_recovery</x:v>
+      </x:c>
+      <x:c r="F284" s="136" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="G284" s="136"/>
+      <x:c r="H284" s="136" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I284" s="136" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J284" s="136" t="str">
+        <x:v>主基地/99F</x:v>
+      </x:c>
+      <x:c r="K284" s="136" t="str">
+        <x:v>功能已接入</x:v>
+      </x:c>
+      <x:c r="L284" s="136" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M284" s="136" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N284" s="136" t="str">
+        <x:v>根缩放1</x:v>
+      </x:c>
+      <x:c r="O284" s="136" t="str">
+        <x:v>assets/art/props/base_world_3d/runtime/recovery_station/prp_base_recovery_station_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P284" s="136" t="str">
+        <x:v>src/ui/BaseRecoveryMenu.gd; src/base/BaseEnergyService.gd</x:v>
+      </x:c>
+      <x:c r="Q284" s="136" t="str">
+        <x:v>恢复舱; HP; 手电; 基地能源</x:v>
+      </x:c>
+      <x:c r="R284" s="136" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C284,D284,E284,F284,H284,I284)</x:f>
+        <x:v>设施|base_facility|base_recovery|root|俯视3D|default</x:v>
+      </x:c>
+      <x:c r="S284" s="136" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$400,R284)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T284" s="136"/>
+      <x:c r="U284" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V284" s="137" t="n">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="W284" s="136" t="str">
+        <x:v>用户自制/项目内资产</x:v>
+      </x:c>
+      <x:c r="X284" s="136" t="str">
+        <x:v>2026-08-20：本轮基地系统、角色母版与资产流程登记。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" ht="66" customHeight="1">
+      <x:c r="A285" s="136" t="str">
+        <x:v>PRP-BASE-AVATAR-WARDROBE-001</x:v>
+      </x:c>
+      <x:c r="B285" s="136" t="str">
+        <x:v>基地角色衣柜</x:v>
+      </x:c>
+      <x:c r="C285" s="136" t="str">
+        <x:v>设施</x:v>
+      </x:c>
+      <x:c r="D285" s="136" t="str">
+        <x:v>base_facility</x:v>
+      </x:c>
+      <x:c r="E285" s="136" t="str">
+        <x:v>avatar_wardrobe</x:v>
+      </x:c>
+      <x:c r="F285" s="136" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="G285" s="136"/>
+      <x:c r="H285" s="136" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I285" s="136" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J285" s="136" t="str">
+        <x:v>主基地/99F</x:v>
+      </x:c>
+      <x:c r="K285" s="136" t="str">
+        <x:v>功能已接入/复用模型</x:v>
+      </x:c>
+      <x:c r="L285" s="136" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M285" s="136" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N285" s="136" t="str">
+        <x:v>根缩放1</x:v>
+      </x:c>
+      <x:c r="O285" s="136" t="str">
+        <x:v>assets/art/props/base_world_3d/runtime/avatar_wardrobe/prp_base_avatar_wardrobe_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P285" s="136" t="str">
+        <x:v>src/ui/wardrobe/WardrobeMenu3D.gd</x:v>
+      </x:c>
+      <x:c r="Q285" s="136" t="str">
+        <x:v>衣柜; avatar; 换装; 6分类</x:v>
+      </x:c>
+      <x:c r="R285" s="136" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C285,D285,E285,F285,H285,I285)</x:f>
+        <x:v>设施|base_facility|avatar_wardrobe|root|俯视3D|default</x:v>
+      </x:c>
+      <x:c r="S285" s="136" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$400,R285)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T285" s="136"/>
+      <x:c r="U285" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V285" s="137" t="n">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="W285" s="136" t="str">
+        <x:v>用户自制/项目内资产</x:v>
+      </x:c>
+      <x:c r="X285" s="136" t="str">
+        <x:v>2026-08-20：本轮基地系统、角色母版与资产流程登记。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" ht="66" customHeight="1">
+      <x:c r="A286" s="136" t="str">
+        <x:v>CHR-PLAYER-AVATAR-TEMPLATE-001</x:v>
+      </x:c>
+      <x:c r="B286" s="136" t="str">
+        <x:v>玩家角色1.5米制作母版</x:v>
+      </x:c>
+      <x:c r="C286" s="136" t="str">
+        <x:v>角色</x:v>
+      </x:c>
+      <x:c r="D286" s="136" t="str">
+        <x:v>authoring_template</x:v>
+      </x:c>
+      <x:c r="E286" s="136" t="str">
+        <x:v>player_avatar_template</x:v>
+      </x:c>
+      <x:c r="F286" s="136" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="G286" s="136" t="str">
+        <x:v>CHR-PLY-CAPSULE01</x:v>
+      </x:c>
+      <x:c r="H286" s="136" t="str">
+        <x:v>全向3D</x:v>
+      </x:c>
+      <x:c r="I286" s="136" t="str">
+        <x:v>template</x:v>
+      </x:c>
+      <x:c r="J286" s="136" t="str">
+        <x:v>角色制作</x:v>
+      </x:c>
+      <x:c r="K286" s="136" t="str">
+        <x:v>正式制作母版</x:v>
+      </x:c>
+      <x:c r="L286" s="136" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M286" s="136" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N286" s="136" t="str">
+        <x:v>1.50m；根缩放1</x:v>
+      </x:c>
+      <x:c r="O286" s="136" t="str">
+        <x:v>assets/art/characters/player/chr_player_avatar_template_3d/source/chr_player_avatar_template_source_v001.blend</x:v>
+      </x:c>
+      <x:c r="P286" s="136" t="str">
+        <x:v>scripts/blender/validate_player_avatar_asset_template.py</x:v>
+      </x:c>
+      <x:c r="Q286" s="136" t="str">
+        <x:v>角色母版; 1.5米; 挂点; 配件</x:v>
+      </x:c>
+      <x:c r="R286" s="136" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C286,D286,E286,F286,H286,I286)</x:f>
+        <x:v>角色|authoring_template|player_avatar_template|root|全向3D|template</x:v>
+      </x:c>
+      <x:c r="S286" s="136" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$400,R286)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T286" s="136"/>
+      <x:c r="U286" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V286" s="137" t="n">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="W286" s="136" t="str">
+        <x:v>用户自制/项目内资产</x:v>
+      </x:c>
+      <x:c r="X286" s="136" t="str">
+        <x:v>2026-08-20：本轮基地系统、角色母版与资产流程登记。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:X2"/>
@@ -36863,7 +37866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R312686a395b54d32"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc90492b8a87c477b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43698,13 +44701,27 @@
       </x:c>
     </x:row>
     <x:row r="23" ht="78" customHeight="1">
-      <x:c r="A23" s="136"/>
-      <x:c r="B23" s="136"/>
-      <x:c r="C23" s="136"/>
-      <x:c r="D23" s="136"/>
-      <x:c r="E23" s="136"/>
-      <x:c r="F23" s="136"/>
-      <x:c r="G23" s="136"/>
+      <x:c r="A23" s="136" t="str">
+        <x:v>v0.1.19</x:v>
+      </x:c>
+      <x:c r="B23" s="137" t="n">
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="C23" s="136" t="str">
+        <x:v>基地系统/时间/Avatar/3D流程收口</x:v>
+      </x:c>
+      <x:c r="D23" s="136" t="str">
+        <x:v>6项资产/3项Skill/5米结构/11设施</x:v>
+      </x:c>
+      <x:c r="E23" s="136" t="str">
+        <x:v>平台改为5米并联动两类楼梯与栏杆碰撞；新增物理楼层权威、时间日夜、基地能源恢复舱、主页面、衣柜、脱困和1.5米角色母版。</x:v>
+      </x:c>
+      <x:c r="F23" s="136" t="str">
+        <x:v>视觉替换不改变原门、设施、玩家碰撞和战斗脚本；旧Z7/H2资产保留回滚；新Skill草稿未安装。</x:v>
+      </x:c>
+      <x:c r="G23" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="100" customHeight="1">
       <x:c r="A24" s="136"/>
@@ -43966,16 +44983,16 @@
         <x:v>3D-场景通用</x:v>
       </x:c>
       <x:c r="C5" s="277" t="n">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D5" s="277" t="n">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E5" s="277" t="n">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F5" s="277" t="n">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G5" s="278" t="str">
         <x:v>关卡结构、地板、墙体、走廊、楼梯、楼板与环境套件</x:v>
@@ -43999,16 +45016,16 @@
         <x:v>3D-设施</x:v>
       </x:c>
       <x:c r="C6" s="280" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D6" s="280" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E6" s="280" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F6" s="280" t="n">
         <x:v>15</x:v>
-      </x:c>
-      <x:c r="D6" s="280" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E6" s="280" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F6" s="280" t="n">
-        <x:v>13</x:v>
       </x:c>
       <x:c r="G6" s="281" t="str">
         <x:v>门扇、灯具、开关、终端、工作台、储物与服务设施</x:v>
@@ -44069,19 +45086,15 @@
         <x:v>3D-角色</x:v>
       </x:c>
       <x:c r="C8" s="280" t="n">
-        <x:f>COUNTA('3D-角色'!$A$5:$A$204)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="280" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="280" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D8" s="280" t="n">
-        <x:f>COUNTIF('3D-角色'!$D$5:$D$204,"&lt;&gt;")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" s="280" t="n">
-        <x:f>COUNTIF('3D-角色'!$G$5:$G$204,"&lt;&gt;")</x:f>
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="F8" s="280" t="n">
-        <x:f>COUNTIF('3D-角色'!$H$5:$H$204,"开")</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="281" t="str">
@@ -44291,19 +45304,19 @@
         <x:v>9个分类分页</x:v>
       </x:c>
       <x:c r="C14" s="315" t="n">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D14" s="315" t="n">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E14" s="315" t="n">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F14" s="315" t="n">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G14" s="316" t="str">
-        <x:v>更新日期：2026-08-18；基地100层上层围护与18米封顶接入</x:v>
+        <x:v>更新日期：2026-08-20；5米基地结构、恢复舱、衣柜与角色母版接入</x:v>
       </x:c>
       <x:c r="H14" s="136"/>
       <x:c r="I14" s="136"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R111badf2faa4436f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rf7216e33164d410c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rfa13bef7b1204d3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R34782d7f354d4ad7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rb2f49475948646de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R0d1a957fa8294355"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R86ee98e9878f4cf7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R5b7fd96b0adc47c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Re43a9b6df2714656"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R2ee6d32d33184c32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R4b1b60d4f0e7483d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R810920693ae24707"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R1511a47ea7da471f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="Rcb69e40406de4a78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="R798ba1463c1c478a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R258657c401384f9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R4219a7cdcc414a13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Rfde33724019b4035"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R6e5bf74ed43240d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb13314ae5c814646"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R39e74cd6de864d6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rb1b35e15a4584379"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rffabaee7ba2d40dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Re751b5868b1441e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R7e9901e3e63a4966"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R8f09021b641d4d8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R6662885e8bac4793"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Re0a0703bba9740e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="Rd1b72dafbfbb4ea5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R8f988ed50f23415b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R6ce89be2f1c74e7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R1e5afcd3bedf4204"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R6c421b06f8264dd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="R3abb5e5f39744e50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R3885524a2f984036"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="Rc2afafb9a4884f6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="R2ddb5f3373ab413d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="Ree41aa69c1fe40ed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -849,7 +849,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="347">
+  <x:cellXfs count="348">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -1665,6 +1665,9 @@
     <x:xf numFmtId="164" fontId="28" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -5088,16 +5091,16 @@
         <x:v>基地99层5米L型楼梯</x:v>
       </x:c>
       <x:c r="C58" s="136" t="str">
-        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_stair_l_z5/env_base99_stair_l_z5_root_top3d_v002.tscn</x:v>
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_stair_l_z5/env_base99_stair_l_z5_root_top3d_v004.tscn</x:v>
       </x:c>
       <x:c r="D58" s="136" t="str">
-        <x:v>assets/art/environments/base_facility_3d/components/env_base99_stair_l_z5/env_base99_stair_l_z5_visual_top3d_v002.glb</x:v>
+        <x:v>assets/art/environments/base_facility_3d/components/env_base99_stair_l_z5/env_base99_stair_l_z5_visual_top3d_v004.glb</x:v>
       </x:c>
       <x:c r="E58" s="136" t="str">
-        <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v002.blend</x:v>
+        <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v004.blend</x:v>
       </x:c>
       <x:c r="F58" s="136" t="str">
-        <x:v>0→2.5→5米双跑L梯；扶手真实投影与阻挡</x:v>
+        <x:v>0→2.5→5米完整双跑L梯；转角扶手收口；真实投影与阻挡</x:v>
       </x:c>
       <x:c r="G58" s="136" t="str">
         <x:v>src/world3d/Base99WalkableModule3D.gd</x:v>
@@ -5109,7 +5112,7 @@
         <x:v>Prefab自身</x:v>
       </x:c>
       <x:c r="J58" s="136" t="str">
-        <x:v>两段连续斜坡+平台+独立扶手Box</x:v>
+        <x:v>单一StaticBody：斜坡+平台+斜坡；独立连续扶手Box</x:v>
       </x:c>
       <x:c r="K58" s="136" t="str">
         <x:v>9.2176×10.538×5.91015m；终点5m</x:v>
@@ -5124,10 +5127,10 @@
         <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="O58" s="136" t="str">
-        <x:v>v002</x:v>
+        <x:v>v004</x:v>
       </x:c>
       <x:c r="P58" s="136" t="str">
-        <x:v>不用逐级碰撞；坡脚/平台/坡顶连续；替代Z7版本</x:v>
+        <x:v>由91个可编辑源组件重建；踏步/斜梁/平台/导光条齐全；转角扶手不穿插；三段行走形状接缝齐平并重叠0.04m。</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="78" customHeight="1">
@@ -7650,7 +7653,7 @@
         <x:v>武器3D表现Prefab；由武器系统装配</x:v>
       </x:c>
       <x:c r="G17" s="192" t="str">
-        <x:v>src/player3d/WeaponModel3D.gd</x:v>
+        <x:v>src/combat3d/WeaponModel3D.gd</x:v>
       </x:c>
       <x:c r="H17" s="192" t="str">
         <x:v>无</x:v>
@@ -7662,7 +7665,7 @@
         <x:v>无</x:v>
       </x:c>
       <x:c r="K17" s="192" t="str">
-        <x:v>握把原点；local -Z枪口；3材质；独立GLB/PackedScene</x:v>
+        <x:v>GripSocket根原点；可见握把中心校正到根；local -Z枪口；3材质；独立GLB/PackedScene</x:v>
       </x:c>
       <x:c r="L17" s="192" t="str">
         <x:v>-Z</x:v>
@@ -7677,7 +7680,7 @@
         <x:v>v001</x:v>
       </x:c>
       <x:c r="P17" s="193" t="str">
-        <x:v>根节点=吹风机(Node3D)</x:v>
+        <x:v>根节点=吹风机(Node3D)；VisualRoot/全部非Grip挂点统一偏移(0,-0.122838,-0.168785)；GripSocket=手掌球中心；待机/开火枪口轴与真实弹道0度差</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="66" customHeight="1">
@@ -11109,10 +11112,8 @@
           <x:t xml:space="preserve">assets/art/weapons/weapon_3d/runtime/hair_dryer/wpn_hair_dryer_root_top3d_v001.tscn</x:t>
         </x:is>
       </x:c>
-      <x:c r="P24" s="138" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">assets/art/weapons/weapon_3d/source/hair_dryer/wpn_hair_dryer_source_v001.blend; src/combat3d/WeaponModel3D.gd</x:t>
-        </x:is>
+      <x:c r="P24" s="138" t="str">
+        <x:v>assets/art/weapons/weapon_3d/source/hair_dryer/wpn_hair_dryer_source_v003.blend; src/combat3d/WeaponModel3D.gd</x:v>
       </x:c>
       <x:c r="Q24" s="138" t="inlineStr">
         <x:is>
@@ -11145,10 +11146,9 @@
           <x:t xml:space="preserve">用户自制Blender资产</x:t>
         </x:is>
       </x:c>
-      <x:c r="X24" s="138" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">由18枪合集拆成独立资产；根节点即握把原点，枪口统一local -Z；无需玩家侧逐枪旋转补丁。</x:t>
-        </x:is>
+      <x:c r="X24" s="138" t="str">
+        <x:v>由18枪合集拆成独立资产；根节点即握把原点，枪口统一local -Z；无需玩家侧逐枪旋转补丁。
+2026-08-21：复用WPN-GUN-BP-PISTOL与v003 GLB；Godot包装层保持GripSocket=根原点，将可见握把中心及全部非Grip语义挂点统一校正(0,-0.122838,-0.168785)。待机与开火时枪模local -Z锁定真实aim_direction，后坐只沿枪轴平移，不改变弹道、伤害、碰撞或装配。</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -25355,10 +25355,11 @@
           <x:t xml:space="preserve">原创 Blender/Godot 组合</x:t>
         </x:is>
       </x:c>
-      <x:c r="X156" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">v0.1 v006：正式BunnyRig保持双手武器姿势；新增BodyJoint/LowerBodySocket；DIY body/head/hand/feet直接映射可见GLB材质；状态画廊覆盖层读数兼容结构化flashlight快照。角色网格保持layer2与现有外部灯光投影契约。</x:t>
-        </x:is>
+      <x:c r="X156" s="306" t="str">
+        <x:v>v0.1 v006：正式BunnyRig保持双手武器姿势；新增BodyJoint/LowerBodySocket；DIY body/head/hand/feet直接映射可见GLB材质；状态画廊覆盖层读数兼容结构化flashlight快照。角色网格保持layer2与现有外部灯光投影契约。
+2026-08-21：复用bunny01 v006与现有武器GLB/AssetID，sidearm_hold改为右前下方低位警戒；仅程序姿势修订，不改玩法碰撞、射击或装配。
+2026-08-21：右手掌球中心、HandJointR与枪械GripSocket改为同一挂点事实；沿用bunny01 v006与现有AssetID，不改玩法。
+2026-08-21：手枪待机取消整枪俯仰/偏航/侧滚，开火角度后坐不再作用于枪身；枪口local -Z与真实aim_direction保持0度差。</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="118" customHeight="1">
@@ -25827,10 +25828,11 @@
           <x:t xml:space="preserve">用户提供 Blender 源文件</x:t>
         </x:is>
       </x:c>
-      <x:c r="X160" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">v0.1 v006：左右手、手腕原点、单/双手握持目标和动作平移统一改用0.606060606米制比例；持枪外观与确认预览一致。</x:t>
-        </x:is>
+      <x:c r="X160" s="306" t="str">
+        <x:v>v0.1 v006：左右手、手腕原点、单/双手握持目标和动作平移统一改用0.606060606米制比例；持枪外观与确认预览一致。
+2026-08-21：右手收紧到GripSocket；手枪待机自由左手前伸胸前，枪口下俯并向角色外侧偏转，正面与三分之四近景保持面部净空。
+2026-08-21：HandJointR/Model使用局部枢轴校正(-0.135996,0.038999,0.018441)，持枪状态每帧按真实GripSocket换算到HandRoot局部空间，三点偏差0mm。
+2026-08-21：右手掌球仍与HandJointR/GripSocket保持0mm；吹风机Prefab另将可见握把中心校正到该同一坐标，未改角色GLB。</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="132" customHeight="1">
@@ -37513,19 +37515,19 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="M282" s="136" t="str">
-        <x:v>v002</x:v>
+        <x:v>v004</x:v>
       </x:c>
       <x:c r="N282" s="136" t="str">
-        <x:v>0→2.5→5m</x:v>
+        <x:v>0→2.5→5m；单一行走体</x:v>
       </x:c>
       <x:c r="O282" s="136" t="str">
-        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_stair_l_z5/env_base99_stair_l_z5_root_top3d_v002.tscn</x:v>
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_stair_l_z5/env_base99_stair_l_z5_root_top3d_v004.tscn</x:v>
       </x:c>
       <x:c r="P282" s="136" t="str">
-        <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v002.blend</x:v>
+        <x:v>assets/art/environments/base_facility_3d/source/env_base99_modular_room/env_base99_modular_room_assets_clean_v004.blend</x:v>
       </x:c>
       <x:c r="Q282" s="136" t="str">
-        <x:v>L梯; 连续坡面; 扶手</x:v>
+        <x:v>L梯; 连续坡面; 单一行走体; 转角扶手收口</x:v>
       </x:c>
       <x:c r="R282" s="136" t="str">
         <x:f>TEXTJOIN("|",TRUE,C282,D282,E282,F282,H282,I282)</x:f>
@@ -37535,7 +37537,9 @@
         <x:f>IF(COUNTIF($R$6:$R$400,R282)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T282" s="136"/>
+      <x:c r="T282" s="136" t="str">
+        <x:v>abfcfdbff300fd1c6be549b6535ff2576a09ceb5eeec57ced70e8d2990f2c026</x:v>
+      </x:c>
       <x:c r="U282" s="136" t="str">
         <x:v>Codex</x:v>
       </x:c>
@@ -37546,7 +37550,7 @@
         <x:v>用户自制/项目内资产</x:v>
       </x:c>
       <x:c r="X282" s="136" t="str">
-        <x:v>2026-08-20：本轮基地系统、角色母版与资产流程登记。</x:v>
+        <x:v>2026-08-20：v004从完整源组件重建；GLB仅表现，Godot Prefab持有单一StaticBody三段行走形状与独立护栏阻挡。</x:v>
       </x:c>
     </x:row>
     <x:row r="283" ht="66" customHeight="1">
@@ -37866,7 +37870,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc90492b8a87c477b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R934658663b8c4c41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39953,10 +39957,8 @@
           <x:t xml:space="preserve">pivot-local GLB / 1.5m比例</x:t>
         </x:is>
       </x:c>
-      <x:c r="G36" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Authored (-0.285833,0.321773,-0.014435); longgun support (0.121212,0.315152,-0.387879)</x:t>
-        </x:is>
+      <x:c r="G36" s="306" t="str">
+        <x:v>Authored (-0.285833,0.321773,-0.014435); sidearm ready (-0.145455,0.333333,-0.351515); longgun support (0.121212,0.315152,-0.387879)</x:v>
       </x:c>
       <x:c r="H36" s="70" t="inlineStr">
         <x:is>
@@ -39966,10 +39968,8 @@
       <x:c r="I36" s="70" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J36" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">手枪自由摆臂；长枪托举；换弹服务；双手枪后坐</x:t>
-        </x:is>
+      <x:c r="J36" s="306" t="str">
+        <x:v>手枪待机前伸警戒/移动自由摆臂；长枪托举；换弹服务；双手枪后坐</x:v>
       </x:c>
       <x:c r="K36" s="70" t="inlineStr">
         <x:is>
@@ -39981,10 +39981,8 @@
           <x:t xml:space="preserve">是</x:t>
         </x:is>
       </x:c>
-      <x:c r="M36" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">手腕圆环近端轴心；网格、挂点与动作米制平移使用0.606060606比例。</x:t>
-        </x:is>
+      <x:c r="M36" s="306" t="str">
+        <x:v>手腕圆环近端轴心；手枪仍为自由左手，待机只前伸形成警戒剪影；网格、挂点与动作米制平移使用0.606060606比例。</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="104" customHeight="1">
@@ -40018,10 +40016,8 @@
           <x:t xml:space="preserve">pivot-local GLB / 1.5m比例</x:t>
         </x:is>
       </x:c>
-      <x:c r="G37" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Authored (0.285833,0.321773,-0.014435); sidearm (0.048485,0.339394,-0.296970)+socket X0.145455; longgun (0.078788,0.339394,-0.296970)</x:t>
-        </x:is>
+      <x:c r="G37" s="306" t="str">
+        <x:v>Authored joint (0.285833,0.321773,-0.014435); Model pivot correction (-0.135996,0.038999,0.018441); sidearm/longgun HandJointR follows GripSocket exactly; hair-dryer visible grip center corrected by Prefab offset (0,-0.122838,-0.168785)</x:v>
       </x:c>
       <x:c r="H37" s="70" t="inlineStr">
         <x:is>
@@ -40031,10 +40027,8 @@
       <x:c r="I37" s="70" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J37" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">手枪/长枪主握把；独立跑步；武器差异射击后坐</x:t>
-        </x:is>
+      <x:c r="J37" s="306" t="str">
+        <x:v>手枪/长枪主握把；掌球中心锁定握把；待机低位警戒；独立跑步；武器差异射击后坐</x:v>
       </x:c>
       <x:c r="K37" s="70" t="inlineStr">
         <x:is>
@@ -40046,10 +40040,8 @@
           <x:t xml:space="preserve">是</x:t>
         </x:is>
       </x:c>
-      <x:c r="M37" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">右手主握把；持枪视觉与手/挂点使用同一0.606060606比例。</x:t>
-        </x:is>
+      <x:c r="M37" s="306" t="str">
+        <x:v>右手大球中心=HandJointR=GripSocket；吹风机可见握把中心也由Prefab包装校正到该坐标。圆环仅为近端腕部造型；不改变武器装配、射击、碰撞或玩法事实源。</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="104" customHeight="1">
@@ -40605,15 +40597,11 @@
           <x:t xml:space="preserve">与身体反相缩放；反向滞后保持头重感</x:t>
         </x:is>
       </x:c>
-      <x:c r="H6" s="100" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">手枪自由左手轻摆；长枪左手保持托举</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I6" s="100" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">握持手与 WeaponSocket 同步稳定呼吸，不脱离握把</x:t>
-        </x:is>
+      <x:c r="H6" s="347" t="str">
+        <x:v>手枪自由左手前伸胸前警戒；长枪左手保持托举</x:v>
+      </x:c>
+      <x:c r="I6" s="347" t="str">
+        <x:v>手枪/长枪右手掌球中心、HandJointR与GripSocket三点重合；手枪WeaponSocket待机右前下移，枪管local -Z保持瞄准同向</x:v>
       </x:c>
       <x:c r="J6" s="100" t="inlineStr">
         <x:is>
@@ -40625,10 +40613,8 @@
           <x:t xml:space="preserve">HUD 待命；无新增VFX</x:t>
         </x:is>
       </x:c>
-      <x:c r="L6" s="100" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">八态 StateMachine 的 idle 唯一驱动；idle_cycle 推进呼吸/换脚；双耳错相并偶发单耳轻弹；moving 本帧归零，停下后恢复</x:t>
-        </x:is>
+      <x:c r="L6" s="347" t="str">
+        <x:v>八态StateMachine的idle唯一驱动；sidearm_hold保持低位警戒与面部净空，但取消整枪俯仰/偏航/侧滚；右手刚性追随GripSocket且掌球中心0mm对齐，左手前伸但不计第二握持。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -42009,10 +41995,8 @@
           <x:t xml:space="preserve">手枪左手不继承后坐；长枪左手托举并小幅刚性回弹</x:t>
         </x:is>
       </x:c>
-      <x:c r="I32" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">右手握把跟随 WeaponSocket；手枪单腕上挑，长枪双手与躯干共同吃后坐</x:t>
-        </x:is>
+      <x:c r="I32" s="306" t="str">
+        <x:v>右手握把跟随WeaponSocket；枪身只沿枪轴平移后坐，local -Z不离开真实弹道；腕部/躯干继续承担枪型差异回弹</x:v>
       </x:c>
       <x:c r="J32" s="70" t="inlineStr">
         <x:is>
@@ -42024,10 +42008,8 @@
           <x:t xml:space="preserve">枪口闪光/后坐</x:t>
         </x:is>
       </x:c>
-      <x:c r="L32" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">真实 shot_fired 信号；WeaponPoseFSM 进入 sidearm_fire/longgun_fire；七种枪体读取独立 fire_style、kick、pitch、roll、lift 参数</x:t>
-        </x:is>
+      <x:c r="L32" s="306" t="str">
+        <x:v>真实shot_fired信号；WeaponPoseFSM进入sidearm_fire/longgun_fire。七枪仍读取独立fire_style/kick/pitch/roll/lift，但远程枪身开火旋转被锁为0，仅手腕/身体使用角度参数；MuzzleSocket -Z与aim_direction误差≤0.5度。</x:v>
       </x:c>
     </x:row>
     <x:row r="33">

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb13314ae5c814646"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R39e74cd6de864d6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rb1b35e15a4584379"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rffabaee7ba2d40dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Re751b5868b1441e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R7e9901e3e63a4966"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R8f09021b641d4d8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R6662885e8bac4793"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Re0a0703bba9740e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="Rd1b72dafbfbb4ea5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R8f988ed50f23415b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R6ce89be2f1c74e7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R1e5afcd3bedf4204"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R6c421b06f8264dd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="R3abb5e5f39744e50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R3885524a2f984036"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="Rc2afafb9a4884f6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="R2ddb5f3373ab413d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="Ree41aa69c1fe40ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8e5a77c426b94f6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R16363a9bc6cc4bd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R550e59ccda8c40ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rd44d8ce22eb34b66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R009d647cea2a4362"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R7006c21436db4d28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Rbb5175bab85848fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R11f7e73bb4b842f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="R13ca7c0a93be43f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R4752a923d0a946e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R0a6d2ab18649448f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="Ra46a32dc4a21480d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R2eb993629e924a80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R37f0a18a8ca34a71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="Rcb56db762c1a414d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R46f8fd3e931a4c43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="Rd7773e308e1c4e1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Ra76c4a7b74544e47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R21cd76452d1d4f88"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6799,7 +6799,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="250" t="str">
-        <x:v>普通敌人、精英、Boss与敌人共用根；本次扫描 1 个独立Prefab。</x:v>
+        <x:v>普通敌人、精英、Boss与敌人共用根；当前2个独立Prefab，其中首只正式精英资产1/12。</x:v>
       </x:c>
       <x:c r="B2" s="250"/>
       <x:c r="C2" s="250"/>
@@ -6911,6 +6911,56 @@
       </x:c>
       <x:c r="P5" s="269" t="str">
         <x:v>根节点=Enemy3D(CharacterBody3D)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="54" customHeight="1">
+      <x:c r="A6" s="136" t="str">
+        <x:v>ENM-ELITE-RIFT-BOAR-ARMED-3D</x:v>
+      </x:c>
+      <x:c r="B6" s="136" t="str">
+        <x:v>背枪的裂口爬虫</x:v>
+      </x:c>
+      <x:c r="C6" s="136" t="str">
+        <x:v>assets/art/enemies/elite_3d/rift_boar_armed/runtime/enm_elite_rift_boar_armed_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="D6" s="136" t="str">
+        <x:v>assets/art/enemies/elite_3d/rift_boar_armed/components/enm_elite_rift_boar_armed_visual_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="E6" s="136" t="str">
+        <x:v>assets/art/enemies/elite_3d/rift_boar_armed/source/enm_elite_rift_boar_armed_source_v001.blend</x:v>
+      </x:c>
+      <x:c r="F6" s="136" t="str">
+        <x:v>首只唯一精英独立表现、背负副枪与命名专属血条</x:v>
+      </x:c>
+      <x:c r="G6" s="136" t="str">
+        <x:v>src/enemy3d/EliteContentCatalog.gd; src/enemy3d/EliteRosterService.gd; src/enemy3d/EnemyAvatar3D.gd; src/enemy3d/Enemy3D.gd</x:v>
+      </x:c>
+      <x:c r="H6" s="136" t="str">
+        <x:v>关（表现资产）</x:v>
+      </x:c>
+      <x:c r="I6" s="136" t="str">
+        <x:v>Enemy3D</x:v>
+      </x:c>
+      <x:c r="J6" s="136" t="str">
+        <x:v>复用melee_chaser CylinderShape3D</x:v>
+      </x:c>
+      <x:c r="K6" s="136" t="str">
+        <x:v>1.970×1.843×1.345m；18 Mesh；4材质</x:v>
+      </x:c>
+      <x:c r="L6" s="136" t="str">
+        <x:v>底部可预测；Blender -Y / Godot -Z 正面；根Scale=1</x:v>
+      </x:c>
+      <x:c r="M6" s="136" t="str">
+        <x:v>每次行动按run_seed在98F/97F/96F三选一；目标层随机ELITE房</x:v>
+      </x:c>
+      <x:c r="N6" s="136" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="O6" s="136" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="P6" s="136" t="str">
+        <x:v>AssetID与elite_id稳定；其余11只仍为design_only，完成专项前不投放。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -37845,6 +37895,82 @@
         <x:v>2026-08-20：本轮基地系统、角色母版与资产流程登记。</x:v>
       </x:c>
     </x:row>
+    <x:row r="287" ht="56" customHeight="1">
+      <x:c r="A287" s="136" t="str">
+        <x:v>ENM-ELITE-RIFT-BOAR-ARMED-3D</x:v>
+      </x:c>
+      <x:c r="B287" s="136" t="str">
+        <x:v>背枪的裂口爬虫3D精英根</x:v>
+      </x:c>
+      <x:c r="C287" s="136" t="str">
+        <x:v>敌人</x:v>
+      </x:c>
+      <x:c r="D287" s="136" t="str">
+        <x:v>elite</x:v>
+      </x:c>
+      <x:c r="E287" s="136" t="str">
+        <x:v>elite_rift_boar_armed</x:v>
+      </x:c>
+      <x:c r="F287" s="136" t="str">
+        <x:v>root_3d</x:v>
+      </x:c>
+      <x:c r="G287" s="136" t="str">
+        <x:v>ENM-ECOSYSTEM-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H287" s="136" t="str">
+        <x:v>Top3D / local -Z 正面</x:v>
+      </x:c>
+      <x:c r="I287" s="136" t="str">
+        <x:v>default / armed_rush</x:v>
+      </x:c>
+      <x:c r="J287" s="136" t="str">
+        <x:v>每次行动98—96F三选一；目标层随机ELITE房</x:v>
+      </x:c>
+      <x:c r="K287" s="136" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="L287" s="136" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M287" s="136" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N287" s="136" t="str">
+        <x:v>1.970×1.843×1.345m；18 Mesh；4材质</x:v>
+      </x:c>
+      <x:c r="O287" s="136" t="str">
+        <x:v>assets/art/enemies/elite_3d/rift_boar_armed/runtime/enm_elite_rift_boar_armed_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="P287" s="136" t="str">
+        <x:v>assets/art/enemies/elite_3d/rift_boar_armed/source/enm_elite_rift_boar_armed_source_v001.blend; assets/art/enemies/elite_3d/rift_boar_armed/components/enm_elite_rift_boar_armed_visual_top3d_v001.glb; scripts/blender/build_elite_rift_boar_armed_v001.py; src/enemy3d/EliteContentCatalog.gd</x:v>
+      </x:c>
+      <x:c r="Q287" s="136" t="str">
+        <x:v>唯一精英;背枪;裂口爬虫;elite_rift_boar_armed;armed_rush;98F;97F;96F;命名血条</x:v>
+      </x:c>
+      <x:c r="R287" s="136" t="str">
+        <x:f>TEXTJOIN("|",TRUE,C287,D287,E287,F287,H287,I287)</x:f>
+        <x:v>敌人|elite|elite_rift_boar_armed|root_3d|Top3D / local -Z 正面|default / armed_rush</x:v>
+      </x:c>
+      <x:c r="S287" s="136" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$400,R287)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T287" s="136" t="str">
+        <x:v>c72d424955324da743f681ce384116e36c9972aaf8b64a23287f0e8ec8591f76</x:v>
+      </x:c>
+      <x:c r="U287" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V287" s="137" t="n">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="W287" s="136" t="str">
+        <x:v>原创 Blender/Godot 组合</x:v>
+      </x:c>
+      <x:c r="X287" s="136" t="str">
+        <x:v>GLB仅表现；core/shell/appendages/weapon_attachment/state_vfx语义齐全；PackedScene无碰撞；Enemy3D继续持有melee_chaser碰撞、AI、生命、伤害与掉落。Forward+固定机位与专项验收通过。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:X2"/>
@@ -37870,7 +37996,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R934658663b8c4c41"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0de1ea16db74209"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44706,13 +44832,27 @@
       </x:c>
     </x:row>
     <x:row r="24" ht="100" customHeight="1">
-      <x:c r="A24" s="136"/>
-      <x:c r="B24" s="136"/>
-      <x:c r="C24" s="136"/>
-      <x:c r="D24" s="136"/>
-      <x:c r="E24" s="136"/>
-      <x:c r="F24" s="136"/>
-      <x:c r="G24" s="136"/>
+      <x:c r="A24" s="136" t="str">
+        <x:v>v0.1.20</x:v>
+      </x:c>
+      <x:c r="B24" s="137" t="n">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C24" s="136" t="str">
+        <x:v>首只唯一精英正式资产</x:v>
+      </x:c>
+      <x:c r="D24" s="136" t="str">
+        <x:v>1 Blend / 1 GLB / 1 Prefab / 98—96F投放</x:v>
+      </x:c>
+      <x:c r="E24" s="136" t="str">
+        <x:v>登记背枪的裂口爬虫独立模型、四材质、五类语义组件、命名血条和表现/碰撞解耦。</x:v>
+      </x:c>
+      <x:c r="F24" s="136" t="str">
+        <x:v>稳定elite_id、AI、生命、伤害、掉落、跨局档案与基础碰撞不变；其余11只不投放。</x:v>
+      </x:c>
+      <x:c r="G24" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="115" customHeight="1">
       <x:c r="A25" s="136"/>
@@ -45102,15 +45242,15 @@
       </x:c>
       <x:c r="C9" s="280" t="n">
         <x:f>COUNTA('3D-敌人'!$A$5:$A$204)</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D9" s="280" t="n">
         <x:f>COUNTIF('3D-敌人'!$D$5:$D$204,"&lt;&gt;")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E9" s="280" t="n">
         <x:f>COUNTIF('3D-敌人'!$G$5:$G$204,"&lt;&gt;")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F9" s="280" t="n">
         <x:f>COUNTIF('3D-敌人'!$H$5:$H$204,"开")</x:f>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rffe08f9c654345a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rdc4d5224fbc94eea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R80e88c0fa44a4860"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R1af8d240d72c40bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rfbbfe682192b4416"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R111b910119f24b05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Rd5fe3728dbc24de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R899ee53eaf1d4a08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="R70e03601a4644bc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R18b1e9f318f2473c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R3bff623e6c494bee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R49bb29fb0ede48d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R3c17055cc9124773"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R6444e17d203e4d94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="Re7fa44e389db4b7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R8bb9dc07b1a54d5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R42fef5f9b4684021"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="R2f9f971e5eb1428d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="Rf3b3217d302d4fba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R73e418439e594897"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rcb3bdfe2d98440b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R5f15db93db9c403b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R453df370f0644bb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R4987e7eabd0648e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb8c6384bb7c144a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R11ea280446784fac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R8c677c472ccf4f0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="R864f4b296e78486e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="Rfb50cc8f5128411d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R9e172d6a84e3493a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="Rc359ed7a60aa4c77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="Rb8d5cab75028451c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R148fc189b5d04318"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="Rf284a3db0baa44e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="Rde157e928e564a7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="Rdf17db2b6e8b4652"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="R56d4bb2ad3b9497e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R201c53da83cf45c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2476,10 +2476,8 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
-      <x:c r="A2" s="145" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">关卡结构、地板、墙体、走廊、楼梯、楼板与环境套件；当前 55 个独立Prefab。</x:t>
-        </x:is>
+      <x:c r="A2" s="145" t="str">
+        <x:v>关卡结构、地板、墙体、走廊、楼梯与楼板；场景模型统一引用 assets/art/shared/palette/设施低亮多巴胺色盘_10x10_512.png。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6819,10 +6817,8 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
-      <x:c r="A2" s="145" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">门扇、灯具、开关、终端、工作台、储物与服务设施；当前 17 个独立Prefab。</x:t>
-        </x:is>
+      <x:c r="A2" s="145" t="str">
+        <x:v>门扇、终端、工作台、储物与服务设施；设施模型统一引用 assets/art/shared/palette/设施低亮多巴胺色盘_10x10_512.png。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -12073,18 +12069,14 @@
           <x:t xml:space="preserve">current</x:t>
         </x:is>
       </x:c>
-      <x:c r="H6" s="345" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">本轮已迭代</x:t>
-        </x:is>
+      <x:c r="H6" s="345" t="str">
+        <x:v>本轮已迭代</x:v>
       </x:c>
       <x:c r="I6" s="346" t="n">
-        <x:v>46254</x:v>
-      </x:c>
-      <x:c r="J6" s="345" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">新增连接模块、高度、坡面、栏杆和投影规则</x:t>
-        </x:is>
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="J6" s="345" t="str">
+        <x:v>强制场景/设施Blender母版仅外链项目公共色盘；GLB禁止嵌图并启用共享色盘验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="56" customHeight="1">
@@ -12123,18 +12115,14 @@
           <x:t xml:space="preserve">current</x:t>
         </x:is>
       </x:c>
-      <x:c r="H7" s="345" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">本轮已迭代</x:t>
-        </x:is>
+      <x:c r="H7" s="345" t="str">
+        <x:v>本轮已迭代</x:v>
       </x:c>
       <x:c r="I7" s="346" t="n">
-        <x:v>46254</x:v>
-      </x:c>
-      <x:c r="J7" s="345" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">新增Prefab台账、结构碰撞和物理楼层规则</x:t>
-        </x:is>
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="J7" s="345" t="str">
+        <x:v>强制场景/设施GLB丢弃嵌入贴图，并由统一后导入脚本绑定公共色盘。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="56" customHeight="1">
@@ -43831,7 +43819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc19beec6666a452c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac91196f6e774148"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -50915,13 +50903,27 @@
       </x:c>
     </x:row>
     <x:row r="26" ht="118" customHeight="1">
-      <x:c r="A26" s="136" t="n"/>
-      <x:c r="B26" s="136" t="n"/>
-      <x:c r="C26" s="136" t="n"/>
-      <x:c r="D26" s="136" t="n"/>
-      <x:c r="E26" s="136" t="n"/>
-      <x:c r="F26" s="136" t="n"/>
-      <x:c r="G26" s="136" t="n"/>
+      <x:c r="A26" s="136" t="str">
+        <x:v>v0.1.22</x:v>
+      </x:c>
+      <x:c r="B26" s="136" t="n">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C26" s="136" t="str">
+        <x:v>场景与设施公共色盘合并</x:v>
+      </x:c>
+      <x:c r="D26" s="136" t="str">
+        <x:v>35个Blend / 44个GLB / 51份重复贴图 / 2项Skill</x:v>
+      </x:c>
+      <x:c r="E26" s="136" t="str">
+        <x:v>Blender母版统一外链固定色盘；GLB移除嵌图；Godot后导入脚本统一绑定；删除组件目录重复PNG。</x:v>
+      </x:c>
+      <x:c r="F26" s="136" t="str">
+        <x:v>不改网格、UV、碰撞、Prefab、AssetID与玩法逻辑；旧版本GLB同样采用统一运行时贴图。</x:v>
+      </x:c>
+      <x:c r="G26" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="118" customHeight="1">
       <x:c r="A27" s="136" t="n"/>
@@ -51072,10 +51074,8 @@
       <x:c r="Q1" s="136" t="n"/>
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
-      <x:c r="A2" s="312" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">详细Prefab不再集中堆放；按分类进入独立分页。本次扫描排除测试场景、UI页面和整关卡入口。</x:t>
-        </x:is>
+      <x:c r="A2" s="312" t="str">
+        <x:v>详细Prefab按分类进入独立分页；场景与固定设施统一使用项目公共色盘，不在模型目录复制贴图。</x:v>
       </x:c>
       <x:c r="H2" s="136" t="n"/>
       <x:c r="I2" s="136" t="n"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R9f5353c9f0f74460"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rf4007becf3784a4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Ree9630c25d33459b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R01ed5428dab14ff4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Re856d5ee93e44599"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R12cf9b41afc64495"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Re51fd9ee750d4786"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R13034c24ded944a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Rffe974c8f08941b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="Ra423ed392708402d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R8751172937554a44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="Rb27b80af0e0047c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R4f31a269550f414b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="Rd1b9d200bf834cbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="R06b4472ed3454dea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="Rbebd04fce47f4c63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R1bd8bfac555e4f3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Re61b0d06df6644d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R9372ad02f4824afa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rde4f5de54a674b69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R05f6a0db583c4eef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rf5e69bbbdbe74b41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R58a3b0f4b6d244f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R9d011f109e2a42ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb4261a59cbc04bc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R953064830c3f4d1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rb79ca1e81d5644e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="R352e226e392e49d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="Rd50b4533f9354baa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="Re43b025197604ff0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="Recb035a5520240ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R980ff08471ce4b33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="Rc3f151c05eca413f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="Re8aa3c5d8310417a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R54f77311a7414610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="Rda3808a7bc0e47ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="R7153f435a9eb444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R46ac016e037b42a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5414,61 +5414,41 @@
           <x:t xml:space="preserve">塔楼9米通用双跑楼梯间</x:t>
         </x:is>
       </x:c>
-      <x:c r="C43" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">assets/art/props/dungeon_3d/prp_tower_stairwell_generic_9m.tscn</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D43" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">assets/art/environments/tower_descent_3d/components/env_tower_stairwell_generic_9m_top3d_v001.glb</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E43" s="192" t="str"/>
-      <x:c r="F43" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Godot原生场景结构Prefab；由关卡脚本按模块实例化</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G43" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">src/world3d/TowerFloorStage3D.gd</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H43" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">无</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I43" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">无</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J43" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">无</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K43" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GLB / 14.751×27.617×约18.41m包围 / 9m层差 / 48子对象</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L43" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">未声明</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M43" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">99层以下通用楼梯/四向旋转/上下楼交通</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N43" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">原型已接入</x:t>
-        </x:is>
+      <x:c r="C43" s="192" t="str">
+        <x:v>assets/art/props/dungeon_3d/prp_tower_stairwell_generic_9m_v001.tscn</x:v>
+      </x:c>
+      <x:c r="D43" s="192" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_stairwell_generic_9m_top3d_v003.glb</x:v>
+      </x:c>
+      <x:c r="E43" s="192" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/source/env_tower_descent_kit_top3d_v010.blend</x:v>
+      </x:c>
+      <x:c r="F43" s="192" t="str">
+        <x:v>版本化PackedScene包装；运行时实例化GLB并从Walkable与四面可见围护生成同形碰撞</x:v>
+      </x:c>
+      <x:c r="G43" s="192" t="str">
+        <x:v>src/world3d/TowerDescent3D.gd</x:v>
+      </x:c>
+      <x:c r="H43" s="192" t="str">
+        <x:v>开</x:v>
+      </x:c>
+      <x:c r="I43" s="192" t="str">
+        <x:v>TowerDescent3D运行时包装</x:v>
+      </x:c>
+      <x:c r="J43" s="192" t="str">
+        <x:v>ConcavePolygonShape3D（同形围护/Walkable）</x:v>
+      </x:c>
+      <x:c r="K43" s="192" t="str">
+        <x:v>GLB / 15×30m占地 / 9m层差 / 四面8.9m围护 / 48子对象</x:v>
+      </x:c>
+      <x:c r="L43" s="192" t="str">
+        <x:v>v003</x:v>
+      </x:c>
+      <x:c r="M43" s="192" t="str">
+        <x:v>99层以下通用楼梯/四向旋转/上下楼交通</x:v>
+      </x:c>
+      <x:c r="N43" s="192" t="str">
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="O43" s="192" t="inlineStr">
         <x:is>
@@ -5492,61 +5472,41 @@
           <x:t xml:space="preserve">塔楼楼顶特殊双跑楼梯间</x:t>
         </x:is>
       </x:c>
-      <x:c r="C44" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">assets/art/props/dungeon_3d/prp_tower_stairwell_rooftop_9m.tscn</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D44" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">assets/art/environments/tower_descent_3d/components/env_tower_stairwell_rooftop_9m_top3d_v001.glb</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E44" s="192" t="str"/>
-      <x:c r="F44" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Godot原生场景结构Prefab；由关卡脚本按模块实例化</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G44" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">src/world3d/TowerFloorStage3D.gd</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H44" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">无</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I44" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">无</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J44" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">无</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K44" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GLB / 14.751×27.617×约15.36m包围 / 9m层差 / 47子对象</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L44" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">未声明</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M44" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">楼顶至99层特殊交通/保留手调墙高</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N44" s="192" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">原型已接入</x:t>
-        </x:is>
+      <x:c r="C44" s="192" t="str">
+        <x:v>assets/art/props/dungeon_3d/prp_tower_stairwell_rooftop_9m_v001.tscn</x:v>
+      </x:c>
+      <x:c r="D44" s="192" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_stairwell_rooftop_9m_top3d_v003.glb</x:v>
+      </x:c>
+      <x:c r="E44" s="192" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/source/env_tower_descent_kit_top3d_v010.blend</x:v>
+      </x:c>
+      <x:c r="F44" s="192" t="str">
+        <x:v>版本化PackedScene包装；运行时实例化GLB并从Walkable与四面可见围护生成同形碰撞</x:v>
+      </x:c>
+      <x:c r="G44" s="192" t="str">
+        <x:v>src/world3d/TowerDescent3D.gd</x:v>
+      </x:c>
+      <x:c r="H44" s="192" t="str">
+        <x:v>开</x:v>
+      </x:c>
+      <x:c r="I44" s="192" t="str">
+        <x:v>TowerDescent3D运行时包装</x:v>
+      </x:c>
+      <x:c r="J44" s="192" t="str">
+        <x:v>ConcavePolygonShape3D（同形围护/Walkable）</x:v>
+      </x:c>
+      <x:c r="K44" s="192" t="str">
+        <x:v>GLB / 15×30m占地 / 9m层差 / 四面8.9m围护 / 47子对象</x:v>
+      </x:c>
+      <x:c r="L44" s="192" t="str">
+        <x:v>v003</x:v>
+      </x:c>
+      <x:c r="M44" s="192" t="str">
+        <x:v>楼顶至99层特殊交通/保留手调墙高</x:v>
+      </x:c>
+      <x:c r="N44" s="192" t="str">
+        <x:v>原型已接入</x:v>
       </x:c>
       <x:c r="O44" s="192" t="inlineStr">
         <x:is>
@@ -28968,25 +28928,17 @@
           <x:t xml:space="preserve">P0</x:t>
         </x:is>
       </x:c>
-      <x:c r="M168" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">v001</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N168" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GLB / 14.751×27.617×约18.41m包围 / 9m层差 / 48子对象</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O168" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">assets/art/environments/tower_descent_3d/components/env_tower_stairwell_generic_9m_top3d_v001.glb</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P168" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Blender根=Stair_Generic_Rotatable_ROOT; env_tower_descent_kit_top3d_v007.blend; export_env_tower_stairwells_v001.py; TowerDescent3D.gd; tests/verification/verify_tower_descent_flow.tscn</x:t>
-        </x:is>
+      <x:c r="M168" s="306" t="str">
+        <x:v>v003</x:v>
+      </x:c>
+      <x:c r="N168" s="306" t="str">
+        <x:v>GLB / 15×30m占地 / 9m层差 / 四面8.9m可见围护 / 48子对象</x:v>
+      </x:c>
+      <x:c r="O168" s="306" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_stairwell_generic_9m_top3d_v003.glb</x:v>
+      </x:c>
+      <x:c r="P168" s="306" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/source/env_tower_descent_kit_top3d_v010.blend; assets/art/environments/tower_descent_3d/source/upgrade_env_tower_stairwell_5m_v010.py; assets/art/environments/tower_descent_3d/source/export_env_tower_stairwells_v003.py; src/world3d/TowerDescent3D.gd; tests/verification/verify_tower_grid_component_alignment.tscn; tests/verification/verify_tower_lighting_wall_combat_regressions.tscn</x:v>
       </x:c>
       <x:c r="Q168" s="306" t="inlineStr">
         <x:is>
@@ -29001,10 +28953,8 @@
         <x:f>IF(COUNTIF($R$6:$R$300,R168)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T168" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">b0416e02b70673bb4cc38a58436210ff04343f6d68b4f5b80f8e1a0c5daaf844</x:t>
-        </x:is>
+      <x:c r="T168" s="306" t="str">
+        <x:v>568ce8602fb4bc0cbc3b3a9912fe871fed55705e77f3dcb0e53a88b6b2b44e47</x:v>
       </x:c>
       <x:c r="U168" s="306" t="inlineStr">
         <x:is>
@@ -29012,7 +28962,7 @@
         </x:is>
       </x:c>
       <x:c r="V168" s="307" t="n">
-        <x:v>46237</x:v>
+        <x:v>46264</x:v>
       </x:c>
       <x:c r="W168" s="306" t="inlineStr">
         <x:is>
@@ -29022,7 +28972,8 @@
       <x:c r="X168" s="306" t="str">
         <x:v>v0.1：继续直接复用用户v006通用9m楼梯视觉与六块Walkable同形常驻碰撞；按5m世界矩形对齐250m整层中的四向楼梯洞口，可旋转通用。上下端门侧分别记录，避免楼梯开口朝向改变后沿用同一侧导致错位。
 2026-08-03：四面围护墙全部直接从可视Mesh生成同形ConcavePolygon碰撞，碰撞不再越过楼梯接口伸入相邻房间。
-2026-08-03：整层布局把楼梯折返空间登记为排他占位，并用导入Mesh世界AABB复核非接口房间；随机支路、普通房和Boss区不得侵入。</x:v>
+2026-08-03：整层布局把楼梯折返空间登记为排他占位，并用导入Mesh世界AABB复核非接口房间；随机支路、普通房和Boss区不得侵入。
+2026-08-30 TWR-01：运行时升级到Blender v010 / GLB v003。由最后干净v008重建，编辑网格先转单用户，消除v009共享网格串改和通用楼梯重复Far墙；两个变体均严格保持四面围护、-9.0..-0.1m可见高度、15×30m占地与下平台-8.9m顶面。Godot从可见网格生成同形碰撞；网格与灯光/墙体综合回归通过。SHA-256 568ce8602fb4。</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="132" customHeight="1">
@@ -29082,25 +29033,17 @@
           <x:t xml:space="preserve">P0</x:t>
         </x:is>
       </x:c>
-      <x:c r="M169" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">v001</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N169" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GLB / 14.751×27.617×约15.36m包围 / 9m层差 / 47子对象</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O169" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">assets/art/environments/tower_descent_3d/components/env_tower_stairwell_rooftop_9m_top3d_v001.glb</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P169" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Blender根=Stair_Special_Rooftop_ROOT; env_tower_descent_kit_top3d_v007.blend; export_env_tower_stairwells_v001.py; TowerDescent3D.gd; tests/verification/verify_tower_descent_flow.tscn</x:t>
-        </x:is>
+      <x:c r="M169" s="306" t="str">
+        <x:v>v003</x:v>
+      </x:c>
+      <x:c r="N169" s="306" t="str">
+        <x:v>GLB / 15×30m占地 / 9m层差 / 四面8.9m可见围护 / 47子对象</x:v>
+      </x:c>
+      <x:c r="O169" s="306" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_stairwell_rooftop_9m_top3d_v003.glb</x:v>
+      </x:c>
+      <x:c r="P169" s="306" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/source/env_tower_descent_kit_top3d_v010.blend; assets/art/environments/tower_descent_3d/source/upgrade_env_tower_stairwell_5m_v010.py; assets/art/environments/tower_descent_3d/source/export_env_tower_stairwells_v003.py; src/world3d/TowerDescent3D.gd; tests/verification/verify_tower_grid_component_alignment.tscn; tests/verification/verify_tower_lighting_wall_combat_regressions.tscn</x:v>
       </x:c>
       <x:c r="Q169" s="306" t="inlineStr">
         <x:is>
@@ -29115,10 +29058,8 @@
         <x:f>IF(COUNTIF($R$6:$R$300,R169)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T169" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">88198a579cc846974f17f5203b46b568b7ab2421fd7bb63c0b7868ddd05684a2</x:t>
-        </x:is>
+      <x:c r="T169" s="306" t="str">
+        <x:v>47ba302134fc12a6e0f0ee8a2834bce431c143e5fe0f4ecefe372f53851dd040</x:v>
       </x:c>
       <x:c r="U169" s="306" t="inlineStr">
         <x:is>
@@ -29126,7 +29067,7 @@
         </x:is>
       </x:c>
       <x:c r="V169" s="307" t="n">
-        <x:v>46237</x:v>
+        <x:v>46264</x:v>
       </x:c>
       <x:c r="W169" s="306" t="inlineStr">
         <x:is>
@@ -29135,7 +29076,8 @@
       </x:c>
       <x:c r="X169" s="306" t="str">
         <x:v>2026-08-02：楼梯间南侧围墙补齐相机抬升元数据；与99层基地之间使用5m地砖及墙体组件拼接可见封闭走廊。
-2026-08-03：四面围护墙全部直接从可视Mesh生成同形ConcavePolygon碰撞；南侧可视墙继续承担相机抬升判定。</x:v>
+2026-08-03：四面围护墙全部直接从可视Mesh生成同形ConcavePolygon碰撞；南侧可视墙继续承担相机抬升判定。
+2026-08-30 TWR-01：运行时升级到Blender v010 / GLB v003。由最后干净v008重建，编辑网格先转单用户，消除v009共享网格串改和通用楼梯重复Far墙；两个变体均严格保持四面围护、-9.0..-0.1m可见高度、15×30m占地与下平台-8.9m顶面。Godot从可见网格生成同形碰撞；网格与灯光/墙体综合回归通过。SHA-256 47ba302134fc。</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -42961,7 +42903,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc326db2f85204853"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a735fad25834523"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rde4f5de54a674b69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R05f6a0db583c4eef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rf5e69bbbdbe74b41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R58a3b0f4b6d244f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R9d011f109e2a42ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb4261a59cbc04bc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R953064830c3f4d1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rb79ca1e81d5644e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="R352e226e392e49d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="Rd50b4533f9354baa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="Re43b025197604ff0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="Recb035a5520240ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R980ff08471ce4b33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="Rc3f151c05eca413f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="Re8aa3c5d8310417a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R54f77311a7414610"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="Rda3808a7bc0e47ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="R7153f435a9eb444a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R46ac016e037b42a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb7bb234acb0448e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rfe2b6e764c3147ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R30de9618b3c84024"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R11eb6056479a4323"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R6d8199beb417470e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R7a92bb8947d3461e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Rdb58194673b748f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Red8499a0afd14a5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="R6571a47c5c664b99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R2390bc2ae5ac48ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R81e3f87924e04ad9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R882369e08bac4777"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="Rf2c0e02ef8af4360"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R9a59d04d1c1b418d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="R867a848145f04e5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="Reb035b6c75ce4449"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R494c9ff5f9554756"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Rea580d59a1e74d4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R86d72343a7844160"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2081,13 +2081,11 @@
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="321" t="n">
-        <x:f>COUNTA('资产主表'!$A$6:$A$300)</x:f>
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B6" s="319"/>
       <x:c r="C6" s="321" t="n">
-        <x:f>COUNTIF('资产主表'!$K$6:$K$300,"已完成")+COUNTIF('资产主表'!$K$6:$K$300,"原型已接入")</x:f>
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D6" s="319" t="n"/>
       <x:c r="E6" s="321" t="n">
@@ -2100,10 +2098,8 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="319" t="n"/>
-      <x:c r="I6" s="322" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">v0.1 3D塔楼：5m组件网格 / 99+100F基地打通 / 可编辑楼板与楼梯Prefab</x:t>
-        </x:is>
+      <x:c r="I6" s="322" t="str">
+        <x:v>v0.1 3D塔楼：5m组件网格 / 99+100F基地打通 / 90×80m天台北侧贴边抬高生活棚、36项独立阻挡、黄色动线零阻挡与双净空契约</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2299,12 +2295,10 @@
         </x:is>
       </x:c>
       <x:c r="B14" s="331" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$300,A14)</x:f>
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C14" s="331" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$300,A14,'资产主表'!$K$6:$K$300,"已完成")+COUNTIFS('资产主表'!$C$6:$C$300,A14,'资产主表'!$K$6:$K$300,"原型已接入")</x:f>
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D14" s="319" t="n"/>
       <x:c r="E14" s="330" t="inlineStr">
@@ -6728,6 +6722,56 @@
       </x:c>
       <x:c r="P60" t="str">
         <x:v>Blender源文件重导；六条高低位物理射线命中；北侧由基地外墙封闭；v002保留回滚。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str">
+        <x:v>ENV-ROOFTOP-SHELTER-90X80</x:v>
+      </x:c>
+      <x:c r="B61" t="str">
+        <x:v>90×80米天台可编辑生活聚落设施</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>assets/art/environments/rooftop_shelter_3d/runtime/env_rooftop_shelter_90x80m_facilities_root_top3d_v017.tscn</x:v>
+      </x:c>
+      <x:c r="D61" t="str">
+        <x:v>assets/art/environments/rooftop_shelter_3d/runtime/layout_v017/components/*.glb（68个）</x:v>
+      </x:c>
+      <x:c r="E61" t="str">
+        <x:v>assets/art/environments/rooftop_shelter_3d/source/env_rooftop_shelter_90x80m_top3d_v017.blend</x:v>
+      </x:c>
+      <x:c r="F61" t="str">
+        <x:v>facilities_only；不导入Blender地板、围护、灯光、植被、VFX与远景；公共色盘；真实投影</x:v>
+      </x:c>
+      <x:c r="G61" t="str">
+        <x:v>src/world3d/TowerFloorStage3D.gd</x:v>
+      </x:c>
+      <x:c r="H61" t="str">
+        <x:v>开</x:v>
+      </x:c>
+      <x:c r="I61" t="str">
+        <x:v>Prefab自身 + TowerFloorStage3D</x:v>
+      </x:c>
+      <x:c r="J61" t="str">
+        <x:v>39个组件级StaticBody3D / 82个Box或Cylinder细分形状；视觉与碰撞随组件共同移动</x:v>
+      </x:c>
+      <x:c r="K61" t="str">
+        <x:v>68个设施组件；布局根Y=-0.34；黄色门前通道零阻挡；Godot原生地砖/围栏/门洞保持</x:v>
+      </x:c>
+      <x:c r="L61" t="str">
+        <x:v>世界矩形参照(-50,-35,90,80)；Godot根缩放1；原生地面Y=0</x:v>
+      </x:c>
+      <x:c r="M61" t="str">
+        <x:v>100F天台</x:v>
+      </x:c>
+      <x:c r="N61" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="O61" t="str">
+        <x:v>v016</x:v>
+      </x:c>
+      <x:c r="P61" t="str">
+        <x:v>通信区(30.5,34,9.5,10.5)位于东北角；棚屋区(7.5,27.5,21,17.5)位于其西侧；种植区(-24,22,12.5,20)；温室只阻挡立柱、太阳能板薄斜面、圆形设施圆柱碰撞；31,461面PaletteUV严格验收通过；Blend SHA256=d5f6c949f89c9aa863f37e41840d23b1308fa03abe024aa93005b421a778a38f；v015保留回滚。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -42822,6 +42866,82 @@
       </x:c>
       <x:c r="X300" t="str">
         <x:v>2026-08-30 AST-04：独立正式场景资产补登记，暂未接入游戏玩法；asset_guard PASS；Blender严格验收通过：4032/4032输出网格、30219/30219面色盘UV有效、4材质、公共色盘唯一外链、无展示地面/混合自发光。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301">
+      <x:c r="A301" t="str">
+        <x:v>ENV-ROOFTOP-SHELTER-90X80</x:v>
+      </x:c>
+      <x:c r="B301" t="str">
+        <x:v>90×80米天台可编辑生活聚落设施</x:v>
+      </x:c>
+      <x:c r="C301" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D301" t="str">
+        <x:v>屋顶环境</x:v>
+      </x:c>
+      <x:c r="E301" t="str">
+        <x:v>rooftop_shelter_90x80</x:v>
+      </x:c>
+      <x:c r="F301" t="str">
+        <x:v>root</x:v>
+      </x:c>
+      <x:c r="G301" t="str">
+        <x:v>ENV-ROOFTOP-SHELTER-50M-3D</x:v>
+      </x:c>
+      <x:c r="H301" t="str">
+        <x:v>3D</x:v>
+      </x:c>
+      <x:c r="I301" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="J301" t="str">
+        <x:v>100F天台设施专用</x:v>
+      </x:c>
+      <x:c r="K301" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="L301" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M301" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N301" t="str">
+        <x:v>设施专用包装；68个TSCN可编辑组件；39组/82形状组合碰撞；布局根Y=-0.34；4共享材质</x:v>
+      </x:c>
+      <x:c r="O301" t="str">
+        <x:v>assets/art/environments/rooftop_shelter_3d/runtime/env_rooftop_shelter_90x80m_facilities_root_top3d_v017.tscn；assets/art/environments/rooftop_shelter_3d/runtime/layout_v017/components/</x:v>
+      </x:c>
+      <x:c r="P301" t="str">
+        <x:v>src/world3d/TowerFloorStage3D.gd；assets/art/environments/rooftop_shelter_3d/source/env_rooftop_shelter_90x80m_top3d_v017.blend；assets/art/environments/rooftop_shelter_3d/reports/validation_v017.json；assets/art/environments/rooftop_shelter_3d/reports/collision_manifest_v017.json；tests/verification/verify_rooftop_shelter_asset_contract.tscn</x:v>
+      </x:c>
+      <x:c r="Q301" t="str">
+        <x:v>rooftop facilities only；native floor and parapet preserved；68 components；39 blockers；82 shapes</x:v>
+      </x:c>
+      <x:c r="R301" t="str">
+        <x:f>LOWER(TRIM(C301)&amp;"|"&amp;TRIM(D301)&amp;"|"&amp;TRIM(E301)&amp;"|"&amp;TRIM(F301)&amp;"|"&amp;TRIM(H301)&amp;"|"&amp;TRIM(I301))</x:f>
+        <x:v>场景|屋顶环境|rooftop_shelter_90x80|root|3d|default</x:v>
+      </x:c>
+      <x:c r="S301" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$301,R301)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T301" t="str">
+        <x:v>24496a071a478409e294480734c1880e37240c4ed346e74195adf2da779c7a33</x:v>
+      </x:c>
+      <x:c r="U301" t="str">
+        <x:v>美术/程序</x:v>
+      </x:c>
+      <x:c r="V301" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="W301" t="str">
+        <x:v>项目自制/内部使用</x:v>
+      </x:c>
+      <x:c r="X301" t="str">
+        <x:v>2026-08-31 v015：生活棚整体北移并以木平台贴合天台边缘，平台高0.5m且设三块踏步/连续坡面碰撞；黄色门前动线阻挡0；种植区与通信区按标注分离。TowerFloorStage3D已正式实例化v015并隐藏旧程序化视觉；68个语义目录待归类对象0，36项主要物体各有独立阻挡；v014保留回滚。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -42903,7 +43023,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a735fad25834523"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cad7fc4aa3d4276"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -50010,58 +50130,143 @@
       </x:c>
     </x:row>
     <x:row r="27" ht="118" customHeight="1">
-      <x:c r="A27" s="136" t="n"/>
-      <x:c r="B27" s="136" t="n"/>
-      <x:c r="C27" s="136" t="n"/>
-      <x:c r="D27" s="136" t="n"/>
-      <x:c r="E27" s="136" t="n"/>
-      <x:c r="F27" s="136" t="n"/>
-      <x:c r="G27" s="136" t="n"/>
+      <x:c r="A27" s="136" t="str">
+        <x:v>v0.1.23</x:v>
+      </x:c>
+      <x:c r="B27" s="136" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C27" s="136" t="str">
+        <x:v>基地设施交互与天台90×80资产对齐</x:v>
+      </x:c>
+      <x:c r="D27" s="136" t="str">
+        <x:v>2项交互修复 / 2项设施移除 / 1个Blend / 1个GLB / 1个Prefab</x:v>
+      </x:c>
+      <x:c r="E27" s="136" t="str">
+        <x:v>交互区域改向房间中央；移除命运占卜屋和基地管理终端；按100F真实18×16网格重制天台并为基地与楼梯间留空。</x:v>
+      </x:c>
+      <x:c r="F27" s="136" t="str">
+        <x:v>不改变远征情报室与枪械工坊的位置、旋转和缩放；天台玩法碰撞继续由TowerFloorStage3D持有；v011保留回滚。</x:v>
+      </x:c>
+      <x:c r="G27" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="118" customHeight="1">
-      <x:c r="A28" s="136" t="n"/>
-      <x:c r="B28" s="136" t="n"/>
-      <x:c r="C28" s="136" t="n"/>
-      <x:c r="D28" s="136" t="n"/>
-      <x:c r="E28" s="136" t="n"/>
-      <x:c r="F28" s="136" t="n"/>
-      <x:c r="G28" s="136" t="n"/>
+      <x:c r="A28" s="136" t="str">
+        <x:v>v0.1.24</x:v>
+      </x:c>
+      <x:c r="B28" s="136" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C28" s="136" t="str">
+        <x:v>天台东侧生活聚落集中布局</x:v>
+      </x:c>
+      <x:c r="D28" s="136" t="str">
+        <x:v>1个Blend / 1个GLB / 1个Prefab / 1项聚落范围门禁</x:v>
+      </x:c>
+      <x:c r="E28" s="136" t="str">
+        <x:v>将生活、种植、能源、供水、通信和杂物集中到东侧24×67米区域；增加餐食、洗衣、晾晒、串灯、盆栽和木板生活动线。</x:v>
+      </x:c>
+      <x:c r="F28" s="136" t="str">
+        <x:v>不改90×80米地表、234格、基地中庭、西侧楼梯间、根缩放及碰撞归属；v012保留回滚。</x:v>
+      </x:c>
+      <x:c r="G28" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="84" customHeight="1">
-      <x:c r="A29" s="136" t="n"/>
-      <x:c r="B29" s="136" t="n"/>
-      <x:c r="C29" s="136" t="n"/>
-      <x:c r="D29" s="136" t="n"/>
-      <x:c r="E29" s="136" t="n"/>
-      <x:c r="F29" s="136" t="n"/>
-      <x:c r="G29" s="136" t="n"/>
+      <x:c r="A29" s="136" t="str">
+        <x:v>v0.1.25</x:v>
+      </x:c>
+      <x:c r="B29" s="136" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C29" s="136" t="str">
+        <x:v>天台部件细分与独立阻挡</x:v>
+      </x:c>
+      <x:c r="D29" s="136" t="str">
+        <x:v>1个Blend / 1个GLB / 1个Prefab / 64个组件目录 / 34个独立阻挡</x:v>
+      </x:c>
+      <x:c r="E29" s="136" t="str">
+        <x:v>将沙发、桌子、桌面收音机及能源/种植/通信设施拆分到独立语义目录；增加Blender阻挡代理与Godot独立StaticBody3D。</x:v>
+      </x:c>
+      <x:c r="F29" s="136" t="str">
+        <x:v>不改东侧聚落布局、90×80米地表、234格、基地中庭、西侧楼梯间及根缩放；v013保留回滚。</x:v>
+      </x:c>
+      <x:c r="G29" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="118" customHeight="1">
-      <x:c r="A30" s="136" t="n"/>
-      <x:c r="B30" s="136" t="n"/>
-      <x:c r="C30" s="136" t="n"/>
-      <x:c r="D30" s="136" t="n"/>
-      <x:c r="E30" s="136" t="n"/>
-      <x:c r="F30" s="136" t="n"/>
-      <x:c r="G30" s="136" t="n"/>
+      <x:c r="A30" s="136" t="str">
+        <x:v>v0.1.26</x:v>
+      </x:c>
+      <x:c r="B30" s="136" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C30" s="136" t="str">
+        <x:v>天台贴边棚屋与标注分区</x:v>
+      </x:c>
+      <x:c r="D30" s="136" t="str">
+        <x:v>1个Blend / 1个GLB / 1个Prefab / 68个组件目录 / 36个独立阻挡</x:v>
+      </x:c>
+      <x:c r="E30" s="136" t="str">
+        <x:v>将0.5米抬高生活棚整体北移至天台边缘，补充小木梯、小风车与风铃；种植区、通信区按标注重新布置，黄色门前动线保持零阻挡。</x:v>
+      </x:c>
+      <x:c r="F30" s="136" t="str">
+        <x:v>不改90×80米地表、234格、基地中庭、西侧楼梯间及根缩放；v014保留回滚。</x:v>
+      </x:c>
+      <x:c r="G30" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="118" customHeight="1">
-      <x:c r="A31" s="136" t="n"/>
-      <x:c r="B31" s="136" t="n"/>
-      <x:c r="C31" s="136" t="n"/>
-      <x:c r="D31" s="136" t="n"/>
-      <x:c r="E31" s="136" t="n"/>
-      <x:c r="F31" s="136" t="n"/>
-      <x:c r="G31" s="136" t="n"/>
+      <x:c r="A31" s="136" t="str">
+        <x:v>v0.1.27</x:v>
+      </x:c>
+      <x:c r="B31" s="136" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C31" s="136" t="str">
+        <x:v>天台TSCN可编辑布局与组合碰撞</x:v>
+      </x:c>
+      <x:c r="D31" s="136" t="str">
+        <x:v>1个Blend / 70个GLB / 1个Prefab / 68个可编辑组件 / 39组82形状阻挡</x:v>
+      </x:c>
+      <x:c r="E31" s="136" t="str">
+        <x:v>将通信高台移至东北角、棚屋置于其西侧并保留2米净距；组件拆分到TSCN五组层级，阻挡随组件移动并按结构细分。</x:v>
+      </x:c>
+      <x:c r="F31" s="136" t="str">
+        <x:v>不改90×80米地表、234格、基地中庭、西楼梯、黄色门前动线及根缩放；v015保留回滚。</x:v>
+      </x:c>
+      <x:c r="G31" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="118" customHeight="1">
-      <x:c r="A32" s="136" t="n"/>
-      <x:c r="B32" s="136" t="n"/>
-      <x:c r="C32" s="136" t="n"/>
-      <x:c r="D32" s="136" t="n"/>
-      <x:c r="E32" s="136" t="n"/>
-      <x:c r="F32" s="136" t="n"/>
-      <x:c r="G32" s="136" t="n"/>
+      <x:c r="A32" s="136" t="str">
+        <x:v>v0.1.28</x:v>
+      </x:c>
+      <x:c r="B32" s="136" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C32" s="136" t="str">
+        <x:v>天台v017仅设施导入与原生地板恢复</x:v>
+      </x:c>
+      <x:c r="D32" s="136" t="str">
+        <x:v>1个Blend / 69个GLB / 1个设施Prefab / 68个可编辑组件 / 39组82形状阻挡</x:v>
+      </x:c>
+      <x:c r="E32" s="136" t="str">
+        <x:v>正式包装改为facilities_only，排除Blender地板与围护；恢复100F原生地砖、围栏和门洞；设施布局下移0.34米对齐原生地面。</x:v>
+      </x:c>
+      <x:c r="F32" s="136" t="str">
+        <x:v>不改100F原生90×80米地表、234格、基地中庭、西楼梯、承重面、外围边界碰撞和设施平面布局；v016保留回滚。</x:v>
+      </x:c>
+      <x:c r="G32" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H32"/>
     </x:row>
     <x:row r="33" ht="128" customHeight="1">
       <x:c r="A33" s="136" t="n"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb7bb234acb0448e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rfe2b6e764c3147ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R30de9618b3c84024"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R11eb6056479a4323"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R6d8199beb417470e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R7a92bb8947d3461e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Rdb58194673b748f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Red8499a0afd14a5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="R6571a47c5c664b99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R2390bc2ae5ac48ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R81e3f87924e04ad9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R882369e08bac4777"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="Rf2c0e02ef8af4360"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R9a59d04d1c1b418d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="R867a848145f04e5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="Reb035b6c75ce4449"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R494c9ff5f9554756"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Rea580d59a1e74d4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R86d72343a7844160"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R68bef88d28464a66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R2969187735c34477"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R422f02c5d087494b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R012c1e75bb8c4436"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R73e1466cbe404844"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Re87312a43fbf4a7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Rdf3df4cd0c7441dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R6631da8fc0b74a76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Rf2ea8e3970bb4663"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R2f7f7bcf3cd4419d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R6159cc6f9d9448c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R456e67a01ec14781"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R58078533bd05404b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R6387f7c573c44d19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="R1a6e068f8c594d34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R69a6b794a99b4915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="Racfd4ba4c89a4441"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="R0f7ad306594649e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R82ec5ca25ddb4f70"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -849,7 +849,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="349">
+  <x:cellXfs count="351">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -1669,6 +1669,10 @@
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -36717,7 +36721,7 @@
 2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_base99_floor_player_collision_flow；verify_base_facility_interaction_zones；SHA 14fd4be6488e→bc849c71619f。</x:v>
       </x:c>
     </x:row>
-    <x:row r="240">
+    <x:row r="240" ht="190" customHeight="1">
       <x:c r="A240" s="136" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ENV-BASE99-ART-LAYOUT-3D</x:t>
@@ -36789,10 +36793,8 @@
           <x:t xml:space="preserve">assets/art/environments/base_facility_3d/runtime/env_base_facility_art_layout_top3d_v001.tscn</x:t>
         </x:is>
       </x:c>
-      <x:c r="P240" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">assets/art/props/base_world_3d/prp_base_facility_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/mission_operations/prp_base_mission_operations_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/weapon_workshop/prp_base_weapon_workshop_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/vending_machine/prp_base_vending_machine_root_top3d_v002.tscn; assets/art/props/base_world_3d/runtime/locker_station/prp_base_locker_station_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/retro_tv_station/prp_base_retro_tv_station_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/workshop_stool/prp_base_workshop_stool_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/mission_command_chair/prp_base_mission_command_chair_root_top3d_v001.tscn; assets/art/3D模型资产目录与命名规范.md</x:t>
-        </x:is>
+      <x:c r="P240" s="349" t="str">
+        <x:v>assets/art/props/base_world_3d/prp_base_facility_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/mission_operations/prp_base_mission_operations_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/weapon_workshop/prp_base_weapon_workshop_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/vending_machine/prp_base_vending_machine_root_top3d_v002.tscn; assets/art/props/base_world_3d/runtime/locker_station/prp_base_locker_station_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/retro_tv_station/prp_base_retro_tv_station_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/workshop_stool/prp_base_workshop_stool_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/mission_command_chair/prp_base_mission_command_chair_root_top3d_v001.tscn; assets/art/3D模型资产目录与命名规范.md; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v003.blend; scripts/blender/build_base_facility_runtime_layout_hq_v003.py; outputs/verification/base_facility_runtime_layout_hq_v003.png; outputs/verification/base_facility_runtime_layout_hq_v003_top.png; outputs/verification/base_facility_runtime_layout_hq_v003_underloft.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v004.blend; scripts/blender/build_base_facility_runtime_layout_hq_v004.py; outputs/verification/base_facility_runtime_layout_hq_v004.png; outputs/verification/base_facility_runtime_layout_hq_v004_top.png; outputs/verification/base_facility_runtime_layout_hq_v004_facilities.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v005.blend; scripts/blender/build_base_facility_runtime_layout_hq_v005.py; outputs/verification/base_facility_runtime_layout_hq_v005.png; outputs/verification/base_facility_runtime_layout_hq_v005_top.png; outputs/verification/base_facility_runtime_layout_hq_v005_stair.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v006.blend; scripts/blender/build_base_facility_runtime_layout_hq_v006.py; outputs/verification/base_facility_runtime_layout_hq_v006.png; outputs/verification/base_facility_runtime_layout_hq_v006_top.png; outputs/verification/base_facility_runtime_layout_hq_v006_floor_close.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v007.blend; source/art/blender/base_facility_layout/component_packages; scripts/blender/organize_base_facility_runtime_layout_hq_v007.py; scripts/blender/validate_base_facility_runtime_layout_hq_v007.py; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_component_catalog_v007.json; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_component_tree_v007.txt; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_runtime_layout_hq_v007.png; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_runtime_layout_hq_v007_top.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v008.blend; source/art/blender/base_facility_layout/component_packages_v008; scripts/blender/build_base_facility_runtime_layout_hq_v008.py; scripts/blender/validate_base_facility_runtime_layout_hq_v008.py; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_component_catalog_v008.json; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_component_tree_v008.txt; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008.png; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008_top.png; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008_south_facilities.png; outputs/verification/base_facility_runtime_layout_hq_v008/strict_palette_validation.log</x:v>
       </x:c>
       <x:c r="Q240" s="136" t="inlineStr">
         <x:is>
@@ -36825,7 +36827,8 @@
       </x:c>
       <x:c r="X240" s="136" t="str">
         <x:v>主场景可编辑布局；现含8个设施及楼板、L梯、外门小梯三个结构Prefab，位置旋转可在tscn直接调整。
-2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_base99_floor_player_collision_flow；verify_base_facility_interaction_zones；SHA 2ecff00457fc→9d7f7b7d6699。</x:v>
+2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_base99_floor_player_collision_flow；verify_base_facility_interaction_zones；SHA 2ecff00457fc→9d7f7b7d6699。
+2026-09-02 HQ-v003：新增30×30m高品质Blender微缩基地母版；20×10m北侧6m阁楼、15×30m东西主通道地面净空、南侧仓储/能源/供水区和240帧循环动效。复用现有墙/地板身份，设施作为独立组件重制；4个共享材质，275002/275002面PaletteUV严格验收通过。Blend SHA256=614039f9aae4。当前仅为Blender美术母版，未替换Godot运行时TSCN、GLB、碰撞或交互。</x:v>
       </x:c>
     </x:row>
     <x:row r="241">
@@ -43023,7 +43026,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cad7fc4aa3d4276"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R011bc4ad22f34fe8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49355,6 +49358,7 @@
     <x:col min="5" max="5" width="60" customWidth="1"/>
     <x:col min="6" max="6" width="48" customWidth="1"/>
     <x:col min="7" max="7" width="12" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="25" customHeight="1">
@@ -50269,49 +50273,157 @@
       <x:c r="H32"/>
     </x:row>
     <x:row r="33" ht="128" customHeight="1">
-      <x:c r="A33" s="136" t="n"/>
-      <x:c r="B33" s="136" t="n"/>
-      <x:c r="C33" s="136" t="n"/>
-      <x:c r="D33" s="136" t="n"/>
-      <x:c r="E33" s="136" t="n"/>
-      <x:c r="F33" s="136" t="n"/>
-      <x:c r="G33" s="136" t="n"/>
-    </x:row>
-    <x:row r="34" ht="96" customHeight="1">
-      <x:c r="A34" s="136" t="n"/>
-      <x:c r="B34" s="136" t="n"/>
-      <x:c r="C34" s="136" t="n"/>
-      <x:c r="D34" s="136" t="n"/>
-      <x:c r="E34" s="136" t="n"/>
-      <x:c r="F34" s="136" t="n"/>
-      <x:c r="G34" s="136" t="n"/>
-    </x:row>
-    <x:row r="35" ht="108" customHeight="1">
-      <x:c r="A35" s="136" t="n"/>
-      <x:c r="B35" s="136" t="n"/>
-      <x:c r="C35" s="136" t="n"/>
-      <x:c r="D35" s="136" t="n"/>
-      <x:c r="E35" s="136" t="n"/>
-      <x:c r="F35" s="136" t="n"/>
-      <x:c r="G35" s="136" t="n"/>
-    </x:row>
-    <x:row r="36" ht="72" customHeight="1">
-      <x:c r="A36" s="136" t="n"/>
-      <x:c r="B36" s="136" t="n"/>
-      <x:c r="C36" s="136" t="n"/>
-      <x:c r="D36" s="136" t="n"/>
-      <x:c r="E36" s="136" t="n"/>
-      <x:c r="F36" s="136" t="n"/>
-      <x:c r="G36" s="136" t="n"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="136" t="n"/>
-      <x:c r="B37" s="137" t="n"/>
-      <x:c r="C37" s="136" t="n"/>
-      <x:c r="D37" s="136" t="n"/>
-      <x:c r="E37" s="136" t="n"/>
-      <x:c r="F37" s="136" t="n"/>
-      <x:c r="G37" s="136" t="n"/>
+      <x:c r="A33" s="136" t="str">
+        <x:v>v0.1.29</x:v>
+      </x:c>
+      <x:c r="B33" s="348" t="n">
+        <x:v>46267</x:v>
+      </x:c>
+      <x:c r="C33" s="136" t="str">
+        <x:v>基地99F高品质微缩布局Blender母版</x:v>
+      </x:c>
+      <x:c r="D33" s="136" t="str">
+        <x:v>1个Blend / 3张预览 / 4共享材质 / 240帧循环动效</x:v>
+      </x:c>
+      <x:c r="E33" s="136" t="str">
+        <x:v>建立30×30米切角可视基地；北侧6米阁楼与L梯、阁楼生活区、BASE CAMP电视墙/储物/武器台/贩卖机、中央15×30米净空通道及南侧仓库设施全部细化。</x:v>
+      </x:c>
+      <x:c r="F33" s="136" t="str">
+        <x:v>仅完成Blender源与视觉验收；未替换Godot TSCN/GLB、碰撞、交互和玩法；既有运行时与v002保留回滚。</x:v>
+      </x:c>
+      <x:c r="G33" s="136" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="86" customHeight="1">
+      <x:c r="A34" s="349" t="str">
+        <x:v>v0.1.30</x:v>
+      </x:c>
+      <x:c r="B34" s="348" t="n">
+        <x:v>46268</x:v>
+      </x:c>
+      <x:c r="C34" s="349" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D34" s="349" t="str">
+        <x:v>基地99层Blender高品质布局v004</x:v>
+      </x:c>
+      <x:c r="E34" s="349" t="str">
+        <x:v>阁楼贴东墙；铁皮封闭体内部清空；重做西侧L梯；设施从南区分散到东西墙与阁楼；移除通道箭头覆层。</x:v>
+      </x:c>
+      <x:c r="F34" s="349" t="str">
+        <x:v>Blender 4.2严格验证通过：4材质，928网格，200052/200052有效PaletteUV面；三张预览人工复核通过。</x:v>
+      </x:c>
+      <x:c r="G34" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H34" s="349" t="str">
+        <x:v>仅更新Blender源场景与资产台账，未修改Godot运行时。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="96" customHeight="1">
+      <x:c r="A35" s="349" t="str">
+        <x:v>v0.1.31</x:v>
+      </x:c>
+      <x:c r="B35" s="348" t="n">
+        <x:v>46268</x:v>
+      </x:c>
+      <x:c r="C35" s="349" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D35" s="349" t="str">
+        <x:v>基地99层西北贴墙L梯布局v005</x:v>
+      </x:c>
+      <x:c r="E35" s="349" t="str">
+        <x:v>按红框将L梯移至西北墙角：第一跑贴西墙向北、转角平台贴西北角、第二跑贴北墙向东，顶层平台接入阁楼西北入口；冲突武器台移至西墙南段。</x:v>
+      </x:c>
+      <x:c r="F35" s="349" t="str">
+        <x:v>接口脚本验收通过：墙边2cm安装缝；20级总高6.09m；踏步、转角、顶层平台和阁楼完成面逐边/逐高程一致；4材质，952网格，201348/201348有效PaletteUV面。</x:v>
+      </x:c>
+      <x:c r="G35" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H35" s="349" t="str">
+        <x:v>Blender源场景版本增量；未修改Godot运行时、碰撞或玩法。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="116" customHeight="1">
+      <x:c r="A36" s="349" t="str">
+        <x:v>v0.1.32</x:v>
+      </x:c>
+      <x:c r="B36" s="348" t="n">
+        <x:v>46268</x:v>
+      </x:c>
+      <x:c r="C36" s="349" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D36" s="349" t="str">
+        <x:v>基地99层参考图地板系统深化v006</x:v>
+      </x:c>
+      <x:c r="E36" s="349" t="str">
+        <x:v>严格锁定30×30m、36块5×5m原地板与全部分缝/高低/方向；仅新增地板压边、内阴影唇、六角固定件、卡扣、编号、9组浅层检修盖、4组格栅、设备端口、全息平台地面接口、青蓝导视、橙白功能标识及轻微使用痕迹。</x:v>
+      </x:c>
+      <x:c r="F36" s="349" t="str">
+        <x:v>参考图优先视觉验收及脚本结构锁定通过；地板附着结构均在Z≤0.32m，9/36检修盖为25%；4材质，3048网格，778326/778326有效PaletteUV面；三张预览人工复核通过。</x:v>
+      </x:c>
+      <x:c r="G36" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H36" s="349" t="str">
+        <x:v>Blender源场景版本增量；南/东墙设施未重做，楼梯、墙体、设备位置与Godot运行时/碰撞/玩法均未修改。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="132" customHeight="1">
+      <x:c r="A37" s="349" t="str">
+        <x:v>v0.1.33</x:v>
+      </x:c>
+      <x:c r="B37" s="348" t="n">
+        <x:v>46268</x:v>
+      </x:c>
+      <x:c r="C37" s="349" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D37" s="349" t="str">
+        <x:v>基地99层资产包文件夹归类v007</x:v>
+      </x:c>
+      <x:c r="E37" s="349" t="str">
+        <x:v>在不修改模型外观、坐标、父子关系、材质与动画的前提下，将游戏输出重组为6个一级分类、76个独立资产包。地面统一归入地面系统，36块5×5m地砖分别包含原砖及其深化内容；阁楼、阁楼外侧视觉中心、仓库设施均按功能拆分，散件、商品、灯光和动效迁回所属设施包。</x:v>
+      </x:c>
+      <x:c r="F37" s="349" t="str">
+        <x:v>严格验收通过：1696个输出对象全部唯一归属；36个地砖包、76个磁盘资产目录与清单齐全；无空包、无旧总集合残留；3211对象、3048网格、22灯光、3相机、4材质与v006一致；全部1552个输出网格保留PaletteUV；对象/变换/网格/材质/动画签名一致。</x:v>
+      </x:c>
+      <x:c r="G37" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H37" s="349" t="str">
+        <x:v>仅整理Blender Collection与未来独立导出目录；资产ID保持ENV-BASE99-ART-LAYOUT-3D，不新增重复ID；未导出独立GLB/碰撞/PackedScene，未修改Godot运行时、碰撞或玩法。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="150" customHeight="1">
+      <x:c r="A38" s="349" t="str">
+        <x:v>v0.1.34</x:v>
+      </x:c>
+      <x:c r="B38" s="348" t="n">
+        <x:v>46268</x:v>
+      </x:c>
+      <x:c r="C38" s="349" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D38" s="349" t="str">
+        <x:v>基地99层南面设施高还原深化v008</x:v>
+      </x:c>
+      <x:c r="E38" s="349" t="str">
+        <x:v>以参考效果图为视觉真值，仅深化BASE CAMP所在南面设施区域：将原误读电视墙修正为原包络内青绿色分段卷帘主门，并深化大型立体标识、主门下方低矮设备柜、MEDICAL与TOOLS柜、窄型电池/应急柜、圆形全息设备平台、三台功能终端、墙面工业管线及二层栏杆附着细节。各设施独立归档，未改变非本批结构。</x:v>
+      </x:c>
+      <x:c r="F38" s="349" t="str">
+        <x:v>严格验收通过：v007/v008锁区签名一致；82个独立资产包、36个地砖包、82份磁盘清单，无空包或跨包混挂；主门中心(5.0,4.64,2.20)、包络5.80×0.40×2.55m，全息平台中心(5.0,1.72)；2038个输出对象、3728网格、914462/914462有效PaletteUV面、4材质；旧电视对象为0。</x:v>
+      </x:c>
+      <x:c r="G38" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H38" s="349" t="str">
+        <x:v>资产ID保持ENV-BASE99-ART-LAYOUT-3D；仅更新Blender源场景、独立设施目录和验收资料。未生成独立GLB/碰撞/PackedScene，未修改Godot运行时、碰撞或玩法。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R68bef88d28464a66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R2969187735c34477"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R422f02c5d087494b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R012c1e75bb8c4436"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R73e1466cbe404844"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Re87312a43fbf4a7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Rdf3df4cd0c7441dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R6631da8fc0b74a76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Rf2ea8e3970bb4663"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R2f7f7bcf3cd4419d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R6159cc6f9d9448c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R456e67a01ec14781"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R58078533bd05404b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R6387f7c573c44d19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="R1a6e068f8c594d34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R69a6b794a99b4915"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="Racfd4ba4c89a4441"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="R0f7ad306594649e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R82ec5ca25ddb4f70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R28c31de824564962"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R9ed11f048aed4d85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R9c91b4a726574dd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R8c952f255c2a448d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R9ba806e9878d40f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R0c89eca6b60940a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R8f0457f905784e51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rd9e7cf0a2d6849f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Ra1eab3fcedca4ff4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="Re0c00f05ef064bec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="Rf3d7026c1f8f4743"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R88184857ae324e4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="Raccef9f3309841bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R08b9582ea9624541"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="Re58f1eea0c7b4ee0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R8675bfbeda944daf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R501c9907ebc34c4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Rca88c93b60094e0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="Rebe9744b2d264ed3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -36721,7 +36721,7 @@
 2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_base99_floor_player_collision_flow；verify_base_facility_interaction_zones；SHA 14fd4be6488e→bc849c71619f。</x:v>
       </x:c>
     </x:row>
-    <x:row r="240" ht="190" customHeight="1">
+    <x:row r="240" ht="225" customHeight="1">
       <x:c r="A240" s="136" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ENV-BASE99-ART-LAYOUT-3D</x:t>
@@ -36794,7 +36794,7 @@
         </x:is>
       </x:c>
       <x:c r="P240" s="349" t="str">
-        <x:v>assets/art/props/base_world_3d/prp_base_facility_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/mission_operations/prp_base_mission_operations_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/weapon_workshop/prp_base_weapon_workshop_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/vending_machine/prp_base_vending_machine_root_top3d_v002.tscn; assets/art/props/base_world_3d/runtime/locker_station/prp_base_locker_station_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/retro_tv_station/prp_base_retro_tv_station_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/workshop_stool/prp_base_workshop_stool_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/mission_command_chair/prp_base_mission_command_chair_root_top3d_v001.tscn; assets/art/3D模型资产目录与命名规范.md; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v003.blend; scripts/blender/build_base_facility_runtime_layout_hq_v003.py; outputs/verification/base_facility_runtime_layout_hq_v003.png; outputs/verification/base_facility_runtime_layout_hq_v003_top.png; outputs/verification/base_facility_runtime_layout_hq_v003_underloft.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v004.blend; scripts/blender/build_base_facility_runtime_layout_hq_v004.py; outputs/verification/base_facility_runtime_layout_hq_v004.png; outputs/verification/base_facility_runtime_layout_hq_v004_top.png; outputs/verification/base_facility_runtime_layout_hq_v004_facilities.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v005.blend; scripts/blender/build_base_facility_runtime_layout_hq_v005.py; outputs/verification/base_facility_runtime_layout_hq_v005.png; outputs/verification/base_facility_runtime_layout_hq_v005_top.png; outputs/verification/base_facility_runtime_layout_hq_v005_stair.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v006.blend; scripts/blender/build_base_facility_runtime_layout_hq_v006.py; outputs/verification/base_facility_runtime_layout_hq_v006.png; outputs/verification/base_facility_runtime_layout_hq_v006_top.png; outputs/verification/base_facility_runtime_layout_hq_v006_floor_close.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v007.blend; source/art/blender/base_facility_layout/component_packages; scripts/blender/organize_base_facility_runtime_layout_hq_v007.py; scripts/blender/validate_base_facility_runtime_layout_hq_v007.py; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_component_catalog_v007.json; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_component_tree_v007.txt; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_runtime_layout_hq_v007.png; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_runtime_layout_hq_v007_top.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v008.blend; source/art/blender/base_facility_layout/component_packages_v008; scripts/blender/build_base_facility_runtime_layout_hq_v008.py; scripts/blender/validate_base_facility_runtime_layout_hq_v008.py; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_component_catalog_v008.json; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_component_tree_v008.txt; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008.png; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008_top.png; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008_south_facilities.png; outputs/verification/base_facility_runtime_layout_hq_v008/strict_palette_validation.log</x:v>
+        <x:v>assets/art/props/base_world_3d/prp_base_facility_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/mission_operations/prp_base_mission_operations_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/weapon_workshop/prp_base_weapon_workshop_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/vending_machine/prp_base_vending_machine_root_top3d_v002.tscn; assets/art/props/base_world_3d/runtime/locker_station/prp_base_locker_station_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/retro_tv_station/prp_base_retro_tv_station_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/workshop_stool/prp_base_workshop_stool_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/mission_command_chair/prp_base_mission_command_chair_root_top3d_v001.tscn; assets/art/3D模型资产目录与命名规范.md; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v003.blend; scripts/blender/build_base_facility_runtime_layout_hq_v003.py; outputs/verification/base_facility_runtime_layout_hq_v003.png; outputs/verification/base_facility_runtime_layout_hq_v003_top.png; outputs/verification/base_facility_runtime_layout_hq_v003_underloft.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v004.blend; scripts/blender/build_base_facility_runtime_layout_hq_v004.py; outputs/verification/base_facility_runtime_layout_hq_v004.png; outputs/verification/base_facility_runtime_layout_hq_v004_top.png; outputs/verification/base_facility_runtime_layout_hq_v004_facilities.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v005.blend; scripts/blender/build_base_facility_runtime_layout_hq_v005.py; outputs/verification/base_facility_runtime_layout_hq_v005.png; outputs/verification/base_facility_runtime_layout_hq_v005_top.png; outputs/verification/base_facility_runtime_layout_hq_v005_stair.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v006.blend; scripts/blender/build_base_facility_runtime_layout_hq_v006.py; outputs/verification/base_facility_runtime_layout_hq_v006.png; outputs/verification/base_facility_runtime_layout_hq_v006_top.png; outputs/verification/base_facility_runtime_layout_hq_v006_floor_close.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v007.blend; source/art/blender/base_facility_layout/component_packages; scripts/blender/organize_base_facility_runtime_layout_hq_v007.py; scripts/blender/validate_base_facility_runtime_layout_hq_v007.py; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_component_catalog_v007.json; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_component_tree_v007.txt; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_runtime_layout_hq_v007.png; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_runtime_layout_hq_v007_top.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v008.blend; source/art/blender/base_facility_layout/component_packages_v008; scripts/blender/build_base_facility_runtime_layout_hq_v008.py; scripts/blender/validate_base_facility_runtime_layout_hq_v008.py; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_component_catalog_v008.json; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_component_tree_v008.txt; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008.png; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008_top.png; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008_south_facilities.png; outputs/verification/base_facility_runtime_layout_hq_v008/strict_palette_validation.log; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v009.blend; source/art/blender/base_facility_layout/component_packages_v009; scripts/blender/build_base_facility_runtime_layout_hq_v009.py; scripts/blender/repair_base_facility_runtime_layout_hq_v009_text_orientation.py; scripts/blender/validate_base_facility_runtime_layout_hq_v009.py; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_component_catalog_v009.json; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_component_tree_v009.txt; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_locked_scope_v008_v009.json; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_runtime_layout_hq_v009_validation.json; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_runtime_layout_hq_v009.png; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_runtime_layout_hq_v009_top.png; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_runtime_layout_hq_v009_east_facilities.png; outputs/verification/base_facility_runtime_layout_hq_v009/strict_palette_validation.log; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v010.blend; source/art/blender/base_facility_layout/component_packages_v010; scripts/blender/build_base_facility_runtime_layout_hq_v010.py; scripts/blender/repair_base_facility_runtime_layout_hq_v010_clearance.py; scripts/blender/repair_base_facility_runtime_layout_hq_v010_stair_sign.py; scripts/blender/validate_base_facility_runtime_layout_hq_v010.py; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_component_catalog_v010.json; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_component_tree_v010.txt; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_locked_scope_v009_v010.json; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010_validation.json; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010.png; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010_top.png; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010_loft_facilities.png; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010_stair_interfaces.png; outputs/verification/base_facility_runtime_layout_hq_v010/strict_palette_validation.log</x:v>
       </x:c>
       <x:c r="Q240" s="136" t="inlineStr">
         <x:is>
@@ -43026,7 +43026,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R011bc4ad22f34fe8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R503a0c05823244a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -50425,6 +50425,58 @@
         <x:v>资产ID保持ENV-BASE99-ART-LAYOUT-3D；仅更新Blender源场景、独立设施目录和验收资料。未生成独立GLB/碰撞/PackedScene，未修改Godot运行时、碰撞或玩法。</x:v>
       </x:c>
     </x:row>
+    <x:row r="39" ht="165" customHeight="1">
+      <x:c r="A39" s="349" t="str">
+        <x:v>v0.1.35</x:v>
+      </x:c>
+      <x:c r="B39" s="348" t="n">
+        <x:v>46268</x:v>
+      </x:c>
+      <x:c r="C39" s="349" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D39" s="349" t="str">
+        <x:v>基地99层东面设施高还原深化v009</x:v>
+      </x:c>
+      <x:c r="E39" s="349" t="str">
+        <x:v>以参考效果图为视觉真值，仅深化东面设施区域：正式人员安全门、SUPPLY 24H自动补给机、POWER工业配电系统、墙顶工业管线、WASTE/FLAMMABLE/RECYCLE三套独立分类设施、维修工作台与工具墙、低矮收纳、团结海报、小型安全设备、植物和圆形工业吊灯。修正所有东墙文字朝向，保持墙体、地砖、阁楼、栏杆和非目标设施不变。</x:v>
+      </x:c>
+      <x:c r="F39" s="349" t="str">
+        <x:v>严格验收通过：v008/v009共1988个锁定对象逐对象一致；91个独立资产包、36个地砖包、91份磁盘清单，无空包或跨包混挂；403个v009局部对象；4438个网格、1089839/1089839有效PaletteUV面、4材质；门框中心(14.38,-2.50,1.32)，SUPPLY主机(13.52,1.55,1.78)，POWER主箱(14.15,-5.55,2.35)。</x:v>
+      </x:c>
+      <x:c r="G39" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H39" s="349" t="str">
+        <x:v>资产ID保持ENV-BASE99-ART-LAYOUT-3D；仅更新Blender源场景、独立设施目录、资产目录与验收资料。未生成独立GLB、碰撞或PackedScene，未修改Godot运行时、碰撞及玩法。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="175" customHeight="1">
+      <x:c r="A40" s="349" t="str">
+        <x:v>v0.1.36</x:v>
+      </x:c>
+      <x:c r="B40" s="348" t="n">
+        <x:v>46268</x:v>
+      </x:c>
+      <x:c r="C40" s="349" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D40" s="349" t="str">
+        <x:v>基地99层二楼设施与楼梯高还原深化v010</x:v>
+      </x:c>
+      <x:c r="E40" s="349" t="str">
+        <x:v>以参考效果图为视觉真值，仅深化二楼生活/休闲/工位/收纳设施及楼梯：重制床与床品、床头柜和暖灯、地毯、条纹隔断、三人沙发、茶几、坐墩、双屏工位、办公椅、GOOD VIBES霓虹、三类收纳柜、箱体、墙面工具板和植物；保留西北L梯原结构并增加防滑与暖光细节，新增参考图东侧上行过渡梯。</x:v>
+      </x:c>
+      <x:c r="F40" s="349" t="str">
+        <x:v>严格验收通过：v009/v010共2332个锁定对象逐对象一致；102个独立资产包、36个地砖包、102份磁盘清单；294个v010范围对象；东侧楼梯与收纳净距0.215m；4909个网格、1190533/1190533有效PaletteUV面、4材质；西北转角与顶层接驳平台坐标未变。</x:v>
+      </x:c>
+      <x:c r="G40" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H40" s="349" t="str">
+        <x:v>资产ID保持ENV-BASE99-ART-LAYOUT-3D；只更新Blender源场景、独立设施目录和验收资料。未生成独立GLB、碰撞、LOD或PackedScene，未修改Godot运行时、玩法或一楼资产。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A3:G3"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R28c31de824564962"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R9ed11f048aed4d85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R9c91b4a726574dd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R8c952f255c2a448d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R9ba806e9878d40f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R0c89eca6b60940a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R8f0457f905784e51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rd9e7cf0a2d6849f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Ra1eab3fcedca4ff4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="Re0c00f05ef064bec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="Rf3d7026c1f8f4743"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R88184857ae324e4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="Raccef9f3309841bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R08b9582ea9624541"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="Re58f1eea0c7b4ee0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R8675bfbeda944daf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R501c9907ebc34c4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Rca88c93b60094e0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="Rebe9744b2d264ed3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb8be578f747a4025"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Raf412043d3b94b63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R42c3d953c00f4d63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Reb41a1fa2b694582"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R6094ccd3b90e42a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rc7081d34711d438a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R646bda4ff5c04881"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R38b64acf4b104285"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Rc6d9a00ee77645ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R74bd62a27f434c7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="Rdd41e0da32e5466a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R393e859e41f845c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="Recb333f16b1349cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="Re1eeb7ecedb245fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="R718b7724d5244906"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="Ra5cf4fb5f9414fbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="Rf478611a88a643a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="R80e473139ee54c62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R3c09fb8f576748ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -36721,7 +36721,7 @@
 2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_base99_floor_player_collision_flow；verify_base_facility_interaction_zones；SHA 14fd4be6488e→bc849c71619f。</x:v>
       </x:c>
     </x:row>
-    <x:row r="240" ht="225" customHeight="1">
+    <x:row r="240" ht="255" customHeight="1">
       <x:c r="A240" s="136" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ENV-BASE99-ART-LAYOUT-3D</x:t>
@@ -36794,7 +36794,7 @@
         </x:is>
       </x:c>
       <x:c r="P240" s="349" t="str">
-        <x:v>assets/art/props/base_world_3d/prp_base_facility_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/mission_operations/prp_base_mission_operations_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/weapon_workshop/prp_base_weapon_workshop_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/vending_machine/prp_base_vending_machine_root_top3d_v002.tscn; assets/art/props/base_world_3d/runtime/locker_station/prp_base_locker_station_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/retro_tv_station/prp_base_retro_tv_station_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/workshop_stool/prp_base_workshop_stool_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/mission_command_chair/prp_base_mission_command_chair_root_top3d_v001.tscn; assets/art/3D模型资产目录与命名规范.md; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v003.blend; scripts/blender/build_base_facility_runtime_layout_hq_v003.py; outputs/verification/base_facility_runtime_layout_hq_v003.png; outputs/verification/base_facility_runtime_layout_hq_v003_top.png; outputs/verification/base_facility_runtime_layout_hq_v003_underloft.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v004.blend; scripts/blender/build_base_facility_runtime_layout_hq_v004.py; outputs/verification/base_facility_runtime_layout_hq_v004.png; outputs/verification/base_facility_runtime_layout_hq_v004_top.png; outputs/verification/base_facility_runtime_layout_hq_v004_facilities.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v005.blend; scripts/blender/build_base_facility_runtime_layout_hq_v005.py; outputs/verification/base_facility_runtime_layout_hq_v005.png; outputs/verification/base_facility_runtime_layout_hq_v005_top.png; outputs/verification/base_facility_runtime_layout_hq_v005_stair.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v006.blend; scripts/blender/build_base_facility_runtime_layout_hq_v006.py; outputs/verification/base_facility_runtime_layout_hq_v006.png; outputs/verification/base_facility_runtime_layout_hq_v006_top.png; outputs/verification/base_facility_runtime_layout_hq_v006_floor_close.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v007.blend; source/art/blender/base_facility_layout/component_packages; scripts/blender/organize_base_facility_runtime_layout_hq_v007.py; scripts/blender/validate_base_facility_runtime_layout_hq_v007.py; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_component_catalog_v007.json; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_component_tree_v007.txt; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_runtime_layout_hq_v007.png; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_runtime_layout_hq_v007_top.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v008.blend; source/art/blender/base_facility_layout/component_packages_v008; scripts/blender/build_base_facility_runtime_layout_hq_v008.py; scripts/blender/validate_base_facility_runtime_layout_hq_v008.py; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_component_catalog_v008.json; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_component_tree_v008.txt; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008.png; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008_top.png; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008_south_facilities.png; outputs/verification/base_facility_runtime_layout_hq_v008/strict_palette_validation.log; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v009.blend; source/art/blender/base_facility_layout/component_packages_v009; scripts/blender/build_base_facility_runtime_layout_hq_v009.py; scripts/blender/repair_base_facility_runtime_layout_hq_v009_text_orientation.py; scripts/blender/validate_base_facility_runtime_layout_hq_v009.py; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_component_catalog_v009.json; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_component_tree_v009.txt; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_locked_scope_v008_v009.json; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_runtime_layout_hq_v009_validation.json; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_runtime_layout_hq_v009.png; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_runtime_layout_hq_v009_top.png; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_runtime_layout_hq_v009_east_facilities.png; outputs/verification/base_facility_runtime_layout_hq_v009/strict_palette_validation.log; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v010.blend; source/art/blender/base_facility_layout/component_packages_v010; scripts/blender/build_base_facility_runtime_layout_hq_v010.py; scripts/blender/repair_base_facility_runtime_layout_hq_v010_clearance.py; scripts/blender/repair_base_facility_runtime_layout_hq_v010_stair_sign.py; scripts/blender/validate_base_facility_runtime_layout_hq_v010.py; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_component_catalog_v010.json; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_component_tree_v010.txt; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_locked_scope_v009_v010.json; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010_validation.json; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010.png; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010_top.png; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010_loft_facilities.png; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010_stair_interfaces.png; outputs/verification/base_facility_runtime_layout_hq_v010/strict_palette_validation.log</x:v>
+        <x:v>assets/art/props/base_world_3d/prp_base_facility_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/mission_operations/prp_base_mission_operations_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/weapon_workshop/prp_base_weapon_workshop_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/vending_machine/prp_base_vending_machine_root_top3d_v002.tscn; assets/art/props/base_world_3d/runtime/locker_station/prp_base_locker_station_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/retro_tv_station/prp_base_retro_tv_station_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/workshop_stool/prp_base_workshop_stool_root_top3d_v001.tscn; assets/art/props/base_world_3d/runtime/mission_command_chair/prp_base_mission_command_chair_root_top3d_v001.tscn; assets/art/3D模型资产目录与命名规范.md; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v003.blend; scripts/blender/build_base_facility_runtime_layout_hq_v003.py; outputs/verification/base_facility_runtime_layout_hq_v003.png; outputs/verification/base_facility_runtime_layout_hq_v003_top.png; outputs/verification/base_facility_runtime_layout_hq_v003_underloft.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v004.blend; scripts/blender/build_base_facility_runtime_layout_hq_v004.py; outputs/verification/base_facility_runtime_layout_hq_v004.png; outputs/verification/base_facility_runtime_layout_hq_v004_top.png; outputs/verification/base_facility_runtime_layout_hq_v004_facilities.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v005.blend; scripts/blender/build_base_facility_runtime_layout_hq_v005.py; outputs/verification/base_facility_runtime_layout_hq_v005.png; outputs/verification/base_facility_runtime_layout_hq_v005_top.png; outputs/verification/base_facility_runtime_layout_hq_v005_stair.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v006.blend; scripts/blender/build_base_facility_runtime_layout_hq_v006.py; outputs/verification/base_facility_runtime_layout_hq_v006.png; outputs/verification/base_facility_runtime_layout_hq_v006_top.png; outputs/verification/base_facility_runtime_layout_hq_v006_floor_close.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v007.blend; source/art/blender/base_facility_layout/component_packages; scripts/blender/organize_base_facility_runtime_layout_hq_v007.py; scripts/blender/validate_base_facility_runtime_layout_hq_v007.py; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_component_catalog_v007.json; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_component_tree_v007.txt; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_runtime_layout_hq_v007.png; outputs/verification/base_facility_runtime_layout_hq_v007/base_facility_runtime_layout_hq_v007_top.png; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v008.blend; source/art/blender/base_facility_layout/component_packages_v008; scripts/blender/build_base_facility_runtime_layout_hq_v008.py; scripts/blender/validate_base_facility_runtime_layout_hq_v008.py; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_component_catalog_v008.json; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_component_tree_v008.txt; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008.png; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008_top.png; outputs/verification/base_facility_runtime_layout_hq_v008/base_facility_runtime_layout_hq_v008_south_facilities.png; outputs/verification/base_facility_runtime_layout_hq_v008/strict_palette_validation.log; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v009.blend; source/art/blender/base_facility_layout/component_packages_v009; scripts/blender/build_base_facility_runtime_layout_hq_v009.py; scripts/blender/repair_base_facility_runtime_layout_hq_v009_text_orientation.py; scripts/blender/validate_base_facility_runtime_layout_hq_v009.py; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_component_catalog_v009.json; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_component_tree_v009.txt; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_locked_scope_v008_v009.json; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_runtime_layout_hq_v009_validation.json; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_runtime_layout_hq_v009.png; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_runtime_layout_hq_v009_top.png; outputs/verification/base_facility_runtime_layout_hq_v009/base_facility_runtime_layout_hq_v009_east_facilities.png; outputs/verification/base_facility_runtime_layout_hq_v009/strict_palette_validation.log; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v010.blend; source/art/blender/base_facility_layout/component_packages_v010; scripts/blender/build_base_facility_runtime_layout_hq_v010.py; scripts/blender/repair_base_facility_runtime_layout_hq_v010_clearance.py; scripts/blender/repair_base_facility_runtime_layout_hq_v010_stair_sign.py; scripts/blender/validate_base_facility_runtime_layout_hq_v010.py; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_component_catalog_v010.json; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_component_tree_v010.txt; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_locked_scope_v009_v010.json; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010_validation.json; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010.png; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010_top.png; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010_loft_facilities.png; outputs/verification/base_facility_runtime_layout_hq_v010/base_facility_runtime_layout_hq_v010_stair_interfaces.png; outputs/verification/base_facility_runtime_layout_hq_v010/strict_palette_validation.log; source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v011.blend; source/art/blender/base_facility_layout/component_packages_v011; scripts/blender/build_base_facility_runtime_layout_hq_v011.py; scripts/blender/refine_base_facility_runtime_layout_hq_v011.py; scripts/blender/validate_base_facility_runtime_layout_hq_v011.py; outputs/verification/base_facility_runtime_layout_hq_v011/base_facility_component_catalog_v011.json; outputs/verification/base_facility_runtime_layout_hq_v011/base_facility_component_tree_v011.txt; outputs/verification/base_facility_runtime_layout_hq_v011/base_facility_locked_scope_v010_v011.json; outputs/verification/base_facility_runtime_layout_hq_v011/base_facility_runtime_layout_hq_v011_validation.json; outputs/verification/base_facility_runtime_layout_hq_v011/base_facility_v011_visual_acceptance.json; outputs/verification/base_facility_runtime_layout_hq_v011/base_facility_runtime_layout_hq_v011_reference_match.png; outputs/verification/base_facility_runtime_layout_hq_v011/base_facility_runtime_layout_hq_v011_loft_detail.png; outputs/verification/base_facility_runtime_layout_hq_v011/base_facility_runtime_layout_hq_v011_stair_interfaces.png; outputs/verification/base_facility_runtime_layout_hq_v011/base_facility_runtime_layout_hq_v011_top.png; outputs/verification/base_facility_runtime_layout_hq_v011/strict_palette_validation.log</x:v>
       </x:c>
       <x:c r="Q240" s="136" t="inlineStr">
         <x:is>
@@ -43026,7 +43026,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R503a0c05823244a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5175f4ed2bbf498b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -50477,6 +50477,32 @@
         <x:v>资产ID保持ENV-BASE99-ART-LAYOUT-3D；只更新Blender源场景、独立设施目录和验收资料。未生成独立GLB、碰撞、LOD或PackedScene，未修改Godot运行时、玩法或一楼资产。</x:v>
       </x:c>
     </x:row>
+    <x:row r="41" ht="205" customHeight="1">
+      <x:c r="A41" s="349" t="str">
+        <x:v>v0.1.37</x:v>
+      </x:c>
+      <x:c r="B41" s="348" t="n">
+        <x:v>46268</x:v>
+      </x:c>
+      <x:c r="C41" s="349" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D41" s="349" t="str">
+        <x:v>基地99层二楼与楼梯参考图高还原迭代v011</x:v>
+      </x:c>
+      <x:c r="E41" s="349" t="str">
+        <x:v>针对v010未达到视觉验收标准的问题，以同一参考镜头重新校准二楼设施：重做床与床品、床头柜、条纹隔断、三人沙发、茶几、坐墩、完整双屏工位、办公椅和紧凑分类收纳；调整东侧楼梯轮廓与接口，深化西侧L梯踏步、转角和顶层接缝；增加前沿暖橙灯带、后墙三路管线、工具区、植物、GOOD VIBES霓虹、屏幕扫描线和克制生活物件。</x:v>
+      </x:c>
+      <x:c r="F41" s="349" t="str">
+        <x:v>验收通过：参考镜头第一眼结构顺序、主色块、设施间距和冷暖灯光关系均已重新核对；v010/v011共2332个锁定对象完全一致；101个独立资产包、36个地砖包、101份manifest；383个v011范围对象；工位至东梯净距1.46m、前沿通行深度3.40m；5075网格、1198313/1198313有效PaletteUV面、4材质。</x:v>
+      </x:c>
+      <x:c r="G41" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H41" s="349" t="str">
+        <x:v>沿用稳定资产ID ENV-BASE99-ART-LAYOUT-3D，Blend SHA-256=eb92c8383f5b86d8d8e4226b9f4da2416a5903ab4ba8668f6a7639161de8dca1。仅更新Blender源、独立资产包和验收资料；未生成独立GLB、碰撞、LOD或PackedScene，未修改Godot运行时和锁定区域。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A3:G3"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb8be578f747a4025"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Raf412043d3b94b63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R42c3d953c00f4d63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Reb41a1fa2b694582"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R6094ccd3b90e42a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rc7081d34711d438a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R646bda4ff5c04881"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R38b64acf4b104285"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Rc6d9a00ee77645ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R74bd62a27f434c7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="Rdd41e0da32e5466a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R393e859e41f845c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="Recb333f16b1349cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="Re1eeb7ecedb245fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="R718b7724d5244906"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="Ra5cf4fb5f9414fbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="Rf478611a88a643a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="R80e473139ee54c62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R3c09fb8f576748ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rcaa9a371ca3540fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rdc25991fdc7f426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rf394921d058d4982"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rf79281c1f1e04185"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rcb05d6cd466c4494"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Re1e8572a07e946e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Rab3495faa7f54918"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rfeec5388505945ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Rd8f01dad8e064ec8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R05b5e9e1bce9488d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R8aaf10fc54114ece"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="Race968441a1f4639"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R1f9fbd22c4564432"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R5998e1b3a0ab49c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="Re12410531f5e4ecc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="Ra6d6920d13ca4ccc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R44f05aa63c3f46d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Re028e1122b354d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="Rbab1878c47c3402d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -42947,6 +42947,8366 @@
         <x:v>2026-08-31 v015：生活棚整体北移并以木平台贴合天台边缘，平台高0.5m且设三块踏步/连续坡面碰撞；黄色门前动线阻挡0；种植区与通信区按标注分离。TowerFloorStage3D已正式实例化v015并隐藏旧程序化视觉；68个语义目录待归类对象0，36项主要物体各有独立阻挡；v014保留回滚。</x:v>
       </x:c>
     </x:row>
+    <x:row r="302" ht="54" customHeight="1">
+      <x:c r="A302" t="str">
+        <x:v>BPK-BASE99-EAST-MEZZANINE-STRUCTURE</x:v>
+      </x:c>
+      <x:c r="B302" t="str">
+        <x:v>基地99层 · 东墙阁楼主体结构</x:v>
+      </x:c>
+      <x:c r="C302" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D302" t="str">
+        <x:v>建筑结构包</x:v>
+      </x:c>
+      <x:c r="E302" t="str">
+        <x:v>base99_package_east_mezzanine_structure</x:v>
+      </x:c>
+      <x:c r="F302" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G302" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H302" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I302" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J302" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K302" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L302" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M302" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N302" s="349" t="str">
+        <x:v>包络 20.080×10.000×7.325m；87 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O302" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/architecture/east_mezzanine_structure/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P302" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q302" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;建筑结构包;east_mezzanine_structure;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R302" s="349" t="str">
+        <x:f>C302&amp;"|"&amp;D302&amp;"|"&amp;E302&amp;"|"&amp;F302&amp;"|"&amp;LOWER(H302)&amp;"|"&amp;I302</x:f>
+        <x:v>基地资产包|建筑结构包|base99_package_east_mezzanine_structure|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S302" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R302)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T302" s="349" t="str">
+        <x:v>85c5a1e4e65168ecb8bad3439181965e5c8dac006af56fcd76b131d9a9de5701</x:v>
+      </x:c>
+      <x:c r="U302" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V302" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W302" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X302" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_mezzanine_structure；对象 87；中心 (5.000, 10.000, 3.663)m；朝向 Blender +Y north；预期导出 east_mezzanine_structure_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" ht="54" customHeight="1">
+      <x:c r="A303" t="str">
+        <x:v>BPK-BASE99-EAST-UPPER-TRANSITION-STAIR</x:v>
+      </x:c>
+      <x:c r="B303" t="str">
+        <x:v>基地99层 · 东侧紧凑上行过渡楼梯</x:v>
+      </x:c>
+      <x:c r="C303" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D303" t="str">
+        <x:v>建筑结构包</x:v>
+      </x:c>
+      <x:c r="E303" t="str">
+        <x:v>base99_package_east_upper_transition_stair</x:v>
+      </x:c>
+      <x:c r="F303" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G303" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H303" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I303" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J303" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K303" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L303" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M303" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N303" s="349" t="str">
+        <x:v>包络 2.120×4.910×3.775m；88 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O303" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/architecture/east_upper_transition_stair/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P303" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q303" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;建筑结构包;east_upper_transition_stair;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R303" s="349" t="str">
+        <x:f>C303&amp;"|"&amp;D303&amp;"|"&amp;E303&amp;"|"&amp;F303&amp;"|"&amp;LOWER(H303)&amp;"|"&amp;I303</x:f>
+        <x:v>基地资产包|建筑结构包|base99_package_east_upper_transition_stair|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S303" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R303)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T303" s="349" t="str">
+        <x:v>d824adb7c6e195f7755698caa68cd0ffcd405211f519be0ddafc59dac045dcf6</x:v>
+      </x:c>
+      <x:c r="U303" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V303" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W303" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X303" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_upper_transition_stair；对象 88；中心 (13.250, 12.465, 7.884)m；朝向 Blender +Y north；预期导出 east_upper_transition_stair_visual_top3d_v001.glb；当前 not_exported；碰撞 source collider attached；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" ht="54" customHeight="1">
+      <x:c r="A304" t="str">
+        <x:v>BPK-BASE99-NORTHWEST-L-STAIR</x:v>
+      </x:c>
+      <x:c r="B304" t="str">
+        <x:v>基地99层 · 西北贴墙L型楼梯</x:v>
+      </x:c>
+      <x:c r="C304" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D304" t="str">
+        <x:v>建筑结构包</x:v>
+      </x:c>
+      <x:c r="E304" t="str">
+        <x:v>base99_package_northwest_l_stair</x:v>
+      </x:c>
+      <x:c r="F304" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G304" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H304" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I304" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J304" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K304" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L304" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M304" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N304" s="349" t="str">
+        <x:v>包络 10.130×6.797×7.128m；178 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O304" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/architecture/northwest_l_stair/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P304" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q304" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;建筑结构包;northwest_l_stair;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R304" s="349" t="str">
+        <x:f>C304&amp;"|"&amp;D304&amp;"|"&amp;E304&amp;"|"&amp;F304&amp;"|"&amp;LOWER(H304)&amp;"|"&amp;I304</x:f>
+        <x:v>基地资产包|建筑结构包|base99_package_northwest_l_stair|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S304" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R304)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T304" s="349" t="str">
+        <x:v>ad848815a5764847814ff4754c671f51e3307116a4d972be5c9ac6a8715b39e7</x:v>
+      </x:c>
+      <x:c r="U304" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V304" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W304" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X304" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::northwest_l_stair；对象 178；中心 (-9.735, 11.402, 3.564)m；朝向 Blender +Y north；预期导出 northwest_l_stair_visual_top3d_v001.glb；当前 not_exported；碰撞 source collider attached；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" ht="54" customHeight="1">
+      <x:c r="A305" t="str">
+        <x:v>BPK-BASE99-RETAINED-WALL-SYSTEM</x:v>
+      </x:c>
+      <x:c r="B305" t="str">
+        <x:v>基地99层 · 四向保留墙体系统</x:v>
+      </x:c>
+      <x:c r="C305" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D305" t="str">
+        <x:v>建筑结构包</x:v>
+      </x:c>
+      <x:c r="E305" t="str">
+        <x:v>base99_package_retained_wall_system</x:v>
+      </x:c>
+      <x:c r="F305" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G305" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H305" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I305" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J305" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K305" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L305" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M305" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N305" s="349" t="str">
+        <x:v>包络 31.171×30.360×9.000m；24 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O305" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/architecture/retained_wall_system/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P305" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q305" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;建筑结构包;retained_wall_system;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R305" s="349" t="str">
+        <x:f>C305&amp;"|"&amp;D305&amp;"|"&amp;E305&amp;"|"&amp;F305&amp;"|"&amp;LOWER(H305)&amp;"|"&amp;I305</x:f>
+        <x:v>基地资产包|建筑结构包|base99_package_retained_wall_system|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S305" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R305)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T305" s="349" t="str">
+        <x:v>bfdd3f8e4a4b8baa937f46280d06ec455d2cf38f8156b75f54ae8acfd4eccbd8</x:v>
+      </x:c>
+      <x:c r="U305" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V305" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W305" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X305" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::retained_wall_system；对象 72；中心 (0.000, 0.000, 4.500)m；朝向 Blender +Y north；预期导出 retained_wall_system_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" ht="54" customHeight="1">
+      <x:c r="A306" t="str">
+        <x:v>BPK-BASE99-UNDERDECK-SHEET-BLOCKER</x:v>
+      </x:c>
+      <x:c r="B306" t="str">
+        <x:v>基地99层 · 阁楼下方铁皮封闭体</x:v>
+      </x:c>
+      <x:c r="C306" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D306" t="str">
+        <x:v>建筑结构包</x:v>
+      </x:c>
+      <x:c r="E306" t="str">
+        <x:v>base99_package_underdeck_sheet_blocker</x:v>
+      </x:c>
+      <x:c r="F306" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G306" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H306" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I306" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J306" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K306" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L306" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M306" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N306" s="349" t="str">
+        <x:v>包络 19.315×9.530×5.400m；5 网格；4 灯</x:v>
+      </x:c>
+      <x:c r="O306" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/architecture/underdeck_sheet_blocker/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P306" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q306" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;建筑结构包;underdeck_sheet_blocker;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R306" s="349" t="str">
+        <x:f>C306&amp;"|"&amp;D306&amp;"|"&amp;E306&amp;"|"&amp;F306&amp;"|"&amp;LOWER(H306)&amp;"|"&amp;I306</x:f>
+        <x:v>基地资产包|建筑结构包|base99_package_underdeck_sheet_blocker|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S306" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R306)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T306" s="349" t="str">
+        <x:v>8b8a3a689384ef1519e86259e762c2f56f2f2c30e04e52e142123f9faa1b0f9b</x:v>
+      </x:c>
+      <x:c r="U306" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V306" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W306" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X306" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::underdeck_sheet_blocker；对象 11；中心 (5.000, 9.685, 2.700)m；朝向 Blender +Y north；预期导出 underdeck_sheet_blocker_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" ht="54" customHeight="1">
+      <x:c r="A307" t="str">
+        <x:v>BPK-BASE99-EAST-FLAMMABLE-BIN</x:v>
+      </x:c>
+      <x:c r="B307" t="str">
+        <x:v>基地99层 · FLAMMABLE可燃垃圾设施</x:v>
+      </x:c>
+      <x:c r="C307" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D307" t="str">
+        <x:v>东侧固定设施包</x:v>
+      </x:c>
+      <x:c r="E307" t="str">
+        <x:v>base99_package_east_flammable_bin</x:v>
+      </x:c>
+      <x:c r="F307" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G307" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H307" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I307" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J307" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K307" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L307" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M307" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N307" s="349" t="str">
+        <x:v>包络 1.298×1.100×1.460m；12 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O307" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_flammable_bin/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P307" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q307" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;东侧固定设施包;east_flammable_bin;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R307" s="349" t="str">
+        <x:f>C307&amp;"|"&amp;D307&amp;"|"&amp;E307&amp;"|"&amp;F307&amp;"|"&amp;LOWER(H307)&amp;"|"&amp;I307</x:f>
+        <x:v>基地资产包|东侧固定设施包|base99_package_east_flammable_bin|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S307" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R307)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T307" s="349" t="str">
+        <x:v>b761ec0a6c0fb6ef88a5b3ce229c69e447bc9d0a8ada0dabf3928b28a0136d3e</x:v>
+      </x:c>
+      <x:c r="U307" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V307" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W307" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X307" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_flammable_bin；对象 12；中心 (10.701, -6.650, 0.730)m；朝向 Blender +Y north；预期导出 east_flammable_bin_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" ht="54" customHeight="1">
+      <x:c r="A308" t="str">
+        <x:v>BPK-BASE99-EAST-INDUSTRIAL-PIPELINE-SYSTEM</x:v>
+      </x:c>
+      <x:c r="B308" t="str">
+        <x:v>基地99层 · 东墙工业管线系统</x:v>
+      </x:c>
+      <x:c r="C308" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D308" t="str">
+        <x:v>东侧固定设施包</x:v>
+      </x:c>
+      <x:c r="E308" t="str">
+        <x:v>base99_package_east_industrial_pipeline_system</x:v>
+      </x:c>
+      <x:c r="F308" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G308" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H308" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I308" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J308" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K308" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L308" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M308" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N308" s="349" t="str">
+        <x:v>包络 0.578×17.600×5.460m；57 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O308" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_industrial_pipeline_system/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P308" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q308" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;东侧固定设施包;east_industrial_pipeline_system;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R308" s="349" t="str">
+        <x:f>C308&amp;"|"&amp;D308&amp;"|"&amp;E308&amp;"|"&amp;F308&amp;"|"&amp;LOWER(H308)&amp;"|"&amp;I308</x:f>
+        <x:v>基地资产包|东侧固定设施包|base99_package_east_industrial_pipeline_system|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S308" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R308)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T308" s="349" t="str">
+        <x:v>1e643d03cda8bd2fd5cae99841172b39fe7df2730d809458376c8ae77c3e75eb</x:v>
+      </x:c>
+      <x:c r="U308" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V308" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W308" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X308" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_industrial_pipeline_system；对象 57；中心 (14.271, -5.000, 4.450)m；朝向 Blender +Y north；预期导出 east_industrial_pipeline_system_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" ht="54" customHeight="1">
+      <x:c r="A309" t="str">
+        <x:v>BPK-BASE99-EAST-LOW-STORAGE-BENCH</x:v>
+      </x:c>
+      <x:c r="B309" t="str">
+        <x:v>基地99层 · 低矮储物收纳区</x:v>
+      </x:c>
+      <x:c r="C309" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D309" t="str">
+        <x:v>东侧固定设施包</x:v>
+      </x:c>
+      <x:c r="E309" t="str">
+        <x:v>base99_package_east_low_storage_bench</x:v>
+      </x:c>
+      <x:c r="F309" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G309" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H309" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I309" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J309" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K309" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L309" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M309" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N309" s="349" t="str">
+        <x:v>包络 2.900×1.225×1.690m；10 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O309" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_low_storage_bench/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P309" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q309" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;东侧固定设施包;east_low_storage_bench;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R309" s="349" t="str">
+        <x:f>C309&amp;"|"&amp;D309&amp;"|"&amp;E309&amp;"|"&amp;F309&amp;"|"&amp;LOWER(H309)&amp;"|"&amp;I309</x:f>
+        <x:v>基地资产包|东侧固定设施包|base99_package_east_low_storage_bench|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S309" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R309)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T309" s="349" t="str">
+        <x:v>da684e47481e7979da47f1ffd0ee9bea0a3cd930a1eedf9d5975c3cf5680a10e</x:v>
+      </x:c>
+      <x:c r="U309" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V309" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W309" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X309" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_low_storage_bench；对象 10；中心 (10.850, -14.037, 0.915)m；朝向 Blender +Y north；预期导出 east_low_storage_bench_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" ht="54" customHeight="1">
+      <x:c r="A310" t="str">
+        <x:v>BPK-BASE99-EAST-MAINTENANCE-WORKSTATION</x:v>
+      </x:c>
+      <x:c r="B310" t="str">
+        <x:v>基地99层 · 维修工作台与工具墙</x:v>
+      </x:c>
+      <x:c r="C310" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D310" t="str">
+        <x:v>东侧固定设施包</x:v>
+      </x:c>
+      <x:c r="E310" t="str">
+        <x:v>base99_package_east_maintenance_workstation</x:v>
+      </x:c>
+      <x:c r="F310" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G310" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H310" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I310" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J310" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K310" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L310" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M310" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N310" s="349" t="str">
+        <x:v>包络 5.000×2.560×4.220m；115 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O310" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_maintenance_workstation/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P310" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q310" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;东侧固定设施包;east_maintenance_workstation;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R310" s="349" t="str">
+        <x:f>C310&amp;"|"&amp;D310&amp;"|"&amp;E310&amp;"|"&amp;F310&amp;"|"&amp;LOWER(H310)&amp;"|"&amp;I310</x:f>
+        <x:v>基地资产包|东侧固定设施包|base99_package_east_maintenance_workstation|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S310" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R310)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T310" s="349" t="str">
+        <x:v>c0c01f4c6663cf2e9fc70ed49e4f8ed1276b887abe41de3a935da3c1a35de344</x:v>
+      </x:c>
+      <x:c r="U310" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V310" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W310" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X310" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_maintenance_workstation；对象 115；中心 (6.200, -13.190, 2.200)m；朝向 Blender +Y north；预期导出 east_maintenance_workstation_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" ht="54" customHeight="1">
+      <x:c r="A311" t="str">
+        <x:v>BPK-BASE99-EAST-PERSONNEL-SECURITY-DOOR</x:v>
+      </x:c>
+      <x:c r="B311" t="str">
+        <x:v>基地99层 · 正式人员安全门</x:v>
+      </x:c>
+      <x:c r="C311" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D311" t="str">
+        <x:v>东侧固定设施包</x:v>
+      </x:c>
+      <x:c r="E311" t="str">
+        <x:v>base99_package_east_personnel_security_door</x:v>
+      </x:c>
+      <x:c r="F311" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G311" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H311" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I311" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J311" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K311" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L311" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M311" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N311" s="349" t="str">
+        <x:v>包络 1.410×2.860×3.022m；44 网格；1 灯</x:v>
+      </x:c>
+      <x:c r="O311" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_personnel_security_door/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P311" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q311" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;东侧固定设施包;east_personnel_security_door;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R311" s="349" t="str">
+        <x:f>C311&amp;"|"&amp;D311&amp;"|"&amp;E311&amp;"|"&amp;F311&amp;"|"&amp;LOWER(H311)&amp;"|"&amp;I311</x:f>
+        <x:v>基地资产包|东侧固定设施包|base99_package_east_personnel_security_door|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S311" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R311)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T311" s="349" t="str">
+        <x:v>e9c0d8cd40212c3dd3ca881a2b2033fdce4cdcccaa42c93bd1c88e98ed376314</x:v>
+      </x:c>
+      <x:c r="U311" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V311" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W311" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X311" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_personnel_security_door；对象 45；中心 (13.905, -2.280, 1.511)m；朝向 Blender +Y north；预期导出 east_personnel_security_door_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" ht="54" customHeight="1">
+      <x:c r="A312" t="str">
+        <x:v>BPK-BASE99-EAST-PLANT-GROUP</x:v>
+      </x:c>
+      <x:c r="B312" t="str">
+        <x:v>基地99层 · 东面植物点缀组</x:v>
+      </x:c>
+      <x:c r="C312" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D312" t="str">
+        <x:v>东侧固定设施包</x:v>
+      </x:c>
+      <x:c r="E312" t="str">
+        <x:v>base99_package_east_plant_group</x:v>
+      </x:c>
+      <x:c r="F312" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G312" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H312" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I312" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J312" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K312" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L312" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M312" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N312" s="349" t="str">
+        <x:v>包络 1.364×17.030×2.000m；15 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O312" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_plant_group/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P312" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q312" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;东侧固定设施包;east_plant_group;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R312" s="349" t="str">
+        <x:f>C312&amp;"|"&amp;D312&amp;"|"&amp;E312&amp;"|"&amp;F312&amp;"|"&amp;LOWER(H312)&amp;"|"&amp;I312</x:f>
+        <x:v>基地资产包|东侧固定设施包|base99_package_east_plant_group|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S312" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R312)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T312" s="349" t="str">
+        <x:v>666e4f4de4e76543f3eea83348d3ba9f4cb2c07dce740b1b4b904b863e38a419</x:v>
+      </x:c>
+      <x:c r="U312" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V312" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W312" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X312" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_plant_group；对象 15；中心 (12.250, -5.035, 1.110)m；朝向 Blender +Y north；预期导出 east_plant_group_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" ht="54" customHeight="1">
+      <x:c r="A313" t="str">
+        <x:v>BPK-BASE99-EAST-POWER-DISTRIBUTION</x:v>
+      </x:c>
+      <x:c r="B313" t="str">
+        <x:v>基地99层 · POWER工业配电系统</x:v>
+      </x:c>
+      <x:c r="C313" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D313" t="str">
+        <x:v>东侧固定设施包</x:v>
+      </x:c>
+      <x:c r="E313" t="str">
+        <x:v>base99_package_east_power_distribution</x:v>
+      </x:c>
+      <x:c r="F313" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G313" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H313" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I313" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J313" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K313" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L313" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M313" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N313" s="349" t="str">
+        <x:v>包络 0.828×1.550×2.690m；25 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O313" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_power_distribution/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P313" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q313" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;东侧固定设施包;east_power_distribution;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R313" s="349" t="str">
+        <x:f>C313&amp;"|"&amp;D313&amp;"|"&amp;E313&amp;"|"&amp;F313&amp;"|"&amp;LOWER(H313)&amp;"|"&amp;I313</x:f>
+        <x:v>基地资产包|东侧固定设施包|base99_package_east_power_distribution|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S313" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R313)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T313" s="349" t="str">
+        <x:v>31413bc33007b2125dd03a05d0abd4260e736810c28225daa92e893a65c6df4c</x:v>
+      </x:c>
+      <x:c r="U313" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V313" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W313" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X313" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_power_distribution；对象 25；中心 (13.986, -5.550, 2.355)m；朝向 Blender +Y north；预期导出 east_power_distribution_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" ht="54" customHeight="1">
+      <x:c r="A314" t="str">
+        <x:v>BPK-BASE99-EAST-RECYCLE-BIN</x:v>
+      </x:c>
+      <x:c r="B314" t="str">
+        <x:v>基地99层 · RECYCLE回收垃圾设施</x:v>
+      </x:c>
+      <x:c r="C314" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D314" t="str">
+        <x:v>东侧固定设施包</x:v>
+      </x:c>
+      <x:c r="E314" t="str">
+        <x:v>base99_package_east_recycle_bin</x:v>
+      </x:c>
+      <x:c r="F314" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G314" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H314" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I314" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J314" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K314" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L314" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M314" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N314" s="349" t="str">
+        <x:v>包络 1.298×1.100×1.460m；12 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O314" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_recycle_bin/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P314" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q314" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;东侧固定设施包;east_recycle_bin;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R314" s="349" t="str">
+        <x:f>C314&amp;"|"&amp;D314&amp;"|"&amp;E314&amp;"|"&amp;F314&amp;"|"&amp;LOWER(H314)&amp;"|"&amp;I314</x:f>
+        <x:v>基地资产包|东侧固定设施包|base99_package_east_recycle_bin|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S314" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R314)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T314" s="349" t="str">
+        <x:v>9f9534f65426a4df833293c470853dbfc90ff80b08b6e1a75ff234680f56d97f</x:v>
+      </x:c>
+      <x:c r="U314" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V314" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W314" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X314" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_recycle_bin；对象 12；中心 (10.701, -8.100, 0.730)m；朝向 Blender +Y north；预期导出 east_recycle_bin_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" ht="54" customHeight="1">
+      <x:c r="A315" t="str">
+        <x:v>BPK-BASE99-EAST-ROUND-PENDANT-LIGHT</x:v>
+      </x:c>
+      <x:c r="B315" t="str">
+        <x:v>基地99层 · 东面圆形工业吊灯</x:v>
+      </x:c>
+      <x:c r="C315" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D315" t="str">
+        <x:v>东侧固定设施包</x:v>
+      </x:c>
+      <x:c r="E315" t="str">
+        <x:v>base99_package_east_round_pendant_light</x:v>
+      </x:c>
+      <x:c r="F315" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G315" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H315" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I315" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J315" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K315" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L315" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M315" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N315" s="349" t="str">
+        <x:v>包络 1.242×1.243×1.560m；10 网格；2 灯</x:v>
+      </x:c>
+      <x:c r="O315" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_round_pendant_light/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P315" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q315" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;东侧固定设施包;east_round_pendant_light;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R315" s="349" t="str">
+        <x:f>C315&amp;"|"&amp;D315&amp;"|"&amp;E315&amp;"|"&amp;F315&amp;"|"&amp;LOWER(H315)&amp;"|"&amp;I315</x:f>
+        <x:v>基地资产包|东侧固定设施包|base99_package_east_round_pendant_light|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S315" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R315)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T315" s="349" t="str">
+        <x:v>722ea4d41aa66a74b7d8b74781181de16b4964be201b54c6e090397a65daf62f</x:v>
+      </x:c>
+      <x:c r="U315" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V315" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W315" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X315" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_round_pendant_light；对象 13；中心 (10.005, -3.392, 7.530)m；朝向 Blender +Y north；预期导出 east_round_pendant_light_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" ht="54" customHeight="1">
+      <x:c r="A316" t="str">
+        <x:v>BPK-BASE99-EAST-SMALL-SAFETY-DEVICES</x:v>
+      </x:c>
+      <x:c r="B316" t="str">
+        <x:v>基地99层 · 东墙小型安全设备</x:v>
+      </x:c>
+      <x:c r="C316" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D316" t="str">
+        <x:v>东侧固定设施包</x:v>
+      </x:c>
+      <x:c r="E316" t="str">
+        <x:v>base99_package_east_small_safety_devices</x:v>
+      </x:c>
+      <x:c r="F316" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G316" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H316" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I316" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J316" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K316" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L316" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M316" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N316" s="349" t="str">
+        <x:v>包络 0.430×12.470×3.790m；28 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O316" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_small_safety_devices/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P316" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q316" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;东侧固定设施包;east_small_safety_devices;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R316" s="349" t="str">
+        <x:f>C316&amp;"|"&amp;D316&amp;"|"&amp;E316&amp;"|"&amp;F316&amp;"|"&amp;LOWER(H316)&amp;"|"&amp;I316</x:f>
+        <x:v>基地资产包|东侧固定设施包|base99_package_east_small_safety_devices|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S316" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R316)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T316" s="349" t="str">
+        <x:v>2e6779275ae84a8102d93d47f11faf3b0194632c912d86eefbc06d48cb9aa5cf</x:v>
+      </x:c>
+      <x:c r="U316" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V316" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W316" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X316" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_small_safety_devices；对象 28；中心 (14.195, -6.425, 2.935)m；朝向 Blender +Y north；预期导出 east_small_safety_devices_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" ht="54" customHeight="1">
+      <x:c r="A317" t="str">
+        <x:v>BPK-BASE99-EAST-SUPPLY-24H-STATION</x:v>
+      </x:c>
+      <x:c r="B317" t="str">
+        <x:v>基地99层 · SUPPLY24H自动补给机</x:v>
+      </x:c>
+      <x:c r="C317" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D317" t="str">
+        <x:v>东侧固定设施包</x:v>
+      </x:c>
+      <x:c r="E317" t="str">
+        <x:v>base99_package_east_supply_24h_station</x:v>
+      </x:c>
+      <x:c r="F317" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G317" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H317" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I317" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J317" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K317" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L317" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M317" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N317" s="349" t="str">
+        <x:v>包络 2.478×2.337×4.720m；50 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O317" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_supply_24h_station/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P317" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q317" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;东侧固定设施包;east_supply_24h_station;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R317" s="349" t="str">
+        <x:f>C317&amp;"|"&amp;D317&amp;"|"&amp;E317&amp;"|"&amp;F317&amp;"|"&amp;LOWER(H317)&amp;"|"&amp;I317</x:f>
+        <x:v>基地资产包|东侧固定设施包|base99_package_east_supply_24h_station|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S317" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R317)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T317" s="349" t="str">
+        <x:v>2be5948f139e759b4282a89549cfd855f0f2dfc0fd7cf4df4e2c4cf1f6d3ff4c</x:v>
+      </x:c>
+      <x:c r="U317" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V317" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W317" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X317" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_supply_24h_station；对象 50；中心 (13.361, 1.531, 2.360)m；朝向 Blender +Y north；预期导出 east_supply_24h_station_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" ht="54" customHeight="1">
+      <x:c r="A318" t="str">
+        <x:v>BPK-BASE99-EAST-WASTE-BIN</x:v>
+      </x:c>
+      <x:c r="B318" t="str">
+        <x:v>基地99层 · WASTE普通垃圾设施</x:v>
+      </x:c>
+      <x:c r="C318" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D318" t="str">
+        <x:v>东侧固定设施包</x:v>
+      </x:c>
+      <x:c r="E318" t="str">
+        <x:v>base99_package_east_waste_bin</x:v>
+      </x:c>
+      <x:c r="F318" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G318" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H318" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I318" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J318" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K318" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L318" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M318" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N318" s="349" t="str">
+        <x:v>包络 1.298×1.100×1.460m；11 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O318" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_waste_bin/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P318" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q318" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;东侧固定设施包;east_waste_bin;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R318" s="349" t="str">
+        <x:f>C318&amp;"|"&amp;D318&amp;"|"&amp;E318&amp;"|"&amp;F318&amp;"|"&amp;LOWER(H318)&amp;"|"&amp;I318</x:f>
+        <x:v>基地资产包|东侧固定设施包|base99_package_east_waste_bin|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S318" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R318)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T318" s="349" t="str">
+        <x:v>6a78c74a3600bc5c4bb34683cf8e487982e3da1045433b3bb5abb0e251cb1408</x:v>
+      </x:c>
+      <x:c r="U318" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V318" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W318" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X318" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_waste_bin；对象 11；中心 (10.701, -5.200, 0.730)m；朝向 Blender +Y north；预期导出 east_waste_bin_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" ht="54" customHeight="1">
+      <x:c r="A319" t="str">
+        <x:v>BPK-BASE99-EAST-WORK-TOGETHER-POSTER</x:v>
+      </x:c>
+      <x:c r="B319" t="str">
+        <x:v>基地99层 · WORK_TOGETHER工业海报</x:v>
+      </x:c>
+      <x:c r="C319" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D319" t="str">
+        <x:v>东侧固定设施包</x:v>
+      </x:c>
+      <x:c r="E319" t="str">
+        <x:v>base99_package_east_work_together_poster</x:v>
+      </x:c>
+      <x:c r="F319" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G319" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H319" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I319" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J319" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K319" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L319" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M319" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N319" s="349" t="str">
+        <x:v>包络 0.544×2.360×1.620m；15 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O319" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_work_together_poster/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P319" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q319" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;东侧固定设施包;east_work_together_poster;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R319" s="349" t="str">
+        <x:f>C319&amp;"|"&amp;D319&amp;"|"&amp;E319&amp;"|"&amp;F319&amp;"|"&amp;LOWER(H319)&amp;"|"&amp;I319</x:f>
+        <x:v>基地资产包|东侧固定设施包|base99_package_east_work_together_poster|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S319" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R319)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T319" s="349" t="str">
+        <x:v>a595e1cab6d94f9b621148105076ea8100dedc1d3b05d3e1fa82e5fe6a426e5d</x:v>
+      </x:c>
+      <x:c r="U319" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V319" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W319" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X319" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_work_together_poster；对象 15；中心 (14.138, -8.450, 4.720)m；朝向 Blender +Y north；预期导出 east_work_together_poster_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" ht="54" customHeight="1">
+      <x:c r="A320" t="str">
+        <x:v>BPK-BASE99-TILE-R01-C01</x:v>
+      </x:c>
+      <x:c r="B320" t="str">
+        <x:v>基地99层 · 地砖_R01C01_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C320" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D320" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E320" t="str">
+        <x:v>base99_package_tile_r01_c01</x:v>
+      </x:c>
+      <x:c r="F320" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G320" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H320" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I320" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J320" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K320" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L320" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M320" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N320" s="349" t="str">
+        <x:v>包络 5.000×5.000×0.448m；20 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O320" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r01_c01/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P320" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q320" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r01_c01;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R320" s="349" t="str">
+        <x:f>C320&amp;"|"&amp;D320&amp;"|"&amp;E320&amp;"|"&amp;F320&amp;"|"&amp;LOWER(H320)&amp;"|"&amp;I320</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r01_c01|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S320" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R320)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T320" s="349" t="str">
+        <x:v>50114ddc61a41a4203b8bf5470c1b7f0d11fdd9f54184096469632a06af30a69</x:v>
+      </x:c>
+      <x:c r="U320" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V320" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W320" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X320" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c01；对象 22；中心 (-12.500, -12.500, -0.076)m；朝向 Blender +Y north；预期导出 tile_r01_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" ht="54" customHeight="1">
+      <x:c r="A321" t="str">
+        <x:v>BPK-BASE99-TILE-R01-C02</x:v>
+      </x:c>
+      <x:c r="B321" t="str">
+        <x:v>基地99层 · 地砖_R01C02_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C321" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D321" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E321" t="str">
+        <x:v>base99_package_tile_r01_c02</x:v>
+      </x:c>
+      <x:c r="F321" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G321" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H321" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I321" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J321" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K321" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L321" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M321" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N321" s="349" t="str">
+        <x:v>包络 5.035×5.000×0.468m；33 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O321" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r01_c02/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P321" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q321" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r01_c02;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R321" s="349" t="str">
+        <x:f>C321&amp;"|"&amp;D321&amp;"|"&amp;E321&amp;"|"&amp;F321&amp;"|"&amp;LOWER(H321)&amp;"|"&amp;I321</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r01_c02|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S321" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R321)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T321" s="349" t="str">
+        <x:v>1b5ac0739c758c20681bf4ac48ca20b1e6ec1da707b52afd008d15d61ed0cc92</x:v>
+      </x:c>
+      <x:c r="U321" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V321" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W321" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X321" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c02；对象 35；中心 (-7.518, -12.500, -0.066)m；朝向 Blender +Y north；预期导出 tile_r01_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" ht="54" customHeight="1">
+      <x:c r="A322" t="str">
+        <x:v>BPK-BASE99-TILE-R01-C03</x:v>
+      </x:c>
+      <x:c r="B322" t="str">
+        <x:v>基地99层 · 地砖_R01C03_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C322" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D322" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E322" t="str">
+        <x:v>base99_package_tile_r01_c03</x:v>
+      </x:c>
+      <x:c r="F322" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G322" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H322" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I322" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J322" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K322" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L322" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M322" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N322" s="349" t="str">
+        <x:v>包络 5.035×5.000×0.465m；31 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O322" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r01_c03/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P322" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q322" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r01_c03;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R322" s="349" t="str">
+        <x:f>C322&amp;"|"&amp;D322&amp;"|"&amp;E322&amp;"|"&amp;F322&amp;"|"&amp;LOWER(H322)&amp;"|"&amp;I322</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r01_c03|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S322" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R322)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T322" s="349" t="str">
+        <x:v>fa8f49384390c5cf0df25001ffc592250eec86f8d178ac19b5ef70d9386a3ae0</x:v>
+      </x:c>
+      <x:c r="U322" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V322" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W322" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X322" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c03；对象 33；中心 (-2.518, -12.500, -0.068)m；朝向 Blender +Y north；预期导出 tile_r01_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" ht="54" customHeight="1">
+      <x:c r="A323" t="str">
+        <x:v>BPK-BASE99-TILE-R01-C04</x:v>
+      </x:c>
+      <x:c r="B323" t="str">
+        <x:v>基地99层 · 地砖_R01C04_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C323" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D323" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E323" t="str">
+        <x:v>base99_package_tile_r01_c04</x:v>
+      </x:c>
+      <x:c r="F323" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G323" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H323" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I323" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J323" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K323" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L323" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M323" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N323" s="349" t="str">
+        <x:v>包络 5.035×5.000×0.448m；21 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O323" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r01_c04/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P323" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q323" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r01_c04;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R323" s="349" t="str">
+        <x:f>C323&amp;"|"&amp;D323&amp;"|"&amp;E323&amp;"|"&amp;F323&amp;"|"&amp;LOWER(H323)&amp;"|"&amp;I323</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r01_c04|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S323" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R323)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T323" s="349" t="str">
+        <x:v>07953f736d6441d1b292f6f093531569e7187ecdd7e74ff972c85d4ecae0bf19</x:v>
+      </x:c>
+      <x:c r="U323" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V323" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W323" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X323" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c04；对象 23；中心 (2.482, -12.500, -0.076)m；朝向 Blender +Y north；预期导出 tile_r01_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" ht="54" customHeight="1">
+      <x:c r="A324" t="str">
+        <x:v>BPK-BASE99-TILE-R01-C05</x:v>
+      </x:c>
+      <x:c r="B324" t="str">
+        <x:v>基地99层 · 地砖_R01C05_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C324" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D324" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E324" t="str">
+        <x:v>base99_package_tile_r01_c05</x:v>
+      </x:c>
+      <x:c r="F324" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G324" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H324" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I324" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J324" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K324" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L324" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M324" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N324" s="349" t="str">
+        <x:v>包络 5.035×5.000×0.468m；33 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O324" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r01_c05/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P324" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q324" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r01_c05;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R324" s="349" t="str">
+        <x:f>C324&amp;"|"&amp;D324&amp;"|"&amp;E324&amp;"|"&amp;F324&amp;"|"&amp;LOWER(H324)&amp;"|"&amp;I324</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r01_c05|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S324" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R324)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T324" s="349" t="str">
+        <x:v>8815ea27facc0a19383962cb9019b1ea199e6dcf230ac7daf0a46ae93d45061c</x:v>
+      </x:c>
+      <x:c r="U324" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V324" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W324" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X324" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c05；对象 35；中心 (7.482, -12.500, -0.066)m；朝向 Blender +Y north；预期导出 tile_r01_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" ht="54" customHeight="1">
+      <x:c r="A325" t="str">
+        <x:v>BPK-BASE99-TILE-R01-C06</x:v>
+      </x:c>
+      <x:c r="B325" t="str">
+        <x:v>基地99层 · 地砖_R01C06_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C325" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D325" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E325" t="str">
+        <x:v>base99_package_tile_r01_c06</x:v>
+      </x:c>
+      <x:c r="F325" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G325" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H325" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I325" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J325" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K325" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L325" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M325" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N325" s="349" t="str">
+        <x:v>包络 5.035×5.000×0.448m；21 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O325" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r01_c06/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P325" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q325" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r01_c06;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R325" s="349" t="str">
+        <x:f>C325&amp;"|"&amp;D325&amp;"|"&amp;E325&amp;"|"&amp;F325&amp;"|"&amp;LOWER(H325)&amp;"|"&amp;I325</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r01_c06|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S325" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R325)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T325" s="349" t="str">
+        <x:v>73fada6c331d64af5514379eb64412301b3674328cea8e34b698f2c0f5562690</x:v>
+      </x:c>
+      <x:c r="U325" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V325" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W325" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X325" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c06；对象 23；中心 (12.482, -12.500, -0.076)m；朝向 Blender +Y north；预期导出 tile_r01_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" ht="54" customHeight="1">
+      <x:c r="A326" t="str">
+        <x:v>BPK-BASE99-TILE-R02-C01</x:v>
+      </x:c>
+      <x:c r="B326" t="str">
+        <x:v>基地99层 · 地砖_R02C01_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C326" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D326" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E326" t="str">
+        <x:v>base99_package_tile_r02_c01</x:v>
+      </x:c>
+      <x:c r="F326" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G326" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H326" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I326" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J326" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K326" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L326" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M326" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N326" s="349" t="str">
+        <x:v>包络 5.000×5.035×0.448m；22 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O326" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r02_c01/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P326" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q326" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r02_c01;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R326" s="349" t="str">
+        <x:f>C326&amp;"|"&amp;D326&amp;"|"&amp;E326&amp;"|"&amp;F326&amp;"|"&amp;LOWER(H326)&amp;"|"&amp;I326</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r02_c01|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S326" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R326)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T326" s="349" t="str">
+        <x:v>6fcc0af792b1356054d6b74858d389fed4d4d46d1b140121faead5a9d6d850a3</x:v>
+      </x:c>
+      <x:c r="U326" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V326" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W326" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X326" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c01；对象 24；中心 (-12.500, -7.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r02_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" ht="54" customHeight="1">
+      <x:c r="A327" t="str">
+        <x:v>BPK-BASE99-TILE-R02-C02</x:v>
+      </x:c>
+      <x:c r="B327" t="str">
+        <x:v>基地99层 · 地砖_R02C02_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C327" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D327" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E327" t="str">
+        <x:v>base99_package_tile_r02_c02</x:v>
+      </x:c>
+      <x:c r="F327" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G327" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H327" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I327" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J327" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K327" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L327" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M327" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N327" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；36 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O327" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r02_c02/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P327" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q327" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r02_c02;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R327" s="349" t="str">
+        <x:f>C327&amp;"|"&amp;D327&amp;"|"&amp;E327&amp;"|"&amp;F327&amp;"|"&amp;LOWER(H327)&amp;"|"&amp;I327</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r02_c02|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S327" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R327)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T327" s="349" t="str">
+        <x:v>9f6df3fa5f32a0404acf1d0029c19324f7189403a1b2169a826a6637040baf5d</x:v>
+      </x:c>
+      <x:c r="U327" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V327" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W327" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X327" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c02；对象 38；中心 (-7.518, -7.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r02_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" ht="54" customHeight="1">
+      <x:c r="A328" t="str">
+        <x:v>BPK-BASE99-TILE-R02-C03</x:v>
+      </x:c>
+      <x:c r="B328" t="str">
+        <x:v>基地99层 · 地砖_R02C03_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C328" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D328" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E328" t="str">
+        <x:v>base99_package_tile_r02_c03</x:v>
+      </x:c>
+      <x:c r="F328" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G328" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H328" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I328" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J328" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K328" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L328" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M328" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N328" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.468m；42 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O328" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r02_c03/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P328" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q328" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r02_c03;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R328" s="349" t="str">
+        <x:f>C328&amp;"|"&amp;D328&amp;"|"&amp;E328&amp;"|"&amp;F328&amp;"|"&amp;LOWER(H328)&amp;"|"&amp;I328</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r02_c03|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S328" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R328)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T328" s="349" t="str">
+        <x:v>5e726328226ee81ac59f23f1db00b5e8a7475c3f882d278afb43fc0a757e981b</x:v>
+      </x:c>
+      <x:c r="U328" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V328" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W328" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X328" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c03；对象 44；中心 (-2.518, -7.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r02_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" ht="54" customHeight="1">
+      <x:c r="A329" t="str">
+        <x:v>BPK-BASE99-TILE-R02-C04</x:v>
+      </x:c>
+      <x:c r="B329" t="str">
+        <x:v>基地99层 · 地砖_R02C04_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C329" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D329" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E329" t="str">
+        <x:v>base99_package_tile_r02_c04</x:v>
+      </x:c>
+      <x:c r="F329" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G329" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H329" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I329" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J329" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K329" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L329" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M329" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N329" s="349" t="str">
+        <x:v>包络 5.190×5.035×0.468m；34 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O329" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r02_c04/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P329" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q329" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r02_c04;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R329" s="349" t="str">
+        <x:f>C329&amp;"|"&amp;D329&amp;"|"&amp;E329&amp;"|"&amp;F329&amp;"|"&amp;LOWER(H329)&amp;"|"&amp;I329</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r02_c04|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S329" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R329)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T329" s="349" t="str">
+        <x:v>38a8093d74018eca0afd3e485dbaee4ffb4f3b5f0b9329e8dbf96f2df2854501</x:v>
+      </x:c>
+      <x:c r="U329" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V329" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W329" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X329" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c04；对象 36；中心 (2.405, -7.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r02_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" ht="54" customHeight="1">
+      <x:c r="A330" t="str">
+        <x:v>BPK-BASE99-TILE-R02-C05</x:v>
+      </x:c>
+      <x:c r="B330" t="str">
+        <x:v>基地99层 · 地砖_R02C05_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C330" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D330" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E330" t="str">
+        <x:v>base99_package_tile_r02_c05</x:v>
+      </x:c>
+      <x:c r="F330" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G330" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H330" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I330" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J330" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K330" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L330" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M330" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N330" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.465m；44 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O330" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r02_c05/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P330" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q330" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r02_c05;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R330" s="349" t="str">
+        <x:f>C330&amp;"|"&amp;D330&amp;"|"&amp;E330&amp;"|"&amp;F330&amp;"|"&amp;LOWER(H330)&amp;"|"&amp;I330</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r02_c05|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S330" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R330)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T330" s="349" t="str">
+        <x:v>5e7f52da5c3544d7fbac389a634ef65207bb512820c1e73cff6dc6f693a04c5d</x:v>
+      </x:c>
+      <x:c r="U330" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V330" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W330" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X330" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c05；对象 46；中心 (7.482, -7.518, -0.068)m；朝向 Blender +Y north；预期导出 tile_r02_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" ht="54" customHeight="1">
+      <x:c r="A331" t="str">
+        <x:v>BPK-BASE99-TILE-R02-C06</x:v>
+      </x:c>
+      <x:c r="B331" t="str">
+        <x:v>基地99层 · 地砖_R02C06_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C331" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D331" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E331" t="str">
+        <x:v>base99_package_tile_r02_c06</x:v>
+      </x:c>
+      <x:c r="F331" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G331" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H331" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I331" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J331" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K331" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L331" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M331" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N331" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.468m；35 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O331" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r02_c06/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P331" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q331" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r02_c06;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R331" s="349" t="str">
+        <x:f>C331&amp;"|"&amp;D331&amp;"|"&amp;E331&amp;"|"&amp;F331&amp;"|"&amp;LOWER(H331)&amp;"|"&amp;I331</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r02_c06|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S331" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R331)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T331" s="349" t="str">
+        <x:v>ce8bffa5705fcab7f2fc7ceccd6593f376a78c793192d27877b13330a65c101b</x:v>
+      </x:c>
+      <x:c r="U331" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V331" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W331" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X331" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c06；对象 37；中心 (12.482, -7.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r02_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" ht="54" customHeight="1">
+      <x:c r="A332" t="str">
+        <x:v>BPK-BASE99-TILE-R03-C01</x:v>
+      </x:c>
+      <x:c r="B332" t="str">
+        <x:v>基地99层 · 地砖_R03C01_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C332" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D332" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E332" t="str">
+        <x:v>base99_package_tile_r03_c01</x:v>
+      </x:c>
+      <x:c r="F332" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G332" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H332" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I332" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J332" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K332" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L332" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M332" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N332" s="349" t="str">
+        <x:v>包络 5.000×5.035×0.468m；37 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O332" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r03_c01/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P332" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q332" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r03_c01;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R332" s="349" t="str">
+        <x:f>C332&amp;"|"&amp;D332&amp;"|"&amp;E332&amp;"|"&amp;F332&amp;"|"&amp;LOWER(H332)&amp;"|"&amp;I332</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r03_c01|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S332" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R332)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T332" s="349" t="str">
+        <x:v>30c2ccc77637326151a6a4a10cc3314938e24ab8825c7c226647bcc3b2bf2fd9</x:v>
+      </x:c>
+      <x:c r="U332" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V332" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W332" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X332" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c01；对象 39；中心 (-12.500, -2.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r03_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" ht="54" customHeight="1">
+      <x:c r="A333" t="str">
+        <x:v>BPK-BASE99-TILE-R03-C02</x:v>
+      </x:c>
+      <x:c r="B333" t="str">
+        <x:v>基地99层 · 地砖_R03C02_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C333" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D333" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E333" t="str">
+        <x:v>base99_package_tile_r03_c02</x:v>
+      </x:c>
+      <x:c r="F333" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G333" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H333" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I333" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J333" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K333" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L333" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M333" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N333" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.465m；41 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O333" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r03_c02/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P333" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q333" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r03_c02;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R333" s="349" t="str">
+        <x:f>C333&amp;"|"&amp;D333&amp;"|"&amp;E333&amp;"|"&amp;F333&amp;"|"&amp;LOWER(H333)&amp;"|"&amp;I333</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r03_c02|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S333" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R333)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T333" s="349" t="str">
+        <x:v>2aaa4cfe2ba32c4ddd89bf705c9771d576ed62bb3d75bcb2e1998409b3326247</x:v>
+      </x:c>
+      <x:c r="U333" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V333" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W333" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X333" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c02；对象 43；中心 (-7.518, -2.518, -0.068)m；朝向 Blender +Y north；预期导出 tile_r03_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" ht="54" customHeight="1">
+      <x:c r="A334" t="str">
+        <x:v>BPK-BASE99-TILE-R03-C03</x:v>
+      </x:c>
+      <x:c r="B334" t="str">
+        <x:v>基地99层 · 地砖_R03C03_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C334" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D334" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E334" t="str">
+        <x:v>base99_package_tile_r03_c03</x:v>
+      </x:c>
+      <x:c r="F334" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G334" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H334" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I334" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J334" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K334" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L334" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M334" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N334" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；22 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O334" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r03_c03/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P334" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q334" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r03_c03;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R334" s="349" t="str">
+        <x:f>C334&amp;"|"&amp;D334&amp;"|"&amp;E334&amp;"|"&amp;F334&amp;"|"&amp;LOWER(H334)&amp;"|"&amp;I334</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r03_c03|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S334" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R334)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T334" s="349" t="str">
+        <x:v>89c023859c7aaaf8a95120fedd52cbb34da7fb0402d06dbf6432103190b935a5</x:v>
+      </x:c>
+      <x:c r="U334" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V334" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W334" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X334" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c03；对象 24；中心 (-2.518, -2.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r03_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" ht="54" customHeight="1">
+      <x:c r="A335" t="str">
+        <x:v>BPK-BASE99-TILE-R03-C04</x:v>
+      </x:c>
+      <x:c r="B335" t="str">
+        <x:v>基地99层 · 地砖_R03C04_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C335" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D335" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E335" t="str">
+        <x:v>base99_package_tile_r03_c04</x:v>
+      </x:c>
+      <x:c r="F335" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G335" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H335" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I335" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J335" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K335" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L335" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M335" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N335" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.468m；40 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O335" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r03_c04/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P335" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q335" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r03_c04;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R335" s="349" t="str">
+        <x:f>C335&amp;"|"&amp;D335&amp;"|"&amp;E335&amp;"|"&amp;F335&amp;"|"&amp;LOWER(H335)&amp;"|"&amp;I335</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r03_c04|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S335" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R335)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T335" s="349" t="str">
+        <x:v>aaedf919f4765fdafe08ef36de30b1fe56a6d6dd39ee82bf58f176068611f0ef</x:v>
+      </x:c>
+      <x:c r="U335" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V335" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W335" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X335" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c04；对象 42；中心 (2.482, -2.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r03_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" ht="54" customHeight="1">
+      <x:c r="A336" t="str">
+        <x:v>BPK-BASE99-TILE-R03-C05</x:v>
+      </x:c>
+      <x:c r="B336" t="str">
+        <x:v>基地99层 · 地砖_R03C05_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C336" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D336" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E336" t="str">
+        <x:v>base99_package_tile_r03_c05</x:v>
+      </x:c>
+      <x:c r="F336" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G336" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H336" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I336" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J336" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K336" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L336" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M336" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N336" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；43 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O336" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r03_c05/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P336" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q336" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r03_c05;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R336" s="349" t="str">
+        <x:f>C336&amp;"|"&amp;D336&amp;"|"&amp;E336&amp;"|"&amp;F336&amp;"|"&amp;LOWER(H336)&amp;"|"&amp;I336</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r03_c05|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S336" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R336)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T336" s="349" t="str">
+        <x:v>554673964f9f14e093a707a1d340631053a132eb3696485003ca73afa8d59a48</x:v>
+      </x:c>
+      <x:c r="U336" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V336" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W336" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X336" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c05；对象 45；中心 (7.482, -2.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r03_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" ht="54" customHeight="1">
+      <x:c r="A337" t="str">
+        <x:v>BPK-BASE99-TILE-R03-C06</x:v>
+      </x:c>
+      <x:c r="B337" t="str">
+        <x:v>基地99层 · 地砖_R03C06_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C337" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D337" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E337" t="str">
+        <x:v>base99_package_tile_r03_c06</x:v>
+      </x:c>
+      <x:c r="F337" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G337" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H337" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I337" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J337" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K337" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L337" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M337" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N337" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；22 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O337" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r03_c06/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P337" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q337" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r03_c06;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R337" s="349" t="str">
+        <x:f>C337&amp;"|"&amp;D337&amp;"|"&amp;E337&amp;"|"&amp;F337&amp;"|"&amp;LOWER(H337)&amp;"|"&amp;I337</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r03_c06|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S337" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R337)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T337" s="349" t="str">
+        <x:v>3bd98c558e72d6c8a8707d35d9f078249c38eb82aa4bb83cfac2c83b292e2ce2</x:v>
+      </x:c>
+      <x:c r="U337" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V337" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W337" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X337" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c06；对象 24；中心 (12.482, -2.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r03_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338" ht="54" customHeight="1">
+      <x:c r="A338" t="str">
+        <x:v>BPK-BASE99-TILE-R04-C01</x:v>
+      </x:c>
+      <x:c r="B338" t="str">
+        <x:v>基地99层 · 地砖_R04C01_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C338" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D338" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E338" t="str">
+        <x:v>base99_package_tile_r04_c01</x:v>
+      </x:c>
+      <x:c r="F338" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G338" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H338" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I338" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J338" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K338" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L338" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M338" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N338" s="349" t="str">
+        <x:v>包络 5.000×5.035×0.448m；21 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O338" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r04_c01/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P338" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q338" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r04_c01;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R338" s="349" t="str">
+        <x:f>C338&amp;"|"&amp;D338&amp;"|"&amp;E338&amp;"|"&amp;F338&amp;"|"&amp;LOWER(H338)&amp;"|"&amp;I338</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r04_c01|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S338" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R338)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T338" s="349" t="str">
+        <x:v>338cb6b5a8069f9cf9456e6f196187931eb7bc6c96cb4b72d0e8a758a5f15ce9</x:v>
+      </x:c>
+      <x:c r="U338" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V338" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W338" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X338" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c01；对象 23；中心 (-12.500, 2.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r04_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339" ht="54" customHeight="1">
+      <x:c r="A339" t="str">
+        <x:v>BPK-BASE99-TILE-R04-C02</x:v>
+      </x:c>
+      <x:c r="B339" t="str">
+        <x:v>基地99层 · 地砖_R04C02_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C339" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D339" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E339" t="str">
+        <x:v>base99_package_tile_r04_c02</x:v>
+      </x:c>
+      <x:c r="F339" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G339" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H339" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I339" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J339" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K339" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L339" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M339" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N339" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.468m；40 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O339" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r04_c02/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P339" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q339" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r04_c02;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R339" s="349" t="str">
+        <x:f>C339&amp;"|"&amp;D339&amp;"|"&amp;E339&amp;"|"&amp;F339&amp;"|"&amp;LOWER(H339)&amp;"|"&amp;I339</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r04_c02|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S339" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R339)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T339" s="349" t="str">
+        <x:v>5738caf788da722683bdcc4809fa1e6cba51e8537ebacde0e866d01fdac3daf9</x:v>
+      </x:c>
+      <x:c r="U339" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V339" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W339" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X339" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c02；对象 42；中心 (-7.518, 2.482, -0.066)m；朝向 Blender +Y north；预期导出 tile_r04_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" ht="54" customHeight="1">
+      <x:c r="A340" t="str">
+        <x:v>BPK-BASE99-TILE-R04-C03</x:v>
+      </x:c>
+      <x:c r="B340" t="str">
+        <x:v>基地99层 · 地砖_R04C03_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C340" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D340" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E340" t="str">
+        <x:v>base99_package_tile_r04_c03</x:v>
+      </x:c>
+      <x:c r="F340" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G340" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H340" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I340" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J340" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K340" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L340" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M340" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N340" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；24 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O340" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r04_c03/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P340" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q340" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r04_c03;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R340" s="349" t="str">
+        <x:f>C340&amp;"|"&amp;D340&amp;"|"&amp;E340&amp;"|"&amp;F340&amp;"|"&amp;LOWER(H340)&amp;"|"&amp;I340</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r04_c03|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S340" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R340)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T340" s="349" t="str">
+        <x:v>e92eab4472a95829706ee534c3e9f320a201b9111d7b08b8306610af9346a34e</x:v>
+      </x:c>
+      <x:c r="U340" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V340" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W340" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X340" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c03；对象 26；中心 (-2.518, 2.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r04_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341" ht="54" customHeight="1">
+      <x:c r="A341" t="str">
+        <x:v>BPK-BASE99-TILE-R04-C04</x:v>
+      </x:c>
+      <x:c r="B341" t="str">
+        <x:v>基地99层 · 地砖_R04C04_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C341" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D341" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E341" t="str">
+        <x:v>base99_package_tile_r04_c04</x:v>
+      </x:c>
+      <x:c r="F341" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G341" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H341" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I341" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J341" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K341" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L341" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M341" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N341" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.492m；60 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O341" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r04_c04/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P341" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q341" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r04_c04;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R341" s="349" t="str">
+        <x:f>C341&amp;"|"&amp;D341&amp;"|"&amp;E341&amp;"|"&amp;F341&amp;"|"&amp;LOWER(H341)&amp;"|"&amp;I341</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r04_c04|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S341" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R341)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T341" s="349" t="str">
+        <x:v>f6ab2f697f3e2aafc6b30a0dd76d3c29da4ee77f8780327de33633e770db5d87</x:v>
+      </x:c>
+      <x:c r="U341" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V341" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W341" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X341" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c04；对象 62；中心 (2.482, 2.482, -0.054)m；朝向 Blender +Y north；预期导出 tile_r04_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" ht="54" customHeight="1">
+      <x:c r="A342" t="str">
+        <x:v>BPK-BASE99-TILE-R04-C05</x:v>
+      </x:c>
+      <x:c r="B342" t="str">
+        <x:v>基地99层 · 地砖_R04C05_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C342" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D342" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E342" t="str">
+        <x:v>base99_package_tile_r04_c05</x:v>
+      </x:c>
+      <x:c r="F342" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G342" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H342" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I342" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J342" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K342" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L342" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M342" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N342" s="349" t="str">
+        <x:v>包络 6.180×5.035×0.493m；61 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O342" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r04_c05/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P342" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q342" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r04_c05;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R342" s="349" t="str">
+        <x:f>C342&amp;"|"&amp;D342&amp;"|"&amp;E342&amp;"|"&amp;F342&amp;"|"&amp;LOWER(H342)&amp;"|"&amp;I342</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r04_c05|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S342" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R342)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T342" s="349" t="str">
+        <x:v>122243e9a67680a77dbb6ac79cca9f5ad4546dc81da0dcc154dbe662de1e4391</x:v>
+      </x:c>
+      <x:c r="U342" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V342" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W342" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X342" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c05；对象 63；中心 (6.910, 2.482, -0.053)m；朝向 Blender +Y north；预期导出 tile_r04_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343" ht="54" customHeight="1">
+      <x:c r="A343" t="str">
+        <x:v>BPK-BASE99-TILE-R04-C06</x:v>
+      </x:c>
+      <x:c r="B343" t="str">
+        <x:v>基地99层 · 地砖_R04C06_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C343" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D343" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E343" t="str">
+        <x:v>base99_package_tile_r04_c06</x:v>
+      </x:c>
+      <x:c r="F343" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G343" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H343" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I343" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J343" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K343" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L343" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M343" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N343" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.468m；39 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O343" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r04_c06/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P343" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q343" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r04_c06;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R343" s="349" t="str">
+        <x:f>C343&amp;"|"&amp;D343&amp;"|"&amp;E343&amp;"|"&amp;F343&amp;"|"&amp;LOWER(H343)&amp;"|"&amp;I343</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r04_c06|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S343" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R343)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T343" s="349" t="str">
+        <x:v>596c60a990893cd7afeb8cc3c482c972682c3f42e955d103a4910d5493cf9137</x:v>
+      </x:c>
+      <x:c r="U343" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V343" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W343" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X343" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c06；对象 41；中心 (12.482, 2.482, -0.066)m；朝向 Blender +Y north；预期导出 tile_r04_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" ht="54" customHeight="1">
+      <x:c r="A344" t="str">
+        <x:v>BPK-BASE99-TILE-R05-C01</x:v>
+      </x:c>
+      <x:c r="B344" t="str">
+        <x:v>基地99层 · 地砖_R05C01_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C344" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D344" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E344" t="str">
+        <x:v>base99_package_tile_r05_c01</x:v>
+      </x:c>
+      <x:c r="F344" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G344" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H344" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I344" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J344" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K344" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L344" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M344" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N344" s="349" t="str">
+        <x:v>包络 5.000×5.035×0.448m；21 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O344" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r05_c01/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P344" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q344" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r05_c01;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R344" s="349" t="str">
+        <x:f>C344&amp;"|"&amp;D344&amp;"|"&amp;E344&amp;"|"&amp;F344&amp;"|"&amp;LOWER(H344)&amp;"|"&amp;I344</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r05_c01|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S344" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R344)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T344" s="349" t="str">
+        <x:v>fe30e9a5abcc4d3e41ff324066e3df45983f1d5f3a9117cb431ecc44c3037b75</x:v>
+      </x:c>
+      <x:c r="U344" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V344" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W344" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X344" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c01；对象 23；中心 (-12.500, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" ht="54" customHeight="1">
+      <x:c r="A345" t="str">
+        <x:v>BPK-BASE99-TILE-R05-C02</x:v>
+      </x:c>
+      <x:c r="B345" t="str">
+        <x:v>基地99层 · 地砖_R05C02_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C345" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D345" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E345" t="str">
+        <x:v>base99_package_tile_r05_c02</x:v>
+      </x:c>
+      <x:c r="F345" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G345" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H345" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I345" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J345" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K345" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L345" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M345" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N345" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；22 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O345" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r05_c02/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P345" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q345" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r05_c02;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R345" s="349" t="str">
+        <x:f>C345&amp;"|"&amp;D345&amp;"|"&amp;E345&amp;"|"&amp;F345&amp;"|"&amp;LOWER(H345)&amp;"|"&amp;I345</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r05_c02|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S345" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R345)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T345" s="349" t="str">
+        <x:v>a783b334746644717eb8f55b714b32053f6cb2b99870192db5ba4f30dc5df837</x:v>
+      </x:c>
+      <x:c r="U345" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V345" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W345" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X345" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c02；对象 24；中心 (-7.518, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346" ht="54" customHeight="1">
+      <x:c r="A346" t="str">
+        <x:v>BPK-BASE99-TILE-R05-C03</x:v>
+      </x:c>
+      <x:c r="B346" t="str">
+        <x:v>基地99层 · 地砖_R05C03_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C346" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D346" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E346" t="str">
+        <x:v>base99_package_tile_r05_c03</x:v>
+      </x:c>
+      <x:c r="F346" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G346" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H346" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I346" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J346" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K346" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L346" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M346" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N346" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；22 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O346" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r05_c03/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P346" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q346" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r05_c03;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R346" s="349" t="str">
+        <x:f>C346&amp;"|"&amp;D346&amp;"|"&amp;E346&amp;"|"&amp;F346&amp;"|"&amp;LOWER(H346)&amp;"|"&amp;I346</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r05_c03|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S346" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R346)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T346" s="349" t="str">
+        <x:v>ee85c0ace45e59a4c21f7d77f77df84a80cc990c8961ffc955d11bc38079b2b0</x:v>
+      </x:c>
+      <x:c r="U346" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V346" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W346" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X346" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c03；对象 24；中心 (-2.518, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347" ht="54" customHeight="1">
+      <x:c r="A347" t="str">
+        <x:v>BPK-BASE99-TILE-R05-C04</x:v>
+      </x:c>
+      <x:c r="B347" t="str">
+        <x:v>基地99层 · 地砖_R05C04_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C347" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D347" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E347" t="str">
+        <x:v>base99_package_tile_r05_c04</x:v>
+      </x:c>
+      <x:c r="F347" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G347" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H347" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I347" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J347" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K347" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L347" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M347" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N347" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；22 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O347" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r05_c04/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P347" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q347" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r05_c04;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R347" s="349" t="str">
+        <x:f>C347&amp;"|"&amp;D347&amp;"|"&amp;E347&amp;"|"&amp;F347&amp;"|"&amp;LOWER(H347)&amp;"|"&amp;I347</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r05_c04|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S347" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R347)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T347" s="349" t="str">
+        <x:v>5d65291670394b9a0d6d15e84770b965a7f9150253bf28a2717f52f5ab87a1ac</x:v>
+      </x:c>
+      <x:c r="U347" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V347" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W347" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X347" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c04；对象 24；中心 (2.482, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" ht="54" customHeight="1">
+      <x:c r="A348" t="str">
+        <x:v>BPK-BASE99-TILE-R05-C05</x:v>
+      </x:c>
+      <x:c r="B348" t="str">
+        <x:v>基地99层 · 地砖_R05C05_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C348" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D348" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E348" t="str">
+        <x:v>base99_package_tile_r05_c05</x:v>
+      </x:c>
+      <x:c r="F348" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G348" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H348" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I348" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J348" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K348" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L348" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M348" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N348" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；22 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O348" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r05_c05/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P348" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q348" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r05_c05;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R348" s="349" t="str">
+        <x:f>C348&amp;"|"&amp;D348&amp;"|"&amp;E348&amp;"|"&amp;F348&amp;"|"&amp;LOWER(H348)&amp;"|"&amp;I348</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r05_c05|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S348" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R348)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T348" s="349" t="str">
+        <x:v>8bd979af8e0fc07fa25bc9c66c204ea64a50e978fb2d09d4b12a5a4a5d5604ce</x:v>
+      </x:c>
+      <x:c r="U348" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V348" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W348" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X348" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c05；对象 24；中心 (7.482, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" ht="54" customHeight="1">
+      <x:c r="A349" t="str">
+        <x:v>BPK-BASE99-TILE-R05-C06</x:v>
+      </x:c>
+      <x:c r="B349" t="str">
+        <x:v>基地99层 · 地砖_R05C06_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C349" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D349" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E349" t="str">
+        <x:v>base99_package_tile_r05_c06</x:v>
+      </x:c>
+      <x:c r="F349" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G349" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H349" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I349" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J349" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K349" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L349" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M349" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N349" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；22 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O349" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r05_c06/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P349" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q349" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r05_c06;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R349" s="349" t="str">
+        <x:f>C349&amp;"|"&amp;D349&amp;"|"&amp;E349&amp;"|"&amp;F349&amp;"|"&amp;LOWER(H349)&amp;"|"&amp;I349</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r05_c06|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S349" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R349)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T349" s="349" t="str">
+        <x:v>db7dfa24d8238709eb3e434f2451dc1dab734e81f6b76a1c162a946a10fe6c22</x:v>
+      </x:c>
+      <x:c r="U349" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V349" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W349" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X349" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c06；对象 24；中心 (12.482, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" ht="54" customHeight="1">
+      <x:c r="A350" t="str">
+        <x:v>BPK-BASE99-TILE-R06-C01</x:v>
+      </x:c>
+      <x:c r="B350" t="str">
+        <x:v>基地99层 · 地砖_R06C01_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C350" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D350" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E350" t="str">
+        <x:v>base99_package_tile_r06_c01</x:v>
+      </x:c>
+      <x:c r="F350" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G350" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H350" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I350" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J350" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K350" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L350" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M350" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N350" s="349" t="str">
+        <x:v>包络 5.000×5.035×0.448m；21 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O350" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r06_c01/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P350" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q350" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r06_c01;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R350" s="349" t="str">
+        <x:f>C350&amp;"|"&amp;D350&amp;"|"&amp;E350&amp;"|"&amp;F350&amp;"|"&amp;LOWER(H350)&amp;"|"&amp;I350</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r06_c01|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S350" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R350)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T350" s="349" t="str">
+        <x:v>12bca314b55122e9c2f6585400641c5da3ab7928943f792e0a56f60d1359f381</x:v>
+      </x:c>
+      <x:c r="U350" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V350" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W350" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X350" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c01；对象 23；中心 (-12.500, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" ht="54" customHeight="1">
+      <x:c r="A351" t="str">
+        <x:v>BPK-BASE99-TILE-R06-C02</x:v>
+      </x:c>
+      <x:c r="B351" t="str">
+        <x:v>基地99层 · 地砖_R06C02_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C351" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D351" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E351" t="str">
+        <x:v>base99_package_tile_r06_c02</x:v>
+      </x:c>
+      <x:c r="F351" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G351" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H351" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I351" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J351" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K351" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L351" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M351" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N351" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；22 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O351" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r06_c02/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P351" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q351" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r06_c02;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R351" s="349" t="str">
+        <x:f>C351&amp;"|"&amp;D351&amp;"|"&amp;E351&amp;"|"&amp;F351&amp;"|"&amp;LOWER(H351)&amp;"|"&amp;I351</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r06_c02|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S351" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R351)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T351" s="349" t="str">
+        <x:v>8b1ebc38d0240518741c35f0e9cb711684e50e794e1b1332f2f954ec1961dff9</x:v>
+      </x:c>
+      <x:c r="U351" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V351" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W351" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X351" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c02；对象 24；中心 (-7.518, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" ht="54" customHeight="1">
+      <x:c r="A352" t="str">
+        <x:v>BPK-BASE99-TILE-R06-C03</x:v>
+      </x:c>
+      <x:c r="B352" t="str">
+        <x:v>基地99层 · 地砖_R06C03_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C352" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D352" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E352" t="str">
+        <x:v>base99_package_tile_r06_c03</x:v>
+      </x:c>
+      <x:c r="F352" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G352" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H352" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I352" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J352" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K352" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L352" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M352" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N352" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；22 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O352" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r06_c03/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P352" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q352" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r06_c03;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R352" s="349" t="str">
+        <x:f>C352&amp;"|"&amp;D352&amp;"|"&amp;E352&amp;"|"&amp;F352&amp;"|"&amp;LOWER(H352)&amp;"|"&amp;I352</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r06_c03|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S352" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R352)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T352" s="349" t="str">
+        <x:v>359eb33a0a69757f863f293df00529484ababa1ffb9694fd869d4d89be9f7195</x:v>
+      </x:c>
+      <x:c r="U352" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V352" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W352" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X352" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c03；对象 24；中心 (-2.518, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" ht="54" customHeight="1">
+      <x:c r="A353" t="str">
+        <x:v>BPK-BASE99-TILE-R06-C04</x:v>
+      </x:c>
+      <x:c r="B353" t="str">
+        <x:v>基地99层 · 地砖_R06C04_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C353" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D353" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E353" t="str">
+        <x:v>base99_package_tile_r06_c04</x:v>
+      </x:c>
+      <x:c r="F353" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G353" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H353" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I353" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J353" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K353" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L353" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M353" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N353" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；22 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O353" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r06_c04/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P353" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q353" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r06_c04;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R353" s="349" t="str">
+        <x:f>C353&amp;"|"&amp;D353&amp;"|"&amp;E353&amp;"|"&amp;F353&amp;"|"&amp;LOWER(H353)&amp;"|"&amp;I353</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r06_c04|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S353" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R353)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T353" s="349" t="str">
+        <x:v>d0f90f5fbe0909fa39a9321863136f93f88807b3efeac80976fa1303172ea452</x:v>
+      </x:c>
+      <x:c r="U353" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V353" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W353" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X353" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c04；对象 24；中心 (2.482, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" ht="54" customHeight="1">
+      <x:c r="A354" t="str">
+        <x:v>BPK-BASE99-TILE-R06-C05</x:v>
+      </x:c>
+      <x:c r="B354" t="str">
+        <x:v>基地99层 · 地砖_R06C05_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C354" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D354" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E354" t="str">
+        <x:v>base99_package_tile_r06_c05</x:v>
+      </x:c>
+      <x:c r="F354" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G354" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H354" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I354" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J354" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K354" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L354" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M354" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N354" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；22 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O354" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r06_c05/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P354" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q354" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r06_c05;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R354" s="349" t="str">
+        <x:f>C354&amp;"|"&amp;D354&amp;"|"&amp;E354&amp;"|"&amp;F354&amp;"|"&amp;LOWER(H354)&amp;"|"&amp;I354</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r06_c05|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S354" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R354)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T354" s="349" t="str">
+        <x:v>c8eb5578976bd3a9f6b731e4624430fdccbd9207ef794650216332e6d05be6d8</x:v>
+      </x:c>
+      <x:c r="U354" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V354" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W354" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X354" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c05；对象 24；中心 (7.482, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" ht="54" customHeight="1">
+      <x:c r="A355" t="str">
+        <x:v>BPK-BASE99-TILE-R06-C06</x:v>
+      </x:c>
+      <x:c r="B355" t="str">
+        <x:v>基地99层 · 地砖_R06C06_原砖与深化内容</x:v>
+      </x:c>
+      <x:c r="C355" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D355" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E355" t="str">
+        <x:v>base99_package_tile_r06_c06</x:v>
+      </x:c>
+      <x:c r="F355" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G355" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H355" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I355" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J355" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K355" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L355" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M355" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N355" s="349" t="str">
+        <x:v>包络 5.035×5.035×0.448m；22 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O355" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r06_c06/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P355" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q355" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r06_c06;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R355" s="349" t="str">
+        <x:f>C355&amp;"|"&amp;D355&amp;"|"&amp;E355&amp;"|"&amp;F355&amp;"|"&amp;LOWER(H355)&amp;"|"&amp;I355</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_tile_r06_c06|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S355" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R355)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T355" s="349" t="str">
+        <x:v>8ae804eb26047b9415efbe30c008e8e26e76d9ef0bec857677b1032028cfc780</x:v>
+      </x:c>
+      <x:c r="U355" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V355" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W355" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X355" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c06；对象 24；中心 (12.482, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" ht="54" customHeight="1">
+      <x:c r="A356" t="str">
+        <x:v>BPK-BASE99-LOFT-BACKWALL-FUNCTION-PANEL-SYSTEM</x:v>
+      </x:c>
+      <x:c r="B356" t="str">
+        <x:v>基地99层 · 二楼后墙功能面板系统</x:v>
+      </x:c>
+      <x:c r="C356" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D356" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E356" t="str">
+        <x:v>base99_package_loft_backwall_function_panel_system</x:v>
+      </x:c>
+      <x:c r="F356" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G356" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H356" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I356" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J356" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K356" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L356" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M356" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N356" s="349" t="str">
+        <x:v>包络 28.800×0.292×2.750m；77 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O356" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_backwall_function_panel_system/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P356" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q356" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_backwall_function_panel_system;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R356" s="349" t="str">
+        <x:f>C356&amp;"|"&amp;D356&amp;"|"&amp;E356&amp;"|"&amp;F356&amp;"|"&amp;LOWER(H356)&amp;"|"&amp;I356</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_backwall_function_panel_system|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S356" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R356)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T356" s="349" t="str">
+        <x:v>e19e912899716a1946613ca8b36cad17279a125e88ba3759d49066b46b623fca</x:v>
+      </x:c>
+      <x:c r="U356" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V356" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W356" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X356" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_backwall_function_panel_system；对象 77；中心 (0.000, 14.356, 8.035)m；朝向 Blender +Y north；预期导出 loft_backwall_function_panel_system_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" ht="54" customHeight="1">
+      <x:c r="A357" t="str">
+        <x:v>BPK-BASE99-LOFT-BACKWALL-SERVICES</x:v>
+      </x:c>
+      <x:c r="B357" t="str">
+        <x:v>基地99层 · 二楼后墙服务管线与应急盒</x:v>
+      </x:c>
+      <x:c r="C357" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D357" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E357" t="str">
+        <x:v>base99_package_loft_backwall_services</x:v>
+      </x:c>
+      <x:c r="F357" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G357" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H357" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I357" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J357" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K357" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L357" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M357" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N357" s="349" t="str">
+        <x:v>包络 25.600×0.818×2.350m；66 网格；6 灯</x:v>
+      </x:c>
+      <x:c r="O357" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_backwall_services/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P357" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q357" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_backwall_services;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R357" s="349" t="str">
+        <x:f>C357&amp;"|"&amp;D357&amp;"|"&amp;E357&amp;"|"&amp;F357&amp;"|"&amp;LOWER(H357)&amp;"|"&amp;I357</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_backwall_services|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S357" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R357)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T357" s="349" t="str">
+        <x:v>e5757210ba00607935a810ba77136f6936a0473d16ba3ead9ec72b232f3dbb42</x:v>
+      </x:c>
+      <x:c r="U357" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V357" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W357" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X357" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_backwall_services；对象 72；中心 (0.700, 14.159, 8.185)m；朝向 Blender +Y north；预期导出 loft_backwall_services_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" ht="54" customHeight="1">
+      <x:c r="A358" t="str">
+        <x:v>BPK-BASE99-LOFT-BATTERY-CABINET</x:v>
+      </x:c>
+      <x:c r="B358" t="str">
+        <x:v>基地99层 · BATTERY模块收纳箱</x:v>
+      </x:c>
+      <x:c r="C358" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D358" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E358" t="str">
+        <x:v>base99_package_loft_battery_cabinet</x:v>
+      </x:c>
+      <x:c r="F358" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G358" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H358" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I358" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J358" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K358" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L358" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M358" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N358" s="349" t="str">
+        <x:v>包络 1.200×0.993×0.850m；12 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O358" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_battery_cabinet/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P358" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q358" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_battery_cabinet;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R358" s="349" t="str">
+        <x:f>C358&amp;"|"&amp;D358&amp;"|"&amp;E358&amp;"|"&amp;F358&amp;"|"&amp;LOWER(H358)&amp;"|"&amp;I358</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_battery_cabinet|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S358" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R358)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T358" s="349" t="str">
+        <x:v>e84bd2da9ba84cddb8cd892c9fd9ef57db9fc4f386a8996fb108e9ef39b6dd60</x:v>
+      </x:c>
+      <x:c r="U358" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V358" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W358" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X358" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_battery_cabinet；对象 12；中心 (-1.950, 13.874, 6.545)m；朝向 Blender +Y north；预期导出 loft_battery_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" ht="54" customHeight="1">
+      <x:c r="A359" t="str">
+        <x:v>BPK-BASE99-LOFT-BED-AND-BEDDING</x:v>
+      </x:c>
+      <x:c r="B359" t="str">
+        <x:v>基地99层 · 参考床架床品与床下收纳</x:v>
+      </x:c>
+      <x:c r="C359" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D359" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E359" t="str">
+        <x:v>base99_package_loft_bed_and_bedding</x:v>
+      </x:c>
+      <x:c r="F359" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G359" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H359" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I359" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J359" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K359" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L359" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M359" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N359" s="349" t="str">
+        <x:v>包络 4.750×2.676×1.318m；37 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O359" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_bed_and_bedding/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P359" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q359" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_bed_and_bedding;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R359" s="349" t="str">
+        <x:f>C359&amp;"|"&amp;D359&amp;"|"&amp;E359&amp;"|"&amp;F359&amp;"|"&amp;LOWER(H359)&amp;"|"&amp;I359</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_bed_and_bedding|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S359" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R359)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T359" s="349" t="str">
+        <x:v>6a00f3fb212e52e1f04ca441ef3edb34fc809d39d955cda83c9680489ba78e4c</x:v>
+      </x:c>
+      <x:c r="U359" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V359" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W359" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X359" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_bed_and_bedding；对象 37；中心 (0.300, 10.957, 6.669)m；朝向 Blender +Y north；预期导出 loft_bed_and_bedding_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360" ht="54" customHeight="1">
+      <x:c r="A360" t="str">
+        <x:v>BPK-BASE99-LOFT-BEDSIDE-LAMP</x:v>
+      </x:c>
+      <x:c r="B360" t="str">
+        <x:v>基地99层 · 暖橙床头灯</x:v>
+      </x:c>
+      <x:c r="C360" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D360" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E360" t="str">
+        <x:v>base99_package_loft_bedside_lamp</x:v>
+      </x:c>
+      <x:c r="F360" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G360" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H360" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I360" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J360" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K360" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L360" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M360" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N360" s="349" t="str">
+        <x:v>包络 0.407×0.407×0.895m；3 网格；1 灯</x:v>
+      </x:c>
+      <x:c r="O360" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_bedside_lamp/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P360" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q360" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_bedside_lamp;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R360" s="349" t="str">
+        <x:f>C360&amp;"|"&amp;D360&amp;"|"&amp;E360&amp;"|"&amp;F360&amp;"|"&amp;LOWER(H360)&amp;"|"&amp;I360</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_bedside_lamp|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S360" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R360)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T360" s="349" t="str">
+        <x:v>6fc0add42c0b3a84549e9b0a26b83168d1c66ae05d98743459ac8a8c988774ee</x:v>
+      </x:c>
+      <x:c r="U360" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V360" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W360" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X360" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_bedside_lamp；对象 4；中心 (-2.800, 11.670, 7.677)m；朝向 Blender +Y north；预期导出 loft_bedside_lamp_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" ht="54" customHeight="1">
+      <x:c r="A361" t="str">
+        <x:v>BPK-BASE99-LOFT-BEDSIDE-RUG</x:v>
+      </x:c>
+      <x:c r="B361" t="str">
+        <x:v>基地99层 · 床边暖灰地毯</x:v>
+      </x:c>
+      <x:c r="C361" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D361" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E361" t="str">
+        <x:v>base99_package_loft_bedside_rug</x:v>
+      </x:c>
+      <x:c r="F361" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G361" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H361" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I361" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J361" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K361" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L361" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M361" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N361" s="349" t="str">
+        <x:v>包络 4.250×0.840×0.056m；6 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O361" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_bedside_rug/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P361" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q361" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_bedside_rug;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R361" s="349" t="str">
+        <x:f>C361&amp;"|"&amp;D361&amp;"|"&amp;E361&amp;"|"&amp;F361&amp;"|"&amp;LOWER(H361)&amp;"|"&amp;I361</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_bedside_rug|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S361" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R361)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T361" s="349" t="str">
+        <x:v>155af02af099a16947c2fce7c1b089557d556979381e07edb7b49a918a21dfe4</x:v>
+      </x:c>
+      <x:c r="U361" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V361" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W361" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X361" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_bedside_rug；对象 6；中心 (0.300, 9.820, 6.092)m；朝向 Blender +Y north；预期导出 loft_bedside_rug_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362" ht="54" customHeight="1">
+      <x:c r="A362" t="str">
+        <x:v>BPK-BASE99-LOFT-COFFEE-TABLE</x:v>
+      </x:c>
+      <x:c r="B362" t="str">
+        <x:v>基地99层 · 红棕茶几与生活物件</x:v>
+      </x:c>
+      <x:c r="C362" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D362" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E362" t="str">
+        <x:v>base99_package_loft_coffee_table</x:v>
+      </x:c>
+      <x:c r="F362" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G362" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H362" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I362" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J362" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K362" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L362" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M362" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N362" s="349" t="str">
+        <x:v>包络 2.850×1.280×0.910m；15 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O362" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_coffee_table/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P362" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q362" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_coffee_table;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R362" s="349" t="str">
+        <x:f>C362&amp;"|"&amp;D362&amp;"|"&amp;E362&amp;"|"&amp;F362&amp;"|"&amp;LOWER(H362)&amp;"|"&amp;I362</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_coffee_table|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S362" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R362)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T362" s="349" t="str">
+        <x:v>ae7976f7d5c94b30cf0c64385a49672b1c2b3bea2512d3a444b52e9e262f84e4</x:v>
+      </x:c>
+      <x:c r="U362" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V362" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W362" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X362" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_coffee_table；对象 15；中心 (6.200, 9.380, 6.555)m；朝向 Blender +Y north；预期导出 loft_coffee_table_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" ht="54" customHeight="1">
+      <x:c r="A363" t="str">
+        <x:v>BPK-BASE99-LOFT-COMPUTER-WORKSTATION</x:v>
+      </x:c>
+      <x:c r="B363" t="str">
+        <x:v>基地99层 · 双屏电脑完整工位</x:v>
+      </x:c>
+      <x:c r="C363" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D363" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E363" t="str">
+        <x:v>base99_package_loft_computer_workstation</x:v>
+      </x:c>
+      <x:c r="F363" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G363" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H363" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I363" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J363" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K363" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L363" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M363" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N363" s="349" t="str">
+        <x:v>包络 6.015×1.468×3.040m；85 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O363" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_computer_workstation/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P363" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q363" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_computer_workstation;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R363" s="349" t="str">
+        <x:f>C363&amp;"|"&amp;D363&amp;"|"&amp;E363&amp;"|"&amp;F363&amp;"|"&amp;LOWER(H363)&amp;"|"&amp;I363</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_computer_workstation|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S363" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R363)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T363" s="349" t="str">
+        <x:v>4d9ffaafc5ef96c16072b1221fce45649b469d530c02977942d6e8b163fa7c70</x:v>
+      </x:c>
+      <x:c r="U363" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V363" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W363" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X363" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_computer_workstation；对象 85；中心 (9.377, 13.634, 7.560)m；朝向 Blender +Y north；预期导出 loft_computer_workstation_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364" ht="54" customHeight="1">
+      <x:c r="A364" t="str">
+        <x:v>BPK-BASE99-LOFT-EXPLORE-POSTER</x:v>
+      </x:c>
+      <x:c r="B364" t="str">
+        <x:v>基地99层 · EXPLORE独立海报</x:v>
+      </x:c>
+      <x:c r="C364" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D364" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E364" t="str">
+        <x:v>base99_package_loft_explore_poster</x:v>
+      </x:c>
+      <x:c r="F364" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G364" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H364" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I364" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J364" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K364" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L364" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M364" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N364" s="349" t="str">
+        <x:v>包络 1.460×0.536×1.755m；14 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O364" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_explore_poster/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P364" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q364" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_explore_poster;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R364" s="349" t="str">
+        <x:f>C364&amp;"|"&amp;D364&amp;"|"&amp;E364&amp;"|"&amp;F364&amp;"|"&amp;LOWER(H364)&amp;"|"&amp;I364</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_explore_poster|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S364" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R364)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T364" s="349" t="str">
+        <x:v>03344c4b9c3a23ff4daae3368a4159bb720760d255d8afa67800bd44e260d720</x:v>
+      </x:c>
+      <x:c r="U364" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V364" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W364" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X364" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_explore_poster；对象 14；中心 (-2.120, 14.487, 8.098)m；朝向 Blender +Y north；预期导出 loft_explore_poster_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365" ht="54" customHeight="1">
+      <x:c r="A365" t="str">
+        <x:v>BPK-BASE99-LOFT-FOOD-CABINET</x:v>
+      </x:c>
+      <x:c r="B365" t="str">
+        <x:v>基地99层 · FOOD模块收纳箱</x:v>
+      </x:c>
+      <x:c r="C365" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D365" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E365" t="str">
+        <x:v>base99_package_loft_food_cabinet</x:v>
+      </x:c>
+      <x:c r="F365" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G365" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H365" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I365" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J365" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K365" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L365" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M365" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N365" s="349" t="str">
+        <x:v>包络 1.200×0.996×0.870m；9 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O365" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_food_cabinet/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P365" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q365" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_food_cabinet;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R365" s="349" t="str">
+        <x:f>C365&amp;"|"&amp;D365&amp;"|"&amp;E365&amp;"|"&amp;F365&amp;"|"&amp;LOWER(H365)&amp;"|"&amp;I365</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_food_cabinet|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S365" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R365)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T365" s="349" t="str">
+        <x:v>3f2bac0b240d54254a5b4f6691d1e04dfedea85475b7770bee48b19e93a4e2c7</x:v>
+      </x:c>
+      <x:c r="U365" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V365" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W365" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X365" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_food_cabinet；对象 9；中心 (-0.650, 13.872, 6.535)m；朝向 Blender +Y north；预期导出 loft_food_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366" ht="54" customHeight="1">
+      <x:c r="A366" t="str">
+        <x:v>BPK-BASE99-LOFT-GOOD-VIBES-NEON</x:v>
+      </x:c>
+      <x:c r="B366" t="str">
+        <x:v>基地99层 · GOOD VIBES霓虹</x:v>
+      </x:c>
+      <x:c r="C366" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D366" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E366" t="str">
+        <x:v>base99_package_loft_good_vibes_neon</x:v>
+      </x:c>
+      <x:c r="F366" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G366" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H366" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I366" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J366" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K366" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L366" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M366" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N366" s="349" t="str">
+        <x:v>包络 1.580×0.915×0.840m；15 网格；3 灯</x:v>
+      </x:c>
+      <x:c r="O366" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_good_vibes_neon/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P366" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q366" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_good_vibes_neon;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R366" s="349" t="str">
+        <x:f>C366&amp;"|"&amp;D366&amp;"|"&amp;E366&amp;"|"&amp;F366&amp;"|"&amp;LOWER(H366)&amp;"|"&amp;I366</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_good_vibes_neon|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S366" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R366)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T366" s="349" t="str">
+        <x:v>b94d3724faa9216d9a5f3e7774395683d54a573a8bc1c114cbf37a914bfc7554</x:v>
+      </x:c>
+      <x:c r="U366" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V366" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W366" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X366" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_good_vibes_neon；对象 18；中心 (10.550, 14.297, 8.480)m；朝向 Blender +Y north；预期导出 loft_good_vibes_neon_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367" ht="54" customHeight="1">
+      <x:c r="A367" t="str">
+        <x:v>BPK-BASE99-LOFT-HANGING-PLANT</x:v>
+      </x:c>
+      <x:c r="B367" t="str">
+        <x:v>基地99层 · 后墙吊挂植物</x:v>
+      </x:c>
+      <x:c r="C367" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D367" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E367" t="str">
+        <x:v>base99_package_loft_hanging_plant</x:v>
+      </x:c>
+      <x:c r="F367" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G367" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H367" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I367" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J367" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K367" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L367" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M367" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N367" s="349" t="str">
+        <x:v>包络 0.606×0.503×1.649m；12 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O367" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_hanging_plant/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P367" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q367" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_hanging_plant;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R367" s="349" t="str">
+        <x:f>C367&amp;"|"&amp;D367&amp;"|"&amp;E367&amp;"|"&amp;F367&amp;"|"&amp;LOWER(H367)&amp;"|"&amp;I367</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_hanging_plant|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S367" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R367)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T367" s="349" t="str">
+        <x:v>a76f5086eeab2510781ac2356968ca855ed7a31274dcb5b90d5a4a8bff7b430f</x:v>
+      </x:c>
+      <x:c r="U367" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V367" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W367" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X367" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_hanging_plant；对象 12；中心 (2.724, 14.150, 8.135)m；朝向 Blender +Y north；预期导出 loft_hanging_plant_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368" ht="54" customHeight="1">
+      <x:c r="A368" t="str">
+        <x:v>BPK-BASE99-LOFT-LOUNGE-RUG</x:v>
+      </x:c>
+      <x:c r="B368" t="str">
+        <x:v>基地99层 · 休闲区低饱和地毯</x:v>
+      </x:c>
+      <x:c r="C368" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D368" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E368" t="str">
+        <x:v>base99_package_loft_lounge_rug</x:v>
+      </x:c>
+      <x:c r="F368" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G368" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H368" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I368" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J368" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K368" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L368" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M368" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N368" s="349" t="str">
+        <x:v>包络 4.900×2.450×0.056m；7 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O368" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_lounge_rug/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P368" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q368" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_lounge_rug;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R368" s="349" t="str">
+        <x:f>C368&amp;"|"&amp;D368&amp;"|"&amp;E368&amp;"|"&amp;F368&amp;"|"&amp;LOWER(H368)&amp;"|"&amp;I368</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_lounge_rug|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S368" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R368)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T368" s="349" t="str">
+        <x:v>9bf45be673d85e4a8e0a61dc0d370bfc22e20331fdd4b4b04a4f44a90702b0b4</x:v>
+      </x:c>
+      <x:c r="U368" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V368" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W368" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X368" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_lounge_rug；对象 7；中心 (6.180, 9.550, 6.092)m；朝向 Blender +Y north；预期导出 loft_lounge_rug_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369" ht="54" customHeight="1">
+      <x:c r="A369" t="str">
+        <x:v>BPK-BASE99-LOFT-LOUNGE-SOFA</x:v>
+      </x:c>
+      <x:c r="B369" t="str">
+        <x:v>基地99层 · 墨绿三人休闲沙发</x:v>
+      </x:c>
+      <x:c r="C369" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D369" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E369" t="str">
+        <x:v>base99_package_loft_lounge_sofa</x:v>
+      </x:c>
+      <x:c r="F369" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G369" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H369" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I369" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J369" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K369" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L369" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M369" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N369" s="349" t="str">
+        <x:v>包络 4.820×1.890×1.844m；35 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O369" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_lounge_sofa/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P369" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q369" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_lounge_sofa;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R369" s="349" t="str">
+        <x:f>C369&amp;"|"&amp;D369&amp;"|"&amp;E369&amp;"|"&amp;F369&amp;"|"&amp;LOWER(H369)&amp;"|"&amp;I369</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_lounge_sofa|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S369" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R369)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T369" s="349" t="str">
+        <x:v>64f2651594439cf2411aa14011398b78e868084d520d0cc28f3dd476c44130b1</x:v>
+      </x:c>
+      <x:c r="U369" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V369" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W369" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X369" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_lounge_sofa；对象 35；中心 (6.250, 12.085, 7.012)m；朝向 Blender +Y north；预期导出 loft_lounge_sofa_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370" ht="54" customHeight="1">
+      <x:c r="A370" t="str">
+        <x:v>BPK-BASE99-LOFT-MEDICAL-CABINET</x:v>
+      </x:c>
+      <x:c r="B370" t="str">
+        <x:v>基地99层 · MEDICAL模块收纳箱</x:v>
+      </x:c>
+      <x:c r="C370" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D370" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E370" t="str">
+        <x:v>base99_package_loft_medical_cabinet</x:v>
+      </x:c>
+      <x:c r="F370" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G370" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H370" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I370" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J370" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K370" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L370" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M370" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N370" s="349" t="str">
+        <x:v>包络 1.200×0.979×0.850m；9 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O370" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_medical_cabinet/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P370" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q370" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_medical_cabinet;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R370" s="349" t="str">
+        <x:f>C370&amp;"|"&amp;D370&amp;"|"&amp;E370&amp;"|"&amp;F370&amp;"|"&amp;LOWER(H370)&amp;"|"&amp;I370</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_medical_cabinet|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S370" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R370)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T370" s="349" t="str">
+        <x:v>1311552bd04b13fe297cf652e06262f7ad83612279134b81478d2d226141b036</x:v>
+      </x:c>
+      <x:c r="U370" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V370" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W370" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X370" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_medical_cabinet；对象 9；中心 (-3.250, 13.881, 6.545)m；朝向 Blender +Y north；预期导出 loft_medical_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" ht="54" customHeight="1">
+      <x:c r="A371" t="str">
+        <x:v>BPK-BASE99-LOFT-NIGHTSTAND</x:v>
+      </x:c>
+      <x:c r="B371" t="str">
+        <x:v>基地99层 · 参考床头柜与生活物件</x:v>
+      </x:c>
+      <x:c r="C371" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D371" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E371" t="str">
+        <x:v>base99_package_loft_nightstand</x:v>
+      </x:c>
+      <x:c r="F371" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G371" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H371" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I371" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J371" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K371" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L371" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M371" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N371" s="349" t="str">
+        <x:v>包络 1.100×1.060×1.465m；10 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O371" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_nightstand/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P371" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q371" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_nightstand;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R371" s="349" t="str">
+        <x:f>C371&amp;"|"&amp;D371&amp;"|"&amp;E371&amp;"|"&amp;F371&amp;"|"&amp;LOWER(H371)&amp;"|"&amp;I371</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_nightstand|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S371" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R371)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T371" s="349" t="str">
+        <x:v>444cf2e125c082b9f1e192c4e36638fa6ff5179ce64e391bedb2f30740dcdab9</x:v>
+      </x:c>
+      <x:c r="U371" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V371" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W371" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X371" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_nightstand；对象 10；中心 (-2.750, 11.320, 6.848)m；朝向 Blender +Y north；预期导出 loft_nightstand_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372" ht="54" customHeight="1">
+      <x:c r="A372" t="str">
+        <x:v>BPK-BASE99-LOFT-OFFICE-CHAIR</x:v>
+      </x:c>
+      <x:c r="B372" t="str">
+        <x:v>基地99层 · 带扶手办公椅</x:v>
+      </x:c>
+      <x:c r="C372" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D372" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E372" t="str">
+        <x:v>base99_package_loft_office_chair</x:v>
+      </x:c>
+      <x:c r="F372" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G372" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H372" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I372" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J372" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K372" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L372" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M372" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N372" s="349" t="str">
+        <x:v>包络 1.280×1.127×2.021m；18 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O372" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_office_chair/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P372" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q372" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_office_chair;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R372" s="349" t="str">
+        <x:f>C372&amp;"|"&amp;D372&amp;"|"&amp;E372&amp;"|"&amp;F372&amp;"|"&amp;LOWER(H372)&amp;"|"&amp;I372</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_office_chair|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S372" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R372)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T372" s="349" t="str">
+        <x:v>bbb9a18203bbc0cf555ab09bd88734aa4f4da837a31849bc6f8d4f60be0e787e</x:v>
+      </x:c>
+      <x:c r="U372" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V372" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W372" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X372" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_office_chair；对象 18；中心 (10.450, 12.259, 7.132)m；朝向 Blender +Y north；预期导出 loft_office_chair_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373" ht="54" customHeight="1">
+      <x:c r="A373" t="str">
+        <x:v>BPK-BASE99-LOFT-POUF-01</x:v>
+      </x:c>
+      <x:c r="B373" t="str">
+        <x:v>基地99层 · 青绿圆形坐墩01</x:v>
+      </x:c>
+      <x:c r="C373" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D373" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E373" t="str">
+        <x:v>base99_package_loft_pouf_01</x:v>
+      </x:c>
+      <x:c r="F373" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G373" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H373" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I373" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J373" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K373" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L373" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M373" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N373" s="349" t="str">
+        <x:v>包络 0.880×0.880×0.570m；3 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O373" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_pouf_01/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P373" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q373" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_pouf_01;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R373" s="349" t="str">
+        <x:f>C373&amp;"|"&amp;D373&amp;"|"&amp;E373&amp;"|"&amp;F373&amp;"|"&amp;LOWER(H373)&amp;"|"&amp;I373</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_pouf_01|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S373" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R373)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T373" s="349" t="str">
+        <x:v>410696ebbbc7cc3ad5269487a9a44a6fe5380a560c4113be6aa0ee9908aae219</x:v>
+      </x:c>
+      <x:c r="U373" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V373" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W373" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X373" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_pouf_01；对象 3；中心 (3.780, 8.550, 6.460)m；朝向 Blender +Y north；预期导出 loft_pouf_01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" ht="54" customHeight="1">
+      <x:c r="A374" t="str">
+        <x:v>BPK-BASE99-LOFT-POUF-02</x:v>
+      </x:c>
+      <x:c r="B374" t="str">
+        <x:v>基地99层 · 深绿圆形坐墩02</x:v>
+      </x:c>
+      <x:c r="C374" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D374" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E374" t="str">
+        <x:v>base99_package_loft_pouf_02</x:v>
+      </x:c>
+      <x:c r="F374" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G374" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H374" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I374" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J374" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K374" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L374" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M374" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N374" s="349" t="str">
+        <x:v>包络 0.880×0.880×0.570m；3 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O374" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_pouf_02/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P374" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q374" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_pouf_02;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R374" s="349" t="str">
+        <x:f>C374&amp;"|"&amp;D374&amp;"|"&amp;E374&amp;"|"&amp;F374&amp;"|"&amp;LOWER(H374)&amp;"|"&amp;I374</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_pouf_02|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S374" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R374)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T374" s="349" t="str">
+        <x:v>31473d4ed82edd5b06fcdc2fd925b506a9ee6079d47d478452f560b218d0223b</x:v>
+      </x:c>
+      <x:c r="U374" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V374" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W374" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X374" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_pouf_02；对象 3；中心 (8.720, 8.620, 6.460)m；朝向 Blender +Y north；预期导出 loft_pouf_02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375" ht="54" customHeight="1">
+      <x:c r="A375" t="str">
+        <x:v>BPK-BASE99-LOFT-SIDE-TABLE</x:v>
+      </x:c>
+      <x:c r="B375" t="str">
+        <x:v>基地99层 · 床前辅助小桌</x:v>
+      </x:c>
+      <x:c r="C375" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D375" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E375" t="str">
+        <x:v>base99_package_loft_side_table</x:v>
+      </x:c>
+      <x:c r="F375" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G375" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H375" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I375" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J375" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K375" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L375" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M375" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N375" s="349" t="str">
+        <x:v>包络 1.120×0.760×0.765m；7 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O375" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_side_table/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P375" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q375" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_side_table;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R375" s="349" t="str">
+        <x:f>C375&amp;"|"&amp;D375&amp;"|"&amp;E375&amp;"|"&amp;F375&amp;"|"&amp;LOWER(H375)&amp;"|"&amp;I375</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_side_table|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S375" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R375)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T375" s="349" t="str">
+        <x:v>7195b627200aee96cc5ad1af2f20deacfaa4187178cf24e5c85e9ad5e382f8b4</x:v>
+      </x:c>
+      <x:c r="U375" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V375" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W375" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X375" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_side_table；对象 7；中心 (1.800, 9.220, 6.503)m；朝向 Blender +Y north；预期导出 loft_side_table_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" ht="54" customHeight="1">
+      <x:c r="A376" t="str">
+        <x:v>BPK-BASE99-LOFT-STAY-CURIOUS-NEON</x:v>
+      </x:c>
+      <x:c r="B376" t="str">
+        <x:v>基地99层 · STAY_CURIOUS楼梯墙标识</x:v>
+      </x:c>
+      <x:c r="C376" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D376" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E376" t="str">
+        <x:v>base99_package_loft_stay_curious_neon</x:v>
+      </x:c>
+      <x:c r="F376" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G376" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H376" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I376" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J376" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K376" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L376" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M376" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N376" s="349" t="str">
+        <x:v>包络 0.608×1.500×0.844m；2 网格；2 灯</x:v>
+      </x:c>
+      <x:c r="O376" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_stay_curious_neon/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P376" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q376" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_stay_curious_neon;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R376" s="349" t="str">
+        <x:f>C376&amp;"|"&amp;D376&amp;"|"&amp;E376&amp;"|"&amp;F376&amp;"|"&amp;LOWER(H376)&amp;"|"&amp;I376</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_stay_curious_neon|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S376" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R376)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T376" s="349" t="str">
+        <x:v>7126cd846635ae528b323245747413e5b6130dd2140ab9d0ddead50aaa7aa0be</x:v>
+      </x:c>
+      <x:c r="U376" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V376" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W376" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X376" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_stay_curious_neon；对象 4；中心 (-14.224, 11.020, 5.178)m；朝向 Blender +Y north；预期导出 loft_stay_curious_neon_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" ht="54" customHeight="1">
+      <x:c r="A377" t="str">
+        <x:v>BPK-BASE99-LOFT-STRIPED-PRIVACY-CURTAIN</x:v>
+      </x:c>
+      <x:c r="B377" t="str">
+        <x:v>基地99层 · 红紫条纹隔断帘</x:v>
+      </x:c>
+      <x:c r="C377" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D377" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E377" t="str">
+        <x:v>base99_package_loft_striped_privacy_curtain</x:v>
+      </x:c>
+      <x:c r="F377" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G377" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H377" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I377" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J377" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K377" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L377" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M377" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N377" s="349" t="str">
+        <x:v>包络 0.263×2.875×2.328m；29 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O377" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_striped_privacy_curtain/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P377" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q377" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_striped_privacy_curtain;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R377" s="349" t="str">
+        <x:f>C377&amp;"|"&amp;D377&amp;"|"&amp;E377&amp;"|"&amp;F377&amp;"|"&amp;LOWER(H377)&amp;"|"&amp;I377</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_striped_privacy_curtain|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S377" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R377)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T377" s="349" t="str">
+        <x:v>d1d3ab10ad5f640d1af0be677718403ebcedf45cc7d1ead355ff20f2f9019501</x:v>
+      </x:c>
+      <x:c r="U377" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V377" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W377" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X377" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_striped_privacy_curtain；对象 29；中心 (3.526, 12.297, 7.816)m；朝向 Blender +Y north；预期导出 loft_striped_privacy_curtain_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" ht="54" customHeight="1">
+      <x:c r="A378" t="str">
+        <x:v>BPK-BASE99-LOFT-TOOL-PEGBOARD</x:v>
+      </x:c>
+      <x:c r="B378" t="str">
+        <x:v>基地99层 · 工具洞洞板与固定工具</x:v>
+      </x:c>
+      <x:c r="C378" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D378" t="str">
+        <x:v>二楼/阁楼设施包</x:v>
+      </x:c>
+      <x:c r="E378" t="str">
+        <x:v>base99_package_loft_tool_pegboard</x:v>
+      </x:c>
+      <x:c r="F378" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G378" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H378" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I378" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J378" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K378" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L378" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M378" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N378" s="349" t="str">
+        <x:v>包络 2.550×0.177×1.340m；41 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O378" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_tool_pegboard/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P378" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q378" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;二楼/阁楼设施包;loft_tool_pegboard;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R378" s="349" t="str">
+        <x:f>C378&amp;"|"&amp;D378&amp;"|"&amp;E378&amp;"|"&amp;F378&amp;"|"&amp;LOWER(H378)&amp;"|"&amp;I378</x:f>
+        <x:v>基地资产包|二楼/阁楼设施包|base99_package_loft_tool_pegboard|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S378" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R378)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T378" s="349" t="str">
+        <x:v>c5ce8fa244331d60ca0efb66680f4ecd382aed050dabf38490f25d2f3adacfe9</x:v>
+      </x:c>
+      <x:c r="U378" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V378" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W378" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X378" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_tool_pegboard；对象 41；中心 (-0.150, 14.671, 8.050)m；朝向 Blender +Y north；预期导出 loft_tool_pegboard_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" ht="54" customHeight="1">
+      <x:c r="A379" t="str">
+        <x:v>BPK-BASE99-CORRIDOR-EMERGENCY-LIGHT-GROUP</x:v>
+      </x:c>
+      <x:c r="B379" t="str">
+        <x:v>基地99层 · 主通道应急灯组</x:v>
+      </x:c>
+      <x:c r="C379" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D379" t="str">
+        <x:v>环境支持包</x:v>
+      </x:c>
+      <x:c r="E379" t="str">
+        <x:v>base99_package_corridor_emergency_light_group</x:v>
+      </x:c>
+      <x:c r="F379" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G379" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H379" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I379" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J379" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K379" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L379" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M379" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N379" s="349" t="str">
+        <x:v>包络 27.820×0.750×0.320m；2 网格；2 灯</x:v>
+      </x:c>
+      <x:c r="O379" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/support/corridor_emergency_light_group/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P379" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q379" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;环境支持包;corridor_emergency_light_group;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R379" s="349" t="str">
+        <x:f>C379&amp;"|"&amp;D379&amp;"|"&amp;E379&amp;"|"&amp;F379&amp;"|"&amp;LOWER(H379)&amp;"|"&amp;I379</x:f>
+        <x:v>基地资产包|环境支持包|base99_package_corridor_emergency_light_group|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S379" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R379)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T379" s="349" t="str">
+        <x:v>cecec84af463ca449d42a76e44a46602847f1d5ae3d3b0574aaae9e4533b27df</x:v>
+      </x:c>
+      <x:c r="U379" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V379" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W379" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X379" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::corridor_emergency_light_group；对象 4；中心 (0.000, 0.000, 2.200)m；朝向 Blender +Y north；预期导出 corridor_emergency_light_group_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" ht="54" customHeight="1">
+      <x:c r="A380" t="str">
+        <x:v>BPK-BASE99-EQUIPMENT-STEAM-FX</x:v>
+      </x:c>
+      <x:c r="B380" t="str">
+        <x:v>基地99层 · 设备蒸汽动效组</x:v>
+      </x:c>
+      <x:c r="C380" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D380" t="str">
+        <x:v>环境支持包</x:v>
+      </x:c>
+      <x:c r="E380" t="str">
+        <x:v>base99_package_equipment_steam_fx</x:v>
+      </x:c>
+      <x:c r="F380" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G380" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H380" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I380" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J380" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K380" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L380" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M380" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N380" s="349" t="str">
+        <x:v>包络 18.064×2.326×1.133m；10 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O380" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/support/equipment_steam_fx/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P380" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q380" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;环境支持包;equipment_steam_fx;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R380" s="349" t="str">
+        <x:f>C380&amp;"|"&amp;D380&amp;"|"&amp;E380&amp;"|"&amp;F380&amp;"|"&amp;LOWER(H380)&amp;"|"&amp;I380</x:f>
+        <x:v>基地资产包|环境支持包|base99_package_equipment_steam_fx|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S380" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R380)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T380" s="349" t="str">
+        <x:v>8ebab144bcd1f2f8a3756eb4d2c384244b5e3606b52841b744c18c646c7613c5</x:v>
+      </x:c>
+      <x:c r="U380" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V380" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W380" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X380" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::equipment_steam_fx；对象 10；中心 (0.168, -10.450, 3.142)m；朝向 Blender +Y north；预期导出 equipment_steam_fx_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" ht="54" customHeight="1">
+      <x:c r="A381" t="str">
+        <x:v>BPK-BASE99-LOFT-LIGHTING-SUPPORT</x:v>
+      </x:c>
+      <x:c r="B381" t="str">
+        <x:v>基地99层 · 二楼分层照明支持</x:v>
+      </x:c>
+      <x:c r="C381" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D381" t="str">
+        <x:v>环境支持包</x:v>
+      </x:c>
+      <x:c r="E381" t="str">
+        <x:v>base99_package_loft_lighting_support</x:v>
+      </x:c>
+      <x:c r="F381" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G381" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H381" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I381" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J381" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K381" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L381" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M381" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N381" s="349" t="str">
+        <x:v>包络 18.321×9.467×5.292m；8 网格；4 灯</x:v>
+      </x:c>
+      <x:c r="O381" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/support/loft_lighting_support/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P381" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q381" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;环境支持包;loft_lighting_support;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R381" s="349" t="str">
+        <x:f>C381&amp;"|"&amp;D381&amp;"|"&amp;E381&amp;"|"&amp;F381&amp;"|"&amp;LOWER(H381)&amp;"|"&amp;I381</x:f>
+        <x:v>基地资产包|环境支持包|base99_package_loft_lighting_support|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S381" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R381)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T381" s="349" t="str">
+        <x:v>c52f581b50aed742ff9cf9567a2188a81024eaadc4f94c98b2b3f178d527a2cf</x:v>
+      </x:c>
+      <x:c r="U381" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V381" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W381" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X381" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_lighting_support；对象 12；中心 (2.961, 9.986, 8.854)m；朝向 Blender +Y north；预期导出 loft_lighting_support_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" ht="54" customHeight="1">
+      <x:c r="A382" t="str">
+        <x:v>BPK-BASE99-VOLUMETRIC-DUST-FX</x:v>
+      </x:c>
+      <x:c r="B382" t="str">
+        <x:v>基地99层 · 光束尘埃动效组</x:v>
+      </x:c>
+      <x:c r="C382" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D382" t="str">
+        <x:v>环境支持包</x:v>
+      </x:c>
+      <x:c r="E382" t="str">
+        <x:v>base99_package_volumetric_dust_fx</x:v>
+      </x:c>
+      <x:c r="F382" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G382" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H382" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I382" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J382" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K382" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L382" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M382" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N382" s="349" t="str">
+        <x:v>包络 23.750×12.014×6.494m；28 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O382" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/support/volumetric_dust_fx/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P382" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q382" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;环境支持包;volumetric_dust_fx;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R382" s="349" t="str">
+        <x:f>C382&amp;"|"&amp;D382&amp;"|"&amp;E382&amp;"|"&amp;F382&amp;"|"&amp;LOWER(H382)&amp;"|"&amp;I382</x:f>
+        <x:v>基地资产包|环境支持包|base99_package_volumetric_dust_fx|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S382" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R382)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T382" s="349" t="str">
+        <x:v>a45cf20c8f73d8fd4d9ea37e05078d6963f31cc6efc873445af2b6c87b8e51b8</x:v>
+      </x:c>
+      <x:c r="U382" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V382" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W382" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X382" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::volumetric_dust_fx；对象 28；中心 (0.204, -0.015, 4.725)m；朝向 Blender +Y north；预期导出 volumetric_dust_fx_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" ht="54" customHeight="1">
+      <x:c r="A383" t="str">
+        <x:v>BPK-BASE99-WAREHOUSE-PENDANT-LIGHT-GROUP</x:v>
+      </x:c>
+      <x:c r="B383" t="str">
+        <x:v>基地99层 · 仓库防爆吊灯组</x:v>
+      </x:c>
+      <x:c r="C383" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D383" t="str">
+        <x:v>环境支持包</x:v>
+      </x:c>
+      <x:c r="E383" t="str">
+        <x:v>base99_package_warehouse_pendant_light_group</x:v>
+      </x:c>
+      <x:c r="F383" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G383" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H383" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I383" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J383" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K383" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L383" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M383" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N383" s="349" t="str">
+        <x:v>包络 21.242×8.043×1.220m；15 网格；5 灯</x:v>
+      </x:c>
+      <x:c r="O383" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/support/warehouse_pendant_light_group/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P383" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q383" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;环境支持包;warehouse_pendant_light_group;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R383" s="349" t="str">
+        <x:f>C383&amp;"|"&amp;D383&amp;"|"&amp;E383&amp;"|"&amp;F383&amp;"|"&amp;LOWER(H383)&amp;"|"&amp;I383</x:f>
+        <x:v>基地资产包|环境支持包|base99_package_warehouse_pendant_light_group|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S383" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R383)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T383" s="349" t="str">
+        <x:v>de64c5243679d4acbdae7545808d2233871703cadcc529a5c3bfd62826476689</x:v>
+      </x:c>
+      <x:c r="U383" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V383" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W383" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X383" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::warehouse_pendant_light_group；对象 25；中心 (0.005, 0.008, 7.490)m；朝向 Blender +Y north；预期导出 warehouse_pendant_light_group_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" ht="54" customHeight="1">
+      <x:c r="A384" t="str">
+        <x:v>BPK-BASE99-ACCESS-TERMINAL</x:v>
+      </x:c>
+      <x:c r="B384" t="str">
+        <x:v>基地99层 · ACCESS门禁终端</x:v>
+      </x:c>
+      <x:c r="C384" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D384" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E384" t="str">
+        <x:v>base99_package_access_terminal</x:v>
+      </x:c>
+      <x:c r="F384" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G384" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H384" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I384" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J384" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K384" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L384" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M384" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N384" s="349" t="str">
+        <x:v>包络 0.560×0.383×1.030m；9 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O384" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/access_terminal/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P384" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q384" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;access_terminal;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R384" s="349" t="str">
+        <x:f>C384&amp;"|"&amp;D384&amp;"|"&amp;E384&amp;"|"&amp;F384&amp;"|"&amp;LOWER(H384)&amp;"|"&amp;I384</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_access_terminal|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S384" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R384)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T384" s="349" t="str">
+        <x:v>84c73e295098a57bf4b0c606a9bc6f94654b6fbff4db25e16f44a530e8c71a76</x:v>
+      </x:c>
+      <x:c r="U384" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V384" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W384" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X384" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::access_terminal；对象 9；中心 (1.350, 4.309, 2.045)m；朝向 Blender +Y north；预期导出 access_terminal_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" ht="54" customHeight="1">
+      <x:c r="A385" t="str">
+        <x:v>BPK-BASE99-BASE-CAMP-NEON-SIGN</x:v>
+      </x:c>
+      <x:c r="B385" t="str">
+        <x:v>基地99层 · BASE_CAMP立体霓虹标识</x:v>
+      </x:c>
+      <x:c r="C385" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D385" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E385" t="str">
+        <x:v>base99_package_base_camp_neon_sign</x:v>
+      </x:c>
+      <x:c r="F385" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G385" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H385" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I385" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J385" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K385" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L385" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M385" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N385" s="349" t="str">
+        <x:v>包络 7.800×0.845×0.998m；17 网格；2 灯</x:v>
+      </x:c>
+      <x:c r="O385" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/base_camp_neon_sign/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P385" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q385" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;base_camp_neon_sign;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R385" s="349" t="str">
+        <x:f>C385&amp;"|"&amp;D385&amp;"|"&amp;E385&amp;"|"&amp;F385&amp;"|"&amp;LOWER(H385)&amp;"|"&amp;I385</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_base_camp_neon_sign|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S385" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R385)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T385" s="349" t="str">
+        <x:v>2ac4aa48342161d2d2bc1873e444044264dcf415363f0118c318e5892566edae</x:v>
+      </x:c>
+      <x:c r="U385" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V385" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W385" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X385" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::base_camp_neon_sign；对象 19；中心 (5.000, 4.603, 4.439)m；朝向 Blender +Y north；预期导出 base_camp_neon_sign_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" ht="54" customHeight="1">
+      <x:c r="A386" t="str">
+        <x:v>BPK-BASE99-BASE-CAMP-ROLLUP-MAIN-DOOR</x:v>
+      </x:c>
+      <x:c r="B386" t="str">
+        <x:v>基地99层 · BASE_CAMP大型卷帘主门</x:v>
+      </x:c>
+      <x:c r="C386" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D386" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E386" t="str">
+        <x:v>base99_package_base_camp_rollup_main_door</x:v>
+      </x:c>
+      <x:c r="F386" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G386" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H386" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I386" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J386" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K386" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L386" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M386" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N386" s="349" t="str">
+        <x:v>包络 6.440×0.910×2.920m；70 网格；1 灯</x:v>
+      </x:c>
+      <x:c r="O386" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/base_camp_rollup_main_door/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P386" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q386" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;base_camp_rollup_main_door;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R386" s="349" t="str">
+        <x:f>C386&amp;"|"&amp;D386&amp;"|"&amp;E386&amp;"|"&amp;F386&amp;"|"&amp;LOWER(H386)&amp;"|"&amp;I386</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_base_camp_rollup_main_door|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S386" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R386)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T386" s="349" t="str">
+        <x:v>c0f32239d47278c2f1977c8c79bfa4c7fbe1266223787b0b11f0fe837c595f29</x:v>
+      </x:c>
+      <x:c r="U386" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V386" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W386" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X386" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::base_camp_rollup_main_door；对象 71；中心 (5.070, 4.385, 2.340)m；朝向 Blender +Y north；预期导出 base_camp_rollup_main_door_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" ht="54" customHeight="1">
+      <x:c r="A387" t="str">
+        <x:v>BPK-BASE99-BASE-STATUS-TERMINAL</x:v>
+      </x:c>
+      <x:c r="B387" t="str">
+        <x:v>基地99层 · BASE_STATUS状态终端</x:v>
+      </x:c>
+      <x:c r="C387" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D387" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E387" t="str">
+        <x:v>base99_package_base_status_terminal</x:v>
+      </x:c>
+      <x:c r="F387" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G387" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H387" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I387" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J387" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K387" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L387" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M387" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N387" s="349" t="str">
+        <x:v>包络 0.620×0.520×0.940m；10 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O387" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/base_status_terminal/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P387" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q387" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;base_status_terminal;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R387" s="349" t="str">
+        <x:f>C387&amp;"|"&amp;D387&amp;"|"&amp;E387&amp;"|"&amp;F387&amp;"|"&amp;LOWER(H387)&amp;"|"&amp;I387</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_base_status_terminal|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S387" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R387)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T387" s="349" t="str">
+        <x:v>c3e5602c0e11fdfa610a67ca18968dc45026639e2e8a03ee67bc7897f2ccf643</x:v>
+      </x:c>
+      <x:c r="U387" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V387" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W387" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X387" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::base_status_terminal；对象 10；中心 (8.380, 3.580, 1.620)m；朝向 Blender +Y north；预期导出 base_status_terminal_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" ht="54" customHeight="1">
+      <x:c r="A388" t="str">
+        <x:v>BPK-BASE99-HOLOGRAM-TERMINAL-PLATFORM</x:v>
+      </x:c>
+      <x:c r="B388" t="str">
+        <x:v>基地99层 · 圆形全息设备平台</x:v>
+      </x:c>
+      <x:c r="C388" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D388" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E388" t="str">
+        <x:v>base99_package_hologram_terminal_platform</x:v>
+      </x:c>
+      <x:c r="F388" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G388" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H388" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I388" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J388" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K388" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L388" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M388" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N388" s="349" t="str">
+        <x:v>包络 2.409×2.409×1.825m；38 网格；1 灯</x:v>
+      </x:c>
+      <x:c r="O388" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/hologram_terminal_platform/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P388" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q388" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;hologram_terminal_platform;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R388" s="349" t="str">
+        <x:f>C388&amp;"|"&amp;D388&amp;"|"&amp;E388&amp;"|"&amp;F388&amp;"|"&amp;LOWER(H388)&amp;"|"&amp;I388</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_hologram_terminal_platform|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S388" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R388)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T388" s="349" t="str">
+        <x:v>b1eb729427faf4168fc13b6a32c05ba07cecd3dcab8eed1f2c7a97a4d2f30c55</x:v>
+      </x:c>
+      <x:c r="U388" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V388" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W388" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X388" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::hologram_terminal_platform；对象 39；中心 (5.000, 1.720, 0.952)m；朝向 Blender +Y north；预期导出 hologram_terminal_platform_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" ht="54" customHeight="1">
+      <x:c r="A389" t="str">
+        <x:v>BPK-BASE99-MAIN-DOOR-LOW-STORAGE-CABINET</x:v>
+      </x:c>
+      <x:c r="B389" t="str">
+        <x:v>基地99层 · 主门下方低矮设备柜</x:v>
+      </x:c>
+      <x:c r="C389" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D389" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E389" t="str">
+        <x:v>base99_package_main_door_low_storage_cabinet</x:v>
+      </x:c>
+      <x:c r="F389" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G389" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H389" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I389" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J389" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K389" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L389" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M389" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N389" s="349" t="str">
+        <x:v>包络 6.280×1.230×2.060m；31 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O389" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/main_door_low_storage_cabinet/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P389" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q389" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;main_door_low_storage_cabinet;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R389" s="349" t="str">
+        <x:f>C389&amp;"|"&amp;D389&amp;"|"&amp;E389&amp;"|"&amp;F389&amp;"|"&amp;LOWER(H389)&amp;"|"&amp;I389</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_main_door_low_storage_cabinet|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S389" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R389)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T389" s="349" t="str">
+        <x:v>a16a84b747c4d97e0e3017ae615753d652d2df297366fbb4c25c4780e75fe45d</x:v>
+      </x:c>
+      <x:c r="U389" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V389" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W389" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X389" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::main_door_low_storage_cabinet；对象 31；中心 (5.000, 3.955, 1.050)m；朝向 Blender +Y north；预期导出 main_door_low_storage_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" ht="54" customHeight="1">
+      <x:c r="A390" t="str">
+        <x:v>BPK-BASE99-MEDICAL-CABINET</x:v>
+      </x:c>
+      <x:c r="B390" t="str">
+        <x:v>基地99层 · MEDICAL医疗柜</x:v>
+      </x:c>
+      <x:c r="C390" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D390" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E390" t="str">
+        <x:v>base99_package_medical_cabinet</x:v>
+      </x:c>
+      <x:c r="F390" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G390" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H390" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I390" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J390" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K390" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L390" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M390" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N390" s="349" t="str">
+        <x:v>包络 1.580×0.973×3.330m；28 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O390" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/medical_cabinet/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P390" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q390" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;medical_cabinet;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R390" s="349" t="str">
+        <x:f>C390&amp;"|"&amp;D390&amp;"|"&amp;E390&amp;"|"&amp;F390&amp;"|"&amp;LOWER(H390)&amp;"|"&amp;I390</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_medical_cabinet|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S390" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R390)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T390" s="349" t="str">
+        <x:v>9c6e519f89e470c4b1f3aba1c856d869e9a9fb8feb456f0e946229d58f82f411</x:v>
+      </x:c>
+      <x:c r="U390" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V390" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W390" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X390" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::medical_cabinet；对象 28；中心 (-3.650, 4.333, 1.685)m；朝向 Blender +Y north；预期导出 medical_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" ht="54" customHeight="1">
+      <x:c r="A391" t="str">
+        <x:v>BPK-BASE99-NARROW-BATTERY-CABINET</x:v>
+      </x:c>
+      <x:c r="B391" t="str">
+        <x:v>基地99层 · 窄型电池柜</x:v>
+      </x:c>
+      <x:c r="C391" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D391" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E391" t="str">
+        <x:v>base99_package_narrow_battery_cabinet</x:v>
+      </x:c>
+      <x:c r="F391" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G391" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H391" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I391" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J391" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K391" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L391" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M391" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N391" s="349" t="str">
+        <x:v>包络 1.580×0.983×3.220m；23 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O391" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/narrow_battery_cabinet/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P391" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q391" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;narrow_battery_cabinet;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R391" s="349" t="str">
+        <x:f>C391&amp;"|"&amp;D391&amp;"|"&amp;E391&amp;"|"&amp;F391&amp;"|"&amp;LOWER(H391)&amp;"|"&amp;I391</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_narrow_battery_cabinet|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S391" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R391)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T391" s="349" t="str">
+        <x:v>6d4f355ae2f78209341d5886b593337db19e898b48d5eadbd3054f48a03bee92</x:v>
+      </x:c>
+      <x:c r="U391" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V391" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W391" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X391" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::narrow_battery_cabinet；对象 23；中心 (11.850, 4.329, 1.630)m；朝向 Blender +Y north；预期导出 narrow_battery_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" ht="54" customHeight="1">
+      <x:c r="A392" t="str">
+        <x:v>BPK-BASE99-NARROW-EMERGENCY-CABINET</x:v>
+      </x:c>
+      <x:c r="B392" t="str">
+        <x:v>基地99层 · 窄型应急柜</x:v>
+      </x:c>
+      <x:c r="C392" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D392" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E392" t="str">
+        <x:v>base99_package_narrow_emergency_cabinet</x:v>
+      </x:c>
+      <x:c r="F392" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G392" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H392" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I392" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J392" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K392" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L392" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M392" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N392" s="349" t="str">
+        <x:v>包络 1.580×0.985×3.220m；24 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O392" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/narrow_emergency_cabinet/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P392" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q392" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;narrow_emergency_cabinet;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R392" s="349" t="str">
+        <x:f>C392&amp;"|"&amp;D392&amp;"|"&amp;E392&amp;"|"&amp;F392&amp;"|"&amp;LOWER(H392)&amp;"|"&amp;I392</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_narrow_emergency_cabinet|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S392" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R392)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T392" s="349" t="str">
+        <x:v>9a5090522f7af48f0e7ac02ef3a52ea2225a292366d6a61cc98cafd159f5a192</x:v>
+      </x:c>
+      <x:c r="U392" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V392" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W392" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X392" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::narrow_emergency_cabinet；对象 24；中心 (13.650, 4.327, 1.630)m；朝向 Blender +Y north；预期导出 narrow_emergency_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" ht="54" customHeight="1">
+      <x:c r="A393" t="str">
+        <x:v>BPK-BASE99-SOUTH-INDUSTRIAL-WALL-DETAILS</x:v>
+      </x:c>
+      <x:c r="B393" t="str">
+        <x:v>基地99层 · 南墙工业墙板附着结构</x:v>
+      </x:c>
+      <x:c r="C393" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D393" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E393" t="str">
+        <x:v>base99_package_south_industrial_wall_details</x:v>
+      </x:c>
+      <x:c r="F393" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G393" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H393" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I393" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J393" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K393" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L393" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M393" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N393" s="349" t="str">
+        <x:v>包络 19.500×0.530×4.785m；53 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O393" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/south_industrial_wall_details/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P393" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q393" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;south_industrial_wall_details;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R393" s="349" t="str">
+        <x:f>C393&amp;"|"&amp;D393&amp;"|"&amp;E393&amp;"|"&amp;F393&amp;"|"&amp;LOWER(H393)&amp;"|"&amp;I393</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_south_industrial_wall_details|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S393" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R393)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T393" s="349" t="str">
+        <x:v>1c3a1bae26ffeab9adad29252b498b44d424d22fcc0522ec7eb6a797b9b67229</x:v>
+      </x:c>
+      <x:c r="U393" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V393" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W393" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X393" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::south_industrial_wall_details；对象 53；中心 (4.950, 4.845, 2.618)m；朝向 Blender +Y north；预期导出 south_industrial_wall_details_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" ht="54" customHeight="1">
+      <x:c r="A394" t="str">
+        <x:v>BPK-BASE99-SOUTH-UPPER-RAILING-DETAILS</x:v>
+      </x:c>
+      <x:c r="B394" t="str">
+        <x:v>基地99层 · 二层栏杆附着细节</x:v>
+      </x:c>
+      <x:c r="C394" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D394" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E394" t="str">
+        <x:v>base99_package_south_upper_railing_details</x:v>
+      </x:c>
+      <x:c r="F394" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G394" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H394" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I394" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J394" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K394" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L394" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M394" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N394" s="349" t="str">
+        <x:v>包络 18.500×0.443×0.783m；26 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O394" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/south_upper_railing_details/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P394" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q394" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;south_upper_railing_details;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R394" s="349" t="str">
+        <x:f>C394&amp;"|"&amp;D394&amp;"|"&amp;E394&amp;"|"&amp;F394&amp;"|"&amp;LOWER(H394)&amp;"|"&amp;I394</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_south_upper_railing_details|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S394" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R394)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T394" s="349" t="str">
+        <x:v>d08e3ac0f25926d4c7d405b3fb8b7503e5b6917b39c6ae1c16cd7e8d01984f09</x:v>
+      </x:c>
+      <x:c r="U394" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V394" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W394" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X394" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::south_upper_railing_details；对象 26；中心 (4.440, 5.069, 6.394)m；朝向 Blender +Y north；预期导出 south_upper_railing_details_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" ht="54" customHeight="1">
+      <x:c r="A395" t="str">
+        <x:v>BPK-BASE99-SOUTH-WALL-PIPELINE-SYSTEM</x:v>
+      </x:c>
+      <x:c r="B395" t="str">
+        <x:v>基地99层 · 南墙工业管线系统</x:v>
+      </x:c>
+      <x:c r="C395" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D395" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E395" t="str">
+        <x:v>base99_package_south_wall_pipeline_system</x:v>
+      </x:c>
+      <x:c r="F395" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G395" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H395" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I395" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J395" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K395" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L395" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M395" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N395" s="349" t="str">
+        <x:v>包络 18.600×0.580×4.950m；21 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O395" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/south_wall_pipeline_system/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P395" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q395" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;south_wall_pipeline_system;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R395" s="349" t="str">
+        <x:f>C395&amp;"|"&amp;D395&amp;"|"&amp;E395&amp;"|"&amp;F395&amp;"|"&amp;LOWER(H395)&amp;"|"&amp;I395</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_south_wall_pipeline_system|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S395" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R395)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T395" s="349" t="str">
+        <x:v>03172fdf43e8c4f7b0bc3d303ea4d0dcc4e2ad1e091d4738cfabc0a293060378</x:v>
+      </x:c>
+      <x:c r="U395" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V395" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W395" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X395" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::south_wall_pipeline_system；对象 21；中心 (5.000, 4.460, 2.845)m；朝向 Blender +Y north；预期导出 south_wall_pipeline_system_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" ht="54" customHeight="1">
+      <x:c r="A396" t="str">
+        <x:v>BPK-BASE99-STORAGE-TERMINAL</x:v>
+      </x:c>
+      <x:c r="B396" t="str">
+        <x:v>基地99层 · STORAGE储物终端</x:v>
+      </x:c>
+      <x:c r="C396" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D396" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E396" t="str">
+        <x:v>base99_package_storage_terminal</x:v>
+      </x:c>
+      <x:c r="F396" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G396" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H396" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I396" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J396" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K396" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L396" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M396" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N396" s="349" t="str">
+        <x:v>包络 0.560×0.383×1.030m；9 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O396" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/storage_terminal/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P396" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q396" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;storage_terminal;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R396" s="349" t="str">
+        <x:f>C396&amp;"|"&amp;D396&amp;"|"&amp;E396&amp;"|"&amp;F396&amp;"|"&amp;LOWER(H396)&amp;"|"&amp;I396</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_storage_terminal|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S396" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R396)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T396" s="349" t="str">
+        <x:v>e81b9e834cb3e3cda6f81182e905051f143fe4d8a95941ffe92a303c2e9fd318</x:v>
+      </x:c>
+      <x:c r="U396" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V396" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W396" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X396" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::storage_terminal；对象 9；中心 (-0.620, 4.279, 1.765)m；朝向 Blender +Y north；预期导出 storage_terminal_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" ht="54" customHeight="1">
+      <x:c r="A397" t="str">
+        <x:v>BPK-BASE99-TOOLS-CABINET</x:v>
+      </x:c>
+      <x:c r="B397" t="str">
+        <x:v>基地99层 · TOOLS工具柜</x:v>
+      </x:c>
+      <x:c r="C397" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D397" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E397" t="str">
+        <x:v>base99_package_tools_cabinet</x:v>
+      </x:c>
+      <x:c r="F397" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G397" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H397" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I397" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J397" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K397" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L397" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M397" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N397" s="349" t="str">
+        <x:v>包络 1.970×1.015×3.220m；25 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O397" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/tools_cabinet/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P397" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q397" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;tools_cabinet;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R397" s="349" t="str">
+        <x:f>C397&amp;"|"&amp;D397&amp;"|"&amp;E397&amp;"|"&amp;F397&amp;"|"&amp;LOWER(H397)&amp;"|"&amp;I397</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_tools_cabinet|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S397" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R397)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T397" s="349" t="str">
+        <x:v>543aa1776613f2279210bb9e1d179be48050412335b4be68c20988422d8bf50f</x:v>
+      </x:c>
+      <x:c r="U397" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V397" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W397" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X397" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tools_cabinet；对象 25；中心 (-1.655, 4.313, 1.630)m；朝向 Blender +Y north；预期导出 tools_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" ht="54" customHeight="1">
+      <x:c r="A398" t="str">
+        <x:v>BPK-BASE99-UNDERSTAIR-BULLETIN-BOARD</x:v>
+      </x:c>
+      <x:c r="B398" t="str">
+        <x:v>基地99层 · 梯下公告留言板</x:v>
+      </x:c>
+      <x:c r="C398" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D398" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E398" t="str">
+        <x:v>base99_package_understair_bulletin_board</x:v>
+      </x:c>
+      <x:c r="F398" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G398" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H398" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I398" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J398" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K398" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L398" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M398" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N398" s="349" t="str">
+        <x:v>包络 1.900×0.149×1.420m；1 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O398" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/understair_bulletin_board/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P398" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q398" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;understair_bulletin_board;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R398" s="349" t="str">
+        <x:f>C398&amp;"|"&amp;D398&amp;"|"&amp;E398&amp;"|"&amp;F398&amp;"|"&amp;LOWER(H398)&amp;"|"&amp;I398</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_understair_bulletin_board|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S398" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R398)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T398" s="349" t="str">
+        <x:v>4f5cc4b2f4604c0b9bd5e2c26a08d3837a50faa6195a902fadf914e317ffa4f5</x:v>
+      </x:c>
+      <x:c r="U398" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V398" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W398" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X398" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::understair_bulletin_board；对象 1；中心 (-10.920, 14.655, 2.250)m；朝向 Blender +Y north；预期导出 understair_bulletin_board_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" ht="54" customHeight="1">
+      <x:c r="A399" t="str">
+        <x:v>BPK-BASE99-UNDERSTAIR-EQUIPMENT-CABINET</x:v>
+      </x:c>
+      <x:c r="B399" t="str">
+        <x:v>基地99层 · 梯下立式设备柜</x:v>
+      </x:c>
+      <x:c r="C399" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D399" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E399" t="str">
+        <x:v>base99_package_understair_equipment_cabinet</x:v>
+      </x:c>
+      <x:c r="F399" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G399" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H399" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I399" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J399" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K399" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L399" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M399" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N399" s="349" t="str">
+        <x:v>包络 1.100×0.927×3.130m；3 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O399" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/understair_equipment_cabinet/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P399" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q399" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;understair_equipment_cabinet;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R399" s="349" t="str">
+        <x:f>C399&amp;"|"&amp;D399&amp;"|"&amp;E399&amp;"|"&amp;F399&amp;"|"&amp;LOWER(H399)&amp;"|"&amp;I399</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_understair_equipment_cabinet|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S399" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R399)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T399" s="349" t="str">
+        <x:v>40df72432d99584f49445d049d1ed7ba481f94d7d18fc764d560e633f5593720</x:v>
+      </x:c>
+      <x:c r="U399" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V399" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W399" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X399" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::understair_equipment_cabinet；对象 3；中心 (-6.820, 14.216, 1.565)m；朝向 Blender +Y north；预期导出 understair_equipment_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 source collider attached；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" ht="54" customHeight="1">
+      <x:c r="A400" t="str">
+        <x:v>BPK-BASE99-UNDERSTAIR-GREEN-BENCH</x:v>
+      </x:c>
+      <x:c r="B400" t="str">
+        <x:v>基地99层 · 梯下绿色软垫长凳</x:v>
+      </x:c>
+      <x:c r="C400" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D400" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E400" t="str">
+        <x:v>base99_package_understair_green_bench</x:v>
+      </x:c>
+      <x:c r="F400" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G400" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H400" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I400" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J400" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K400" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L400" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M400" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N400" s="349" t="str">
+        <x:v>包络 2.580×0.912×1.660m；2 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O400" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/understair_green_bench/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P400" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q400" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;understair_green_bench;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R400" s="349" t="str">
+        <x:f>C400&amp;"|"&amp;D400&amp;"|"&amp;E400&amp;"|"&amp;F400&amp;"|"&amp;LOWER(H400)&amp;"|"&amp;I400</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_understair_green_bench|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S400" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R400)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T400" s="349" t="str">
+        <x:v>8aec1c6114e2b1d6415d86371450bb3c734d217dc75c13495da2b4aba91db8f4</x:v>
+      </x:c>
+      <x:c r="U400" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V400" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W400" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X400" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::understair_green_bench；对象 2；中心 (-11.150, 14.154, 0.830)m；朝向 Blender +Y north；预期导出 understair_green_bench_visual_top3d_v001.glb；当前 not_exported；碰撞 source collider attached；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" ht="54" customHeight="1">
+      <x:c r="A401" t="str">
+        <x:v>BPK-BASE99-UNDERSTAIR-LIGHTING-LIVING-SUPPORT</x:v>
+      </x:c>
+      <x:c r="B401" t="str">
+        <x:v>基地99层 · 梯下暖光与生活点缀</x:v>
+      </x:c>
+      <x:c r="C401" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D401" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E401" t="str">
+        <x:v>base99_package_understair_lighting_living_support</x:v>
+      </x:c>
+      <x:c r="F401" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G401" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H401" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I401" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J401" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K401" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L401" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M401" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N401" s="349" t="str">
+        <x:v>包络 3.100×1.030×3.690m；3 网格；2 灯</x:v>
+      </x:c>
+      <x:c r="O401" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/understair_lighting_living_support/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P401" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q401" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;understair_lighting_living_support;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R401" s="349" t="str">
+        <x:f>C401&amp;"|"&amp;D401&amp;"|"&amp;E401&amp;"|"&amp;F401&amp;"|"&amp;LOWER(H401)&amp;"|"&amp;I401</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_understair_lighting_living_support|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S401" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R401)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T401" s="349" t="str">
+        <x:v>0bfb375054fc31ad9ceda6fb8fdbf7e1395d1f0b860121768c46afdb3a6a94d1</x:v>
+      </x:c>
+      <x:c r="U401" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V401" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W401" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X401" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::understair_lighting_living_support；对象 5；中心 (-8.800, 14.235, 1.845)m；朝向 Blender +Y north；预期导出 understair_lighting_living_support_visual_top3d_v001.glb；当前 not_exported；碰撞 source collider attached；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" ht="54" customHeight="1">
+      <x:c r="A402" t="str">
+        <x:v>BPK-BASE99-UNDERSTAIR-STORAGE-SHELF</x:v>
+      </x:c>
+      <x:c r="B402" t="str">
+        <x:v>基地99层 · 梯下层架与收纳</x:v>
+      </x:c>
+      <x:c r="C402" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D402" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E402" t="str">
+        <x:v>base99_package_understair_storage_shelf</x:v>
+      </x:c>
+      <x:c r="F402" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G402" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H402" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I402" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J402" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K402" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L402" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M402" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N402" s="349" t="str">
+        <x:v>包络 1.240×0.934×2.600m；2 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O402" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/understair_storage_shelf/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P402" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q402" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;understair_storage_shelf;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R402" s="349" t="str">
+        <x:f>C402&amp;"|"&amp;D402&amp;"|"&amp;E402&amp;"|"&amp;F402&amp;"|"&amp;LOWER(H402)&amp;"|"&amp;I402</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_understair_storage_shelf|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S402" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R402)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T402" s="349" t="str">
+        <x:v>07ceb970797ac439ce0ecdd91078112c20a02b14041f12d17296e50d17a7f3c4</x:v>
+      </x:c>
+      <x:c r="U402" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V402" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W402" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X402" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::understair_storage_shelf；对象 2；中心 (-8.580, 14.203, 1.300)m；朝向 Blender +Y north；预期导出 understair_storage_shelf_visual_top3d_v001.glb；当前 not_exported；碰撞 source collider attached；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" ht="54" customHeight="1">
+      <x:c r="A403" t="str">
+        <x:v>BPK-BASE99-WEAPON-WORKSHOP-STATION</x:v>
+      </x:c>
+      <x:c r="B403" t="str">
+        <x:v>基地99层 · 武器工作台与弹药附件</x:v>
+      </x:c>
+      <x:c r="C403" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D403" t="str">
+        <x:v>阁楼下方固定设施包</x:v>
+      </x:c>
+      <x:c r="E403" t="str">
+        <x:v>base99_package_weapon_workshop_station</x:v>
+      </x:c>
+      <x:c r="F403" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G403" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H403" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I403" t="str">
+        <x:v>static / fixture_light</x:v>
+      </x:c>
+      <x:c r="J403" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K403" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L403" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M403" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N403" s="349" t="str">
+        <x:v>包络 2.330×6.000×4.491m；12 网格；1 灯</x:v>
+      </x:c>
+      <x:c r="O403" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/underloft/weapon_workshop_station/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P403" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q403" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;阁楼下方固定设施包;weapon_workshop_station;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R403" s="349" t="str">
+        <x:f>C403&amp;"|"&amp;D403&amp;"|"&amp;E403&amp;"|"&amp;F403&amp;"|"&amp;LOWER(H403)&amp;"|"&amp;I403</x:f>
+        <x:v>基地资产包|阁楼下方固定设施包|base99_package_weapon_workshop_station|package_root|top3d / blender +y北|static / fixture_light</x:v>
+      </x:c>
+      <x:c r="S403" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R403)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T403" s="349" t="str">
+        <x:v>54bd41c8a807e19cf9f0689441981635f012e1ccaf1f12c811d3d2e9e25804c5</x:v>
+      </x:c>
+      <x:c r="U403" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V403" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W403" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X403" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::weapon_workshop_station；对象 13；中心 (-12.975, -3.400, 2.370)m；朝向 Blender +Y north；预期导出 weapon_workshop_station_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" ht="54" customHeight="1">
+      <x:c r="A404" t="str">
+        <x:v>BPK-BASE99-AIR-COMPRESSOR</x:v>
+      </x:c>
+      <x:c r="B404" t="str">
+        <x:v>基地99层 · 空气压缩机</x:v>
+      </x:c>
+      <x:c r="C404" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D404" t="str">
+        <x:v>仓库设施包</x:v>
+      </x:c>
+      <x:c r="E404" t="str">
+        <x:v>base99_package_air_compressor</x:v>
+      </x:c>
+      <x:c r="F404" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G404" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H404" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I404" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J404" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K404" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L404" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M404" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N404" s="349" t="str">
+        <x:v>包络 2.000×1.450×1.200m；2 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O404" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/warehouse/air_compressor/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P404" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q404" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;仓库设施包;air_compressor;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R404" s="349" t="str">
+        <x:f>C404&amp;"|"&amp;D404&amp;"|"&amp;E404&amp;"|"&amp;F404&amp;"|"&amp;LOWER(H404)&amp;"|"&amp;I404</x:f>
+        <x:v>基地资产包|仓库设施包|base99_package_air_compressor|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S404" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R404)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T404" s="349" t="str">
+        <x:v>a2803d7ba558baab5d23bbf2b8453259ca6f367475660a5db1c2fb4be27323c0</x:v>
+      </x:c>
+      <x:c r="U404" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V404" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W404" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X404" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::air_compressor；对象 2；中心 (-13.000, -1.550, 0.780)m；朝向 Blender +Y north；预期导出 air_compressor_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" ht="54" customHeight="1">
+      <x:c r="A405" t="str">
+        <x:v>BPK-BASE99-BACKUP-GENERATOR</x:v>
+      </x:c>
+      <x:c r="B405" t="str">
+        <x:v>基地99层 · 备用发电机</x:v>
+      </x:c>
+      <x:c r="C405" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D405" t="str">
+        <x:v>仓库设施包</x:v>
+      </x:c>
+      <x:c r="E405" t="str">
+        <x:v>base99_package_backup_generator</x:v>
+      </x:c>
+      <x:c r="F405" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G405" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H405" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I405" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J405" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K405" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L405" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M405" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N405" s="349" t="str">
+        <x:v>包络 2.325×3.100×1.655m；3 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O405" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/warehouse/backup_generator/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P405" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q405" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;仓库设施包;backup_generator;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R405" s="349" t="str">
+        <x:f>C405&amp;"|"&amp;D405&amp;"|"&amp;E405&amp;"|"&amp;F405&amp;"|"&amp;LOWER(H405)&amp;"|"&amp;I405</x:f>
+        <x:v>基地资产包|仓库设施包|base99_package_backup_generator|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S405" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R405)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T405" s="349" t="str">
+        <x:v>d958a816a983dec19f9a121f96cb050a3fc39fb83778dd670491969e73b9b03e</x:v>
+      </x:c>
+      <x:c r="U405" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V405" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W405" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X405" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::backup_generator；对象 3；中心 (13.162, -9.100, 0.953)m；朝向 Blender +Y north；预期导出 backup_generator_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" ht="54" customHeight="1">
+      <x:c r="A406" t="str">
+        <x:v>BPK-BASE99-BATTERY-BANK</x:v>
+      </x:c>
+      <x:c r="B406" t="str">
+        <x:v>基地99层 · 蓄电池组</x:v>
+      </x:c>
+      <x:c r="C406" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D406" t="str">
+        <x:v>仓库设施包</x:v>
+      </x:c>
+      <x:c r="E406" t="str">
+        <x:v>base99_package_battery_bank</x:v>
+      </x:c>
+      <x:c r="F406" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G406" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H406" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I406" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J406" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K406" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L406" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M406" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N406" s="349" t="str">
+        <x:v>包络 1.320×2.280×0.820m；6 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O406" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/warehouse/battery_bank/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P406" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q406" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;仓库设施包;battery_bank;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R406" s="349" t="str">
+        <x:f>C406&amp;"|"&amp;D406&amp;"|"&amp;E406&amp;"|"&amp;F406&amp;"|"&amp;LOWER(H406)&amp;"|"&amp;I406</x:f>
+        <x:v>基地资产包|仓库设施包|base99_package_battery_bank|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S406" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R406)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T406" s="349" t="str">
+        <x:v>2472c6e24341f034f65fb178a1dc03ad9b99e134a1af4e8c44a851e1d0c9ec48</x:v>
+      </x:c>
+      <x:c r="U406" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V406" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W406" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X406" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::battery_bank；对象 6；中心 (12.865, -12.120, 0.520)m；朝向 Blender +Y north；预期导出 battery_bank_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" ht="54" customHeight="1">
+      <x:c r="A407" t="str">
+        <x:v>BPK-BASE99-HEAVY-SUPPLY-SHELF</x:v>
+      </x:c>
+      <x:c r="B407" t="str">
+        <x:v>基地99层 · 重型货架与补给箱</x:v>
+      </x:c>
+      <x:c r="C407" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D407" t="str">
+        <x:v>仓库设施包</x:v>
+      </x:c>
+      <x:c r="E407" t="str">
+        <x:v>base99_package_heavy_supply_shelf</x:v>
+      </x:c>
+      <x:c r="F407" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G407" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H407" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I407" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J407" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K407" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L407" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M407" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N407" s="349" t="str">
+        <x:v>包络 5.340×0.820×3.640m；22 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O407" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/warehouse/heavy_supply_shelf/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P407" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q407" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;仓库设施包;heavy_supply_shelf;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R407" s="349" t="str">
+        <x:f>C407&amp;"|"&amp;D407&amp;"|"&amp;E407&amp;"|"&amp;F407&amp;"|"&amp;LOWER(H407)&amp;"|"&amp;I407</x:f>
+        <x:v>基地资产包|仓库设施包|base99_package_heavy_supply_shelf|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S407" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R407)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T407" s="349" t="str">
+        <x:v>185fcbce3e743c73d82ee94ff345f58879aac5b767a29e06e43d2d7ec8d7332c</x:v>
+      </x:c>
+      <x:c r="U407" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V407" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W407" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X407" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::heavy_supply_shelf；对象 22；中心 (-10.800, -13.550, 1.820)m；朝向 Blender +Y north；预期导出 heavy_supply_shelf_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" ht="54" customHeight="1">
+      <x:c r="A408" t="str">
+        <x:v>BPK-BASE99-HOSE-REEL</x:v>
+      </x:c>
+      <x:c r="B408" t="str">
+        <x:v>基地99层 · 水管卷盘</x:v>
+      </x:c>
+      <x:c r="C408" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D408" t="str">
+        <x:v>仓库设施包</x:v>
+      </x:c>
+      <x:c r="E408" t="str">
+        <x:v>base99_package_hose_reel</x:v>
+      </x:c>
+      <x:c r="F408" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G408" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H408" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I408" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J408" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K408" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L408" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M408" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N408" s="349" t="str">
+        <x:v>包络 1.240×0.250×1.240m；1 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O408" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/warehouse/hose_reel/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P408" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q408" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;仓库设施包;hose_reel;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R408" s="349" t="str">
+        <x:f>C408&amp;"|"&amp;D408&amp;"|"&amp;E408&amp;"|"&amp;F408&amp;"|"&amp;LOWER(H408)&amp;"|"&amp;I408</x:f>
+        <x:v>基地资产包|仓库设施包|base99_package_hose_reel|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S408" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R408)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T408" s="349" t="str">
+        <x:v>4a7f78ea56b56e29bcce1dde3bb2d0c65a841e81c143cb74b55f999d5057c8c8</x:v>
+      </x:c>
+      <x:c r="U408" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V408" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W408" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X408" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::hose_reel；对象 1；中心 (-14.050, -10.600, 2.650)m；朝向 Blender +Y north；预期导出 hose_reel_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" ht="54" customHeight="1">
+      <x:c r="A409" t="str">
+        <x:v>BPK-BASE99-INDUSTRIAL-WATER-TANK</x:v>
+      </x:c>
+      <x:c r="B409" t="str">
+        <x:v>基地99层 · 工业水箱</x:v>
+      </x:c>
+      <x:c r="C409" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D409" t="str">
+        <x:v>仓库设施包</x:v>
+      </x:c>
+      <x:c r="E409" t="str">
+        <x:v>base99_package_industrial_water_tank</x:v>
+      </x:c>
+      <x:c r="F409" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G409" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H409" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I409" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J409" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K409" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L409" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M409" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N409" s="349" t="str">
+        <x:v>包络 2.000×2.000×2.550m；1 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O409" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/warehouse/industrial_water_tank/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P409" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q409" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;仓库设施包;industrial_water_tank;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R409" s="349" t="str">
+        <x:f>C409&amp;"|"&amp;D409&amp;"|"&amp;E409&amp;"|"&amp;F409&amp;"|"&amp;LOWER(H409)&amp;"|"&amp;I409</x:f>
+        <x:v>基地资产包|仓库设施包|base99_package_industrial_water_tank|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S409" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R409)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T409" s="349" t="str">
+        <x:v>c133e666268b455d5132220eb5857310f3dea4ef114c4496fa7a08e56e284738</x:v>
+      </x:c>
+      <x:c r="U409" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V409" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W409" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X409" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::industrial_water_tank；对象 1；中心 (-13.150, -7.700, 1.350)m；朝向 Blender +Y north；预期导出 industrial_water_tank_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" ht="54" customHeight="1">
+      <x:c r="A410" t="str">
+        <x:v>BPK-BASE99-SOUTH-WALL-INFORMATION-BOARDS</x:v>
+      </x:c>
+      <x:c r="B410" t="str">
+        <x:v>基地99层 · 南墙资料板组</x:v>
+      </x:c>
+      <x:c r="C410" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D410" t="str">
+        <x:v>仓库设施包</x:v>
+      </x:c>
+      <x:c r="E410" t="str">
+        <x:v>base99_package_south_wall_information_boards</x:v>
+      </x:c>
+      <x:c r="F410" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G410" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H410" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I410" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J410" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K410" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L410" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M410" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N410" s="349" t="str">
+        <x:v>包络 16.200×0.200×1.300m；6 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O410" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/warehouse/south_wall_information_boards/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P410" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q410" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;仓库设施包;south_wall_information_boards;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R410" s="349" t="str">
+        <x:f>C410&amp;"|"&amp;D410&amp;"|"&amp;E410&amp;"|"&amp;F410&amp;"|"&amp;LOWER(H410)&amp;"|"&amp;I410</x:f>
+        <x:v>基地资产包|仓库设施包|base99_package_south_wall_information_boards|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S410" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R410)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T410" s="349" t="str">
+        <x:v>d0f70e0eb43fe077fdf49b7d262b825bfbd064defcd8121df94d0b86dab5da0b</x:v>
+      </x:c>
+      <x:c r="U410" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V410" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W410" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X410" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::south_wall_information_boards；对象 6；中心 (2.400, -14.510, 4.650)m；朝向 Blender +Y north；预期导出 south_wall_information_boards_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" ht="54" customHeight="1">
+      <x:c r="A411" t="str">
+        <x:v>BPK-BASE99-WATER-PURIFIER</x:v>
+      </x:c>
+      <x:c r="B411" t="str">
+        <x:v>基地99层 · 净水器</x:v>
+      </x:c>
+      <x:c r="C411" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D411" t="str">
+        <x:v>仓库设施包</x:v>
+      </x:c>
+      <x:c r="E411" t="str">
+        <x:v>base99_package_water_purifier</x:v>
+      </x:c>
+      <x:c r="F411" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G411" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H411" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I411" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J411" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K411" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L411" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M411" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N411" s="349" t="str">
+        <x:v>包络 1.992×1.500×2.450m；3 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O411" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/warehouse/water_purifier/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P411" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q411" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;仓库设施包;water_purifier;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R411" s="349" t="str">
+        <x:f>C411&amp;"|"&amp;D411&amp;"|"&amp;E411&amp;"|"&amp;F411&amp;"|"&amp;LOWER(H411)&amp;"|"&amp;I411</x:f>
+        <x:v>基地资产包|仓库设施包|base99_package_water_purifier|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S411" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$411,R411)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T411" s="349" t="str">
+        <x:v>ebf0d4ae0c14ccc2a6c23a55cc62e8c9a1c1879bfb18dfdffcd4bbca2a33381a</x:v>
+      </x:c>
+      <x:c r="U411" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V411" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W411" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X411" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::water_purifier；对象 3；中心 (-12.979, -4.900, 1.300)m；朝向 Blender +Y north；预期导出 water_purifier_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:X2"/>
@@ -43026,7 +51386,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5175f4ed2bbf498b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c26cbbf1fdf4fdb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48281,6 +56641,36 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="15" ht="48" customHeight="1">
+      <x:c r="A15" s="349" t="str">
+        <x:v>BPK</x:v>
+      </x:c>
+      <x:c r="B15" s="349" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="C15" s="349" t="str">
+        <x:v>建筑结构包 / 地面系统包 / 东侧固定设施包 / 二楼阁楼设施包 / 阁楼下方固定设施包 / 仓库设施包 / 环境支持包</x:v>
+      </x:c>
+      <x:c r="D15" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/&lt;category&gt;/&lt;asset_slug&gt;/</x:v>
+      </x:c>
+      <x:c r="E15" s="349" t="str">
+        <x:v>bpk_base99_{asset_slug}_visual_top3d_v001.{blend|glb|json}</x:v>
+      </x:c>
+      <x:c r="F15" s="349" t="str">
+        <x:v>BPK-BASE99-ROLLUP-MAIN-DOOR</x:v>
+      </x:c>
+      <x:c r="G15" s="349"/>
+      <x:c r="H15" s="349" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="I15" s="349" t="str">
+        <x:v>基地99层可独立导入、替换、导出或维护的 Blender 设施包；实体灯随所属设施包</x:v>
+      </x:c>
+      <x:c r="J15" s="349" t="str">
+        <x:v>3D-设施</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A3:F3"/>
@@ -50501,6 +58891,84 @@
       </x:c>
       <x:c r="H41" s="349" t="str">
         <x:v>沿用稳定资产ID ENV-BASE99-ART-LAYOUT-3D，Blend SHA-256=eb92c8383f5b86d8d8e4226b9f4da2416a5903ab4ba8668f6a7639161de8dca1。仅更新Blender源、独立资产包和验收资料；未生成独立GLB、碰撞、LOD或PackedScene，未修改Godot运行时和锁定区域。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="54" customHeight="1">
+      <x:c r="A42" t="str">
+        <x:v>v0.1.38</x:v>
+      </x:c>
+      <x:c r="B42" s="350" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>Blender 基地设施布局 v016</x:v>
+      </x:c>
+      <x:c r="E42" s="349" t="str">
+        <x:v>基于用户手改 v015 的纯新增二楼与楼梯细节补完；5870 个既有对象逐项锁定零改动。新增 89 个成品组件及 89 个可编辑源组件，均按独立设施资产包镜像归类；101 个资产包、36 个地砖包、101 份磁盘清单。</x:v>
+      </x:c>
+      <x:c r="F42" s="349" t="str">
+        <x:v>Blender Game Prop Standard：任务验收 PASS；v016 新增范围 PaletteUV 14072/14072 面通过；4 个共享材质；楼梯四处接口精确通过。全场严格命名报告仍含 v012-v015 继承警告，锁定未改。</x:v>
+      </x:c>
+      <x:c r="G42" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>仅更新 Blender 源、独立设施资产包和验收资料；文件：source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v016.blend。未生成 GLB、碰撞、LOD 或 PackedScene，未修改 Godot 运行时。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="66" customHeight="1">
+      <x:c r="A43" t="str">
+        <x:v>v0.1.39</x:v>
+      </x:c>
+      <x:c r="B43" s="350" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>Blender 基地设施归类与灯光归属 v017</x:v>
+      </x:c>
+      <x:c r="E43" s="349" t="str">
+        <x:v>仅对 v016 进行 Collection 与资产清单归类，不改网格、材质、坐标、旋转、缩放或动画。旧区域总集合已拆为独立资产包；110 个成品包、36 个地砖包、110 份磁盘清单；2,954 个制作源组件全部镜像归入对应独立设施包。</x:v>
+      </x:c>
+      <x:c r="F43" s="349" t="str">
+        <x:v>组件归类审计 PASS：空包/未归包/多包归属/清单错配/未镜像源组件均为 0。灯光归属验收 PASS：55 个 LIGHT；33 个实体灯随实体设施包、12 个源灯随源资产包；4 个无实体全局补光与 6 个预览验收灯均为显式例外。</x:v>
+      </x:c>
+      <x:c r="G43" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H43" s="349" t="str">
+        <x:v>文件：source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend。v016 的 6,048 个既有对象签名保持一致；仅对象 Collection 归属及 manifest/catalog 更新。未生成 GLB、碰撞、LOD 或 PackedScene，未修改 Godot 运行时。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="66" customHeight="1">
+      <x:c r="A44" t="str">
+        <x:v>v0.1.40</x:v>
+      </x:c>
+      <x:c r="B44" s="350" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>基地99层独立资产包逐项登记</x:v>
+      </x:c>
+      <x:c r="E44" s="349" t="str">
+        <x:v>新增大类“基地资产包”，并按 3D-设施口径将 v017 的 110 个独立包逐条写入资产主表：7 类（建筑结构、地面、东侧固定设施、二楼/阁楼、阁楼下方固定设施、仓库、环境支持），36 个为独立地砖包。</x:v>
+      </x:c>
+      <x:c r="F44" s="349" t="str">
+        <x:v>每条记录关联 v017 manifest、目录、世界中心、包络、对象/网格/灯光计数、预期导出名与 manifest SHA-256；不改变 Blender 模型、运行时资产或 Godot 引用。</x:v>
+      </x:c>
+      <x:c r="G44" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H44" s="349" t="str">
+        <x:v>资产包用于未来独立导入、替换、导出与维护；当前仅完成 Blender 源及目录/清单登记，仍未生成独立 GLB、碰撞、LOD 或 PackedScene。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rcaa9a371ca3540fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rdc25991fdc7f426b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rf394921d058d4982"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rf79281c1f1e04185"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rcb05d6cd466c4494"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Re1e8572a07e946e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Rab3495faa7f54918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rfeec5388505945ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Rd8f01dad8e064ec8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R05b5e9e1bce9488d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R8aaf10fc54114ece"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="Race968441a1f4639"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R1f9fbd22c4564432"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="R5998e1b3a0ab49c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="Re12410531f5e4ecc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="Ra6d6920d13ca4ccc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R44f05aa63c3f46d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Re028e1122b354d95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="Rbab1878c47c3402d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8afeb2b6b4864a75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R81c9b22349f74ac2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rca341ef7b55c4dc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R594da9fd9b4549cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R6ebeefccc02948c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb72a534d1d1e40c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R031bdda7ef7847a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R4c0d4cc65d8e489c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Rc190ab542a0c4fe8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R58e9dd8d4f174fe3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R59a8b8ab06644ad5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R036fd604e08f420d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R8c5e6b6f6c6e4768"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="Raaea924131aa48a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="R47f94373719044dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R2031ae4118ed4070"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R1f58acb953134439"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="R36c92ee44e014d12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="Rde2c647ffed045bd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43631,7 +43631,7 @@
         <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_maintenance_workstation；对象 115；中心 (6.200, -13.190, 2.200)m；朝向 Blender +Y north；预期导出 east_maintenance_workstation_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
       </x:c>
     </x:row>
-    <x:row r="311" ht="54" customHeight="1">
+    <x:row r="311" ht="72" customHeight="1">
       <x:c r="A311" t="str">
         <x:v>BPK-BASE99-EAST-PERSONNEL-SECURITY-DOOR</x:v>
       </x:c>
@@ -43672,7 +43672,7 @@
         <x:v>v017</x:v>
       </x:c>
       <x:c r="N311" s="349" t="str">
-        <x:v>包络 1.410×2.860×3.022m；44 网格；1 灯</x:v>
+        <x:v>包络 0.898×2.040×2.340m；2 网格；1 灯</x:v>
       </x:c>
       <x:c r="O311" s="349" t="str">
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_personnel_security_door/asset_manifest.json</x:v>
@@ -43688,11 +43688,11 @@
         <x:v>基地资产包|东侧固定设施包|base99_package_east_personnel_security_door|package_root|top3d / blender +y北|static / fixture_light</x:v>
       </x:c>
       <x:c r="S311" s="349" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$411,R311)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$413,R311)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T311" s="349" t="str">
-        <x:v>e9c0d8cd40212c3dd3ca881a2b2033fdce4cdcccaa42c93bd1c88e98ed376314</x:v>
+        <x:v>e983c70eaacb530b1683c62b86ff64a515bf84e0d6efd55abc7a9eeb313e1304</x:v>
       </x:c>
       <x:c r="U311" s="349" t="str">
         <x:v>Codex</x:v>
@@ -43704,7 +43704,7 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X311" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_personnel_security_door；对象 45；中心 (13.905, -2.280, 1.511)m；朝向 Blender +Y north；预期导出 east_personnel_security_door_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_personnel_security_door；中心 (15.000, 2.500, 1.270)m；独立复制 west_door_lift_instance 的620mm双面加厚滑升门；东侧专属门禁包未改动。视觉迭代 v017_east_copies_west_double_sided_003；预期替换 undefined；当前 not_exported。</x:v>
       </x:c>
     </x:row>
     <x:row r="312" ht="54" customHeight="1">
@@ -44144,11 +44144,11 @@
         <x:v>基地资产包|东侧固定设施包|base99_package_east_supply_24h_station|package_root|top3d / blender +y北|static / default</x:v>
       </x:c>
       <x:c r="S317" s="349" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$411,R317)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$413,R317)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T317" s="349" t="str">
-        <x:v>2be5948f139e759b4282a89549cfd855f0f2dfc0fd7cf4df4e2c4cf1f6d3ff4c</x:v>
+        <x:v>4bc326d8363149f73a9826556842550888e40b54b1111f1edc7405e80e627c26</x:v>
       </x:c>
       <x:c r="U317" s="349" t="str">
         <x:v>Codex</x:v>
@@ -44160,7 +44160,7 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X317" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_supply_24h_station；对象 50；中心 (13.361, 1.531, 2.360)m；朝向 Blender +Y north；预期导出 east_supply_24h_station_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_supply_24h_station；对象 50；中心 (13.361, -3.469, 2.360)m；朝向 Blender +Y north；相邻独立设施；仅 SUPPLY 24H 整包已南移至锚点 (13.520, -3.450, 0.000)m，不包含门旁的电池柜与 Emergency 柜；预期导出 east_supply_24h_station_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass。</x:v>
       </x:c>
     </x:row>
     <x:row r="318" ht="54" customHeight="1">
@@ -51305,6 +51305,310 @@
       </x:c>
       <x:c r="X411" s="349" t="str">
         <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::water_purifier；对象 3；中心 (-12.979, -4.900, 1.300)m；朝向 Blender +Y north；预期导出 water_purifier_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" ht="54" customHeight="1">
+      <x:c r="A412" t="str">
+        <x:v>BPK-BASE99-EAST-DOOR-ACCESS-CONTROL</x:v>
+      </x:c>
+      <x:c r="B412" t="str">
+        <x:v>基地99层 · 东墙门禁外围控制</x:v>
+      </x:c>
+      <x:c r="C412" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D412" t="str">
+        <x:v>东侧固定设施包</x:v>
+      </x:c>
+      <x:c r="E412" t="str">
+        <x:v>base99_package_east_door_access_control</x:v>
+      </x:c>
+      <x:c r="F412" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G412" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H412" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I412" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J412" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K412" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L412" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M412" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N412" s="349" t="str">
+        <x:v>包络 0.410×1.835×2.731m；17 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O412" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/east_facilities/east_door_access_control/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P412" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q412" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;东侧固定设施包;east_door_access_control;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R412" s="349" t="str">
+        <x:f>C412&amp;"|"&amp;D412&amp;"|"&amp;E412&amp;"|"&amp;F412&amp;"|"&amp;LOWER(H412)&amp;"|"&amp;I412</x:f>
+        <x:v>基地资产包|东侧固定设施包|base99_package_east_door_access_control|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S412" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$413,R412)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T412" s="349" t="str">
+        <x:v>681f349e6e957fbf0863f1b07095d8c082aceb4043cfe6de8aa5c48a3e9c2453</x:v>
+      </x:c>
+      <x:c r="U412" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V412" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W412" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X412" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_door_access_control；对象 17；中心 (14.555, 3.232, 1.656)m；朝向 Blender +Y north；组件组 base99_east_door_wall_set 的独立门禁外围控制，已随门洞换至保留东墙_03（北段），附着同一门洞但保持可独立导入维护；预期导出 east_door_access_control_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" ht="76" customHeight="1">
+      <x:c r="A413" t="str">
+        <x:v>BPK-BASE99-EAST-DOOR-WALL-MODULE</x:v>
+      </x:c>
+      <x:c r="B413" t="str">
+        <x:v>基地99层 · 北段带门墙模块</x:v>
+      </x:c>
+      <x:c r="C413" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D413" t="str">
+        <x:v>建筑结构包</x:v>
+      </x:c>
+      <x:c r="E413" t="str">
+        <x:v>base99_package_east_door_wall_module</x:v>
+      </x:c>
+      <x:c r="F413" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G413" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H413" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I413" t="str">
+        <x:v>static / wall_owned_frame</x:v>
+      </x:c>
+      <x:c r="J413" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K413" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L413" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M413" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N413" s="349" t="str">
+        <x:v>包络 1.051×5.000×9.000m；1 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O413" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/architecture/east_door_wall_module/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P413" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q413" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;建筑结构包;east_door_wall_module;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R413" s="349" t="str">
+        <x:f>C413&amp;"|"&amp;D413&amp;"|"&amp;E413&amp;"|"&amp;F413&amp;"|"&amp;LOWER(H413)&amp;"|"&amp;I413</x:f>
+        <x:v>基地资产包|建筑结构包|base99_package_east_door_wall_module|package_root|top3d / blender +y北|static / wall_owned_frame</x:v>
+      </x:c>
+      <x:c r="S413" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$413,R413)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T413" s="349" t="str">
+        <x:v>07817b0d140cb5634813c7cd0dc246b859489872ca15b454ab84396b08c5c682</x:v>
+      </x:c>
+      <x:c r="U413" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V413" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W413" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X413" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::east_door_wall_module；主体墙面50个哑光面仅调整 PaletteUV 至与相邻东墙一致的(9,9)；门框、门扇、灯光、几何、朝向均未改动。视觉迭代 v017_east_door_wall_palette_aligned_004；当前尚未建立独立运行时 GLB 映射；当前 not_exported。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" ht="72" customHeight="1">
+      <x:c r="A414" t="str">
+        <x:v>BPK-BASE99-WEST-DOOR-WALL-MODULE</x:v>
+      </x:c>
+      <x:c r="B414" t="str">
+        <x:v>基地99层 · 西侧第三段带门墙模块</x:v>
+      </x:c>
+      <x:c r="C414" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D414" t="str">
+        <x:v>建筑结构包</x:v>
+      </x:c>
+      <x:c r="E414" t="str">
+        <x:v>base99_package_west_door_wall_module</x:v>
+      </x:c>
+      <x:c r="F414" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G414" t="str">
+        <x:v>ENV-BASE99-WALL-DOOR-5X9</x:v>
+      </x:c>
+      <x:c r="H414" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I414" t="str">
+        <x:v>static / wall_owned_frame</x:v>
+      </x:c>
+      <x:c r="J414" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K414" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L414" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M414" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N414" s="349" t="str">
+        <x:v>包络 1.051×5.000×9.000m；1 网格；0 灯</x:v>
+      </x:c>
+      <x:c r="O414" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/architecture/west_door_wall_module/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P414" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json; assets/art/environments/base_facility_3d/runtime/env_base99_wall_door_5x9/env_base99_wall_door_5x9_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="Q414" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;建筑结构包;west_door_wall_module;ENV-BASE99-WALL-DOOR-5X9;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R414" s="349" t="str">
+        <x:f>C414&amp;"|"&amp;D414&amp;"|"&amp;E414&amp;"|"&amp;F414&amp;"|"&amp;LOWER(H414)&amp;"|"&amp;I414</x:f>
+        <x:v>基地资产包|建筑结构包|base99_package_west_door_wall_module|package_root|top3d / blender +y北|static / wall_owned_frame</x:v>
+      </x:c>
+      <x:c r="S414" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$415,R414)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T414" s="349" t="str">
+        <x:v>245e0924385ade489200c0c2c9ee1f2941da655f93723b5db3de23f9d8b34028</x:v>
+      </x:c>
+      <x:c r="U414" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V414" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W414" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X414" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::west_door_wall_module；中心 (-15.000, 2.500, 4.500)m；双面闭合门框与360mm墙芯同中心；最大可见厚度1.051m；门框归属墙模块。视觉迭代 v017_west_double_sided_alignment_002；预期替换 assets/art/environments/base_facility_3d/components/env_base99_wall_door_5x9/env_base99_wall_door_5x9_visual_top3d_v001.glb；当前 source_ready_reuses_existing_runtime_asset_not_exported_in_this_iteration；碰撞与玩法归 DungeonRoom3D + RoomDoor3D。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" ht="72" customHeight="1">
+      <x:c r="A415" t="str">
+        <x:v>BPK-BASE99-WEST-DOOR-LIFT-INSTANCE</x:v>
+      </x:c>
+      <x:c r="B415" t="str">
+        <x:v>基地99层 · 西侧第三段通用滑升门实例</x:v>
+      </x:c>
+      <x:c r="C415" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D415" t="str">
+        <x:v>西侧固定设施实例</x:v>
+      </x:c>
+      <x:c r="E415" t="str">
+        <x:v>base99_placement_west_door_lift_instance</x:v>
+      </x:c>
+      <x:c r="F415" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G415" t="str">
+        <x:v>ENV-BASE99-DOOR-LIFT-22X25</x:v>
+      </x:c>
+      <x:c r="H415" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I415" t="str">
+        <x:v>static / fixture_light / shared_runtime_asset</x:v>
+      </x:c>
+      <x:c r="J415" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K415" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L415" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M415" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N415" s="349" t="str">
+        <x:v>包络 0.898×2.040×2.340m；2 网格；1 灯</x:v>
+      </x:c>
+      <x:c r="O415" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/west_facilities/west_door_lift_instance/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P415" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json; assets/art/environments/base_facility_3d/runtime/env_base99_door_lift_2p2x2p5/env_base99_door_lift_2p2x2p5_root_top3d_v001.tscn</x:v>
+      </x:c>
+      <x:c r="Q415" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;西侧固定设施实例;west_door_lift_instance;ENV-BASE99-DOOR-LIFT-22X25;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R415" s="349" t="str">
+        <x:f>C415&amp;"|"&amp;D415&amp;"|"&amp;E415&amp;"|"&amp;F415&amp;"|"&amp;LOWER(H415)&amp;"|"&amp;I415</x:f>
+        <x:v>基地资产包|西侧固定设施实例|base99_placement_west_door_lift_instance|package_root|top3d / blender +y北|static / fixture_light / shared_runtime_asset</x:v>
+      </x:c>
+      <x:c r="S415" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$415,R415)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T415" s="349" t="str">
+        <x:v>7866d64dc38165e095f54b393e5d711d45626d0e1a4145729d2dbb66f213842d</x:v>
+      </x:c>
+      <x:c r="U415" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V415" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W415" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X415" s="349" t="str">
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::west_door_lift_instance；中心 (-15.000, 2.500, 1.270)m；620mm加厚双面滑升门；两面同构嵌板、警示条和状态灯；局部点光位于厚度中轴。视觉迭代 v017_west_double_sided_alignment_002；预期替换 assets/art/environments/base_facility_3d/components/env_base99_door_lift_2p2x2p5/env_base99_door_lift_2p2x2p5_visual_top3d_v001.glb；当前 source_ready_reuses_existing_runtime_asset_not_exported_in_this_iteration；碰撞与玩法归 RoomDoor3D。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -51386,7 +51690,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c26cbbf1fdf4fdb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra58f5976dc6f4f68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -58971,6 +59275,240 @@
         <x:v>资产包用于未来独立导入、替换、导出与维护；当前仅完成 Blender 源及目录/清单登记，仍未生成独立 GLB、碰撞、LOD 或 PackedScene。</x:v>
       </x:c>
     </x:row>
+    <x:row r="45" ht="72" customHeight="1">
+      <x:c r="A45" t="str">
+        <x:v>v0.1.41</x:v>
+      </x:c>
+      <x:c r="B45" s="350" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>v017 东墙门体规格与 SUPPLY 24H 位置纠正</x:v>
+      </x:c>
+      <x:c r="E45" s="349" t="str">
+        <x:v>依据参考图互换东墙标准人员门与 SUPPLY 24H 自动补给机的位置；门体改为直接复用游戏资产 ENV-BASE99-DOOR-LIFT-22X25，并新建独立‘东墙门禁外围控制’资产包。基地资产包总数由 110 增至 111。</x:v>
+      </x:c>
+      <x:c r="F45" s="349" t="str">
+        <x:v>除东墙人员门、SUPPLY 24H 与新增门禁外围控制包外，5,855 个既有对象锁定签名一致。门体场景包络为 0.325×2.200×2.500m；实体状态灯及其源镜像均随门体资产包归属。</x:v>
+      </x:c>
+      <x:c r="G45" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H45" s="349" t="str">
+        <x:v>Blender 源场景和目录/manifest/资产账本已更新；未新增独立 GLB、碰撞、LOD 或 PackedScene，运行时门碰撞仍归 RoomDoor3D。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="72" customHeight="1">
+      <x:c r="A46" t="str">
+        <x:v>v0.1.42</x:v>
+      </x:c>
+      <x:c r="B46" s="350" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>v017 东墙带门组件组纠正</x:v>
+      </x:c>
+      <x:c r="E46" s="349" t="str">
+        <x:v>将东墙门洞恢复为游戏成套组件：新增独立带门墙模块包，标准滑升门与门禁外围控制嵌入同一门洞；SUPPLY 24H 恢复为相邻设施。基地资产包总数由 111 增至 112。</x:v>
+      </x:c>
+      <x:c r="F46" s="349" t="str">
+        <x:v>东墙带门墙模块、滑升门、门禁外围控制均分别保留独立源/输出包，并以 base99_east_door_wall_set 组装清单绑定；范围外 5,853 个既有对象锁定签名一致。</x:v>
+      </x:c>
+      <x:c r="G46" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H46" s="349" t="str">
+        <x:v>仅更新 Blender 源场景、资产包目录/清单和台账；未新增独立 GLB、碰撞、LOD 或 PackedScene。运行时碰撞仍由 DungeonRoom3D + RoomDoor3D 负责。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="78" customHeight="1">
+      <x:c r="A47" t="str">
+        <x:v>v0.1.43</x:v>
+      </x:c>
+      <x:c r="B47" s="350" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>v017 东墙北南墙格与 SUPPLY 24H 位置交换</x:v>
+      </x:c>
+      <x:c r="E47" s="349" t="str">
+        <x:v>依据参考图，将带门墙组件组由保留东墙_02（南段）换至保留东墙_03（北段）；门、门禁外围控制随门洞北移。SUPPLY 24H 自动补给机仅自身包南移，不携带电池柜与 Emergency 柜。基地资产包总数保持 112。</x:v>
+      </x:c>
+      <x:c r="F47" s="349" t="str">
+        <x:v>东墙带门墙模块、标准滑升门、门禁外围控制继续以 base99_east_door_wall_set 绑定；目标外 5,850 个对象锁定签名一致。门墙中心 (15.000, 2.500, 4.500)m，门中心 (15.000, 2.500, 1.250)m，SUPPLY 24H 主体锚点 (13.520, -3.450, 1.780)m。</x:v>
+      </x:c>
+      <x:c r="G47" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H47" s="349" t="str">
+        <x:v>仅更新 Blender 源场景、资产包清单、组装清单与资产账本；未新增独立 GLB、碰撞、LOD 或 PackedScene。运行时碰撞仍由 DungeonRoom3D + RoomDoor3D 负责。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="76" customHeight="1">
+      <x:c r="A48" t="str">
+        <x:v>v0.1.44</x:v>
+      </x:c>
+      <x:c r="B48" s="350" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>v017 北段人员门参考图高还原深化</x:v>
+      </x:c>
+      <x:c r="E48" s="349" t="str">
+        <x:v>依据参考图重制北段标准人员滑升门的可见结构：八角金属框、冷灰分层门板、橙色锁扣和冷青状态条。门洞坐标与规格保持不变，基地资产包总数保持 112。</x:v>
+      </x:c>
+      <x:c r="F48" s="349" t="str">
+        <x:v>仅 east_personnel_security_door 的输出/源网格及其两盏归属门体的状态照明可修改。其余 5,997 个对象锁定签名一致；门包与源镜像各 3 个对象，严格 PaletteUV 校验通过。</x:v>
+      </x:c>
+      <x:c r="G48" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H48" s="349" t="str">
+        <x:v>仅更新 Blender 源场景、门资产包清单、catalog 与资产账本；未新增独立 GLB、碰撞、LOD 或 PackedScene。运行时门碰撞仍归 RoomDoor3D。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="76" customHeight="1">
+      <x:c r="A49" t="str">
+        <x:v>v0.1.45</x:v>
+      </x:c>
+      <x:c r="B49" s="350" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>v017 北段带门墙模块门框深化</x:v>
+      </x:c>
+      <x:c r="E49" s="349" t="str">
+        <x:v>依据参考图补足北段带门墙模块的墙体归属门框：八角外轮廓、双层冷灰门洞饰条、顶部橙色服务铭牌和紧固件。门扇、门灯与门禁继续维持独立资产包，基地资产包总数保持 112。</x:v>
+      </x:c>
+      <x:c r="F49" s="349" t="str">
+        <x:v>仅 east_door_wall_module 的输出/源墙体网格可修改。其余 5,997 个对象锁定签名一致；墙包与源镜像各 3 个对象，严格 PaletteUV、共享材质和灯光归属校验通过。</x:v>
+      </x:c>
+      <x:c r="G49" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H49" s="349" t="str">
+        <x:v>仅更新 Blender 源场景、墙模块资产包清单、catalog 与资产账本；未新增独立 GLB、碰撞、LOD 或 PackedScene。运行时门碰撞仍归 RoomDoor3D。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="76" customHeight="1">
+      <x:c r="A50" t="str">
+        <x:v>v0.1.46</x:v>
+      </x:c>
+      <x:c r="B50" s="350" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>ENV-BASE99-WALL-DOOR-5X9 / ENV-BASE99-DOOR-LIFT-22X25</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
+        <x:v>v017 西侧第三段带门组件对齐</x:v>
+      </x:c>
+      <x:c r="E50" s="349" t="str">
+        <x:v>西侧带门墙由北向南第四段修正至第三段：Blender (-15,+2.5,0) 对应游戏 (-15,-9,+2.5)。墙模块复用已验收东侧门框，门扇复用既有通用滑升门。</x:v>
+      </x:c>
+      <x:c r="F50" s="349" t="str">
+        <x:v>新增两个独立 Blender 资产包记录和源镜像。组合严格对应 DungeonRoom3D 的 ENV-BASE99-WALL-DOOR-5X9 与 RoomDoor3D 的 ENV-BASE99-DOOR-LIFT-22X25；不含东侧专属门禁。114 包、6 网格、1,068 个有效 PaletteUV 面通过。</x:v>
+      </x:c>
+      <x:c r="G50" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H50" s="349" t="str">
+        <x:v>仅更新 v017 Blender 源场景、资产包目录、组件组清单、catalog 与台账；未覆盖正式 GLB 或 PackedScene，现有运行时路径保留作为后续替换目标。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="80" customHeight="1">
+      <x:c r="A51" t="str">
+        <x:v>v0.1.47</x:v>
+      </x:c>
+      <x:c r="B51" s="350" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>ENV-BASE99-WALL-DOOR-5X9 / ENV-BASE99-DOOR-LIFT-22X25</x:v>
+      </x:c>
+      <x:c r="D51" t="str">
+        <x:v>v017 西侧带门墙双面对齐模型迭代</x:v>
+      </x:c>
+      <x:c r="E51" s="349" t="str">
+        <x:v>修复西侧门墙中心偏移与门框脱离：5×9m墙芯回归相邻西墙共用中心线；门框改为归属墙模块的双面闭合结构，门扇改为双面加厚滑升门。</x:v>
+      </x:c>
+      <x:c r="F51" s="349" t="str">
+        <x:v>仅调整 west_door_wall_module 与 west_door_lift_instance 及其源镜像；6,000 个范围外对象签名不变。114 包、6 网格、764 个有效 PaletteUV 面、双面厚度与归属检查通过。</x:v>
+      </x:c>
+      <x:c r="G51" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H51" s="349" t="str">
+        <x:v>仅更新 v017 Blender 源场景、两套资产包清单、组件组清单、catalog 与台账；未覆盖正式 GLB 或 PackedScene。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="80" customHeight="1">
+      <x:c r="A52" t="str">
+        <x:v>v0.1.48</x:v>
+      </x:c>
+      <x:c r="B52" s="350" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>ENV-BASE99-WALL-DOOR-5X9 / ENV-BASE99-DOOR-LIFT-22X25</x:v>
+      </x:c>
+      <x:c r="D52" t="str">
+        <x:v>v017 东侧复用西侧双面带门墙</x:v>
+      </x:c>
+      <x:c r="E52" s="349" t="str">
+        <x:v>东侧带门墙模块与滑升门改为西侧已验收双面模型的独立网格副本；保持东侧反向墙朝向、中心线和运行时组件映射。</x:v>
+      </x:c>
+      <x:c r="F52" s="349" t="str">
+        <x:v>只更新 east_door_wall_module 与 east_personnel_security_door 及源镜像；东侧门禁包、自动补给机和其余设施未改。114 包、双面厚度、PaletteUV、灯光归属和组件组验收通过。</x:v>
+      </x:c>
+      <x:c r="G52" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H52" s="349" t="str">
+        <x:v>仅更新 v017 Blender 源场景、两个既有资产包清单、东侧组件组清单、catalog 与台账；未覆盖正式 GLB 或 PackedScene。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="80" customHeight="1">
+      <x:c r="A53" t="str">
+        <x:v>v0.1.49</x:v>
+      </x:c>
+      <x:c r="B53" s="350" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>ENV-BASE99-WALL-DOOR-5X9</x:v>
+      </x:c>
+      <x:c r="D53" t="str">
+        <x:v>v017 东侧带门墙 PaletteUV 对齐</x:v>
+      </x:c>
+      <x:c r="E53" s="349" t="str">
+        <x:v>仅将 east_door_wall_module 的50个主体哑光墙面从 PaletteUV (9,5) 对齐到相邻东墙使用的 (9,9)，消除偏白色差。</x:v>
+      </x:c>
+      <x:c r="F53" s="349" t="str">
+        <x:v>门框、门扇、灯光、结构、坐标、朝向、独立资产包与其他设施不变；输出和源镜像同步，范围外 6,008 个对象的变换及 PaletteUV 不变。</x:v>
+      </x:c>
+      <x:c r="G53" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H53" s="349" t="str">
+        <x:v>仅更新 v017 Blender 源场景、东侧门墙资产清单、catalog 与台账；未覆盖正式 GLB 或 PackedScene。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A3:G3"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8afeb2b6b4864a75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R81c9b22349f74ac2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rca341ef7b55c4dc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R594da9fd9b4549cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R6ebeefccc02948c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rb72a534d1d1e40c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R031bdda7ef7847a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R4c0d4cc65d8e489c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="Rc190ab542a0c4fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R58e9dd8d4f174fe3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R59a8b8ab06644ad5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="R036fd604e08f420d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="R8c5e6b6f6c6e4768"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="Raaea924131aa48a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="R47f94373719044dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R2031ae4118ed4070"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R1f58acb953134439"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="R36c92ee44e014d12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="Rde2c647ffed045bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R6b6332d3775e472e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R6a1c2fe1a8a74eee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rc149ee20cda9488e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R18a9ac7524fb43b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R4ce0440945f04152"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Reccf02ab19444c37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Ra703b2ebc4cf4032"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Re58529081b964983"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="R5eafcd442a904568"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="Rd0459b8fee2c4f2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R4911e9357d094884"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="Raf2ae07c70c84cda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="Rae51b4e8ba4743ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="Rc242b832ad104284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="Rdd6b77afd26748bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="Re880f3c440964421"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R2246e4603ffd41ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Rc1fb169950a44989"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R62eea2deb9514d78"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -47279,12 +47279,12 @@
         <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_battery_cabinet；对象 12；中心 (-1.950, 13.874, 6.545)m；朝向 Blender +Y north；预期导出 loft_battery_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
       </x:c>
     </x:row>
-    <x:row r="359" ht="54" customHeight="1">
+    <x:row r="359" ht="72" customHeight="1">
       <x:c r="A359" t="str">
         <x:v>BPK-BASE99-LOFT-BED-AND-BEDDING</x:v>
       </x:c>
       <x:c r="B359" t="str">
-        <x:v>基地99层 · 参考床架床品与床下收纳</x:v>
+        <x:v>基地99层 · 二楼床铺与床品</x:v>
       </x:c>
       <x:c r="C359" t="str">
         <x:v>基地资产包</x:v>
@@ -47320,7 +47320,7 @@
         <x:v>v017</x:v>
       </x:c>
       <x:c r="N359" s="349" t="str">
-        <x:v>包络 4.750×2.676×1.318m；37 网格；0 灯</x:v>
+        <x:v>包络 4.750×2.906×1.318m；37 对象；源镜像 37 对象</x:v>
       </x:c>
       <x:c r="O359" s="349" t="str">
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_bed_and_bedding/asset_manifest.json</x:v>
@@ -47340,7 +47340,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T359" s="349" t="str">
-        <x:v>6a00f3fb212e52e1f04ca441ef3edb34fc809d39d955cda83c9680489ba78e4c</x:v>
+        <x:v>4ca6da9f44b40f7a2c49d63698599f5bca1f3732093787ed16c8a5947de58890</x:v>
       </x:c>
       <x:c r="U359" s="349" t="str">
         <x:v>Codex</x:v>
@@ -47352,7 +47352,7 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X359" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_bed_and_bedding；对象 37；中心 (0.300, 10.957, 6.669)m；朝向 Blender +Y north；预期导出 loft_bed_and_bedding_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>恢复参考长度4.75m；床架沿Y方向加宽至2.55m，床垫宽2.30m，床架、床脚、床罩和滚边同步对齐。 revision=v017_loft_bed_width_corrected_006；中心 (0.300, 11.072, 6.669)m；PaletteUV、范围锁和独占归属验收通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="360" ht="54" customHeight="1">
@@ -47963,12 +47963,12 @@
         <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_hanging_plant；对象 12；中心 (2.724, 14.150, 8.135)m；朝向 Blender +Y north；预期导出 loft_hanging_plant_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
       </x:c>
     </x:row>
-    <x:row r="368" ht="54" customHeight="1">
+    <x:row r="368" ht="72" customHeight="1">
       <x:c r="A368" t="str">
         <x:v>BPK-BASE99-LOFT-LOUNGE-RUG</x:v>
       </x:c>
       <x:c r="B368" t="str">
-        <x:v>基地99层 · 休闲区低饱和地毯</x:v>
+        <x:v>基地99层 · 二楼休闲区多色桌毯</x:v>
       </x:c>
       <x:c r="C368" t="str">
         <x:v>基地资产包</x:v>
@@ -48004,7 +48004,7 @@
         <x:v>v017</x:v>
       </x:c>
       <x:c r="N368" s="349" t="str">
-        <x:v>包络 4.900×2.450×0.056m；7 网格；0 灯</x:v>
+        <x:v>包络 4.900×2.450×0.070m；13 对象；源镜像 13 对象</x:v>
       </x:c>
       <x:c r="O368" s="349" t="str">
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/loft/loft_lounge_rug/asset_manifest.json</x:v>
@@ -48024,7 +48024,7 @@
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T368" s="349" t="str">
-        <x:v>9bf45be673d85e4a8e0a61dc0d370bfc22e20331fdd4b4b04a4f44a90702b0b4</x:v>
+        <x:v>ec707f122b5860e4db4824f6b557f006af83025556dd2907dd19d422d9c68d9c</x:v>
       </x:c>
       <x:c r="U368" s="349" t="str">
         <x:v>Codex</x:v>
@@ -48036,7 +48036,7 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X368" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_lounge_rug；对象 7；中心 (6.180, 9.550, 6.092)m；朝向 Blender +Y north；预期导出 loft_lounge_rug_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>桌毯按参考图重做为暗紫红基底、紫灰边框和低饱和暖棕细纹；地面深化层低于桌毯，咖啡桌本体未改。 revision=v017_loft_lounge_rug_reference_palette_006；中心 (6.180, 9.550, 6.099)m；PaletteUV、范围锁和独占归属验收通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="369" ht="54" customHeight="1">
@@ -51609,6 +51609,82 @@
       </x:c>
       <x:c r="X415" s="349" t="str">
         <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::west_door_lift_instance；中心 (-15.000, 2.500, 1.270)m；620mm加厚双面滑升门；两面同构嵌板、警示条和状态灯；局部点光位于厚度中轴。视觉迭代 v017_west_double_sided_alignment_002；预期替换 assets/art/environments/base_facility_3d/components/env_base99_door_lift_2p2x2p5/env_base99_door_lift_2p2x2p5_visual_top3d_v001.glb；当前 source_ready_reuses_existing_runtime_asset_not_exported_in_this_iteration；碰撞与玩法归 RoomDoor3D。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" ht="72" customHeight="1">
+      <x:c r="A416" t="str">
+        <x:v>BPK-BASE99-LOFT-FLOOR-FINISH</x:v>
+      </x:c>
+      <x:c r="B416" t="str">
+        <x:v>基地99层 · 二楼地板色彩深化</x:v>
+      </x:c>
+      <x:c r="C416" t="str">
+        <x:v>基地资产包</x:v>
+      </x:c>
+      <x:c r="D416" t="str">
+        <x:v>地面系统包</x:v>
+      </x:c>
+      <x:c r="E416" t="str">
+        <x:v>base99_package_loft_floor_finish</x:v>
+      </x:c>
+      <x:c r="F416" t="str">
+        <x:v>package_root</x:v>
+      </x:c>
+      <x:c r="G416" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H416" t="str">
+        <x:v>Top3D / Blender +Y北</x:v>
+      </x:c>
+      <x:c r="I416" t="str">
+        <x:v>static / default</x:v>
+      </x:c>
+      <x:c r="J416" t="str">
+        <x:v>3D-设施 / 基地99层独立资产包</x:v>
+      </x:c>
+      <x:c r="K416" t="str">
+        <x:v>Blender源已完成</x:v>
+      </x:c>
+      <x:c r="L416" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M416" t="str">
+        <x:v>v017</x:v>
+      </x:c>
+      <x:c r="N416" s="349" t="str">
+        <x:v>包络 19.600×9.600×0.108m；11 对象；源镜像 11 对象</x:v>
+      </x:c>
+      <x:c r="O416" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/loft_floor_finish/asset_manifest.json</x:v>
+      </x:c>
+      <x:c r="P416" s="349" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+      </x:c>
+      <x:c r="Q416" s="349" t="str">
+        <x:v>基地99层;基地资产包;3D设施;地面系统包;loft_floor_finish;PaletteUV</x:v>
+      </x:c>
+      <x:c r="R416" s="349" t="str">
+        <x:f>C416&amp;"|"&amp;D416&amp;"|"&amp;E416&amp;"|"&amp;F416&amp;"|"&amp;LOWER(H416)&amp;"|"&amp;I416</x:f>
+        <x:v>基地资产包|地面系统包|base99_package_loft_floor_finish|package_root|top3d / blender +y北|static / default</x:v>
+      </x:c>
+      <x:c r="S416" s="349" t="str">
+        <x:f>IF(COUNTIF($R$6:$R$416,R416)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T416" s="349" t="str">
+        <x:v>6ce5eed8db6dcb29f09ffd20644573e353fcfef1e0f56690db403c1e825602ae</x:v>
+      </x:c>
+      <x:c r="U416" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V416" s="348" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W416" s="349" t="str">
+        <x:v>用户自制Blender资产</x:v>
+      </x:c>
+      <x:c r="X416" s="349" t="str">
+        <x:v>可见地板恢复深红棕主色，以暗红、暖棕拼板和少量紫灰细缝深化；不含绿色大面与承重楼板。 revision=v017_loft_floor_reference_redbrown_006；中心 (5.000, 10.000, 6.044)m；PaletteUV、范围锁和独占归属验收通过。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -51690,7 +51766,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra58f5976dc6f4f68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6635dd5019624413"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -59509,6 +59585,58 @@
         <x:v>仅更新 v017 Blender 源场景、东侧门墙资产清单、catalog 与台账；未覆盖正式 GLB 或 PackedScene。</x:v>
       </x:c>
     </x:row>
+    <x:row r="54" ht="84" customHeight="1">
+      <x:c r="A54" t="str">
+        <x:v>v0.1.50</x:v>
+      </x:c>
+      <x:c r="B54" s="350" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>BPK-BASE99-LOFT-BED-AND-BEDDING / BPK-BASE99-LOFT-LOUNGE-RUG / BPK-BASE99-LOFT-FLOOR-FINISH</x:v>
+      </x:c>
+      <x:c r="D54" t="str">
+        <x:v>v017 二楼床铺、桌毯与可见地板局部深化</x:v>
+      </x:c>
+      <x:c r="E54" s="349" t="str">
+        <x:v>床铺加宽至床架5.45m、床垫5.20m；桌毯改为暖红、青绿、紫灰、暖橙多色层次；二楼可见地板从阁楼主体拆为独立地面系统包。</x:v>
+      </x:c>
+      <x:c r="F54" s="349" t="str">
+        <x:v>仅3个资产包及其源镜像；床37、桌毯13、地板11对象，源输出数量一致；PaletteUV、独占归属和范围锁均验收通过。</x:v>
+      </x:c>
+      <x:c r="G54" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H54" s="349" t="str">
+        <x:v>未改楼梯、栏杆、沙发、工位、咖啡桌本体或一楼资产；未导出GLB/PackedScene。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="84" customHeight="1">
+      <x:c r="A55" t="str">
+        <x:v>v0.1.51</x:v>
+      </x:c>
+      <x:c r="B55" s="350" t="n">
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>BPK-BASE99-LOFT-BED-AND-BEDDING / BPK-BASE99-LOFT-LOUNGE-RUG / BPK-BASE99-LOFT-FLOOR-FINISH</x:v>
+      </x:c>
+      <x:c r="D55" t="str">
+        <x:v>v017 二楼床铺、桌毯与地板参考图纠正</x:v>
+      </x:c>
+      <x:c r="E55" s="349" t="str">
+        <x:v>纠正上一轮床轴向误读：恢复X向长度4.75m，仅将Y向床架加宽至2.55m、床垫加宽至2.30m。桌毯恢复暗紫红、紫灰、暖棕配色，二楼地面恢复深红棕主色并移除绿色大面。</x:v>
+      </x:c>
+      <x:c r="F55" s="349" t="str">
+        <x:v>仅重做3个资产包及其源镜像。床37、桌毯13、地板11对象，源输出数量一致；桌毯未再被地面分区覆盖；PaletteUV、独占归属和范围锁通过。</x:v>
+      </x:c>
+      <x:c r="G55" s="349" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H55" s="349" t="str">
+        <x:v>未改楼梯、栏杆、沙发、工位、咖啡桌本体或一楼资产。未导出GLB/PackedScene。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A3:G3"/>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R6b6332d3775e472e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R6a1c2fe1a8a74eee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rc149ee20cda9488e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R18a9ac7524fb43b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R4ce0440945f04152"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Reccf02ab19444c37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Ra703b2ebc4cf4032"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Re58529081b964983"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="R5eafcd442a904568"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="Rd0459b8fee2c4f2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R4911e9357d094884"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="Raf2ae07c70c84cda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="Rae51b4e8ba4743ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="Rc242b832ad104284"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="Rdd6b77afd26748bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="Re880f3c440964421"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="R2246e4603ffd41ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Rc1fb169950a44989"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="R62eea2deb9514d78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd85d8180d1eb4f3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rce4ee0fb47b54051"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R36e76d6ee8674160"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R3c30a26bf6d84d89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rf44a2802f4234538"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R7a812d9bf5ae42dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R5dca77775aab4961"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R5c7f9820c7fd4420"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="9" r:id="R7c3d86b198094f39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="10" r:id="R0a35471c77ce44b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="11" r:id="R6b1cc6577e00461d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-道具" sheetId="12" r:id="Rc8e9e19579b441ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-角色" sheetId="13" r:id="Rc6d7508a2b7d4b4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-敌人" sheetId="14" r:id="Rf8fd8aa2d24a47a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-武器" sheetId="15" r:id="R0104d80793c0403b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-物品" sheetId="16" r:id="R2afb9906d06248fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-特效" sheetId="17" r:id="Rd33212270e9c4e6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="18" r:id="Ra8f8d60037004fc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="19" r:id="Ra11cffcdc5da47c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1782,7 +1782,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssetMasterTable" displayName="AssetMasterTable" ref="A5:X112" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssetMasterTable" displayName="AssetMasterTable" ref="A5:X115" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="24">
     <x:tableColumn id="1" name="AssetID"/>
     <x:tableColumn id="2" name="中文名"/>
@@ -2085,11 +2085,11 @@
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="321" t="n">
-        <x:v>296</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B6" s="319"/>
       <x:c r="C6" s="321" t="n">
-        <x:v>166</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D6" s="319" t="n"/>
       <x:c r="E6" s="321" t="n">
@@ -2165,11 +2165,9 @@
         </x:is>
       </x:c>
       <x:c r="B10" s="329" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$300,A10)</x:f>
         <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="329" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$300,A10,'资产主表'!$K$6:$K$300,"已完成")+COUNTIFS('资产主表'!$C$6:$C$300,A10,'资产主表'!$K$6:$K$300,"原型已接入")</x:f>
         <x:v>28</x:v>
       </x:c>
       <x:c r="D10" s="319" t="n"/>
@@ -2199,11 +2197,9 @@
         </x:is>
       </x:c>
       <x:c r="B11" s="331" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$300,A11)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="C11" s="331" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$300,A11,'资产主表'!$K$6:$K$300,"已完成")+COUNTIFS('资产主表'!$C$6:$C$300,A11,'资产主表'!$K$6:$K$300,"原型已接入")</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="D11" s="319" t="n"/>
@@ -2231,11 +2227,9 @@
         <x:v>武器</x:v>
       </x:c>
       <x:c r="B12" s="331" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$300,A12)</x:f>
         <x:v>36</x:v>
       </x:c>
       <x:c r="C12" s="331" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$300,A12,'资产主表'!$K$6:$K$300,"已完成")+COUNTIFS('资产主表'!$C$6:$C$300,A12,'资产主表'!$K$6:$K$300,"原型已接入")</x:f>
         <x:v>19</x:v>
       </x:c>
       <x:c r="D12" s="319" t="n"/>
@@ -2265,11 +2259,9 @@
         </x:is>
       </x:c>
       <x:c r="B13" s="331" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$300,A13)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="331" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$300,A13,'资产主表'!$K$6:$K$300,"已完成")+COUNTIFS('资产主表'!$C$6:$C$300,A13,'资产主表'!$K$6:$K$300,"原型已接入")</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="D13" s="319" t="n"/>
@@ -2299,10 +2291,10 @@
         </x:is>
       </x:c>
       <x:c r="B14" s="331" t="n">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C14" s="331" t="n">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D14" s="319" t="n"/>
       <x:c r="E14" s="330" t="inlineStr">
@@ -2331,11 +2323,9 @@
         </x:is>
       </x:c>
       <x:c r="B15" s="331" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$300,A15)</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="C15" s="331" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$300,A15,'资产主表'!$K$6:$K$300,"已完成")+COUNTIFS('资产主表'!$C$6:$C$300,A15,'资产主表'!$K$6:$K$300,"原型已接入")</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="D15" s="319" t="n"/>
@@ -2353,11 +2343,9 @@
         </x:is>
       </x:c>
       <x:c r="B16" s="331" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$300,A16)</x:f>
         <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="331" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$300,A16,'资产主表'!$K$6:$K$300,"已完成")+COUNTIFS('资产主表'!$C$6:$C$300,A16,'资产主表'!$K$6:$K$300,"原型已接入")</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="D16" s="319" t="n"/>
@@ -2375,11 +2363,9 @@
         </x:is>
       </x:c>
       <x:c r="B17" s="331" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$300,A17)</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="C17" s="331" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$300,A17,'资产主表'!$K$6:$K$300,"已完成")+COUNTIFS('资产主表'!$C$6:$C$300,A17,'资产主表'!$K$6:$K$300,"原型已接入")</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="D17" s="319" t="n"/>
@@ -2397,11 +2383,9 @@
         </x:is>
       </x:c>
       <x:c r="B18" s="331" t="n">
-        <x:f>COUNTIF('资产主表'!$C$6:$C$300,A18)</x:f>
         <x:v>57</x:v>
       </x:c>
       <x:c r="C18" s="331" t="n">
-        <x:f>COUNTIFS('资产主表'!$C$6:$C$300,A18,'资产主表'!$K$6:$K$300,"已完成")+COUNTIFS('资产主表'!$C$6:$C$300,A18,'资产主表'!$K$6:$K$300,"原型已接入")</x:f>
         <x:v>44</x:v>
       </x:c>
       <x:c r="D18" s="319" t="n"/>
@@ -2649,10 +2633,9 @@
           <x:t xml:space="preserve">v001</x:t>
         </x:is>
       </x:c>
-      <x:c r="P5" s="190" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">根节点=基地99层_美术布置层(Node3D)；子Prefab=8；2026-08-18扫描补登记资产主表</x:t>
-        </x:is>
+      <x:c r="P5" s="190" t="str">
+        <x:v>根节点=基地99层_美术布置层(Node3D)；子Prefab=8；2026-08-18扫描补登记资产主表
+2026-09-04：子Prefab新增 assets/art/environments/base_facility_3d/runtime/env_base99_floor_visuals_v017/env_base99_floor_visuals_root_top3d_v001.tscn；一层地板保留18块普通板+18块铆钉板复用，V017只叠加无碰撞深化覆层与二层面层。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="66" customHeight="1">
@@ -6505,13 +6488,13 @@
         <x:v>99层基地楼中楼</x:v>
       </x:c>
       <x:c r="N57" s="136" t="str">
-        <x:v>正式美术已接入</x:v>
+        <x:v>未在正式基地布局实例化（保留回滚）</x:v>
       </x:c>
       <x:c r="O57" s="136" t="str">
-        <x:v>v003</x:v>
+        <x:v>已完成，未接入</x:v>
       </x:c>
       <x:c r="P57" s="136" t="str">
-        <x:v>Blender母版v005；660/660面PaletteUV有效；边缘共面数0；视觉/碰撞/功能分离。</x:v>
+        <x:v>Blender母版v005；660/660面PaletteUV有效；边缘共面数0；视觉/碰撞/功能分离。2026-09-04：旧阁楼架实例从基地布局撤下，资产文件保留回滚。</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="78" customHeight="1">
@@ -6580,20 +6563,14 @@
           <x:t xml:space="preserve">99层基地一楼至楼中楼</x:t>
         </x:is>
       </x:c>
-      <x:c r="N58" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">正式美术已接入</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O58" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">v004</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P58" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">由91个可编辑源组件重建；踏步/斜梁/平台/导光条齐全；转角扶手不穿插；三段行走形状接缝齐平并重叠0.04m。</x:t>
-        </x:is>
+      <x:c r="N58" s="136" t="str">
+        <x:v>未在正式基地布局实例化（保留回滚）</x:v>
+      </x:c>
+      <x:c r="O58" s="136" t="str">
+        <x:v>已完成，未接入</x:v>
+      </x:c>
+      <x:c r="P58" s="136" t="str">
+        <x:v>由91个可编辑源组件重建；踏步/斜梁/平台/导光条齐全；转角扶手不穿插；三段行走形状接缝齐平并重叠0.04m。2026-09-04：旧L型楼梯实例从基地布局撤下，资产文件保留回滚。</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="78" customHeight="1">
@@ -6719,13 +6696,13 @@
         <x:v>99层基地楼中楼下方</x:v>
       </x:c>
       <x:c r="N60" t="str">
-        <x:v>正式美术已接入</x:v>
+        <x:v>未在正式基地布局实例化（保留回滚）</x:v>
       </x:c>
       <x:c r="O60" t="str">
-        <x:v>v003</x:v>
+        <x:v>已完成，未接入</x:v>
       </x:c>
       <x:c r="P60" t="str">
-        <x:v>Blender源文件重导；六条高低位物理射线命中；北侧由基地外墙封闭；v002保留回滚。</x:v>
+        <x:v>Blender源文件重导；六条高低位物理射线命中；北侧由基地外墙封闭；v002保留回滚。2026-09-04：下方工业铁门实例及其永久碰撞从基地布局撤下，资产文件保留回滚。</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -6776,6 +6753,154 @@
       </x:c>
       <x:c r="P61" t="str">
         <x:v>通信区(30.5,34,9.5,10.5)位于东北角；棚屋区(7.5,27.5,21,17.5)位于其西侧；种植区(-24,22,12.5,20)；温室只阻挡立柱、太阳能板薄斜面、圆形设施圆柱碰撞；31,461面PaletteUV严格验收通过；Blend SHA256=d5f6c949f89c9aa863f37e41840d23b1308fa03abe024aa93005b421a778a38f；v015保留回滚。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="str">
+        <x:v>ENV-BASE99-FLOOR-DETAILS-V017</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>基地99层完整地板替换 V021</x:v>
+      </x:c>
+      <x:c r="C62" t="str">
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_root_top3d_v003.tscn</x:v>
+      </x:c>
+      <x:c r="D62" t="str">
+        <x:v>assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_visual_top3d_v003.glb</x:v>
+      </x:c>
+      <x:c r="E62" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（v020）</x:v>
+      </x:c>
+      <x:c r="F62" t="str">
+        <x:v>完整36块新地板表现替换旧普通/铆钉MultiMesh；FloorSupport承重规格不变。</x:v>
+      </x:c>
+      <x:c r="G62" t="str">
+        <x:v>src/world3d/DungeonRoom3D.gd</x:v>
+      </x:c>
+      <x:c r="H62" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="I62" t="str">
+        <x:v>TowerFloorStage3D</x:v>
+      </x:c>
+      <x:c r="J62" t="str">
+        <x:v>无；仅视觉</x:v>
+      </x:c>
+      <x:c r="K62" t="str">
+        <x:v>30×30m；6×6×5m；2网格；4材质表面；498,920三角面；无内置碰撞</x:v>
+      </x:c>
+      <x:c r="L62" t="str">
+        <x:v>layout_origin；Blender +Y北 / Godot -Z北；根Y=0</x:v>
+      </x:c>
+      <x:c r="M62" t="str">
+        <x:v>99层基地一层</x:v>
+      </x:c>
+      <x:c r="N62" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="O62" t="str">
+        <x:v>v003</x:v>
+      </x:c>
+      <x:c r="P62" t="str">
+        <x:v>Blender源文件=base_facility_runtime_layout_hq_v020.blend；Blender版本=v020；完整36块结构砖与深化内容导入；旧普通/铆钉MultiMesh视觉已移除；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；共面重叠0、朝下三角面0；verify_base99_floor_visuals_v021与verify_base99_floor_player_collision_flow通过。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="str">
+        <x:v>ENV-BASE99-LOFT-FLOOR-FINISH-V017</x:v>
+      </x:c>
+      <x:c r="B63" t="str">
+        <x:v>基地99层二层地板面层 V020</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_loft_floor_finish_v020/env_base99_loft_floor_finish_v020_root_top3d_v002.tscn</x:v>
+      </x:c>
+      <x:c r="D63" t="str">
+        <x:v>assets/art/environments/base_facility_3d/components/env_base99_loft_floor_finish_v020/env_base99_loft_floor_finish_v020_visual_top3d_v002.glb</x:v>
+      </x:c>
+      <x:c r="E63" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（v020）</x:v>
+      </x:c>
+      <x:c r="F63" t="str">
+        <x:v>仅表现；Blender V020新增二楼地板面层保持不动；旧阁楼承重/栏杆、L型楼梯和下方铁门已撤出。</x:v>
+      </x:c>
+      <x:c r="G63" t="str">
+        <x:v>src/world3d/DungeonRoom3D.gd</x:v>
+      </x:c>
+      <x:c r="H63" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="I63" t="str">
+        <x:v>无；仅视觉（旧楼中楼承重碰撞已随架体撤下）</x:v>
+      </x:c>
+      <x:c r="J63" t="str">
+        <x:v>无；仅视觉</x:v>
+      </x:c>
+      <x:c r="K63" t="str">
+        <x:v>19.6×9.6×0.108m；1网格；2材质表面；206三角面；无内置碰撞</x:v>
+      </x:c>
+      <x:c r="L63" t="str">
+        <x:v>layout_origin；装配层Y=-1m，将Blender Z=6对齐Godot Y=5</x:v>
+      </x:c>
+      <x:c r="M63" t="str">
+        <x:v>99层基地北侧20×10米楼中楼</x:v>
+      </x:c>
+      <x:c r="N63" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="O63" t="str">
+        <x:v>v002</x:v>
+      </x:c>
+      <x:c r="P63" t="str">
+        <x:v>Blender源文件=base_facility_runtime_layout_hq_v020.blend；Blender版本=v020；二楼新增地板保持不动，不新增碰撞；共面重叠0、朝下三角面0；tests/verification/verify_base99_floor_visuals_v021.tscn通过。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str">
+        <x:v>ENV-BASE99-FLOOR-VISUAL-LAYOUT-V017</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>基地99层完整地板表现装配 V021</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_floor_visuals_v021/env_base99_floor_visuals_root_top3d_v003.tscn</x:v>
+      </x:c>
+      <x:c r="D64"/>
+      <x:c r="E64" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（v020）</x:v>
+      </x:c>
+      <x:c r="F64" t="str">
+        <x:v>完整一层新地板与二层面层的运行时装配；由基地美术布局直接实例化。</x:v>
+      </x:c>
+      <x:c r="G64" t="str">
+        <x:v>src/world3d/DungeonRoom3D.gd</x:v>
+      </x:c>
+      <x:c r="H64" t="str">
+        <x:v>无</x:v>
+      </x:c>
+      <x:c r="I64" t="str">
+        <x:v>既有TowerFloorStage3D与楼中楼Prefab</x:v>
+      </x:c>
+      <x:c r="J64" t="str">
+        <x:v>无；仅视觉</x:v>
+      </x:c>
+      <x:c r="K64" t="str">
+        <x:v>一层30×30m；二层20×10m；无内置碰撞</x:v>
+      </x:c>
+      <x:c r="L64" t="str">
+        <x:v>layout_origin；二层面层Y=-1m</x:v>
+      </x:c>
+      <x:c r="M64" t="str">
+        <x:v>99层基地美术布局</x:v>
+      </x:c>
+      <x:c r="N64" t="str">
+        <x:v>正式美术已接入</x:v>
+      </x:c>
+      <x:c r="O64" t="str">
+        <x:v>v003</x:v>
+      </x:c>
+      <x:c r="P64" t="str">
+        <x:v>Blender源文件=base_facility_runtime_layout_hq_v020.blend；Blender版本=v020；一层替换旧MultiMesh，二层保留V020面层；FloorSupport碰撞保持不变。2026-09-04：旧5米阁楼架、L型楼梯和下方工业铁门已从基地布局撤下；tests/verification/verify_base99_mezzanine_placement_removal.tscn通过。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -22835,336 +22960,228 @@
       <x:c r="X112" s="138"/>
     </x:row>
     <x:row r="113" ht="155" customHeight="1">
-      <x:c r="A113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CHR-PLY-CAPSULE01-3D</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">方形猫角色3D根组件</x:t>
-        </x:is>
+      <x:c r="A113" s="306" t="str">
+        <x:v>ENV-BASE99-FLOOR-DETAILS-V017</x:v>
+      </x:c>
+      <x:c r="B113" s="306" t="str">
+        <x:v>基地99层完整地板替换 V021</x:v>
       </x:c>
       <x:c r="C113" s="306" t="str">
-        <x:v>角色</x:v>
-      </x:c>
-      <x:c r="D113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">player</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">player_capsule01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">root_3d</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CHR-PLY-CAPSULE01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">俯视3D</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">default</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3D玩家场景</x:t>
-        </x:is>
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D113" s="306" t="str">
+        <x:v>environment_module_3d</x:v>
+      </x:c>
+      <x:c r="E113" s="306" t="str">
+        <x:v>base99_floor_full_replacement_v021</x:v>
+      </x:c>
+      <x:c r="F113" s="306" t="str">
+        <x:v>full_floor_visual_replacement</x:v>
+      </x:c>
+      <x:c r="G113" s="306" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H113" s="306" t="str">
+        <x:v>Top3D / local -Z 正面</x:v>
+      </x:c>
+      <x:c r="I113" s="306" t="str">
+        <x:v>default / visual_only</x:v>
+      </x:c>
+      <x:c r="J113" s="306" t="str">
+        <x:v>99层基地地面表现</x:v>
       </x:c>
       <x:c r="K113" s="306" t="str">
-        <x:v>原型已接入</x:v>
-      </x:c>
-      <x:c r="L113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">P0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">v001</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PackedScene/程序材质</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">scenes/Player3D.tscn</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">胶囊;防护服;3D;模块角色</x:t>
-        </x:is>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L113" s="306" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M113" s="306" t="str">
+        <x:v>v003</x:v>
+      </x:c>
+      <x:c r="N113" s="306" t="str">
+        <x:v>30×30m；6×6×5m；2网格；4材质表面；498,920三角面；无内置碰撞</x:v>
+      </x:c>
+      <x:c r="O113" s="306" t="str">
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_root_top3d_v003.tscn</x:v>
+      </x:c>
+      <x:c r="P113" s="306" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json；scripts/blender/export_base_facility_v021_floor_replacement.py；tests/verification/verify_base99_floor_visuals_v021.tscn</x:v>
+      </x:c>
+      <x:c r="Q113" s="306" t="str">
+        <x:v>基地99层;完整地板替换;V021;PaletteUV;visual_only;旧MultiMesh已移除;无重叠</x:v>
       </x:c>
       <x:c r="R113" s="306" t="str">
-        <x:f>LOWER(TRIM(C113)&amp;"|"&amp;TRIM(D113)&amp;"|"&amp;TRIM(E113)&amp;"|"&amp;TRIM(F113)&amp;"|"&amp;TRIM(H113)&amp;"|"&amp;TRIM(I113))</x:f>
-        <x:v>角色|player|player_capsule01|root_3d|俯视3d|default</x:v>
+        <x:v>场景|environment_module_3d|base99_floor_full_replacement_v021|full_floor_visual_replacement|top3d / local -z 正面|default / visual_only</x:v>
       </x:c>
       <x:c r="S113" s="306" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$300,R113)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$419,R113)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T113" s="306" t="str">
-        <x:v>2802d5526c3eb7a8ab01a09bb9d2115c7dc531563442527460ddfd71870cbdec</x:v>
-      </x:c>
-      <x:c r="U113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
+        <x:v>aee79560972e7d301486cd1dc1388259105ae10a47a3a77045959fd8e29b0498</x:v>
+      </x:c>
+      <x:c r="U113" s="306" t="str">
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="V113" s="307" t="n">
-        <x:v>46264</x:v>
-      </x:c>
-      <x:c r="W113" s="306" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">原创程序几何</x:t>
-        </x:is>
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W113" s="306" t="str">
+        <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X113" s="306" t="str">
-        <x:v>玩家随身三灯通过 layer 1/2 隔离避免自身投影；角色网格恢复外部太阳光/室内灯投影，GI保持关闭；tests/verification/verify_tower_lighting_wall_combat_regressions.tscn
-2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_player3d_avatar_bounds；verify_player3d_weapon_pose_collision_flow；SHA cf0b3b648d56→2802d5526c3e。</x:v>
+        <x:v>GLB SHA256=6655e4322cd654e533e53670fb1e6611ce65818068de016faaea1b59ffb6835a；基础18普通板+18铆钉板保持复用；V017独占细节聚合为2网格，承重碰撞不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
-      <x:c r="A114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CHR-PLY-CAPSULE01-BODY-3D</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">方形猫角色3D身躯</x:t>
-        </x:is>
+      <x:c r="A114" s="136" t="str">
+        <x:v>ENV-BASE99-LOFT-FLOOR-FINISH-V017</x:v>
+      </x:c>
+      <x:c r="B114" s="136" t="str">
+        <x:v>基地99层二层地板面层 V020</x:v>
       </x:c>
       <x:c r="C114" s="136" t="str">
-        <x:v>角色</x:v>
-      </x:c>
-      <x:c r="D114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">player</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">player_capsule01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">body_3d</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CHR-PLY-CAPSULE01-3D</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">俯视3D</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">default</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3D玩家场景</x:t>
-        </x:is>
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D114" s="136" t="str">
+        <x:v>environment_module_3d</x:v>
+      </x:c>
+      <x:c r="E114" s="136" t="str">
+        <x:v>base99_loft_floor_finish_v020</x:v>
+      </x:c>
+      <x:c r="F114" s="136" t="str">
+        <x:v>loft_floor_finish_overlay</x:v>
+      </x:c>
+      <x:c r="G114" s="136" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H114" s="136" t="str">
+        <x:v>Top3D / local -Z 正面</x:v>
+      </x:c>
+      <x:c r="I114" s="136" t="str">
+        <x:v>default / visual_only</x:v>
+      </x:c>
+      <x:c r="J114" s="136" t="str">
+        <x:v>99层基地楼中楼地面表现</x:v>
       </x:c>
       <x:c r="K114" s="136" t="str">
-        <x:v>原型已接入</x:v>
-      </x:c>
-      <x:c r="L114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">P0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">v001</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CapsuleMesh节点</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VisualRoot/Body</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">身躯;防护服;无腿;3D</x:t>
-        </x:is>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L114" s="136" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M114" s="136" t="str">
+        <x:v>v002</x:v>
+      </x:c>
+      <x:c r="N114" s="136" t="str">
+        <x:v>19.6×9.6×0.108m；1网格；2材质表面；206三角面；无内置碰撞</x:v>
+      </x:c>
+      <x:c r="O114" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_loft_floor_finish_v020/env_base99_loft_floor_finish_v020_root_top3d_v002.tscn</x:v>
+      </x:c>
+      <x:c r="P114" s="136" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_loft_floor_finish_v020/env_base99_loft_floor_finish_v020_visual_top3d_v002.glb；scripts/blender/export_base_facility_v020_floor_visuals.py；tests/verification/verify_base99_floor_visuals_v020.tscn</x:v>
+      </x:c>
+      <x:c r="Q114" s="136" t="str">
+        <x:v>基地99层;二层地板;V020;PaletteUV;visual_only;无重叠</x:v>
       </x:c>
       <x:c r="R114" s="136" t="str">
-        <x:f>LOWER(TRIM(C114)&amp;"|"&amp;TRIM(D114)&amp;"|"&amp;TRIM(E114)&amp;"|"&amp;TRIM(F114)&amp;"|"&amp;TRIM(H114)&amp;"|"&amp;TRIM(I114))</x:f>
-        <x:v>角色|player|player_capsule01|body_3d|俯视3d|default</x:v>
+        <x:v>场景|environment_module_3d|base99_loft_floor_finish_v020|loft_floor_finish_overlay|top3d / local -z 正面|default / visual_only</x:v>
       </x:c>
       <x:c r="S114" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$300,R114)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$419,R114)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T114" s="136" t="str">
-        <x:v>2802d5526c3eb7a8ab01a09bb9d2115c7dc531563442527460ddfd71870cbdec</x:v>
-      </x:c>
-      <x:c r="U114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
+        <x:v>aee79560972e7d301486cd1dc1388259105ae10a47a3a77045959fd8e29b0498</x:v>
+      </x:c>
+      <x:c r="U114" s="136" t="str">
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="V114" s="137" t="n">
-        <x:v>46264</x:v>
-      </x:c>
-      <x:c r="W114" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">原创程序几何</x:t>
-        </x:is>
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W114" s="136" t="str">
+        <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X114" s="136" t="str">
-        <x:v>VisualRoot/Body：BoxMesh身躯、BellyPatch、圆形TailStub；v0.1方形猫原型；tests/verification/verify_player3d_diy_flow / gallery flow / visual PASS
-2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_player3d_avatar_bounds；verify_player3d_weapon_pose_collision_flow；SHA cf0b3b648d56→2802d5526c3e。</x:v>
+        <x:v>GLB SHA256=bf66319f75f5cac1c301dbfc09e4e7fe4ec0f518b7ee7dadb8e7068b94a2939c；运行时Y=-1m偏移；V020新增二楼地板面层保留。2026-09-04：旧阁楼承重/栏杆、L型楼梯和下方铁门实例已从基地布局撤下；本资产仍为仅视觉表现，不新增碰撞。</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CHR-PLY-CAPSULE01-HEAD-3D</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">方形猫角色3D头部</x:t>
-        </x:is>
+      <x:c r="A115" s="136" t="str">
+        <x:v>ENV-BASE99-FLOOR-VISUAL-LAYOUT-V017</x:v>
+      </x:c>
+      <x:c r="B115" s="136" t="str">
+        <x:v>基地99层完整地板表现装配 V021</x:v>
       </x:c>
       <x:c r="C115" s="136" t="str">
-        <x:v>角色</x:v>
-      </x:c>
-      <x:c r="D115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">player</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">player_capsule01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">head_3d</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CHR-PLY-CAPSULE01-3D</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">俯视3D</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">default</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3D玩家场景</x:t>
-        </x:is>
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D115" s="136" t="str">
+        <x:v>environment_module_3d</x:v>
+      </x:c>
+      <x:c r="E115" s="136" t="str">
+        <x:v>base99_floor_visual_layout_v021</x:v>
+      </x:c>
+      <x:c r="F115" s="136" t="str">
+        <x:v>floor_visual_assembly</x:v>
+      </x:c>
+      <x:c r="G115" s="136" t="str">
+        <x:v>ENV-BASE99-ART-LAYOUT-3D</x:v>
+      </x:c>
+      <x:c r="H115" s="136" t="str">
+        <x:v>Top3D / local -Z 正面</x:v>
+      </x:c>
+      <x:c r="I115" s="136" t="str">
+        <x:v>default / visual_only</x:v>
+      </x:c>
+      <x:c r="J115" s="136" t="str">
+        <x:v>99层基地美术布局</x:v>
       </x:c>
       <x:c r="K115" s="136" t="str">
-        <x:v>原型已接入</x:v>
-      </x:c>
-      <x:c r="L115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">P0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">v001</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SphereMesh节点</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">assets/art/characters/player/chr_player_capsule01_3d/chr_player_capsule01_root_top3d_v001.tscn</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VisualRoot/Head</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">头壳;单传感器;3D</x:t>
-        </x:is>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L115" s="136" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M115" s="136" t="str">
+        <x:v>v003</x:v>
+      </x:c>
+      <x:c r="N115" s="136" t="str">
+        <x:v>一层30×30m + 二层20×10m；无内置碰撞</x:v>
+      </x:c>
+      <x:c r="O115" s="136" t="str">
+        <x:v>assets/art/environments/base_facility_3d/runtime/env_base99_floor_visuals_v021/env_base99_floor_visuals_root_top3d_v003.tscn</x:v>
+      </x:c>
+      <x:c r="P115" s="136" t="str">
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/runtime/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_root_top3d_v003.tscn；assets/art/environments/base_facility_3d/runtime/env_base99_loft_floor_finish_v020/env_base99_loft_floor_finish_v020_root_top3d_v002.tscn；tests/verification/verify_base99_floor_visuals_v021.tscn</x:v>
+      </x:c>
+      <x:c r="Q115" s="136" t="str">
+        <x:v>基地99层;完整地板表现装配;V021;visual_only;旧MultiMesh已移除</x:v>
       </x:c>
       <x:c r="R115" s="136" t="str">
-        <x:f>LOWER(TRIM(C115)&amp;"|"&amp;TRIM(D115)&amp;"|"&amp;TRIM(E115)&amp;"|"&amp;TRIM(F115)&amp;"|"&amp;TRIM(H115)&amp;"|"&amp;TRIM(I115))</x:f>
-        <x:v>角色|player|player_capsule01|head_3d|俯视3d|default</x:v>
+        <x:v>场景|environment_module_3d|base99_floor_visual_layout_v021|floor_visual_assembly|top3d / local -z 正面|default / visual_only</x:v>
       </x:c>
       <x:c r="S115" s="136" t="str">
-        <x:f>IF(COUNTIF($R$6:$R$300,R115)&gt;1,"重复","唯一")</x:f>
+        <x:f>IF(COUNTIF($R$6:$R$419,R115)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
       <x:c r="T115" s="136" t="str">
-        <x:v>2802d5526c3eb7a8ab01a09bb9d2115c7dc531563442527460ddfd71870cbdec</x:v>
-      </x:c>
-      <x:c r="U115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Codex</x:t>
-        </x:is>
+        <x:v>aee79560972e7d301486cd1dc1388259105ae10a47a3a77045959fd8e29b0498</x:v>
+      </x:c>
+      <x:c r="U115" s="136" t="str">
+        <x:v>Codex</x:v>
       </x:c>
       <x:c r="V115" s="137" t="n">
-        <x:v>46264</x:v>
-      </x:c>
-      <x:c r="W115" s="136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">原创程序几何</x:t>
-        </x:is>
+        <x:v>46269</x:v>
+      </x:c>
+      <x:c r="W115" s="136" t="str">
+        <x:v>项目现有Godot资产</x:v>
       </x:c>
       <x:c r="X115" s="136" t="str">
-        <x:v>VisualRoot/Head：BoxMesh方头；Eyes双矩形眼；Ears双三角耳；v0.1方形猫原型；tests/verification/verify_player3d_diy_flow / gallery flow / visual PASS
-2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_player3d_avatar_bounds；verify_player3d_weapon_pose_collision_flow；SHA cf0b3b648d56→2802d5526c3e。</x:v>
+        <x:v>运行时布局接入点；一层保持Blender V021完整地板替换与既有FloorSupport碰撞；二层保留Blender V020新增地板面层。2026-09-04：旧5米阁楼架、L型楼梯和下方工业铁门已从基地布局撤下，资产文件保留回滚。</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -36828,7 +36845,10 @@
       <x:c r="X240" s="136" t="str">
         <x:v>主场景可编辑布局；现含8个设施及楼板、L梯、外门小梯三个结构Prefab，位置旋转可在tscn直接调整。
 2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_base99_floor_player_collision_flow；verify_base_facility_interaction_zones；SHA 2ecff00457fc→9d7f7b7d6699。
-2026-09-02 HQ-v003：新增30×30m高品质Blender微缩基地母版；20×10m北侧6m阁楼、15×30m东西主通道地面净空、南侧仓储/能源/供水区和240帧循环动效。复用现有墙/地板身份，设施作为独立组件重制；4个共享材质，275002/275002面PaletteUV严格验收通过。Blend SHA256=614039f9aae4。当前仅为Blender美术母版，未替换Godot运行时TSCN、GLB、碰撞或交互。</x:v>
+2026-09-02 HQ-v003：新增30×30m高品质Blender微缩基地母版；20×10m北侧6m阁楼、15×30m东西主通道地面净空、南侧仓储/能源/供水区和240帧循环动效。复用现有墙/地板身份，设施作为独立组件重制；4个共享材质，275002/275002面PaletteUV严格验收通过。Blend SHA256=614039f9aae4。当前仅为Blender美术母版，未替换Godot运行时TSCN、GLB、碰撞或交互。
+2026-09-04：已挂载 assets/art/environments/base_facility_3d/runtime/env_base99_floor_visuals_v017/env_base99_floor_visuals_root_top3d_v001.tscn。基础地砖维持18块 ENV-BASE99-FLOOR-PLAIN-5M 与18块 ENV-BASE99-FLOOR-RIVET-5M 的棋盘格复用；V017新增一层深化覆层与二层面层，均无玩法碰撞。
+2026-09-04 V020：地板表现装配已切换至 env_base99_floor_visuals_v020/env_base99_floor_visuals_root_top3d_v002.tscn；源文件 base_facility_runtime_layout_hq_v020.blend（Blender v020）；V017输出保留回滚。
+2026-09-04 V021：完整新地板装配已切换至 assets/art/environments/base_facility_3d/runtime/env_base99_floor_visuals_v021/env_base99_floor_visuals_root_top3d_v003.tscn；旧DungeonRoom3D普通/铆钉MultiMesh视觉不再生成，FloorSupport碰撞规格保持不变。</x:v>
       </x:c>
     </x:row>
     <x:row r="241">
@@ -44347,7 +44367,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K320" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L320" t="str">
         <x:v>P0</x:v>
@@ -44362,7 +44382,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r01_c01/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P320" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q320" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r01_c01;PaletteUV</x:v>
@@ -44388,7 +44408,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X320" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c01；对象 22；中心 (-12.500, -12.500, -0.076)m；朝向 Blender +Y north；预期导出 tile_r01_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c01；对象 22；中心 (-12.500, -12.500, -0.076)m；朝向 Blender +Y north；预期导出 tile_r01_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="321" ht="54" customHeight="1">
@@ -44423,7 +44446,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K321" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L321" t="str">
         <x:v>P0</x:v>
@@ -44438,7 +44461,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r01_c02/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P321" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q321" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r01_c02;PaletteUV</x:v>
@@ -44464,7 +44487,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X321" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c02；对象 35；中心 (-7.518, -12.500, -0.066)m；朝向 Blender +Y north；预期导出 tile_r01_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c02；对象 35；中心 (-7.518, -12.500, -0.066)m；朝向 Blender +Y north；预期导出 tile_r01_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="322" ht="54" customHeight="1">
@@ -44499,7 +44525,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K322" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L322" t="str">
         <x:v>P0</x:v>
@@ -44514,7 +44540,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r01_c03/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P322" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q322" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r01_c03;PaletteUV</x:v>
@@ -44540,7 +44566,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X322" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c03；对象 33；中心 (-2.518, -12.500, -0.068)m；朝向 Blender +Y north；预期导出 tile_r01_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c03；对象 33；中心 (-2.518, -12.500, -0.068)m；朝向 Blender +Y north；预期导出 tile_r01_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="323" ht="54" customHeight="1">
@@ -44575,7 +44604,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K323" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L323" t="str">
         <x:v>P0</x:v>
@@ -44590,7 +44619,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r01_c04/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P323" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q323" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r01_c04;PaletteUV</x:v>
@@ -44616,7 +44645,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X323" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c04；对象 23；中心 (2.482, -12.500, -0.076)m；朝向 Blender +Y north；预期导出 tile_r01_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c04；对象 23；中心 (2.482, -12.500, -0.076)m；朝向 Blender +Y north；预期导出 tile_r01_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="324" ht="54" customHeight="1">
@@ -44651,7 +44683,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K324" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L324" t="str">
         <x:v>P0</x:v>
@@ -44666,7 +44698,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r01_c05/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P324" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q324" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r01_c05;PaletteUV</x:v>
@@ -44692,7 +44724,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X324" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c05；对象 35；中心 (7.482, -12.500, -0.066)m；朝向 Blender +Y north；预期导出 tile_r01_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c05；对象 35；中心 (7.482, -12.500, -0.066)m；朝向 Blender +Y north；预期导出 tile_r01_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="325" ht="54" customHeight="1">
@@ -44727,7 +44762,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K325" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L325" t="str">
         <x:v>P0</x:v>
@@ -44742,7 +44777,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r01_c06/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P325" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q325" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r01_c06;PaletteUV</x:v>
@@ -44768,7 +44803,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X325" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c06；对象 23；中心 (12.482, -12.500, -0.076)m；朝向 Blender +Y north；预期导出 tile_r01_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r01_c06；对象 23；中心 (12.482, -12.500, -0.076)m；朝向 Blender +Y north；预期导出 tile_r01_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="326" ht="54" customHeight="1">
@@ -44803,7 +44841,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K326" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L326" t="str">
         <x:v>P0</x:v>
@@ -44818,7 +44856,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r02_c01/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P326" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q326" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r02_c01;PaletteUV</x:v>
@@ -44844,7 +44882,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X326" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c01；对象 24；中心 (-12.500, -7.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r02_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c01；对象 24；中心 (-12.500, -7.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r02_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="327" ht="54" customHeight="1">
@@ -44879,7 +44920,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K327" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L327" t="str">
         <x:v>P0</x:v>
@@ -44894,7 +44935,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r02_c02/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P327" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q327" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r02_c02;PaletteUV</x:v>
@@ -44920,7 +44961,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X327" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c02；对象 38；中心 (-7.518, -7.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r02_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c02；对象 38；中心 (-7.518, -7.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r02_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="328" ht="54" customHeight="1">
@@ -44955,7 +44999,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K328" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L328" t="str">
         <x:v>P0</x:v>
@@ -44970,7 +45014,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r02_c03/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P328" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q328" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r02_c03;PaletteUV</x:v>
@@ -44996,7 +45040,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X328" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c03；对象 44；中心 (-2.518, -7.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r02_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c03；对象 44；中心 (-2.518, -7.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r02_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="329" ht="54" customHeight="1">
@@ -45031,7 +45078,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K329" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L329" t="str">
         <x:v>P0</x:v>
@@ -45046,7 +45093,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r02_c04/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P329" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q329" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r02_c04;PaletteUV</x:v>
@@ -45072,7 +45119,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X329" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c04；对象 36；中心 (2.405, -7.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r02_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c04；对象 36；中心 (2.405, -7.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r02_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="330" ht="54" customHeight="1">
@@ -45107,7 +45157,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K330" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L330" t="str">
         <x:v>P0</x:v>
@@ -45122,7 +45172,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r02_c05/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P330" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q330" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r02_c05;PaletteUV</x:v>
@@ -45148,7 +45198,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X330" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c05；对象 46；中心 (7.482, -7.518, -0.068)m；朝向 Blender +Y north；预期导出 tile_r02_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c05；对象 46；中心 (7.482, -7.518, -0.068)m；朝向 Blender +Y north；预期导出 tile_r02_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="331" ht="54" customHeight="1">
@@ -45183,7 +45236,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K331" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L331" t="str">
         <x:v>P0</x:v>
@@ -45198,7 +45251,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r02_c06/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P331" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q331" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r02_c06;PaletteUV</x:v>
@@ -45224,7 +45277,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X331" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c06；对象 37；中心 (12.482, -7.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r02_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r02_c06；对象 37；中心 (12.482, -7.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r02_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="332" ht="54" customHeight="1">
@@ -45259,7 +45315,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K332" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L332" t="str">
         <x:v>P0</x:v>
@@ -45274,7 +45330,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r03_c01/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P332" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q332" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r03_c01;PaletteUV</x:v>
@@ -45300,7 +45356,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X332" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c01；对象 39；中心 (-12.500, -2.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r03_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c01；对象 39；中心 (-12.500, -2.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r03_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="333" ht="54" customHeight="1">
@@ -45335,7 +45394,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K333" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L333" t="str">
         <x:v>P0</x:v>
@@ -45350,7 +45409,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r03_c02/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P333" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q333" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r03_c02;PaletteUV</x:v>
@@ -45376,7 +45435,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X333" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c02；对象 43；中心 (-7.518, -2.518, -0.068)m；朝向 Blender +Y north；预期导出 tile_r03_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c02；对象 43；中心 (-7.518, -2.518, -0.068)m；朝向 Blender +Y north；预期导出 tile_r03_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="334" ht="54" customHeight="1">
@@ -45411,7 +45473,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K334" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L334" t="str">
         <x:v>P0</x:v>
@@ -45426,7 +45488,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r03_c03/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P334" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q334" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r03_c03;PaletteUV</x:v>
@@ -45452,7 +45514,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X334" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c03；对象 24；中心 (-2.518, -2.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r03_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c03；对象 24；中心 (-2.518, -2.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r03_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="335" ht="54" customHeight="1">
@@ -45487,7 +45552,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K335" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L335" t="str">
         <x:v>P0</x:v>
@@ -45502,7 +45567,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r03_c04/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P335" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q335" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r03_c04;PaletteUV</x:v>
@@ -45528,7 +45593,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X335" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c04；对象 42；中心 (2.482, -2.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r03_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c04；对象 42；中心 (2.482, -2.518, -0.066)m；朝向 Blender +Y north；预期导出 tile_r03_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="336" ht="54" customHeight="1">
@@ -45563,7 +45631,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K336" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L336" t="str">
         <x:v>P0</x:v>
@@ -45578,7 +45646,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r03_c05/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P336" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q336" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r03_c05;PaletteUV</x:v>
@@ -45604,7 +45672,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X336" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c05；对象 45；中心 (7.482, -2.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r03_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c05；对象 45；中心 (7.482, -2.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r03_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="337" ht="54" customHeight="1">
@@ -45639,7 +45710,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K337" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L337" t="str">
         <x:v>P0</x:v>
@@ -45654,7 +45725,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r03_c06/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P337" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q337" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r03_c06;PaletteUV</x:v>
@@ -45680,7 +45751,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X337" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c06；对象 24；中心 (12.482, -2.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r03_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r03_c06；对象 24；中心 (12.482, -2.518, -0.076)m；朝向 Blender +Y north；预期导出 tile_r03_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="338" ht="54" customHeight="1">
@@ -45715,7 +45789,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K338" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L338" t="str">
         <x:v>P0</x:v>
@@ -45730,7 +45804,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r04_c01/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P338" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q338" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r04_c01;PaletteUV</x:v>
@@ -45756,7 +45830,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X338" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c01；对象 23；中心 (-12.500, 2.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r04_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c01；对象 23；中心 (-12.500, 2.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r04_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="339" ht="54" customHeight="1">
@@ -45791,7 +45868,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K339" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L339" t="str">
         <x:v>P0</x:v>
@@ -45806,7 +45883,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r04_c02/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P339" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q339" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r04_c02;PaletteUV</x:v>
@@ -45832,7 +45909,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X339" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c02；对象 42；中心 (-7.518, 2.482, -0.066)m；朝向 Blender +Y north；预期导出 tile_r04_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c02；对象 42；中心 (-7.518, 2.482, -0.066)m；朝向 Blender +Y north；预期导出 tile_r04_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="340" ht="54" customHeight="1">
@@ -45867,7 +45947,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K340" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L340" t="str">
         <x:v>P0</x:v>
@@ -45882,7 +45962,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r04_c03/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P340" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q340" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r04_c03;PaletteUV</x:v>
@@ -45908,7 +45988,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X340" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c03；对象 26；中心 (-2.518, 2.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r04_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c03；对象 26；中心 (-2.518, 2.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r04_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="341" ht="54" customHeight="1">
@@ -45943,7 +46026,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K341" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L341" t="str">
         <x:v>P0</x:v>
@@ -45958,7 +46041,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r04_c04/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P341" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q341" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r04_c04;PaletteUV</x:v>
@@ -45984,7 +46067,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X341" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c04；对象 62；中心 (2.482, 2.482, -0.054)m；朝向 Blender +Y north；预期导出 tile_r04_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c04；对象 62；中心 (2.482, 2.482, -0.054)m；朝向 Blender +Y north；预期导出 tile_r04_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="342" ht="54" customHeight="1">
@@ -46019,7 +46105,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K342" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L342" t="str">
         <x:v>P0</x:v>
@@ -46034,7 +46120,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r04_c05/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P342" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q342" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r04_c05;PaletteUV</x:v>
@@ -46060,7 +46146,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X342" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c05；对象 63；中心 (6.910, 2.482, -0.053)m；朝向 Blender +Y north；预期导出 tile_r04_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c05；对象 63；中心 (6.910, 2.482, -0.053)m；朝向 Blender +Y north；预期导出 tile_r04_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="343" ht="54" customHeight="1">
@@ -46095,7 +46184,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K343" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L343" t="str">
         <x:v>P0</x:v>
@@ -46110,7 +46199,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r04_c06/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P343" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q343" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r04_c06;PaletteUV</x:v>
@@ -46136,7 +46225,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X343" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c06；对象 41；中心 (12.482, 2.482, -0.066)m；朝向 Blender +Y north；预期导出 tile_r04_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r04_c06；对象 41；中心 (12.482, 2.482, -0.066)m；朝向 Blender +Y north；预期导出 tile_r04_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="344" ht="54" customHeight="1">
@@ -46171,7 +46263,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K344" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L344" t="str">
         <x:v>P0</x:v>
@@ -46186,7 +46278,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r05_c01/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P344" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q344" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r05_c01;PaletteUV</x:v>
@@ -46212,7 +46304,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X344" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c01；对象 23；中心 (-12.500, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c01；对象 23；中心 (-12.500, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="345" ht="54" customHeight="1">
@@ -46247,7 +46342,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K345" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L345" t="str">
         <x:v>P0</x:v>
@@ -46262,7 +46357,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r05_c02/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P345" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q345" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r05_c02;PaletteUV</x:v>
@@ -46288,7 +46383,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X345" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c02；对象 24；中心 (-7.518, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c02；对象 24；中心 (-7.518, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="346" ht="54" customHeight="1">
@@ -46323,7 +46421,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K346" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L346" t="str">
         <x:v>P0</x:v>
@@ -46338,7 +46436,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r05_c03/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P346" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q346" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r05_c03;PaletteUV</x:v>
@@ -46364,7 +46462,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X346" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c03；对象 24；中心 (-2.518, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c03；对象 24；中心 (-2.518, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="347" ht="54" customHeight="1">
@@ -46399,7 +46500,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K347" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L347" t="str">
         <x:v>P0</x:v>
@@ -46414,7 +46515,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r05_c04/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P347" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q347" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r05_c04;PaletteUV</x:v>
@@ -46440,7 +46541,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X347" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c04；对象 24；中心 (2.482, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c04；对象 24；中心 (2.482, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="348" ht="54" customHeight="1">
@@ -46475,7 +46579,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K348" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L348" t="str">
         <x:v>P0</x:v>
@@ -46490,7 +46594,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r05_c05/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P348" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q348" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r05_c05;PaletteUV</x:v>
@@ -46516,7 +46620,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X348" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c05；对象 24；中心 (7.482, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c05；对象 24；中心 (7.482, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="349" ht="54" customHeight="1">
@@ -46551,7 +46658,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K349" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L349" t="str">
         <x:v>P0</x:v>
@@ -46566,7 +46673,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r05_c06/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P349" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q349" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r05_c06;PaletteUV</x:v>
@@ -46592,7 +46699,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X349" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c06；对象 24；中心 (12.482, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r05_c06；对象 24；中心 (12.482, 7.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r05_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="350" ht="54" customHeight="1">
@@ -46627,7 +46737,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K350" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L350" t="str">
         <x:v>P0</x:v>
@@ -46642,7 +46752,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r06_c01/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P350" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q350" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r06_c01;PaletteUV</x:v>
@@ -46668,7 +46778,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X350" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c01；对象 23；中心 (-12.500, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c01；对象 23；中心 (-12.500, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c01_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="351" ht="54" customHeight="1">
@@ -46703,7 +46816,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K351" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L351" t="str">
         <x:v>P0</x:v>
@@ -46718,7 +46831,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r06_c02/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P351" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q351" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r06_c02;PaletteUV</x:v>
@@ -46744,7 +46857,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X351" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c02；对象 24；中心 (-7.518, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c02；对象 24；中心 (-7.518, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c02_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="352" ht="54" customHeight="1">
@@ -46779,7 +46895,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K352" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L352" t="str">
         <x:v>P0</x:v>
@@ -46794,7 +46910,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r06_c03/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P352" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q352" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r06_c03;PaletteUV</x:v>
@@ -46820,7 +46936,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X352" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c03；对象 24；中心 (-2.518, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c03；对象 24；中心 (-2.518, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c03_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="353" ht="54" customHeight="1">
@@ -46855,7 +46974,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K353" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L353" t="str">
         <x:v>P0</x:v>
@@ -46870,7 +46989,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r06_c04/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P353" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q353" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r06_c04;PaletteUV</x:v>
@@ -46896,7 +47015,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X353" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c04；对象 24；中心 (2.482, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c04；对象 24；中心 (2.482, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c04_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="354" ht="54" customHeight="1">
@@ -46931,7 +47053,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K354" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L354" t="str">
         <x:v>P0</x:v>
@@ -46946,7 +47068,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r06_c05/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P354" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q354" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r06_c05;PaletteUV</x:v>
@@ -46972,7 +47094,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X354" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c05；对象 24；中心 (7.482, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c05；对象 24；中心 (7.482, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c05_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-RIVET-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="355" ht="54" customHeight="1">
@@ -47007,7 +47132,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K355" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L355" t="str">
         <x:v>P0</x:v>
@@ -47022,7 +47147,7 @@
         <x:v>source/art/blender/base_facility_layout/component_packages_v017/floor/tile_r06_c06/asset_manifest.json</x:v>
       </x:c>
       <x:c r="P355" s="349" t="str">
-        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v017.blend; outputs/verification/base_facility_runtime_layout_hq_v017/base_facility_component_catalog_v017.json</x:v>
+        <x:v>source/art/blender/base_facility_layout/base_facility_runtime_layout_hq_v020.blend（Blender v020）；assets/art/environments/base_facility_3d/components/env_base99_floor_full_replacement_v021/env_base99_floor_full_replacement_v021_runtime_manifest_v003.json</x:v>
       </x:c>
       <x:c r="Q355" s="349" t="str">
         <x:v>基地99层;基地资产包;3D设施;地面系统包;tile_r06_c06;PaletteUV</x:v>
@@ -47048,7 +47173,10 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X355" s="349" t="str">
-        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c06；对象 24；中心 (12.482, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</x:v>
+        <x:v>package_id=ENV-BASE99-ART-LAYOUT-3D::tile_r06_c06；对象 24；中心 (12.482, 12.482, -0.076)m；朝向 Blender +Y north；预期导出 tile_r06_c06_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-04：运行时接入；基础砖复用 ENV-BASE99-FLOOR-PLAIN-5M，V017独占深化统一合并至 assets/art/environments/base_facility_3d/components/env_base99_floor_details_v017/env_base99_floor_details_v017_visual_top3d_v001.glb（2网格/4材质表面）。无新增碰撞，承重仍归 TowerFloorStage3D；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。
+2026-09-04 V020：运行时视觉源已指向 base_facility_runtime_layout_hq_v020.blend（Blender v020）；使用 env_base99_floor_details_v020_visual_top3d_v002.glb。共面重叠0、朝下三角面0；基础承重与碰撞复用保持不变；验收 verify_base99_floor_visuals_v020。
+2026-09-04 V021：完整地板视觉已替换旧普通/铆钉MultiMesh，改用 env_base99_floor_full_replacement_v021_visual_top3d_v003.glb；FloorSupport碰撞保持Y=0、30×30m、6×6×5m；验收 verify_base99_floor_visuals_v021。</x:v>
       </x:c>
     </x:row>
     <x:row r="356" ht="54" customHeight="1">
@@ -51643,7 +51771,7 @@
         <x:v>3D-设施 / 基地99层独立资产包</x:v>
       </x:c>
       <x:c r="K416" t="str">
-        <x:v>Blender源已完成</x:v>
+        <x:v>正式美术已接入</x:v>
       </x:c>
       <x:c r="L416" t="str">
         <x:v>P0</x:v>
@@ -51684,8 +51812,21 @@
         <x:v>用户自制Blender资产</x:v>
       </x:c>
       <x:c r="X416" s="349" t="str">
-        <x:v>可见地板恢复深红棕主色，以暗红、暖棕拼板和少量紫灰细缝深化；不含绿色大面与承重楼板。 revision=v017_loft_floor_reference_redbrown_006；中心 (5.000, 10.000, 6.044)m；PaletteUV、范围锁和独占归属验收通过。</x:v>
-      </x:c>
+        <x:v>可见地板恢复深红棕主色，以暗红、暖棕拼板和少量紫灰细缝深化；不含绿色大面与承重楼板。 revision=v017_loft_floor_reference_redbrown_006；中心 (5.000, 10.000, 6.044)m；PaletteUV、范围锁和独占归属验收通过。
+2026-09-04：运行时接入；导出 assets/art/environments/base_facility_3d/components/env_base99_loft_floor_finish_v017/env_base99_loft_floor_finish_v017_visual_top3d_v001.glb（1网格/2材质表面），由 assets/art/environments/base_facility_3d/runtime/env_base99_loft_floor_finish_v017/env_base99_loft_floor_finish_v017_root_top3d_v001.tscn 包装。仅视觉；装配层Y=-1m，使Blender Z=6面层对齐Godot Y=5楼中楼；验收 tests/verification/verify_base99_floor_visuals_v017.tscn。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417">
+      <x:c r="R417"/>
+      <x:c r="S417"/>
+    </x:row>
+    <x:row r="418">
+      <x:c r="R418"/>
+      <x:c r="S418"/>
+    </x:row>
+    <x:row r="419">
+      <x:c r="R419"/>
+      <x:c r="S419"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -51766,7 +51907,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6635dd5019624413"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raab8cfe939f74e5b"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -36903,16 +36903,16 @@
         <f>IF(COUNTIF($R$6:$R$300,R240)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
-      <c r="T240" s="136" t="str">
-        <v>9d7f7b7d669940c008d578317d033ed09ec73de09c3d7ad835eca39dcc6cb93b</v>
+      <c r="T240" t="str" s="136">
+        <v>ae4eed46dcea1624c5c30db80e8ba48a4270d9b75f159fefd281e3776d09dce9</v>
       </c>
       <c r="U240" s="136" t="inlineStr">
         <is>
           <t xml:space="preserve">Codex</t>
         </is>
       </c>
-      <c r="V240" t="n" s="137">
-        <v>46271</v>
+      <c r="V240" t="str" s="137">
+        <v>2026-09-06</v>
       </c>
       <c r="W240" s="136" t="inlineStr">
         <is>
@@ -36926,7 +36926,8 @@
 2026-09-04：已挂载 assets/art/environments/base_facility_3d/runtime/env_base99_floor_visuals_v017/env_base99_floor_visuals_root_top3d_v001.tscn。基础地砖维持18块 ENV-BASE99-FLOOR-PLAIN-5M 与18块 ENV-BASE99-FLOOR-RIVET-5M 的棋盘格复用；V017新增一层深化覆层与二层面层，均无玩法碰撞。
 2026-09-04 V020：地板表现装配已切换至 env_base99_floor_visuals_v020/env_base99_floor_visuals_root_top3d_v002.tscn；源文件 base_facility_runtime_layout_hq_v020.blend（Blender v020）；V017输出保留回滚。
 2026-09-04 V021：完整新地板装配已切换至 assets/art/environments/base_facility_3d/runtime/env_base99_floor_visuals_v021/env_base99_floor_visuals_root_top3d_v003.tscn；旧DungeonRoom3D普通/铆钉MultiMesh视觉不再生成，FloorSupport碰撞规格保持不变。
-2026-09-06：19个既有GLB补齐共享色盘导入脚本及禁止内嵌图参数；基地中央主灯改为中性冷白，保留1盏投影灯及原开关。122模型353材质共享色盘专项通过。</v>
+2026-09-06：19个既有GLB补齐共享色盘导入脚本及禁止内嵌图参数；基地中央主灯改为中性冷白，保留1盏投影灯及原开关。122模型353材质共享色盘专项通过。
+2026-09-06 灯具表现：BaseFixtureGlow3D 为9组霓虹/灯具提供分级HDR自发光，并为BASE CAMP、GOOD VIBES、STAY CURIOUS、床头灯、梯下壁灯、东侧吊灯和仓库吊灯增加7盏环境层局部灯；其余设备发光面保留轻微微光。共53个运行时发光材质，继续复用共享色盘与原UV；冷色适度去饱和，暖灯保留橙色温度，无阴影且距离淡出。验证 verify_base_fixture_glow，源Blend与GLB未改动。</v>
       </c>
     </row>
     <row r="241">

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2304,22 +2304,22 @@
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="321">
-        <f>COUNTA('资产主表'!$A$6:$A$424)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$423)</f>
         <v/>
       </c>
       <c r="B6" s="354" t="n"/>
       <c r="C6" s="321">
-        <f>COUNTIF('资产主表'!$K$6:$K$424,"已完成")+COUNTIF('资产主表'!$K$6:$K$424,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$424,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$424,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$424,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$424,"已导入；优化完成")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$423,"已完成")+COUNTIF('资产主表'!$K$6:$K$423,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$423,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$423,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$423,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$423,"已导入；优化完成")</f>
         <v/>
       </c>
       <c r="D6" s="354" t="n"/>
       <c r="E6" s="321">
-        <f>COUNTIF('资产主表'!$K$6:$K$424,"待制作")+COUNTIF('资产主表'!$K$6:$K$424,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$423,"待制作")+COUNTIF('资产主表'!$K$6:$K$423,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="354" t="n"/>
       <c r="G6" s="321">
-        <f>COUNTIF('资产主表'!$S$6:$S$424,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$423,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="354" t="n"/>
@@ -2388,11 +2388,11 @@
         </is>
       </c>
       <c r="B10" s="329">
-        <f>COUNTIF('资产主表'!$C$6:$C$424,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$423,A10)</f>
         <v/>
       </c>
       <c r="C10" s="329">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$424=A10)*(('资产主表'!$K$6:$K$424="已完成")+('资产主表'!$K$6:$K$424="原型已接入")+('资产主表'!$K$6:$K$424="正式美术已接入")+('资产主表'!$K$6:$K$424="已优化并正式接入")+('资产主表'!$K$6:$K$424="Blender源已完成")+('资产主表'!$K$6:$K$424="已导入；优化完成")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$423=A10)*(('资产主表'!$K$6:$K$423="已完成")+('资产主表'!$K$6:$K$423="原型已接入")+('资产主表'!$K$6:$K$423="正式美术已接入")+('资产主表'!$K$6:$K$423="已优化并正式接入")+('资产主表'!$K$6:$K$423="Blender源已完成")+('资产主表'!$K$6:$K$423="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D10" s="354" t="n"/>
@@ -2422,11 +2422,11 @@
         </is>
       </c>
       <c r="B11" s="331">
-        <f>COUNTIF('资产主表'!$C$6:$C$424,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$423,A11)</f>
         <v/>
       </c>
       <c r="C11" s="331">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$424=A11)*(('资产主表'!$K$6:$K$424="已完成")+('资产主表'!$K$6:$K$424="原型已接入")+('资产主表'!$K$6:$K$424="正式美术已接入")+('资产主表'!$K$6:$K$424="已优化并正式接入")+('资产主表'!$K$6:$K$424="Blender源已完成")+('资产主表'!$K$6:$K$424="已导入；优化完成")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$423=A11)*(('资产主表'!$K$6:$K$423="已完成")+('资产主表'!$K$6:$K$423="原型已接入")+('资产主表'!$K$6:$K$423="正式美术已接入")+('资产主表'!$K$6:$K$423="已优化并正式接入")+('资产主表'!$K$6:$K$423="Blender源已完成")+('资产主表'!$K$6:$K$423="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D11" s="354" t="n"/>
@@ -2456,11 +2456,11 @@
         </is>
       </c>
       <c r="B12" s="331">
-        <f>COUNTIF('资产主表'!$C$6:$C$424,A12)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$423,A12)</f>
         <v/>
       </c>
       <c r="C12" s="331">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$424=A12)*(('资产主表'!$K$6:$K$424="已完成")+('资产主表'!$K$6:$K$424="原型已接入")+('资产主表'!$K$6:$K$424="正式美术已接入")+('资产主表'!$K$6:$K$424="已优化并正式接入")+('资产主表'!$K$6:$K$424="Blender源已完成")+('资产主表'!$K$6:$K$424="已导入；优化完成")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$423=A12)*(('资产主表'!$K$6:$K$423="已完成")+('资产主表'!$K$6:$K$423="原型已接入")+('资产主表'!$K$6:$K$423="正式美术已接入")+('资产主表'!$K$6:$K$423="已优化并正式接入")+('资产主表'!$K$6:$K$423="Blender源已完成")+('资产主表'!$K$6:$K$423="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D12" s="354" t="n"/>
@@ -2490,11 +2490,11 @@
         </is>
       </c>
       <c r="B13" s="331">
-        <f>COUNTIF('资产主表'!$C$6:$C$424,A13)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$423,A13)</f>
         <v/>
       </c>
       <c r="C13" s="331">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$424=A13)*(('资产主表'!$K$6:$K$424="已完成")+('资产主表'!$K$6:$K$424="原型已接入")+('资产主表'!$K$6:$K$424="正式美术已接入")+('资产主表'!$K$6:$K$424="已优化并正式接入")+('资产主表'!$K$6:$K$424="Blender源已完成")+('资产主表'!$K$6:$K$424="已导入；优化完成")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$423=A13)*(('资产主表'!$K$6:$K$423="已完成")+('资产主表'!$K$6:$K$423="原型已接入")+('资产主表'!$K$6:$K$423="正式美术已接入")+('资产主表'!$K$6:$K$423="已优化并正式接入")+('资产主表'!$K$6:$K$423="Blender源已完成")+('资产主表'!$K$6:$K$423="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D13" s="354" t="n"/>
@@ -2524,11 +2524,11 @@
         </is>
       </c>
       <c r="B14" s="331">
-        <f>COUNTIF('资产主表'!$C$6:$C$424,A14)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$423,A14)</f>
         <v/>
       </c>
       <c r="C14" s="331">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$424=A14)*(('资产主表'!$K$6:$K$424="已完成")+('资产主表'!$K$6:$K$424="原型已接入")+('资产主表'!$K$6:$K$424="正式美术已接入")+('资产主表'!$K$6:$K$424="已优化并正式接入")+('资产主表'!$K$6:$K$424="Blender源已完成")+('资产主表'!$K$6:$K$424="已导入；优化完成")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$423=A14)*(('资产主表'!$K$6:$K$423="已完成")+('资产主表'!$K$6:$K$423="原型已接入")+('资产主表'!$K$6:$K$423="正式美术已接入")+('资产主表'!$K$6:$K$423="已优化并正式接入")+('资产主表'!$K$6:$K$423="Blender源已完成")+('资产主表'!$K$6:$K$423="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D14" s="354" t="n"/>
@@ -2558,11 +2558,11 @@
         </is>
       </c>
       <c r="B15" s="331">
-        <f>COUNTIF('资产主表'!$C$6:$C$424,A15)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$423,A15)</f>
         <v/>
       </c>
       <c r="C15" s="331">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$424=A15)*(('资产主表'!$K$6:$K$424="已完成")+('资产主表'!$K$6:$K$424="原型已接入")+('资产主表'!$K$6:$K$424="正式美术已接入")+('资产主表'!$K$6:$K$424="已优化并正式接入")+('资产主表'!$K$6:$K$424="Blender源已完成")+('资产主表'!$K$6:$K$424="已导入；优化完成")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$423=A15)*(('资产主表'!$K$6:$K$423="已完成")+('资产主表'!$K$6:$K$423="原型已接入")+('资产主表'!$K$6:$K$423="正式美术已接入")+('资产主表'!$K$6:$K$423="已优化并正式接入")+('资产主表'!$K$6:$K$423="Blender源已完成")+('资产主表'!$K$6:$K$423="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D15" s="354" t="n"/>
@@ -2580,11 +2580,11 @@
         </is>
       </c>
       <c r="B16" s="331">
-        <f>COUNTIF('资产主表'!$C$6:$C$424,A16)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$423,A16)</f>
         <v/>
       </c>
       <c r="C16" s="331">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$424=A16)*(('资产主表'!$K$6:$K$424="已完成")+('资产主表'!$K$6:$K$424="原型已接入")+('资产主表'!$K$6:$K$424="正式美术已接入")+('资产主表'!$K$6:$K$424="已优化并正式接入")+('资产主表'!$K$6:$K$424="Blender源已完成")+('资产主表'!$K$6:$K$424="已导入；优化完成")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$423=A16)*(('资产主表'!$K$6:$K$423="已完成")+('资产主表'!$K$6:$K$423="原型已接入")+('资产主表'!$K$6:$K$423="正式美术已接入")+('资产主表'!$K$6:$K$423="已优化并正式接入")+('资产主表'!$K$6:$K$423="Blender源已完成")+('资产主表'!$K$6:$K$423="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D16" s="354" t="n"/>
@@ -2602,11 +2602,11 @@
         </is>
       </c>
       <c r="B17" s="331">
-        <f>COUNTIF('资产主表'!$C$6:$C$424,A17)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$423,A17)</f>
         <v/>
       </c>
       <c r="C17" s="331">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$424=A17)*(('资产主表'!$K$6:$K$424="已完成")+('资产主表'!$K$6:$K$424="原型已接入")+('资产主表'!$K$6:$K$424="正式美术已接入")+('资产主表'!$K$6:$K$424="已优化并正式接入")+('资产主表'!$K$6:$K$424="Blender源已完成")+('资产主表'!$K$6:$K$424="已导入；优化完成")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$423=A17)*(('资产主表'!$K$6:$K$423="已完成")+('资产主表'!$K$6:$K$423="原型已接入")+('资产主表'!$K$6:$K$423="正式美术已接入")+('资产主表'!$K$6:$K$423="已优化并正式接入")+('资产主表'!$K$6:$K$423="Blender源已完成")+('资产主表'!$K$6:$K$423="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D17" s="354" t="n"/>
@@ -2624,11 +2624,11 @@
         </is>
       </c>
       <c r="B18" s="331">
-        <f>COUNTIF('资产主表'!$C$6:$C$424,A18)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$423,A18)</f>
         <v/>
       </c>
       <c r="C18" s="331">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$424=A18)*(('资产主表'!$K$6:$K$424="已完成")+('资产主表'!$K$6:$K$424="原型已接入")+('资产主表'!$K$6:$K$424="正式美术已接入")+('资产主表'!$K$6:$K$424="已优化并正式接入")+('资产主表'!$K$6:$K$424="Blender源已完成")+('资产主表'!$K$6:$K$424="已导入；优化完成")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$423=A18)*(('资产主表'!$K$6:$K$423="已完成")+('资产主表'!$K$6:$K$423="原型已接入")+('资产主表'!$K$6:$K$423="正式美术已接入")+('资产主表'!$K$6:$K$423="已优化并正式接入")+('资产主表'!$K$6:$K$423="Blender源已完成")+('资产主表'!$K$6:$K$423="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D18" s="354" t="n"/>
@@ -14188,7 +14188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y424"/>
+  <dimension ref="A1:Y423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -14472,7 +14472,7 @@
         <v/>
       </c>
       <c r="S6" s="301">
-        <f>IF(COUNTIF($R$6:$R$424,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="301" t="inlineStr">
@@ -14593,7 +14593,7 @@
         <v/>
       </c>
       <c r="S7" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="138" t="inlineStr">
@@ -14708,7 +14708,7 @@
         <v/>
       </c>
       <c r="S8" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="138" t="inlineStr">
@@ -14823,7 +14823,7 @@
         <v/>
       </c>
       <c r="S9" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="138" t="inlineStr">
@@ -14938,7 +14938,7 @@
         <v/>
       </c>
       <c r="S10" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="138" t="inlineStr">
@@ -15053,7 +15053,7 @@
         <v/>
       </c>
       <c r="S11" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="138" t="inlineStr">
@@ -15168,7 +15168,7 @@
         <v/>
       </c>
       <c r="S12" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="138" t="str"/>
@@ -15271,7 +15271,7 @@
         <v/>
       </c>
       <c r="S13" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="138" t="str"/>
@@ -15374,7 +15374,7 @@
         <v/>
       </c>
       <c r="S14" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="138" t="str"/>
@@ -15477,7 +15477,7 @@
         <v/>
       </c>
       <c r="S15" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="138" t="str"/>
@@ -15580,7 +15580,7 @@
         <v/>
       </c>
       <c r="S16" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="138" t="str"/>
@@ -15691,7 +15691,7 @@
         <v/>
       </c>
       <c r="S17" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="138" t="str"/>
@@ -15802,7 +15802,7 @@
         <v/>
       </c>
       <c r="S18" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="138" t="str"/>
@@ -15909,7 +15909,7 @@
         <v/>
       </c>
       <c r="S19" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="138" t="str"/>
@@ -16016,7 +16016,7 @@
         <v/>
       </c>
       <c r="S20" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="138" t="str"/>
@@ -16123,7 +16123,7 @@
         <v/>
       </c>
       <c r="S21" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="138" t="str"/>
@@ -16230,7 +16230,7 @@
         <v/>
       </c>
       <c r="S22" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="138" t="str"/>
@@ -16337,7 +16337,7 @@
         <v/>
       </c>
       <c r="S23" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="138" t="str"/>
@@ -16452,7 +16452,7 @@
         <v/>
       </c>
       <c r="S24" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="138" t="inlineStr">
@@ -16574,7 +16574,7 @@
         <v/>
       </c>
       <c r="S25" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="138" t="inlineStr">
@@ -16695,7 +16695,7 @@
         <v/>
       </c>
       <c r="S26" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="138" t="inlineStr">
@@ -16816,7 +16816,7 @@
         <v/>
       </c>
       <c r="S27" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="138" t="inlineStr">
@@ -16937,7 +16937,7 @@
         <v/>
       </c>
       <c r="S28" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="138" t="inlineStr">
@@ -17058,7 +17058,7 @@
         <v/>
       </c>
       <c r="S29" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="138" t="inlineStr">
@@ -17179,7 +17179,7 @@
         <v/>
       </c>
       <c r="S30" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="138" t="inlineStr">
@@ -17292,7 +17292,7 @@
         <v/>
       </c>
       <c r="S31" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="138" t="str"/>
@@ -17400,7 +17400,7 @@
         <v/>
       </c>
       <c r="S32" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="138" t="str"/>
@@ -17508,7 +17508,7 @@
         <v/>
       </c>
       <c r="S33" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="138" t="str"/>
@@ -17616,7 +17616,7 @@
         <v/>
       </c>
       <c r="S34" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="138" t="str"/>
@@ -17724,7 +17724,7 @@
         <v/>
       </c>
       <c r="S35" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="138" t="str"/>
@@ -17832,7 +17832,7 @@
         <v/>
       </c>
       <c r="S36" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="138" t="str"/>
@@ -17940,7 +17940,7 @@
         <v/>
       </c>
       <c r="S37" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="138" t="str"/>
@@ -18048,7 +18048,7 @@
         <v/>
       </c>
       <c r="S38" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R38)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R38)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T38" s="138" t="str"/>
@@ -18156,7 +18156,7 @@
         <v/>
       </c>
       <c r="S39" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R39)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R39)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T39" s="138" t="str"/>
@@ -18264,7 +18264,7 @@
         <v/>
       </c>
       <c r="S40" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R40)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R40)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T40" s="138" t="str"/>
@@ -18372,7 +18372,7 @@
         <v/>
       </c>
       <c r="S41" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R41)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R41)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T41" s="138" t="str"/>
@@ -18480,7 +18480,7 @@
         <v/>
       </c>
       <c r="S42" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R42)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R42)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T42" s="138" t="str"/>
@@ -18588,7 +18588,7 @@
         <v/>
       </c>
       <c r="S43" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R43)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R43)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T43" s="138" t="str"/>
@@ -18696,7 +18696,7 @@
         <v/>
       </c>
       <c r="S44" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R44)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R44)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T44" s="138" t="str"/>
@@ -18804,7 +18804,7 @@
         <v/>
       </c>
       <c r="S45" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R45)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R45)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T45" s="138" t="str"/>
@@ -18907,7 +18907,7 @@
         <v/>
       </c>
       <c r="S46" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R46)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R46)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T46" s="138" t="str"/>
@@ -19010,7 +19010,7 @@
         <v/>
       </c>
       <c r="S47" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R47)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R47)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T47" s="138" t="str"/>
@@ -19113,7 +19113,7 @@
         <v/>
       </c>
       <c r="S48" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R48)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R48)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T48" s="138" t="str"/>
@@ -19220,7 +19220,7 @@
         <v/>
       </c>
       <c r="S49" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R49)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R49)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T49" s="138" t="inlineStr">
@@ -19337,7 +19337,7 @@
         <v/>
       </c>
       <c r="S50" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R50)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R50)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T50" s="138" t="inlineStr">
@@ -19450,7 +19450,7 @@
         <v/>
       </c>
       <c r="S51" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R51)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R51)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T51" s="138" t="str"/>
@@ -19557,7 +19557,7 @@
         <v/>
       </c>
       <c r="S52" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R52)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R52)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T52" s="138" t="str"/>
@@ -19664,7 +19664,7 @@
         <v/>
       </c>
       <c r="S53" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R53)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R53)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T53" s="138" t="str"/>
@@ -19771,7 +19771,7 @@
         <v/>
       </c>
       <c r="S54" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R54)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R54)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T54" s="138" t="str"/>
@@ -19878,7 +19878,7 @@
         <v/>
       </c>
       <c r="S55" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R55)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R55)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T55" s="138" t="str"/>
@@ -19985,7 +19985,7 @@
         <v/>
       </c>
       <c r="S56" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R56)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R56)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T56" s="138" t="str"/>
@@ -20092,7 +20092,7 @@
         <v/>
       </c>
       <c r="S57" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R57)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R57)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T57" s="138" t="str"/>
@@ -20199,7 +20199,7 @@
         <v/>
       </c>
       <c r="S58" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R58)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R58)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T58" s="138" t="str"/>
@@ -20306,7 +20306,7 @@
         <v/>
       </c>
       <c r="S59" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R59)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R59)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T59" s="138" t="str"/>
@@ -20413,7 +20413,7 @@
         <v/>
       </c>
       <c r="S60" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R60)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R60)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T60" s="138" t="str"/>
@@ -20520,7 +20520,7 @@
         <v/>
       </c>
       <c r="S61" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R61)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R61)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T61" s="138" t="str"/>
@@ -20627,7 +20627,7 @@
         <v/>
       </c>
       <c r="S62" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R62)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R62)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T62" s="138" t="str"/>
@@ -20734,7 +20734,7 @@
         <v/>
       </c>
       <c r="S63" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R63)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R63)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T63" s="138" t="str"/>
@@ -20841,7 +20841,7 @@
         <v/>
       </c>
       <c r="S64" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R64)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R64)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T64" s="138" t="str"/>
@@ -20948,7 +20948,7 @@
         <v/>
       </c>
       <c r="S65" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R65)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R65)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T65" s="138" t="str"/>
@@ -21055,7 +21055,7 @@
         <v/>
       </c>
       <c r="S66" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R66)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R66)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T66" s="138" t="str"/>
@@ -21162,7 +21162,7 @@
         <v/>
       </c>
       <c r="S67" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R67)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R67)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T67" s="138" t="str"/>
@@ -21269,7 +21269,7 @@
         <v/>
       </c>
       <c r="S68" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R68)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R68)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T68" s="138" t="str"/>
@@ -21384,7 +21384,7 @@
         <v/>
       </c>
       <c r="S69" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R69)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R69)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T69" s="138" t="inlineStr">
@@ -21505,7 +21505,7 @@
         <v/>
       </c>
       <c r="S70" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R70)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R70)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T70" s="138" t="inlineStr">
@@ -21618,7 +21618,7 @@
         <v/>
       </c>
       <c r="S71" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R71)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R71)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T71" s="138" t="str"/>
@@ -21725,7 +21725,7 @@
         <v/>
       </c>
       <c r="S72" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R72)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R72)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T72" s="138" t="str"/>
@@ -21832,7 +21832,7 @@
         <v/>
       </c>
       <c r="S73" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R73)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R73)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T73" s="138" t="str"/>
@@ -21939,7 +21939,7 @@
         <v/>
       </c>
       <c r="S74" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R74)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R74)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T74" s="138" t="str"/>
@@ -22046,7 +22046,7 @@
         <v/>
       </c>
       <c r="S75" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R75)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R75)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T75" s="138" t="str"/>
@@ -22153,7 +22153,7 @@
         <v/>
       </c>
       <c r="S76" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R76)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R76)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T76" s="138" t="str"/>
@@ -22260,7 +22260,7 @@
         <v/>
       </c>
       <c r="S77" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R77)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R77)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T77" s="138" t="str"/>
@@ -22367,7 +22367,7 @@
         <v/>
       </c>
       <c r="S78" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R78)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R78)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T78" s="138" t="str"/>
@@ -22478,7 +22478,7 @@
         <v/>
       </c>
       <c r="S79" s="304">
-        <f>IF(COUNTIF($R$6:$R$424,R79)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R79)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T79" s="304" t="inlineStr">
@@ -22595,7 +22595,7 @@
         <v/>
       </c>
       <c r="S80" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R80)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R80)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T80" s="138" t="inlineStr">
@@ -22708,7 +22708,7 @@
         <v/>
       </c>
       <c r="S81" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R81)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R81)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T81" s="138" t="str"/>
@@ -22815,7 +22815,7 @@
         <v/>
       </c>
       <c r="S82" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R82)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R82)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T82" s="138" t="str"/>
@@ -22922,7 +22922,7 @@
         <v/>
       </c>
       <c r="S83" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R83)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R83)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T83" s="138" t="str"/>
@@ -23029,7 +23029,7 @@
         <v/>
       </c>
       <c r="S84" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R84)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R84)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T84" s="138" t="str"/>
@@ -23136,7 +23136,7 @@
         <v/>
       </c>
       <c r="S85" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R85)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R85)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T85" s="138" t="str"/>
@@ -23243,7 +23243,7 @@
         <v/>
       </c>
       <c r="S86" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R86)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R86)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T86" s="138" t="str"/>
@@ -23350,7 +23350,7 @@
         <v/>
       </c>
       <c r="S87" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R87)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R87)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T87" s="138" t="str"/>
@@ -23457,7 +23457,7 @@
         <v/>
       </c>
       <c r="S88" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R88)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R88)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T88" s="138" t="str"/>
@@ -23564,7 +23564,7 @@
         <v/>
       </c>
       <c r="S89" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R89)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R89)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T89" s="138" t="str"/>
@@ -23671,7 +23671,7 @@
         <v/>
       </c>
       <c r="S90" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R90)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R90)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T90" s="138" t="str"/>
@@ -23778,7 +23778,7 @@
         <v/>
       </c>
       <c r="S91" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R91)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R91)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T91" s="138" t="str"/>
@@ -23885,7 +23885,7 @@
         <v/>
       </c>
       <c r="S92" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R92)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R92)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T92" s="138" t="str"/>
@@ -23992,7 +23992,7 @@
         <v/>
       </c>
       <c r="S93" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R93)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R93)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T93" s="138" t="str"/>
@@ -24099,7 +24099,7 @@
         <v/>
       </c>
       <c r="S94" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R94)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R94)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T94" s="138" t="str"/>
@@ -24206,7 +24206,7 @@
         <v/>
       </c>
       <c r="S95" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R95)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R95)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T95" s="138" t="str"/>
@@ -24313,7 +24313,7 @@
         <v/>
       </c>
       <c r="S96" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R96)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R96)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T96" s="138" t="str"/>
@@ -24424,7 +24424,7 @@
         <v/>
       </c>
       <c r="S97" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R97)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R97)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T97" s="138" t="inlineStr">
@@ -24536,7 +24536,7 @@
         <v/>
       </c>
       <c r="S98" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R98)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R98)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T98" s="138" t="str"/>
@@ -24643,7 +24643,7 @@
         <v/>
       </c>
       <c r="S99" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R99)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R99)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T99" s="138" t="str"/>
@@ -24750,7 +24750,7 @@
         <v/>
       </c>
       <c r="S100" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R100)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R100)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T100" s="138" t="str"/>
@@ -24857,7 +24857,7 @@
         <v/>
       </c>
       <c r="S101" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R101)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R101)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T101" s="138" t="str"/>
@@ -24960,7 +24960,7 @@
         <v/>
       </c>
       <c r="S102" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R102)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R102)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T102" s="138" t="str"/>
@@ -25063,7 +25063,7 @@
         <v/>
       </c>
       <c r="S103" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R103)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R103)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T103" s="138" t="str"/>
@@ -25166,7 +25166,7 @@
         <v/>
       </c>
       <c r="S104" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R104)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R104)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T104" s="138" t="str"/>
@@ -25269,7 +25269,7 @@
         <v/>
       </c>
       <c r="S105" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R105)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R105)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T105" s="138" t="str"/>
@@ -25372,7 +25372,7 @@
         <v/>
       </c>
       <c r="S106" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R106)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R106)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T106" s="138" t="str"/>
@@ -25475,7 +25475,7 @@
         <v/>
       </c>
       <c r="S107" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R107)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R107)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T107" s="138" t="str"/>
@@ -25578,7 +25578,7 @@
         <v/>
       </c>
       <c r="S108" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R108)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R108)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T108" s="138" t="str"/>
@@ -25681,7 +25681,7 @@
         <v/>
       </c>
       <c r="S109" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R109)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R109)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T109" s="138" t="str"/>
@@ -25784,7 +25784,7 @@
         <v/>
       </c>
       <c r="S110" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R110)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R110)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T110" s="138" t="str"/>
@@ -25887,7 +25887,7 @@
         <v/>
       </c>
       <c r="S111" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R111)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R111)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T111" s="138" t="str"/>
@@ -25990,7 +25990,7 @@
         <v/>
       </c>
       <c r="S112" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R112)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R112)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T112" s="138" t="str"/>
@@ -26105,7 +26105,7 @@
         <v/>
       </c>
       <c r="S113" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R113)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R113)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T113" s="364" t="inlineStr">
@@ -26228,7 +26228,7 @@
         <v/>
       </c>
       <c r="S114" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R114)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R114)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T114" s="349" t="inlineStr">
@@ -26351,7 +26351,7 @@
         <v/>
       </c>
       <c r="S115" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R115)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R115)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T115" s="349" t="inlineStr">
@@ -26474,7 +26474,7 @@
         <v/>
       </c>
       <c r="S116" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R116)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R116)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T116" s="349" t="inlineStr">
@@ -26598,7 +26598,7 @@
         <v/>
       </c>
       <c r="S117" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R117)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R117)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T117" s="349" t="inlineStr">
@@ -26722,7 +26722,7 @@
         <v/>
       </c>
       <c r="S118" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R118)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R118)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T118" s="349" t="inlineStr">
@@ -26846,7 +26846,7 @@
         <v/>
       </c>
       <c r="S119" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R119)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R119)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T119" s="349" t="inlineStr">
@@ -26969,7 +26969,7 @@
         <v/>
       </c>
       <c r="S120" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R120)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R120)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T120" s="364" t="inlineStr">
@@ -27093,7 +27093,7 @@
         <v/>
       </c>
       <c r="S121" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R121)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R121)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T121" s="349" t="inlineStr">
@@ -27216,7 +27216,7 @@
         <v/>
       </c>
       <c r="S122" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R122)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R122)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T122" s="349" t="inlineStr">
@@ -27335,7 +27335,7 @@
         <v/>
       </c>
       <c r="S123" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R123)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R123)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T123" s="364" t="inlineStr">
@@ -27458,7 +27458,7 @@
         <v/>
       </c>
       <c r="S124" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R124)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R124)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T124" s="349" t="inlineStr">
@@ -27581,7 +27581,7 @@
         <v/>
       </c>
       <c r="S125" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R125)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R125)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T125" s="349" t="inlineStr">
@@ -27704,7 +27704,7 @@
         <v/>
       </c>
       <c r="S126" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R126)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R126)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T126" s="349" t="inlineStr">
@@ -27827,7 +27827,7 @@
         <v/>
       </c>
       <c r="S127" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R127)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R127)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T127" s="349" t="inlineStr">
@@ -27950,7 +27950,7 @@
         <v/>
       </c>
       <c r="S128" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R128)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R128)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T128" s="364" t="inlineStr">
@@ -28074,7 +28074,7 @@
         <v/>
       </c>
       <c r="S129" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R129)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R129)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T129" s="349" t="inlineStr">
@@ -28197,7 +28197,7 @@
         <v/>
       </c>
       <c r="S130" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R130)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R130)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T130" s="349" t="inlineStr">
@@ -28320,7 +28320,7 @@
         <v/>
       </c>
       <c r="S131" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R131)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R131)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T131" s="349" t="inlineStr">
@@ -28443,7 +28443,7 @@
         <v/>
       </c>
       <c r="S132" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R132)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R132)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T132" s="349" t="inlineStr">
@@ -28567,7 +28567,7 @@
         <v/>
       </c>
       <c r="S133" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R133)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R133)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T133" s="349" t="inlineStr">
@@ -28686,7 +28686,7 @@
         <v/>
       </c>
       <c r="S134" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R134)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R134)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T134" s="349" t="inlineStr">
@@ -28806,7 +28806,7 @@
         <v/>
       </c>
       <c r="S135" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R135)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R135)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T135" s="349" t="inlineStr">
@@ -28925,7 +28925,7 @@
         <v/>
       </c>
       <c r="S136" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R136)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R136)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T136" s="349" t="inlineStr">
@@ -29044,7 +29044,7 @@
         <v/>
       </c>
       <c r="S137" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R137)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R137)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T137" s="349" t="inlineStr">
@@ -29167,7 +29167,7 @@
         <v/>
       </c>
       <c r="S138" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R138)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R138)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T138" s="349" t="inlineStr">
@@ -29291,7 +29291,7 @@
         <v/>
       </c>
       <c r="S139" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R139)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R139)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T139" s="349" t="inlineStr">
@@ -29414,7 +29414,7 @@
         <v/>
       </c>
       <c r="S140" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R140)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R140)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T140" s="349" t="inlineStr">
@@ -29538,7 +29538,7 @@
         <v/>
       </c>
       <c r="S141" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R141)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R141)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T141" s="349" t="inlineStr">
@@ -29658,7 +29658,7 @@
         <v/>
       </c>
       <c r="S142" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R142)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R142)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T142" s="349" t="inlineStr">
@@ -29782,7 +29782,7 @@
         <v/>
       </c>
       <c r="S143" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R143)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R143)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T143" s="364" t="inlineStr">
@@ -29906,7 +29906,7 @@
         <v/>
       </c>
       <c r="S144" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R144)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R144)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T144" s="349" t="inlineStr">
@@ -30030,7 +30030,7 @@
         <v/>
       </c>
       <c r="S145" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R145)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R145)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T145" s="349" t="inlineStr">
@@ -30153,7 +30153,7 @@
         <v/>
       </c>
       <c r="S146" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R146)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R146)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T146" s="349" t="inlineStr">
@@ -30277,7 +30277,7 @@
         <v/>
       </c>
       <c r="S147" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R147)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R147)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T147" s="349" t="inlineStr">
@@ -30401,7 +30401,7 @@
         <v/>
       </c>
       <c r="S148" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R148)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R148)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T148" s="349" t="inlineStr">
@@ -30525,7 +30525,7 @@
         <v/>
       </c>
       <c r="S149" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R149)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R149)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T149" s="349" t="inlineStr">
@@ -30649,7 +30649,7 @@
         <v/>
       </c>
       <c r="S150" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R150)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R150)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T150" s="349" t="inlineStr">
@@ -30773,7 +30773,7 @@
         <v/>
       </c>
       <c r="S151" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R151)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R151)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T151" s="349" t="inlineStr">
@@ -30897,7 +30897,7 @@
         <v/>
       </c>
       <c r="S152" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R152)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R152)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T152" s="349" t="inlineStr">
@@ -31021,7 +31021,7 @@
         <v/>
       </c>
       <c r="S153" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R153)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R153)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T153" s="349" t="inlineStr">
@@ -31145,7 +31145,7 @@
         <v/>
       </c>
       <c r="S154" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R154)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R154)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T154" s="349" t="inlineStr">
@@ -31269,7 +31269,7 @@
         <v/>
       </c>
       <c r="S155" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R155)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R155)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T155" s="349" t="inlineStr">
@@ -31393,7 +31393,7 @@
         <v/>
       </c>
       <c r="S156" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R156)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R156)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T156" s="364" t="inlineStr">
@@ -31525,7 +31525,7 @@
         <v/>
       </c>
       <c r="S157" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R157)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R157)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T157" s="364" t="inlineStr">
@@ -31653,7 +31653,7 @@
         <v/>
       </c>
       <c r="S158" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R158)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R158)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T158" s="364" t="inlineStr">
@@ -31781,7 +31781,7 @@
         <v/>
       </c>
       <c r="S159" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R159)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R159)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T159" s="364" t="inlineStr">
@@ -31909,7 +31909,7 @@
         <v/>
       </c>
       <c r="S160" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R160)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R160)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T160" s="364" t="inlineStr">
@@ -32040,7 +32040,7 @@
         <v/>
       </c>
       <c r="S161" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R161)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R161)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T161" s="364" t="inlineStr">
@@ -32168,7 +32168,7 @@
         <v/>
       </c>
       <c r="S162" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R162)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R162)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T162" s="364" t="inlineStr">
@@ -32296,7 +32296,7 @@
         <v/>
       </c>
       <c r="S163" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R163)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R163)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T163" s="364" t="inlineStr">
@@ -32423,7 +32423,7 @@
         <v/>
       </c>
       <c r="S164" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R164)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R164)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T164" s="364" t="inlineStr">
@@ -32549,7 +32549,7 @@
         <v/>
       </c>
       <c r="S165" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R165)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R165)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T165" s="364" t="inlineStr">
@@ -32675,7 +32675,7 @@
         <v/>
       </c>
       <c r="S166" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R166)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R166)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T166" s="364" t="inlineStr">
@@ -32798,7 +32798,7 @@
         <v/>
       </c>
       <c r="S167" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R167)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R167)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T167" s="364" t="inlineStr">
@@ -32921,7 +32921,7 @@
         <v/>
       </c>
       <c r="S168" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R168)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R168)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T168" s="364" t="inlineStr">
@@ -33047,7 +33047,7 @@
         <v/>
       </c>
       <c r="S169" s="364">
-        <f>IF(COUNTIF($R$6:$R$424,R169)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R169)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T169" s="364" t="inlineStr">
@@ -33172,7 +33172,7 @@
         <v/>
       </c>
       <c r="S170" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R170)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R170)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T170" s="349" t="inlineStr">
@@ -33289,7 +33289,7 @@
         <v/>
       </c>
       <c r="S171" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R171)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R171)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T171" s="349" t="n"/>
@@ -33408,7 +33408,7 @@
         <v/>
       </c>
       <c r="S172" s="309">
-        <f>IF(COUNTIF($R$6:$R$424,R172)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R172)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T172" s="309" t="inlineStr">
@@ -33534,7 +33534,7 @@
         <v/>
       </c>
       <c r="S173" s="309">
-        <f>IF(COUNTIF($R$6:$R$424,R173)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R173)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T173" s="309" t="inlineStr">
@@ -33655,7 +33655,7 @@
         <v/>
       </c>
       <c r="S174" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R174)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R174)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T174" s="349" t="inlineStr">
@@ -33774,7 +33774,7 @@
         <v/>
       </c>
       <c r="S175" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R175)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R175)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T175" s="349" t="inlineStr">
@@ -33893,7 +33893,7 @@
         <v/>
       </c>
       <c r="S176" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R176)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R176)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T176" s="349" t="inlineStr">
@@ -34012,7 +34012,7 @@
         <v/>
       </c>
       <c r="S177" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R177)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R177)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T177" s="349" t="inlineStr">
@@ -34131,7 +34131,7 @@
         <v/>
       </c>
       <c r="S178" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R178)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R178)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T178" s="349" t="inlineStr">
@@ -34250,7 +34250,7 @@
         <v/>
       </c>
       <c r="S179" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R179)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R179)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T179" s="349" t="inlineStr">
@@ -34369,7 +34369,7 @@
         <v/>
       </c>
       <c r="S180" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R180)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R180)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T180" s="349" t="inlineStr">
@@ -34488,7 +34488,7 @@
         <v/>
       </c>
       <c r="S181" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R181)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R181)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T181" s="349" t="inlineStr">
@@ -34607,7 +34607,7 @@
         <v/>
       </c>
       <c r="S182" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R182)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R182)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T182" s="349" t="inlineStr">
@@ -34726,7 +34726,7 @@
         <v/>
       </c>
       <c r="S183" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R183)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R183)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T183" s="349" t="inlineStr">
@@ -34845,7 +34845,7 @@
         <v/>
       </c>
       <c r="S184" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R184)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R184)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T184" s="349" t="inlineStr">
@@ -34964,7 +34964,7 @@
         <v/>
       </c>
       <c r="S185" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R185)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R185)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T185" s="349" t="inlineStr">
@@ -35083,7 +35083,7 @@
         <v/>
       </c>
       <c r="S186" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R186)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R186)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T186" s="349" t="inlineStr">
@@ -35202,7 +35202,7 @@
         <v/>
       </c>
       <c r="S187" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R187)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R187)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T187" s="349" t="inlineStr">
@@ -35321,7 +35321,7 @@
         <v/>
       </c>
       <c r="S188" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R188)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R188)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T188" s="349" t="inlineStr">
@@ -35440,7 +35440,7 @@
         <v/>
       </c>
       <c r="S189" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R189)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R189)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T189" s="349" t="inlineStr">
@@ -35559,7 +35559,7 @@
         <v/>
       </c>
       <c r="S190" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R190)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R190)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T190" s="349" t="inlineStr">
@@ -35678,7 +35678,7 @@
         <v/>
       </c>
       <c r="S191" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R191)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R191)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T191" s="349" t="inlineStr">
@@ -35797,7 +35797,7 @@
         <v/>
       </c>
       <c r="S192" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R192)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R192)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T192" s="349" t="inlineStr">
@@ -35916,7 +35916,7 @@
         <v/>
       </c>
       <c r="S193" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R193)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R193)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T193" s="349" t="inlineStr">
@@ -36035,7 +36035,7 @@
         <v/>
       </c>
       <c r="S194" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R194)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R194)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T194" s="349" t="inlineStr">
@@ -36154,7 +36154,7 @@
         <v/>
       </c>
       <c r="S195" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R195)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R195)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T195" s="349" t="inlineStr">
@@ -36273,7 +36273,7 @@
         <v/>
       </c>
       <c r="S196" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R196)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R196)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T196" s="349" t="inlineStr">
@@ -36392,7 +36392,7 @@
         <v/>
       </c>
       <c r="S197" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R197)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R197)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T197" s="349" t="inlineStr">
@@ -36511,7 +36511,7 @@
         <v/>
       </c>
       <c r="S198" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R198)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R198)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T198" s="349" t="inlineStr">
@@ -36630,7 +36630,7 @@
         <v/>
       </c>
       <c r="S199" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R199)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R199)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T199" s="349" t="inlineStr">
@@ -36749,7 +36749,7 @@
         <v/>
       </c>
       <c r="S200" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R200)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R200)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T200" s="349" t="inlineStr">
@@ -36868,7 +36868,7 @@
         <v/>
       </c>
       <c r="S201" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R201)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R201)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T201" s="349" t="inlineStr">
@@ -36987,7 +36987,7 @@
         <v/>
       </c>
       <c r="S202" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R202)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R202)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T202" s="349" t="inlineStr">
@@ -37106,7 +37106,7 @@
         <v/>
       </c>
       <c r="S203" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R203)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R203)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T203" s="349" t="inlineStr">
@@ -37225,7 +37225,7 @@
         <v/>
       </c>
       <c r="S204" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R204)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R204)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T204" s="349" t="inlineStr">
@@ -37348,7 +37348,7 @@
         <v/>
       </c>
       <c r="S205" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R205)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R205)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T205" s="349" t="inlineStr">
@@ -37473,7 +37473,7 @@
         <v/>
       </c>
       <c r="S206" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R206)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R206)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T206" s="349" t="n"/>
@@ -37588,7 +37588,7 @@
         <v/>
       </c>
       <c r="S207" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R207)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R207)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T207" s="349" t="n"/>
@@ -37703,7 +37703,7 @@
         <v/>
       </c>
       <c r="S208" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R208)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R208)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T208" s="349" t="inlineStr">
@@ -37822,7 +37822,7 @@
         <v/>
       </c>
       <c r="S209" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R209)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R209)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T209" s="349" t="inlineStr">
@@ -37941,7 +37941,7 @@
         <v/>
       </c>
       <c r="S210" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R210)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R210)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T210" s="349" t="inlineStr">
@@ -38060,7 +38060,7 @@
         <v/>
       </c>
       <c r="S211" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R211)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R211)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T211" s="138" t="inlineStr">
@@ -38181,7 +38181,7 @@
         <v/>
       </c>
       <c r="S212" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R212)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R212)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T212" s="138" t="inlineStr">
@@ -38302,7 +38302,7 @@
         <v/>
       </c>
       <c r="S213" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R213)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R213)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T213" s="138" t="inlineStr">
@@ -38423,7 +38423,7 @@
         <v/>
       </c>
       <c r="S214" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R214)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R214)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T214" s="138" t="inlineStr">
@@ -38544,7 +38544,7 @@
         <v/>
       </c>
       <c r="S215" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R215)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R215)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T215" s="138" t="inlineStr">
@@ -38665,7 +38665,7 @@
         <v/>
       </c>
       <c r="S216" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R216)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R216)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T216" s="138" t="inlineStr">
@@ -38786,7 +38786,7 @@
         <v/>
       </c>
       <c r="S217" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R217)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R217)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T217" s="138" t="inlineStr">
@@ -38907,7 +38907,7 @@
         <v/>
       </c>
       <c r="S218" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R218)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R218)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T218" s="138" t="inlineStr">
@@ -39028,7 +39028,7 @@
         <v/>
       </c>
       <c r="S219" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R219)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R219)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T219" s="138" t="inlineStr">
@@ -39149,7 +39149,7 @@
         <v/>
       </c>
       <c r="S220" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R220)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R220)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T220" s="138" t="inlineStr">
@@ -39270,7 +39270,7 @@
         <v/>
       </c>
       <c r="S221" s="138">
-        <f>IF(COUNTIF($R$6:$R$424,R221)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R221)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T221" s="138" t="inlineStr">
@@ -39395,7 +39395,7 @@
         <v/>
       </c>
       <c r="S222" s="309">
-        <f>IF(COUNTIF($R$6:$R$424,R222)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R222)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T222" s="309" t="inlineStr">
@@ -39521,7 +39521,7 @@
         <v/>
       </c>
       <c r="S223" s="309">
-        <f>IF(COUNTIF($R$6:$R$424,R223)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R223)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T223" s="309" t="inlineStr">
@@ -39643,7 +39643,7 @@
         <v/>
       </c>
       <c r="S224" s="309">
-        <f>IF(COUNTIF($R$6:$R$424,R224)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R224)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T224" s="309" t="inlineStr">
@@ -39764,7 +39764,7 @@
         <v/>
       </c>
       <c r="S225" s="309">
-        <f>IF(COUNTIF($R$6:$R$424,R225)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R225)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T225" s="309" t="inlineStr">
@@ -39885,7 +39885,7 @@
         <v/>
       </c>
       <c r="S226" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R226)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R226)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T226" s="349" t="inlineStr">
@@ -40005,7 +40005,7 @@
         <v/>
       </c>
       <c r="S227" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R227)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R227)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T227" s="349" t="inlineStr">
@@ -40125,7 +40125,7 @@
         <v/>
       </c>
       <c r="S228" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R228)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R228)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T228" s="349" t="inlineStr">
@@ -40245,7 +40245,7 @@
         <v/>
       </c>
       <c r="S229" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R229)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R229)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T229" s="349" t="inlineStr">
@@ -40365,7 +40365,7 @@
         <v/>
       </c>
       <c r="S230" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R230)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R230)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T230" s="349" t="inlineStr">
@@ -40485,7 +40485,7 @@
         <v/>
       </c>
       <c r="S231" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R231)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R231)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T231" s="349" t="inlineStr">
@@ -40605,7 +40605,7 @@
         <v/>
       </c>
       <c r="S232" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R232)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R232)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T232" s="349" t="inlineStr">
@@ -40725,7 +40725,7 @@
         <v/>
       </c>
       <c r="S233" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R233)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R233)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T233" s="349" t="inlineStr">
@@ -40845,7 +40845,7 @@
         <v/>
       </c>
       <c r="S234" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R234)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R234)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T234" s="349" t="inlineStr">
@@ -40965,7 +40965,7 @@
         <v/>
       </c>
       <c r="S235" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R235)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R235)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T235" s="349" t="n"/>
@@ -41085,7 +41085,7 @@
         <v/>
       </c>
       <c r="S236" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R236)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R236)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T236" s="349" t="inlineStr">
@@ -41197,7 +41197,7 @@
       </c>
       <c r="P237" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/export/v025/base_facility_runtime_layout_hq-v025-door_wall_palette.blend; assets/art/environments/base_facility_3d/components/env_base99_wall_door_5x9/env_base99_wall_door_5x9_visual_top3d_v003.glb</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/export/v025/base_facility_runtime_layout_hq-v025-door_wall_palette.blend; assets/art/environments/base_facility_3d/components/env_base99_wall_door_5x9/env_base99_wall_door_5x9_visual_top3d_v003.glb</t>
         </is>
       </c>
       <c r="Q237" s="349" t="inlineStr">
@@ -41210,7 +41210,7 @@
         <v/>
       </c>
       <c r="S237" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R237)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R237)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T237" s="349" t="inlineStr">
@@ -41335,7 +41335,7 @@
         <v/>
       </c>
       <c r="S238" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R238)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R238)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T238" s="349" t="inlineStr">
@@ -41460,7 +41460,7 @@
         <v/>
       </c>
       <c r="S239" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R239)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R239)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T239" s="349" t="inlineStr">
@@ -41572,7 +41572,7 @@
       </c>
       <c r="P240" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; assets/art/environments/base_facility_3d/runtime/env_base_facility_art_layout_top3d_v002.tscn</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; assets/art/environments/base_facility_3d/runtime/env_base_facility_art_layout_top3d_v002.tscn</t>
         </is>
       </c>
       <c r="Q240" s="349" t="inlineStr">
@@ -41585,12 +41585,12 @@
         <v/>
       </c>
       <c r="S240" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R240)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R240)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T240" s="349" t="inlineStr">
         <is>
-          <t>b7fbba923cf19ebfdedc882d9645aa60a57ffa90a270b5a28606cb15d8c343af</t>
+          <t>d39857923f3e86ef98175297c8849286612196e2a22298a406349f1666d635c9</t>
         </is>
       </c>
       <c r="U240" s="349" t="inlineStr">
@@ -41704,7 +41704,7 @@
       </c>
       <c r="P241" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/architecture/base_corner_l_5m/base_corner_l_5m_source_v024.blend; assets/art/environments/base_facility_3d/components/env_base99_corner_l_5m/env_base99_corner_l_5m_visual_top3d_v001.glb</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/architecture/base_corner_l_5m/base_corner_l_5m_source_v024.blend; assets/art/environments/base_facility_3d/components/env_base99_corner_l_5m/env_base99_corner_l_5m_visual_top3d_v001.glb</t>
         </is>
       </c>
       <c r="Q241" s="349" t="inlineStr">
@@ -41717,12 +41717,12 @@
         <v/>
       </c>
       <c r="S241" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R241)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R241)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T241" s="349" t="inlineStr">
         <is>
-          <t>24dba4d2f70d8ed2cb58602102f44537a381a63f8c4108b399ed06030a6948f2</t>
+          <t>cca0761bf62acd0ce6af1cddd9ff466545385ec7725e7c0a00523eb88b7f0d5c</t>
         </is>
       </c>
       <c r="U241" s="349" t="inlineStr">
@@ -41841,7 +41841,7 @@
         <v/>
       </c>
       <c r="S242" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R242)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R242)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T242" s="349" t="inlineStr">
@@ -41965,7 +41965,7 @@
         <v/>
       </c>
       <c r="S243" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R243)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R243)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T243" s="349" t="inlineStr">
@@ -42089,7 +42089,7 @@
         <v/>
       </c>
       <c r="S244" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R244)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R244)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T244" s="349" t="inlineStr">
@@ -42213,7 +42213,7 @@
         <v/>
       </c>
       <c r="S245" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R245)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R245)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T245" s="349" t="inlineStr">
@@ -42337,7 +42337,7 @@
         <v/>
       </c>
       <c r="S246" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R246)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R246)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T246" s="349" t="inlineStr">
@@ -42461,7 +42461,7 @@
         <v/>
       </c>
       <c r="S247" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R247)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R247)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T247" s="349" t="inlineStr">
@@ -42585,7 +42585,7 @@
         <v/>
       </c>
       <c r="S248" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R248)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R248)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T248" s="349" t="inlineStr">
@@ -42709,7 +42709,7 @@
         <v/>
       </c>
       <c r="S249" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R249)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R249)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T249" s="349" t="inlineStr">
@@ -42833,7 +42833,7 @@
         <v/>
       </c>
       <c r="S250" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R250)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R250)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T250" s="349" t="inlineStr">
@@ -42957,7 +42957,7 @@
         <v/>
       </c>
       <c r="S251" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R251)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R251)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T251" s="349" t="inlineStr">
@@ -43081,7 +43081,7 @@
         <v/>
       </c>
       <c r="S252" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R252)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R252)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T252" s="349" t="inlineStr">
@@ -43205,7 +43205,7 @@
         <v/>
       </c>
       <c r="S253" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R253)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R253)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T253" s="349" t="inlineStr">
@@ -43329,7 +43329,7 @@
         <v/>
       </c>
       <c r="S254" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R254)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R254)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T254" s="349" t="inlineStr">
@@ -43453,7 +43453,7 @@
         <v/>
       </c>
       <c r="S255" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R255)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R255)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T255" s="349" t="inlineStr">
@@ -43577,7 +43577,7 @@
         <v/>
       </c>
       <c r="S256" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R256)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R256)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T256" s="349" t="inlineStr">
@@ -43701,7 +43701,7 @@
         <v/>
       </c>
       <c r="S257" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R257)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R257)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T257" s="349" t="inlineStr">
@@ -43825,7 +43825,7 @@
         <v/>
       </c>
       <c r="S258" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R258)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R258)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T258" s="349" t="inlineStr">
@@ -43949,7 +43949,7 @@
         <v/>
       </c>
       <c r="S259" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R259)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R259)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T259" s="349" t="inlineStr">
@@ -44073,7 +44073,7 @@
         <v/>
       </c>
       <c r="S260" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R260)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R260)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T260" s="349" t="inlineStr">
@@ -44197,7 +44197,7 @@
         <v/>
       </c>
       <c r="S261" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R261)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R261)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T261" s="349" t="inlineStr">
@@ -44321,7 +44321,7 @@
         <v/>
       </c>
       <c r="S262" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R262)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R262)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T262" s="349" t="inlineStr">
@@ -44445,7 +44445,7 @@
         <v/>
       </c>
       <c r="S263" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R263)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R263)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T263" s="349" t="inlineStr">
@@ -44569,7 +44569,7 @@
         <v/>
       </c>
       <c r="S264" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R264)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R264)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T264" s="349" t="inlineStr">
@@ -44693,7 +44693,7 @@
         <v/>
       </c>
       <c r="S265" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R265)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R265)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T265" s="349" t="inlineStr">
@@ -44817,7 +44817,7 @@
         <v/>
       </c>
       <c r="S266" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R266)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R266)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T266" s="349" t="inlineStr">
@@ -44941,7 +44941,7 @@
         <v/>
       </c>
       <c r="S267" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R267)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R267)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T267" s="349" t="inlineStr">
@@ -45065,7 +45065,7 @@
         <v/>
       </c>
       <c r="S268" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R268)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R268)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T268" s="349" t="inlineStr">
@@ -45189,7 +45189,7 @@
         <v/>
       </c>
       <c r="S269" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R269)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R269)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T269" s="349" t="inlineStr">
@@ -45313,7 +45313,7 @@
         <v/>
       </c>
       <c r="S270" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R270)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R270)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T270" s="349" t="inlineStr">
@@ -45437,7 +45437,7 @@
         <v/>
       </c>
       <c r="S271" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R271)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R271)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T271" s="349" t="inlineStr">
@@ -45561,7 +45561,7 @@
         <v/>
       </c>
       <c r="S272" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R272)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R272)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T272" s="349" t="inlineStr">
@@ -45685,7 +45685,7 @@
         <v/>
       </c>
       <c r="S273" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R273)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R273)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T273" s="349" t="inlineStr">
@@ -45809,7 +45809,7 @@
         <v/>
       </c>
       <c r="S274" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R274)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R274)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T274" s="349" t="inlineStr">
@@ -45932,7 +45932,7 @@
         <v/>
       </c>
       <c r="S275" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R275)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R275)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T275" s="349" t="inlineStr">
@@ -46057,7 +46057,7 @@
         <v/>
       </c>
       <c r="S276" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R276)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R276)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T276" s="349" t="inlineStr">
@@ -46182,7 +46182,7 @@
         <v/>
       </c>
       <c r="S277" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R277)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R277)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T277" s="349" t="inlineStr">
@@ -46307,7 +46307,7 @@
         <v/>
       </c>
       <c r="S278" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R278)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R278)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T278" s="349" t="inlineStr">
@@ -46432,7 +46432,7 @@
         <v/>
       </c>
       <c r="S279" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R279)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R279)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T279" s="349" t="inlineStr">
@@ -46557,7 +46557,7 @@
         <v/>
       </c>
       <c r="S280">
-        <f>IF(COUNTIF($R$6:$R$424,R280)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R280)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T280" t="inlineStr">
@@ -46682,7 +46682,7 @@
         <v/>
       </c>
       <c r="S281" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R281)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R281)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T281" s="349" t="inlineStr">
@@ -46808,7 +46808,7 @@
         <v/>
       </c>
       <c r="S282" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R282)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R282)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T282" s="349" t="inlineStr">
@@ -46934,7 +46934,7 @@
         <v/>
       </c>
       <c r="S283" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R283)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R283)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T283" s="349" t="inlineStr">
@@ -47060,7 +47060,7 @@
         <v/>
       </c>
       <c r="S284" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R284)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R284)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T284" s="349" t="inlineStr">
@@ -47183,7 +47183,7 @@
         <v/>
       </c>
       <c r="S285" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R285)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R285)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T285" s="349" t="inlineStr">
@@ -47308,7 +47308,7 @@
         <v/>
       </c>
       <c r="S286" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R286)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R286)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T286" s="349" t="inlineStr">
@@ -47433,7 +47433,7 @@
         <v/>
       </c>
       <c r="S287" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R287)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R287)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T287" s="349" t="inlineStr">
@@ -47553,7 +47553,7 @@
         <v/>
       </c>
       <c r="S288">
-        <f>IF(COUNTIF($R$6:$R$424,R288)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R288)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T288" t="inlineStr">
@@ -47671,7 +47671,7 @@
         <v/>
       </c>
       <c r="S289">
-        <f>IF(COUNTIF($R$6:$R$424,R289)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R289)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T289" t="inlineStr">
@@ -47789,7 +47789,7 @@
         <v/>
       </c>
       <c r="S290">
-        <f>IF(COUNTIF($R$6:$R$424,R290)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R290)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T290" t="inlineStr">
@@ -47907,7 +47907,7 @@
         <v/>
       </c>
       <c r="S291">
-        <f>IF(COUNTIF($R$6:$R$424,R291)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R291)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T291" t="inlineStr">
@@ -48025,7 +48025,7 @@
         <v/>
       </c>
       <c r="S292">
-        <f>IF(COUNTIF($R$6:$R$424,R292)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R292)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T292" t="inlineStr">
@@ -48143,7 +48143,7 @@
         <v/>
       </c>
       <c r="S293">
-        <f>IF(COUNTIF($R$6:$R$424,R293)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R293)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T293" t="inlineStr">
@@ -48261,7 +48261,7 @@
         <v/>
       </c>
       <c r="S294">
-        <f>IF(COUNTIF($R$6:$R$424,R294)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R294)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T294" t="inlineStr">
@@ -48379,7 +48379,7 @@
         <v/>
       </c>
       <c r="S295">
-        <f>IF(COUNTIF($R$6:$R$424,R295)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R295)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T295" t="inlineStr">
@@ -48497,7 +48497,7 @@
         <v/>
       </c>
       <c r="S296">
-        <f>IF(COUNTIF($R$6:$R$424,R296)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R296)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T296" t="inlineStr">
@@ -48621,7 +48621,7 @@
         <v/>
       </c>
       <c r="S297">
-        <f>IF(COUNTIF($R$6:$R$424,R297)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R297)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T297" t="inlineStr">
@@ -48743,7 +48743,7 @@
         <v/>
       </c>
       <c r="S298">
-        <f>IF(COUNTIF($R$6:$R$424,R298)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R298)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T298" t="inlineStr">
@@ -48861,7 +48861,7 @@
         <v/>
       </c>
       <c r="S299">
-        <f>IF(COUNTIF($R$6:$R$424,R299)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R299)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T299" t="inlineStr">
@@ -48979,7 +48979,7 @@
         <v/>
       </c>
       <c r="S300">
-        <f>IF(COUNTIF($R$6:$R$424,R300)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R300)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T300" t="inlineStr">
@@ -49102,7 +49102,7 @@
         <v/>
       </c>
       <c r="S301">
-        <f>IF(COUNTIF($R$6:$R$424,R301)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R301)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T301" t="inlineStr">
@@ -49213,7 +49213,7 @@
       </c>
       <c r="P302" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/architecture/east_mezzanine_structure/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/architecture/east_mezzanine_structure/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q302" s="349" t="inlineStr">
@@ -49226,7 +49226,7 @@
         <v/>
       </c>
       <c r="S302" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R302)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R302)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T302" s="349" t="inlineStr">
@@ -49339,7 +49339,7 @@
       </c>
       <c r="P303" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/architecture/east_upper_transition_stair/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/architecture/east_upper_transition_stair/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q303" s="349" t="inlineStr">
@@ -49352,7 +49352,7 @@
         <v/>
       </c>
       <c r="S303" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R303)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R303)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T303" s="349" t="inlineStr">
@@ -49464,7 +49464,7 @@
       </c>
       <c r="P304" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/architecture/northwest_l_stair/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/architecture/northwest_l_stair/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q304" s="349" t="inlineStr">
@@ -49477,7 +49477,7 @@
         <v/>
       </c>
       <c r="S304" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R304)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R304)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T304" s="349" t="inlineStr">
@@ -49589,7 +49589,7 @@
       </c>
       <c r="P305" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/architecture/retained_wall_system/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/architecture/retained_wall_system/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q305" s="349" t="inlineStr">
@@ -49602,7 +49602,7 @@
         <v/>
       </c>
       <c r="S305" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R305)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R305)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T305" s="349" t="inlineStr">
@@ -49712,7 +49712,7 @@
       </c>
       <c r="P306" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/architecture/underdeck_sheet_blocker/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/architecture/underdeck_sheet_blocker/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q306" s="349" t="inlineStr">
@@ -49725,7 +49725,7 @@
         <v/>
       </c>
       <c r="S306" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R306)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R306)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T306" s="349" t="inlineStr">
@@ -49837,7 +49837,7 @@
       </c>
       <c r="P307" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_flammable_bin/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_flammable_bin/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q307" s="349" t="inlineStr">
@@ -49850,7 +49850,7 @@
         <v/>
       </c>
       <c r="S307" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R307)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R307)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T307" s="349" t="inlineStr">
@@ -49960,7 +49960,7 @@
       </c>
       <c r="P308" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_industrial_pipeline_system/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_industrial_pipeline_system/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q308" s="349" t="inlineStr">
@@ -49973,7 +49973,7 @@
         <v/>
       </c>
       <c r="S308" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R308)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R308)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T308" s="349" t="inlineStr">
@@ -50083,7 +50083,7 @@
       </c>
       <c r="P309" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_low_storage_bench/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_low_storage_bench/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q309" s="349" t="inlineStr">
@@ -50096,7 +50096,7 @@
         <v/>
       </c>
       <c r="S309" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R309)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R309)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T309" s="349" t="inlineStr">
@@ -50206,7 +50206,7 @@
       </c>
       <c r="P310" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_maintenance_workstation/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_maintenance_workstation/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q310" s="349" t="inlineStr">
@@ -50219,7 +50219,7 @@
         <v/>
       </c>
       <c r="S310" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R310)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R310)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T310" s="349" t="inlineStr">
@@ -50329,7 +50329,7 @@
       </c>
       <c r="P311" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_personnel_security_door/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_personnel_security_door/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q311" s="349" t="inlineStr">
@@ -50342,7 +50342,7 @@
         <v/>
       </c>
       <c r="S311" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R311)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R311)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T311" s="349" t="inlineStr">
@@ -50452,7 +50452,7 @@
       </c>
       <c r="P312" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_plant_group/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_plant_group/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q312" s="349" t="inlineStr">
@@ -50465,7 +50465,7 @@
         <v/>
       </c>
       <c r="S312" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R312)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R312)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T312" s="349" t="inlineStr">
@@ -50575,7 +50575,7 @@
       </c>
       <c r="P313" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_power_distribution/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_power_distribution/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q313" s="349" t="inlineStr">
@@ -50588,7 +50588,7 @@
         <v/>
       </c>
       <c r="S313" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R313)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R313)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T313" s="349" t="inlineStr">
@@ -50698,7 +50698,7 @@
       </c>
       <c r="P314" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_recycle_bin/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_recycle_bin/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q314" s="349" t="inlineStr">
@@ -50711,7 +50711,7 @@
         <v/>
       </c>
       <c r="S314" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R314)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R314)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T314" s="349" t="inlineStr">
@@ -50821,7 +50821,7 @@
       </c>
       <c r="P315" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_round_pendant_light/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_round_pendant_light/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q315" s="349" t="inlineStr">
@@ -50834,7 +50834,7 @@
         <v/>
       </c>
       <c r="S315" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R315)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R315)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T315" s="349" t="inlineStr">
@@ -50944,7 +50944,7 @@
       </c>
       <c r="P316" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_small_safety_devices/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_small_safety_devices/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q316" s="349" t="inlineStr">
@@ -50957,7 +50957,7 @@
         <v/>
       </c>
       <c r="S316" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R316)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R316)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T316" s="349" t="inlineStr">
@@ -51067,7 +51067,7 @@
       </c>
       <c r="P317" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_supply_24h_station/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_supply_24h_station/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q317" s="349" t="inlineStr">
@@ -51080,7 +51080,7 @@
         <v/>
       </c>
       <c r="S317" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R317)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R317)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T317" s="349" t="inlineStr">
@@ -51191,7 +51191,7 @@
       </c>
       <c r="P318" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_waste_bin/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_waste_bin/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q318" s="349" t="inlineStr">
@@ -51204,7 +51204,7 @@
         <v/>
       </c>
       <c r="S318" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R318)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R318)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T318" s="349" t="inlineStr">
@@ -51314,7 +51314,7 @@
       </c>
       <c r="P319" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_work_together_poster/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/east_facilities/east_work_together_poster/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q319" s="349" t="inlineStr">
@@ -51327,7 +51327,7 @@
         <v/>
       </c>
       <c r="S319" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R319)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R319)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T319" s="349" t="inlineStr">
@@ -51437,7 +51437,7 @@
       </c>
       <c r="P320" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r01_c01/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r01_c01/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q320" s="349" t="inlineStr">
@@ -51450,7 +51450,7 @@
         <v/>
       </c>
       <c r="S320" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R320)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R320)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T320" s="349" t="inlineStr">
@@ -51563,7 +51563,7 @@
       </c>
       <c r="P321" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r01_c02/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r01_c02/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q321" s="349" t="inlineStr">
@@ -51576,7 +51576,7 @@
         <v/>
       </c>
       <c r="S321" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R321)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R321)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T321" s="349" t="inlineStr">
@@ -51689,7 +51689,7 @@
       </c>
       <c r="P322" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r01_c03/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r01_c03/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q322" s="349" t="inlineStr">
@@ -51702,7 +51702,7 @@
         <v/>
       </c>
       <c r="S322" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R322)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R322)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T322" s="349" t="inlineStr">
@@ -51815,7 +51815,7 @@
       </c>
       <c r="P323" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r01_c04/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r01_c04/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q323" s="349" t="inlineStr">
@@ -51828,7 +51828,7 @@
         <v/>
       </c>
       <c r="S323" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R323)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R323)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T323" s="349" t="inlineStr">
@@ -51941,7 +51941,7 @@
       </c>
       <c r="P324" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r01_c05/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r01_c05/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q324" s="349" t="inlineStr">
@@ -51954,7 +51954,7 @@
         <v/>
       </c>
       <c r="S324" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R324)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R324)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T324" s="349" t="inlineStr">
@@ -52067,7 +52067,7 @@
       </c>
       <c r="P325" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r01_c06/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r01_c06/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q325" s="349" t="inlineStr">
@@ -52080,7 +52080,7 @@
         <v/>
       </c>
       <c r="S325" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R325)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R325)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T325" s="349" t="inlineStr">
@@ -52193,7 +52193,7 @@
       </c>
       <c r="P326" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r02_c01/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r02_c01/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q326" s="349" t="inlineStr">
@@ -52206,7 +52206,7 @@
         <v/>
       </c>
       <c r="S326" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R326)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R326)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T326" s="349" t="inlineStr">
@@ -52319,7 +52319,7 @@
       </c>
       <c r="P327" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r02_c02/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r02_c02/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q327" s="349" t="inlineStr">
@@ -52332,7 +52332,7 @@
         <v/>
       </c>
       <c r="S327" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R327)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R327)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T327" s="349" t="inlineStr">
@@ -52445,7 +52445,7 @@
       </c>
       <c r="P328" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r02_c03/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r02_c03/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q328" s="349" t="inlineStr">
@@ -52458,7 +52458,7 @@
         <v/>
       </c>
       <c r="S328" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R328)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R328)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T328" s="349" t="inlineStr">
@@ -52571,7 +52571,7 @@
       </c>
       <c r="P329" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r02_c04/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r02_c04/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q329" s="349" t="inlineStr">
@@ -52584,7 +52584,7 @@
         <v/>
       </c>
       <c r="S329" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R329)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R329)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T329" s="349" t="inlineStr">
@@ -52697,7 +52697,7 @@
       </c>
       <c r="P330" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r02_c05/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r02_c05/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q330" s="349" t="inlineStr">
@@ -52710,7 +52710,7 @@
         <v/>
       </c>
       <c r="S330" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R330)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R330)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T330" s="349" t="inlineStr">
@@ -52823,7 +52823,7 @@
       </c>
       <c r="P331" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r02_c06/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r02_c06/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q331" s="349" t="inlineStr">
@@ -52836,7 +52836,7 @@
         <v/>
       </c>
       <c r="S331" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R331)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R331)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T331" s="349" t="inlineStr">
@@ -52949,7 +52949,7 @@
       </c>
       <c r="P332" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r03_c01/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r03_c01/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q332" s="349" t="inlineStr">
@@ -52962,7 +52962,7 @@
         <v/>
       </c>
       <c r="S332" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R332)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R332)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T332" s="349" t="inlineStr">
@@ -53075,7 +53075,7 @@
       </c>
       <c r="P333" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r03_c02/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r03_c02/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q333" s="349" t="inlineStr">
@@ -53088,7 +53088,7 @@
         <v/>
       </c>
       <c r="S333" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R333)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R333)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T333" s="349" t="inlineStr">
@@ -53201,7 +53201,7 @@
       </c>
       <c r="P334" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r03_c03/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r03_c03/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q334" s="349" t="inlineStr">
@@ -53214,7 +53214,7 @@
         <v/>
       </c>
       <c r="S334" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R334)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R334)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T334" s="349" t="inlineStr">
@@ -53327,7 +53327,7 @@
       </c>
       <c r="P335" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r03_c04/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r03_c04/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q335" s="349" t="inlineStr">
@@ -53340,7 +53340,7 @@
         <v/>
       </c>
       <c r="S335" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R335)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R335)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T335" s="349" t="inlineStr">
@@ -53453,7 +53453,7 @@
       </c>
       <c r="P336" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r03_c05/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r03_c05/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q336" s="349" t="inlineStr">
@@ -53466,7 +53466,7 @@
         <v/>
       </c>
       <c r="S336" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R336)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R336)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T336" s="349" t="inlineStr">
@@ -53579,7 +53579,7 @@
       </c>
       <c r="P337" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r03_c06/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r03_c06/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q337" s="349" t="inlineStr">
@@ -53592,7 +53592,7 @@
         <v/>
       </c>
       <c r="S337" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R337)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R337)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T337" s="349" t="inlineStr">
@@ -53705,7 +53705,7 @@
       </c>
       <c r="P338" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r04_c01/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r04_c01/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q338" s="349" t="inlineStr">
@@ -53718,7 +53718,7 @@
         <v/>
       </c>
       <c r="S338" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R338)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R338)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T338" s="349" t="inlineStr">
@@ -53831,7 +53831,7 @@
       </c>
       <c r="P339" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r04_c02/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r04_c02/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q339" s="349" t="inlineStr">
@@ -53844,7 +53844,7 @@
         <v/>
       </c>
       <c r="S339" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R339)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R339)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T339" s="349" t="inlineStr">
@@ -53957,7 +53957,7 @@
       </c>
       <c r="P340" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r04_c03/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r04_c03/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q340" s="349" t="inlineStr">
@@ -53970,7 +53970,7 @@
         <v/>
       </c>
       <c r="S340" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R340)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R340)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T340" s="349" t="inlineStr">
@@ -54083,7 +54083,7 @@
       </c>
       <c r="P341" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r04_c04/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r04_c04/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q341" s="349" t="inlineStr">
@@ -54096,7 +54096,7 @@
         <v/>
       </c>
       <c r="S341" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R341)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R341)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T341" s="349" t="inlineStr">
@@ -54209,7 +54209,7 @@
       </c>
       <c r="P342" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r04_c05/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r04_c05/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q342" s="349" t="inlineStr">
@@ -54222,7 +54222,7 @@
         <v/>
       </c>
       <c r="S342" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R342)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R342)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T342" s="349" t="inlineStr">
@@ -54335,7 +54335,7 @@
       </c>
       <c r="P343" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r04_c06/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r04_c06/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q343" s="349" t="inlineStr">
@@ -54348,7 +54348,7 @@
         <v/>
       </c>
       <c r="S343" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R343)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R343)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T343" s="349" t="inlineStr">
@@ -54461,7 +54461,7 @@
       </c>
       <c r="P344" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r05_c01/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r05_c01/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q344" s="349" t="inlineStr">
@@ -54474,7 +54474,7 @@
         <v/>
       </c>
       <c r="S344" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R344)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R344)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T344" s="349" t="inlineStr">
@@ -54587,7 +54587,7 @@
       </c>
       <c r="P345" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r05_c02/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r05_c02/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q345" s="349" t="inlineStr">
@@ -54600,7 +54600,7 @@
         <v/>
       </c>
       <c r="S345" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R345)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R345)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T345" s="349" t="inlineStr">
@@ -54713,7 +54713,7 @@
       </c>
       <c r="P346" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r05_c03/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r05_c03/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q346" s="349" t="inlineStr">
@@ -54726,7 +54726,7 @@
         <v/>
       </c>
       <c r="S346" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R346)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R346)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T346" s="349" t="inlineStr">
@@ -54839,7 +54839,7 @@
       </c>
       <c r="P347" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r05_c04/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r05_c04/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q347" s="349" t="inlineStr">
@@ -54852,7 +54852,7 @@
         <v/>
       </c>
       <c r="S347" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R347)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R347)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T347" s="349" t="inlineStr">
@@ -54965,7 +54965,7 @@
       </c>
       <c r="P348" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r05_c05/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r05_c05/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q348" s="349" t="inlineStr">
@@ -54978,7 +54978,7 @@
         <v/>
       </c>
       <c r="S348" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R348)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R348)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T348" s="349" t="inlineStr">
@@ -55091,7 +55091,7 @@
       </c>
       <c r="P349" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r05_c06/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r05_c06/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q349" s="349" t="inlineStr">
@@ -55104,7 +55104,7 @@
         <v/>
       </c>
       <c r="S349" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R349)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R349)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T349" s="349" t="inlineStr">
@@ -55217,7 +55217,7 @@
       </c>
       <c r="P350" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r06_c01/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r06_c01/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q350" s="349" t="inlineStr">
@@ -55230,7 +55230,7 @@
         <v/>
       </c>
       <c r="S350" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R350)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R350)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T350" s="349" t="inlineStr">
@@ -55343,7 +55343,7 @@
       </c>
       <c r="P351" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r06_c02/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r06_c02/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q351" s="349" t="inlineStr">
@@ -55356,7 +55356,7 @@
         <v/>
       </c>
       <c r="S351" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R351)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R351)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T351" s="349" t="inlineStr">
@@ -55469,7 +55469,7 @@
       </c>
       <c r="P352" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r06_c03/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r06_c03/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q352" s="349" t="inlineStr">
@@ -55482,7 +55482,7 @@
         <v/>
       </c>
       <c r="S352" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R352)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R352)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T352" s="349" t="inlineStr">
@@ -55595,7 +55595,7 @@
       </c>
       <c r="P353" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r06_c04/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r06_c04/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q353" s="349" t="inlineStr">
@@ -55608,7 +55608,7 @@
         <v/>
       </c>
       <c r="S353" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R353)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R353)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T353" s="349" t="inlineStr">
@@ -55721,7 +55721,7 @@
       </c>
       <c r="P354" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r06_c05/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r06_c05/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q354" s="349" t="inlineStr">
@@ -55734,7 +55734,7 @@
         <v/>
       </c>
       <c r="S354" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R354)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R354)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T354" s="349" t="inlineStr">
@@ -55847,7 +55847,7 @@
       </c>
       <c r="P355" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r06_c06/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/floor/tile_r06_c06/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q355" s="349" t="inlineStr">
@@ -55860,7 +55860,7 @@
         <v/>
       </c>
       <c r="S355" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R355)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R355)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T355" s="349" t="inlineStr">
@@ -55973,7 +55973,7 @@
       </c>
       <c r="P356" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_backwall_function_panel_system/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_backwall_function_panel_system/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q356" s="349" t="inlineStr">
@@ -55986,7 +55986,7 @@
         <v/>
       </c>
       <c r="S356" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R356)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R356)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T356" s="349" t="inlineStr">
@@ -56096,7 +56096,7 @@
       </c>
       <c r="P357" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_backwall_services/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_backwall_services/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q357" s="349" t="inlineStr">
@@ -56109,7 +56109,7 @@
         <v/>
       </c>
       <c r="S357" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R357)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R357)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T357" s="349" t="inlineStr">
@@ -56219,7 +56219,7 @@
       </c>
       <c r="P358" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_battery_cabinet/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_battery_cabinet/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q358" s="349" t="inlineStr">
@@ -56232,7 +56232,7 @@
         <v/>
       </c>
       <c r="S358" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R358)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R358)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T358" s="349" t="inlineStr">
@@ -56343,7 +56343,7 @@
       </c>
       <c r="P359" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_bed_and_bedding/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_bed_and_bedding/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q359" s="349" t="inlineStr">
@@ -56356,7 +56356,7 @@
         <v/>
       </c>
       <c r="S359" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R359)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R359)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T359" s="349" t="inlineStr">
@@ -56467,7 +56467,7 @@
       </c>
       <c r="P360" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_bedside_lamp/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_bedside_lamp/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q360" s="349" t="inlineStr">
@@ -56480,7 +56480,7 @@
         <v/>
       </c>
       <c r="S360" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R360)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R360)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T360" s="349" t="inlineStr">
@@ -56591,7 +56591,7 @@
       </c>
       <c r="P361" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_bedside_rug/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_bedside_rug/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q361" s="349" t="inlineStr">
@@ -56604,7 +56604,7 @@
         <v/>
       </c>
       <c r="S361" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R361)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R361)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T361" s="349" t="inlineStr">
@@ -56715,7 +56715,7 @@
       </c>
       <c r="P362" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_coffee_table/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_coffee_table/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q362" s="349" t="inlineStr">
@@ -56728,7 +56728,7 @@
         <v/>
       </c>
       <c r="S362" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R362)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R362)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T362" s="349" t="inlineStr">
@@ -56839,7 +56839,7 @@
       </c>
       <c r="P363" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_computer_workstation/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_computer_workstation/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q363" s="349" t="inlineStr">
@@ -56852,7 +56852,7 @@
         <v/>
       </c>
       <c r="S363" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R363)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R363)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T363" s="349" t="inlineStr">
@@ -56964,7 +56964,7 @@
       </c>
       <c r="P364" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_explore_poster/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_explore_poster/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q364" s="349" t="inlineStr">
@@ -56977,7 +56977,7 @@
         <v/>
       </c>
       <c r="S364" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R364)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R364)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T364" s="349" t="inlineStr">
@@ -57087,7 +57087,7 @@
       </c>
       <c r="P365" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_food_cabinet/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_food_cabinet/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q365" s="349" t="inlineStr">
@@ -57100,7 +57100,7 @@
         <v/>
       </c>
       <c r="S365" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R365)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R365)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T365" s="349" t="inlineStr">
@@ -57211,7 +57211,7 @@
       </c>
       <c r="P366" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_good_vibes_neon/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_good_vibes_neon/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q366" s="349" t="inlineStr">
@@ -57224,7 +57224,7 @@
         <v/>
       </c>
       <c r="S366" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R366)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R366)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T366" s="349" t="inlineStr">
@@ -57334,7 +57334,7 @@
       </c>
       <c r="P367" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_hanging_plant/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_hanging_plant/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q367" s="349" t="inlineStr">
@@ -57347,7 +57347,7 @@
         <v/>
       </c>
       <c r="S367" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R367)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R367)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T367" s="349" t="inlineStr">
@@ -57457,7 +57457,7 @@
       </c>
       <c r="P368" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_lounge_rug/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_lounge_rug/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q368" s="349" t="inlineStr">
@@ -57470,7 +57470,7 @@
         <v/>
       </c>
       <c r="S368" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R368)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R368)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T368" s="349" t="inlineStr">
@@ -57581,7 +57581,7 @@
       </c>
       <c r="P369" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_lounge_sofa/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_lounge_sofa/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q369" s="349" t="inlineStr">
@@ -57594,7 +57594,7 @@
         <v/>
       </c>
       <c r="S369" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R369)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R369)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T369" s="349" t="inlineStr">
@@ -57706,7 +57706,7 @@
       </c>
       <c r="P370" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_medical_cabinet/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_medical_cabinet/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q370" s="349" t="inlineStr">
@@ -57719,7 +57719,7 @@
         <v/>
       </c>
       <c r="S370" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R370)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R370)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T370" s="349" t="inlineStr">
@@ -57830,7 +57830,7 @@
       </c>
       <c r="P371" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_nightstand/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_nightstand/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q371" s="349" t="inlineStr">
@@ -57843,7 +57843,7 @@
         <v/>
       </c>
       <c r="S371" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R371)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R371)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T371" s="349" t="inlineStr">
@@ -57954,7 +57954,7 @@
       </c>
       <c r="P372" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_office_chair/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_office_chair/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q372" s="349" t="inlineStr">
@@ -57967,7 +57967,7 @@
         <v/>
       </c>
       <c r="S372" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R372)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R372)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T372" s="349" t="inlineStr">
@@ -58078,7 +58078,7 @@
       </c>
       <c r="P373" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_pouf_01/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_pouf_01/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q373" s="349" t="inlineStr">
@@ -58091,7 +58091,7 @@
         <v/>
       </c>
       <c r="S373" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R373)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R373)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T373" s="349" t="inlineStr">
@@ -58202,7 +58202,7 @@
       </c>
       <c r="P374" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_pouf_02/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_pouf_02/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q374" s="349" t="inlineStr">
@@ -58215,7 +58215,7 @@
         <v/>
       </c>
       <c r="S374" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R374)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R374)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T374" s="349" t="inlineStr">
@@ -58326,7 +58326,7 @@
       </c>
       <c r="P375" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_side_table/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_side_table/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q375" s="349" t="inlineStr">
@@ -58339,7 +58339,7 @@
         <v/>
       </c>
       <c r="S375" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R375)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R375)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T375" s="349" t="inlineStr">
@@ -58450,7 +58450,7 @@
       </c>
       <c r="P376" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_stay_curious_neon/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_stay_curious_neon/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q376" s="349" t="inlineStr">
@@ -58463,7 +58463,7 @@
         <v/>
       </c>
       <c r="S376" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R376)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R376)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T376" s="349" t="inlineStr">
@@ -58573,7 +58573,7 @@
       </c>
       <c r="P377" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_striped_privacy_curtain/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_striped_privacy_curtain/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q377" s="349" t="inlineStr">
@@ -58586,7 +58586,7 @@
         <v/>
       </c>
       <c r="S377" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R377)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R377)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T377" s="349" t="inlineStr">
@@ -58697,7 +58697,7 @@
       </c>
       <c r="P378" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_tool_pegboard/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/loft/loft_tool_pegboard/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q378" s="349" t="inlineStr">
@@ -58710,7 +58710,7 @@
         <v/>
       </c>
       <c r="S378" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R378)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R378)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T378" s="349" t="inlineStr">
@@ -58820,7 +58820,7 @@
       </c>
       <c r="P379" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/support/corridor_emergency_light_group/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/support/corridor_emergency_light_group/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q379" s="349" t="inlineStr">
@@ -58833,7 +58833,7 @@
         <v/>
       </c>
       <c r="S379" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R379)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R379)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T379" s="349" t="inlineStr">
@@ -58868,12 +58868,12 @@
     <row r="380" ht="54" customHeight="1">
       <c r="A380" t="inlineStr">
         <is>
-          <t>BPK-BASE99-EQUIPMENT-STEAM-FX</t>
+          <t>BPK-BASE99-LOFT-LIGHTING-SUPPORT</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>基地99层 · 设备蒸汽动效组</t>
+          <t>基地99层 · 二楼分层照明支持</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -58888,7 +58888,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>base99_package_equipment_steam_fx</t>
+          <t>base99_package_loft_lighting_support</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -58908,7 +58908,7 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>static / default</t>
+          <t>static / fixture_light</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
@@ -58933,22 +58933,22 @@
       </c>
       <c r="N380" s="349" t="inlineStr">
         <is>
-          <t>包络 18.064×2.326×1.133m；10 网格；0 灯</t>
+          <t>包络 18.321×9.467×5.292m；8 网格；4 灯</t>
         </is>
       </c>
       <c r="O380" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/component_packages/support/equipment_steam_fx/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/component_packages/support/loft_lighting_support/asset_manifest.json</t>
         </is>
       </c>
       <c r="P380" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/support/equipment_steam_fx/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/support/loft_lighting_support/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q380" s="349" t="inlineStr">
         <is>
-          <t>基地99层;基地资产包;3D设施;环境支持包;equipment_steam_fx;PaletteUV</t>
+          <t>基地99层;基地资产包;3D设施;环境支持包;loft_lighting_support;PaletteUV</t>
         </is>
       </c>
       <c r="R380" s="349">
@@ -58956,12 +58956,12 @@
         <v/>
       </c>
       <c r="S380" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R380)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R380)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T380" s="349" t="inlineStr">
         <is>
-          <t>4a8443d20ccf76de6a16363539963169732bac5672274b60c569e88a1a748681</t>
+          <t>abe38c11684b2be621edcb448b12850da7d3472d215e9f18c78a0a9592948f23</t>
         </is>
       </c>
       <c r="U380" s="349" t="inlineStr">
@@ -58979,24 +58979,25 @@
       </c>
       <c r="X380" s="375" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>50</t>
         </is>
       </c>
       <c r="Y380" s="349" t="inlineStr">
         <is>
-          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::equipment_steam_fx；对象 10；中心 (0.168, -10.450, 3.142)m；朝向 Blender +Y north；预期导出 equipment_steam_fx_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
+          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_lighting_support；对象 12；中心 (2.961, 9.986, 8.854)m；朝向 Blender +Y north；预期导出 loft_lighting_support_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-05：运行时Prefab根节点Y=-1偏移已撤销，阁楼资产恢复Blender烘焙高度（整体上移1m）。</t>
         </is>
       </c>
     </row>
     <row r="381" ht="54" customHeight="1">
       <c r="A381" t="inlineStr">
         <is>
-          <t>BPK-BASE99-LOFT-LIGHTING-SUPPORT</t>
+          <t>BPK-BASE99-VOLUMETRIC-DUST-FX</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>基地99层 · 二楼分层照明支持</t>
+          <t>基地99层 · 光束尘埃动效组</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -59011,7 +59012,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>base99_package_loft_lighting_support</t>
+          <t>base99_package_volumetric_dust_fx</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -59031,7 +59032,7 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>static / fixture_light</t>
+          <t>static / default</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
@@ -59056,22 +59057,22 @@
       </c>
       <c r="N381" s="349" t="inlineStr">
         <is>
-          <t>包络 18.321×9.467×5.292m；8 网格；4 灯</t>
+          <t>包络 23.750×12.014×6.494m；28 网格；0 灯</t>
         </is>
       </c>
       <c r="O381" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/component_packages/support/loft_lighting_support/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/component_packages/support/volumetric_dust_fx/asset_manifest.json</t>
         </is>
       </c>
       <c r="P381" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/support/loft_lighting_support/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/support/volumetric_dust_fx/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q381" s="349" t="inlineStr">
         <is>
-          <t>基地99层;基地资产包;3D设施;环境支持包;loft_lighting_support;PaletteUV</t>
+          <t>基地99层;基地资产包;3D设施;环境支持包;volumetric_dust_fx;PaletteUV</t>
         </is>
       </c>
       <c r="R381" s="349">
@@ -59079,12 +59080,12 @@
         <v/>
       </c>
       <c r="S381" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R381)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R381)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T381" s="349" t="inlineStr">
         <is>
-          <t>abe38c11684b2be621edcb448b12850da7d3472d215e9f18c78a0a9592948f23</t>
+          <t>70a699d6ddb5c3005b0c982960be90e7997595c76c6b22110d635452f3fde467</t>
         </is>
       </c>
       <c r="U381" s="349" t="inlineStr">
@@ -59102,25 +59103,24 @@
       </c>
       <c r="X381" s="375" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>64</t>
         </is>
       </c>
       <c r="Y381" s="349" t="inlineStr">
         <is>
-          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::loft_lighting_support；对象 12；中心 (2.961, 9.986, 8.854)m；朝向 Blender +Y north；预期导出 loft_lighting_support_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
-2026-09-05：运行时Prefab根节点Y=-1偏移已撤销，阁楼资产恢复Blender烘焙高度（整体上移1m）。</t>
+          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::volumetric_dust_fx；对象 28；中心 (0.204, -0.015, 4.725)m；朝向 Blender +Y north；预期导出 volumetric_dust_fx_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
         </is>
       </c>
     </row>
     <row r="382" ht="54" customHeight="1">
       <c r="A382" t="inlineStr">
         <is>
-          <t>BPK-BASE99-VOLUMETRIC-DUST-FX</t>
+          <t>BPK-BASE99-WAREHOUSE-PENDANT-LIGHT-GROUP</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>基地99层 · 光束尘埃动效组</t>
+          <t>基地99层 · 仓库防爆吊灯组</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -59135,7 +59135,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>base99_package_volumetric_dust_fx</t>
+          <t>base99_package_warehouse_pendant_light_group</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -59155,7 +59155,7 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>static / default</t>
+          <t>static / fixture_light</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
@@ -59180,22 +59180,22 @@
       </c>
       <c r="N382" s="349" t="inlineStr">
         <is>
-          <t>包络 23.750×12.014×6.494m；28 网格；0 灯</t>
+          <t>包络 21.242×8.043×1.220m；15 网格；5 灯</t>
         </is>
       </c>
       <c r="O382" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/component_packages/support/volumetric_dust_fx/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/component_packages/support/warehouse_pendant_light_group/asset_manifest.json</t>
         </is>
       </c>
       <c r="P382" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/support/volumetric_dust_fx/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/support/warehouse_pendant_light_group/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q382" s="349" t="inlineStr">
         <is>
-          <t>基地99层;基地资产包;3D设施;环境支持包;volumetric_dust_fx;PaletteUV</t>
+          <t>基地99层;基地资产包;3D设施;环境支持包;warehouse_pendant_light_group;PaletteUV</t>
         </is>
       </c>
       <c r="R382" s="349">
@@ -59203,12 +59203,12 @@
         <v/>
       </c>
       <c r="S382" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R382)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R382)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T382" s="349" t="inlineStr">
         <is>
-          <t>70a699d6ddb5c3005b0c982960be90e7997595c76c6b22110d635452f3fde467</t>
+          <t>543f336c346e31fd89c4cf60b28a843e41023b7cd8be1b1d1036b3e28b711343</t>
         </is>
       </c>
       <c r="U382" s="349" t="inlineStr">
@@ -59226,24 +59226,24 @@
       </c>
       <c r="X382" s="375" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>61</t>
         </is>
       </c>
       <c r="Y382" s="349" t="inlineStr">
         <is>
-          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::volumetric_dust_fx；对象 28；中心 (0.204, -0.015, 4.725)m；朝向 Blender +Y north；预期导出 volumetric_dust_fx_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
+          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::warehouse_pendant_light_group；对象 25；中心 (0.005, 0.008, 7.490)m；朝向 Blender +Y north；预期导出 warehouse_pendant_light_group_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
         </is>
       </c>
     </row>
     <row r="383" ht="54" customHeight="1">
       <c r="A383" t="inlineStr">
         <is>
-          <t>BPK-BASE99-WAREHOUSE-PENDANT-LIGHT-GROUP</t>
+          <t>BPK-BASE99-ACCESS-TERMINAL</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>基地99层 · 仓库防爆吊灯组</t>
+          <t>基地99层 · ACCESS门禁终端</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -59253,12 +59253,12 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>环境支持包</t>
+          <t>阁楼下方固定设施包</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>base99_package_warehouse_pendant_light_group</t>
+          <t>base99_package_access_terminal</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -59278,7 +59278,7 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>static / fixture_light</t>
+          <t>static / default</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
@@ -59303,22 +59303,22 @@
       </c>
       <c r="N383" s="349" t="inlineStr">
         <is>
-          <t>包络 21.242×8.043×1.220m；15 网格；5 灯</t>
+          <t>包络 0.560×0.383×1.030m；9 网格；0 灯</t>
         </is>
       </c>
       <c r="O383" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/component_packages/support/warehouse_pendant_light_group/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/component_packages/underloft/access_terminal/asset_manifest.json</t>
         </is>
       </c>
       <c r="P383" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/support/warehouse_pendant_light_group/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/underloft/access_terminal/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q383" s="349" t="inlineStr">
         <is>
-          <t>基地99层;基地资产包;3D设施;环境支持包;warehouse_pendant_light_group;PaletteUV</t>
+          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;access_terminal;PaletteUV</t>
         </is>
       </c>
       <c r="R383" s="349">
@@ -59326,12 +59326,12 @@
         <v/>
       </c>
       <c r="S383" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R383)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R383)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T383" s="349" t="inlineStr">
         <is>
-          <t>543f336c346e31fd89c4cf60b28a843e41023b7cd8be1b1d1036b3e28b711343</t>
+          <t>36db763dbbc616a69a135d71b83b094d1773b8196858c2340505527cf8574f1f</t>
         </is>
       </c>
       <c r="U383" s="349" t="inlineStr">
@@ -59349,24 +59349,24 @@
       </c>
       <c r="X383" s="375" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>52</t>
         </is>
       </c>
       <c r="Y383" s="349" t="inlineStr">
         <is>
-          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::warehouse_pendant_light_group；对象 25；中心 (0.005, 0.008, 7.490)m；朝向 Blender +Y north；预期导出 warehouse_pendant_light_group_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
+          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::access_terminal；对象 9；中心 (1.350, 4.309, 2.045)m；朝向 Blender +Y north；预期导出 access_terminal_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
         </is>
       </c>
     </row>
     <row r="384" ht="54" customHeight="1">
       <c r="A384" t="inlineStr">
         <is>
-          <t>BPK-BASE99-ACCESS-TERMINAL</t>
+          <t>BPK-BASE99-BASE-CAMP-NEON-SIGN</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>基地99层 · ACCESS门禁终端</t>
+          <t>基地99层 · BASE_CAMP立体霓虹标识</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -59381,7 +59381,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>base99_package_access_terminal</t>
+          <t>base99_package_base_camp_neon_sign</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -59401,7 +59401,7 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>static / default</t>
+          <t>static / fixture_light</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
@@ -59426,22 +59426,22 @@
       </c>
       <c r="N384" s="349" t="inlineStr">
         <is>
-          <t>包络 0.560×0.383×1.030m；9 网格；0 灯</t>
+          <t>包络 7.800×0.845×0.998m；17 网格；2 灯</t>
         </is>
       </c>
       <c r="O384" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/component_packages/underloft/access_terminal/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/component_packages/underloft/base_camp_neon_sign/asset_manifest.json</t>
         </is>
       </c>
       <c r="P384" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/underloft/access_terminal/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/underloft/base_camp_neon_sign/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q384" s="349" t="inlineStr">
         <is>
-          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;access_terminal;PaletteUV</t>
+          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;base_camp_neon_sign;PaletteUV</t>
         </is>
       </c>
       <c r="R384" s="349">
@@ -59449,12 +59449,12 @@
         <v/>
       </c>
       <c r="S384" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R384)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R384)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T384" s="349" t="inlineStr">
         <is>
-          <t>36db763dbbc616a69a135d71b83b094d1773b8196858c2340505527cf8574f1f</t>
+          <t>ba7d0fb2dbba09a1b860340c6b59b47c6b1eb598ab8b502ee36e288272de2e45</t>
         </is>
       </c>
       <c r="U384" s="349" t="inlineStr">
@@ -59472,24 +59472,24 @@
       </c>
       <c r="X384" s="375" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Y384" s="349" t="inlineStr">
         <is>
-          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::access_terminal；对象 9；中心 (1.350, 4.309, 2.045)m；朝向 Blender +Y north；预期导出 access_terminal_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
+          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::base_camp_neon_sign；对象 19；中心 (5.000, 4.603, 4.439)m；朝向 Blender +Y north；预期导出 base_camp_neon_sign_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
         </is>
       </c>
     </row>
     <row r="385" ht="54" customHeight="1">
       <c r="A385" t="inlineStr">
         <is>
-          <t>BPK-BASE99-BASE-CAMP-NEON-SIGN</t>
+          <t>BPK-BASE99-BASE-CAMP-ROLLUP-MAIN-DOOR</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>基地99层 · BASE_CAMP立体霓虹标识</t>
+          <t>基地99层 · BASE_CAMP大型卷帘主门</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -59504,7 +59504,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>base99_package_base_camp_neon_sign</t>
+          <t>base99_package_base_camp_rollup_main_door</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -59534,7 +59534,7 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>已优化并正式接入</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -59544,27 +59544,27 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>v017</t>
+          <t>v024</t>
         </is>
       </c>
       <c r="N385" s="349" t="inlineStr">
         <is>
-          <t>包络 7.800×0.845×0.998m；17 网格；2 灯</t>
+          <t>包络 6.440×0.910×2.920m；顶视角优化；向下朝向面已剔除；单一盒体阻挡</t>
         </is>
       </c>
       <c r="O385" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/component_packages/underloft/base_camp_neon_sign/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/component_packages/underloft/base_camp_rollup_main_door/asset_manifest.json</t>
         </is>
       </c>
       <c r="P385" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/underloft/base_camp_neon_sign/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/underloft/base_camp_rollup_main_door/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q385" s="349" t="inlineStr">
         <is>
-          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;base_camp_neon_sign;PaletteUV</t>
+          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;base_camp_rollup_main_door;PaletteUV</t>
         </is>
       </c>
       <c r="R385" s="349">
@@ -59572,12 +59572,12 @@
         <v/>
       </c>
       <c r="S385" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R385)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R385)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T385" s="349" t="inlineStr">
         <is>
-          <t>ba7d0fb2dbba09a1b860340c6b59b47c6b1eb598ab8b502ee36e288272de2e45</t>
+          <t>10136ee036092b66b19780625e92a9f7bc808770838a285a8f1c52bc44e88581</t>
         </is>
       </c>
       <c r="U385" s="349" t="inlineStr">
@@ -59595,24 +59595,24 @@
       </c>
       <c r="X385" s="375" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Y385" s="349" t="inlineStr">
         <is>
-          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::base_camp_neon_sign；对象 19；中心 (5.000, 4.603, 4.439)m；朝向 Blender +Y north；预期导出 base_camp_neon_sign_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
+          <t>2026-09-05：42号由 base_facility_runtime_layout_hq_v017.blend 进入V021优化流程并正式导入；运行时使用 base_camp_rollup_main_door_visual_top3d_v001.glb，单一BoxShape3D阻挡按V017包络尺寸 6.440×0.910×2.920m 对齐；验收：verify_base99_remaining_facilities_v021。</t>
         </is>
       </c>
     </row>
     <row r="386" ht="54" customHeight="1">
       <c r="A386" t="inlineStr">
         <is>
-          <t>BPK-BASE99-BASE-CAMP-ROLLUP-MAIN-DOOR</t>
+          <t>BPK-BASE99-BASE-STATUS-TERMINAL</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>基地99层 · BASE_CAMP大型卷帘主门</t>
+          <t>基地99层 · BASE_STATUS状态终端</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -59627,7 +59627,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>base99_package_base_camp_rollup_main_door</t>
+          <t>base99_package_base_status_terminal</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -59647,7 +59647,7 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>static / fixture_light</t>
+          <t>static / default</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
@@ -59657,7 +59657,7 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>已优化并正式接入</t>
+          <t>Blender源已完成</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -59667,27 +59667,27 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>v024</t>
+          <t>v017</t>
         </is>
       </c>
       <c r="N386" s="349" t="inlineStr">
         <is>
-          <t>包络 6.440×0.910×2.920m；顶视角优化；向下朝向面已剔除；单一盒体阻挡</t>
+          <t>包络 0.620×0.520×0.940m；10 网格；0 灯</t>
         </is>
       </c>
       <c r="O386" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/component_packages/underloft/base_camp_rollup_main_door/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/component_packages/underloft/base_status_terminal/asset_manifest.json</t>
         </is>
       </c>
       <c r="P386" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/underloft/base_camp_rollup_main_door/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/underloft/base_status_terminal/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q386" s="349" t="inlineStr">
         <is>
-          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;base_camp_rollup_main_door;PaletteUV</t>
+          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;base_status_terminal;PaletteUV</t>
         </is>
       </c>
       <c r="R386" s="349">
@@ -59695,12 +59695,12 @@
         <v/>
       </c>
       <c r="S386" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R386)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R386)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T386" s="349" t="inlineStr">
         <is>
-          <t>10136ee036092b66b19780625e92a9f7bc808770838a285a8f1c52bc44e88581</t>
+          <t>f5083ec93792056dedf834c275351c144170c170e265c45907654bab1a2e2d18</t>
         </is>
       </c>
       <c r="U386" s="349" t="inlineStr">
@@ -59718,24 +59718,24 @@
       </c>
       <c r="X386" s="375" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>53</t>
         </is>
       </c>
       <c r="Y386" s="349" t="inlineStr">
         <is>
-          <t>2026-09-05：42号由 base_facility_runtime_layout_hq_v017.blend 进入V021优化流程并正式导入；运行时使用 base_camp_rollup_main_door_visual_top3d_v001.glb，单一BoxShape3D阻挡按V017包络尺寸 6.440×0.910×2.920m 对齐；验收：verify_base99_remaining_facilities_v021。</t>
+          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::base_status_terminal；对象 10；中心 (8.380, 3.580, 1.620)m；朝向 Blender +Y north；预期导出 base_status_terminal_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
         </is>
       </c>
     </row>
     <row r="387" ht="54" customHeight="1">
       <c r="A387" t="inlineStr">
         <is>
-          <t>BPK-BASE99-BASE-STATUS-TERMINAL</t>
+          <t>BPK-BASE99-HOLOGRAM-TERMINAL-PLATFORM</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>基地99层 · BASE_STATUS状态终端</t>
+          <t>基地99层 · 圆形全息设备平台</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -59750,7 +59750,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>base99_package_base_status_terminal</t>
+          <t>base99_package_hologram_terminal_platform</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -59770,7 +59770,7 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>static / default</t>
+          <t>static / fixture_light</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
@@ -59790,27 +59790,27 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>v017</t>
+          <t>v022</t>
         </is>
       </c>
       <c r="N387" s="349" t="inlineStr">
         <is>
-          <t>包络 0.620×0.520×0.940m；10 网格；0 灯</t>
+          <t>包络 2.409×2.409×1.825m；38 网格；1 灯</t>
         </is>
       </c>
       <c r="O387" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/component_packages/underloft/base_status_terminal/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/component_packages/underloft/hologram_terminal_platform/asset_manifest.json</t>
         </is>
       </c>
       <c r="P387" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/underloft/base_status_terminal/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/underloft/hologram_terminal_platform/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q387" s="349" t="inlineStr">
         <is>
-          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;base_status_terminal;PaletteUV</t>
+          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;hologram_terminal_platform;PaletteUV</t>
         </is>
       </c>
       <c r="R387" s="349">
@@ -59818,12 +59818,12 @@
         <v/>
       </c>
       <c r="S387" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R387)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R387)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T387" s="349" t="inlineStr">
         <is>
-          <t>f5083ec93792056dedf834c275351c144170c170e265c45907654bab1a2e2d18</t>
+          <t>761b1591ee608316a47fa06e85a5a7f2a18d87dac3cb80f5294b54c47813852d</t>
         </is>
       </c>
       <c r="U387" s="349" t="inlineStr">
@@ -59841,24 +59841,24 @@
       </c>
       <c r="X387" s="375" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51</t>
         </is>
       </c>
       <c r="Y387" s="349" t="inlineStr">
         <is>
-          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::base_status_terminal；对象 10；中心 (8.380, 3.580, 1.620)m；朝向 Blender +Y north；预期导出 base_status_terminal_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
+          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::hologram_terminal_platform；对象 39；中心 (5.000, 1.720, 0.952)m；朝向 Blender +Y north；预期导出 hologram_terminal_platform_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
         </is>
       </c>
     </row>
     <row r="388" ht="54" customHeight="1">
       <c r="A388" t="inlineStr">
         <is>
-          <t>BPK-BASE99-HOLOGRAM-TERMINAL-PLATFORM</t>
+          <t>BPK-BASE99-MAIN-DOOR-LOW-STORAGE-CABINET</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>基地99层 · 圆形全息设备平台</t>
+          <t>基地99层 · 主门下方低矮设备柜</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -59873,7 +59873,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>base99_package_hologram_terminal_platform</t>
+          <t>base99_package_main_door_low_storage_cabinet</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -59893,7 +59893,7 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>static / fixture_light</t>
+          <t>static / default</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
@@ -59913,27 +59913,27 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>v022</t>
+          <t>v017</t>
         </is>
       </c>
       <c r="N388" s="349" t="inlineStr">
         <is>
-          <t>包络 2.409×2.409×1.825m；38 网格；1 灯</t>
+          <t>包络 6.280×1.230×2.060m；31 网格；0 灯</t>
         </is>
       </c>
       <c r="O388" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/component_packages/underloft/hologram_terminal_platform/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/component_packages/underloft/main_door_low_storage_cabinet/asset_manifest.json</t>
         </is>
       </c>
       <c r="P388" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/underloft/hologram_terminal_platform/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/underloft/main_door_low_storage_cabinet/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q388" s="349" t="inlineStr">
         <is>
-          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;hologram_terminal_platform;PaletteUV</t>
+          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;main_door_low_storage_cabinet;PaletteUV</t>
         </is>
       </c>
       <c r="R388" s="349">
@@ -59941,12 +59941,12 @@
         <v/>
       </c>
       <c r="S388" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R388)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R388)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T388" s="349" t="inlineStr">
         <is>
-          <t>761b1591ee608316a47fa06e85a5a7f2a18d87dac3cb80f5294b54c47813852d</t>
+          <t>5fa3be4b090c09f631db5d18960be6180696449b04bcba402aba6d34674fb928</t>
         </is>
       </c>
       <c r="U388" s="349" t="inlineStr">
@@ -59964,24 +59964,24 @@
       </c>
       <c r="X388" s="375" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>43</t>
         </is>
       </c>
       <c r="Y388" s="349" t="inlineStr">
         <is>
-          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::hologram_terminal_platform；对象 39；中心 (5.000, 1.720, 0.952)m；朝向 Blender +Y north；预期导出 hologram_terminal_platform_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
+          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::main_door_low_storage_cabinet；对象 31；中心 (5.000, 3.955, 1.050)m；朝向 Blender +Y north；预期导出 main_door_low_storage_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
         </is>
       </c>
     </row>
     <row r="389" ht="54" customHeight="1">
       <c r="A389" t="inlineStr">
         <is>
-          <t>BPK-BASE99-MAIN-DOOR-LOW-STORAGE-CABINET</t>
+          <t>BPK-BASE99-MEDICAL-CABINET</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>基地99层 · 主门下方低矮设备柜</t>
+          <t>基地99层 · MEDICAL医疗柜</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -59996,7 +59996,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>base99_package_main_door_low_storage_cabinet</t>
+          <t>base99_package_medical_cabinet</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -60026,7 +60026,7 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -60041,22 +60041,22 @@
       </c>
       <c r="N389" s="349" t="inlineStr">
         <is>
-          <t>包络 6.280×1.230×2.060m；31 网格；0 灯</t>
+          <t>包络 1.580×0.973×3.330m；28 网格；0 灯</t>
         </is>
       </c>
       <c r="O389" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/component_packages/underloft/main_door_low_storage_cabinet/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/component_packages/underloft/medical_cabinet/asset_manifest.json</t>
         </is>
       </c>
       <c r="P389" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/underloft/main_door_low_storage_cabinet/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/underloft/medical_cabinet/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q389" s="349" t="inlineStr">
         <is>
-          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;main_door_low_storage_cabinet;PaletteUV</t>
+          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;medical_cabinet;PaletteUV; base_recovery</t>
         </is>
       </c>
       <c r="R389" s="349">
@@ -60064,12 +60064,12 @@
         <v/>
       </c>
       <c r="S389" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R389)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R389)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T389" s="349" t="inlineStr">
         <is>
-          <t>5fa3be4b090c09f631db5d18960be6180696449b04bcba402aba6d34674fb928</t>
+          <t>e5d0bcd80ad4c56e60e6e5ead83154e036d46f6b3e7c7fd691c8d2eb12073f79</t>
         </is>
       </c>
       <c r="U389" s="349" t="inlineStr">
@@ -60087,24 +60087,25 @@
       </c>
       <c r="X389" s="375" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Y389" s="349" t="inlineStr">
         <is>
-          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::main_door_low_storage_cabinet；对象 31；中心 (5.000, 3.955, 1.050)m；朝向 Blender +Y north；预期导出 main_door_low_storage_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
+          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::medical_cabinet；对象 28；中心 (-3.650, 4.333, 1.685)m；朝向 Blender +Y north；预期导出 medical_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-12：新增TowerDescent99F玩法包装 assets/art/environments/base_facility_3d/runtime/env_base99_remaining_facilities_v021/medical_cabinet/medical_cabinet_facility_top3d_v001.tscn；绑定base_recovery；交互区为源包碰撞包围盒+0.8m；源资产坐标与碰撞保持。</t>
         </is>
       </c>
     </row>
     <row r="390" ht="54" customHeight="1">
       <c r="A390" t="inlineStr">
         <is>
-          <t>BPK-BASE99-MEDICAL-CABINET</t>
+          <t>BPK-BASE99-NARROW-BATTERY-CABINET</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>基地99层 · MEDICAL医疗柜</t>
+          <t>基地99层 · 窄型电池柜</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -60119,7 +60120,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>base99_package_medical_cabinet</t>
+          <t>base99_package_narrow_battery_cabinet</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -60164,22 +60165,22 @@
       </c>
       <c r="N390" s="349" t="inlineStr">
         <is>
-          <t>包络 1.580×0.973×3.330m；28 网格；0 灯</t>
+          <t>包络 1.580×0.983×3.220m；23 网格；0 灯</t>
         </is>
       </c>
       <c r="O390" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/component_packages/underloft/medical_cabinet/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/component_packages/underloft/narrow_battery_cabinet/asset_manifest.json</t>
         </is>
       </c>
       <c r="P390" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/underloft/medical_cabinet/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/underloft/narrow_battery_cabinet/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q390" s="349" t="inlineStr">
         <is>
-          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;medical_cabinet;PaletteUV; base_recovery</t>
+          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;narrow_battery_cabinet;PaletteUV; vault</t>
         </is>
       </c>
       <c r="R390" s="349">
@@ -60187,12 +60188,12 @@
         <v/>
       </c>
       <c r="S390" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R390)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R390)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T390" s="349" t="inlineStr">
         <is>
-          <t>e5d0bcd80ad4c56e60e6e5ead83154e036d46f6b3e7c7fd691c8d2eb12073f79</t>
+          <t>8d0866fc43cd1c50b0977d3b37c81ec27ad5203055dec4da99117ff788d45f2e</t>
         </is>
       </c>
       <c r="U390" s="349" t="inlineStr">
@@ -60210,25 +60211,25 @@
       </c>
       <c r="X390" s="375" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47</t>
         </is>
       </c>
       <c r="Y390" s="349" t="inlineStr">
         <is>
-          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::medical_cabinet；对象 28；中心 (-3.650, 4.333, 1.685)m；朝向 Blender +Y north；预期导出 medical_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
-2026-09-12：新增TowerDescent99F玩法包装 assets/art/environments/base_facility_3d/runtime/env_base99_remaining_facilities_v021/medical_cabinet/medical_cabinet_facility_top3d_v001.tscn；绑定base_recovery；交互区为源包碰撞包围盒+0.8m；源资产坐标与碰撞保持。</t>
+          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::narrow_battery_cabinet；对象 23；中心 (11.850, 4.329, 1.630)m；朝向 Blender +Y north；预期导出 narrow_battery_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
+2026-09-12：新增TowerDescent99F玩法包装 assets/art/environments/base_facility_3d/runtime/env_base99_remaining_facilities_v021/narrow_battery_cabinet/narrow_battery_cabinet_facility_top3d_v001.tscn；绑定vault；交互区为源包碰撞包围盒+0.8m；源资产坐标与碰撞保持。</t>
         </is>
       </c>
     </row>
     <row r="391" ht="54" customHeight="1">
       <c r="A391" t="inlineStr">
         <is>
-          <t>BPK-BASE99-NARROW-BATTERY-CABINET</t>
+          <t>BPK-BASE99-NARROW-EMERGENCY-CABINET</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>基地99层 · 窄型电池柜</t>
+          <t>基地99层 · 窄型应急柜</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -60243,7 +60244,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>base99_package_narrow_battery_cabinet</t>
+          <t>base99_package_narrow_emergency_cabinet</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -60273,7 +60274,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>正式美术已接入</t>
+          <t>Blender源已完成</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -60288,22 +60289,22 @@
       </c>
       <c r="N391" s="349" t="inlineStr">
         <is>
-          <t>包络 1.580×0.983×3.220m；23 网格；0 灯</t>
+          <t>包络 1.580×0.985×3.220m；24 网格；0 灯</t>
         </is>
       </c>
       <c r="O391" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/component_packages/underloft/narrow_battery_cabinet/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/component_packages/underloft/narrow_emergency_cabinet/asset_manifest.json</t>
         </is>
       </c>
       <c r="P391" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/underloft/narrow_battery_cabinet/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/underloft/narrow_emergency_cabinet/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q391" s="349" t="inlineStr">
         <is>
-          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;narrow_battery_cabinet;PaletteUV; vault</t>
+          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;narrow_emergency_cabinet;PaletteUV</t>
         </is>
       </c>
       <c r="R391" s="349">
@@ -60311,12 +60312,12 @@
         <v/>
       </c>
       <c r="S391" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R391)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R391)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T391" s="349" t="inlineStr">
         <is>
-          <t>8d0866fc43cd1c50b0977d3b37c81ec27ad5203055dec4da99117ff788d45f2e</t>
+          <t>2d3e67ae01fb8d2722d637fd58c007ced90f44746aec4301eb762814acb1ed45</t>
         </is>
       </c>
       <c r="U391" s="349" t="inlineStr">
@@ -60334,25 +60335,24 @@
       </c>
       <c r="X391" s="375" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="Y391" s="349" t="inlineStr">
         <is>
-          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::narrow_battery_cabinet；对象 23；中心 (11.850, 4.329, 1.630)m；朝向 Blender +Y north；预期导出 narrow_battery_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。
-2026-09-12：新增TowerDescent99F玩法包装 assets/art/environments/base_facility_3d/runtime/env_base99_remaining_facilities_v021/narrow_battery_cabinet/narrow_battery_cabinet_facility_top3d_v001.tscn；绑定vault；交互区为源包碰撞包围盒+0.8m；源资产坐标与碰撞保持。</t>
+          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::narrow_emergency_cabinet；对象 24；中心 (13.650, 4.327, 1.630)m；朝向 Blender +Y north；预期导出 narrow_emergency_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
         </is>
       </c>
     </row>
     <row r="392" ht="54" customHeight="1">
       <c r="A392" t="inlineStr">
         <is>
-          <t>BPK-BASE99-NARROW-EMERGENCY-CABINET</t>
+          <t>BPK-BASE99-SOUTH-INDUSTRIAL-WALL-DETAILS</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>基地99层 · 窄型应急柜</t>
+          <t>基地99层 · 南墙工业墙板附着结构</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -60367,7 +60367,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>base99_package_narrow_emergency_cabinet</t>
+          <t>base99_package_south_industrial_wall_details</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -60412,22 +60412,22 @@
       </c>
       <c r="N392" s="349" t="inlineStr">
         <is>
-          <t>包络 1.580×0.985×3.220m；24 网格；0 灯</t>
+          <t>包络 19.500×0.530×4.785m；53 网格；0 灯</t>
         </is>
       </c>
       <c r="O392" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/component_packages/underloft/narrow_emergency_cabinet/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/component_packages/underloft/south_industrial_wall_details/asset_manifest.json</t>
         </is>
       </c>
       <c r="P392" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/underloft/narrow_emergency_cabinet/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/underloft/south_industrial_wall_details/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q392" s="349" t="inlineStr">
         <is>
-          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;narrow_emergency_cabinet;PaletteUV</t>
+          <t>基地99层;基地资产包;3D设施;阁楼下方固定设施包;south_industrial_wall_details;PaletteUV</t>
         </is>
       </c>
       <c r="R392" s="349">
@@ -60435,12 +60435,12 @@
         <v/>
       </c>
       <c r="S392" s="349">
-        <f>IF(COUNTIF($R$6:$R$424,R392)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$423,R392)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T392" s="349" t="inlineStr">
         <is>
-          <t>2d3e67ae01fb8d2722d637fd58c007ced90f44746aec4301eb762814acb1ed45</t>
+          <t>b5c165d27e34d5e679129345e0a8fc19d716535f818f59946544275bbe2078df</t>
         </is>
       </c>
       <c r="U392" s="349" t="inlineStr">
@@ -60458,24 +60458,24 @@
       </c>
       <c r="X392" s="375" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>41</t>
         </is>
       </c>
       <c r="Y392" s="349" t="inlineStr">
         <is>
-          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::narrow_emergency_cabinet；对象 24；中心 (13.650, 4.327, 1.630)m；朝向 Blender +Y north；预期导出 narrow_emergency_cabinet_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
+          <t>package_id=ENV-BASE99-ART-LAYOUT-3D::south_industrial_wall_details；对象 53；中心 (4.950, 4.845, 2.618)m；朝向 Blender +Y north；预期导出 south_industrial_wall_details_visual_top3d_v001.glb；当前 not_exported；碰撞 not_authored_in_this_collection_only_pass；母版SHA-256=65ea9b7e5a75。</t>
         </is>
       </c>
     </row>
     <row r="393" ht="54" customHeight="1">
       <c r="A393" t="inlineStr">
         <is>
-          <t>BPK-BASE99-SOUTH-INDUSTRIAL-WALL-DETAILS</t>
+          <t>BPK-BASE99-SOUTH-UPPER-RAILING-DETAILS</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>基地99层 · 南墙工业墙板附着结构</t>
+          <t>基地99层 · 二层栏杆附着细节</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -60490,7 +60490,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>base99_package_south_industrial_wall_details</t>
+          <t>base99_package_south_upper_railing_details</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -60535,22 +60535,22 @@
       </c>
       <c r="N393" s="349" t="inlineStr">
         <is>
-          <t>包络 19.500×0.530×4.785m；53 网格；0 灯</t>
+          <t>包络 18.500×0.443×0.783m；26 网格；0 灯</t>
         </is>
       </c>
       <c r="O393" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/component_packages/underloft/south_industrial_wall_details/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/component_packages/underloft/south_upper_railing_details/asset_manifest.json</t>
         </is>
       </c>
       <c r="P393" s="349" t="inlineStr">
         <is>
-          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v025.blend; source/art/blender/base_facility_layout/component_packages/underloft/south_industrial_wall_details/asset_manifest.json</t>
+          <t>source/art/blender/base_facility_layout/source/base_facility_runtime_layout_hq_v026.blend; source/art/blender/base_facility_layout/component_packages/underloft/south_upper_railing_details/asset_manifest.json</t>
         </is>
       </c>
       <c r="Q393" s="349" t="inlineStr">
         <is>
-          <t>基地